--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -52559,6 +52559,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2270">
+      <c r="A2270" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2270" t="n">
+        <v>1918374</v>
+      </c>
+      <c r="C2270" t="n">
+        <v>6.36999988555908</v>
+      </c>
+      <c r="D2270" t="n">
+        <v>6.28499984741211</v>
+      </c>
+      <c r="E2270" t="n">
+        <v>6.34999990463257</v>
+      </c>
+      <c r="F2270" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="G2270" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -52582,6 +52582,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2271">
+      <c r="A2271" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2271" t="n">
+        <v>2328705</v>
+      </c>
+      <c r="C2271" t="n">
+        <v>6.32499980926514</v>
+      </c>
+      <c r="D2271" t="n">
+        <v>6.17999982833862</v>
+      </c>
+      <c r="E2271" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="F2271" t="n">
+        <v>6.30499982833862</v>
+      </c>
+      <c r="G2271" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -52605,6 +52605,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2272">
+      <c r="A2272" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2272" t="n">
+        <v>1116454</v>
+      </c>
+      <c r="C2272" t="n">
+        <v>6.35500001907349</v>
+      </c>
+      <c r="D2272" t="n">
+        <v>6.28999996185303</v>
+      </c>
+      <c r="E2272" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="F2272" t="n">
+        <v>6.31500005722046</v>
+      </c>
+      <c r="G2272" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -52628,6 +52628,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2273">
+      <c r="A2273" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2273" t="n">
+        <v>1404186</v>
+      </c>
+      <c r="C2273" t="n">
+        <v>6.41249990463257</v>
+      </c>
+      <c r="D2273" t="n">
+        <v>6.31500005722046</v>
+      </c>
+      <c r="E2273" t="n">
+        <v>6.31500005722046</v>
+      </c>
+      <c r="F2273" t="n">
+        <v>6.39499998092651</v>
+      </c>
+      <c r="G2273" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -52469,22 +52469,22 @@
     </row>
     <row r="2266">
       <c r="A2266" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2266" t="n">
-        <v>840310</v>
+        <v>851369</v>
       </c>
       <c r="C2266" t="n">
-        <v>6.6100001335144</v>
+        <v>6.61999988555908</v>
       </c>
       <c r="D2266" t="n">
-        <v>6.45499992370605</v>
+        <v>6.53499984741211</v>
       </c>
       <c r="E2266" t="n">
-        <v>6.53000020980835</v>
+        <v>6.57499980926514</v>
       </c>
       <c r="F2266" t="n">
-        <v>6.50500011444092</v>
+        <v>6.58500003814697</v>
       </c>
       <c r="G2266" t="s">
         <v>7</v>
@@ -52492,22 +52492,22 @@
     </row>
     <row r="2267">
       <c r="A2267" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2267" t="n">
-        <v>1737645</v>
+        <v>840310</v>
       </c>
       <c r="C2267" t="n">
-        <v>6.5</v>
+        <v>6.6100001335144</v>
       </c>
       <c r="D2267" t="n">
-        <v>6.30499982833862</v>
+        <v>6.45499992370605</v>
       </c>
       <c r="E2267" t="n">
-        <v>6.5</v>
+        <v>6.53000020980835</v>
       </c>
       <c r="F2267" t="n">
-        <v>6.3600001335144</v>
+        <v>6.50500011444092</v>
       </c>
       <c r="G2267" t="s">
         <v>7</v>
@@ -52515,22 +52515,22 @@
     </row>
     <row r="2268">
       <c r="A2268" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2268" t="n">
-        <v>1572225</v>
+        <v>1737645</v>
       </c>
       <c r="C2268" t="n">
-        <v>6.44999980926514</v>
+        <v>6.5</v>
       </c>
       <c r="D2268" t="n">
-        <v>6.28499984741211</v>
+        <v>6.30499982833862</v>
       </c>
       <c r="E2268" t="n">
-        <v>6.34999990463257</v>
+        <v>6.5</v>
       </c>
       <c r="F2268" t="n">
-        <v>6.28499984741211</v>
+        <v>6.3600001335144</v>
       </c>
       <c r="G2268" t="s">
         <v>7</v>
@@ -52538,22 +52538,22 @@
     </row>
     <row r="2269">
       <c r="A2269" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2269" t="n">
-        <v>1445169</v>
+        <v>1572225</v>
       </c>
       <c r="C2269" t="n">
-        <v>6.41499996185303</v>
+        <v>6.44999980926514</v>
       </c>
       <c r="D2269" t="n">
-        <v>6.30999994277954</v>
+        <v>6.28499984741211</v>
       </c>
       <c r="E2269" t="n">
-        <v>6.34000015258789</v>
+        <v>6.34999990463257</v>
       </c>
       <c r="F2269" t="n">
-        <v>6.35500001907349</v>
+        <v>6.28499984741211</v>
       </c>
       <c r="G2269" t="s">
         <v>7</v>
@@ -52561,22 +52561,22 @@
     </row>
     <row r="2270">
       <c r="A2270" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2270" t="n">
-        <v>1918374</v>
+        <v>1445169</v>
       </c>
       <c r="C2270" t="n">
-        <v>6.36999988555908</v>
+        <v>6.41499996185303</v>
       </c>
       <c r="D2270" t="n">
-        <v>6.28499984741211</v>
+        <v>6.30999994277954</v>
       </c>
       <c r="E2270" t="n">
-        <v>6.34999990463257</v>
+        <v>6.34000015258789</v>
       </c>
       <c r="F2270" t="n">
-        <v>6.30000019073486</v>
+        <v>6.35500001907349</v>
       </c>
       <c r="G2270" t="s">
         <v>7</v>
@@ -52584,22 +52584,22 @@
     </row>
     <row r="2271">
       <c r="A2271" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2271" t="n">
-        <v>2328705</v>
+        <v>1918374</v>
       </c>
       <c r="C2271" t="n">
-        <v>6.32499980926514</v>
+        <v>6.36999988555908</v>
       </c>
       <c r="D2271" t="n">
-        <v>6.17999982833862</v>
+        <v>6.28499984741211</v>
       </c>
       <c r="E2271" t="n">
+        <v>6.34999990463257</v>
+      </c>
+      <c r="F2271" t="n">
         <v>6.30000019073486</v>
-      </c>
-      <c r="F2271" t="n">
-        <v>6.30499982833862</v>
       </c>
       <c r="G2271" t="s">
         <v>7</v>
@@ -52607,22 +52607,22 @@
     </row>
     <row r="2272">
       <c r="A2272" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2272" t="n">
-        <v>1116454</v>
+        <v>2328705</v>
       </c>
       <c r="C2272" t="n">
-        <v>6.35500001907349</v>
+        <v>6.32499980926514</v>
       </c>
       <c r="D2272" t="n">
-        <v>6.28999996185303</v>
+        <v>6.17999982833862</v>
       </c>
       <c r="E2272" t="n">
         <v>6.30000019073486</v>
       </c>
       <c r="F2272" t="n">
-        <v>6.31500005722046</v>
+        <v>6.30499982833862</v>
       </c>
       <c r="G2272" t="s">
         <v>7</v>
@@ -52630,24 +52630,47 @@
     </row>
     <row r="2273">
       <c r="A2273" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2273" t="n">
-        <v>1404186</v>
+        <v>1116454</v>
       </c>
       <c r="C2273" t="n">
-        <v>6.41249990463257</v>
+        <v>6.35500001907349</v>
       </c>
       <c r="D2273" t="n">
+        <v>6.28999996185303</v>
+      </c>
+      <c r="E2273" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="F2273" t="n">
         <v>6.31500005722046</v>
       </c>
-      <c r="E2273" t="n">
-        <v>6.31500005722046</v>
-      </c>
-      <c r="F2273" t="n">
+      <c r="G2273" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2274" t="n">
+        <v>2539056</v>
+      </c>
+      <c r="C2274" t="n">
+        <v>6.42500019073486</v>
+      </c>
+      <c r="D2274" t="n">
+        <v>6.35500001907349</v>
+      </c>
+      <c r="E2274" t="n">
+        <v>6.3600001335144</v>
+      </c>
+      <c r="F2274" t="n">
         <v>6.39499998092651</v>
       </c>
-      <c r="G2273" t="s">
+      <c r="G2274" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G2" t="n">
-        <v>5.00744867324829</v>
+        <v>5.00744962692261</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>5.18545770645142</v>
+        <v>5.18545818328857</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G5" t="n">
-        <v>5.0771050453186</v>
+        <v>5.07710456848145</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G7" t="n">
-        <v>5.1119327545166</v>
+        <v>5.11193323135376</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>6.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.03066778182983</v>
+        <v>5.03066825866699</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>5.02679777145386</v>
+        <v>5.02679824829102</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>4.98423051834106</v>
+        <v>4.98423099517822</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>5.02679777145386</v>
+        <v>5.02679824829102</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>6.5</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03066778182983</v>
+        <v>5.03066825866699</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G19" t="n">
-        <v>5.10806274414062</v>
+        <v>5.10806226730347</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>6.75</v>
       </c>
       <c r="G21" t="n">
-        <v>5.22415494918823</v>
+        <v>5.22415447235107</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G23" t="n">
-        <v>5.375075340271</v>
+        <v>5.37507581710815</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>5.41764211654663</v>
+        <v>5.41764259338379</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G26" t="n">
-        <v>5.45633983612061</v>
+        <v>5.45634078979492</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G28" t="n">
-        <v>5.35185670852661</v>
+        <v>5.35185623168945</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>5.23189449310303</v>
+        <v>5.23189496994019</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G32" t="n">
-        <v>5.26285266876221</v>
+        <v>5.26285314559937</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>5.26285266876221</v>
+        <v>5.26285314559937</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>5.28994131088257</v>
+        <v>5.28994083404541</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G38" t="n">
-        <v>5.45246982574463</v>
+        <v>5.45247030258179</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G42" t="n">
-        <v>5.4640793800354</v>
+        <v>5.46407890319824</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>5.34024810791016</v>
+        <v>5.34024715423584</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>5.42925214767456</v>
+        <v>5.4292516708374</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G47" t="n">
-        <v>5.37120532989502</v>
+        <v>5.37120580673218</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G49" t="n">
-        <v>5.56469249725342</v>
+        <v>5.56469297409058</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>5.5337347984314</v>
+        <v>5.53373527526855</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>5.48342800140381</v>
+        <v>5.48342895507812</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G56" t="n">
-        <v>5.4718189239502</v>
+        <v>5.47181844711304</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>5.5337347984314</v>
+        <v>5.53373527526855</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>5.54921340942383</v>
+        <v>5.54921388626099</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>5.5956506729126</v>
+        <v>5.59565019607544</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.25</v>
       </c>
       <c r="G62" t="n">
-        <v>5.61113023757935</v>
+        <v>5.61112928390503</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G63" t="n">
-        <v>5.68078517913818</v>
+        <v>5.68078565597534</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G65" t="n">
-        <v>5.84718418121338</v>
+        <v>5.84718370437622</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G66" t="n">
-        <v>5.99036455154419</v>
+        <v>5.99036502838135</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>6.14902448654175</v>
+        <v>6.14902400970459</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>7.75</v>
       </c>
       <c r="G69" t="n">
-        <v>5.99810409545898</v>
+        <v>5.99810457229614</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>7.86499977111816</v>
       </c>
       <c r="G71" t="n">
-        <v>6.08710861206055</v>
+        <v>6.08710813522339</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G72" t="n">
-        <v>6.09097814559937</v>
+        <v>6.09097766876221</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G74" t="n">
-        <v>6.05228090286255</v>
+        <v>6.05228137969971</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G76" t="n">
-        <v>6.09097814559937</v>
+        <v>6.09097766876221</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G77" t="n">
-        <v>6.05228090286255</v>
+        <v>6.05228137969971</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G81" t="n">
-        <v>6.05228090286255</v>
+        <v>6.05228137969971</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G83" t="n">
-        <v>6.00584411621094</v>
+        <v>6.00584363937378</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G84" t="n">
-        <v>6.00584411621094</v>
+        <v>6.00584363937378</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7.76399993896484</v>
       </c>
       <c r="G85" t="n">
-        <v>6.00893974304199</v>
+        <v>6.00893878936768</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G86" t="n">
-        <v>5.88201189041138</v>
+        <v>5.88201141357422</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G87" t="n">
-        <v>5.72722244262695</v>
+        <v>5.72722196578979</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>7.28599977493286</v>
       </c>
       <c r="G88" t="n">
-        <v>5.638991355896</v>
+        <v>5.63899183273315</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G95" t="n">
-        <v>5.78139877319336</v>
+        <v>5.7813982963562</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>7.67600011825562</v>
       </c>
       <c r="G96" t="n">
-        <v>5.94083166122437</v>
+        <v>5.94083213806152</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>7.52199983596802</v>
       </c>
       <c r="G97" t="n">
-        <v>5.82164430618286</v>
+        <v>5.82164335250854</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G99" t="n">
-        <v>5.73186588287354</v>
+        <v>5.73186540603638</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>5.71174335479736</v>
+        <v>5.71174287796021</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G101" t="n">
-        <v>5.79687690734863</v>
+        <v>5.79687738418579</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G102" t="n">
-        <v>5.79687690734863</v>
+        <v>5.79687738418579</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G103" t="n">
-        <v>5.79687690734863</v>
+        <v>5.79687738418579</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>7.28800010681152</v>
       </c>
       <c r="G104" t="n">
-        <v>5.64053964614868</v>
+        <v>5.64053916931152</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>7.0479998588562</v>
       </c>
       <c r="G105" t="n">
-        <v>5.45479154586792</v>
+        <v>5.45479202270508</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>6.91200017929077</v>
       </c>
       <c r="G106" t="n">
-        <v>5.34953498840332</v>
+        <v>5.34953546524048</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>7.26599979400635</v>
       </c>
       <c r="G112" t="n">
-        <v>5.62351322174072</v>
+        <v>5.62351274490356</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G113" t="n">
-        <v>5.52754354476929</v>
+        <v>5.52754306793213</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G114" t="n">
-        <v>5.4718189239502</v>
+        <v>5.47181844711304</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>5.51051616668701</v>
+        <v>5.51051568984985</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>5.58017206192017</v>
+        <v>5.58017158508301</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>7.19799995422363</v>
       </c>
       <c r="G118" t="n">
-        <v>5.57088422775269</v>
+        <v>5.57088470458984</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G120" t="n">
-        <v>5.51051616668701</v>
+        <v>5.51051568984985</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>5.4640793800354</v>
+        <v>5.46407890319824</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G123" t="n">
-        <v>5.42538213729858</v>
+        <v>5.42538166046143</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>7.03599977493286</v>
       </c>
       <c r="G124" t="n">
-        <v>5.44550466537476</v>
+        <v>5.44550371170044</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>5.57243204116821</v>
+        <v>5.57243156433105</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>7.16800022125244</v>
       </c>
       <c r="G126" t="n">
-        <v>5.54766654968262</v>
+        <v>5.54766607284546</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G128" t="n">
-        <v>5.55540561676025</v>
+        <v>5.5554051399231</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>7.11199998855591</v>
       </c>
       <c r="G130" t="n">
-        <v>5.5043249130249</v>
+        <v>5.50432443618774</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503803253174</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>5.5337347984314</v>
+        <v>5.53373527526855</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>7.25</v>
       </c>
       <c r="G135" t="n">
-        <v>5.61113023757935</v>
+        <v>5.61112928390503</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>5.54921340942383</v>
+        <v>5.54921388626099</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>7.02199983596802</v>
       </c>
       <c r="G137" t="n">
-        <v>5.43466949462891</v>
+        <v>5.43466901779175</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G141" t="n">
-        <v>5.57243204116821</v>
+        <v>5.57243156433105</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.13600015640259</v>
       </c>
       <c r="G142" t="n">
-        <v>5.52289962768555</v>
+        <v>5.52290010452271</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>7.2519998550415</v>
       </c>
       <c r="G143" t="n">
-        <v>5.61267709732056</v>
+        <v>5.61267757415771</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>7.2039999961853</v>
       </c>
       <c r="G145" t="n">
-        <v>5.57552814483643</v>
+        <v>5.57552719116211</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.28200006484985</v>
       </c>
       <c r="G147" t="n">
-        <v>5.63589572906494</v>
+        <v>5.6358962059021</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>7.28599977493286</v>
       </c>
       <c r="G148" t="n">
-        <v>5.638991355896</v>
+        <v>5.63899183273315</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>7.26800012588501</v>
       </c>
       <c r="G150" t="n">
-        <v>5.62506055831909</v>
+        <v>5.62506103515625</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503803253174</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>7.01200008392334</v>
       </c>
       <c r="G152" t="n">
-        <v>5.42693042755127</v>
+        <v>5.42692995071411</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.14400005340576</v>
       </c>
       <c r="G154" t="n">
-        <v>5.52909135818481</v>
+        <v>5.52909088134766</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>7.4539999961853</v>
       </c>
       <c r="G155" t="n">
-        <v>5.76901483535767</v>
+        <v>5.76901531219482</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.5479998588562</v>
       </c>
       <c r="G157" t="n">
-        <v>5.84176683425903</v>
+        <v>5.84176635742188</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>5.89749145507812</v>
+        <v>5.89749050140381</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>7.28599977493286</v>
       </c>
       <c r="G162" t="n">
-        <v>5.638991355896</v>
+        <v>5.63899183273315</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G163" t="n">
-        <v>5.75044107437134</v>
+        <v>5.75044059753418</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7.20800018310547</v>
       </c>
       <c r="G165" t="n">
-        <v>5.57862424850464</v>
+        <v>5.57862329483032</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>7.26399993896484</v>
       </c>
       <c r="G166" t="n">
-        <v>5.62196445465088</v>
+        <v>5.62196493148804</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>7.36199998855591</v>
       </c>
       <c r="G169" t="n">
-        <v>5.6978120803833</v>
+        <v>5.69781255722046</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7.47599983215332</v>
       </c>
       <c r="G170" t="n">
-        <v>5.78604221343994</v>
+        <v>5.78604173660278</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>7.52400016784668</v>
       </c>
       <c r="G174" t="n">
-        <v>5.82319211959839</v>
+        <v>5.82319164276123</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>5.77365970611572</v>
+        <v>5.77365922927856</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G176" t="n">
-        <v>5.75044107437134</v>
+        <v>5.75044059753418</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>5.72722244262695</v>
+        <v>5.72722196578979</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G178" t="n">
-        <v>5.76591968536377</v>
+        <v>5.76591920852661</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>5.67304515838623</v>
+        <v>5.67304563522339</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G182" t="n">
-        <v>5.60339069366455</v>
+        <v>5.60339021682739</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>7.25</v>
       </c>
       <c r="G184" t="n">
-        <v>5.61113023757935</v>
+        <v>5.61112928390503</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.2519998550415</v>
       </c>
       <c r="G185" t="n">
-        <v>5.61267709732056</v>
+        <v>5.61267757415771</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>7.12400007247925</v>
       </c>
       <c r="G187" t="n">
-        <v>5.51361227035522</v>
+        <v>5.51361179351807</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>7.24200010299683</v>
       </c>
       <c r="G190" t="n">
-        <v>5.60493755340576</v>
+        <v>5.60493803024292</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G191" t="n">
-        <v>5.55540561676025</v>
+        <v>5.5554051399231</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>7.2960000038147</v>
       </c>
       <c r="G192" t="n">
-        <v>5.64673137664795</v>
+        <v>5.64673185348511</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7.13600015640259</v>
       </c>
       <c r="G193" t="n">
-        <v>5.52289962768555</v>
+        <v>5.52290010452271</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G194" t="n">
-        <v>5.56469249725342</v>
+        <v>5.56469297409058</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7.15799999237061</v>
       </c>
       <c r="G195" t="n">
-        <v>5.53992748260498</v>
+        <v>5.53992652893066</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7</v>
       </c>
       <c r="G196" t="n">
-        <v>5.41764211654663</v>
+        <v>5.41764259338379</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="n">
-        <v>5.41764211654663</v>
+        <v>5.41764259338379</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>5.38668441772461</v>
+        <v>5.38668489456177</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.0460000038147</v>
       </c>
       <c r="G201" t="n">
-        <v>5.45324468612671</v>
+        <v>5.45324420928955</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.13199996948242</v>
       </c>
       <c r="G202" t="n">
-        <v>5.51980352401733</v>
+        <v>5.51980400085449</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G203" t="n">
-        <v>5.52754354476929</v>
+        <v>5.52754306793213</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G204" t="n">
-        <v>5.4718189239502</v>
+        <v>5.47181844711304</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.13399982452393</v>
       </c>
       <c r="G205" t="n">
-        <v>5.52135181427002</v>
+        <v>5.52135133743286</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>5.5337347984314</v>
+        <v>5.53373527526855</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>7.44600009918213</v>
       </c>
       <c r="G207" t="n">
-        <v>5.76282405853271</v>
+        <v>5.76282358169556</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>7.46600008010864</v>
       </c>
       <c r="G208" t="n">
-        <v>5.7783031463623</v>
+        <v>5.77830219268799</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>7.52199983596802</v>
       </c>
       <c r="G209" t="n">
-        <v>5.82164430618286</v>
+        <v>5.82164335250854</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>7.47200012207031</v>
       </c>
       <c r="G210" t="n">
-        <v>5.78294658660889</v>
+        <v>5.78294610977173</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7.19799995422363</v>
       </c>
       <c r="G212" t="n">
-        <v>5.57088422775269</v>
+        <v>5.57088470458984</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>5.51825523376465</v>
+        <v>5.51825571060181</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>7.20800018310547</v>
       </c>
       <c r="G214" t="n">
-        <v>5.57862424850464</v>
+        <v>5.57862329483032</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.66599988937378</v>
       </c>
       <c r="G216" t="n">
-        <v>5.93309211730957</v>
+        <v>5.93309259414673</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.66599988937378</v>
       </c>
       <c r="G217" t="n">
-        <v>5.93309211730957</v>
+        <v>5.93309259414673</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>5.88201189041138</v>
+        <v>5.88201141357422</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>7.62200021743774</v>
       </c>
       <c r="G220" t="n">
-        <v>5.89903879165649</v>
+        <v>5.89903926849365</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>7.63800001144409</v>
       </c>
       <c r="G221" t="n">
-        <v>5.91142177581787</v>
+        <v>5.91142225265503</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>7.57800006866455</v>
       </c>
       <c r="G223" t="n">
-        <v>5.86498498916626</v>
+        <v>5.8649845123291</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>7.25</v>
       </c>
       <c r="G225" t="n">
-        <v>5.61113023757935</v>
+        <v>5.61112928390503</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>7.1560001373291</v>
       </c>
       <c r="G227" t="n">
-        <v>5.53837823867798</v>
+        <v>5.53837871551514</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G229" t="n">
-        <v>5.62041664123535</v>
+        <v>5.62041711807251</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.25</v>
       </c>
       <c r="G230" t="n">
-        <v>5.61113023757935</v>
+        <v>5.61112928390503</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>6.93800020217896</v>
       </c>
       <c r="G232" t="n">
-        <v>5.36965799331665</v>
+        <v>5.36965847015381</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>6.92799997329712</v>
       </c>
       <c r="G234" t="n">
-        <v>5.3619179725647</v>
+        <v>5.36191844940186</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>6.92799997329712</v>
       </c>
       <c r="G235" t="n">
-        <v>5.3619179725647</v>
+        <v>5.36191844940186</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>6.67199993133545</v>
       </c>
       <c r="G237" t="n">
-        <v>5.16378784179688</v>
+        <v>5.16378736495972</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G238" t="n">
-        <v>5.36346673965454</v>
+        <v>5.36346578598022</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7.01200008392334</v>
       </c>
       <c r="G239" t="n">
-        <v>5.42693042755127</v>
+        <v>5.42692995071411</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503803253174</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G244" t="n">
-        <v>5.55695295333862</v>
+        <v>5.55695343017578</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>7.18800020217896</v>
       </c>
       <c r="G245" t="n">
-        <v>5.56314563751221</v>
+        <v>5.56314468383789</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7.20599985122681</v>
       </c>
       <c r="G246" t="n">
-        <v>5.57707548141479</v>
+        <v>5.57707643508911</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>5.51051616668701</v>
+        <v>5.51051568984985</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>7.10599994659424</v>
       </c>
       <c r="G248" t="n">
-        <v>5.499680519104</v>
+        <v>5.49968147277832</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G253" t="n">
-        <v>5.5662407875061</v>
+        <v>5.56624031066895</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G255" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503803253174</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>5.25511264801025</v>
+        <v>5.25511312484741</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>6.56599998474121</v>
       </c>
       <c r="G258" t="n">
-        <v>5.08174848556519</v>
+        <v>5.08174896240234</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>4.87587833404541</v>
+        <v>4.87587738037109</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G263" t="n">
-        <v>4.84646797180176</v>
+        <v>4.84646844863892</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>4.78300428390503</v>
+        <v>4.78300380706787</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G268" t="n">
-        <v>4.5709433555603</v>
+        <v>4.57094287872314</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G271" t="n">
-        <v>4.75204658508301</v>
+        <v>4.75204610824585</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>6.2480001449585</v>
       </c>
       <c r="G272" t="n">
-        <v>4.83563280105591</v>
+        <v>4.83563327789307</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>6.53800010681152</v>
       </c>
       <c r="G274" t="n">
-        <v>5.06007766723633</v>
+        <v>5.06007814407349</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G275" t="n">
-        <v>5.02602434158325</v>
+        <v>5.02602481842041</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G277" t="n">
-        <v>4.94088983535767</v>
+        <v>4.94088888168335</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.34600019454956</v>
       </c>
       <c r="G278" t="n">
-        <v>4.91147994995117</v>
+        <v>4.91148042678833</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>5.01518869400024</v>
+        <v>5.0151891708374</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>6.2020001411438</v>
       </c>
       <c r="G286" t="n">
-        <v>4.80003118515015</v>
+        <v>4.80003070831299</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G287" t="n">
-        <v>4.80467510223389</v>
+        <v>4.80467557907104</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>6.23400020599365</v>
       </c>
       <c r="G289" t="n">
-        <v>4.82479763031006</v>
+        <v>4.82479810714722</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G290" t="n">
-        <v>4.93005514144897</v>
+        <v>4.9300537109375</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.42399978637695</v>
       </c>
       <c r="G292" t="n">
-        <v>4.97184753417969</v>
+        <v>4.97184801101685</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G293" t="n">
-        <v>5.02602434158325</v>
+        <v>5.02602481842041</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.40799999237061</v>
       </c>
       <c r="G294" t="n">
-        <v>4.95946502685547</v>
+        <v>4.95946455001831</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G295" t="n">
-        <v>4.79848289489746</v>
+        <v>4.79848384857178</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>6.24399995803833</v>
       </c>
       <c r="G296" t="n">
-        <v>4.83253717422485</v>
+        <v>4.8325366973877</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G297" t="n">
-        <v>4.80467510223389</v>
+        <v>4.80467557907104</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>6.22599983215332</v>
       </c>
       <c r="G299" t="n">
-        <v>4.81860589981079</v>
+        <v>4.81860542297363</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>6.20599985122681</v>
       </c>
       <c r="G300" t="n">
-        <v>4.8031268119812</v>
+        <v>4.80312728881836</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>6.00400018692017</v>
       </c>
       <c r="G301" t="n">
-        <v>4.64678955078125</v>
+        <v>4.64678907394409</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.95800018310547</v>
       </c>
       <c r="G302" t="n">
-        <v>4.61118793487549</v>
+        <v>4.61118745803833</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G304" t="n">
-        <v>4.55855941772461</v>
+        <v>4.55855894088745</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>4.58487272262573</v>
+        <v>4.58487319946289</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.00799989700317</v>
       </c>
       <c r="G306" t="n">
-        <v>4.6498851776123</v>
+        <v>4.64988470077515</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G309" t="n">
-        <v>4.38674306869507</v>
+        <v>4.38674163818359</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>4.34804582595825</v>
+        <v>4.34804487228394</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G314" t="n">
-        <v>4.34185361862183</v>
+        <v>4.34185409545898</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>5.55399990081787</v>
       </c>
       <c r="G315" t="n">
-        <v>4.29851198196411</v>
+        <v>4.29851245880127</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.44600009918213</v>
       </c>
       <c r="G316" t="n">
-        <v>4.21492576599121</v>
+        <v>4.21492671966553</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.63800001144409</v>
       </c>
       <c r="G318" t="n">
-        <v>4.36352443695068</v>
+        <v>4.36352396011353</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G319" t="n">
-        <v>4.48116445541382</v>
+        <v>4.48116397857666</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>6.0460000038147</v>
       </c>
       <c r="G323" t="n">
-        <v>4.6792950630188</v>
+        <v>4.67929553985596</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>5.95800018310547</v>
       </c>
       <c r="G326" t="n">
-        <v>4.61118793487549</v>
+        <v>4.61118745803833</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>4.72108840942383</v>
+        <v>4.72108888626099</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>6.02799987792969</v>
       </c>
       <c r="G329" t="n">
-        <v>4.66536426544189</v>
+        <v>4.66536378860474</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G331" t="n">
-        <v>4.71489715576172</v>
+        <v>4.71489667892456</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>4.55855941772461</v>
+        <v>4.55855894088745</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G336" t="n">
-        <v>4.41460466384888</v>
+        <v>4.41460514068604</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>5.69799995422363</v>
       </c>
       <c r="G337" t="n">
-        <v>4.40996074676514</v>
+        <v>4.40996122360229</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.77600002288818</v>
       </c>
       <c r="G338" t="n">
-        <v>4.47032928466797</v>
+        <v>4.47032880783081</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.98199987411499</v>
       </c>
       <c r="G339" t="n">
-        <v>4.62976264953613</v>
+        <v>4.62976217269897</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G340" t="n">
-        <v>4.68239116668701</v>
+        <v>4.68239164352417</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G341" t="n">
-        <v>4.49199962615967</v>
+        <v>4.49200010299683</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G342" t="n">
-        <v>4.34804582595825</v>
+        <v>4.34804487228394</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G345" t="n">
-        <v>4.71489715576172</v>
+        <v>4.71489667892456</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.07399988174438</v>
       </c>
       <c r="G347" t="n">
-        <v>4.7009654045105</v>
+        <v>4.70096588134766</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G349" t="n">
-        <v>4.55855941772461</v>
+        <v>4.55855894088745</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G351" t="n">
-        <v>4.72108840942383</v>
+        <v>4.72108888626099</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>6.05800008773804</v>
       </c>
       <c r="G353" t="n">
-        <v>4.68858289718628</v>
+        <v>4.68858242034912</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G354" t="n">
-        <v>4.69477415084839</v>
+        <v>4.69477462768555</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>4.5662989616394</v>
+        <v>4.56629848480225</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>6.07600021362305</v>
       </c>
       <c r="G357" t="n">
-        <v>4.70251369476318</v>
+        <v>4.70251321792603</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>6.15399980545044</v>
       </c>
       <c r="G358" t="n">
-        <v>4.76288175582886</v>
+        <v>4.7628812789917</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>4.72108840942383</v>
+        <v>4.72108888626099</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G360" t="n">
-        <v>4.67465162277222</v>
+        <v>4.67465209960938</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G363" t="n">
-        <v>4.49509572982788</v>
+        <v>4.49509525299072</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.80600023269653</v>
       </c>
       <c r="G365" t="n">
-        <v>4.49354696273804</v>
+        <v>4.4935474395752</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>4.61273527145386</v>
+        <v>4.61273574829102</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G371" t="n">
-        <v>4.68548679351807</v>
+        <v>4.68548631668091</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.93400001525879</v>
       </c>
       <c r="G372" t="n">
-        <v>4.59261226654053</v>
+        <v>4.59261322021484</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>5.84600019454956</v>
       </c>
       <c r="G373" t="n">
-        <v>4.52450513839722</v>
+        <v>4.52450561523438</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.73799991607666</v>
       </c>
       <c r="G377" t="n">
-        <v>4.44091844558716</v>
+        <v>4.44091892242432</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G379" t="n">
-        <v>4.64059782028198</v>
+        <v>4.64059686660767</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G380" t="n">
-        <v>4.79848289489746</v>
+        <v>4.79848384857178</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.26800012588501</v>
       </c>
       <c r="G383" t="n">
-        <v>4.8511118888855</v>
+        <v>4.85111141204834</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G385" t="n">
-        <v>4.84492111206055</v>
+        <v>4.84492063522339</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G386" t="n">
-        <v>4.91612339019775</v>
+        <v>4.91612386703491</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.60200023651123</v>
       </c>
       <c r="G387" t="n">
-        <v>5.10961151123047</v>
+        <v>5.10961103439331</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G389" t="n">
-        <v>5.02757167816162</v>
+        <v>5.02757215499878</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.5</v>
       </c>
       <c r="G390" t="n">
-        <v>5.03066778182983</v>
+        <v>5.03066825866699</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>4.98423051834106</v>
+        <v>4.98423099517822</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>6.44199991226196</v>
       </c>
       <c r="G393" t="n">
-        <v>4.98577928543091</v>
+        <v>4.98577880859375</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G395" t="n">
-        <v>5.02602434158325</v>
+        <v>5.02602481842041</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.50799989700317</v>
       </c>
       <c r="G397" t="n">
-        <v>5.03685998916626</v>
+        <v>5.0368595123291</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>6.17799997329712</v>
       </c>
       <c r="G399" t="n">
-        <v>4.78145694732666</v>
+        <v>4.7814564704895</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>4.5662989616394</v>
+        <v>4.56629848480225</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>5.77799987792969</v>
       </c>
       <c r="G403" t="n">
-        <v>4.47187662124634</v>
+        <v>4.4718770980835</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>5.72800016403198</v>
       </c>
       <c r="G404" t="n">
-        <v>4.43317890167236</v>
+        <v>4.43317985534668</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G405" t="n">
-        <v>4.34185361862183</v>
+        <v>4.34185409545898</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G409" t="n">
-        <v>4.48271226882935</v>
+        <v>4.48271179199219</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G410" t="n">
-        <v>4.3749361038208</v>
+        <v>4.37493562698364</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G414" t="n">
-        <v>4.25039339065552</v>
+        <v>4.25039386749268</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G416" t="n">
-        <v>4.14660835266113</v>
+        <v>4.14660882949829</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G420" t="n">
-        <v>4.08114433288574</v>
+        <v>4.08114385604858</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G425" t="n">
-        <v>4.18971872329712</v>
+        <v>4.18971967697144</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.32800006866455</v>
       </c>
       <c r="G426" t="n">
-        <v>4.253586769104</v>
+        <v>4.25358724594116</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G427" t="n">
-        <v>4.13223886489868</v>
+        <v>4.13223838806152</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.25</v>
       </c>
       <c r="G428" t="n">
-        <v>4.19131565093994</v>
+        <v>4.1913161277771</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.29199981689453</v>
       </c>
       <c r="G429" t="n">
-        <v>4.22484636306763</v>
+        <v>4.22484683990479</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5.19600009918213</v>
       </c>
       <c r="G438" t="n">
-        <v>4.14820575714111</v>
+        <v>4.14820623397827</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>5.30600023269653</v>
       </c>
       <c r="G440" t="n">
-        <v>4.23602390289307</v>
+        <v>4.23602342605591</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5.25</v>
       </c>
       <c r="G442" t="n">
-        <v>4.19131565093994</v>
+        <v>4.1913161277771</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G445" t="n">
-        <v>4.36056518554688</v>
+        <v>4.36056566238403</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G446" t="n">
-        <v>4.25039339065552</v>
+        <v>4.25039386749268</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>5.39400005340576</v>
       </c>
       <c r="G447" t="n">
-        <v>4.30627775192261</v>
+        <v>4.30627822875977</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54737854003906</v>
+        <v>4.5473780632019</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>5.55399990081787</v>
       </c>
       <c r="G451" t="n">
-        <v>4.43401288986206</v>
+        <v>4.43401336669922</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G453" t="n">
-        <v>4.1513991355896</v>
+        <v>4.15139865875244</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G454" t="n">
-        <v>4.14022207260132</v>
+        <v>4.14022159576416</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5.68200016021729</v>
       </c>
       <c r="G456" t="n">
-        <v>4.53620100021362</v>
+        <v>4.53620147705078</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G458" t="n">
-        <v>4.55057096481323</v>
+        <v>4.55057191848755</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.60799980163574</v>
       </c>
       <c r="G459" t="n">
-        <v>4.47712373733521</v>
+        <v>4.47712421417236</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.31400012969971</v>
       </c>
       <c r="G461" t="n">
-        <v>4.24241018295288</v>
+        <v>4.24241065979004</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.38800001144409</v>
       </c>
       <c r="G463" t="n">
-        <v>4.30148792266846</v>
+        <v>4.30148839950562</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>3.87197756767273</v>
+        <v>3.87197804450989</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G466" t="n">
-        <v>3.76819252967834</v>
+        <v>3.76819229125977</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>4.85699987411499</v>
       </c>
       <c r="G468" t="n">
-        <v>3.87756562232971</v>
+        <v>3.87756609916687</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G470" t="n">
-        <v>3.67398762702942</v>
+        <v>3.673987865448</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.75299978256226</v>
       </c>
       <c r="G471" t="n">
-        <v>3.79453802108765</v>
+        <v>3.79453825950623</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G472" t="n">
-        <v>3.64444923400879</v>
+        <v>3.64444875717163</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G474" t="n">
-        <v>3.67957663536072</v>
+        <v>3.6795768737793</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G476" t="n">
-        <v>3.74264574050903</v>
+        <v>3.74264621734619</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.81300020217896</v>
       </c>
       <c r="G477" t="n">
-        <v>3.8424391746521</v>
+        <v>3.84243869781494</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.6729998588562</v>
       </c>
       <c r="G478" t="n">
-        <v>3.73066997528076</v>
+        <v>3.73067045211792</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.74100017547607</v>
       </c>
       <c r="G479" t="n">
-        <v>3.78495860099792</v>
+        <v>3.78495788574219</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.82407689094543</v>
+        <v>3.82407736778259</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>3.77218413352966</v>
+        <v>3.77218437194824</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>3.76020979881287</v>
+        <v>3.76020956039429</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.6729998588562</v>
       </c>
       <c r="G485" t="n">
-        <v>3.73066997528076</v>
+        <v>3.73067045211792</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G487" t="n">
-        <v>4.0683708190918</v>
+        <v>4.06837034225464</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G489" t="n">
-        <v>4.27274751663208</v>
+        <v>4.27274799346924</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G491" t="n">
-        <v>4.26316738128662</v>
+        <v>4.26316690444946</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>4.55057096481323</v>
+        <v>4.55057191848755</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G495" t="n">
-        <v>4.49468755722046</v>
+        <v>4.49468803405762</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G496" t="n">
-        <v>4.52183151245117</v>
+        <v>4.52183103561401</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G498" t="n">
-        <v>4.52183151245117</v>
+        <v>4.52183103561401</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G504" t="n">
-        <v>4.333420753479</v>
+        <v>4.33342123031616</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.25</v>
       </c>
       <c r="G506" t="n">
-        <v>4.19131565093994</v>
+        <v>4.1913161277771</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5.11800003051758</v>
       </c>
       <c r="G508" t="n">
-        <v>4.08593463897705</v>
+        <v>4.08593416213989</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.12200021743774</v>
       </c>
       <c r="G509" t="n">
-        <v>4.08912801742554</v>
+        <v>4.0891284942627</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G510" t="n">
-        <v>4.01727676391602</v>
+        <v>4.01727628707886</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G514" t="n">
-        <v>4.333420753479</v>
+        <v>4.33342123031616</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G515" t="n">
-        <v>4.48510694503784</v>
+        <v>4.485107421875</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.4539999961853</v>
       </c>
       <c r="G519" t="n">
-        <v>4.35417890548706</v>
+        <v>4.3541784286499</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G520" t="n">
-        <v>4.40048265457153</v>
+        <v>4.40048313140869</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G521" t="n">
-        <v>4.31266403198242</v>
+        <v>4.31266450881958</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.4539999961853</v>
       </c>
       <c r="G522" t="n">
-        <v>4.35417890548706</v>
+        <v>4.3541784286499</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G525" t="n">
-        <v>4.63679265975952</v>
+        <v>4.63679361343384</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G529" t="n">
-        <v>4.32703495025635</v>
+        <v>4.32703447341919</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G530" t="n">
-        <v>4.28552055358887</v>
+        <v>4.28552103042603</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.28711795806885</v>
+        <v>4.28711748123169</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>4.3749361038208</v>
+        <v>4.37493562698364</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.4980001449585</v>
       </c>
       <c r="G534" t="n">
-        <v>4.38930559158325</v>
+        <v>4.38930606842041</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G536" t="n">
-        <v>4.28073072433472</v>
+        <v>4.28073120117188</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.27600002288818</v>
       </c>
       <c r="G539" t="n">
-        <v>4.21207284927368</v>
+        <v>4.21207332611084</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G543" t="n">
-        <v>4.13543176651001</v>
+        <v>4.13543128967285</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.27600002288818</v>
       </c>
       <c r="G544" t="n">
-        <v>4.21207284927368</v>
+        <v>4.21207332611084</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.26399993896484</v>
       </c>
       <c r="G547" t="n">
-        <v>4.20249271392822</v>
+        <v>4.20249223709106</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G550" t="n">
-        <v>4.03164720535278</v>
+        <v>4.03164768218994</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.07800006866455</v>
       </c>
       <c r="G552" t="n">
-        <v>4.05400085449219</v>
+        <v>4.05400133132935</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.14200019836426</v>
       </c>
       <c r="G553" t="n">
-        <v>4.10509538650513</v>
+        <v>4.10509443283081</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>4.07156419754028</v>
+        <v>4.07156372070312</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G555" t="n">
-        <v>4.10669183731079</v>
+        <v>4.10669136047363</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G560" t="n">
-        <v>4.20089673995972</v>
+        <v>4.20089626312256</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G561" t="n">
-        <v>4.16576910018921</v>
+        <v>4.16576862335205</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G562" t="n">
-        <v>4.098708152771</v>
+        <v>4.09870767593384</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G563" t="n">
-        <v>4.15778589248657</v>
+        <v>4.15778541564941</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G565" t="n">
-        <v>4.15299606323242</v>
+        <v>4.15299558639526</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G566" t="n">
-        <v>4.10349750518799</v>
+        <v>4.10349798202515</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G570" t="n">
-        <v>4.16576910018921</v>
+        <v>4.16576862335205</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G575" t="n">
-        <v>4.06358098983765</v>
+        <v>4.06358051300049</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.02799987792969</v>
       </c>
       <c r="G576" t="n">
-        <v>4.01408338546753</v>
+        <v>4.01408290863037</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.03800010681152</v>
       </c>
       <c r="G581" t="n">
-        <v>4.02206611633301</v>
+        <v>4.02206659317017</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.78900003433228</v>
       </c>
       <c r="G583" t="n">
-        <v>3.82327890396118</v>
+        <v>3.82327842712402</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G584" t="n">
-        <v>3.64524745941162</v>
+        <v>3.64524722099304</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.58300018310547</v>
       </c>
       <c r="G585" t="n">
-        <v>3.65881943702698</v>
+        <v>3.65881967544556</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G586" t="n">
-        <v>3.75302386283875</v>
+        <v>3.75302457809448</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G588" t="n">
-        <v>3.49036884307861</v>
+        <v>3.49036860466003</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.36299991607666</v>
       </c>
       <c r="G590" t="n">
-        <v>3.48318314552307</v>
+        <v>3.48318338394165</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G591" t="n">
-        <v>3.68037533760071</v>
+        <v>3.68037438392639</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.59299993515015</v>
       </c>
       <c r="G592" t="n">
-        <v>3.66680264472961</v>
+        <v>3.66680240631104</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.50899982452393</v>
       </c>
       <c r="G594" t="n">
-        <v>3.59974145889282</v>
+        <v>3.5997416973114</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.45100021362305</v>
       </c>
       <c r="G595" t="n">
-        <v>3.55343818664551</v>
+        <v>3.55343747138977</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G596" t="n">
-        <v>3.67957663536072</v>
+        <v>3.6795768737793</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G597" t="n">
-        <v>3.60054016113281</v>
+        <v>3.60053992271423</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>3.60852360725403</v>
+        <v>3.60852384567261</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G599" t="n">
-        <v>3.76819252967834</v>
+        <v>3.76819229125977</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.70900011062622</v>
       </c>
       <c r="G600" t="n">
-        <v>3.75941109657288</v>
+        <v>3.75941133499146</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.86600017547607</v>
       </c>
       <c r="G601" t="n">
-        <v>3.88475131988525</v>
+        <v>3.88475179672241</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G602" t="n">
-        <v>3.86798572540283</v>
+        <v>3.86798620223999</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.75299978256226</v>
       </c>
       <c r="G603" t="n">
-        <v>3.79453802108765</v>
+        <v>3.79453825950623</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.36100006103516</v>
       </c>
       <c r="G605" t="n">
-        <v>3.48158693313599</v>
+        <v>3.48158645629883</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G606" t="n">
-        <v>3.55742931365967</v>
+        <v>3.55742907524109</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.25299978256226</v>
       </c>
       <c r="G608" t="n">
-        <v>3.39536499977112</v>
+        <v>3.3953652381897</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.01399993896484</v>
       </c>
       <c r="G610" t="n">
-        <v>3.20456051826477</v>
+        <v>3.20456027984619</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>3.12951588630676</v>
+        <v>3.12951564788818</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G614" t="n">
-        <v>2.97304034233093</v>
+        <v>2.97304010391235</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>2.95228290557861</v>
+        <v>2.95228314399719</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.81299996376038</v>
       </c>
       <c r="G616" t="n">
-        <v>3.04409289360046</v>
+        <v>3.04409265518188</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G620" t="n">
-        <v>2.68004727363586</v>
+        <v>2.68004775047302</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G622" t="n">
-        <v>3.04169797897339</v>
+        <v>3.04169774055481</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G624" t="n">
-        <v>2.76866340637207</v>
+        <v>2.76866364479065</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.45300006866455</v>
       </c>
       <c r="G626" t="n">
-        <v>2.75668835639954</v>
+        <v>2.75668859481812</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>3.38100004196167</v>
       </c>
       <c r="G627" t="n">
-        <v>2.69920754432678</v>
+        <v>2.6992073059082</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G628" t="n">
-        <v>2.65450024604797</v>
+        <v>2.65450048446655</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>3.34100008010864</v>
       </c>
       <c r="G629" t="n">
-        <v>2.66727375984192</v>
+        <v>2.66727352142334</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>2.52676463127136</v>
+        <v>2.52676486968994</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>2.52676463127136</v>
+        <v>2.52676486968994</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G634" t="n">
-        <v>2.55790042877197</v>
+        <v>2.55790019035339</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G637" t="n">
-        <v>2.69681262969971</v>
+        <v>2.69681239128113</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G638" t="n">
-        <v>2.64731526374817</v>
+        <v>2.64731478691101</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G639" t="n">
-        <v>2.49083924293518</v>
+        <v>2.4908390045166</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.28600001335144</v>
       </c>
       <c r="G640" t="n">
-        <v>2.62336468696594</v>
+        <v>2.62336444854736</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>2.71437621116638</v>
+        <v>2.7143759727478</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G643" t="n">
-        <v>2.65689516067505</v>
+        <v>2.65689539909363</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G645" t="n">
-        <v>2.64731526374817</v>
+        <v>2.64731478691101</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G646" t="n">
-        <v>2.68004727363586</v>
+        <v>2.68004775047302</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G648" t="n">
-        <v>2.73513293266296</v>
+        <v>2.73513317108154</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G653" t="n">
-        <v>2.95387983322144</v>
+        <v>2.95388007164001</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>2.95387983322144</v>
+        <v>2.95388007164001</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>3.66899991035461</v>
       </c>
       <c r="G655" t="n">
-        <v>2.92913126945496</v>
+        <v>2.92913103103638</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.60700011253357</v>
       </c>
       <c r="G656" t="n">
-        <v>2.87963390350342</v>
+        <v>2.87963366508484</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>2.90997076034546</v>
+        <v>2.90997099876404</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G658" t="n">
-        <v>2.87005376815796</v>
+        <v>2.87005352973938</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.59699988365173</v>
       </c>
       <c r="G660" t="n">
-        <v>2.87164998054504</v>
+        <v>2.87165021896362</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.45099997520447</v>
       </c>
       <c r="G662" t="n">
-        <v>2.75509190559387</v>
+        <v>2.75509166717529</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G666" t="n">
-        <v>2.89320588111877</v>
+        <v>2.8932056427002</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>2.95387983322144</v>
+        <v>2.95388007164001</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G668" t="n">
-        <v>3.05127787590027</v>
+        <v>3.05127811431885</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G671" t="n">
-        <v>3.21094703674316</v>
+        <v>3.21094727516174</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G676" t="n">
-        <v>3.47919154167175</v>
+        <v>3.47919130325317</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G677" t="n">
-        <v>3.38498616218567</v>
+        <v>3.38498640060425</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G684" t="n">
-        <v>3.14069247245789</v>
+        <v>3.14069271087646</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.01100015640259</v>
       </c>
       <c r="G687" t="n">
-        <v>3.20216536521912</v>
+        <v>3.2021656036377</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G688" t="n">
-        <v>3.04010152816772</v>
+        <v>3.04010128974915</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>3.04010152816772</v>
+        <v>3.04010128974915</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G691" t="n">
-        <v>3.09758234024048</v>
+        <v>3.0975821018219</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G693" t="n">
-        <v>2.93791317939758</v>
+        <v>2.937912940979</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G694" t="n">
-        <v>3.05447125434875</v>
+        <v>3.05447149276733</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.78099989891052</v>
       </c>
       <c r="G697" t="n">
-        <v>3.01854562759399</v>
+        <v>3.01854586601257</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>3.75</v>
       </c>
       <c r="G698" t="n">
-        <v>2.99379706382751</v>
+        <v>2.99379730224609</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.64100003242493</v>
       </c>
       <c r="G699" t="n">
-        <v>2.90677762031555</v>
+        <v>2.90677738189697</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G702" t="n">
-        <v>2.96026659011841</v>
+        <v>2.96026682853699</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G703" t="n">
-        <v>3.05287480354309</v>
+        <v>3.05287456512451</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G706" t="n">
-        <v>2.98581385612488</v>
+        <v>2.9858136177063</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G707" t="n">
-        <v>3.09758234024048</v>
+        <v>3.0975821018219</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>3.76699995994568</v>
       </c>
       <c r="G708" t="n">
-        <v>3.00736880302429</v>
+        <v>3.00736904144287</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>3.78099989891052</v>
       </c>
       <c r="G709" t="n">
-        <v>3.01854562759399</v>
+        <v>3.01854586601257</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G711" t="n">
-        <v>2.90997076034546</v>
+        <v>2.90997099876404</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G714" t="n">
-        <v>2.7734534740448</v>
+        <v>2.77345323562622</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.46399998664856</v>
       </c>
       <c r="G716" t="n">
-        <v>2.76547002792358</v>
+        <v>2.76547050476074</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>2.89001226425171</v>
+        <v>2.89001202583313</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G718" t="n">
-        <v>2.94908976554871</v>
+        <v>2.94909000396729</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G719" t="n">
-        <v>2.80858087539673</v>
+        <v>2.80858039855957</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>3.5</v>
       </c>
       <c r="G721" t="n">
-        <v>2.79421091079712</v>
+        <v>2.79421043395996</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G722" t="n">
-        <v>2.9682502746582</v>
+        <v>2.96825003623962</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G723" t="n">
-        <v>2.996990442276</v>
+        <v>2.99699068069458</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G724" t="n">
-        <v>2.98581385612488</v>
+        <v>2.9858136177063</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G727" t="n">
-        <v>2.96345996856689</v>
+        <v>2.96346020698547</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G730" t="n">
-        <v>2.85488486289978</v>
+        <v>2.85488510131836</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G733" t="n">
-        <v>2.95068693161011</v>
+        <v>2.95068645477295</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>2.96186351776123</v>
+        <v>2.96186327934265</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G735" t="n">
-        <v>2.90757584571838</v>
+        <v>2.9075756072998</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>3.62100005149841</v>
       </c>
       <c r="G736" t="n">
-        <v>2.89081025123596</v>
+        <v>2.89081072807312</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G737" t="n">
-        <v>2.85408639907837</v>
+        <v>2.85408663749695</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G738" t="n">
-        <v>2.87085175514221</v>
+        <v>2.87085151672363</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G740" t="n">
-        <v>2.95228290557861</v>
+        <v>2.95228314399719</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G742" t="n">
-        <v>3.0448911190033</v>
+        <v>3.04489135742188</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G743" t="n">
-        <v>3.07522821426392</v>
+        <v>3.0752284526825</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G746" t="n">
-        <v>3.08321189880371</v>
+        <v>3.08321213722229</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G747" t="n">
-        <v>3.06165671348572</v>
+        <v>3.06165647506714</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G754" t="n">
-        <v>2.98980522155762</v>
+        <v>2.9898054599762</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G757" t="n">
-        <v>2.97304034233093</v>
+        <v>2.97304010391235</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.53299999237061</v>
       </c>
       <c r="G760" t="n">
-        <v>2.82055616378784</v>
+        <v>2.82055568695068</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.62100005149841</v>
       </c>
       <c r="G761" t="n">
-        <v>2.89081025123596</v>
+        <v>2.89081072807312</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.82699990272522</v>
       </c>
       <c r="G763" t="n">
-        <v>3.05526947975159</v>
+        <v>3.05526971817017</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>3.8529999256134</v>
       </c>
       <c r="G765" t="n">
-        <v>3.07602691650391</v>
+        <v>3.07602667808533</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G766" t="n">
-        <v>3.11674213409424</v>
+        <v>3.1167426109314</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G768" t="n">
-        <v>3.06884145736694</v>
+        <v>3.06884169578552</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G770" t="n">
-        <v>2.93950963020325</v>
+        <v>2.93950986862183</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G772" t="n">
-        <v>3.06964015960693</v>
+        <v>3.06963992118835</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.78299999237061</v>
       </c>
       <c r="G774" t="n">
-        <v>3.02014255523682</v>
+        <v>3.02014231681824</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G775" t="n">
-        <v>3.28120183944702</v>
+        <v>3.2812020778656</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.94300007820129</v>
       </c>
       <c r="G776" t="n">
-        <v>3.14787793159485</v>
+        <v>3.14787769317627</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G777" t="n">
-        <v>3.00577235221863</v>
+        <v>3.00577211380005</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G778" t="n">
-        <v>2.79261374473572</v>
+        <v>2.7926139831543</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G780" t="n">
-        <v>2.85807800292969</v>
+        <v>2.85807824134827</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.69099998474121</v>
       </c>
       <c r="G785" t="n">
-        <v>2.94669485092163</v>
+        <v>2.94669461250305</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G786" t="n">
-        <v>3.36582636833191</v>
+        <v>3.36582660675049</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.27899980545044</v>
       </c>
       <c r="G788" t="n">
-        <v>3.4161217212677</v>
+        <v>3.41612219810486</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G790" t="n">
-        <v>3.33708548545837</v>
+        <v>3.33708596229553</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.26300001144409</v>
       </c>
       <c r="G792" t="n">
-        <v>3.40334892272949</v>
+        <v>3.40334844589233</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G794" t="n">
-        <v>3.34666585922241</v>
+        <v>3.34666609764099</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G795" t="n">
-        <v>3.33708548545837</v>
+        <v>3.33708596229553</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G796" t="n">
-        <v>3.31792545318604</v>
+        <v>3.31792569160461</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G798" t="n">
-        <v>3.45843458175659</v>
+        <v>3.45843434333801</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G800" t="n">
-        <v>3.4688127040863</v>
+        <v>3.46881294250488</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.5</v>
       </c>
       <c r="G801" t="n">
-        <v>3.59255623817444</v>
+        <v>3.59255719184875</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.50099992752075</v>
       </c>
       <c r="G802" t="n">
-        <v>3.59335494041443</v>
+        <v>3.59335446357727</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.38100004196167</v>
       </c>
       <c r="G803" t="n">
-        <v>3.49755358695984</v>
+        <v>3.49755311012268</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G805" t="n">
-        <v>3.60213685035706</v>
+        <v>3.60213708877563</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>3.55663084983826</v>
+        <v>3.55663061141968</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.48899984359741</v>
       </c>
       <c r="G811" t="n">
-        <v>3.58377432823181</v>
+        <v>3.58377456665039</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G813" t="n">
-        <v>3.57259821891785</v>
+        <v>3.57259750366211</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>3.45683741569519</v>
+        <v>3.45683789253235</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.35099983215332</v>
       </c>
       <c r="G817" t="n">
-        <v>3.47360301017761</v>
+        <v>3.47360277175903</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G819" t="n">
-        <v>3.60453176498413</v>
+        <v>3.60453152656555</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>3.56062293052673</v>
+        <v>3.56062245368958</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.35900020599365</v>
       </c>
       <c r="G822" t="n">
-        <v>3.47999000549316</v>
+        <v>3.47998976707458</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G823" t="n">
-        <v>3.42330741882324</v>
+        <v>3.42330718040466</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>3.54465627670288</v>
+        <v>3.54465579986572</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G826" t="n">
-        <v>3.54944586753845</v>
+        <v>3.54944562911987</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G827" t="n">
-        <v>3.50633549690247</v>
+        <v>3.50633525848389</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G830" t="n">
-        <v>3.54465627670288</v>
+        <v>3.54465579986572</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G832" t="n">
-        <v>3.53667259216309</v>
+        <v>3.53667211532593</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.19399976730347</v>
       </c>
       <c r="G837" t="n">
-        <v>3.34826254844666</v>
+        <v>3.34826278686523</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.26900005340576</v>
       </c>
       <c r="G839" t="n">
-        <v>3.40813851356506</v>
+        <v>3.40813875198364</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.27899980545044</v>
       </c>
       <c r="G840" t="n">
-        <v>3.4161217212677</v>
+        <v>3.41612219810486</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G841" t="n">
-        <v>3.44087076187134</v>
+        <v>3.44087100028992</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G842" t="n">
-        <v>3.41692066192627</v>
+        <v>3.41692090034485</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.3730001449585</v>
       </c>
       <c r="G843" t="n">
-        <v>3.49116683006287</v>
+        <v>3.49116659164429</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.72300004959106</v>
       </c>
       <c r="G847" t="n">
-        <v>3.770587682724</v>
+        <v>3.77058792114258</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G850" t="n">
-        <v>3.73226761817932</v>
+        <v>3.732266664505</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.68100023269653</v>
       </c>
       <c r="G851" t="n">
-        <v>3.73705744743347</v>
+        <v>3.73705792427063</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>3.78815126419067</v>
+        <v>3.78815102577209</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>3.76420140266418</v>
+        <v>3.76420116424561</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G854" t="n">
-        <v>3.68995475769043</v>
+        <v>3.68995547294617</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.60099983215332</v>
       </c>
       <c r="G855" t="n">
-        <v>3.67318940162659</v>
+        <v>3.67318964004517</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>3.75861263275146</v>
+        <v>3.75861239433289</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>3.90790319442749</v>
+        <v>3.90790367126465</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.77099990844727</v>
       </c>
       <c r="G858" t="n">
-        <v>3.80890798568726</v>
+        <v>3.80890822410583</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G860" t="n">
-        <v>3.81609344482422</v>
+        <v>3.81609296798706</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G861" t="n">
-        <v>3.81210207939148</v>
+        <v>3.8121018409729</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G862" t="n">
-        <v>3.86399412155151</v>
+        <v>3.86399459838867</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G863" t="n">
-        <v>3.86080074310303</v>
+        <v>3.86080121994019</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G865" t="n">
-        <v>3.84802746772766</v>
+        <v>3.84802794456482</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.75</v>
       </c>
       <c r="G866" t="n">
-        <v>3.79214286804199</v>
+        <v>3.79214262962341</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.9689998626709</v>
       </c>
       <c r="G867" t="n">
-        <v>3.96698093414307</v>
+        <v>3.96698045730591</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G868" t="n">
-        <v>3.95340943336487</v>
+        <v>3.95340847969055</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G870" t="n">
-        <v>3.91508817672729</v>
+        <v>3.91508865356445</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G872" t="n">
-        <v>3.96378755569458</v>
+        <v>3.96378707885742</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G873" t="n">
-        <v>3.9126935005188</v>
+        <v>3.91269302368164</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5</v>
       </c>
       <c r="G874" t="n">
-        <v>3.99172925949097</v>
+        <v>3.99172973632812</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G875" t="n">
-        <v>4.04442071914673</v>
+        <v>4.04441976547241</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>5.0939998626709</v>
       </c>
       <c r="G876" t="n">
-        <v>4.06677341461182</v>
+        <v>4.06677389144897</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.97700023651123</v>
       </c>
       <c r="G877" t="n">
-        <v>3.97336840629578</v>
+        <v>3.97336745262146</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.93599987030029</v>
       </c>
       <c r="G878" t="n">
-        <v>3.94063520431519</v>
+        <v>3.94063472747803</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G883" t="n">
-        <v>4.14022207260132</v>
+        <v>4.14022159576416</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>5.0019998550415</v>
       </c>
       <c r="G884" t="n">
-        <v>3.99332594871521</v>
+        <v>3.99332642555237</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.02799987792969</v>
       </c>
       <c r="G886" t="n">
-        <v>4.01408338546753</v>
+        <v>4.01408290863037</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G888" t="n">
-        <v>3.99013328552246</v>
+        <v>3.99013233184814</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.94399976730347</v>
       </c>
       <c r="G890" t="n">
-        <v>3.94702219963074</v>
+        <v>3.94702172279358</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G893" t="n">
-        <v>3.92626547813416</v>
+        <v>3.926265001297</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G894" t="n">
-        <v>3.99971270561218</v>
+        <v>3.99971318244934</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G895" t="n">
-        <v>3.95740127563477</v>
+        <v>3.95740032196045</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G896" t="n">
-        <v>3.84802746772766</v>
+        <v>3.84802794456482</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G897" t="n">
-        <v>3.9126935005188</v>
+        <v>3.91269302368164</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>5.0019998550415</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99332594871521</v>
+        <v>3.99332642555237</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>5.02600002288818</v>
       </c>
       <c r="G900" t="n">
-        <v>4.01248598098755</v>
+        <v>4.01248693466187</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G901" t="n">
-        <v>3.94542574882507</v>
+        <v>3.94542527198792</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.79699993133545</v>
       </c>
       <c r="G902" t="n">
-        <v>3.82966494560242</v>
+        <v>3.82966542243958</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G903" t="n">
-        <v>3.75701546669006</v>
+        <v>3.75701570510864</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.73299980163574</v>
       </c>
       <c r="G905" t="n">
-        <v>3.77857136726379</v>
+        <v>3.77857089042664</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G906" t="n">
-        <v>3.67638325691223</v>
+        <v>3.67638349533081</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G907" t="n">
-        <v>3.68436646461487</v>
+        <v>3.68436598777771</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G908" t="n">
-        <v>3.69155144691467</v>
+        <v>3.69155120849609</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>4.58099985122681</v>
       </c>
       <c r="G911" t="n">
-        <v>3.657222032547</v>
+        <v>3.65722250938416</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G912" t="n">
-        <v>3.66839957237244</v>
+        <v>3.66839933395386</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.71299982070923</v>
       </c>
       <c r="G913" t="n">
-        <v>3.76260447502136</v>
+        <v>3.76260423660278</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G915" t="n">
-        <v>3.75222587585449</v>
+        <v>3.75222516059875</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G916" t="n">
-        <v>3.79533696174622</v>
+        <v>3.79533624649048</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G919" t="n">
-        <v>3.74823427200317</v>
+        <v>3.74823403358459</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G921" t="n">
-        <v>3.79054641723633</v>
+        <v>3.79054665565491</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.72900009155273</v>
       </c>
       <c r="G922" t="n">
-        <v>3.77537822723389</v>
+        <v>3.77537775039673</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G924" t="n">
-        <v>3.86399412155151</v>
+        <v>3.86399459838867</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.85699987411499</v>
       </c>
       <c r="G925" t="n">
-        <v>3.87756562232971</v>
+        <v>3.87756609916687</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G926" t="n">
-        <v>3.93185377120972</v>
+        <v>3.9318540096283</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G928" t="n">
-        <v>4.06517696380615</v>
+        <v>4.06517744064331</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.20599985122681</v>
       </c>
       <c r="G930" t="n">
-        <v>4.15618848800659</v>
+        <v>4.15618896484375</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G932" t="n">
-        <v>4.10349750518799</v>
+        <v>4.10349798202515</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>5.12200021743774</v>
       </c>
       <c r="G935" t="n">
-        <v>4.08912801742554</v>
+        <v>4.0891284942627</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G936" t="n">
-        <v>4.10349750518799</v>
+        <v>4.10349798202515</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>4.15345907211304</v>
+        <v>4.15345859527588</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G941" t="n">
-        <v>4.1339898109436</v>
+        <v>4.13398933410645</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G942" t="n">
-        <v>4.0755820274353</v>
+        <v>4.07558107376099</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.98299980163574</v>
       </c>
       <c r="G946" t="n">
-        <v>4.04232120513916</v>
+        <v>4.04232168197632</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.9229998588562</v>
       </c>
       <c r="G948" t="n">
-        <v>3.99364805221558</v>
+        <v>3.993647813797</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.93900012969971</v>
       </c>
       <c r="G951" t="n">
-        <v>4.00662755966187</v>
+        <v>4.00662708282471</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.99200010299683</v>
       </c>
       <c r="G952" t="n">
-        <v>4.04962253570557</v>
+        <v>4.04962205886841</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.86899995803833</v>
       </c>
       <c r="G953" t="n">
-        <v>3.94984197616577</v>
+        <v>3.94984245300293</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.93100023269653</v>
       </c>
       <c r="G955" t="n">
-        <v>4.00013828277588</v>
+        <v>4.00013780593872</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G961" t="n">
-        <v>3.914959192276</v>
+        <v>3.91495966911316</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G964" t="n">
-        <v>4.12912273406982</v>
+        <v>4.12912225723267</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G965" t="n">
-        <v>4.1339898109436</v>
+        <v>4.13398933410645</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>5.02199983596802</v>
       </c>
       <c r="G966" t="n">
-        <v>4.07395935058594</v>
+        <v>4.07395887374878</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>5.07600021362305</v>
       </c>
       <c r="G967" t="n">
-        <v>4.11776542663574</v>
+        <v>4.1177659034729</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>5.12400007247925</v>
       </c>
       <c r="G968" t="n">
-        <v>4.15670347213745</v>
+        <v>4.15670394897461</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G969" t="n">
-        <v>4.13561201095581</v>
+        <v>4.13561248779297</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G971" t="n">
-        <v>4.1064076423645</v>
+        <v>4.10640716552734</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G974" t="n">
-        <v>4.42116212844849</v>
+        <v>4.42116260528564</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G980" t="n">
-        <v>4.40007066726685</v>
+        <v>4.40007019042969</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G983" t="n">
-        <v>4.24756097793579</v>
+        <v>4.24756050109863</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G984" t="n">
-        <v>4.20699977874756</v>
+        <v>4.2069993019104</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.16800022125244</v>
       </c>
       <c r="G985" t="n">
-        <v>4.19239807128906</v>
+        <v>4.1923975944519</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G986" t="n">
-        <v>4.21024417877197</v>
+        <v>4.21024465560913</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G989" t="n">
-        <v>4.21348905563354</v>
+        <v>4.2134895324707</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G993" t="n">
-        <v>4.19888782501221</v>
+        <v>4.19888734817505</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>5.12400007247925</v>
       </c>
       <c r="G994" t="n">
-        <v>4.15670347213745</v>
+        <v>4.15670394897461</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>5.13600015640259</v>
       </c>
       <c r="G997" t="n">
-        <v>4.16643857955933</v>
+        <v>4.16643905639648</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G998" t="n">
-        <v>4.19888782501221</v>
+        <v>4.19888734817505</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G999" t="n">
-        <v>4.15345907211304</v>
+        <v>4.15345859527588</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>5.2519998550415</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.26054000854492</v>
+        <v>4.26054048538208</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.20213222503662</v>
+        <v>4.20213174819946</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.19888782501221</v>
+        <v>4.19888734817505</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.19564199447632</v>
+        <v>4.19564294815063</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.23782634735107</v>
+        <v>4.23782682418823</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.05205631256104</v>
+        <v>4.05205678939819</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>5.02199983596802</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.07395935058594</v>
+        <v>4.07395887374878</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.98699998855591</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.04556655883789</v>
+        <v>4.04556608200073</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.05124473571777</v>
+        <v>4.05124425888062</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>5.08400011062622</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.12425518035889</v>
+        <v>4.12425565719604</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.21348905563354</v>
+        <v>4.2134895324707</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>5.31199979782104</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.30921363830566</v>
+        <v>4.30921316146851</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>5.31199979782104</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.30921363830566</v>
+        <v>4.30921316146851</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.31570339202881</v>
+        <v>4.31570386886597</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.42765235900879</v>
+        <v>4.42765188217163</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.54284572601318</v>
+        <v>4.54284524917603</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.49579429626465</v>
+        <v>4.49579477310181</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.67264175415039</v>
+        <v>4.67264127731323</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.69860076904297</v>
+        <v>4.69860029220581</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.73916101455688</v>
+        <v>4.73916149139404</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>5.84600019454956</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.74240636825562</v>
+        <v>4.74240684509277</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.6969780921936</v>
+        <v>4.69697761535645</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.68399858474731</v>
+        <v>4.68399906158447</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.65966176986694</v>
+        <v>4.65966129302979</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>4.49417209625244</v>
+        <v>4.4941725730896</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>5.5460000038147</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.49903964996338</v>
+        <v>4.49903917312622</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>5.9520001411438</v>
       </c>
       <c r="G1062" t="n">
-        <v>4.82839632034302</v>
+        <v>4.82839584350586</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.84299755096436</v>
+        <v>4.84299802780151</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>5.97399997711182</v>
       </c>
       <c r="G1065" t="n">
-        <v>4.84624290466309</v>
+        <v>4.84624242782593</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>5.94399976730347</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.82190561294556</v>
+        <v>4.82190608978271</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.84299755096436</v>
+        <v>4.84299802780151</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>5.87400007247925</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.76512002944946</v>
+        <v>4.76512098312378</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G1072" t="n">
-        <v>4.87869167327881</v>
+        <v>4.87869215011597</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>6.11600017547607</v>
       </c>
       <c r="G1076" t="n">
-        <v>4.96143674850464</v>
+        <v>4.9614372253418</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>6.5</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.27294588088989</v>
+        <v>5.27294635772705</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.43800020217896</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.2226505279541</v>
+        <v>5.22265005111694</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.28917026519775</v>
+        <v>5.28917074203491</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6.58400011062622</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.34108877182007</v>
+        <v>5.34108829498291</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>6.59200000762939</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.34757804870605</v>
+        <v>5.34757852554321</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.22427320480347</v>
+        <v>5.22427272796631</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.00037574768066</v>
+        <v>5.00037527084351</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>6.28599977493286</v>
       </c>
       <c r="G1096" t="n">
-        <v>5.09934425354004</v>
+        <v>5.09934377670288</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.05553770065308</v>
+        <v>5.05553817749023</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>6.29199981689453</v>
       </c>
       <c r="G1100" t="n">
-        <v>5.10421133041382</v>
+        <v>5.10421180725098</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.89978408813477</v>
+        <v>4.89978361129761</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>6.13199996948242</v>
       </c>
       <c r="G1104" t="n">
-        <v>4.97441577911377</v>
+        <v>4.97441625595093</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G1108" t="n">
-        <v>4.74889659881592</v>
+        <v>4.74889707565308</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>5.9980001449585</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.86571216583252</v>
+        <v>4.86571264266968</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.76349830627441</v>
+        <v>4.76349878311157</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>5.75799989700317</v>
       </c>
       <c r="G1112" t="n">
-        <v>4.67101907730103</v>
+        <v>4.67101860046387</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>5.61199998855591</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.5525803565979</v>
+        <v>4.55258083343506</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>5.66200017929077</v>
       </c>
       <c r="G1114" t="n">
-        <v>4.59314107894897</v>
+        <v>4.59314155578613</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>5.65199995040894</v>
       </c>
       <c r="G1115" t="n">
-        <v>4.58502864837646</v>
+        <v>4.58502960205078</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.21024417877197</v>
+        <v>4.21024465560913</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.82247972488403</v>
+        <v>3.82248020172119</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>4.65700006484985</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.7778627872467</v>
+        <v>3.77786302566528</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>4.32600021362305</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.50934886932373</v>
+        <v>3.50934863090515</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>4.67799997329712</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.79489850997925</v>
+        <v>3.79489827156067</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.67402648925781</v>
+        <v>3.67402625083923</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>4.66099977493286</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.78110766410828</v>
+        <v>3.7811074256897</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>4.84700012207031</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.93199491500854</v>
+        <v>3.9319953918457</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.93767404556274</v>
+        <v>3.93767356872559</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.8938684463501</v>
+        <v>3.89386749267578</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>4.93100023269653</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.00013828277588</v>
+        <v>4.00013780593872</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>4.8769998550415</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.95633220672607</v>
+        <v>3.95633172988892</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.68457221984863</v>
+        <v>3.68457245826721</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.59209299087524</v>
+        <v>3.59209322929382</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.6066951751709</v>
+        <v>3.60669469833374</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>4.52099990844727</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.66753697395325</v>
+        <v>3.66753673553467</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>4.54300022125244</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.68538379669189</v>
+        <v>3.68538355827332</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.85817456245422</v>
+        <v>3.85817408561707</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>4.88100004196167</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.95957684516907</v>
+        <v>3.95957636833191</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.84925031661987</v>
+        <v>3.84924983978271</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>4.69600009918213</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.8095006942749</v>
+        <v>3.80950045585632</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>4.5770001411438</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.71296548843384</v>
+        <v>3.71296501159668</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.71377611160278</v>
+        <v>3.71377635002136</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.60831737518311</v>
+        <v>3.60831761360168</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.45100021362305</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.61075162887573</v>
+        <v>3.61075115203857</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>4.4689998626709</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.62535262107849</v>
+        <v>3.62535333633423</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>4.56799983978271</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.70566391944885</v>
+        <v>3.70566415786743</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>4.63899993896484</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.76326107978821</v>
+        <v>3.76326084136963</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.81761240959167</v>
+        <v>3.81761264801025</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>4.68699979782104</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.80219960212708</v>
+        <v>3.8021993637085</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.68781709671021</v>
+        <v>3.68781757354736</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>4.51399993896484</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.66185808181763</v>
+        <v>3.66185784339905</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>4.51100015640259</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.79477190971375</v>
+        <v>3.7947723865509</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.85449886322021</v>
+        <v>3.85449838638306</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>4.65100002288818</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.91254353523254</v>
+        <v>3.9125440120697</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.92768597602844</v>
+        <v>3.92768549919128</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.84860992431641</v>
+        <v>3.84861040115356</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.80402565002441</v>
+        <v>3.80402541160583</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.74177479743958</v>
+        <v>3.74177503585815</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>4.32299995422363</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.63662123680115</v>
+        <v>3.63662147521973</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.37752366065979</v>
+        <v>3.37752342224121</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.21299982070923</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.54408621788025</v>
+        <v>3.54408645629883</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>4.25899982452393</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.58278274536133</v>
+        <v>3.58278250694275</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.3363037109375</v>
+        <v>3.33630347251892</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.40191960334778</v>
+        <v>3.4019193649292</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.38341236114502</v>
+        <v>3.38341212272644</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.41958498954773</v>
+        <v>3.41958475112915</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.33125638961792</v>
+        <v>3.33125615119934</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.4995014667511</v>
+        <v>3.49950122833252</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>4.12099981307983</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.46669340133667</v>
+        <v>3.46669363975525</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>4.12900018692017</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.47342371940613</v>
+        <v>3.47342395782471</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>4.20800018310547</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.5398805141449</v>
+        <v>3.53988075256348</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.58025932312012</v>
+        <v>3.5802595615387</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>4.40700006484985</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.70728421211243</v>
+        <v>3.70728445053101</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.58194160461426</v>
+        <v>3.58194184303284</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.66774678230286</v>
+        <v>3.66774702072144</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.6240029335022</v>
+        <v>3.62400317192078</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.16721701622009</v>
+        <v>3.16721725463867</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.7590000629425</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.16216969490051</v>
+        <v>3.16216993331909</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.297607421875</v>
+        <v>3.29760718345642</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.16637587547302</v>
+        <v>3.16637563705444</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G1261" t="n">
-        <v>3.17647075653076</v>
+        <v>3.17647051811218</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.1596462726593</v>
+        <v>3.15964603424072</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.90223097801208</v>
+        <v>2.90223073959351</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>3.56900000572205</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.00233674049377</v>
+        <v>3.00233697891235</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.95775198936462</v>
+        <v>2.95775175094604</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.20675492286682</v>
+        <v>3.20675468444824</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1294" t="n">
-        <v>3.41369676589966</v>
+        <v>3.41369652748108</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>4.04099988937378</v>
       </c>
       <c r="G1297" t="n">
-        <v>3.39939522743225</v>
+        <v>3.39939546585083</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>4.13299989700317</v>
       </c>
       <c r="G1298" t="n">
-        <v>3.47678828239441</v>
+        <v>3.47678852081299</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.4793119430542</v>
+        <v>3.47931218147278</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.51127862930298</v>
+        <v>3.5112783908844</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.46585249900818</v>
+        <v>3.4658522605896</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.4288387298584</v>
+        <v>3.42883849143982</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>4.12099981307983</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.46669340133667</v>
+        <v>3.46669363975525</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.51969075202942</v>
+        <v>3.519690990448</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.5583872795105</v>
+        <v>3.55838751792908</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.52642059326172</v>
+        <v>3.5264208316803</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>4.15399980545044</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.49445414543152</v>
+        <v>3.49445390701294</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.43893313407898</v>
+        <v>3.4389328956604</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.36658763885498</v>
+        <v>3.3665874004364</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>4.15100002288818</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.49193072319031</v>
+        <v>3.49193048477173</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.35985827445984</v>
+        <v>3.35985803604126</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.4271559715271</v>
+        <v>3.42715573310852</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>4.09299993515015</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.44313955307007</v>
+        <v>3.44313931465149</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>4.4229998588562</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.72074365615845</v>
+        <v>3.72074413299561</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.87721228599548</v>
+        <v>3.87721276283264</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.94366908073425</v>
+        <v>3.94366955757141</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>4.59100008010864</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.86206984519958</v>
+        <v>3.86207032203674</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.85113453865051</v>
+        <v>3.85113406181335</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>4.56899976730347</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.84356307983398</v>
+        <v>3.84356260299683</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.85618138313293</v>
+        <v>3.85618185997009</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.82758021354675</v>
+        <v>3.82757997512817</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.85618138313293</v>
+        <v>3.85618185997009</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>4.65899991989136</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.91927337646484</v>
+        <v>3.919273853302</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.90917825698853</v>
+        <v>3.90917873382568</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.16407012939453</v>
+        <v>4.16406965255737</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>4.95300006866455</v>
       </c>
       <c r="G1372" t="n">
-        <v>4.1665940284729</v>
+        <v>4.16659450531006</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>4.88299989700317</v>
       </c>
       <c r="G1374" t="n">
-        <v>4.10770750045776</v>
+        <v>4.10770797729492</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.05639362335205</v>
+        <v>4.05639314651489</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>4.89099979400635</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.11443758010864</v>
+        <v>4.1144380569458</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G1377" t="n">
-        <v>4.12285041809082</v>
+        <v>4.12284994125366</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>4.50299978256226</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.78804159164429</v>
+        <v>3.78804206848145</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.66942930221558</v>
+        <v>3.669429063797</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.73672723770142</v>
+        <v>3.73672699928284</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.75607585906982</v>
+        <v>3.7560760974884</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.76448726654053</v>
+        <v>3.76448750495911</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>4.48299980163574</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.77121758460999</v>
+        <v>3.77121782302856</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.79056620597839</v>
+        <v>3.79056572914124</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.92768597602844</v>
+        <v>3.92768549919128</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.84860992431641</v>
+        <v>3.84861040115356</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.12285041809082</v>
+        <v>4.12284994125366</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.90299987792969</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.12453269958496</v>
+        <v>4.12453317642212</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>4.8289999961853</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.0622820854187</v>
+        <v>4.06228160858154</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>4.83099985122681</v>
       </c>
       <c r="G1427" t="n">
-        <v>4.06396436691284</v>
+        <v>4.06396484375</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>4.58699989318848</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.85870504379272</v>
+        <v>3.85870552062988</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.87468862533569</v>
+        <v>3.87468814849854</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.83262729644775</v>
+        <v>3.83262705802917</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.82758021354675</v>
+        <v>3.82757997512817</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>4.46700000762939</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.75775790214539</v>
+        <v>3.75775814056396</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.87468862533569</v>
+        <v>3.87468814849854</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.82337379455566</v>
+        <v>3.82337403297424</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>4.49900007247925</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.78467702865601</v>
+        <v>3.78467726707458</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.83178567886353</v>
+        <v>3.8317859172821</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.90917825698853</v>
+        <v>3.90917873382568</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.77710580825806</v>
+        <v>3.77710604667664</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.43300008773804</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.72915625572205</v>
+        <v>3.72915601730347</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.74345731735229</v>
+        <v>3.74345707893372</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.70307850837708</v>
+        <v>3.7030782699585</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.74345731735229</v>
+        <v>3.74345707893372</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.78131198883057</v>
+        <v>3.78131246566772</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.78383636474609</v>
+        <v>3.78383612632751</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.82085037231445</v>
+        <v>3.82085013389587</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>4.47599983215332</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.76532912254333</v>
+        <v>3.76532888412476</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.81412029266357</v>
+        <v>3.814120054245</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.90917825698853</v>
+        <v>3.90917873382568</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1481" t="n">
-        <v>4.27238130569458</v>
+        <v>4.27238178253174</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.29880857467651</v>
+        <v>4.29880809783936</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1483" t="n">
-        <v>4.27238130569458</v>
+        <v>4.27238178253174</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>4.76800012588501</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.20014762878418</v>
+        <v>4.20014715194702</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G1485" t="n">
-        <v>4.17988634109497</v>
+        <v>4.17988681793213</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G1486" t="n">
-        <v>4.11558103561401</v>
+        <v>4.11558055877686</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.07858276367188</v>
+        <v>4.07858324050903</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07065439224243</v>
+        <v>4.07065391540527</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>4.60400009155273</v>
       </c>
       <c r="G1489" t="n">
-        <v>4.05567932128906</v>
+        <v>4.0556788444519</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.99401569366455</v>
+        <v>3.99401617050171</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>4.58099985122681</v>
       </c>
       <c r="G1502" t="n">
-        <v>4.03541803359985</v>
+        <v>4.03541851043701</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1513" t="n">
-        <v>4.18252897262573</v>
+        <v>4.18252944946289</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G1516" t="n">
-        <v>4.17988634109497</v>
+        <v>4.17988681793213</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>4.85300016403198</v>
       </c>
       <c r="G1517" t="n">
-        <v>4.2750244140625</v>
+        <v>4.27502393722534</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>4.71299982070923</v>
       </c>
       <c r="G1520" t="n">
-        <v>4.15169715881348</v>
+        <v>4.15169763565063</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>4.56099987030029</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.01780033111572</v>
+        <v>4.01779985427856</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.8715705871582</v>
+        <v>3.87157011032104</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>4.35099983215332</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.83281016349792</v>
+        <v>3.8328104019165</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>4.44299983978271</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.91385340690613</v>
+        <v>3.91385388374329</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>4.47100019454956</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.93851947784424</v>
+        <v>3.93851900100708</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.87597465515137</v>
+        <v>3.87597513198853</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.66455793380737</v>
+        <v>3.66455817222595</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>4.20100021362305</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.70067548751831</v>
+        <v>3.70067524909973</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>4.3270001411438</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.81166934967041</v>
+        <v>3.81166911125183</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>4.39300012588501</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.8698091506958</v>
+        <v>3.86980867385864</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.97111248970032</v>
+        <v>3.97111225128174</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G1571" t="n">
-        <v>4.18957614898682</v>
+        <v>4.18957662582397</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G1572" t="n">
-        <v>4.18957614898682</v>
+        <v>4.18957662582397</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>4.80700016021729</v>
       </c>
       <c r="G1576" t="n">
-        <v>4.23450231552124</v>
+        <v>4.2345027923584</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G1581" t="n">
-        <v>4.23009824752808</v>
+        <v>4.23009777069092</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G1584" t="n">
-        <v>4.27942800521851</v>
+        <v>4.27942848205566</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>4.9229998588562</v>
       </c>
       <c r="G1586" t="n">
-        <v>4.33668756484985</v>
+        <v>4.3366870880127</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G1588" t="n">
-        <v>4.34990119934082</v>
+        <v>4.34990167617798</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.39042282104492</v>
+        <v>4.39042234420776</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>5.19799995422363</v>
       </c>
       <c r="G1597" t="n">
-        <v>4.57893562316895</v>
+        <v>4.5789361000061</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G1601" t="n">
-        <v>4.50317764282227</v>
+        <v>4.50317811965942</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G1605" t="n">
-        <v>4.50317764282227</v>
+        <v>4.50317811965942</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G1608" t="n">
-        <v>4.52255773544312</v>
+        <v>4.52255725860596</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1616" t="n">
-        <v>4.70402431488037</v>
+        <v>4.70402383804321</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.74278402328491</v>
+        <v>4.74278354644775</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>5.41800022125244</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.77273511886597</v>
+        <v>4.77273464202881</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>5.3439998626709</v>
       </c>
       <c r="G1623" t="n">
-        <v>4.70754718780518</v>
+        <v>4.70754766464233</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1633" t="n">
-        <v>5.05638551712036</v>
+        <v>5.0563850402832</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>5.33799982070923</v>
       </c>
       <c r="G1639" t="n">
-        <v>4.70226240158081</v>
+        <v>4.70226192474365</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>5.3439998626709</v>
       </c>
       <c r="G1640" t="n">
-        <v>4.70754718780518</v>
+        <v>4.70754766464233</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1643" t="n">
-        <v>4.91720294952393</v>
+        <v>4.91720247268677</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1648" t="n">
-        <v>4.9735803604126</v>
+        <v>4.97357988357544</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1651" t="n">
-        <v>4.9735803604126</v>
+        <v>4.97357988357544</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1652" t="n">
-        <v>5.07576513290405</v>
+        <v>5.07576560974121</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G1655" t="n">
-        <v>5.16561698913574</v>
+        <v>5.1656174659729</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>5.8439998626709</v>
       </c>
       <c r="G1657" t="n">
-        <v>5.14799928665161</v>
+        <v>5.14799880981445</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G1658" t="n">
-        <v>5.11276292800903</v>
+        <v>5.11276340484619</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1660" t="n">
-        <v>5.15328502655029</v>
+        <v>5.15328454971313</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>5.23256635665894</v>
+        <v>5.23256587982178</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G1672" t="n">
-        <v>5.36646318435669</v>
+        <v>5.36646366119385</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>6.00400018692017</v>
       </c>
       <c r="G1673" t="n">
-        <v>5.28894424438477</v>
+        <v>5.28894376754761</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>6.17799997329712</v>
       </c>
       <c r="G1675" t="n">
-        <v>5.44222068786621</v>
+        <v>5.44222116470337</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1679" t="n">
-        <v>5.46160078048706</v>
+        <v>5.4616003036499</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G1689" t="n">
-        <v>5.41403245925903</v>
+        <v>5.41403198242188</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1692" t="n">
-        <v>5.20613861083984</v>
+        <v>5.206139087677</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G1694" t="n">
-        <v>5.29775285720825</v>
+        <v>5.29775333404541</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1698" t="n">
-        <v>5.32946586608887</v>
+        <v>5.32946538925171</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>5.86600017547607</v>
       </c>
       <c r="G1703" t="n">
-        <v>5.1673789024353</v>
+        <v>5.16737937927246</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>5.86199998855591</v>
       </c>
       <c r="G1705" t="n">
-        <v>5.16385555267334</v>
+        <v>5.1638560295105</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1706" t="n">
-        <v>5.13566637039185</v>
+        <v>5.135666847229</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -59548,6 +59548,32 @@
         <v>6.47499990463257</v>
       </c>
       <c r="H2276" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2277" t="n">
+        <v>2084201</v>
+      </c>
+      <c r="C2277" t="n">
+        <v>6.57499980926514</v>
+      </c>
+      <c r="D2277" t="n">
+        <v>6.45499992370605</v>
+      </c>
+      <c r="E2277" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="F2277" t="n">
+        <v>6.57499980926514</v>
+      </c>
+      <c r="G2277" t="n">
+        <v>6.57499980926514</v>
+      </c>
+      <c r="H2277" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -447,7 +447,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>5.19319772720337</v>
+        <v>5.19319725036621</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G5" t="n">
-        <v>5.0771050453186</v>
+        <v>5.07710409164429</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G6" t="n">
-        <v>5.10419321060181</v>
+        <v>5.10419273376465</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G7" t="n">
-        <v>5.11193323135376</v>
+        <v>5.1119327545166</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G8" t="n">
-        <v>5.03453826904297</v>
+        <v>5.03453731536865</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>5.02679777145386</v>
+        <v>5.02679824829102</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>4.99971055984497</v>
+        <v>4.99970960617065</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G13" t="n">
-        <v>4.90683603286743</v>
+        <v>4.90683650970459</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>5.02679777145386</v>
+        <v>5.02679824829102</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G15" t="n">
-        <v>5.04227733612061</v>
+        <v>5.04227685928345</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G17" t="n">
-        <v>5.02292776107788</v>
+        <v>5.0229287147522</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G18" t="n">
-        <v>5.04227733612061</v>
+        <v>5.04227685928345</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G19" t="n">
-        <v>5.10806322097778</v>
+        <v>5.10806274414062</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G20" t="n">
-        <v>5.11580276489258</v>
+        <v>5.11580228805542</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G23" t="n">
-        <v>5.375075340271</v>
+        <v>5.37507581710815</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G24" t="n">
-        <v>5.3325080871582</v>
+        <v>5.33250856399536</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>5.41764211654663</v>
+        <v>5.41764259338379</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G28" t="n">
-        <v>5.35185718536377</v>
+        <v>5.35185623168945</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>5.23189496994019</v>
+        <v>5.23189449310303</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>5.29381132125854</v>
+        <v>5.29381036758423</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G32" t="n">
-        <v>5.26285314559937</v>
+        <v>5.26285266876221</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>5.26285314559937</v>
+        <v>5.26285266876221</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>5.29381132125854</v>
+        <v>5.29381036758423</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>5.44860076904297</v>
+        <v>5.44860029220581</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G38" t="n">
-        <v>5.45246982574463</v>
+        <v>5.45247030258179</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>5.44860076904297</v>
+        <v>5.44860029220581</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G42" t="n">
-        <v>5.46407890319824</v>
+        <v>5.4640793800354</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>5.42151308059692</v>
+        <v>5.42151212692261</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>5.340247631073</v>
+        <v>5.34024810791016</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>5.4292516708374</v>
+        <v>5.42925214767456</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G47" t="n">
-        <v>5.37120580673218</v>
+        <v>5.37120532989502</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G48" t="n">
-        <v>5.53760528564453</v>
+        <v>5.53760480880737</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G49" t="n">
-        <v>5.56469345092773</v>
+        <v>5.56469297409058</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G51" t="n">
-        <v>5.58791065216064</v>
+        <v>5.5879111289978</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>5.62273836135864</v>
+        <v>5.6227388381958</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>5.5337347984314</v>
+        <v>5.53373527526855</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>5.48342847824097</v>
+        <v>5.48342800140381</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G56" t="n">
-        <v>5.47181844711304</v>
+        <v>5.4718189239502</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G58" t="n">
-        <v>5.52986478805542</v>
+        <v>5.52986526489258</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>5.5337347984314</v>
+        <v>5.53373527526855</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>5.5956506729126</v>
+        <v>5.59565019607544</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G66" t="n">
-        <v>5.99036455154419</v>
+        <v>5.99036502838135</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>6.04841089248657</v>
+        <v>6.04841041564941</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>6.14902448654175</v>
+        <v>6.14902496337891</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>7.75</v>
       </c>
       <c r="G69" t="n">
-        <v>5.99810409545898</v>
+        <v>5.99810457229614</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G74" t="n">
-        <v>6.05228042602539</v>
+        <v>6.05228090286255</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G77" t="n">
-        <v>6.05228042602539</v>
+        <v>6.05228090286255</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>5.98262548446655</v>
+        <v>5.98262500762939</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G81" t="n">
-        <v>6.05228042602539</v>
+        <v>6.05228090286255</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G82" t="n">
-        <v>6.06930732727051</v>
+        <v>6.06930685043335</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G83" t="n">
-        <v>6.00584411621094</v>
+        <v>6.00584363937378</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G84" t="n">
-        <v>6.00584411621094</v>
+        <v>6.00584363937378</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G86" t="n">
-        <v>5.88201141357422</v>
+        <v>5.88201189041138</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G87" t="n">
-        <v>5.72722196578979</v>
+        <v>5.72722244262695</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G92" t="n">
-        <v>5.69007205963135</v>
+        <v>5.69007349014282</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>7.24399995803833</v>
       </c>
       <c r="G93" t="n">
-        <v>5.60648679733276</v>
+        <v>5.60648536682129</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>7.43400001525879</v>
       </c>
       <c r="G94" t="n">
-        <v>5.75353622436523</v>
+        <v>5.75353670120239</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G95" t="n">
-        <v>5.78139781951904</v>
+        <v>5.7813982963562</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>7.67600011825562</v>
       </c>
       <c r="G96" t="n">
-        <v>5.94083213806152</v>
+        <v>5.94083166122437</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G99" t="n">
-        <v>5.73186540603638</v>
+        <v>5.73186588287354</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>5.71174335479736</v>
+        <v>5.71174240112305</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G101" t="n">
-        <v>5.79687690734863</v>
+        <v>5.79687786102295</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G102" t="n">
-        <v>5.79687690734863</v>
+        <v>5.79687786102295</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G103" t="n">
-        <v>5.79687690734863</v>
+        <v>5.79687786102295</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>6.89200019836426</v>
       </c>
       <c r="G107" t="n">
-        <v>5.33405590057373</v>
+        <v>5.33405637741089</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G108" t="n">
-        <v>5.48574924468994</v>
+        <v>5.4857497215271</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G109" t="n">
-        <v>5.56159687042236</v>
+        <v>5.56159639358521</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>7.31599998474121</v>
       </c>
       <c r="G110" t="n">
-        <v>5.6622109413147</v>
+        <v>5.66220998764038</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>5.62660884857178</v>
+        <v>5.62660837173462</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G114" t="n">
-        <v>5.47181844711304</v>
+        <v>5.4718189239502</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>5.46407890319824</v>
+        <v>5.4640793800354</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G123" t="n">
-        <v>5.42538213729858</v>
+        <v>5.42538166046143</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>7.03599977493286</v>
       </c>
       <c r="G124" t="n">
-        <v>5.44550466537476</v>
+        <v>5.4455041885376</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>5.57243204116821</v>
+        <v>5.57243156433105</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>7.16800022125244</v>
       </c>
       <c r="G126" t="n">
-        <v>5.5476655960083</v>
+        <v>5.54766607284546</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.02799987792969</v>
       </c>
       <c r="G127" t="n">
-        <v>5.43931293487549</v>
+        <v>5.43931245803833</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G128" t="n">
-        <v>5.55540561676025</v>
+        <v>5.5554051399231</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>7.11199998855591</v>
       </c>
       <c r="G130" t="n">
-        <v>5.50432538986206</v>
+        <v>5.5043249130249</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G131" t="n">
-        <v>5.56159687042236</v>
+        <v>5.56159639358521</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>5.5337347984314</v>
+        <v>5.53373527526855</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G138" t="n">
-        <v>5.44086074829102</v>
+        <v>5.44086122512817</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>7.02400016784668</v>
       </c>
       <c r="G139" t="n">
-        <v>5.43621683120728</v>
+        <v>5.43621730804443</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G141" t="n">
-        <v>5.57243204116821</v>
+        <v>5.57243156433105</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.13600015640259</v>
       </c>
       <c r="G142" t="n">
-        <v>5.52289962768555</v>
+        <v>5.52290010452271</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>7.2519998550415</v>
       </c>
       <c r="G143" t="n">
-        <v>5.61267709732056</v>
+        <v>5.61267757415771</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>7.2039999961853</v>
       </c>
       <c r="G145" t="n">
-        <v>5.57552814483643</v>
+        <v>5.57552766799927</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G146" t="n">
-        <v>5.69007205963135</v>
+        <v>5.69007349014282</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G153" t="n">
-        <v>5.38823175430298</v>
+        <v>5.38823223114014</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>7.4539999961853</v>
       </c>
       <c r="G155" t="n">
-        <v>5.76901483535767</v>
+        <v>5.76901531219482</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G163" t="n">
-        <v>5.75044012069702</v>
+        <v>5.75044059753418</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G164" t="n">
-        <v>5.69626379013062</v>
+        <v>5.69626426696777</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7.20800018310547</v>
       </c>
       <c r="G165" t="n">
-        <v>5.57862424850464</v>
+        <v>5.57862329483032</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>7.26399993896484</v>
       </c>
       <c r="G166" t="n">
-        <v>5.62196445465088</v>
+        <v>5.62196493148804</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>7.36199998855591</v>
       </c>
       <c r="G169" t="n">
-        <v>5.69781160354614</v>
+        <v>5.69781255722046</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7.47599983215332</v>
       </c>
       <c r="G170" t="n">
-        <v>5.78604221343994</v>
+        <v>5.78604125976562</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>7.44199991226196</v>
       </c>
       <c r="G171" t="n">
-        <v>5.7597279548645</v>
+        <v>5.75972747802734</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>7.43400001525879</v>
       </c>
       <c r="G172" t="n">
-        <v>5.75353622436523</v>
+        <v>5.75353670120239</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>7.27600002288818</v>
       </c>
       <c r="G173" t="n">
-        <v>5.63125276565552</v>
+        <v>5.63125228881836</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>7.52400016784668</v>
       </c>
       <c r="G174" t="n">
-        <v>5.82319164276123</v>
+        <v>5.82319211959839</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G176" t="n">
-        <v>5.75044012069702</v>
+        <v>5.75044059753418</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>5.72722196578979</v>
+        <v>5.72722244262695</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G179" t="n">
-        <v>5.72257852554321</v>
+        <v>5.7225775718689</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.64982652664185</v>
+        <v>5.64982748031616</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G182" t="n">
-        <v>5.60339069366455</v>
+        <v>5.60339021682739</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G183" t="n">
-        <v>5.6931676864624</v>
+        <v>5.69316864013672</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.2519998550415</v>
       </c>
       <c r="G185" t="n">
-        <v>5.61267709732056</v>
+        <v>5.61267757415771</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>7.29199981689453</v>
       </c>
       <c r="G186" t="n">
-        <v>5.64363479614258</v>
+        <v>5.64363574981689</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>7.12400007247925</v>
       </c>
       <c r="G187" t="n">
-        <v>5.51361227035522</v>
+        <v>5.51361274719238</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>7.24200010299683</v>
       </c>
       <c r="G190" t="n">
-        <v>5.60493850708008</v>
+        <v>5.60493803024292</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G191" t="n">
-        <v>5.55540561676025</v>
+        <v>5.5554051399231</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>7.2960000038147</v>
       </c>
       <c r="G192" t="n">
-        <v>5.64673089981079</v>
+        <v>5.64673185348511</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7.13600015640259</v>
       </c>
       <c r="G193" t="n">
-        <v>5.52289962768555</v>
+        <v>5.52290010452271</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G194" t="n">
-        <v>5.56469345092773</v>
+        <v>5.56469297409058</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7.15799999237061</v>
       </c>
       <c r="G195" t="n">
-        <v>5.53992605209351</v>
+        <v>5.53992652893066</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7</v>
       </c>
       <c r="G196" t="n">
-        <v>5.41764211654663</v>
+        <v>5.41764259338379</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="n">
-        <v>5.41764211654663</v>
+        <v>5.41764259338379</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.02799987792969</v>
       </c>
       <c r="G199" t="n">
-        <v>5.43931293487549</v>
+        <v>5.43931245803833</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.0460000038147</v>
       </c>
       <c r="G201" t="n">
-        <v>5.45324468612671</v>
+        <v>5.45324420928955</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.13199996948242</v>
       </c>
       <c r="G202" t="n">
-        <v>5.51980352401733</v>
+        <v>5.51980400085449</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G204" t="n">
-        <v>5.47181844711304</v>
+        <v>5.4718189239502</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.13399982452393</v>
       </c>
       <c r="G205" t="n">
-        <v>5.5213508605957</v>
+        <v>5.52135181427002</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>5.5337347984314</v>
+        <v>5.53373527526855</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>7.46600008010864</v>
       </c>
       <c r="G208" t="n">
-        <v>5.7783031463623</v>
+        <v>5.77830219268799</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>7.47200012207031</v>
       </c>
       <c r="G210" t="n">
-        <v>5.78294706344604</v>
+        <v>5.78294610977173</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G211" t="n">
-        <v>5.69007205963135</v>
+        <v>5.69007349014282</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>5.51825618743896</v>
+        <v>5.51825571060181</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>7.20800018310547</v>
       </c>
       <c r="G214" t="n">
-        <v>5.57862424850464</v>
+        <v>5.57862329483032</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>7.48799991607666</v>
       </c>
       <c r="G215" t="n">
-        <v>5.79532861709595</v>
+        <v>5.79532909393311</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.66599988937378</v>
       </c>
       <c r="G216" t="n">
-        <v>5.93309259414673</v>
+        <v>5.93309211730957</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.66599988937378</v>
       </c>
       <c r="G217" t="n">
-        <v>5.93309259414673</v>
+        <v>5.93309211730957</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.60400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>5.88510751724243</v>
+        <v>5.88510799407959</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>5.88201141357422</v>
+        <v>5.88201189041138</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>7.62200021743774</v>
       </c>
       <c r="G220" t="n">
-        <v>5.89903879165649</v>
+        <v>5.89903831481934</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>7.60200023651123</v>
       </c>
       <c r="G222" t="n">
-        <v>5.8835597038269</v>
+        <v>5.88356018066406</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G226" t="n">
-        <v>5.69626379013062</v>
+        <v>5.69626426696777</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>7.1560001373291</v>
       </c>
       <c r="G227" t="n">
-        <v>5.53837871551514</v>
+        <v>5.53837823867798</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G228" t="n">
-        <v>5.56159687042236</v>
+        <v>5.56159639358521</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>7.27600002288818</v>
       </c>
       <c r="G231" t="n">
-        <v>5.63125276565552</v>
+        <v>5.63125228881836</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>6.93800020217896</v>
       </c>
       <c r="G232" t="n">
-        <v>5.36965751647949</v>
+        <v>5.36965799331665</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G236" t="n">
-        <v>5.21641540527344</v>
+        <v>5.2164158821106</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G240" t="n">
-        <v>5.49813270568848</v>
+        <v>5.49813365936279</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G242" t="n">
-        <v>5.49813270568848</v>
+        <v>5.49813365936279</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G244" t="n">
-        <v>5.55695390701294</v>
+        <v>5.55695343017578</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>7.18800020217896</v>
       </c>
       <c r="G245" t="n">
-        <v>5.56314468383789</v>
+        <v>5.56314516067505</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7.20599985122681</v>
       </c>
       <c r="G246" t="n">
-        <v>5.57707595825195</v>
+        <v>5.57707643508911</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>7.10599994659424</v>
       </c>
       <c r="G248" t="n">
-        <v>5.49968147277832</v>
+        <v>5.49968099594116</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G249" t="n">
-        <v>5.48574924468994</v>
+        <v>5.4857497215271</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G250" t="n">
-        <v>5.56159687042236</v>
+        <v>5.56159639358521</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.99200010299683</v>
       </c>
       <c r="G254" t="n">
-        <v>5.41145133972168</v>
+        <v>5.41145086288452</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>5.25511360168457</v>
+        <v>5.25511264801025</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G259" t="n">
-        <v>5.17771816253662</v>
+        <v>5.17771863937378</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>4.86813831329346</v>
+        <v>4.86813926696777</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>6.24200010299683</v>
       </c>
       <c r="G265" t="n">
-        <v>4.83098936080933</v>
+        <v>4.83098840713501</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>4.78300428390503</v>
+        <v>4.78300380706787</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G267" t="n">
-        <v>4.54153156280518</v>
+        <v>4.54153203964233</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G269" t="n">
-        <v>4.53534030914307</v>
+        <v>4.53534126281738</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G270" t="n">
-        <v>4.53534030914307</v>
+        <v>4.53534126281738</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G273" t="n">
-        <v>4.91457509994507</v>
+        <v>4.91457605361938</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G275" t="n">
-        <v>5.02602386474609</v>
+        <v>5.02602434158325</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>6.44600009918213</v>
       </c>
       <c r="G276" t="n">
-        <v>4.9888744354248</v>
+        <v>4.98887491226196</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.34600019454956</v>
       </c>
       <c r="G278" t="n">
-        <v>4.91147994995117</v>
+        <v>4.91148042678833</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>5.01518869400024</v>
+        <v>5.0151891708374</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G282" t="n">
-        <v>4.79074382781982</v>
+        <v>4.79074335098267</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G287" t="n">
-        <v>4.80467462539673</v>
+        <v>4.80467557907104</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>6.23400020599365</v>
       </c>
       <c r="G289" t="n">
-        <v>4.82479810714722</v>
+        <v>4.82479763031006</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G290" t="n">
-        <v>4.93005466461182</v>
+        <v>4.93005418777466</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>6.32600021362305</v>
       </c>
       <c r="G291" t="n">
-        <v>4.89600133895874</v>
+        <v>4.89600086212158</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.42399978637695</v>
       </c>
       <c r="G292" t="n">
-        <v>4.97184801101685</v>
+        <v>4.97184753417969</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G293" t="n">
-        <v>5.02602386474609</v>
+        <v>5.02602434158325</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G295" t="n">
-        <v>4.79848289489746</v>
+        <v>4.79848337173462</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>6.24399995803833</v>
       </c>
       <c r="G296" t="n">
-        <v>4.83253717422485</v>
+        <v>4.8325366973877</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G297" t="n">
-        <v>4.80467462539673</v>
+        <v>4.80467557907104</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>6.43400001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>4.97958755493164</v>
+        <v>4.97958707809448</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G303" t="n">
-        <v>4.53534030914307</v>
+        <v>4.53534126281738</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>4.58487367630005</v>
+        <v>4.58487319946289</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.00799989700317</v>
       </c>
       <c r="G306" t="n">
-        <v>4.6498851776123</v>
+        <v>4.64988470077515</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.72599983215332</v>
       </c>
       <c r="G308" t="n">
-        <v>4.43163108825684</v>
+        <v>4.43163156509399</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G309" t="n">
-        <v>4.38674211502075</v>
+        <v>4.38674259185791</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G313" t="n">
-        <v>4.27529382705688</v>
+        <v>4.27529335021973</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>5.55399990081787</v>
       </c>
       <c r="G315" t="n">
-        <v>4.29851245880127</v>
+        <v>4.29851198196411</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.44600009918213</v>
       </c>
       <c r="G316" t="n">
-        <v>4.21492624282837</v>
+        <v>4.21492576599121</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G317" t="n">
-        <v>4.40531730651855</v>
+        <v>4.40531778335571</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.63800001144409</v>
       </c>
       <c r="G318" t="n">
-        <v>4.36352348327637</v>
+        <v>4.36352396011353</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G319" t="n">
-        <v>4.48116445541382</v>
+        <v>4.48116397857666</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.9980001449585</v>
       </c>
       <c r="G321" t="n">
-        <v>4.64214563369751</v>
+        <v>4.64214611053467</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G322" t="n">
-        <v>4.69013071060181</v>
+        <v>4.69013023376465</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>6.06199979782104</v>
       </c>
       <c r="G324" t="n">
-        <v>4.69167804718018</v>
+        <v>4.69167852401733</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>4.65917205810547</v>
+        <v>4.65917253494263</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>6.05200004577637</v>
       </c>
       <c r="G327" t="n">
-        <v>4.68393898010254</v>
+        <v>4.68393850326538</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>4.72108840942383</v>
+        <v>4.72108888626099</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>6.02799987792969</v>
       </c>
       <c r="G329" t="n">
-        <v>4.66536378860474</v>
+        <v>4.66536426544189</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>6.04400014877319</v>
       </c>
       <c r="G332" t="n">
-        <v>4.67774772644043</v>
+        <v>4.67774724960327</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G336" t="n">
-        <v>4.41460466384888</v>
+        <v>4.41460418701172</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.77600002288818</v>
       </c>
       <c r="G338" t="n">
-        <v>4.47032928466797</v>
+        <v>4.47032833099365</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.98199987411499</v>
       </c>
       <c r="G339" t="n">
-        <v>4.62976264953613</v>
+        <v>4.62976217269897</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G341" t="n">
-        <v>4.49199914932251</v>
+        <v>4.49200010299683</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>5.98400020599365</v>
       </c>
       <c r="G346" t="n">
-        <v>4.63131046295166</v>
+        <v>4.63131093978882</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.07399988174438</v>
       </c>
       <c r="G347" t="n">
-        <v>4.70096588134766</v>
+        <v>4.7009654045105</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G348" t="n">
-        <v>4.65452814102173</v>
+        <v>4.65452861785889</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G351" t="n">
-        <v>4.72108840942383</v>
+        <v>4.72108888626099</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>6.05800008773804</v>
       </c>
       <c r="G353" t="n">
-        <v>4.68858242034912</v>
+        <v>4.68858289718628</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G354" t="n">
-        <v>4.69477415084839</v>
+        <v>4.69477462768555</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>4.56629848480225</v>
+        <v>4.5662989616394</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>6.15399980545044</v>
       </c>
       <c r="G358" t="n">
-        <v>4.76288080215454</v>
+        <v>4.7628812789917</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>4.72108840942383</v>
+        <v>4.72108888626099</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G360" t="n">
-        <v>4.67465162277222</v>
+        <v>4.67465114593506</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>4.65917205810547</v>
+        <v>4.65917253494263</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.83799982070923</v>
       </c>
       <c r="G366" t="n">
-        <v>4.51831436157227</v>
+        <v>4.51831388473511</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>4.61273527145386</v>
+        <v>4.61273574829102</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.97200012207031</v>
       </c>
       <c r="G368" t="n">
-        <v>4.62202310562134</v>
+        <v>4.6220235824585</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G369" t="n">
-        <v>4.67000818252563</v>
+        <v>4.67000770568848</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G370" t="n">
-        <v>4.67000818252563</v>
+        <v>4.67000770568848</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G371" t="n">
-        <v>4.68548631668091</v>
+        <v>4.68548679351807</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>5.84600019454956</v>
       </c>
       <c r="G373" t="n">
-        <v>4.52450561523438</v>
+        <v>4.52450513839722</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>5.82800006866455</v>
       </c>
       <c r="G378" t="n">
-        <v>4.51057481765747</v>
+        <v>4.51057434082031</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G379" t="n">
-        <v>4.64059734344482</v>
+        <v>4.64059686660767</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G380" t="n">
-        <v>4.79848289489746</v>
+        <v>4.79848337173462</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>6.24599981307983</v>
       </c>
       <c r="G381" t="n">
-        <v>4.83408498764038</v>
+        <v>4.83408451080322</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G382" t="n">
-        <v>4.86813831329346</v>
+        <v>4.86813926696777</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.26800012588501</v>
       </c>
       <c r="G383" t="n">
-        <v>4.8511118888855</v>
+        <v>4.85111141204834</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>4.79074382781982</v>
+        <v>4.79074335098267</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G386" t="n">
-        <v>4.91612339019775</v>
+        <v>4.91612386703491</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.60200023651123</v>
       </c>
       <c r="G387" t="n">
-        <v>5.10961103439331</v>
+        <v>5.10961151123047</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G389" t="n">
-        <v>5.02757263183594</v>
+        <v>5.02757215499878</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G392" t="n">
-        <v>4.96875143051147</v>
+        <v>4.96875238418579</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.4060001373291</v>
       </c>
       <c r="G394" t="n">
-        <v>4.95791721343994</v>
+        <v>4.95791673660278</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G395" t="n">
-        <v>5.02602386474609</v>
+        <v>5.02602434158325</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G396" t="n">
-        <v>4.99971055984497</v>
+        <v>4.99970960617065</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>6.17799997329712</v>
       </c>
       <c r="G399" t="n">
-        <v>4.7814564704895</v>
+        <v>4.78145694732666</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>5.97399997711182</v>
       </c>
       <c r="G400" t="n">
-        <v>4.62357139587402</v>
+        <v>4.62357091903687</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>4.56629848480225</v>
+        <v>4.5662989616394</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G406" t="n">
-        <v>4.40376996994019</v>
+        <v>4.40376949310303</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>5.78399991989136</v>
       </c>
       <c r="G408" t="n">
-        <v>4.47652101516724</v>
+        <v>4.47652006149292</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G410" t="n">
-        <v>4.37493562698364</v>
+        <v>4.3749361038208</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G412" t="n">
-        <v>4.36695146560669</v>
+        <v>4.36695194244385</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G414" t="n">
-        <v>4.25039386749268</v>
+        <v>4.25039339065552</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G416" t="n">
-        <v>4.14660835266113</v>
+        <v>4.14660882949829</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G418" t="n">
-        <v>4.1434154510498</v>
+        <v>4.14341449737549</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G420" t="n">
-        <v>4.08114433288574</v>
+        <v>4.0811448097229</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.25600004196167</v>
       </c>
       <c r="G421" t="n">
-        <v>4.19610595703125</v>
+        <v>4.19610643386841</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5.17799997329712</v>
       </c>
       <c r="G422" t="n">
-        <v>4.13383483886719</v>
+        <v>4.13383531570435</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G424" t="n">
-        <v>4.1434154510498</v>
+        <v>4.14341449737549</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.32800006866455</v>
       </c>
       <c r="G426" t="n">
-        <v>4.25358724594116</v>
+        <v>4.253586769104</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G427" t="n">
-        <v>4.13223886489868</v>
+        <v>4.13223838806152</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.25</v>
       </c>
       <c r="G428" t="n">
-        <v>4.19131565093994</v>
+        <v>4.19131660461426</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.29199981689453</v>
       </c>
       <c r="G429" t="n">
-        <v>4.22484683990479</v>
+        <v>4.22484636306763</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.2519998550415</v>
       </c>
       <c r="G430" t="n">
-        <v>4.19291305541992</v>
+        <v>4.19291257858276</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>5.2979998588562</v>
       </c>
       <c r="G431" t="n">
-        <v>4.22963619232178</v>
+        <v>4.22963666915894</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G432" t="n">
-        <v>4.27913475036621</v>
+        <v>4.27913427352905</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>5.47599983215332</v>
       </c>
       <c r="G433" t="n">
-        <v>4.371741771698</v>
+        <v>4.37174224853516</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G435" t="n">
-        <v>4.35577535629272</v>
+        <v>4.35577487945557</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G436" t="n">
-        <v>4.29829406738281</v>
+        <v>4.29829454421997</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>4.2312331199646</v>
+        <v>4.23123407363892</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5.19600009918213</v>
       </c>
       <c r="G438" t="n">
-        <v>4.14820528030396</v>
+        <v>4.14820623397827</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>5.30600023269653</v>
       </c>
       <c r="G440" t="n">
-        <v>4.23602342605591</v>
+        <v>4.23602390289307</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>4.15938234329224</v>
+        <v>4.15938282012939</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5.25</v>
       </c>
       <c r="G442" t="n">
-        <v>4.19131565093994</v>
+        <v>4.19131660461426</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>4.2312331199646</v>
+        <v>4.23123407363892</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G446" t="n">
-        <v>4.25039386749268</v>
+        <v>4.25039339065552</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>5.39400005340576</v>
       </c>
       <c r="G447" t="n">
-        <v>4.30627775192261</v>
+        <v>4.30627822875977</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5.67799997329712</v>
       </c>
       <c r="G449" t="n">
-        <v>4.53300809860229</v>
+        <v>4.53300857543945</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54737901687622</v>
+        <v>4.54737854003906</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>5.55399990081787</v>
       </c>
       <c r="G451" t="n">
-        <v>4.43401336669922</v>
+        <v>4.43401288986206</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>5.36399984359741</v>
       </c>
       <c r="G452" t="n">
-        <v>4.28232717514038</v>
+        <v>4.28232765197754</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G453" t="n">
-        <v>4.15139818191528</v>
+        <v>4.1513991355896</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G454" t="n">
-        <v>4.14022159576416</v>
+        <v>4.14022207260132</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G455" t="n">
-        <v>4.17534923553467</v>
+        <v>4.17534971237183</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G457" t="n">
-        <v>4.63359928131104</v>
+        <v>4.63359975814819</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G458" t="n">
-        <v>4.55057144165039</v>
+        <v>4.55057191848755</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.60799980163574</v>
       </c>
       <c r="G459" t="n">
-        <v>4.47712373733521</v>
+        <v>4.47712421417236</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.38800001144409</v>
       </c>
       <c r="G463" t="n">
-        <v>4.3014874458313</v>
+        <v>4.30148792266846</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.01599979400635</v>
       </c>
       <c r="G464" t="n">
-        <v>4.00450325012207</v>
+        <v>4.00450277328491</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>3.87197732925415</v>
+        <v>3.87197804450989</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G466" t="n">
-        <v>3.76819205284119</v>
+        <v>3.76819252967834</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>4.85699987411499</v>
       </c>
       <c r="G468" t="n">
-        <v>3.87756609916687</v>
+        <v>3.87756562232971</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>3.70831656455994</v>
+        <v>3.70831727981567</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G470" t="n">
-        <v>3.67398762702942</v>
+        <v>3.67398810386658</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.75299978256226</v>
       </c>
       <c r="G471" t="n">
-        <v>3.79453825950623</v>
+        <v>3.79453778266907</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G472" t="n">
-        <v>3.64444923400879</v>
+        <v>3.64444899559021</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G474" t="n">
-        <v>3.67957663536072</v>
+        <v>3.67957711219788</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G476" t="n">
-        <v>3.74264597892761</v>
+        <v>3.74264574050903</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.81300020217896</v>
       </c>
       <c r="G477" t="n">
-        <v>3.84243893623352</v>
+        <v>3.8424391746521</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.6729998588562</v>
       </c>
       <c r="G478" t="n">
-        <v>3.73067021369934</v>
+        <v>3.73066997528076</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.84700012207031</v>
       </c>
       <c r="G480" t="n">
-        <v>3.86958312988281</v>
+        <v>3.86958265304565</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.82407689094543</v>
+        <v>3.82407736778259</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>3.76020932197571</v>
+        <v>3.76020956039429</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.6729998588562</v>
       </c>
       <c r="G485" t="n">
-        <v>3.73067021369934</v>
+        <v>3.73066997528076</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.97300004959106</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97017359733582</v>
+        <v>3.97017502784729</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G490" t="n">
-        <v>4.31585788726807</v>
+        <v>4.31585836410522</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G491" t="n">
-        <v>4.26316690444946</v>
+        <v>4.26316738128662</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>4.4228367805481</v>
+        <v>4.42283630371094</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G493" t="n">
-        <v>4.51863765716553</v>
+        <v>4.51863813400269</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>4.55057144165039</v>
+        <v>4.55057191848755</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G496" t="n">
-        <v>4.52183103561401</v>
+        <v>4.52183151245117</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G498" t="n">
-        <v>4.52183103561401</v>
+        <v>4.52183151245117</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G500" t="n">
-        <v>4.28871440887451</v>
+        <v>4.28871393203735</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G502" t="n">
-        <v>4.31585788726807</v>
+        <v>4.31585836410522</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>4.4228367805481</v>
+        <v>4.42283630371094</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G504" t="n">
-        <v>4.33342170715332</v>
+        <v>4.333420753479</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.25</v>
       </c>
       <c r="G506" t="n">
-        <v>4.19131565093994</v>
+        <v>4.19131660461426</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G507" t="n">
-        <v>4.17055988311768</v>
+        <v>4.17055892944336</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.12200021743774</v>
       </c>
       <c r="G509" t="n">
-        <v>4.08912754058838</v>
+        <v>4.08912801742554</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G513" t="n">
-        <v>4.31585788726807</v>
+        <v>4.31585836410522</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G514" t="n">
-        <v>4.33342170715332</v>
+        <v>4.333420753479</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.69399976730347</v>
       </c>
       <c r="G516" t="n">
-        <v>4.54578161239624</v>
+        <v>4.54578113555908</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G518" t="n">
-        <v>4.31585788726807</v>
+        <v>4.31585836410522</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G520" t="n">
-        <v>4.40048265457153</v>
+        <v>4.40048217773438</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.18200016021729</v>
       </c>
       <c r="G527" t="n">
-        <v>4.13702821731567</v>
+        <v>4.13702869415283</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G530" t="n">
-        <v>4.28552103042603</v>
+        <v>4.28552055358887</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.28711748123169</v>
+        <v>4.28711795806885</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>4.37493562698364</v>
+        <v>4.3749361038208</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.44799995422363</v>
       </c>
       <c r="G533" t="n">
-        <v>4.34938907623291</v>
+        <v>4.34938859939575</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.4980001449585</v>
       </c>
       <c r="G534" t="n">
-        <v>4.38930606842041</v>
+        <v>4.38930559158325</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.4148530960083</v>
+        <v>4.41485261917114</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G538" t="n">
-        <v>4.24879693984985</v>
+        <v>4.24879741668701</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.27600002288818</v>
       </c>
       <c r="G539" t="n">
-        <v>4.21207284927368</v>
+        <v>4.21207332611084</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>4.1434154510498</v>
+        <v>4.14341449737549</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.27600002288818</v>
       </c>
       <c r="G544" t="n">
-        <v>4.21207284927368</v>
+        <v>4.21207332611084</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.26399993896484</v>
       </c>
       <c r="G547" t="n">
-        <v>4.20249319076538</v>
+        <v>4.20249271392822</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G548" t="n">
-        <v>4.11148118972778</v>
+        <v>4.11148166656494</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G549" t="n">
-        <v>4.06996774673462</v>
+        <v>4.06996726989746</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G550" t="n">
-        <v>4.03164625167847</v>
+        <v>4.03164672851562</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G551" t="n">
-        <v>4.06996774673462</v>
+        <v>4.06996726989746</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.14200019836426</v>
       </c>
       <c r="G553" t="n">
-        <v>4.10509443283081</v>
+        <v>4.10509538650513</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G555" t="n">
-        <v>4.10669136047363</v>
+        <v>4.10669088363647</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G556" t="n">
-        <v>4.17055988311768</v>
+        <v>4.17055892944336</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G558" t="n">
-        <v>4.17055988311768</v>
+        <v>4.17055892944336</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G560" t="n">
-        <v>4.20089673995972</v>
+        <v>4.20089626312256</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.21600008010864</v>
       </c>
       <c r="G564" t="n">
-        <v>4.16417264938354</v>
+        <v>4.16417217254639</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G565" t="n">
-        <v>4.15299510955811</v>
+        <v>4.15299558639526</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G566" t="n">
-        <v>4.10349750518799</v>
+        <v>4.10349798202515</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>4.15938234329224</v>
+        <v>4.15938282012939</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.14599990844727</v>
       </c>
       <c r="G569" t="n">
-        <v>4.1082878112793</v>
+        <v>4.10828828811646</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G571" t="n">
-        <v>4.24720048904419</v>
+        <v>4.24720096588135</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>5.28599977493286</v>
       </c>
       <c r="G572" t="n">
-        <v>4.22005605697632</v>
+        <v>4.22005653381348</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G573" t="n">
-        <v>4.2312331199646</v>
+        <v>4.23123407363892</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.25400018692017</v>
       </c>
       <c r="G574" t="n">
-        <v>4.19450998306274</v>
+        <v>4.19450902938843</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G575" t="n">
-        <v>4.06358098983765</v>
+        <v>4.06358051300049</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.02799987792969</v>
       </c>
       <c r="G576" t="n">
-        <v>4.01408386230469</v>
+        <v>4.01408338546753</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G577" t="n">
-        <v>4.05080699920654</v>
+        <v>4.0508074760437</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>4.05559730529785</v>
+        <v>4.05559682846069</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G582" t="n">
-        <v>3.92147541046143</v>
+        <v>3.92147564888</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.78900003433228</v>
       </c>
       <c r="G583" t="n">
-        <v>3.8232786655426</v>
+        <v>3.82327890396118</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G584" t="n">
-        <v>3.64524722099304</v>
+        <v>3.64524745941162</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.58300018310547</v>
       </c>
       <c r="G585" t="n">
-        <v>3.65881943702698</v>
+        <v>3.6588191986084</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G588" t="n">
-        <v>3.49036836624146</v>
+        <v>3.49036908149719</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.59299993515015</v>
       </c>
       <c r="G592" t="n">
-        <v>3.66680264472961</v>
+        <v>3.66680240631104</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>3.62848210334778</v>
+        <v>3.62848258018494</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.45100021362305</v>
       </c>
       <c r="G595" t="n">
-        <v>3.55343794822693</v>
+        <v>3.55343818664551</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G596" t="n">
-        <v>3.67957663536072</v>
+        <v>3.67957711219788</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G599" t="n">
-        <v>3.76819205284119</v>
+        <v>3.76819252967834</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.70900011062622</v>
       </c>
       <c r="G600" t="n">
-        <v>3.75941061973572</v>
+        <v>3.75941109657288</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.86600017547607</v>
       </c>
       <c r="G601" t="n">
-        <v>3.88475108146667</v>
+        <v>3.88475179672241</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.75299978256226</v>
       </c>
       <c r="G603" t="n">
-        <v>3.79453825950623</v>
+        <v>3.79453778266907</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.45900011062622</v>
       </c>
       <c r="G604" t="n">
-        <v>3.5598247051239</v>
+        <v>3.55982446670532</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.36100006103516</v>
       </c>
       <c r="G605" t="n">
-        <v>3.48158669471741</v>
+        <v>3.48158693313599</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G606" t="n">
-        <v>3.55742907524109</v>
+        <v>3.55742931365967</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G607" t="n">
-        <v>3.44885468482971</v>
+        <v>3.44885420799255</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.25299978256226</v>
       </c>
       <c r="G608" t="n">
-        <v>3.39536476135254</v>
+        <v>3.39536499977112</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>3.27321815490723</v>
+        <v>3.27321791648865</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.01700019836426</v>
       </c>
       <c r="G611" t="n">
-        <v>3.20695543289185</v>
+        <v>3.20695567131042</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>3.12951612472534</v>
+        <v>3.12951588630676</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.13700008392334</v>
       </c>
       <c r="G617" t="n">
-        <v>2.50441145896912</v>
+        <v>2.50441122055054</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G618" t="n">
-        <v>2.79740405082703</v>
+        <v>2.79740381240845</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G619" t="n">
-        <v>2.54832005500793</v>
+        <v>2.54832029342651</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G620" t="n">
-        <v>2.68004727363586</v>
+        <v>2.68004751205444</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.61899995803833</v>
       </c>
       <c r="G621" t="n">
-        <v>2.88921403884888</v>
+        <v>2.8892138004303</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G622" t="n">
-        <v>3.04169774055481</v>
+        <v>3.04169797897339</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G623" t="n">
-        <v>2.87404489517212</v>
+        <v>2.8740451335907</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G628" t="n">
-        <v>2.65450000762939</v>
+        <v>2.65450048446655</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>3.34100008010864</v>
       </c>
       <c r="G629" t="n">
-        <v>2.66727352142334</v>
+        <v>2.66727375984192</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44134187698364</v>
+        <v>2.44134163856506</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G634" t="n">
-        <v>2.55790042877197</v>
+        <v>2.55790019035339</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G635" t="n">
-        <v>2.56748080253601</v>
+        <v>2.56748032569885</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.38199996948242</v>
       </c>
       <c r="G636" t="n">
-        <v>2.70000600814819</v>
+        <v>2.70000576972961</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G638" t="n">
-        <v>2.64731502532959</v>
+        <v>2.64731526374817</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G639" t="n">
-        <v>2.49083924293518</v>
+        <v>2.4908390045166</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.28600001335144</v>
       </c>
       <c r="G640" t="n">
-        <v>2.62336444854736</v>
+        <v>2.62336468696594</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>2.62655806541443</v>
+        <v>2.62655782699585</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>2.71437621116638</v>
+        <v>2.7143759727478</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G643" t="n">
-        <v>2.65689563751221</v>
+        <v>2.65689539909363</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G645" t="n">
-        <v>2.64731502532959</v>
+        <v>2.64731526374817</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G646" t="n">
-        <v>2.68004727363586</v>
+        <v>2.68004751205444</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G649" t="n">
-        <v>2.81816101074219</v>
+        <v>2.81816124916077</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3.55399990081787</v>
       </c>
       <c r="G650" t="n">
-        <v>2.83732151985168</v>
+        <v>2.83732128143311</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G651" t="n">
-        <v>2.81017780303955</v>
+        <v>2.81017756462097</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G652" t="n">
-        <v>2.83253121376038</v>
+        <v>2.83253145217896</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G653" t="n">
-        <v>2.95387983322144</v>
+        <v>2.95388007164001</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>2.95387983322144</v>
+        <v>2.95388007164001</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G658" t="n">
-        <v>2.87005352973938</v>
+        <v>2.87005376815796</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>3.58699989318848</v>
       </c>
       <c r="G659" t="n">
-        <v>2.86366701126099</v>
+        <v>2.86366677284241</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.59699988365173</v>
       </c>
       <c r="G660" t="n">
-        <v>2.87165021896362</v>
+        <v>2.87164998054504</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G661" t="n">
-        <v>2.92593765258789</v>
+        <v>2.92593789100647</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.45099997520447</v>
       </c>
       <c r="G662" t="n">
-        <v>2.75509166717529</v>
+        <v>2.75509190559387</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3.52699995040894</v>
       </c>
       <c r="G663" t="n">
-        <v>2.81576585769653</v>
+        <v>2.81576609611511</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.58899998664856</v>
       </c>
       <c r="G664" t="n">
-        <v>2.86526370048523</v>
+        <v>2.86526346206665</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.57699990272522</v>
       </c>
       <c r="G665" t="n">
-        <v>2.85568308830261</v>
+        <v>2.85568332672119</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G666" t="n">
-        <v>2.89320588111877</v>
+        <v>2.8932056427002</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>2.95387983322144</v>
+        <v>2.95388007164001</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>3.21733427047729</v>
+        <v>3.21733379364014</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G671" t="n">
-        <v>3.21094703674316</v>
+        <v>3.21094727516174</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G673" t="n">
-        <v>3.37380957603455</v>
+        <v>3.37380933761597</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.20699977874756</v>
       </c>
       <c r="G674" t="n">
-        <v>3.35864114761353</v>
+        <v>3.3586413860321</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G676" t="n">
-        <v>3.47919130325317</v>
+        <v>3.47919154167175</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G678" t="n">
-        <v>3.36502814292908</v>
+        <v>3.3650279045105</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G680" t="n">
-        <v>3.11354923248291</v>
+        <v>3.11354899406433</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.9210000038147</v>
       </c>
       <c r="G681" t="n">
-        <v>3.13031435012817</v>
+        <v>3.13031411170959</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.11354923248291</v>
+        <v>3.11354899406433</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.01100015640259</v>
       </c>
       <c r="G687" t="n">
-        <v>3.20216584205627</v>
+        <v>3.2021656036377</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G688" t="n">
-        <v>3.04010128974915</v>
+        <v>3.04010152816772</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G689" t="n">
-        <v>3.04808449745178</v>
+        <v>3.04808497428894</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>3.04010128974915</v>
+        <v>3.04010152816772</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G693" t="n">
-        <v>2.93791270256042</v>
+        <v>2.937912940979</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G694" t="n">
-        <v>3.05447125434875</v>
+        <v>3.05447149276733</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G695" t="n">
-        <v>2.96505641937256</v>
+        <v>2.96505689620972</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.78099989891052</v>
       </c>
       <c r="G697" t="n">
-        <v>3.01854610443115</v>
+        <v>3.01854562759399</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G700" t="n">
-        <v>2.96585488319397</v>
+        <v>2.96585464477539</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G701" t="n">
-        <v>3.02094078063965</v>
+        <v>3.02094101905823</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G702" t="n">
-        <v>2.96026659011841</v>
+        <v>2.96026635169983</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G704" t="n">
-        <v>3.03371453285217</v>
+        <v>3.03371477127075</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>3.76900005340576</v>
       </c>
       <c r="G705" t="n">
-        <v>3.00896573066711</v>
+        <v>3.00896596908569</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>3.78099989891052</v>
       </c>
       <c r="G709" t="n">
-        <v>3.01854610443115</v>
+        <v>3.01854562759399</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>3.61899995803833</v>
       </c>
       <c r="G710" t="n">
-        <v>2.88921403884888</v>
+        <v>2.8892138004303</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>3.58899998664856</v>
       </c>
       <c r="G713" t="n">
-        <v>2.86526370048523</v>
+        <v>2.86526346206665</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G714" t="n">
-        <v>2.77345371246338</v>
+        <v>2.77345323562622</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.46399998664856</v>
       </c>
       <c r="G716" t="n">
-        <v>2.76547002792358</v>
+        <v>2.76547026634216</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>2.89001226425171</v>
+        <v>2.89001202583313</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G718" t="n">
-        <v>2.94908952713013</v>
+        <v>2.94909000396729</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G720" t="n">
-        <v>2.7111828327179</v>
+        <v>2.71118259429932</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>3.73300004005432</v>
       </c>
       <c r="G728" t="n">
-        <v>2.98022532463074</v>
+        <v>2.98022508621216</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>3.6470000743866</v>
       </c>
       <c r="G729" t="n">
-        <v>2.9115674495697</v>
+        <v>2.91156792640686</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G730" t="n">
-        <v>2.8548846244812</v>
+        <v>2.85488486289978</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>2.96186327934265</v>
+        <v>2.96186351776123</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>3.62100005149841</v>
       </c>
       <c r="G736" t="n">
-        <v>2.89081072807312</v>
+        <v>2.89081048965454</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G738" t="n">
-        <v>2.87085175514221</v>
+        <v>2.87085151672363</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.90597915649414</v>
+        <v>2.90597939491272</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G742" t="n">
-        <v>3.04489135742188</v>
+        <v>3.0448911190033</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G744" t="n">
-        <v>3.11354923248291</v>
+        <v>3.11354899406433</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G746" t="n">
-        <v>3.08321213722229</v>
+        <v>3.08321166038513</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>3.94799995422363</v>
       </c>
       <c r="G749" t="n">
-        <v>3.15186977386475</v>
+        <v>3.15186953544617</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.95900011062622</v>
       </c>
       <c r="G750" t="n">
-        <v>3.16065144538879</v>
+        <v>3.16065168380737</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>3.81900000572205</v>
       </c>
       <c r="G753" t="n">
-        <v>3.04888296127319</v>
+        <v>3.04888319969177</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G754" t="n">
-        <v>2.98980522155762</v>
+        <v>2.9898054599762</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G755" t="n">
-        <v>2.90597915649414</v>
+        <v>2.90597939491272</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G756" t="n">
-        <v>3.01774740219116</v>
+        <v>3.01774716377258</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.62100005149841</v>
       </c>
       <c r="G761" t="n">
-        <v>2.89081072807312</v>
+        <v>2.89081048965454</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>3.8529999256134</v>
       </c>
       <c r="G765" t="n">
-        <v>3.07602715492249</v>
+        <v>3.07602667808533</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G766" t="n">
-        <v>3.11674237251282</v>
+        <v>3.11674213409424</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G770" t="n">
-        <v>2.93950963020325</v>
+        <v>2.93950986862183</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G772" t="n">
-        <v>3.06963992118835</v>
+        <v>3.06964015960693</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.68899989128113</v>
       </c>
       <c r="G773" t="n">
-        <v>2.94509816169739</v>
+        <v>2.94509792327881</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.78299999237061</v>
       </c>
       <c r="G774" t="n">
-        <v>3.02014255523682</v>
+        <v>3.02014231681824</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.94300007820129</v>
       </c>
       <c r="G776" t="n">
-        <v>3.14787769317627</v>
+        <v>3.14787793159485</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G777" t="n">
-        <v>3.00577259063721</v>
+        <v>3.00577211380005</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.4539999961853</v>
       </c>
       <c r="G779" t="n">
-        <v>2.75748682022095</v>
+        <v>2.75748658180237</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G781" t="n">
-        <v>2.91396236419678</v>
+        <v>2.91396284103394</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G783" t="n">
-        <v>2.96505641937256</v>
+        <v>2.96505689620972</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G786" t="n">
-        <v>3.36582660675049</v>
+        <v>3.36582636833191</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.27899980545044</v>
       </c>
       <c r="G788" t="n">
-        <v>3.4161217212677</v>
+        <v>3.41612195968628</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.22900009155273</v>
       </c>
       <c r="G791" t="n">
-        <v>3.37620520591736</v>
+        <v>3.3762047290802</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.26300001144409</v>
       </c>
       <c r="G792" t="n">
-        <v>3.40334892272949</v>
+        <v>3.40334868431091</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.28700017929077</v>
       </c>
       <c r="G793" t="n">
-        <v>3.42250895500183</v>
+        <v>3.42250919342041</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G796" t="n">
-        <v>3.31792569160461</v>
+        <v>3.31792545318604</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G797" t="n">
-        <v>3.40734028816223</v>
+        <v>3.40734052658081</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G800" t="n">
-        <v>3.46881294250488</v>
+        <v>3.46881246566772</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.5</v>
       </c>
       <c r="G801" t="n">
-        <v>3.59255647659302</v>
+        <v>3.5925567150116</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.50099992752075</v>
       </c>
       <c r="G802" t="n">
-        <v>3.59335470199585</v>
+        <v>3.59335517883301</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.42199993133545</v>
       </c>
       <c r="G804" t="n">
-        <v>3.53028559684753</v>
+        <v>3.53028583526611</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>3.55663084983826</v>
+        <v>3.55663108825684</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.45900011062622</v>
       </c>
       <c r="G807" t="n">
-        <v>3.5598247051239</v>
+        <v>3.55982446670532</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.55299997329712</v>
       </c>
       <c r="G808" t="n">
-        <v>3.63486886024475</v>
+        <v>3.63486862182617</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.48899984359741</v>
       </c>
       <c r="G811" t="n">
-        <v>3.58377456665039</v>
+        <v>3.58377432823181</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G812" t="n">
-        <v>3.51272177696228</v>
+        <v>3.51272201538086</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G814" t="n">
-        <v>3.73945236206055</v>
+        <v>3.73945212364197</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.35099983215332</v>
       </c>
       <c r="G817" t="n">
-        <v>3.47360253334045</v>
+        <v>3.47360301017761</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.40299987792969</v>
       </c>
       <c r="G818" t="n">
-        <v>3.51511716842651</v>
+        <v>3.51511693000793</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>3.56062245368958</v>
+        <v>3.56062269210815</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.35900020599365</v>
       </c>
       <c r="G822" t="n">
-        <v>3.47999024391174</v>
+        <v>3.47998976707458</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.29300022125244</v>
       </c>
       <c r="G824" t="n">
-        <v>3.42729902267456</v>
+        <v>3.42729926109314</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>3.5446560382843</v>
+        <v>3.54465627670288</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G826" t="n">
-        <v>3.54944610595703</v>
+        <v>3.54944562911987</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G829" t="n">
-        <v>3.58297634124756</v>
+        <v>3.58297610282898</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G830" t="n">
-        <v>3.5446560382843</v>
+        <v>3.54465627670288</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G831" t="n">
-        <v>3.46322417259216</v>
+        <v>3.46322441101074</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G832" t="n">
-        <v>3.53667211532593</v>
+        <v>3.53667235374451</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.47900009155273</v>
       </c>
       <c r="G834" t="n">
-        <v>3.57579135894775</v>
+        <v>3.57579112052917</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.19399976730347</v>
       </c>
       <c r="G837" t="n">
-        <v>3.34826278686523</v>
+        <v>3.34826254844666</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G838" t="n">
-        <v>3.44885468482971</v>
+        <v>3.44885420799255</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.26900005340576</v>
       </c>
       <c r="G839" t="n">
-        <v>3.40813875198364</v>
+        <v>3.40813851356506</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.27899980545044</v>
       </c>
       <c r="G840" t="n">
-        <v>3.4161217212677</v>
+        <v>3.41612195968628</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G841" t="n">
-        <v>3.44087100028992</v>
+        <v>3.44087052345276</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G842" t="n">
-        <v>3.41692090034485</v>
+        <v>3.41692066192627</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G845" t="n">
-        <v>3.72029161453247</v>
+        <v>3.72029185295105</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.67600011825562</v>
       </c>
       <c r="G846" t="n">
-        <v>3.733065366745</v>
+        <v>3.73306560516357</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.72300004959106</v>
       </c>
       <c r="G847" t="n">
-        <v>3.77058815956116</v>
+        <v>3.77058792114258</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G849" t="n">
-        <v>3.71630096435547</v>
+        <v>3.71630024909973</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.68100023269653</v>
       </c>
       <c r="G851" t="n">
-        <v>3.73705697059631</v>
+        <v>3.73705792427063</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>3.78815078735352</v>
+        <v>3.78815150260925</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>3.76420140266418</v>
+        <v>3.76420116424561</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G854" t="n">
-        <v>3.68995475769043</v>
+        <v>3.68995499610901</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.60099983215332</v>
       </c>
       <c r="G855" t="n">
-        <v>3.67318916320801</v>
+        <v>3.67318940162659</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>3.75861310958862</v>
+        <v>3.75861239433289</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>3.90790295600891</v>
+        <v>3.90790319442749</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.77099990844727</v>
       </c>
       <c r="G858" t="n">
-        <v>3.80890798568726</v>
+        <v>3.80890870094299</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.81400012969971</v>
       </c>
       <c r="G859" t="n">
-        <v>3.84323763847351</v>
+        <v>3.84323692321777</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G860" t="n">
-        <v>3.81609392166138</v>
+        <v>3.81609344482422</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G861" t="n">
-        <v>3.81210160255432</v>
+        <v>3.8121018409729</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G862" t="n">
-        <v>3.86399483680725</v>
+        <v>3.86399459838867</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G864" t="n">
-        <v>3.89592862129211</v>
+        <v>3.89592814445496</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G865" t="n">
-        <v>3.84802722930908</v>
+        <v>3.84802746772766</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.9689998626709</v>
       </c>
       <c r="G867" t="n">
-        <v>3.96698069572449</v>
+        <v>3.96698045730591</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G868" t="n">
-        <v>3.95340871810913</v>
+        <v>3.95340895652771</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.94899988174438</v>
       </c>
       <c r="G869" t="n">
-        <v>3.95101428031921</v>
+        <v>3.9510133266449</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G870" t="n">
-        <v>3.91508793830872</v>
+        <v>3.91508865356445</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.90299987792969</v>
       </c>
       <c r="G871" t="n">
-        <v>3.91428971290588</v>
+        <v>3.91428995132446</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G872" t="n">
-        <v>3.96378755569458</v>
+        <v>3.96378707885742</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G873" t="n">
-        <v>3.9126935005188</v>
+        <v>3.91269302368164</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5</v>
       </c>
       <c r="G874" t="n">
-        <v>3.99172949790955</v>
+        <v>3.99172925949097</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>5.0939998626709</v>
       </c>
       <c r="G876" t="n">
-        <v>4.06677436828613</v>
+        <v>4.06677341461182</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.97700023651123</v>
       </c>
       <c r="G877" t="n">
-        <v>3.97336769104004</v>
+        <v>3.97336792945862</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.93599987030029</v>
       </c>
       <c r="G878" t="n">
-        <v>3.94063520431519</v>
+        <v>3.94063472747803</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G879" t="n">
-        <v>3.94622397422791</v>
+        <v>3.94622349739075</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>5.00799989700317</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99811601638794</v>
+        <v>3.99811577796936</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G881" t="n">
-        <v>3.96777939796448</v>
+        <v>3.96777892112732</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G883" t="n">
-        <v>4.14022159576416</v>
+        <v>4.14022207260132</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>5.0019998550415</v>
       </c>
       <c r="G884" t="n">
-        <v>3.99332571029663</v>
+        <v>3.99332642555237</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.02799987792969</v>
       </c>
       <c r="G886" t="n">
-        <v>4.01408386230469</v>
+        <v>4.01408338546753</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>5.05200004577637</v>
       </c>
       <c r="G887" t="n">
-        <v>4.03324317932129</v>
+        <v>4.03324365615845</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G888" t="n">
-        <v>3.99013304710388</v>
+        <v>3.99013328552246</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.9060001373291</v>
       </c>
       <c r="G889" t="n">
-        <v>3.91668486595154</v>
+        <v>3.91668462753296</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.94399976730347</v>
       </c>
       <c r="G890" t="n">
-        <v>3.94702172279358</v>
+        <v>3.94702219963074</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.9210000038147</v>
       </c>
       <c r="G892" t="n">
-        <v>3.92866063117981</v>
+        <v>3.92865967750549</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G893" t="n">
-        <v>3.92626547813416</v>
+        <v>3.926265001297</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G895" t="n">
-        <v>3.95740056037903</v>
+        <v>3.95740032196045</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G896" t="n">
-        <v>3.84802722930908</v>
+        <v>3.84802746772766</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G897" t="n">
-        <v>3.9126935005188</v>
+        <v>3.91269302368164</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.96299982070923</v>
       </c>
       <c r="G898" t="n">
-        <v>3.9621901512146</v>
+        <v>3.96219062805176</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>5.0019998550415</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99332571029663</v>
+        <v>3.99332642555237</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>5.02600002288818</v>
       </c>
       <c r="G900" t="n">
-        <v>4.01248741149902</v>
+        <v>4.01248598098755</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G901" t="n">
-        <v>3.94542503356934</v>
+        <v>3.94542527198792</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.79699993133545</v>
       </c>
       <c r="G902" t="n">
-        <v>3.829665184021</v>
+        <v>3.82966494560242</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G903" t="n">
-        <v>3.75701546669006</v>
+        <v>3.75701594352722</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G907" t="n">
-        <v>3.68436646461487</v>
+        <v>3.68436598777771</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.66099977493286</v>
       </c>
       <c r="G909" t="n">
-        <v>3.72109031677246</v>
+        <v>3.72109007835388</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G910" t="n">
-        <v>3.71630096435547</v>
+        <v>3.71630024909973</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>3.73945236206055</v>
+        <v>3.73945212364197</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G915" t="n">
-        <v>3.75222587585449</v>
+        <v>3.75222563743591</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G916" t="n">
-        <v>3.79533648490906</v>
+        <v>3.79533672332764</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>3.72029161453247</v>
+        <v>3.72029185295105</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G919" t="n">
-        <v>3.74823379516602</v>
+        <v>3.74823451042175</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G920" t="n">
-        <v>3.76499915122986</v>
+        <v>3.76499891281128</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.72900009155273</v>
       </c>
       <c r="G922" t="n">
-        <v>3.77537775039673</v>
+        <v>3.77537798881531</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G924" t="n">
-        <v>3.86399483680725</v>
+        <v>3.86399459838867</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.85699987411499</v>
       </c>
       <c r="G925" t="n">
-        <v>3.87756609916687</v>
+        <v>3.87756562232971</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G927" t="n">
-        <v>3.97097277641296</v>
+        <v>3.97097229957581</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G928" t="n">
-        <v>4.06517791748047</v>
+        <v>4.06517744064331</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>5.17799997329712</v>
       </c>
       <c r="G931" t="n">
-        <v>4.13383483886719</v>
+        <v>4.13383531570435</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G932" t="n">
-        <v>4.10349750518799</v>
+        <v>4.10349798202515</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>5.16200017929077</v>
       </c>
       <c r="G933" t="n">
-        <v>4.12106227874756</v>
+        <v>4.12106132507324</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>5.16200017929077</v>
       </c>
       <c r="G934" t="n">
-        <v>4.12106227874756</v>
+        <v>4.12106132507324</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>5.12200021743774</v>
       </c>
       <c r="G935" t="n">
-        <v>4.08912754058838</v>
+        <v>4.08912801742554</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G936" t="n">
-        <v>4.10349750518799</v>
+        <v>4.10349798202515</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>4.12744855880737</v>
+        <v>4.12744808197021</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G941" t="n">
-        <v>4.1339898109436</v>
+        <v>4.13399028778076</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G942" t="n">
-        <v>4.0755820274353</v>
+        <v>4.07558155059814</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G947" t="n">
-        <v>3.97174525260925</v>
+        <v>3.97174453735352</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G949" t="n">
-        <v>4.00338220596313</v>
+        <v>4.00338268280029</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.86899995803833</v>
       </c>
       <c r="G953" t="n">
-        <v>3.94984197616577</v>
+        <v>3.94984245300293</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.97200012207031</v>
       </c>
       <c r="G954" t="n">
-        <v>4.03339862823486</v>
+        <v>4.03339815139771</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.93100023269653</v>
       </c>
       <c r="G955" t="n">
-        <v>4.00013828277588</v>
+        <v>4.00013780593872</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G958" t="n">
-        <v>3.94254088401794</v>
+        <v>3.9425413608551</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G959" t="n">
-        <v>3.96850037574768</v>
+        <v>3.96850061416626</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G961" t="n">
-        <v>3.91495990753174</v>
+        <v>3.91495966911316</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.99900007247925</v>
       </c>
       <c r="G962" t="n">
-        <v>4.05530166625977</v>
+        <v>4.05530118942261</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G964" t="n">
-        <v>4.12912273406982</v>
+        <v>4.12912225723267</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G965" t="n">
-        <v>4.1339898109436</v>
+        <v>4.13399028778076</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>5.07600021362305</v>
       </c>
       <c r="G967" t="n">
-        <v>4.11776542663574</v>
+        <v>4.1177659034729</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>5.12400007247925</v>
       </c>
       <c r="G968" t="n">
-        <v>4.15670442581177</v>
+        <v>4.15670394897461</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G971" t="n">
-        <v>4.10640811920166</v>
+        <v>4.1064076423645</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G972" t="n">
-        <v>4.14534711837769</v>
+        <v>4.14534664154053</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G974" t="n">
-        <v>4.42116260528564</v>
+        <v>4.42116212844849</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G975" t="n">
-        <v>4.38546848297119</v>
+        <v>4.38546895980835</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>5.31400012969971</v>
       </c>
       <c r="G981" t="n">
-        <v>4.31083631515503</v>
+        <v>4.31083583831787</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G984" t="n">
-        <v>4.2069993019104</v>
+        <v>4.20699977874756</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G986" t="n">
-        <v>4.21024465560913</v>
+        <v>4.21024417877197</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>5.16200017929077</v>
       </c>
       <c r="G987" t="n">
-        <v>4.18753099441528</v>
+        <v>4.18753051757812</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>5.15199995040894</v>
       </c>
       <c r="G988" t="n">
-        <v>4.17941761016846</v>
+        <v>4.17941808700562</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.14799976348877</v>
       </c>
       <c r="G990" t="n">
-        <v>4.17617273330688</v>
+        <v>4.17617225646973</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G991" t="n">
-        <v>4.11614227294922</v>
+        <v>4.11614274978638</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G993" t="n">
-        <v>4.19888782501221</v>
+        <v>4.19888734817505</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>5.12400007247925</v>
       </c>
       <c r="G994" t="n">
-        <v>4.15670442581177</v>
+        <v>4.15670394897461</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>5.15199995040894</v>
       </c>
       <c r="G995" t="n">
-        <v>4.17941761016846</v>
+        <v>4.17941808700562</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>5.15399980545044</v>
       </c>
       <c r="G996" t="n">
-        <v>4.18104028701782</v>
+        <v>4.18104076385498</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>5.13600015640259</v>
       </c>
       <c r="G997" t="n">
-        <v>4.16643857955933</v>
+        <v>4.16643905639648</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G998" t="n">
-        <v>4.19888782501221</v>
+        <v>4.19888734817505</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>5.14599990844727</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.17455005645752</v>
+        <v>4.17455148696899</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.20213222503662</v>
+        <v>4.20213174819946</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.19888782501221</v>
+        <v>4.19888734817505</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.26703071594238</v>
+        <v>4.26703023910522</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.15994882583618</v>
+        <v>4.15994834899902</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.12100982666016</v>
+        <v>4.121009349823</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>4.12100982666016</v>
+        <v>4.121009349823</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.97661232948303</v>
+        <v>3.97661304473877</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.98699998855591</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.04556608200073</v>
+        <v>4.04556655883789</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.07233667373657</v>
+        <v>4.07233715057373</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.10478591918945</v>
+        <v>4.10478544235229</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>5.08400011062622</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.12425518035889</v>
+        <v>4.12425565719604</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.06422424316406</v>
+        <v>4.06422472000122</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>5.00600004196167</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.06097936630249</v>
+        <v>4.06097984313965</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.11614227294922</v>
+        <v>4.11614274978638</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>5.06799983978271</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.11127519607544</v>
+        <v>4.1112756729126</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.10478591918945</v>
+        <v>4.10478544235229</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.31894826889038</v>
+        <v>4.31894779205322</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>5.31199979782104</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.30921363830566</v>
+        <v>4.30921316146851</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.33192777633667</v>
+        <v>4.33192873001099</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>5.31199979782104</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.30921363830566</v>
+        <v>4.30921316146851</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.32057094573975</v>
+        <v>4.3205714225769</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.38546848297119</v>
+        <v>4.38546895980835</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.42765235900879</v>
+        <v>4.42765188217163</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.54284524917603</v>
+        <v>4.54284572601318</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>5.53800010681152</v>
       </c>
       <c r="G1040" t="n">
-        <v>4.49254989624023</v>
+        <v>4.49255037307739</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.46659088134766</v>
+        <v>4.4665904045105</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.49579429626465</v>
+        <v>4.49579477310181</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.51364231109619</v>
+        <v>4.51364183425903</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.67264175415039</v>
+        <v>4.67264127731323</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>5.84600019454956</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.74240684509277</v>
+        <v>4.74240636825562</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>5.78200006484985</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.69048881530762</v>
+        <v>4.69048833847046</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.74565124511719</v>
+        <v>4.74565076828003</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G1054" t="n">
-        <v>4.4308967590332</v>
+        <v>4.43089723587036</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>5.40399980545044</v>
       </c>
       <c r="G1055" t="n">
-        <v>4.38384580612183</v>
+        <v>4.38384628295898</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G1056" t="n">
-        <v>4.40331554412842</v>
+        <v>4.40331506729126</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>5.97399997711182</v>
       </c>
       <c r="G1065" t="n">
-        <v>4.84624338150024</v>
+        <v>4.84624242782593</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.85111093521118</v>
+        <v>4.85111045837402</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>5.95599985122681</v>
       </c>
       <c r="G1071" t="n">
-        <v>4.83164072036743</v>
+        <v>4.83164119720459</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G1072" t="n">
-        <v>4.87869119644165</v>
+        <v>4.87869167327881</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>6.09600019454956</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.94521236419678</v>
+        <v>4.94521284103394</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G1075" t="n">
-        <v>4.94845724105835</v>
+        <v>4.94845676422119</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>6.11600017547607</v>
       </c>
       <c r="G1076" t="n">
-        <v>4.9614372253418</v>
+        <v>4.96143674850464</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>6.10799980163574</v>
       </c>
       <c r="G1077" t="n">
-        <v>4.95494651794434</v>
+        <v>4.95494604110718</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>6.15199995040894</v>
       </c>
       <c r="G1078" t="n">
-        <v>4.99063968658447</v>
+        <v>4.99064064025879</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>6.17600011825562</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.01011037826538</v>
+        <v>5.01010990142822</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>6.5</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.27294683456421</v>
+        <v>5.27294588088989</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>6.42600011825562</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.21291589736938</v>
+        <v>5.21291542053223</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6.58400011062622</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.34108877182007</v>
+        <v>5.34108829498291</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>6.67600011825562</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.41572093963623</v>
+        <v>5.41572141647339</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.26970100402832</v>
+        <v>5.26970052719116</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>6.08799982070923</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.93872165679932</v>
+        <v>4.93872213363647</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>6.28599977493286</v>
       </c>
       <c r="G1096" t="n">
-        <v>5.09934377670288</v>
+        <v>5.09934425354004</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.99712991714478</v>
+        <v>4.99713039398193</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>6.04400014877319</v>
       </c>
       <c r="G1103" t="n">
-        <v>4.90302896499634</v>
+        <v>4.90302801132202</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>6.11800003051758</v>
       </c>
       <c r="G1105" t="n">
-        <v>4.963059425354</v>
+        <v>4.96305894851685</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.04580307006836</v>
+        <v>5.04580354690552</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G1110" t="n">
-        <v>4.76025295257568</v>
+        <v>4.76025342941284</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>5.66200017929077</v>
       </c>
       <c r="G1114" t="n">
-        <v>4.59314155578613</v>
+        <v>4.59314107894897</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>5.65199995040894</v>
       </c>
       <c r="G1115" t="n">
-        <v>4.58502912521362</v>
+        <v>4.58502864837646</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>5.06400012969971</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.10803079605103</v>
+        <v>4.10803031921387</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.21024465560913</v>
+        <v>4.21024417877197</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G1118" t="n">
-        <v>4.0098729133606</v>
+        <v>4.00987243652344</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.82247996330261</v>
+        <v>3.82248020172119</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>4.65700006484985</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.77786350250244</v>
+        <v>3.77786302566528</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>4.32600021362305</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.50934839248657</v>
+        <v>3.50934886932373</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.50772547721863</v>
+        <v>3.50772571563721</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>4.67799997329712</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.79489922523499</v>
+        <v>3.79489874839783</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.68700575828552</v>
+        <v>3.68700623512268</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.67402648925781</v>
+        <v>3.67402601242065</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.97661232948303</v>
+        <v>3.97661304473877</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>4.84700012207031</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.93199610710144</v>
+        <v>3.9319953918457</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>4.84899997711182</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.93361806869507</v>
+        <v>3.93361783027649</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.86953091621399</v>
+        <v>3.86953067779541</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.93767380714417</v>
+        <v>3.93767404556274</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.9311842918396</v>
+        <v>3.93118381500244</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>5.01800012588501</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.07071495056152</v>
+        <v>4.07071447372437</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G1140" t="n">
-        <v>4.0544900894165</v>
+        <v>4.05449056625366</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>4.93100023269653</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.00013828277588</v>
+        <v>4.00013780593872</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>4.9060001373291</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.97985768318176</v>
+        <v>3.9798572063446</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>4.8769998550415</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.95633149147034</v>
+        <v>3.95633220672607</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.89549040794373</v>
+        <v>3.89549016952515</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.68457269668579</v>
+        <v>3.68457221984863</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.59209322929382</v>
+        <v>3.59209299087524</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.6066951751709</v>
+        <v>3.60669493675232</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>4.54300022125244</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.68538379669189</v>
+        <v>3.68538355827332</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.85817384719849</v>
+        <v>3.85817360877991</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>4.88100004196167</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.95957660675049</v>
+        <v>3.95957636833191</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.84925007820129</v>
+        <v>3.84925031661987</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>4.5770001411438</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.71296548843384</v>
+        <v>3.71296501159668</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>4.66599988937378</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.78516340255737</v>
+        <v>3.78516364097595</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>4.61700010299683</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.74541401863098</v>
+        <v>3.74541425704956</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>4.4689998626709</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.62535285949707</v>
+        <v>3.62535309791565</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>4.63899993896484</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.76326060295105</v>
+        <v>3.76326131820679</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.81761288642883</v>
+        <v>3.81761312484741</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.68781781196594</v>
+        <v>3.68781733512878</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>4.51399993896484</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.66185832023621</v>
+        <v>3.66185784339905</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>4.51100015640259</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.79477214813232</v>
+        <v>3.79477190971375</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>4.42899990081787</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.72579145431519</v>
+        <v>3.72579169273376</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.85449910163879</v>
+        <v>3.85449886322021</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.86543488502502</v>
+        <v>3.86543464660645</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>4.66699981689453</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.92600321769714</v>
+        <v>3.92600297927856</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.87132334709167</v>
+        <v>3.87132382392883</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>4.65100002288818</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.91254377365112</v>
+        <v>3.91254353523254</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.92768597602844</v>
+        <v>3.92768549919128</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.92852687835693</v>
+        <v>3.92852711677551</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.58900022506714</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.8603880405426</v>
+        <v>3.86038780212402</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.80402517318726</v>
+        <v>3.80402541160583</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.37752342224121</v>
+        <v>3.37752366065979</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.21299982070923</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.54408645629883</v>
+        <v>3.54408621788025</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.56679916381836</v>
+        <v>3.56679940223694</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>4.25899982452393</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.58278274536133</v>
+        <v>3.58278250694275</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.56848192214966</v>
+        <v>3.56848216056824</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.53483295440674</v>
+        <v>3.53483319282532</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.3363037109375</v>
+        <v>3.33630347251892</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.40191960334778</v>
+        <v>3.4019193649292</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.93700003623962</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.31190800666809</v>
+        <v>3.31190824508667</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>3.90300011634827</v>
       </c>
       <c r="G1206" t="n">
-        <v>3.28330659866333</v>
+        <v>3.28330636024475</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.25218105316162</v>
+        <v>3.25218081474304</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>4.07100009918213</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.42463254928589</v>
+        <v>3.42463231086731</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.48267698287964</v>
+        <v>3.48267674446106</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.41958498954773</v>
+        <v>3.41958475112915</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>4.08699989318848</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.43809175491333</v>
+        <v>3.43809199333191</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.33125638961792</v>
+        <v>3.33125615119934</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>4.09100008010864</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.44145727157593</v>
+        <v>3.44145703315735</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>4.20300006866455</v>
       </c>
       <c r="G1217" t="n">
-        <v>3.53567433357239</v>
+        <v>3.53567409515381</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>4.16900014877319</v>
       </c>
       <c r="G1218" t="n">
-        <v>3.50707292556763</v>
+        <v>3.50707268714905</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.11700010299683</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.46332883834839</v>
+        <v>3.46332907676697</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>4.12900018692017</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.47342371940613</v>
+        <v>3.47342395782471</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.35649299621582</v>
+        <v>3.35649275779724</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>4.20800018310547</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.53988027572632</v>
+        <v>3.5398805141449</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>4.17700004577637</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.51380228996277</v>
+        <v>3.51380252838135</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G1227" t="n">
-        <v>3.44566345214844</v>
+        <v>3.44566321372986</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.66774702072144</v>
+        <v>3.66774725914001</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.59624266624451</v>
+        <v>3.59624242782593</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>3.87899994850159</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.26311707496643</v>
+        <v>3.26311659812927</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>3.70900011062622</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.12010860443115</v>
+        <v>3.12010836601257</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.16721725463867</v>
+        <v>3.16721749305725</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.29760718345642</v>
+        <v>3.297607421875</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.13609147071838</v>
+        <v>3.13609170913696</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.16637587547302</v>
+        <v>3.16637563705444</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.1596462726593</v>
+        <v>3.15964603424072</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G1263" t="n">
-        <v>3.04692196846008</v>
+        <v>3.04692149162292</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.90223097801208</v>
+        <v>2.90223073959351</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.87867641448975</v>
+        <v>2.87867665290833</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.75080990791321</v>
+        <v>2.75081014633179</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.3659999370575</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.83156776428223</v>
+        <v>2.83156800270081</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.50300002098083</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.94681572914124</v>
+        <v>2.94681596755981</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.86858177185059</v>
+        <v>2.86858201026917</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.84839224815369</v>
+        <v>2.84839248657227</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.5</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.94429206848145</v>
+        <v>2.94429230690002</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>3.56900000572205</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.00233674049377</v>
+        <v>3.00233697891235</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1283" t="n">
-        <v>3.01579618453979</v>
+        <v>3.01579642295837</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.11085486412048</v>
+        <v>3.11085510253906</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.21180200576782</v>
+        <v>3.2118022441864</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.1327269077301</v>
+        <v>3.13272666931152</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1292" t="n">
-        <v>3.16301107406616</v>
+        <v>3.16301083564758</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1294" t="n">
-        <v>3.41369676589966</v>
+        <v>3.41369652748108</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G1295" t="n">
-        <v>3.43052101135254</v>
+        <v>3.43052124977112</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1296" t="n">
-        <v>3.38593626022339</v>
+        <v>3.38593602180481</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>4.04099988937378</v>
       </c>
       <c r="G1297" t="n">
-        <v>3.39939570426941</v>
+        <v>3.39939546585083</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>4.13299989700317</v>
       </c>
       <c r="G1298" t="n">
-        <v>3.47678828239441</v>
+        <v>3.47678852081299</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.4793119430542</v>
+        <v>3.47931218147278</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.4288387298584</v>
+        <v>3.42883849143982</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.5583872795105</v>
+        <v>3.55838704109192</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.56679916381836</v>
+        <v>3.56679940223694</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.56343483924866</v>
+        <v>3.56343460083008</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.14300012588501</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.48520088195801</v>
+        <v>3.48520064353943</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.43893313407898</v>
+        <v>3.4389328956604</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>4.16900014877319</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.50707292556763</v>
+        <v>3.50707268714905</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>4.15100002288818</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.49193024635315</v>
+        <v>3.49193048477173</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>4.02899980545044</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.38930082321167</v>
+        <v>3.38930058479309</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.35985827445984</v>
+        <v>3.35985803604126</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.38593626022339</v>
+        <v>3.38593602180481</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.38677740097046</v>
+        <v>3.38677716255188</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>4.08900022506714</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.43977451324463</v>
+        <v>3.43977427482605</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>4.4229998588562</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.72074389457703</v>
+        <v>3.72074413299561</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>4.44099998474121</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.73588633537292</v>
+        <v>3.73588585853577</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G1338" t="n">
-        <v>3.82926249504089</v>
+        <v>3.82926225662231</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.82926249504089</v>
+        <v>3.82926225662231</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.84019827842712</v>
+        <v>3.84019804000854</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.87721252441406</v>
+        <v>3.87721276283264</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.90329027175903</v>
+        <v>3.90329003334045</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.94366931915283</v>
+        <v>3.94366908073425</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.97058773040771</v>
+        <v>3.97058820724487</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>4.59100008010864</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.86207032203674</v>
+        <v>3.86206984519958</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>4.53700017929077</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.81664395332336</v>
+        <v>3.81664371490479</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>4.60300016403198</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.87216472625732</v>
+        <v>3.8721649646759</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>4.56899976730347</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.84356284141541</v>
+        <v>3.84356307983398</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.90497303009033</v>
+        <v>3.90497255325317</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.85618162155151</v>
+        <v>3.85618185997009</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.82758021354675</v>
+        <v>3.82757997512817</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>4.58599996566772</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.85786390304565</v>
+        <v>3.85786414146423</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.85618162155151</v>
+        <v>3.85618185997009</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>4.65399980545044</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.91506695747375</v>
+        <v>3.91506719589233</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.91590929031372</v>
+        <v>3.9159083366394</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.95208120346069</v>
+        <v>3.95208144187927</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.83767414093018</v>
+        <v>3.83767437934875</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.9091784954071</v>
+        <v>3.90917873382568</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.16407012939453</v>
+        <v>4.16406965255737</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G1370" t="n">
-        <v>4.0589165687561</v>
+        <v>4.05891704559326</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>4.95300006866455</v>
       </c>
       <c r="G1372" t="n">
-        <v>4.1665940284729</v>
+        <v>4.16659450531006</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>4.94700002670288</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.16154718399048</v>
+        <v>4.16154670715332</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G1382" t="n">
-        <v>4.0757417678833</v>
+        <v>4.07574129104614</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.74900007247925</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.99498391151428</v>
+        <v>3.9949836730957</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>4.50299978256226</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.78804183006287</v>
+        <v>3.78804206848145</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.86627626419067</v>
+        <v>3.86627650260925</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.74682211875916</v>
+        <v>3.746821641922</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.75607585906982</v>
+        <v>3.75607562065125</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>4.45699977874756</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.74934577941895</v>
+        <v>3.74934530258179</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>4.34899997711182</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.65849304199219</v>
+        <v>3.65849351882935</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.69634819030762</v>
+        <v>3.6963484287262</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>4.40899991989136</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.70896673202515</v>
+        <v>3.70896697044373</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.76448774337769</v>
+        <v>3.76448798179626</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>4.55900001525879</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.83515095710754</v>
+        <v>3.83515071868896</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.88814830780029</v>
+        <v>3.88814854621887</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>4.62599992752075</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.89151263237</v>
+        <v>3.89151310920715</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>4.48299980163574</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.77121734619141</v>
+        <v>3.77121782302856</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.79056620597839</v>
+        <v>3.79056572914124</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.61700010299683</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.8839418888092</v>
+        <v>3.88394212722778</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.88141822814941</v>
+        <v>3.88141846656799</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.95208120346069</v>
+        <v>3.95208144187927</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.95796966552734</v>
+        <v>3.95796990394592</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1408" t="n">
-        <v>4.03788661956787</v>
+        <v>4.03788614273071</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1409" t="n">
-        <v>4.02442646026611</v>
+        <v>4.02442693710327</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.92768597602844</v>
+        <v>3.92768549919128</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.91843199729919</v>
+        <v>3.91843247413635</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>4.63899993896484</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.90244841575623</v>
+        <v>3.90244889259338</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.88814830780029</v>
+        <v>3.88814854621887</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>4.63700008392334</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.90076613426208</v>
+        <v>3.90076637268066</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.99246025085449</v>
+        <v>3.99246001243591</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.91843199729919</v>
+        <v>3.91843247413635</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.99414300918579</v>
+        <v>3.99414277076721</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>4.72100019454956</v>
       </c>
       <c r="G1419" t="n">
-        <v>3.97143006324768</v>
+        <v>3.9714298248291</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G1421" t="n">
-        <v>4.14303970336914</v>
+        <v>4.14303922653198</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.90299987792969</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.1245322227478</v>
+        <v>4.12453317642212</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.151451587677</v>
+        <v>4.15145206451416</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>4.83099985122681</v>
       </c>
       <c r="G1427" t="n">
-        <v>4.06396389007568</v>
+        <v>4.06396484375</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>4.88399982452393</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.10854959487915</v>
+        <v>4.10854911804199</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>4.89400005340576</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.11696147918701</v>
+        <v>4.11696195602417</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1432" t="n">
-        <v>4.06312370300293</v>
+        <v>4.06312322616577</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>4.58699989318848</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.8587052822113</v>
+        <v>3.85870552062988</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>4.51900005340576</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.80150175094604</v>
+        <v>3.80150151252747</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.87468838691711</v>
+        <v>3.87468862533569</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.83262753486633</v>
+        <v>3.83262705802917</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.82758021354675</v>
+        <v>3.82757997512817</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.87468838691711</v>
+        <v>3.87468862533569</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>4.58300018310547</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.85534048080444</v>
+        <v>3.85534000396729</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.83178567886353</v>
+        <v>3.8317859172821</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>4.64300012588501</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.90581393241882</v>
+        <v>3.90581369400024</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>4.68100023269653</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.93778038024902</v>
+        <v>3.9377806186676</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.9091784954071</v>
+        <v>3.90917873382568</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>4.61899995803833</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.8856246471405</v>
+        <v>3.88562440872192</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1451" t="n">
-        <v>3.84440469741821</v>
+        <v>3.84440422058105</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.43300008773804</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.72915625572205</v>
+        <v>3.72915601730347</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.70307803153992</v>
+        <v>3.7030782699585</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.73504519462585</v>
+        <v>3.73504495620728</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.78131222724915</v>
+        <v>3.78131246566772</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.80570769309998</v>
+        <v>3.80570793151855</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>4.57100009918213</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.8452455997467</v>
+        <v>3.84524536132812</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.82085037231445</v>
+        <v>3.82085013389587</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.72999739646912</v>
+        <v>3.7299976348877</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>4.47599983215332</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.76532936096191</v>
+        <v>3.76532888412476</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.76364660263062</v>
+        <v>3.76364636421204</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.814120054245</v>
+        <v>3.81412053108215</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>4.63700008392334</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.90076613426208</v>
+        <v>3.90076637268066</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.97058773040771</v>
+        <v>3.97058820724487</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.95544648170471</v>
+        <v>3.95544624328613</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.9091784954071</v>
+        <v>3.90917873382568</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.96890544891357</v>
+        <v>3.96890568733215</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.97058773040771</v>
+        <v>3.97058820724487</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>4.82399988174438</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.05807590484619</v>
+        <v>4.05807542800903</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.07153558731079</v>
+        <v>4.07153511047363</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>4.91699981689453</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.33140230178833</v>
+        <v>4.33140182495117</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1481" t="n">
-        <v>4.27238130569458</v>
+        <v>4.27238178253174</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.29880857467651</v>
+        <v>4.29880809783936</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1483" t="n">
-        <v>4.27238130569458</v>
+        <v>4.27238178253174</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>4.76800012588501</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.20014762878418</v>
+        <v>4.20014715194702</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G1485" t="n">
-        <v>4.17988634109497</v>
+        <v>4.17988681793213</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.07858276367188</v>
+        <v>4.07858324050903</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07065439224243</v>
+        <v>4.07065391540527</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>4.60400009155273</v>
       </c>
       <c r="G1489" t="n">
-        <v>4.05567932128906</v>
+        <v>4.0556788444519</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>4.56899976730347</v>
       </c>
       <c r="G1492" t="n">
-        <v>4.02484703063965</v>
+        <v>4.02484750747681</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1494" t="n">
-        <v>4.00458717346191</v>
+        <v>4.00458669662476</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>4.51700019836426</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.97904086112976</v>
+        <v>3.97904062271118</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>4.50699996948242</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.97023129463196</v>
+        <v>3.97023153305054</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.94997119903564</v>
+        <v>3.94997096061707</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>4.49300003051758</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.95789885520935</v>
+        <v>3.95789909362793</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.99401545524597</v>
+        <v>3.99401617050171</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>4.58099985122681</v>
       </c>
       <c r="G1502" t="n">
-        <v>4.03541803359985</v>
+        <v>4.03541851043701</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>4.73299980163574</v>
       </c>
       <c r="G1506" t="n">
-        <v>4.16931533813477</v>
+        <v>4.16931581497192</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>4.7039999961853</v>
       </c>
       <c r="G1509" t="n">
-        <v>4.14376974105835</v>
+        <v>4.14376926422119</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>4.68900012969971</v>
       </c>
       <c r="G1515" t="n">
-        <v>4.13055610656738</v>
+        <v>4.13055658340454</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G1516" t="n">
-        <v>4.17988634109497</v>
+        <v>4.17988681793213</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>4.85300016403198</v>
       </c>
       <c r="G1517" t="n">
-        <v>4.2750244140625</v>
+        <v>4.27502393722534</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>4.56099987030029</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.01780033111572</v>
+        <v>4.01779985427856</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.94468593597412</v>
+        <v>3.94468545913696</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>4.44399976730347</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.91473460197449</v>
+        <v>3.91473436355591</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.8715705871582</v>
+        <v>3.87157011032104</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>4.35099983215332</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.83281016349792</v>
+        <v>3.8328104019165</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>4.44299983978271</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.91385364532471</v>
+        <v>3.91385388374329</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>4.47100019454956</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.93851923942566</v>
+        <v>3.93851900100708</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.87597465515137</v>
+        <v>3.87597513198853</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.96230340003967</v>
+        <v>3.96230363845825</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.95349431037903</v>
+        <v>3.95349454879761</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.92530512809753</v>
+        <v>3.92530536651611</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.66455793380737</v>
+        <v>3.66455817222595</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.62051296234131</v>
+        <v>3.62051320075989</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>4.20100021362305</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.70067548751831</v>
+        <v>3.70067524909973</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>4.3270001411438</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.81166934967041</v>
+        <v>3.81166911125183</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>4.39300012588501</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.86980891227722</v>
+        <v>3.86980867385864</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>4.44700002670288</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.91737747192383</v>
+        <v>3.91737723350525</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>4.44099998474121</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.9120922088623</v>
+        <v>3.91209173202515</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.98961138725281</v>
+        <v>3.98961114883423</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.98961138725281</v>
+        <v>3.98961114883423</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1559" t="n">
-        <v>4.00458717346191</v>
+        <v>4.00458669662476</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>4.46099996566772</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.92971014976501</v>
+        <v>3.92970991134644</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.94997119903564</v>
+        <v>3.94997096061707</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.95173287391663</v>
+        <v>3.95173263549805</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.97111248970032</v>
+        <v>3.97111225128174</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>4.54899978637695</v>
       </c>
       <c r="G1565" t="n">
-        <v>4.00722885131836</v>
+        <v>4.00722932815552</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G1566" t="n">
-        <v>4.01339626312256</v>
+        <v>4.0133957862854</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.20631313323975</v>
+        <v>4.2063136100769</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>4.86100006103516</v>
       </c>
       <c r="G1578" t="n">
-        <v>4.28207159042358</v>
+        <v>4.28207111358643</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G1579" t="n">
-        <v>4.25123977661133</v>
+        <v>4.25123929977417</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>4.78700017929077</v>
       </c>
       <c r="G1580" t="n">
-        <v>4.21688508987427</v>
+        <v>4.21688461303711</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G1581" t="n">
-        <v>4.23009824752808</v>
+        <v>4.23009777069092</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>4.84899997711182</v>
       </c>
       <c r="G1582" t="n">
-        <v>4.27150106430054</v>
+        <v>4.27150058746338</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G1584" t="n">
-        <v>4.27942800521851</v>
+        <v>4.27942848205566</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>4.9229998588562</v>
       </c>
       <c r="G1586" t="n">
-        <v>4.33668756484985</v>
+        <v>4.3366870880127</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G1588" t="n">
-        <v>4.34990119934082</v>
+        <v>4.34990167617798</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G1591" t="n">
-        <v>4.26181030273438</v>
+        <v>4.26181077957153</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1594" t="n">
-        <v>4.56307935714722</v>
+        <v>4.56307888031006</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G1596" t="n">
-        <v>4.67231130599976</v>
+        <v>4.67231178283691</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>5.19799995422363</v>
       </c>
       <c r="G1597" t="n">
-        <v>4.57893562316895</v>
+        <v>4.5789361000061</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G1599" t="n">
-        <v>4.48556041717529</v>
+        <v>4.48555994033813</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1600" t="n">
-        <v>4.47498941421509</v>
+        <v>4.47498893737793</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1602" t="n">
-        <v>4.47498941421509</v>
+        <v>4.47498893737793</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>5.2039999961853</v>
       </c>
       <c r="G1606" t="n">
-        <v>4.58422088623047</v>
+        <v>4.58422136306763</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1607" t="n">
-        <v>4.55427074432373</v>
+        <v>4.55427026748657</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G1608" t="n">
-        <v>4.52255773544312</v>
+        <v>4.52255725860596</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>5.01399993896484</v>
       </c>
       <c r="G1610" t="n">
-        <v>4.4168496131897</v>
+        <v>4.41684913635254</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.74278402328491</v>
+        <v>4.74278354644775</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>5.3439998626709</v>
       </c>
       <c r="G1623" t="n">
-        <v>4.70754718780518</v>
+        <v>4.70754766464233</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G1632" t="n">
-        <v>4.99472188949585</v>
+        <v>4.99472236633301</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1634" t="n">
-        <v>4.88020420074463</v>
+        <v>4.88020467758179</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>5.41400003433228</v>
       </c>
       <c r="G1635" t="n">
-        <v>4.76921033859253</v>
+        <v>4.76921081542969</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G1636" t="n">
-        <v>4.72868967056274</v>
+        <v>4.72868919372559</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G1638" t="n">
-        <v>4.71459484100342</v>
+        <v>4.71459531784058</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>5.3439998626709</v>
       </c>
       <c r="G1640" t="n">
-        <v>4.70754718780518</v>
+        <v>4.70754766464233</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1642" t="n">
-        <v>4.87139558792114</v>
+        <v>4.8713960647583</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G1644" t="n">
-        <v>4.89606142044067</v>
+        <v>4.89606094360352</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1648" t="n">
-        <v>4.97358083724976</v>
+        <v>4.97357988357544</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G1649" t="n">
-        <v>4.99472188949585</v>
+        <v>4.99472236633301</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1651" t="n">
-        <v>4.97358083724976</v>
+        <v>4.97357988357544</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G1655" t="n">
-        <v>5.16561698913574</v>
+        <v>5.1656174659729</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>5.8439998626709</v>
       </c>
       <c r="G1657" t="n">
-        <v>5.14799928665161</v>
+        <v>5.14799880981445</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G1658" t="n">
-        <v>5.11276292800903</v>
+        <v>5.11276340484619</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>5.80200004577637</v>
       </c>
       <c r="G1661" t="n">
-        <v>5.11100101470947</v>
+        <v>5.11100149154663</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1663" t="n">
-        <v>5.17090272903442</v>
+        <v>5.17090320587158</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1664" t="n">
-        <v>5.12333393096924</v>
+        <v>5.1233344078064</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>5.23256635665894</v>
+        <v>5.23256587982178</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G1666" t="n">
-        <v>5.27484941482544</v>
+        <v>5.27484893798828</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>5.97800016403198</v>
       </c>
       <c r="G1667" t="n">
-        <v>5.26604080200195</v>
+        <v>5.26604032516479</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>5.96799993515015</v>
       </c>
       <c r="G1671" t="n">
-        <v>5.25723171234131</v>
+        <v>5.25723123550415</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>6.00400018692017</v>
       </c>
       <c r="G1673" t="n">
-        <v>5.28894424438477</v>
+        <v>5.28894376754761</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G1676" t="n">
-        <v>5.29951429367065</v>
+        <v>5.29951477050781</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>6.23400020599365</v>
       </c>
       <c r="G1678" t="n">
-        <v>5.49155235290527</v>
+        <v>5.49155187606812</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1679" t="n">
-        <v>5.46160078048706</v>
+        <v>5.4616003036499</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>6.08599996566772</v>
       </c>
       <c r="G1687" t="n">
-        <v>5.36117744445801</v>
+        <v>5.36117792129517</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G1691" t="n">
-        <v>5.45279169082642</v>
+        <v>5.45279216766357</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G1694" t="n">
-        <v>5.29775285720825</v>
+        <v>5.29775333404541</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1698" t="n">
-        <v>5.32946586608887</v>
+        <v>5.32946538925171</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G1701" t="n">
-        <v>5.29951429367065</v>
+        <v>5.29951477050781</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>5.96799993515015</v>
       </c>
       <c r="G1702" t="n">
-        <v>5.25723171234131</v>
+        <v>5.25723123550415</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>5.86199998855591</v>
       </c>
       <c r="G1705" t="n">
-        <v>5.16385555267334</v>
+        <v>5.1638560295105</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1713" t="n">
-        <v>5.07062578201294</v>
+        <v>5.07062530517578</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1714" t="n">
-        <v>5.12169694900513</v>
+        <v>5.12169647216797</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1715" t="n">
-        <v>5.02137851715088</v>
+        <v>5.02137899398804</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G1718" t="n">
-        <v>5.16547203063965</v>
+        <v>5.16547155380249</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>5.57399988174438</v>
       </c>
       <c r="G1720" t="n">
-        <v>5.08339357376099</v>
+        <v>5.08339309692383</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1721" t="n">
-        <v>5.14905643463135</v>
+        <v>5.14905595779419</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1723" t="n">
-        <v>5.22931098937988</v>
+        <v>5.22931051254272</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1725" t="n">
-        <v>5.25484657287598</v>
+        <v>5.25484609603882</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>5.75</v>
       </c>
       <c r="G1732" t="n">
-        <v>5.24390268325806</v>
+        <v>5.2439022064209</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1733" t="n">
-        <v>5.30774164199829</v>
+        <v>5.30774116516113</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1734" t="n">
-        <v>5.2657904624939</v>
+        <v>5.26578998565674</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1737" t="n">
-        <v>5.07062578201294</v>
+        <v>5.07062530517578</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1738" t="n">
-        <v>4.97760391235352</v>
+        <v>4.97760343551636</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G1740" t="n">
-        <v>4.7496075630188</v>
+        <v>4.74960803985596</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G1744" t="n">
-        <v>4.78426265716553</v>
+        <v>4.78426313400269</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>5.38199996948242</v>
       </c>
       <c r="G1748" t="n">
-        <v>4.90829229354858</v>
+        <v>4.90829277038574</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1750" t="n">
-        <v>4.94294786453247</v>
+        <v>4.94294834136963</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>5.43200016021729</v>
       </c>
       <c r="G1753" t="n">
-        <v>4.95389223098755</v>
+        <v>4.95389175415039</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>5.52799987792969</v>
       </c>
       <c r="G1758" t="n">
-        <v>5.04144239425659</v>
+        <v>5.04144191741943</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1760" t="n">
-        <v>4.99584293365479</v>
+        <v>4.99584341049194</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1767" t="n">
-        <v>4.9611873626709</v>
+        <v>4.96118783950806</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G1769" t="n">
-        <v>4.92106008529663</v>
+        <v>4.92106056213379</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1777" t="n">
-        <v>5.07062578201294</v>
+        <v>5.07062530517578</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>5.21199989318848</v>
       </c>
       <c r="G1780" t="n">
-        <v>4.75325584411621</v>
+        <v>4.75325536727905</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G1785" t="n">
-        <v>4.89552450180054</v>
+        <v>4.8955249786377</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G1791" t="n">
-        <v>4.87546157836914</v>
+        <v>4.87546110153198</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>5.24399995803833</v>
       </c>
       <c r="G1795" t="n">
-        <v>4.78243923187256</v>
+        <v>4.7824387550354</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1797" t="n">
-        <v>4.7167763710022</v>
+        <v>4.71677589416504</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>5.15799999237061</v>
       </c>
       <c r="G1798" t="n">
-        <v>4.70400857925415</v>
+        <v>4.70400810241699</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1799" t="n">
-        <v>4.6201057434082</v>
+        <v>4.62010622024536</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1802" t="n">
-        <v>4.6201057434082</v>
+        <v>4.62010622024536</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>5.10400009155273</v>
       </c>
       <c r="G1807" t="n">
-        <v>4.65476131439209</v>
+        <v>4.65476179122925</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1808" t="n">
-        <v>4.7167763710022</v>
+        <v>4.71677589416504</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>4.96700000762939</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.52981948852539</v>
+        <v>4.52981996536255</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G1811" t="n">
-        <v>4.63469791412354</v>
+        <v>4.63469743728638</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>5.16599988937378</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.71130418777466</v>
+        <v>4.71130466461182</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.7167763710022</v>
+        <v>4.71677589416504</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G1822" t="n">
-        <v>4.68212080001831</v>
+        <v>4.68212032318115</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G1825" t="n">
-        <v>4.78426265716553</v>
+        <v>4.78426313400269</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.87546157836914</v>
+        <v>4.87546110153198</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G1828" t="n">
-        <v>4.92106008529663</v>
+        <v>4.92106056213379</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1834" t="n">
-        <v>5.02137851715088</v>
+        <v>5.02137899398804</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1835" t="n">
-        <v>5.04326629638672</v>
+        <v>5.04326677322388</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.97760391235352</v>
+        <v>4.97760343551636</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.99219512939453</v>
+        <v>4.99219465255737</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1846" t="n">
-        <v>5.09068870544434</v>
+        <v>5.09068918228149</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1847" t="n">
-        <v>5.09616136550903</v>
+        <v>5.09616088867188</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1848" t="n">
-        <v>5.07062578201294</v>
+        <v>5.07062530517578</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1849" t="n">
-        <v>5.18006324768066</v>
+        <v>5.18006372451782</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1851" t="n">
-        <v>5.22931098937988</v>
+        <v>5.22931051254272</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1854" t="n">
-        <v>5.23843002319336</v>
+        <v>5.23843050003052</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>5.82800006866455</v>
       </c>
       <c r="G1856" t="n">
-        <v>5.31503677368164</v>
+        <v>5.3150372505188</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>5.85200023651123</v>
       </c>
       <c r="G1857" t="n">
-        <v>5.33692502975464</v>
+        <v>5.33692455291748</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>5.78200006484985</v>
       </c>
       <c r="G1860" t="n">
-        <v>5.2730860710144</v>
+        <v>5.27308559417725</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1863" t="n">
-        <v>5.13263988494873</v>
+        <v>5.13264036178589</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1864" t="n">
-        <v>5.10710525512695</v>
+        <v>5.10710477828979</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>5.53800010681152</v>
       </c>
       <c r="G1865" t="n">
-        <v>5.05056190490723</v>
+        <v>5.05056238174438</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1866" t="n">
-        <v>5.10710525512695</v>
+        <v>5.10710477828979</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1868" t="n">
-        <v>5.10710525512695</v>
+        <v>5.10710477828979</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1869" t="n">
-        <v>5.14358425140381</v>
+        <v>5.14358377456665</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G1871" t="n">
-        <v>5.24572610855103</v>
+        <v>5.24572658538818</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>5.72800016403198</v>
       </c>
       <c r="G1876" t="n">
-        <v>5.22383880615234</v>
+        <v>5.2238392829895</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1880" t="n">
-        <v>5.30774164199829</v>
+        <v>5.30774116516113</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G1882" t="n">
-        <v>5.50290584564209</v>
+        <v>5.50290536880493</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>5.75</v>
       </c>
       <c r="G1884" t="n">
-        <v>5.24390268325806</v>
+        <v>5.2439022064209</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1886" t="n">
-        <v>5.30774164199829</v>
+        <v>5.30774116516113</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49431,7 +49431,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1887" t="n">
-        <v>5.14905643463135</v>
+        <v>5.14905595779419</v>
       </c>
       <c r="H1887" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>5.66599988937378</v>
       </c>
       <c r="G1888" t="n">
-        <v>5.16729545593262</v>
+        <v>5.16729593276978</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1889" t="n">
-        <v>5.12169694900513</v>
+        <v>5.12169647216797</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1891" t="n">
-        <v>5.25484657287598</v>
+        <v>5.25484609603882</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G1892" t="n">
-        <v>5.40258741378784</v>
+        <v>5.40258693695068</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1894" t="n">
-        <v>5.40441131591797</v>
+        <v>5.40441179275513</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1895" t="n">
-        <v>5.40441131591797</v>
+        <v>5.40441179275513</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1897" t="n">
-        <v>5.36246013641357</v>
+        <v>5.36246061325073</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G1899" t="n">
-        <v>5.24572610855103</v>
+        <v>5.24572658538818</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1900" t="n">
-        <v>5.09616136550903</v>
+        <v>5.09616088867188</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.99219512939453</v>
+        <v>4.99219465255737</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G1905" t="n">
-        <v>4.97577953338623</v>
+        <v>4.97577905654907</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.84262943267822</v>
+        <v>4.84262990951538</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>4.80299997329712</v>
       </c>
       <c r="G1911" t="n">
-        <v>4.3802547454834</v>
+        <v>4.38025426864624</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G1913" t="n">
-        <v>4.50793170928955</v>
+        <v>4.50793218612671</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.56903553009033</v>
+        <v>4.56903505325317</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G1916" t="n">
-        <v>4.58909845352173</v>
+        <v>4.58909893035889</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>5.36399984359741</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.89187669754028</v>
+        <v>4.89187717437744</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>5.53599977493286</v>
       </c>
       <c r="G1926" t="n">
-        <v>5.0487380027771</v>
+        <v>5.04873752593994</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G1930" t="n">
-        <v>5.40258741378784</v>
+        <v>5.40258693695068</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>5.91800022125244</v>
       </c>
       <c r="G1934" t="n">
-        <v>5.39711618423462</v>
+        <v>5.39711570739746</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1935" t="n">
-        <v>5.45365858078003</v>
+        <v>5.45365810394287</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G1936" t="n">
-        <v>5.57404041290283</v>
+        <v>5.57403993606567</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1937" t="n">
-        <v>5.62693548202515</v>
+        <v>5.62693500518799</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>6.13800001144409</v>
       </c>
       <c r="G1939" t="n">
-        <v>5.5977520942688</v>
+        <v>5.59775161743164</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1943" t="n">
-        <v>5.73637294769287</v>
+        <v>5.73637342453003</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1946" t="n">
-        <v>5.69077396392822</v>
+        <v>5.69077348709106</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>6.18599987030029</v>
       </c>
       <c r="G1952" t="n">
-        <v>5.64152669906616</v>
+        <v>5.64152717590332</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1959" t="n">
-        <v>5.53208923339844</v>
+        <v>5.53208875656128</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -59600,6 +59600,32 @@
         <v>6.48999977111816</v>
       </c>
       <c r="H2278" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2279" t="n">
+        <v>1846618</v>
+      </c>
+      <c r="C2279" t="n">
+        <v>6.55999994277954</v>
+      </c>
+      <c r="D2279" t="n">
+        <v>6.43499994277954</v>
+      </c>
+      <c r="E2279" t="n">
+        <v>6.46999979019165</v>
+      </c>
+      <c r="F2279" t="n">
+        <v>6.5149998664856</v>
+      </c>
+      <c r="G2279" t="n">
+        <v>6.5149998664856</v>
+      </c>
+      <c r="H2279" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G2" t="n">
-        <v>5.00744915008545</v>
+        <v>5.00744962692261</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>5.19319725036621</v>
+        <v>5.19319772720337</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>5.18545818328857</v>
+        <v>5.18545770645142</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G5" t="n">
-        <v>5.07710409164429</v>
+        <v>5.0771050453186</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G6" t="n">
-        <v>5.10419273376465</v>
+        <v>5.10419321060181</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G8" t="n">
-        <v>5.03453731536865</v>
+        <v>5.03453779220581</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>4.98423099517822</v>
+        <v>4.98423147201538</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G13" t="n">
-        <v>4.90683650970459</v>
+        <v>4.90683603286743</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>6.75</v>
       </c>
       <c r="G21" t="n">
-        <v>5.22415542602539</v>
+        <v>5.22415494918823</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G22" t="n">
-        <v>5.40990304946899</v>
+        <v>5.40990257263184</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G23" t="n">
-        <v>5.37507581710815</v>
+        <v>5.375075340271</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G24" t="n">
-        <v>5.33250856399536</v>
+        <v>5.3325080871582</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>5.41764259338379</v>
+        <v>5.41764307022095</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G28" t="n">
-        <v>5.35185623168945</v>
+        <v>5.35185670852661</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>5.23189449310303</v>
+        <v>5.23189496994019</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>5.29381036758423</v>
+        <v>5.29381084442139</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G31" t="n">
-        <v>5.30541944503784</v>
+        <v>5.305419921875</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G32" t="n">
-        <v>5.26285266876221</v>
+        <v>5.26285362243652</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>5.26285266876221</v>
+        <v>5.26285362243652</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>5.29381036758423</v>
+        <v>5.29381084442139</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>5.44860029220581</v>
+        <v>5.44860076904297</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G38" t="n">
-        <v>5.45247030258179</v>
+        <v>5.45246982574463</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>5.44860029220581</v>
+        <v>5.44860076904297</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>5.47955799102783</v>
+        <v>5.47955846786499</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G42" t="n">
-        <v>5.4640793800354</v>
+        <v>5.46407985687256</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>5.34024810791016</v>
+        <v>5.340247631073</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>5.42925214767456</v>
+        <v>5.42925119400024</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G46" t="n">
-        <v>5.39442348480225</v>
+        <v>5.3944239616394</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G47" t="n">
-        <v>5.37120532989502</v>
+        <v>5.37120580673218</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G51" t="n">
-        <v>5.5879111289978</v>
+        <v>5.58791065216064</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>5.6227388381958</v>
+        <v>5.62273931503296</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G53" t="n">
-        <v>5.59178066253662</v>
+        <v>5.59178113937378</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>5.53373527526855</v>
+        <v>5.5337347984314</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>5.48342800140381</v>
+        <v>5.48342847824097</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>5.47955799102783</v>
+        <v>5.47955846786499</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>5.53373527526855</v>
+        <v>5.5337347984314</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>5.54921340942383</v>
+        <v>5.54921388626099</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>5.59565019607544</v>
+        <v>5.5956506729126</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G63" t="n">
-        <v>5.68078565597534</v>
+        <v>5.68078517913818</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G66" t="n">
-        <v>5.99036502838135</v>
+        <v>5.99036455154419</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>6.14902496337891</v>
+        <v>6.14902448654175</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>7.75</v>
       </c>
       <c r="G69" t="n">
-        <v>5.99810457229614</v>
+        <v>5.99810409545898</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G70" t="n">
-        <v>6.098717212677</v>
+        <v>6.09871816635132</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>6.03680181503296</v>
+        <v>6.03680229187012</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>5.98262500762939</v>
+        <v>5.98262453079224</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G79" t="n">
-        <v>5.97101640701294</v>
+        <v>5.9710168838501</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7.76399993896484</v>
       </c>
       <c r="G85" t="n">
-        <v>6.00893926620483</v>
+        <v>6.00893974304199</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G86" t="n">
-        <v>5.88201189041138</v>
+        <v>5.88201141357422</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G87" t="n">
-        <v>5.72722244262695</v>
+        <v>5.72722148895264</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>7.23799991607666</v>
       </c>
       <c r="G91" t="n">
-        <v>5.60184192657471</v>
+        <v>5.60184240341187</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G92" t="n">
-        <v>5.69007349014282</v>
+        <v>5.69007301330566</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>7.24399995803833</v>
       </c>
       <c r="G93" t="n">
-        <v>5.60648536682129</v>
+        <v>5.60648632049561</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>7.43400001525879</v>
       </c>
       <c r="G94" t="n">
-        <v>5.75353670120239</v>
+        <v>5.75353574752808</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>7.67600011825562</v>
       </c>
       <c r="G96" t="n">
-        <v>5.94083166122437</v>
+        <v>5.94083213806152</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G99" t="n">
-        <v>5.73186588287354</v>
+        <v>5.73186540603638</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>5.71174240112305</v>
+        <v>5.71174287796021</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G101" t="n">
-        <v>5.79687786102295</v>
+        <v>5.79687738418579</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G102" t="n">
-        <v>5.79687786102295</v>
+        <v>5.79687738418579</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G103" t="n">
-        <v>5.79687786102295</v>
+        <v>5.79687738418579</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>7.0479998588562</v>
       </c>
       <c r="G105" t="n">
-        <v>5.45479202270508</v>
+        <v>5.45479154586792</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G108" t="n">
-        <v>5.4857497215271</v>
+        <v>5.48575019836426</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G109" t="n">
-        <v>5.56159639358521</v>
+        <v>5.56159687042236</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G113" t="n">
-        <v>5.52754354476929</v>
+        <v>5.52754306793213</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>7.08199977874756</v>
       </c>
       <c r="G117" t="n">
-        <v>5.48110628128052</v>
+        <v>5.48110580444336</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>5.4640793800354</v>
+        <v>5.46407985687256</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>5.4021635055542</v>
+        <v>5.40216398239136</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G123" t="n">
-        <v>5.42538166046143</v>
+        <v>5.42538213729858</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>7.16800022125244</v>
       </c>
       <c r="G126" t="n">
-        <v>5.54766607284546</v>
+        <v>5.5476655960083</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.02799987792969</v>
       </c>
       <c r="G127" t="n">
-        <v>5.43931245803833</v>
+        <v>5.43931293487549</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G128" t="n">
-        <v>5.5554051399231</v>
+        <v>5.55540561676025</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G131" t="n">
-        <v>5.56159639358521</v>
+        <v>5.56159687042236</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503707885742</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>5.53373527526855</v>
+        <v>5.5337347984314</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>5.54921340942383</v>
+        <v>5.54921388626099</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>7.02199983596802</v>
       </c>
       <c r="G137" t="n">
-        <v>5.43466949462891</v>
+        <v>5.43466901779175</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.13600015640259</v>
       </c>
       <c r="G142" t="n">
-        <v>5.52290010452271</v>
+        <v>5.52289962768555</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>7.2519998550415</v>
       </c>
       <c r="G143" t="n">
-        <v>5.61267757415771</v>
+        <v>5.61267709732056</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>7.2039999961853</v>
       </c>
       <c r="G145" t="n">
-        <v>5.57552766799927</v>
+        <v>5.57552862167358</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G146" t="n">
-        <v>5.69007349014282</v>
+        <v>5.69007301330566</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.28200006484985</v>
       </c>
       <c r="G147" t="n">
-        <v>5.63589572906494</v>
+        <v>5.6358962059021</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>7.26800012588501</v>
       </c>
       <c r="G150" t="n">
-        <v>5.62506055831909</v>
+        <v>5.62506103515625</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503707885742</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.14400005340576</v>
       </c>
       <c r="G154" t="n">
-        <v>5.52909135818481</v>
+        <v>5.52909183502197</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>7.61199998855591</v>
       </c>
       <c r="G158" t="n">
-        <v>5.8912992477417</v>
+        <v>5.89129877090454</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7.67799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>5.94237947463989</v>
+        <v>5.94237995147705</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>5.89749050140381</v>
+        <v>5.89749097824097</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7.20800018310547</v>
       </c>
       <c r="G165" t="n">
-        <v>5.57862329483032</v>
+        <v>5.57862424850464</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>7.26399993896484</v>
       </c>
       <c r="G166" t="n">
-        <v>5.62196493148804</v>
+        <v>5.62196588516235</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>7.36199998855591</v>
       </c>
       <c r="G169" t="n">
-        <v>5.69781255722046</v>
+        <v>5.69781160354614</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7.47599983215332</v>
       </c>
       <c r="G170" t="n">
-        <v>5.78604125976562</v>
+        <v>5.7860426902771</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>7.44199991226196</v>
       </c>
       <c r="G171" t="n">
-        <v>5.75972747802734</v>
+        <v>5.7597279548645</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>7.43400001525879</v>
       </c>
       <c r="G172" t="n">
-        <v>5.75353670120239</v>
+        <v>5.75353574752808</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>7.52400016784668</v>
       </c>
       <c r="G174" t="n">
-        <v>5.82319211959839</v>
+        <v>5.82319116592407</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>5.72722244262695</v>
+        <v>5.72722148895264</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G178" t="n">
-        <v>5.76591920852661</v>
+        <v>5.76591968536377</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G179" t="n">
-        <v>5.7225775718689</v>
+        <v>5.72257852554321</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G182" t="n">
-        <v>5.60339021682739</v>
+        <v>5.60338973999023</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.2519998550415</v>
       </c>
       <c r="G185" t="n">
-        <v>5.61267757415771</v>
+        <v>5.61267709732056</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>7.12400007247925</v>
       </c>
       <c r="G187" t="n">
-        <v>5.51361274719238</v>
+        <v>5.51361227035522</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G188" t="n">
-        <v>5.53528213500977</v>
+        <v>5.53528308868408</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G189" t="n">
-        <v>5.53528213500977</v>
+        <v>5.53528308868408</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G191" t="n">
-        <v>5.5554051399231</v>
+        <v>5.55540561676025</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7.13600015640259</v>
       </c>
       <c r="G193" t="n">
-        <v>5.52290010452271</v>
+        <v>5.52289962768555</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7</v>
       </c>
       <c r="G196" t="n">
-        <v>5.41764259338379</v>
+        <v>5.41764307022095</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="n">
-        <v>5.41764259338379</v>
+        <v>5.41764307022095</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.02799987792969</v>
       </c>
       <c r="G199" t="n">
-        <v>5.43931245803833</v>
+        <v>5.43931293487549</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>5.47955799102783</v>
+        <v>5.47955846786499</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.13199996948242</v>
       </c>
       <c r="G202" t="n">
-        <v>5.51980400085449</v>
+        <v>5.51980352401733</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G203" t="n">
-        <v>5.52754354476929</v>
+        <v>5.52754306793213</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>5.53373527526855</v>
+        <v>5.5337347984314</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>7.44600009918213</v>
       </c>
       <c r="G207" t="n">
-        <v>5.76282358169556</v>
+        <v>5.76282405853271</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>7.46600008010864</v>
       </c>
       <c r="G208" t="n">
-        <v>5.77830219268799</v>
+        <v>5.77830266952515</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G211" t="n">
-        <v>5.69007349014282</v>
+        <v>5.69007301330566</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>5.51825571060181</v>
+        <v>5.51825618743896</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>7.20800018310547</v>
       </c>
       <c r="G214" t="n">
-        <v>5.57862329483032</v>
+        <v>5.57862424850464</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.66599988937378</v>
       </c>
       <c r="G216" t="n">
-        <v>5.93309211730957</v>
+        <v>5.93309259414673</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.66599988937378</v>
       </c>
       <c r="G217" t="n">
-        <v>5.93309211730957</v>
+        <v>5.93309259414673</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.60400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>5.88510799407959</v>
+        <v>5.88510751724243</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>5.88201189041138</v>
+        <v>5.88201141357422</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>7.62200021743774</v>
       </c>
       <c r="G220" t="n">
-        <v>5.89903831481934</v>
+        <v>5.89903879165649</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G228" t="n">
-        <v>5.56159639358521</v>
+        <v>5.56159687042236</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G229" t="n">
-        <v>5.62041711807251</v>
+        <v>5.62041759490967</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>6.93800020217896</v>
       </c>
       <c r="G232" t="n">
-        <v>5.36965799331665</v>
+        <v>5.36965751647949</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>6.67199993133545</v>
       </c>
       <c r="G237" t="n">
-        <v>5.16378688812256</v>
+        <v>5.16378784179688</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G240" t="n">
-        <v>5.49813365936279</v>
+        <v>5.49813318252563</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503707885742</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G242" t="n">
-        <v>5.49813365936279</v>
+        <v>5.49813318252563</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>7.22200012207031</v>
       </c>
       <c r="G243" t="n">
-        <v>5.58945941925049</v>
+        <v>5.58945894241333</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G244" t="n">
-        <v>5.55695343017578</v>
+        <v>5.55695295333862</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7.20599985122681</v>
       </c>
       <c r="G246" t="n">
-        <v>5.57707643508911</v>
+        <v>5.57707595825195</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>7.10599994659424</v>
       </c>
       <c r="G248" t="n">
-        <v>5.49968099594116</v>
+        <v>5.49968147277832</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G249" t="n">
-        <v>5.4857497215271</v>
+        <v>5.48575019836426</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G250" t="n">
-        <v>5.56159639358521</v>
+        <v>5.56159687042236</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.99200010299683</v>
       </c>
       <c r="G254" t="n">
-        <v>5.41145086288452</v>
+        <v>5.41145038604736</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G255" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503707885742</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>6.56599998474121</v>
       </c>
       <c r="G258" t="n">
-        <v>5.08174896240234</v>
+        <v>5.08174848556519</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G259" t="n">
-        <v>5.17771863937378</v>
+        <v>5.17771816253662</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>4.86813926696777</v>
+        <v>4.86813831329346</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G261" t="n">
-        <v>4.73037576675415</v>
+        <v>4.73037624359131</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G263" t="n">
-        <v>4.84646844863892</v>
+        <v>4.84646797180176</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>6.24200010299683</v>
       </c>
       <c r="G265" t="n">
-        <v>4.83098840713501</v>
+        <v>4.83098936080933</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>4.78300380706787</v>
+        <v>4.78300428390503</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G267" t="n">
-        <v>4.54153203964233</v>
+        <v>4.54153251647949</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G268" t="n">
-        <v>4.57094287872314</v>
+        <v>4.57094240188599</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G271" t="n">
-        <v>4.75204658508301</v>
+        <v>4.75204610824585</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>6.44600009918213</v>
       </c>
       <c r="G276" t="n">
-        <v>4.98887491226196</v>
+        <v>4.9888744354248</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G277" t="n">
-        <v>4.94088935852051</v>
+        <v>4.94088983535767</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.34600019454956</v>
       </c>
       <c r="G278" t="n">
-        <v>4.91148042678833</v>
+        <v>4.91147947311401</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>5.0151891708374</v>
+        <v>5.01518869400024</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>6.33599996566772</v>
       </c>
       <c r="G281" t="n">
-        <v>4.90373992919922</v>
+        <v>4.90374040603638</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G282" t="n">
-        <v>4.79074335098267</v>
+        <v>4.79074382781982</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>5.89200019836426</v>
       </c>
       <c r="G283" t="n">
-        <v>4.56010770797729</v>
+        <v>4.56010723114014</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>6.12400007247925</v>
       </c>
       <c r="G285" t="n">
-        <v>4.73966360092163</v>
+        <v>4.73966312408447</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>6.29199981689453</v>
       </c>
       <c r="G288" t="n">
-        <v>4.86968660354614</v>
+        <v>4.8696870803833</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>6.23400020599365</v>
       </c>
       <c r="G289" t="n">
-        <v>4.82479763031006</v>
+        <v>4.8247971534729</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G290" t="n">
-        <v>4.93005418777466</v>
+        <v>4.93005466461182</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>6.32600021362305</v>
       </c>
       <c r="G291" t="n">
-        <v>4.89600086212158</v>
+        <v>4.89600038528442</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.42399978637695</v>
       </c>
       <c r="G292" t="n">
-        <v>4.97184753417969</v>
+        <v>4.97184801101685</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G295" t="n">
-        <v>4.79848337173462</v>
+        <v>4.79848289489746</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>6.24399995803833</v>
       </c>
       <c r="G296" t="n">
-        <v>4.8325366973877</v>
+        <v>4.83253717422485</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>6.20599985122681</v>
       </c>
       <c r="G300" t="n">
-        <v>4.8031268119812</v>
+        <v>4.80312776565552</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>6.00400018692017</v>
       </c>
       <c r="G301" t="n">
-        <v>4.64678907394409</v>
+        <v>4.64679002761841</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G304" t="n">
-        <v>4.55855941772461</v>
+        <v>4.55855846405029</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>4.58487319946289</v>
+        <v>4.58487272262573</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.00799989700317</v>
       </c>
       <c r="G306" t="n">
-        <v>4.64988470077515</v>
+        <v>4.6498851776123</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>4.52760076522827</v>
+        <v>4.52760124206543</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.72599983215332</v>
       </c>
       <c r="G308" t="n">
-        <v>4.43163156509399</v>
+        <v>4.43163108825684</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G309" t="n">
-        <v>4.38674259185791</v>
+        <v>4.38674211502075</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.60799980163574</v>
       </c>
       <c r="G311" t="n">
-        <v>4.34030532836914</v>
+        <v>4.34030485153198</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>4.34804487228394</v>
+        <v>4.34804534912109</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G313" t="n">
-        <v>4.27529335021973</v>
+        <v>4.27529430389404</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G317" t="n">
-        <v>4.40531778335571</v>
+        <v>4.4053168296814</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.63800001144409</v>
       </c>
       <c r="G318" t="n">
-        <v>4.36352396011353</v>
+        <v>4.36352348327637</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.96600008010864</v>
       </c>
       <c r="G320" t="n">
-        <v>4.6173791885376</v>
+        <v>4.61737966537476</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.9980001449585</v>
       </c>
       <c r="G321" t="n">
-        <v>4.64214611053467</v>
+        <v>4.64214563369751</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G322" t="n">
-        <v>4.69013023376465</v>
+        <v>4.69013071060181</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>4.72108888626099</v>
+        <v>4.72108840942383</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>5.94799995422363</v>
       </c>
       <c r="G333" t="n">
-        <v>4.60344791412354</v>
+        <v>4.60344839096069</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>5.81199979782104</v>
       </c>
       <c r="G334" t="n">
-        <v>4.49819087982178</v>
+        <v>4.49819040298462</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>4.55855941772461</v>
+        <v>4.55855846405029</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G336" t="n">
-        <v>4.41460418701172</v>
+        <v>4.41460466384888</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>5.69799995422363</v>
       </c>
       <c r="G337" t="n">
-        <v>4.40996074676514</v>
+        <v>4.40996026992798</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.77600002288818</v>
       </c>
       <c r="G338" t="n">
-        <v>4.47032833099365</v>
+        <v>4.47032880783081</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G340" t="n">
-        <v>4.68239116668701</v>
+        <v>4.68239068984985</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G341" t="n">
-        <v>4.49200010299683</v>
+        <v>4.49199962615967</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G342" t="n">
-        <v>4.34804487228394</v>
+        <v>4.34804534912109</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>6.06799983978271</v>
       </c>
       <c r="G344" t="n">
-        <v>4.69632196426392</v>
+        <v>4.69632148742676</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>5.98400020599365</v>
       </c>
       <c r="G346" t="n">
-        <v>4.63131093978882</v>
+        <v>4.6313099861145</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G349" t="n">
-        <v>4.55855941772461</v>
+        <v>4.55855846405029</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>6.11600017547607</v>
       </c>
       <c r="G350" t="n">
-        <v>4.73347187042236</v>
+        <v>4.73347234725952</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G351" t="n">
-        <v>4.72108888626099</v>
+        <v>4.72108840942383</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G354" t="n">
-        <v>4.69477462768555</v>
+        <v>4.69477415084839</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G355" t="n">
-        <v>4.50438261032104</v>
+        <v>4.50438356399536</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>4.5662989616394</v>
+        <v>4.56629848480225</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>6.07600021362305</v>
       </c>
       <c r="G357" t="n">
-        <v>4.70251417160034</v>
+        <v>4.70251369476318</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>4.72108888626099</v>
+        <v>4.72108840942383</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G360" t="n">
-        <v>4.67465114593506</v>
+        <v>4.67465162277222</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G362" t="n">
-        <v>4.5477237701416</v>
+        <v>4.54772424697876</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G363" t="n">
-        <v>4.49509572982788</v>
+        <v>4.49509525299072</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.80600023269653</v>
       </c>
       <c r="G365" t="n">
-        <v>4.4935474395752</v>
+        <v>4.49354839324951</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>4.61273574829102</v>
+        <v>4.61273527145386</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G371" t="n">
-        <v>4.68548679351807</v>
+        <v>4.68548727035522</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.93400001525879</v>
       </c>
       <c r="G372" t="n">
-        <v>4.59261274337769</v>
+        <v>4.59261322021484</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>5.84600019454956</v>
       </c>
       <c r="G373" t="n">
-        <v>4.52450513839722</v>
+        <v>4.52450561523438</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.73799991607666</v>
       </c>
       <c r="G377" t="n">
-        <v>4.44091892242432</v>
+        <v>4.44091844558716</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G379" t="n">
-        <v>4.64059686660767</v>
+        <v>4.64059782028198</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G380" t="n">
-        <v>4.79848337173462</v>
+        <v>4.79848289489746</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>6.24599981307983</v>
       </c>
       <c r="G381" t="n">
-        <v>4.83408451080322</v>
+        <v>4.83408498764038</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G382" t="n">
-        <v>4.86813926696777</v>
+        <v>4.86813831329346</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.26800012588501</v>
       </c>
       <c r="G383" t="n">
-        <v>4.85111141204834</v>
+        <v>4.85111236572266</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>4.79074335098267</v>
+        <v>4.79074382781982</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.60200023651123</v>
       </c>
       <c r="G387" t="n">
-        <v>5.10961151123047</v>
+        <v>5.10961103439331</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.51200008392334</v>
       </c>
       <c r="G388" t="n">
-        <v>5.03995561599731</v>
+        <v>5.03995513916016</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G389" t="n">
-        <v>5.02757215499878</v>
+        <v>5.02757263183594</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>4.98423099517822</v>
+        <v>4.98423147201538</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G392" t="n">
-        <v>4.96875238418579</v>
+        <v>4.96875143051147</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>6.44199991226196</v>
       </c>
       <c r="G393" t="n">
-        <v>4.98577928543091</v>
+        <v>4.98577880859375</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.50799989700317</v>
       </c>
       <c r="G397" t="n">
-        <v>5.0368595123291</v>
+        <v>5.03685998916626</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.30600023269653</v>
       </c>
       <c r="G398" t="n">
-        <v>4.88052225112915</v>
+        <v>4.88052177429199</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>6.17799997329712</v>
       </c>
       <c r="G399" t="n">
-        <v>4.78145694732666</v>
+        <v>4.7814564704895</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>5.97399997711182</v>
       </c>
       <c r="G400" t="n">
-        <v>4.62357091903687</v>
+        <v>4.62357044219971</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G401" t="n">
-        <v>4.55081987380981</v>
+        <v>4.55082035064697</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>4.5662989616394</v>
+        <v>4.56629848480225</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G409" t="n">
-        <v>4.48271179199219</v>
+        <v>4.48271226882935</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G410" t="n">
-        <v>4.3749361038208</v>
+        <v>4.37493515014648</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>5.57600021362305</v>
       </c>
       <c r="G411" t="n">
-        <v>4.45157670974731</v>
+        <v>4.45157718658447</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.34800004959106</v>
       </c>
       <c r="G413" t="n">
-        <v>4.26955366134644</v>
+        <v>4.26955413818359</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G414" t="n">
-        <v>4.25039339065552</v>
+        <v>4.25039386749268</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G416" t="n">
-        <v>4.14660882949829</v>
+        <v>4.14660835266113</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G418" t="n">
-        <v>4.14341449737549</v>
+        <v>4.1434154510498</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5.17799997329712</v>
       </c>
       <c r="G422" t="n">
-        <v>4.13383531570435</v>
+        <v>4.13383483886719</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5.18800020217896</v>
       </c>
       <c r="G423" t="n">
-        <v>4.14181852340698</v>
+        <v>4.14181804656982</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G424" t="n">
-        <v>4.14341449737549</v>
+        <v>4.1434154510498</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.32800006866455</v>
       </c>
       <c r="G426" t="n">
-        <v>4.253586769104</v>
+        <v>4.25358724594116</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G427" t="n">
-        <v>4.13223838806152</v>
+        <v>4.13223886489868</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.25</v>
       </c>
       <c r="G428" t="n">
-        <v>4.19131660461426</v>
+        <v>4.19131565093994</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.29199981689453</v>
       </c>
       <c r="G429" t="n">
-        <v>4.22484636306763</v>
+        <v>4.22484683990479</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G435" t="n">
-        <v>4.35577487945557</v>
+        <v>4.35577535629272</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>4.23123407363892</v>
+        <v>4.2312331199646</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5.19600009918213</v>
       </c>
       <c r="G438" t="n">
-        <v>4.14820623397827</v>
+        <v>4.1482048034668</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>5.19799995422363</v>
       </c>
       <c r="G439" t="n">
-        <v>4.14980173110962</v>
+        <v>4.14980268478394</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>5.30600023269653</v>
       </c>
       <c r="G440" t="n">
-        <v>4.23602390289307</v>
+        <v>4.23602342605591</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>4.15938282012939</v>
+        <v>4.15938138961792</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5.25</v>
       </c>
       <c r="G442" t="n">
-        <v>4.19131660461426</v>
+        <v>4.19131565093994</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>4.23123407363892</v>
+        <v>4.2312331199646</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G445" t="n">
-        <v>4.36056566238403</v>
+        <v>4.36056518554688</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G446" t="n">
-        <v>4.25039339065552</v>
+        <v>4.25039386749268</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>5.39400005340576</v>
       </c>
       <c r="G447" t="n">
-        <v>4.30627822875977</v>
+        <v>4.30627775192261</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G448" t="n">
-        <v>4.40367603302002</v>
+        <v>4.40367555618286</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5.67799997329712</v>
       </c>
       <c r="G449" t="n">
-        <v>4.53300857543945</v>
+        <v>4.53300762176514</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54737854003906</v>
+        <v>4.5473780632019</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G453" t="n">
-        <v>4.1513991355896</v>
+        <v>4.15139865875244</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G455" t="n">
-        <v>4.17534971237183</v>
+        <v>4.17534923553467</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G458" t="n">
-        <v>4.55057191848755</v>
+        <v>4.55057144165039</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.60799980163574</v>
       </c>
       <c r="G459" t="n">
-        <v>4.47712421417236</v>
+        <v>4.47712373733521</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.46799993515015</v>
       </c>
       <c r="G460" t="n">
-        <v>4.36535501480103</v>
+        <v>4.36535549163818</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>3.87197804450989</v>
+        <v>3.87197709083557</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G466" t="n">
-        <v>3.76819252967834</v>
+        <v>3.76819229125977</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>3.70831727981567</v>
+        <v>3.70831680297852</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G470" t="n">
-        <v>3.67398810386658</v>
+        <v>3.673987865448</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.75299978256226</v>
       </c>
       <c r="G471" t="n">
-        <v>3.79453778266907</v>
+        <v>3.79453802108765</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G473" t="n">
-        <v>3.60532999038696</v>
+        <v>3.60532975196838</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G474" t="n">
-        <v>3.67957711219788</v>
+        <v>3.67957663536072</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.51300001144409</v>
       </c>
       <c r="G475" t="n">
-        <v>3.60293507575989</v>
+        <v>3.60293555259705</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G476" t="n">
-        <v>3.74264574050903</v>
+        <v>3.74264550209045</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.81300020217896</v>
       </c>
       <c r="G477" t="n">
-        <v>3.8424391746521</v>
+        <v>3.84243869781494</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.6729998588562</v>
       </c>
       <c r="G478" t="n">
-        <v>3.73066997528076</v>
+        <v>3.73067045211792</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.82407736778259</v>
+        <v>3.82407641410828</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>3.77218437194824</v>
+        <v>3.77218461036682</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>3.76020956039429</v>
+        <v>3.76020932197571</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.6729998588562</v>
       </c>
       <c r="G485" t="n">
-        <v>3.73066997528076</v>
+        <v>3.73067045211792</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.97300004959106</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97017502784729</v>
+        <v>3.97017407417297</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G487" t="n">
-        <v>4.06837129592896</v>
+        <v>4.0683708190918</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G489" t="n">
-        <v>4.27274751663208</v>
+        <v>4.27274799346924</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G490" t="n">
-        <v>4.31585836410522</v>
+        <v>4.31585788726807</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G491" t="n">
-        <v>4.26316738128662</v>
+        <v>4.2631664276123</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G493" t="n">
-        <v>4.51863813400269</v>
+        <v>4.51863765716553</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>4.55057191848755</v>
+        <v>4.55057144165039</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G495" t="n">
-        <v>4.49468755722046</v>
+        <v>4.49468803405762</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G496" t="n">
-        <v>4.52183151245117</v>
+        <v>4.52183103561401</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G497" t="n">
-        <v>4.56973218917847</v>
+        <v>4.56973171234131</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G498" t="n">
-        <v>4.52183151245117</v>
+        <v>4.52183103561401</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>5.44199991226196</v>
       </c>
       <c r="G499" t="n">
-        <v>4.34459829330444</v>
+        <v>4.3445987701416</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G500" t="n">
-        <v>4.28871393203735</v>
+        <v>4.28871440887451</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G502" t="n">
-        <v>4.31585836410522</v>
+        <v>4.31585788726807</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G504" t="n">
-        <v>4.333420753479</v>
+        <v>4.33342170715332</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G505" t="n">
-        <v>4.33022832870483</v>
+        <v>4.33022785186768</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.25</v>
       </c>
       <c r="G506" t="n">
-        <v>4.19131660461426</v>
+        <v>4.19131565093994</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5.11800003051758</v>
       </c>
       <c r="G508" t="n">
-        <v>4.08593463897705</v>
+        <v>4.08593416213989</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.12200021743774</v>
       </c>
       <c r="G509" t="n">
-        <v>4.08912801742554</v>
+        <v>4.08912754058838</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G511" t="n">
-        <v>4.07954788208008</v>
+        <v>4.07954740524292</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G513" t="n">
-        <v>4.31585836410522</v>
+        <v>4.31585788726807</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G514" t="n">
-        <v>4.333420753479</v>
+        <v>4.33342170715332</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G515" t="n">
-        <v>4.485107421875</v>
+        <v>4.48510694503784</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.69399976730347</v>
       </c>
       <c r="G516" t="n">
-        <v>4.54578113555908</v>
+        <v>4.54578161239624</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G518" t="n">
-        <v>4.31585836410522</v>
+        <v>4.31585788726807</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.4539999961853</v>
       </c>
       <c r="G519" t="n">
-        <v>4.3541784286499</v>
+        <v>4.35417890548706</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.4539999961853</v>
       </c>
       <c r="G522" t="n">
-        <v>4.3541784286499</v>
+        <v>4.35417890548706</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.18800020217896</v>
       </c>
       <c r="G526" t="n">
-        <v>4.14181852340698</v>
+        <v>4.14181804656982</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.18200016021729</v>
       </c>
       <c r="G527" t="n">
-        <v>4.13702869415283</v>
+        <v>4.13702774047852</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G529" t="n">
-        <v>4.32703542709351</v>
+        <v>4.32703495025635</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G530" t="n">
-        <v>4.28552055358887</v>
+        <v>4.28552007675171</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.28711795806885</v>
+        <v>4.28711748123169</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>4.3749361038208</v>
+        <v>4.37493515014648</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.4980001449585</v>
       </c>
       <c r="G534" t="n">
-        <v>4.38930559158325</v>
+        <v>4.38930606842041</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.41485261917114</v>
+        <v>4.4148530960083</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G536" t="n">
-        <v>4.28073120117188</v>
+        <v>4.28073072433472</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G537" t="n">
-        <v>4.22644376754761</v>
+        <v>4.22644329071045</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G538" t="n">
-        <v>4.24879741668701</v>
+        <v>4.24879693984985</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.27600002288818</v>
       </c>
       <c r="G539" t="n">
-        <v>4.21207332611084</v>
+        <v>4.21207284927368</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>4.14341449737549</v>
+        <v>4.1434154510498</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.18800020217896</v>
       </c>
       <c r="G542" t="n">
-        <v>4.14181852340698</v>
+        <v>4.14181804656982</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G543" t="n">
-        <v>4.13543128967285</v>
+        <v>4.13543176651001</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.27600002288818</v>
       </c>
       <c r="G544" t="n">
-        <v>4.21207332611084</v>
+        <v>4.21207284927368</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G546" t="n">
-        <v>4.22644376754761</v>
+        <v>4.22644329071045</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G548" t="n">
-        <v>4.11148166656494</v>
+        <v>4.11148118972778</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.07800006866455</v>
       </c>
       <c r="G552" t="n">
-        <v>4.05400085449219</v>
+        <v>4.05400037765503</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.14200019836426</v>
       </c>
       <c r="G553" t="n">
-        <v>4.10509538650513</v>
+        <v>4.10509490966797</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>4.07156372070312</v>
+        <v>4.07156419754028</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G555" t="n">
-        <v>4.10669088363647</v>
+        <v>4.10669183731079</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.28200006484985</v>
       </c>
       <c r="G557" t="n">
-        <v>4.21686315536499</v>
+        <v>4.21686267852783</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G561" t="n">
-        <v>4.16576862335205</v>
+        <v>4.16576910018921</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G562" t="n">
-        <v>4.09870767593384</v>
+        <v>4.098708152771</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G566" t="n">
-        <v>4.10349798202515</v>
+        <v>4.1034984588623</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G567" t="n">
-        <v>4.26795673370361</v>
+        <v>4.26795768737793</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>4.15938282012939</v>
+        <v>4.15938138961792</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.14599990844727</v>
       </c>
       <c r="G569" t="n">
-        <v>4.10828828811646</v>
+        <v>4.1082878112793</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G570" t="n">
-        <v>4.16576862335205</v>
+        <v>4.16576910018921</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G571" t="n">
-        <v>4.24720096588135</v>
+        <v>4.24720048904419</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G573" t="n">
-        <v>4.23123407363892</v>
+        <v>4.2312331199646</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.25400018692017</v>
       </c>
       <c r="G574" t="n">
-        <v>4.19450902938843</v>
+        <v>4.19450950622559</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.02799987792969</v>
       </c>
       <c r="G576" t="n">
-        <v>4.01408338546753</v>
+        <v>4.01408290863037</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G578" t="n">
-        <v>4.04761362075806</v>
+        <v>4.04761409759521</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>4.05559682846069</v>
+        <v>4.05559730529785</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.03800010681152</v>
       </c>
       <c r="G581" t="n">
-        <v>4.02206659317017</v>
+        <v>4.02206707000732</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.78900003433228</v>
       </c>
       <c r="G583" t="n">
-        <v>3.82327890396118</v>
+        <v>3.82327914237976</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G584" t="n">
-        <v>3.64524745941162</v>
+        <v>3.6452476978302</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.58300018310547</v>
       </c>
       <c r="G585" t="n">
-        <v>3.6588191986084</v>
+        <v>3.65881896018982</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G587" t="n">
-        <v>3.62129688262939</v>
+        <v>3.62129712104797</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G588" t="n">
-        <v>3.49036908149719</v>
+        <v>3.49036812782288</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>3.62848258018494</v>
+        <v>3.62848281860352</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.45100021362305</v>
       </c>
       <c r="G595" t="n">
-        <v>3.55343818664551</v>
+        <v>3.55343794822693</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G596" t="n">
-        <v>3.67957711219788</v>
+        <v>3.67957663536072</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>3.60852360725403</v>
+        <v>3.60852336883545</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G599" t="n">
-        <v>3.76819252967834</v>
+        <v>3.76819229125977</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.70900011062622</v>
       </c>
       <c r="G600" t="n">
-        <v>3.75941109657288</v>
+        <v>3.7594108581543</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.75299978256226</v>
       </c>
       <c r="G603" t="n">
-        <v>3.79453778266907</v>
+        <v>3.79453802108765</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.45900011062622</v>
       </c>
       <c r="G604" t="n">
-        <v>3.55982446670532</v>
+        <v>3.5598247051239</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.36100006103516</v>
       </c>
       <c r="G605" t="n">
-        <v>3.48158693313599</v>
+        <v>3.48158645629883</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G606" t="n">
-        <v>3.55742931365967</v>
+        <v>3.55742907524109</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G607" t="n">
-        <v>3.44885420799255</v>
+        <v>3.44885444641113</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.25299978256226</v>
       </c>
       <c r="G608" t="n">
-        <v>3.39536499977112</v>
+        <v>3.3953652381897</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>3.27321791648865</v>
+        <v>3.27321815490723</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.01700019836426</v>
       </c>
       <c r="G611" t="n">
-        <v>3.20695567131042</v>
+        <v>3.20695543289185</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>3.12951588630676</v>
+        <v>3.12951612472534</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>2.95228290557861</v>
+        <v>2.95228314399719</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G618" t="n">
-        <v>2.79740381240845</v>
+        <v>2.79740405082703</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G619" t="n">
-        <v>2.54832029342651</v>
+        <v>2.54832005500793</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G620" t="n">
-        <v>2.68004751205444</v>
+        <v>2.68004727363586</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G622" t="n">
-        <v>3.04169797897339</v>
+        <v>3.04169821739197</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G623" t="n">
-        <v>2.8740451335907</v>
+        <v>2.87404489517212</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G625" t="n">
-        <v>2.86606192588806</v>
+        <v>2.8660614490509</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.45300006866455</v>
       </c>
       <c r="G626" t="n">
-        <v>2.75668859481812</v>
+        <v>2.75668835639954</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G628" t="n">
-        <v>2.65450048446655</v>
+        <v>2.65450000762939</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44134163856506</v>
+        <v>2.44134211540222</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>2.52676486968994</v>
+        <v>2.52676463127136</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>2.52676486968994</v>
+        <v>2.52676463127136</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G634" t="n">
-        <v>2.55790019035339</v>
+        <v>2.55790042877197</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.38199996948242</v>
       </c>
       <c r="G636" t="n">
-        <v>2.70000576972961</v>
+        <v>2.70000600814819</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G638" t="n">
-        <v>2.64731526374817</v>
+        <v>2.64731502532959</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>2.7143759727478</v>
+        <v>2.71437644958496</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G644" t="n">
-        <v>2.61857461929321</v>
+        <v>2.61857438087463</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G645" t="n">
-        <v>2.64731526374817</v>
+        <v>2.64731502532959</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G646" t="n">
-        <v>2.68004751205444</v>
+        <v>2.68004727363586</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G648" t="n">
-        <v>2.73513340950012</v>
+        <v>2.73513317108154</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G649" t="n">
-        <v>2.81816124916077</v>
+        <v>2.81816101074219</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3.55399990081787</v>
       </c>
       <c r="G650" t="n">
-        <v>2.83732128143311</v>
+        <v>2.83732104301453</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G652" t="n">
-        <v>2.83253145217896</v>
+        <v>2.83253121376038</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G653" t="n">
-        <v>2.95388007164001</v>
+        <v>2.95387983322144</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>2.95388007164001</v>
+        <v>2.95387983322144</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>3.66899991035461</v>
       </c>
       <c r="G655" t="n">
-        <v>2.92913103103638</v>
+        <v>2.92913126945496</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.59699988365173</v>
       </c>
       <c r="G660" t="n">
-        <v>2.87164998054504</v>
+        <v>2.87165021896362</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G661" t="n">
-        <v>2.92593789100647</v>
+        <v>2.92593765258789</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.45099997520447</v>
       </c>
       <c r="G662" t="n">
-        <v>2.75509190559387</v>
+        <v>2.75509166717529</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3.52699995040894</v>
       </c>
       <c r="G663" t="n">
-        <v>2.81576609611511</v>
+        <v>2.81576561927795</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.57699990272522</v>
       </c>
       <c r="G665" t="n">
-        <v>2.85568332672119</v>
+        <v>2.85568308830261</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>2.95388007164001</v>
+        <v>2.95387983322144</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G669" t="n">
-        <v>3.30116033554077</v>
+        <v>3.30116057395935</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>3.21733379364014</v>
+        <v>3.21733403205872</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G673" t="n">
-        <v>3.37380933761597</v>
+        <v>3.37380957603455</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.20699977874756</v>
       </c>
       <c r="G674" t="n">
-        <v>3.3586413860321</v>
+        <v>3.35864090919495</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G675" t="n">
-        <v>3.53986573219299</v>
+        <v>3.53986597061157</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G676" t="n">
-        <v>3.47919154167175</v>
+        <v>3.47919130325317</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G678" t="n">
-        <v>3.3650279045105</v>
+        <v>3.36502838134766</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G680" t="n">
-        <v>3.11354899406433</v>
+        <v>3.11354947090149</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.9210000038147</v>
       </c>
       <c r="G681" t="n">
-        <v>3.13031411170959</v>
+        <v>3.13031435012817</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.99300003051758</v>
       </c>
       <c r="G682" t="n">
-        <v>3.18779516220093</v>
+        <v>3.18779540061951</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3.89100003242493</v>
       </c>
       <c r="G685" t="n">
-        <v>3.10636377334595</v>
+        <v>3.10636401176453</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.11354899406433</v>
+        <v>3.11354947090149</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.01100015640259</v>
       </c>
       <c r="G687" t="n">
-        <v>3.2021656036377</v>
+        <v>3.20216536521912</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G689" t="n">
-        <v>3.04808497428894</v>
+        <v>3.04808473587036</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G691" t="n">
-        <v>3.09758234024048</v>
+        <v>3.0975821018219</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G695" t="n">
-        <v>2.96505689620972</v>
+        <v>2.96505665779114</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.78099989891052</v>
       </c>
       <c r="G697" t="n">
-        <v>3.01854562759399</v>
+        <v>3.01854586601257</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.64100003242493</v>
       </c>
       <c r="G699" t="n">
-        <v>2.90677738189697</v>
+        <v>2.90677762031555</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G700" t="n">
-        <v>2.96585464477539</v>
+        <v>2.96585512161255</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G701" t="n">
-        <v>3.02094101905823</v>
+        <v>3.02094078063965</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G703" t="n">
-        <v>3.05287456512451</v>
+        <v>3.05287504196167</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G704" t="n">
-        <v>3.03371477127075</v>
+        <v>3.03371429443359</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>3.76900005340576</v>
       </c>
       <c r="G705" t="n">
-        <v>3.00896596908569</v>
+        <v>3.00896549224854</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G706" t="n">
-        <v>2.9858136177063</v>
+        <v>2.98581385612488</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G707" t="n">
-        <v>3.09758234024048</v>
+        <v>3.0975821018219</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>3.78099989891052</v>
       </c>
       <c r="G709" t="n">
-        <v>3.01854562759399</v>
+        <v>3.01854586601257</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G714" t="n">
-        <v>2.77345323562622</v>
+        <v>2.7734534740448</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.46399998664856</v>
       </c>
       <c r="G716" t="n">
-        <v>2.76547026634216</v>
+        <v>2.76547002792358</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>2.89001202583313</v>
+        <v>2.89001178741455</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G718" t="n">
-        <v>2.94909000396729</v>
+        <v>2.94908976554871</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G720" t="n">
-        <v>2.71118259429932</v>
+        <v>2.7111828327179</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>3.5</v>
       </c>
       <c r="G721" t="n">
-        <v>2.79421067237854</v>
+        <v>2.79421091079712</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G722" t="n">
-        <v>2.96825003623962</v>
+        <v>2.9682502746582</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G724" t="n">
-        <v>2.9858136177063</v>
+        <v>2.98581385612488</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>3.73300004005432</v>
       </c>
       <c r="G728" t="n">
-        <v>2.98022508621216</v>
+        <v>2.98022532463074</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>3.6470000743866</v>
       </c>
       <c r="G729" t="n">
-        <v>2.91156792640686</v>
+        <v>2.9115674495697</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G730" t="n">
-        <v>2.85488486289978</v>
+        <v>2.85488510131836</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.69899988174438</v>
       </c>
       <c r="G731" t="n">
-        <v>2.95308136940002</v>
+        <v>2.9530816078186</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G733" t="n">
-        <v>2.95068669319153</v>
+        <v>2.95068645477295</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>2.96186351776123</v>
+        <v>2.96186327934265</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>3.62100005149841</v>
       </c>
       <c r="G736" t="n">
-        <v>2.89081048965454</v>
+        <v>2.89081025123596</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G737" t="n">
-        <v>2.85408663749695</v>
+        <v>2.85408639907837</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G738" t="n">
-        <v>2.87085151672363</v>
+        <v>2.87085199356079</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.90597939491272</v>
+        <v>2.90597915649414</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G740" t="n">
-        <v>2.95228290557861</v>
+        <v>2.95228314399719</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G743" t="n">
-        <v>3.07522821426392</v>
+        <v>3.0752284526825</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G744" t="n">
-        <v>3.11354899406433</v>
+        <v>3.11354947090149</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>3.88100004196167</v>
       </c>
       <c r="G745" t="n">
-        <v>3.09838056564331</v>
+        <v>3.09838032722473</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G746" t="n">
-        <v>3.08321166038513</v>
+        <v>3.08321189880371</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G747" t="n">
-        <v>3.06165671348572</v>
+        <v>3.06165647506714</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.95900011062622</v>
       </c>
       <c r="G750" t="n">
-        <v>3.16065168380737</v>
+        <v>3.16065144538879</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.75699996948242</v>
       </c>
       <c r="G751" t="n">
-        <v>2.99938559532166</v>
+        <v>2.99938535690308</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>3.81900000572205</v>
       </c>
       <c r="G753" t="n">
-        <v>3.04888319969177</v>
+        <v>3.04888296127319</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G754" t="n">
-        <v>2.9898054599762</v>
+        <v>2.98980569839478</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G755" t="n">
-        <v>2.90597939491272</v>
+        <v>2.90597915649414</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G756" t="n">
-        <v>3.01774716377258</v>
+        <v>3.01774740219116</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.58299994468689</v>
       </c>
       <c r="G759" t="n">
-        <v>2.86047315597534</v>
+        <v>2.86047339439392</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.53299999237061</v>
       </c>
       <c r="G760" t="n">
-        <v>2.82055592536926</v>
+        <v>2.82055616378784</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.62100005149841</v>
       </c>
       <c r="G761" t="n">
-        <v>2.89081048965454</v>
+        <v>2.89081025123596</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>3.9909999370575</v>
       </c>
       <c r="G764" t="n">
-        <v>3.18619847297668</v>
+        <v>3.18619871139526</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>3.8529999256134</v>
       </c>
       <c r="G765" t="n">
-        <v>3.07602667808533</v>
+        <v>3.07602691650391</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G766" t="n">
-        <v>3.11674213409424</v>
+        <v>3.1167426109314</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G768" t="n">
-        <v>3.06884145736694</v>
+        <v>3.06884169578552</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G770" t="n">
-        <v>2.93950986862183</v>
+        <v>2.93950963020325</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G771" t="n">
-        <v>2.95707321166992</v>
+        <v>2.9570734500885</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G772" t="n">
-        <v>3.06964015960693</v>
+        <v>3.06963992118835</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.68899989128113</v>
       </c>
       <c r="G773" t="n">
-        <v>2.94509792327881</v>
+        <v>2.94509816169739</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.78299999237061</v>
       </c>
       <c r="G774" t="n">
-        <v>3.02014231681824</v>
+        <v>3.02014255523682</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G775" t="n">
-        <v>3.28120183944702</v>
+        <v>3.28120160102844</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G777" t="n">
-        <v>3.00577211380005</v>
+        <v>3.00577259063721</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G778" t="n">
-        <v>2.7926139831543</v>
+        <v>2.79261374473572</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.4539999961853</v>
       </c>
       <c r="G779" t="n">
-        <v>2.75748658180237</v>
+        <v>2.75748682022095</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G780" t="n">
-        <v>2.85807824134827</v>
+        <v>2.85807847976685</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G781" t="n">
-        <v>2.91396284103394</v>
+        <v>2.91396260261536</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.86899995803833</v>
       </c>
       <c r="G782" t="n">
-        <v>3.08880019187927</v>
+        <v>3.08880043029785</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G783" t="n">
-        <v>2.96505689620972</v>
+        <v>2.96505665779114</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.69099998474121</v>
       </c>
       <c r="G785" t="n">
-        <v>2.94669485092163</v>
+        <v>2.94669461250305</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G786" t="n">
-        <v>3.36582636833191</v>
+        <v>3.36582589149475</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.23299980163574</v>
       </c>
       <c r="G787" t="n">
-        <v>3.37939810752869</v>
+        <v>3.37939786911011</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.27899980545044</v>
       </c>
       <c r="G788" t="n">
-        <v>3.41612195968628</v>
+        <v>3.4161217212677</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.22900009155273</v>
       </c>
       <c r="G791" t="n">
-        <v>3.3762047290802</v>
+        <v>3.37620496749878</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.26300001144409</v>
       </c>
       <c r="G792" t="n">
-        <v>3.40334868431091</v>
+        <v>3.40334844589233</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.28700017929077</v>
       </c>
       <c r="G793" t="n">
-        <v>3.42250919342041</v>
+        <v>3.42250943183899</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G798" t="n">
-        <v>3.45843410491943</v>
+        <v>3.45843458175659</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G799" t="n">
-        <v>3.54146218299866</v>
+        <v>3.54146265983582</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G800" t="n">
-        <v>3.46881246566772</v>
+        <v>3.4688127040863</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.50099992752075</v>
       </c>
       <c r="G802" t="n">
-        <v>3.59335517883301</v>
+        <v>3.59335494041443</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.38100004196167</v>
       </c>
       <c r="G803" t="n">
-        <v>3.49755358695984</v>
+        <v>3.49755311012268</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G805" t="n">
-        <v>3.60213708877563</v>
+        <v>3.60213661193848</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>3.55663108825684</v>
+        <v>3.55663132667542</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.45900011062622</v>
       </c>
       <c r="G807" t="n">
-        <v>3.55982446670532</v>
+        <v>3.5598247051239</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.39699983596802</v>
       </c>
       <c r="G809" t="n">
-        <v>3.51032686233521</v>
+        <v>3.51032733917236</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.48899984359741</v>
       </c>
       <c r="G811" t="n">
-        <v>3.58377432823181</v>
+        <v>3.58377480506897</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G812" t="n">
-        <v>3.51272201538086</v>
+        <v>3.5127215385437</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G813" t="n">
-        <v>3.57259774208069</v>
+        <v>3.57259798049927</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G814" t="n">
-        <v>3.73945212364197</v>
+        <v>3.73945236206055</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>3.45683765411377</v>
+        <v>3.45683789253235</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G819" t="n">
-        <v>3.60453152656555</v>
+        <v>3.60453176498413</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>3.56062269210815</v>
+        <v>3.56062245368958</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.43300008773804</v>
       </c>
       <c r="G821" t="n">
-        <v>3.53906750679016</v>
+        <v>3.53906774520874</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.35900020599365</v>
       </c>
       <c r="G822" t="n">
-        <v>3.47998976707458</v>
+        <v>3.47999024391174</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G823" t="n">
-        <v>3.42330741882324</v>
+        <v>3.42330718040466</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.29300022125244</v>
       </c>
       <c r="G824" t="n">
-        <v>3.42729926109314</v>
+        <v>3.42729878425598</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>3.54465627670288</v>
+        <v>3.5446560382843</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G827" t="n">
-        <v>3.50633525848389</v>
+        <v>3.50633549690247</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G828" t="n">
-        <v>3.62129688262939</v>
+        <v>3.62129712104797</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G830" t="n">
-        <v>3.54465627670288</v>
+        <v>3.5446560382843</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G831" t="n">
-        <v>3.46322441101074</v>
+        <v>3.46322417259216</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G832" t="n">
-        <v>3.53667235374451</v>
+        <v>3.53667211532593</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.47900009155273</v>
       </c>
       <c r="G834" t="n">
-        <v>3.57579112052917</v>
+        <v>3.57579135894775</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.43100023269653</v>
       </c>
       <c r="G835" t="n">
-        <v>3.5374710559845</v>
+        <v>3.53747057914734</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G838" t="n">
-        <v>3.44885420799255</v>
+        <v>3.44885444641113</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.26900005340576</v>
       </c>
       <c r="G839" t="n">
-        <v>3.40813851356506</v>
+        <v>3.40813899040222</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.27899980545044</v>
       </c>
       <c r="G840" t="n">
-        <v>3.41612195968628</v>
+        <v>3.4161217212677</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G841" t="n">
-        <v>3.44087052345276</v>
+        <v>3.44087076187134</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.3730001449585</v>
       </c>
       <c r="G843" t="n">
-        <v>3.49116659164429</v>
+        <v>3.49116683006287</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G845" t="n">
-        <v>3.72029185295105</v>
+        <v>3.72029137611389</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.72300004959106</v>
       </c>
       <c r="G847" t="n">
-        <v>3.77058792114258</v>
+        <v>3.770587682724</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.69299983978271</v>
       </c>
       <c r="G848" t="n">
-        <v>3.74663710594177</v>
+        <v>3.74663734436035</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G850" t="n">
-        <v>3.73226714134216</v>
+        <v>3.73226737976074</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.68100023269653</v>
       </c>
       <c r="G851" t="n">
-        <v>3.73705792427063</v>
+        <v>3.73705744743347</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>3.78815150260925</v>
+        <v>3.78815102577209</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>3.76420116424561</v>
+        <v>3.76420140266418</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G854" t="n">
-        <v>3.68995499610901</v>
+        <v>3.68995523452759</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.60099983215332</v>
       </c>
       <c r="G855" t="n">
-        <v>3.67318940162659</v>
+        <v>3.67318916320801</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>3.75861239433289</v>
+        <v>3.75861310958862</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.77099990844727</v>
       </c>
       <c r="G858" t="n">
-        <v>3.80890870094299</v>
+        <v>3.80890822410583</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.81400012969971</v>
       </c>
       <c r="G859" t="n">
-        <v>3.84323692321777</v>
+        <v>3.84323740005493</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G860" t="n">
-        <v>3.81609344482422</v>
+        <v>3.8160936832428</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G861" t="n">
-        <v>3.8121018409729</v>
+        <v>3.81210231781006</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G862" t="n">
-        <v>3.86399459838867</v>
+        <v>3.86399412155151</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G864" t="n">
-        <v>3.89592814445496</v>
+        <v>3.89592862129211</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.9689998626709</v>
       </c>
       <c r="G867" t="n">
-        <v>3.96698045730591</v>
+        <v>3.96698069572449</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G870" t="n">
-        <v>3.91508865356445</v>
+        <v>3.91508817672729</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.90299987792969</v>
       </c>
       <c r="G871" t="n">
-        <v>3.91428995132446</v>
+        <v>3.9142894744873</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G872" t="n">
-        <v>3.96378707885742</v>
+        <v>3.96378755569458</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G873" t="n">
-        <v>3.91269302368164</v>
+        <v>3.91269397735596</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5</v>
       </c>
       <c r="G874" t="n">
-        <v>3.99172925949097</v>
+        <v>3.99172973632812</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G875" t="n">
-        <v>4.04442071914673</v>
+        <v>4.04442024230957</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>5.0939998626709</v>
       </c>
       <c r="G876" t="n">
-        <v>4.06677341461182</v>
+        <v>4.06677389144897</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G882" t="n">
-        <v>4.00769662857056</v>
+        <v>4.0076961517334</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>5.0019998550415</v>
       </c>
       <c r="G884" t="n">
-        <v>3.99332642555237</v>
+        <v>3.99332594871521</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G885" t="n">
-        <v>3.98693943023682</v>
+        <v>3.98693895339966</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.02799987792969</v>
       </c>
       <c r="G886" t="n">
-        <v>4.01408338546753</v>
+        <v>4.01408290863037</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G888" t="n">
-        <v>3.99013328552246</v>
+        <v>3.9901328086853</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.9060001373291</v>
       </c>
       <c r="G889" t="n">
-        <v>3.91668462753296</v>
+        <v>3.91668510437012</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.94399976730347</v>
       </c>
       <c r="G890" t="n">
-        <v>3.94702219963074</v>
+        <v>3.94702172279358</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.9210000038147</v>
       </c>
       <c r="G892" t="n">
-        <v>3.92865967750549</v>
+        <v>3.92866015434265</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G894" t="n">
-        <v>3.99971318244934</v>
+        <v>3.9997136592865</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G897" t="n">
-        <v>3.91269302368164</v>
+        <v>3.91269397735596</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.96299982070923</v>
       </c>
       <c r="G898" t="n">
-        <v>3.96219062805176</v>
+        <v>3.9621901512146</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>5.0019998550415</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99332642555237</v>
+        <v>3.99332594871521</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>5.02600002288818</v>
       </c>
       <c r="G900" t="n">
-        <v>4.01248598098755</v>
+        <v>4.01248645782471</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G903" t="n">
-        <v>3.75701594352722</v>
+        <v>3.75701498985291</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.67700004577637</v>
       </c>
       <c r="G904" t="n">
-        <v>3.73386359214783</v>
+        <v>3.73386406898499</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.73299980163574</v>
       </c>
       <c r="G905" t="n">
-        <v>3.77857136726379</v>
+        <v>3.77857089042664</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G908" t="n">
-        <v>3.69155168533325</v>
+        <v>3.69155192375183</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G912" t="n">
-        <v>3.66839957237244</v>
+        <v>3.66839933395386</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.71299982070923</v>
       </c>
       <c r="G913" t="n">
-        <v>3.76260423660278</v>
+        <v>3.76260375976562</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>3.73945212364197</v>
+        <v>3.73945236206055</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>3.72029185295105</v>
+        <v>3.72029137611389</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.67700004577637</v>
       </c>
       <c r="G918" t="n">
-        <v>3.73386359214783</v>
+        <v>3.73386406898499</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G919" t="n">
-        <v>3.74823451042175</v>
+        <v>3.74823427200317</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G920" t="n">
-        <v>3.76499891281128</v>
+        <v>3.76499962806702</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G921" t="n">
-        <v>3.79054665565491</v>
+        <v>3.79054641723633</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.72900009155273</v>
       </c>
       <c r="G922" t="n">
-        <v>3.77537798881531</v>
+        <v>3.77537822723389</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.85200023651123</v>
       </c>
       <c r="G923" t="n">
-        <v>3.87357449531555</v>
+        <v>3.87357497215271</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G924" t="n">
-        <v>3.86399459838867</v>
+        <v>3.86399412155151</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G927" t="n">
-        <v>3.97097229957581</v>
+        <v>3.97097277641296</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.20599985122681</v>
       </c>
       <c r="G930" t="n">
-        <v>4.15618896484375</v>
+        <v>4.15618848800659</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>5.17799997329712</v>
       </c>
       <c r="G931" t="n">
-        <v>4.13383531570435</v>
+        <v>4.13383483886719</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G932" t="n">
-        <v>4.10349798202515</v>
+        <v>4.1034984588623</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>5.16200017929077</v>
       </c>
       <c r="G933" t="n">
-        <v>4.12106132507324</v>
+        <v>4.1210618019104</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>5.16200017929077</v>
       </c>
       <c r="G934" t="n">
-        <v>4.12106132507324</v>
+        <v>4.1210618019104</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>5.12200021743774</v>
       </c>
       <c r="G935" t="n">
-        <v>4.08912801742554</v>
+        <v>4.08912754058838</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G936" t="n">
-        <v>4.10349798202515</v>
+        <v>4.1034984588623</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>4.12744808197021</v>
+        <v>4.12744855880737</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>4.02366352081299</v>
+        <v>4.02366399765015</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G942" t="n">
-        <v>4.07558155059814</v>
+        <v>4.0755820274353</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>5.03399991989136</v>
       </c>
       <c r="G943" t="n">
-        <v>4.08369398117065</v>
+        <v>4.0836935043335</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.98299980163574</v>
       </c>
       <c r="G946" t="n">
-        <v>4.04232168197632</v>
+        <v>4.04232120513916</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G947" t="n">
-        <v>3.97174453735352</v>
+        <v>3.97174549102783</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.9229998588562</v>
       </c>
       <c r="G948" t="n">
-        <v>3.99364805221558</v>
+        <v>3.99364829063416</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.99200010299683</v>
       </c>
       <c r="G952" t="n">
-        <v>4.04962253570557</v>
+        <v>4.04962301254272</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.86899995803833</v>
       </c>
       <c r="G953" t="n">
-        <v>3.94984245300293</v>
+        <v>3.94984221458435</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.97200012207031</v>
       </c>
       <c r="G954" t="n">
-        <v>4.03339815139771</v>
+        <v>4.03339862823486</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.93100023269653</v>
       </c>
       <c r="G955" t="n">
-        <v>4.00013780593872</v>
+        <v>4.00013828277588</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G956" t="n">
-        <v>4.00581645965576</v>
+        <v>4.00581693649292</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G957" t="n">
-        <v>3.99608182907104</v>
+        <v>3.99608206748962</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G958" t="n">
-        <v>3.9425413608551</v>
+        <v>3.94254088401794</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G959" t="n">
-        <v>3.96850061416626</v>
+        <v>3.9685001373291</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G960" t="n">
-        <v>3.85168480873108</v>
+        <v>3.85168385505676</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G961" t="n">
-        <v>3.91495966911316</v>
+        <v>3.91495943069458</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.96099996566772</v>
       </c>
       <c r="G963" t="n">
-        <v>4.02447414398193</v>
+        <v>4.02447462081909</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>5.07600021362305</v>
       </c>
       <c r="G967" t="n">
-        <v>4.1177659034729</v>
+        <v>4.11776542663574</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G969" t="n">
-        <v>4.13561248779297</v>
+        <v>4.13561201095581</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G970" t="n">
-        <v>4.16968297958374</v>
+        <v>4.1696834564209</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G975" t="n">
-        <v>4.38546895980835</v>
+        <v>4.38546848297119</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G976" t="n">
-        <v>4.38222360610962</v>
+        <v>4.38222408294678</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>5.44600009918213</v>
       </c>
       <c r="G979" t="n">
-        <v>4.41791772842407</v>
+        <v>4.41791725158691</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G980" t="n">
-        <v>4.40007066726685</v>
+        <v>4.40007019042969</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>5.31400012969971</v>
       </c>
       <c r="G981" t="n">
-        <v>4.31083583831787</v>
+        <v>4.31083631515503</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G982" t="n">
-        <v>4.35788726806641</v>
+        <v>4.35788679122925</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G983" t="n">
-        <v>4.24756097793579</v>
+        <v>4.24756050109863</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.16800022125244</v>
       </c>
       <c r="G985" t="n">
-        <v>4.19239807128906</v>
+        <v>4.1923975944519</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G986" t="n">
-        <v>4.21024417877197</v>
+        <v>4.21024465560913</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>5.15199995040894</v>
       </c>
       <c r="G988" t="n">
-        <v>4.17941808700562</v>
+        <v>4.17941761016846</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.14799976348877</v>
       </c>
       <c r="G990" t="n">
-        <v>4.17617225646973</v>
+        <v>4.17617273330688</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G993" t="n">
-        <v>4.19888734817505</v>
+        <v>4.19888782501221</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>5.15199995040894</v>
       </c>
       <c r="G995" t="n">
-        <v>4.17941808700562</v>
+        <v>4.17941761016846</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>5.13600015640259</v>
       </c>
       <c r="G997" t="n">
-        <v>4.16643905639648</v>
+        <v>4.16643857955933</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G998" t="n">
-        <v>4.19888734817505</v>
+        <v>4.19888782501221</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>5.2519998550415</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.26054048538208</v>
+        <v>4.26054000854492</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>5.21199989318848</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.2280912399292</v>
+        <v>4.22809171676636</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>5.14599990844727</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.17455148696899</v>
+        <v>4.17455053329468</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.20213174819946</v>
+        <v>4.20213222503662</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.19888734817505</v>
+        <v>4.19888782501221</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>5.21199989318848</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.2280912399292</v>
+        <v>4.22809171676636</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.26703023910522</v>
+        <v>4.26703071594238</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.23782634735107</v>
+        <v>4.23782587051392</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.15994834899902</v>
+        <v>4.15994882583618</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.13074493408203</v>
+        <v>4.13074445724487</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.121009349823</v>
+        <v>4.12101030349731</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>4.121009349823</v>
+        <v>4.12101030349731</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.05205631256104</v>
+        <v>4.05205583572388</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.97661304473877</v>
+        <v>3.97661280632019</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.98699998855591</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.04556655883789</v>
+        <v>4.04556608200073</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.05124473571777</v>
+        <v>4.05124425888062</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>5.03599977493286</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.08531618118286</v>
+        <v>4.0853157043457</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.07233715057373</v>
+        <v>4.07233667373657</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>5.00600004196167</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.06097984313965</v>
+        <v>4.06097936630249</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.31894779205322</v>
+        <v>4.31894826889038</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>5.31199979782104</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.30921316146851</v>
+        <v>4.30921363830566</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.33192873001099</v>
+        <v>4.33192777633667</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>5.31199979782104</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.30921316146851</v>
+        <v>4.30921363830566</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.3205714225769</v>
+        <v>4.32057046890259</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.38546895980835</v>
+        <v>4.38546848297119</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.42765188217163</v>
+        <v>4.42765235900879</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.54284572601318</v>
+        <v>4.54284524917603</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>5.53800010681152</v>
       </c>
       <c r="G1040" t="n">
-        <v>4.49255037307739</v>
+        <v>4.49254989624023</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.4665904045105</v>
+        <v>4.46659088134766</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.49579477310181</v>
+        <v>4.49579429626465</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.67264127731323</v>
+        <v>4.67264223098755</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>5.84600019454956</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.74240636825562</v>
+        <v>4.74240684509277</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.68399858474731</v>
+        <v>4.68399906158447</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>5.78200006484985</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.69048833847046</v>
+        <v>4.6904878616333</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.74565076828003</v>
+        <v>4.74565124511719</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>5.40399980545044</v>
       </c>
       <c r="G1055" t="n">
-        <v>4.38384628295898</v>
+        <v>4.38384675979614</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G1056" t="n">
-        <v>4.40331506729126</v>
+        <v>4.40331554412842</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>4.49417209625244</v>
+        <v>4.4941725730896</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>5.5460000038147</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.49903964996338</v>
+        <v>4.49904012680054</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1060" t="n">
-        <v>4.66128396987915</v>
+        <v>4.66128444671631</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>5.92799997329712</v>
       </c>
       <c r="G1061" t="n">
-        <v>4.80892658233643</v>
+        <v>4.80892610549927</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>5.96400022506714</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.83813095092773</v>
+        <v>4.83813142776489</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.84299802780151</v>
+        <v>4.84299755096436</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.84299802780151</v>
+        <v>4.84299755096436</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>5.87400007247925</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.76512098312378</v>
+        <v>4.76512050628662</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>5.95599985122681</v>
       </c>
       <c r="G1071" t="n">
-        <v>4.83164119720459</v>
+        <v>4.83164072036743</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G1072" t="n">
-        <v>4.87869167327881</v>
+        <v>4.87869215011597</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>6.09600019454956</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.94521284103394</v>
+        <v>4.94521236419678</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>6.10400009155273</v>
       </c>
       <c r="G1074" t="n">
-        <v>4.95170211791992</v>
+        <v>4.95170164108276</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>6.10799980163574</v>
       </c>
       <c r="G1077" t="n">
-        <v>4.95494604110718</v>
+        <v>4.95494651794434</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>6.42600011825562</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.21291542053223</v>
+        <v>5.21291589736938</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6.58400011062622</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.34108829498291</v>
+        <v>5.34108877182007</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>6.59200000762939</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.34757852554321</v>
+        <v>5.34757804870605</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>6.69600009918213</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.43194580078125</v>
+        <v>5.43194532394409</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>6.62799978256226</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.37678241729736</v>
+        <v>5.37678289413452</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.26970052719116</v>
+        <v>5.26970100402832</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>6.08799982070923</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.93872213363647</v>
+        <v>4.93872261047363</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.00037574768066</v>
+        <v>5.00037527084351</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.99713039398193</v>
+        <v>4.99712991714478</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.05553865432739</v>
+        <v>5.05553817749023</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>6.29199981689453</v>
       </c>
       <c r="G1100" t="n">
-        <v>5.10421133041382</v>
+        <v>5.10421180725098</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>6.24599981307983</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.06689500808716</v>
+        <v>5.06689548492432</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>6.13199996948242</v>
       </c>
       <c r="G1104" t="n">
-        <v>4.97441625595093</v>
+        <v>4.97441577911377</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>6.11800003051758</v>
       </c>
       <c r="G1105" t="n">
-        <v>4.96305894851685</v>
+        <v>4.96305847167969</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G1108" t="n">
-        <v>4.74889659881592</v>
+        <v>4.74889612197876</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>5.66200017929077</v>
       </c>
       <c r="G1114" t="n">
-        <v>4.59314107894897</v>
+        <v>4.59314155578613</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>5.65199995040894</v>
       </c>
       <c r="G1115" t="n">
-        <v>4.58502864837646</v>
+        <v>4.58502912521362</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.21024417877197</v>
+        <v>4.21024465560913</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G1118" t="n">
-        <v>4.00987243652344</v>
+        <v>4.0098729133606</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>4.60099983215332</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.73243427276611</v>
+        <v>3.73243403434753</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.82248020172119</v>
+        <v>3.82248044013977</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>4.65700006484985</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.77786302566528</v>
+        <v>3.77786326408386</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>4.32600021362305</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.50934886932373</v>
+        <v>3.50934863090515</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.50772571563721</v>
+        <v>3.50772595405579</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.68700623512268</v>
+        <v>3.68700647354126</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.67402601242065</v>
+        <v>3.67402648925781</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>4.6710000038147</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.78922009468079</v>
+        <v>3.78922033309937</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.97661304473877</v>
+        <v>3.97661280632019</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>4.84700012207031</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.9319953918457</v>
+        <v>3.93199563026428</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.86953067779541</v>
+        <v>3.86953091621399</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.87358713150024</v>
+        <v>3.8735876083374</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G1140" t="n">
-        <v>4.05449056625366</v>
+        <v>4.0544900894165</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>4.93100023269653</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.00013780593872</v>
+        <v>4.00013828277588</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>4.8769998550415</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.95633220672607</v>
+        <v>3.9563319683075</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.89549016952515</v>
+        <v>3.89549040794373</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.68457221984863</v>
+        <v>3.68457245826721</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>4.41300010681152</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.57992458343506</v>
+        <v>3.57992482185364</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.60669493675232</v>
+        <v>3.60669469833374</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>4.54300022125244</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.68538355827332</v>
+        <v>3.68538379669189</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>4.88100004196167</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.95957636833191</v>
+        <v>3.95957684516907</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.84925031661987</v>
+        <v>3.84925055503845</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>4.69600009918213</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.80950093269348</v>
+        <v>3.80950045585632</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>4.5770001411438</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.71296501159668</v>
+        <v>3.71296548843384</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>4.66599988937378</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.78516364097595</v>
+        <v>3.78516411781311</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.85168480873108</v>
+        <v>3.85168385505676</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.71377635002136</v>
+        <v>3.71377658843994</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.71215415000916</v>
+        <v>3.71215391159058</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.60831737518311</v>
+        <v>3.60831761360168</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.45100021362305</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.61075162887573</v>
+        <v>3.61075115203857</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>4.30100011825562</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.48906803131104</v>
+        <v>3.48906826972961</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>4.4689998626709</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.62535309791565</v>
+        <v>3.62535333633423</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>4.56799983978271</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.70566368103027</v>
+        <v>3.70566415786743</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>4.63899993896484</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.76326131820679</v>
+        <v>3.76326036453247</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.75</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.85330653190613</v>
+        <v>3.85330677032471</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.81761312484741</v>
+        <v>3.81761264801025</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>4.68699979782104</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.8021993637085</v>
+        <v>3.80219960212708</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.71134281158447</v>
+        <v>3.71134257316589</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.68781733512878</v>
+        <v>3.68781709671021</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>4.51399993896484</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.66185784339905</v>
+        <v>3.66185808181763</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>4.40100002288818</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.70223712921143</v>
+        <v>3.70223736763</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>4.42899990081787</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.72579169273376</v>
+        <v>3.72579121589661</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.86543464660645</v>
+        <v>3.86543488502502</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>4.66699981689453</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.92600297927856</v>
+        <v>3.92600321769714</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.87132382392883</v>
+        <v>3.87132358551025</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>4.65100002288818</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.91254353523254</v>
+        <v>3.91254377365112</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.92768549919128</v>
+        <v>3.92768526077271</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.84861040115356</v>
+        <v>3.84861016273499</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.92852711677551</v>
+        <v>3.92852687835693</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.58900022506714</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.86038780212402</v>
+        <v>3.8603880405426</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>4.32299995422363</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.63662123680115</v>
+        <v>3.63662147521973</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.21299982070923</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.54408621788025</v>
+        <v>3.54408645629883</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.3901424407959</v>
+        <v>3.39014220237732</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.56679940223694</v>
+        <v>3.56679916381836</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>4.25899982452393</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.58278250694275</v>
+        <v>3.58278274536133</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.53483319282532</v>
+        <v>3.5348334312439</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.33630347251892</v>
+        <v>3.3363037109375</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.38341212272644</v>
+        <v>3.38341188430786</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>3.90300011634827</v>
       </c>
       <c r="G1206" t="n">
-        <v>3.28330636024475</v>
+        <v>3.28330659866333</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.17478799819946</v>
+        <v>3.17478823661804</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>4.07100009918213</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.42463231086731</v>
+        <v>3.42463254928589</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.41958475112915</v>
+        <v>3.41958498954773</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>4.08699989318848</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.43809199333191</v>
+        <v>3.43809175491333</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.875</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.25975203514099</v>
+        <v>3.25975227355957</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>4.20300006866455</v>
       </c>
       <c r="G1217" t="n">
-        <v>3.53567409515381</v>
+        <v>3.53567433357239</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.11700010299683</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.46332907676697</v>
+        <v>3.46332883834839</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>4.12900018692017</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.47342395782471</v>
+        <v>3.47342371940613</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.2959246635437</v>
+        <v>3.29592490196228</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.35649275779724</v>
+        <v>3.3564932346344</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>4.20800018310547</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.5398805141449</v>
+        <v>3.53988075256348</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1228" t="n">
-        <v>3.60044884681702</v>
+        <v>3.6004490852356</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.58025908470154</v>
+        <v>3.58025932312012</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>4.40700006484985</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.70728445053101</v>
+        <v>3.70728468894958</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.58194184303284</v>
+        <v>3.58194160461426</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.66774725914001</v>
+        <v>3.66774654388428</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.6240029335022</v>
+        <v>3.62400317192078</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.59624242782593</v>
+        <v>3.59624266624451</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.46164608001709</v>
+        <v>3.46164631843567</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.3901424407959</v>
+        <v>3.39014220237732</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.2706880569458</v>
+        <v>3.27068781852722</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1241" t="n">
-        <v>3.28078293800354</v>
+        <v>3.28078269958496</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>3.87899994850159</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.26311659812927</v>
+        <v>3.26311683654785</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.14113926887512</v>
+        <v>3.14113903045654</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>3.70900011062622</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.12010836601257</v>
+        <v>3.12010860443115</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.14113926887512</v>
+        <v>3.14113903045654</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.16721749305725</v>
+        <v>3.16721725463867</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.2168493270874</v>
+        <v>3.21684956550598</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.20507216453552</v>
+        <v>3.2050724029541</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.13609170913696</v>
+        <v>3.13609147071838</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G1263" t="n">
-        <v>3.04692149162292</v>
+        <v>3.0469217300415</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.91484928131104</v>
+        <v>2.91484904289246</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.90223073959351</v>
+        <v>2.90223097801208</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.3659999370575</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.83156800270081</v>
+        <v>2.83156776428223</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.86858201026917</v>
+        <v>2.86858177185059</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>3.40400004386902</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.86353445053101</v>
+        <v>2.86353421211243</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.5460000038147</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.98298859596252</v>
+        <v>2.98298835754395</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>3.62299990653992</v>
       </c>
       <c r="G1281" t="n">
-        <v>3.04776287078857</v>
+        <v>3.04776310920715</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>3.56900000572205</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.00233697891235</v>
+        <v>3.00233674049377</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1283" t="n">
-        <v>3.01579642295837</v>
+        <v>3.01579618453979</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.11085510253906</v>
+        <v>3.11085486412048</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.17478799819946</v>
+        <v>3.17478823661804</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.13272666931152</v>
+        <v>3.1327269077301</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1292" t="n">
-        <v>3.16301083564758</v>
+        <v>3.16301107406616</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1293" t="n">
-        <v>3.07552337646484</v>
+        <v>3.07552313804626</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1294" t="n">
-        <v>3.41369652748108</v>
+        <v>3.4136962890625</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G1295" t="n">
-        <v>3.43052124977112</v>
+        <v>3.43052101135254</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>4.13299989700317</v>
       </c>
       <c r="G1298" t="n">
-        <v>3.47678852081299</v>
+        <v>3.47678828239441</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.5112783908844</v>
+        <v>3.51127886772156</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.42883849143982</v>
+        <v>3.42883896827698</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G1304" t="n">
-        <v>3.50623154640198</v>
+        <v>3.5062313079834</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.4591224193573</v>
+        <v>3.45912289619446</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.5011842250824</v>
+        <v>3.50118398666382</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.519690990448</v>
+        <v>3.51969075202942</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>4.22300004959106</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.55249881744385</v>
+        <v>3.55249834060669</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.5264208316803</v>
+        <v>3.52642059326172</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.56679940223694</v>
+        <v>3.56679916381836</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.56343460083008</v>
+        <v>3.56343483924866</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.14300012588501</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.48520064353943</v>
+        <v>3.48520088195801</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.4389328956604</v>
+        <v>3.43893313407898</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.35985803604126</v>
+        <v>3.35985779762268</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>4.00699996948242</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.37079381942749</v>
+        <v>3.37079405784607</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.38677716255188</v>
+        <v>3.38677740097046</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>4.06099987030029</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.41621994972229</v>
+        <v>3.41621971130371</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.36827039718628</v>
+        <v>3.36827063560486</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>4.08900022506714</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.43977427482605</v>
+        <v>3.43977451324463</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>4.4229998588562</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.72074413299561</v>
+        <v>3.72074365615845</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>4.44099998474121</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.73588585853577</v>
+        <v>3.73588633537292</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G1338" t="n">
-        <v>3.82926225662231</v>
+        <v>3.82926201820374</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.82926225662231</v>
+        <v>3.82926201820374</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1340" t="n">
-        <v>3.81916761398315</v>
+        <v>3.81916737556458</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.90749621391296</v>
+        <v>3.90749645233154</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.87721276283264</v>
+        <v>3.87721228599548</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.90329003334045</v>
+        <v>3.90329027175903</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.94366908073425</v>
+        <v>3.94366884231567</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.97058820724487</v>
+        <v>3.97058796882629</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>4.53700017929077</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.81664371490479</v>
+        <v>3.81664395332336</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>4.60300016403198</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.8721649646759</v>
+        <v>3.87216520309448</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.85113406181335</v>
+        <v>3.85113430023193</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>4.56899976730347</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.84356307983398</v>
+        <v>3.84356260299683</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.90497255325317</v>
+        <v>3.90497279167175</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.85618185997009</v>
+        <v>3.85618162155151</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.82757997512817</v>
+        <v>3.82758045196533</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>4.58599996566772</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.85786414146423</v>
+        <v>3.85786366462708</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.85618185997009</v>
+        <v>3.85618162155151</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>4.65899991989136</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.919273853302</v>
+        <v>3.91927337646484</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>4.75899982452393</v>
       </c>
       <c r="G1359" t="n">
-        <v>4.00339603424072</v>
+        <v>4.00339555740356</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.9159083366394</v>
+        <v>3.91590881347656</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.95208144187927</v>
+        <v>3.95208120346069</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.83767437934875</v>
+        <v>3.83767485618591</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.90917873382568</v>
+        <v>3.9091784954071</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>4.88299989700317</v>
       </c>
       <c r="G1374" t="n">
-        <v>4.10770797729492</v>
+        <v>4.10770750045776</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G1377" t="n">
-        <v>4.12284994125366</v>
+        <v>4.12285089492798</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>4.94399976730347</v>
       </c>
       <c r="G1378" t="n">
-        <v>4.15902233123779</v>
+        <v>4.15902280807495</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.74900007247925</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.9949836730957</v>
+        <v>3.99498391151428</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>4.50299978256226</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.78804206848145</v>
+        <v>3.78804183006287</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.73672747612</v>
+        <v>3.73672699928284</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.68961882591248</v>
+        <v>3.6896185874939</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.746821641922</v>
+        <v>3.74682235717773</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.79561328887939</v>
+        <v>3.79561352729797</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>4.45699977874756</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.74934530258179</v>
+        <v>3.74934577941895</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>4.34899997711182</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.65849351882935</v>
+        <v>3.65849328041077</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.6963484287262</v>
+        <v>3.69634866714478</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.76448798179626</v>
+        <v>3.76448750495911</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.88814854621887</v>
+        <v>3.88814878463745</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>4.62599992752075</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.89151310920715</v>
+        <v>3.89151287078857</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.95460510253906</v>
+        <v>3.95460534095764</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>4.48299980163574</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.77121782302856</v>
+        <v>3.77121758460999</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.88141846656799</v>
+        <v>3.88141798973083</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.95208144187927</v>
+        <v>3.95208120346069</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1408" t="n">
-        <v>4.03788614273071</v>
+        <v>4.03788661956787</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.92768549919128</v>
+        <v>3.92768526077271</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.91843247413635</v>
+        <v>3.91843199729919</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.84861040115356</v>
+        <v>3.84861016273499</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.88814854621887</v>
+        <v>3.88814878463745</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.99246001243591</v>
+        <v>3.99246025085449</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.91843247413635</v>
+        <v>3.91843199729919</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.99414277076721</v>
+        <v>3.99414229393005</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>4.72100019454956</v>
       </c>
       <c r="G1419" t="n">
-        <v>3.9714298248291</v>
+        <v>3.97142934799194</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.12284994125366</v>
+        <v>4.12285089492798</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G1421" t="n">
-        <v>4.14303922653198</v>
+        <v>4.1430401802063</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>4.88199996948242</v>
       </c>
       <c r="G1422" t="n">
-        <v>4.10686731338501</v>
+        <v>4.10686683654785</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.90299987792969</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.12453317642212</v>
+        <v>4.12453269958496</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G1424" t="n">
-        <v>4.0235857963562</v>
+        <v>4.02358531951904</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>4.8289999961853</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.06228160858154</v>
+        <v>4.06228256225586</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>4.83099985122681</v>
       </c>
       <c r="G1427" t="n">
-        <v>4.06396484375</v>
+        <v>4.06396436691284</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>4.58699989318848</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.85870552062988</v>
+        <v>3.85870504379272</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>4.51900005340576</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.80150151252747</v>
+        <v>3.80150198936462</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.83262705802917</v>
+        <v>3.83262753486633</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.82757997512817</v>
+        <v>3.82758045196533</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.70812559127808</v>
+        <v>3.70812582969666</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>4.46700000762939</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.75775814056396</v>
+        <v>3.75775790214539</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>4.58300018310547</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.85534000396729</v>
+        <v>3.85534048080444</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.82337355613708</v>
+        <v>3.82337379455566</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>4.49900007247925</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.78467726707458</v>
+        <v>3.78467774391174</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.8317859172821</v>
+        <v>3.83178615570068</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>4.64300012588501</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.90581369400024</v>
+        <v>3.90581393241882</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>4.68100023269653</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.9377806186676</v>
+        <v>3.93778014183044</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>4.67899990081787</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.93609762191772</v>
+        <v>3.93609809875488</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.90917873382568</v>
+        <v>3.9091784954071</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>4.61899995803833</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.88562440872192</v>
+        <v>3.88562417030334</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1451" t="n">
-        <v>3.84440422058105</v>
+        <v>3.84440445899963</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.77710604667664</v>
+        <v>3.77710628509521</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.43300008773804</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.72915601730347</v>
+        <v>3.72915649414062</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.73504495620728</v>
+        <v>3.73504519462585</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.78131246566772</v>
+        <v>3.78131198883057</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.80570793151855</v>
+        <v>3.80570840835571</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>4.56400012969971</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.83935689926147</v>
+        <v>3.83935737609863</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>4.57100009918213</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.84524536132812</v>
+        <v>3.8452455997467</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.82085013389587</v>
+        <v>3.82084965705872</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.7299976348877</v>
+        <v>3.72999787330627</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>4.47599983215332</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.76532888412476</v>
+        <v>3.76532912254333</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.81412053108215</v>
+        <v>3.814120054245</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.97058820724487</v>
+        <v>3.97058796882629</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.90917873382568</v>
+        <v>3.9091784954071</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.96890568733215</v>
+        <v>3.96890592575073</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.97058820724487</v>
+        <v>3.97058796882629</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>4.82399988174438</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.05807542800903</v>
+        <v>4.05807590484619</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.07153511047363</v>
+        <v>4.07153558731079</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.18869590759277</v>
+        <v>4.18869543075562</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G1478" t="n">
-        <v>4.15081644058228</v>
+        <v>4.15081691741943</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1481" t="n">
-        <v>4.27238178253174</v>
+        <v>4.27238082885742</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.29880809783936</v>
+        <v>4.29880905151367</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1483" t="n">
-        <v>4.27238178253174</v>
+        <v>4.27238082885742</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>4.76800012588501</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.20014715194702</v>
+        <v>4.20014762878418</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.07858324050903</v>
+        <v>4.07858228683472</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07065391540527</v>
+        <v>4.07065439224243</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>4.51399993896484</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.97639775276184</v>
+        <v>3.97639751434326</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>4.56899976730347</v>
       </c>
       <c r="G1492" t="n">
-        <v>4.02484750747681</v>
+        <v>4.02484703063965</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>4.55100011825562</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.00899124145508</v>
+        <v>4.00899171829224</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1494" t="n">
-        <v>4.00458669662476</v>
+        <v>4.0045862197876</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>4.51700019836426</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.97904062271118</v>
+        <v>3.97904086112976</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>4.50699996948242</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.97023153305054</v>
+        <v>3.97023129463196</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>4.49700021743774</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.96142268180847</v>
+        <v>3.96142244338989</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.99401617050171</v>
+        <v>3.99401593208313</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>4.58099985122681</v>
       </c>
       <c r="G1502" t="n">
-        <v>4.03541851043701</v>
+        <v>4.03541803359985</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>4.60699987411499</v>
       </c>
       <c r="G1503" t="n">
-        <v>4.05832147598267</v>
+        <v>4.05832195281982</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>4.73299980163574</v>
       </c>
       <c r="G1506" t="n">
-        <v>4.16931581497192</v>
+        <v>4.16931533813477</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1513" t="n">
-        <v>4.18252944946289</v>
+        <v>4.18252897262573</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>4.68900012969971</v>
       </c>
       <c r="G1515" t="n">
-        <v>4.13055658340454</v>
+        <v>4.13055610656738</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>4.85300016403198</v>
       </c>
       <c r="G1517" t="n">
-        <v>4.27502393722534</v>
+        <v>4.2750244140625</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G1518" t="n">
-        <v>4.26004886627197</v>
+        <v>4.26004934310913</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1523" t="n">
-        <v>4.01868104934692</v>
+        <v>4.01868152618408</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>4.56099987030029</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.01779985427856</v>
+        <v>4.01780033111572</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.94468545913696</v>
+        <v>3.94468569755554</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>4.44399976730347</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.91473436355591</v>
+        <v>3.91473412513733</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.87157011032104</v>
+        <v>3.87157034873962</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>4.44299983978271</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.91385388374329</v>
+        <v>3.91385364532471</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>4.47100019454956</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.93851900100708</v>
+        <v>3.93851947784424</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.87597513198853</v>
+        <v>3.87597489356995</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.95349454879761</v>
+        <v>3.95349407196045</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.92530536651611</v>
+        <v>3.92530512809753</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.84073901176453</v>
+        <v>3.84073853492737</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.66455817222595</v>
+        <v>3.66455793380737</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.58175325393677</v>
+        <v>3.58175301551819</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.62051320075989</v>
+        <v>3.62051296234131</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.58527684211731</v>
+        <v>3.58527708053589</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>4.23299980163574</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.72886395454407</v>
+        <v>3.72886371612549</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.88302206993103</v>
+        <v>3.88302230834961</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.84073901176453</v>
+        <v>3.84073853492737</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>4.44700002670288</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.91737723350525</v>
+        <v>3.91737747192383</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.88302206993103</v>
+        <v>3.88302230834961</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>4.44099998474121</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.91209173202515</v>
+        <v>3.9120922088623</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.98961114883423</v>
+        <v>3.98961138725281</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.98961114883423</v>
+        <v>3.98961138725281</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.93587589263916</v>
+        <v>3.93587613105774</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1559" t="n">
-        <v>4.00458669662476</v>
+        <v>4.0045862197876</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>4.46099996566772</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.92970991134644</v>
+        <v>3.92970967292786</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G1566" t="n">
-        <v>4.0133957862854</v>
+        <v>4.01339626312256</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G1568" t="n">
-        <v>4.01515769958496</v>
+        <v>4.0151572227478</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.01868104934692</v>
+        <v>4.01868152618408</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>4.53299999237061</v>
       </c>
       <c r="G1570" t="n">
-        <v>3.99313521385193</v>
+        <v>3.99313497543335</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1575" t="n">
-        <v>4.2459545135498</v>
+        <v>4.24595403671265</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>4.86100006103516</v>
       </c>
       <c r="G1578" t="n">
-        <v>4.28207111358643</v>
+        <v>4.28207159042358</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G1579" t="n">
-        <v>4.25123929977417</v>
+        <v>4.25123977661133</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G1581" t="n">
-        <v>4.23009777069092</v>
+        <v>4.23009824752808</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G1585" t="n">
-        <v>4.28823757171631</v>
+        <v>4.28823804855347</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G1588" t="n">
-        <v>4.34990167617798</v>
+        <v>4.34990119934082</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>4.83099985122681</v>
       </c>
       <c r="G1589" t="n">
-        <v>4.25564384460449</v>
+        <v>4.25564432144165</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>4.8439998626709</v>
       </c>
       <c r="G1590" t="n">
-        <v>4.26709604263306</v>
+        <v>4.2670955657959</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G1591" t="n">
-        <v>4.26181077957153</v>
+        <v>4.26181030273438</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.39042234420776</v>
+        <v>4.39042282104492</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1594" t="n">
-        <v>4.56307888031006</v>
+        <v>4.56307935714722</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1595" t="n">
-        <v>4.69169187545776</v>
+        <v>4.69169139862061</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G1596" t="n">
-        <v>4.67231178283691</v>
+        <v>4.67231130599976</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1607" t="n">
-        <v>4.55427026748657</v>
+        <v>4.55427074432373</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G1608" t="n">
-        <v>4.52255725860596</v>
+        <v>4.52255773544312</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>5.03800010681152</v>
       </c>
       <c r="G1609" t="n">
-        <v>4.43799161911011</v>
+        <v>4.43799114227295</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>5.01399993896484</v>
       </c>
       <c r="G1610" t="n">
-        <v>4.41684913635254</v>
+        <v>4.4168496131897</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>4.95800018310547</v>
       </c>
       <c r="G1612" t="n">
-        <v>4.36751890182495</v>
+        <v>4.36751937866211</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1616" t="n">
-        <v>4.70402383804321</v>
+        <v>4.70402431488037</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.74278354644775</v>
+        <v>4.74278402328491</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>5.41800022125244</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.77273464202881</v>
+        <v>4.77273511886597</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G1622" t="n">
-        <v>4.68464422225952</v>
+        <v>4.68464374542236</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1625" t="n">
-        <v>4.77449655532837</v>
+        <v>4.77449607849121</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G1626" t="n">
-        <v>4.80268573760986</v>
+        <v>4.80268526077271</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.80620861053467</v>
+        <v>4.80620908737183</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1631" t="n">
-        <v>4.95948600769043</v>
+        <v>4.95948648452759</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G1638" t="n">
-        <v>4.71459531784058</v>
+        <v>4.71459484100342</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>5.54400014877319</v>
       </c>
       <c r="G1641" t="n">
-        <v>4.88372802734375</v>
+        <v>4.88372850418091</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1643" t="n">
-        <v>4.91720247268677</v>
+        <v>4.91720199584961</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G1644" t="n">
-        <v>4.89606094360352</v>
+        <v>4.89606142044067</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1645" t="n">
-        <v>4.9330587387085</v>
+        <v>4.93305921554565</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>5.58599996566772</v>
       </c>
       <c r="G1646" t="n">
-        <v>4.92072629928589</v>
+        <v>4.92072677612305</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>5.65399980545044</v>
       </c>
       <c r="G1647" t="n">
-        <v>4.98062753677368</v>
+        <v>4.98062705993652</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1648" t="n">
-        <v>4.97357988357544</v>
+        <v>4.97358083724976</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1651" t="n">
-        <v>4.97357988357544</v>
+        <v>4.97358083724976</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1663" t="n">
-        <v>5.17090320587158</v>
+        <v>5.17090272903442</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1664" t="n">
-        <v>5.1233344078064</v>
+        <v>5.12333345413208</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G1666" t="n">
-        <v>5.27484893798828</v>
+        <v>5.27484941482544</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>6</v>
       </c>
       <c r="G1670" t="n">
-        <v>5.28541994094849</v>
+        <v>5.28542041778564</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>6.00400018692017</v>
       </c>
       <c r="G1673" t="n">
-        <v>5.28894376754761</v>
+        <v>5.28894424438477</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G1676" t="n">
-        <v>5.29951477050781</v>
+        <v>5.29951429367065</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>6.06799983978271</v>
       </c>
       <c r="G1677" t="n">
-        <v>5.34532165527344</v>
+        <v>5.34532117843628</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1679" t="n">
-        <v>5.4616003036499</v>
+        <v>5.46160078048706</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>6.11399984359741</v>
       </c>
       <c r="G1682" t="n">
-        <v>5.38584327697754</v>
+        <v>5.38584280014038</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>6</v>
       </c>
       <c r="G1685" t="n">
-        <v>5.28541994094849</v>
+        <v>5.28542041778564</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G1686" t="n">
-        <v>5.36470174789429</v>
+        <v>5.36470127105713</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G1689" t="n">
-        <v>5.41403198242188</v>
+        <v>5.41403150558472</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>6.17399978637695</v>
       </c>
       <c r="G1690" t="n">
-        <v>5.43869733810425</v>
+        <v>5.43869686126709</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G1694" t="n">
-        <v>5.29775333404541</v>
+        <v>5.29775285720825</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>5.97599983215332</v>
       </c>
       <c r="G1695" t="n">
-        <v>5.26427841186523</v>
+        <v>5.26427888870239</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>5.94399976730347</v>
       </c>
       <c r="G1696" t="n">
-        <v>5.23608922958374</v>
+        <v>5.2360897064209</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>6.0460000038147</v>
       </c>
       <c r="G1697" t="n">
-        <v>5.32594203948975</v>
+        <v>5.32594156265259</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1698" t="n">
-        <v>5.32946538925171</v>
+        <v>5.32946586608887</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G1701" t="n">
-        <v>5.29951477050781</v>
+        <v>5.29951429367065</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>5.86199998855591</v>
       </c>
       <c r="G1705" t="n">
-        <v>5.1638560295105</v>
+        <v>5.16385555267334</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1706" t="n">
-        <v>5.135666847229</v>
+        <v>5.13566637039185</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1713" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1714" t="n">
-        <v>5.12169647216797</v>
+        <v>5.12169694900513</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1715" t="n">
-        <v>5.02137899398804</v>
+        <v>5.02137851715088</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G1718" t="n">
-        <v>5.16547155380249</v>
+        <v>5.16547203063965</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>5.57399988174438</v>
       </c>
       <c r="G1720" t="n">
-        <v>5.08339309692383</v>
+        <v>5.08339357376099</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1721" t="n">
-        <v>5.14905595779419</v>
+        <v>5.14905643463135</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1723" t="n">
-        <v>5.22931051254272</v>
+        <v>5.22931098937988</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1725" t="n">
-        <v>5.25484609603882</v>
+        <v>5.25484657287598</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>5.75</v>
       </c>
       <c r="G1732" t="n">
-        <v>5.2439022064209</v>
+        <v>5.24390268325806</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1733" t="n">
-        <v>5.30774116516113</v>
+        <v>5.30774164199829</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1734" t="n">
-        <v>5.26578998565674</v>
+        <v>5.2657904624939</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1737" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1738" t="n">
-        <v>4.97760343551636</v>
+        <v>4.97760391235352</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G1740" t="n">
-        <v>4.74960803985596</v>
+        <v>4.7496075630188</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G1744" t="n">
-        <v>4.78426313400269</v>
+        <v>4.78426265716553</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>5.38199996948242</v>
       </c>
       <c r="G1748" t="n">
-        <v>4.90829277038574</v>
+        <v>4.90829229354858</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1750" t="n">
-        <v>4.94294834136963</v>
+        <v>4.94294786453247</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>5.43200016021729</v>
       </c>
       <c r="G1753" t="n">
-        <v>4.95389175415039</v>
+        <v>4.95389223098755</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>5.52799987792969</v>
       </c>
       <c r="G1758" t="n">
-        <v>5.04144191741943</v>
+        <v>5.04144239425659</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1760" t="n">
-        <v>4.99584341049194</v>
+        <v>4.99584293365479</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1767" t="n">
-        <v>4.96118783950806</v>
+        <v>4.9611873626709</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G1769" t="n">
-        <v>4.92106056213379</v>
+        <v>4.92106008529663</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1777" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>5.21199989318848</v>
       </c>
       <c r="G1780" t="n">
-        <v>4.75325536727905</v>
+        <v>4.75325584411621</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G1785" t="n">
-        <v>4.8955249786377</v>
+        <v>4.89552450180054</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G1791" t="n">
-        <v>4.87546110153198</v>
+        <v>4.87546157836914</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>5.24399995803833</v>
       </c>
       <c r="G1795" t="n">
-        <v>4.7824387550354</v>
+        <v>4.78243923187256</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1797" t="n">
-        <v>4.71677589416504</v>
+        <v>4.7167763710022</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>5.15799999237061</v>
       </c>
       <c r="G1798" t="n">
-        <v>4.70400810241699</v>
+        <v>4.70400857925415</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1799" t="n">
-        <v>4.62010622024536</v>
+        <v>4.6201057434082</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1802" t="n">
-        <v>4.62010622024536</v>
+        <v>4.6201057434082</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>5.10400009155273</v>
       </c>
       <c r="G1807" t="n">
-        <v>4.65476179122925</v>
+        <v>4.65476131439209</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1808" t="n">
-        <v>4.71677589416504</v>
+        <v>4.7167763710022</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>4.96700000762939</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.52981996536255</v>
+        <v>4.52981948852539</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G1811" t="n">
-        <v>4.63469743728638</v>
+        <v>4.63469791412354</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>5.16599988937378</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.71130466461182</v>
+        <v>4.71130418777466</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.71677589416504</v>
+        <v>4.7167763710022</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G1822" t="n">
-        <v>4.68212032318115</v>
+        <v>4.68212080001831</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G1825" t="n">
-        <v>4.78426313400269</v>
+        <v>4.78426265716553</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.87546110153198</v>
+        <v>4.87546157836914</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G1828" t="n">
-        <v>4.92106056213379</v>
+        <v>4.92106008529663</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1834" t="n">
-        <v>5.02137899398804</v>
+        <v>5.02137851715088</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1835" t="n">
-        <v>5.04326677322388</v>
+        <v>5.04326629638672</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.97760343551636</v>
+        <v>4.97760391235352</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.99219465255737</v>
+        <v>4.99219512939453</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1846" t="n">
-        <v>5.09068918228149</v>
+        <v>5.09068870544434</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1847" t="n">
-        <v>5.09616088867188</v>
+        <v>5.09616136550903</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1848" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1849" t="n">
-        <v>5.18006372451782</v>
+        <v>5.18006324768066</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1851" t="n">
-        <v>5.22931051254272</v>
+        <v>5.22931098937988</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1854" t="n">
-        <v>5.23843050003052</v>
+        <v>5.23843002319336</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>5.82800006866455</v>
       </c>
       <c r="G1856" t="n">
-        <v>5.3150372505188</v>
+        <v>5.31503677368164</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>5.85200023651123</v>
       </c>
       <c r="G1857" t="n">
-        <v>5.33692455291748</v>
+        <v>5.33692502975464</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>5.78200006484985</v>
       </c>
       <c r="G1860" t="n">
-        <v>5.27308559417725</v>
+        <v>5.2730860710144</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1863" t="n">
-        <v>5.13264036178589</v>
+        <v>5.13263988494873</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1864" t="n">
-        <v>5.10710477828979</v>
+        <v>5.10710525512695</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>5.53800010681152</v>
       </c>
       <c r="G1865" t="n">
-        <v>5.05056238174438</v>
+        <v>5.05056190490723</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1866" t="n">
-        <v>5.10710477828979</v>
+        <v>5.10710525512695</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1868" t="n">
-        <v>5.10710477828979</v>
+        <v>5.10710525512695</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1869" t="n">
-        <v>5.14358377456665</v>
+        <v>5.14358425140381</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G1871" t="n">
-        <v>5.24572658538818</v>
+        <v>5.24572610855103</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>5.72800016403198</v>
       </c>
       <c r="G1876" t="n">
-        <v>5.2238392829895</v>
+        <v>5.22383880615234</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1880" t="n">
-        <v>5.30774116516113</v>
+        <v>5.30774164199829</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G1882" t="n">
-        <v>5.50290536880493</v>
+        <v>5.50290584564209</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>5.75</v>
       </c>
       <c r="G1884" t="n">
-        <v>5.2439022064209</v>
+        <v>5.24390268325806</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1886" t="n">
-        <v>5.30774116516113</v>
+        <v>5.30774164199829</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49431,7 +49431,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1887" t="n">
-        <v>5.14905595779419</v>
+        <v>5.14905643463135</v>
       </c>
       <c r="H1887" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>5.66599988937378</v>
       </c>
       <c r="G1888" t="n">
-        <v>5.16729593276978</v>
+        <v>5.16729545593262</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1889" t="n">
-        <v>5.12169647216797</v>
+        <v>5.12169694900513</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1891" t="n">
-        <v>5.25484609603882</v>
+        <v>5.25484657287598</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G1892" t="n">
-        <v>5.40258693695068</v>
+        <v>5.40258741378784</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1894" t="n">
-        <v>5.40441179275513</v>
+        <v>5.40441131591797</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1895" t="n">
-        <v>5.40441179275513</v>
+        <v>5.40441131591797</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1897" t="n">
-        <v>5.36246061325073</v>
+        <v>5.36246013641357</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G1899" t="n">
-        <v>5.24572658538818</v>
+        <v>5.24572610855103</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1900" t="n">
-        <v>5.09616088867188</v>
+        <v>5.09616136550903</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.99219465255737</v>
+        <v>4.99219512939453</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G1905" t="n">
-        <v>4.97577905654907</v>
+        <v>4.97577953338623</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.84262990951538</v>
+        <v>4.84262943267822</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>4.80299997329712</v>
       </c>
       <c r="G1911" t="n">
-        <v>4.38025426864624</v>
+        <v>4.3802547454834</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G1913" t="n">
-        <v>4.50793218612671</v>
+        <v>4.50793170928955</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.56903505325317</v>
+        <v>4.56903553009033</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G1916" t="n">
-        <v>4.58909893035889</v>
+        <v>4.58909845352173</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>5.36399984359741</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.89187717437744</v>
+        <v>4.89187669754028</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>5.53599977493286</v>
       </c>
       <c r="G1926" t="n">
-        <v>5.04873752593994</v>
+        <v>5.0487380027771</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G1930" t="n">
-        <v>5.40258693695068</v>
+        <v>5.40258741378784</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>5.91800022125244</v>
       </c>
       <c r="G1934" t="n">
-        <v>5.39711570739746</v>
+        <v>5.39711618423462</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1935" t="n">
-        <v>5.45365810394287</v>
+        <v>5.45365858078003</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G1936" t="n">
-        <v>5.57403993606567</v>
+        <v>5.57404041290283</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1937" t="n">
-        <v>5.62693500518799</v>
+        <v>5.62693548202515</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>6.13800001144409</v>
       </c>
       <c r="G1939" t="n">
-        <v>5.59775161743164</v>
+        <v>5.5977520942688</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1943" t="n">
-        <v>5.73637342453003</v>
+        <v>5.73637294769287</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1946" t="n">
-        <v>5.69077348709106</v>
+        <v>5.69077396392822</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>6.18599987030029</v>
       </c>
       <c r="G1952" t="n">
-        <v>5.64152717590332</v>
+        <v>5.64152669906616</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1959" t="n">
-        <v>5.53208875656128</v>
+        <v>5.53208923339844</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -59626,6 +59626,32 @@
         <v>6.5149998664856</v>
       </c>
       <c r="H2279" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2280" t="n">
+        <v>1048725</v>
+      </c>
+      <c r="C2280" t="n">
+        <v>6.53499984741211</v>
+      </c>
+      <c r="D2280" t="n">
+        <v>6.41499996185303</v>
+      </c>
+      <c r="E2280" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F2280" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="G2280" t="n">
+        <v>6.48000001907349</v>
+      </c>
+      <c r="H2280" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G2" t="n">
-        <v>5.00744962692261</v>
+        <v>5.00744915008545</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G5" t="n">
-        <v>5.07710456848145</v>
+        <v>5.0771050453186</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G6" t="n">
-        <v>5.10419321060181</v>
+        <v>5.10419273376465</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G7" t="n">
-        <v>5.11193227767944</v>
+        <v>5.1119327545166</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>6.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.03066825866699</v>
+        <v>5.03066778182983</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>5.02679824829102</v>
+        <v>5.02679777145386</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>4.99971055984497</v>
+        <v>4.99971008300781</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>4.98423051834106</v>
+        <v>4.98423147201538</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G13" t="n">
-        <v>4.90683650970459</v>
+        <v>4.90683603286743</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>5.02679824829102</v>
+        <v>5.02679777145386</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G15" t="n">
-        <v>5.04227685928345</v>
+        <v>5.04227733612061</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>6.5</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03066825866699</v>
+        <v>5.03066778182983</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G18" t="n">
-        <v>5.04227685928345</v>
+        <v>5.04227733612061</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G19" t="n">
-        <v>5.10806274414062</v>
+        <v>5.10806322097778</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G20" t="n">
-        <v>5.11580276489258</v>
+        <v>5.11580228805542</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>6.75</v>
       </c>
       <c r="G21" t="n">
-        <v>5.22415494918823</v>
+        <v>5.22415447235107</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G24" t="n">
-        <v>5.33250761032104</v>
+        <v>5.3325080871582</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>5.41764259338379</v>
+        <v>5.41764211654663</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G26" t="n">
-        <v>5.45633983612061</v>
+        <v>5.45634031295776</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G27" t="n">
-        <v>5.36733531951904</v>
+        <v>5.3673357963562</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G28" t="n">
-        <v>5.35185623168945</v>
+        <v>5.35185718536377</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>5.23189496994019</v>
+        <v>5.23189544677734</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>5.29381036758423</v>
+        <v>5.29381084442139</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G32" t="n">
-        <v>5.26285314559937</v>
+        <v>5.26285266876221</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>5.26285314559937</v>
+        <v>5.26285266876221</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>5.29381036758423</v>
+        <v>5.29381084442139</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>5.28994131088257</v>
+        <v>5.28994083404541</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>5.44859981536865</v>
+        <v>5.44860076904297</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G38" t="n">
-        <v>5.45247077941895</v>
+        <v>5.45246982574463</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>5.44859981536865</v>
+        <v>5.44860076904297</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>5.47955846786499</v>
+        <v>5.47955894470215</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G42" t="n">
-        <v>5.46407890319824</v>
+        <v>5.4640793800354</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>5.42151212692261</v>
+        <v>5.42151165008545</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>5.340247631073</v>
+        <v>5.34024715423584</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>5.42925119400024</v>
+        <v>5.4292516708374</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G50" t="n">
-        <v>5.61886978149414</v>
+        <v>5.61886930465698</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G51" t="n">
-        <v>5.5879111289978</v>
+        <v>5.58791160583496</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G53" t="n">
-        <v>5.59178113937378</v>
+        <v>5.59178018569946</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G56" t="n">
-        <v>5.47181940078735</v>
+        <v>5.47181844711304</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>5.47955846786499</v>
+        <v>5.47955894470215</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G63" t="n">
-        <v>5.68078470230103</v>
+        <v>5.68078565597534</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>5.73496198654175</v>
+        <v>5.73496150970459</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G65" t="n">
-        <v>5.84718370437622</v>
+        <v>5.84718418121338</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>6.04841041564941</v>
+        <v>6.04841089248657</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>6.14902448654175</v>
+        <v>6.14902400970459</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G70" t="n">
-        <v>6.09871816635132</v>
+        <v>6.098717212677</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G73" t="n">
-        <v>6.13741445541382</v>
+        <v>6.13741493225098</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G74" t="n">
-        <v>6.05228042602539</v>
+        <v>6.05228090286255</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G77" t="n">
-        <v>6.05228042602539</v>
+        <v>6.05228090286255</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G79" t="n">
-        <v>5.97101593017578</v>
+        <v>5.9710168838501</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>5.94392681121826</v>
+        <v>5.94392824172974</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G81" t="n">
-        <v>6.05228042602539</v>
+        <v>6.05228090286255</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G82" t="n">
-        <v>6.06930732727051</v>
+        <v>6.06930780410767</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G86" t="n">
-        <v>5.88201236724854</v>
+        <v>5.88201141357422</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G87" t="n">
-        <v>5.72722291946411</v>
+        <v>5.72722244262695</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.55800008773804</v>
       </c>
       <c r="G89" t="n">
-        <v>5.84950590133667</v>
+        <v>5.84950685501099</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>7.32800006866455</v>
       </c>
       <c r="G90" t="n">
-        <v>5.67149782180786</v>
+        <v>5.67149829864502</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G95" t="n">
-        <v>5.78139877319336</v>
+        <v>5.78139781951904</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>7.67600011825562</v>
       </c>
       <c r="G96" t="n">
-        <v>5.94083166122437</v>
+        <v>5.94083261489868</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>7.52199983596802</v>
       </c>
       <c r="G97" t="n">
-        <v>5.8216438293457</v>
+        <v>5.82164430618286</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>7.41599988937378</v>
       </c>
       <c r="G98" t="n">
-        <v>5.73960494995117</v>
+        <v>5.73960542678833</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>5.71174287796021</v>
+        <v>5.71174335479736</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G101" t="n">
-        <v>5.79687690734863</v>
+        <v>5.79687738418579</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G102" t="n">
-        <v>5.79687690734863</v>
+        <v>5.79687738418579</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G103" t="n">
-        <v>5.79687690734863</v>
+        <v>5.79687738418579</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>7.28800010681152</v>
       </c>
       <c r="G104" t="n">
-        <v>5.640540599823</v>
+        <v>5.64053964614868</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>6.91200017929077</v>
       </c>
       <c r="G106" t="n">
-        <v>5.34953498840332</v>
+        <v>5.34953546524048</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>6.89200019836426</v>
       </c>
       <c r="G107" t="n">
-        <v>5.33405590057373</v>
+        <v>5.33405637741089</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G108" t="n">
-        <v>5.4857497215271</v>
+        <v>5.48574924468994</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G109" t="n">
-        <v>5.56159687042236</v>
+        <v>5.56159639358521</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>5.62660884857178</v>
+        <v>5.62660837173462</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G114" t="n">
-        <v>5.47181940078735</v>
+        <v>5.47181844711304</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>5.51051616668701</v>
+        <v>5.51051568984985</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>7.19799995422363</v>
       </c>
       <c r="G118" t="n">
-        <v>5.57088375091553</v>
+        <v>5.57088422775269</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G119" t="n">
-        <v>5.61886978149414</v>
+        <v>5.61886930465698</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G120" t="n">
-        <v>5.51051616668701</v>
+        <v>5.51051568984985</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>5.46407890319824</v>
+        <v>5.4640793800354</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>5.40216398239136</v>
+        <v>5.4021635055542</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G123" t="n">
-        <v>5.42538213729858</v>
+        <v>5.42538261413574</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>5.57243204116821</v>
+        <v>5.57243251800537</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G128" t="n">
-        <v>5.5554051399231</v>
+        <v>5.55540561676025</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>7.11199998855591</v>
       </c>
       <c r="G130" t="n">
-        <v>5.5043249130249</v>
+        <v>5.50432538986206</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G131" t="n">
-        <v>5.56159687042236</v>
+        <v>5.56159639358521</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503707885742</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G134" t="n">
-        <v>5.61886978149414</v>
+        <v>5.61886930465698</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>7.02199983596802</v>
       </c>
       <c r="G137" t="n">
-        <v>5.43466854095459</v>
+        <v>5.43466901779175</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>7.02400016784668</v>
       </c>
       <c r="G139" t="n">
-        <v>5.43621826171875</v>
+        <v>5.43621730804443</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G141" t="n">
-        <v>5.57243204116821</v>
+        <v>5.57243251800537</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.13600015640259</v>
       </c>
       <c r="G142" t="n">
-        <v>5.52289962768555</v>
+        <v>5.52289915084839</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>7.2519998550415</v>
       </c>
       <c r="G143" t="n">
-        <v>5.61267757415771</v>
+        <v>5.61267709732056</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.28200006484985</v>
       </c>
       <c r="G147" t="n">
-        <v>5.6358962059021</v>
+        <v>5.63589572906494</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.32800006866455</v>
       </c>
       <c r="G149" t="n">
-        <v>5.67149782180786</v>
+        <v>5.67149829864502</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>7.26800012588501</v>
       </c>
       <c r="G150" t="n">
-        <v>5.62506103515625</v>
+        <v>5.62506151199341</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503707885742</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>7.01200008392334</v>
       </c>
       <c r="G152" t="n">
-        <v>5.42692947387695</v>
+        <v>5.42692995071411</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.14400005340576</v>
       </c>
       <c r="G154" t="n">
-        <v>5.52909088134766</v>
+        <v>5.52909135818481</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G156" t="n">
-        <v>5.73496198654175</v>
+        <v>5.73496150970459</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>7.61199998855591</v>
       </c>
       <c r="G158" t="n">
-        <v>5.8912992477417</v>
+        <v>5.89129972457886</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7.67799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>5.94237947463989</v>
+        <v>5.94238042831421</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>5.89749050140381</v>
+        <v>5.89749097824097</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>7.41599988937378</v>
       </c>
       <c r="G161" t="n">
-        <v>5.73960494995117</v>
+        <v>5.73960542678833</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G163" t="n">
-        <v>5.75044059753418</v>
+        <v>5.75044012069702</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7.20800018310547</v>
       </c>
       <c r="G165" t="n">
-        <v>5.57862329483032</v>
+        <v>5.57862424850464</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>7.26399993896484</v>
       </c>
       <c r="G166" t="n">
-        <v>5.6219654083252</v>
+        <v>5.62196493148804</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>7.31799983978271</v>
       </c>
       <c r="G167" t="n">
-        <v>5.66375827789307</v>
+        <v>5.66375780105591</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>7.32800006866455</v>
       </c>
       <c r="G168" t="n">
-        <v>5.67149782180786</v>
+        <v>5.67149829864502</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>7.36199998855591</v>
       </c>
       <c r="G169" t="n">
-        <v>5.6978120803833</v>
+        <v>5.69781255722046</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7.47599983215332</v>
       </c>
       <c r="G170" t="n">
-        <v>5.78604221343994</v>
+        <v>5.78604173660278</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>7.27600002288818</v>
       </c>
       <c r="G173" t="n">
-        <v>5.63125228881836</v>
+        <v>5.63125276565552</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>5.77365875244141</v>
+        <v>5.77365970611572</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G176" t="n">
-        <v>5.75044059753418</v>
+        <v>5.75044012069702</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>5.72722291946411</v>
+        <v>5.72722244262695</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G178" t="n">
-        <v>5.76591968536377</v>
+        <v>5.76591920852661</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G179" t="n">
-        <v>5.72257804870605</v>
+        <v>5.72257852554321</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>5.67304563522339</v>
+        <v>5.67304515838623</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.649827003479</v>
+        <v>5.64982748031616</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G182" t="n">
-        <v>5.60339021682739</v>
+        <v>5.60339069366455</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G183" t="n">
-        <v>5.69316816329956</v>
+        <v>5.69316864013672</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.2519998550415</v>
       </c>
       <c r="G185" t="n">
-        <v>5.61267757415771</v>
+        <v>5.61267709732056</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>7.29199981689453</v>
       </c>
       <c r="G186" t="n">
-        <v>5.64363527297974</v>
+        <v>5.64363574981689</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>7.12400007247925</v>
       </c>
       <c r="G187" t="n">
-        <v>5.51361179351807</v>
+        <v>5.51361227035522</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G188" t="n">
-        <v>5.53528213500977</v>
+        <v>5.53528261184692</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G189" t="n">
-        <v>5.53528213500977</v>
+        <v>5.53528261184692</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>7.24200010299683</v>
       </c>
       <c r="G190" t="n">
-        <v>5.60493898391724</v>
+        <v>5.60493850708008</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G191" t="n">
-        <v>5.5554051399231</v>
+        <v>5.55540561676025</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7.13600015640259</v>
       </c>
       <c r="G193" t="n">
-        <v>5.52289962768555</v>
+        <v>5.52289915084839</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7.15799999237061</v>
       </c>
       <c r="G195" t="n">
-        <v>5.53992652893066</v>
+        <v>5.53992605209351</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7</v>
       </c>
       <c r="G196" t="n">
-        <v>5.41764259338379</v>
+        <v>5.41764211654663</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="n">
-        <v>5.41764259338379</v>
+        <v>5.41764211654663</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>5.47955846786499</v>
+        <v>5.47955894470215</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.0460000038147</v>
       </c>
       <c r="G201" t="n">
-        <v>5.45324468612671</v>
+        <v>5.45324420928955</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>7.13199996948242</v>
       </c>
       <c r="G202" t="n">
-        <v>5.51980352401733</v>
+        <v>5.51980400085449</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G204" t="n">
-        <v>5.47181940078735</v>
+        <v>5.47181844711304</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.13399982452393</v>
       </c>
       <c r="G205" t="n">
-        <v>5.5213508605957</v>
+        <v>5.52135133743286</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>7.44600009918213</v>
       </c>
       <c r="G207" t="n">
-        <v>5.76282358169556</v>
+        <v>5.76282405853271</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>7.46600008010864</v>
       </c>
       <c r="G208" t="n">
-        <v>5.7783031463623</v>
+        <v>5.77830266952515</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>7.52199983596802</v>
       </c>
       <c r="G209" t="n">
-        <v>5.8216438293457</v>
+        <v>5.82164430618286</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>7.47200012207031</v>
       </c>
       <c r="G210" t="n">
-        <v>5.78294610977173</v>
+        <v>5.78294658660889</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7.19799995422363</v>
       </c>
       <c r="G212" t="n">
-        <v>5.57088375091553</v>
+        <v>5.57088422775269</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>5.51825571060181</v>
+        <v>5.51825618743896</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>7.20800018310547</v>
       </c>
       <c r="G214" t="n">
-        <v>5.57862329483032</v>
+        <v>5.57862424850464</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>7.48799991607666</v>
       </c>
       <c r="G215" t="n">
-        <v>5.79532909393311</v>
+        <v>5.79532957077026</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.66599988937378</v>
       </c>
       <c r="G216" t="n">
-        <v>5.93309259414673</v>
+        <v>5.93309211730957</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.66599988937378</v>
       </c>
       <c r="G217" t="n">
-        <v>5.93309259414673</v>
+        <v>5.93309211730957</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.60400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>5.88510704040527</v>
+        <v>5.88510751724243</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>5.88201236724854</v>
+        <v>5.88201141357422</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>7.62200021743774</v>
       </c>
       <c r="G220" t="n">
-        <v>5.89903879165649</v>
+        <v>5.89903926849365</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>7.63800001144409</v>
       </c>
       <c r="G221" t="n">
-        <v>5.91142225265503</v>
+        <v>5.91142177581787</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>7.57800006866455</v>
       </c>
       <c r="G223" t="n">
-        <v>5.86498546600342</v>
+        <v>5.8649845123291</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>7.59800004959106</v>
       </c>
       <c r="G224" t="n">
-        <v>5.88046407699585</v>
+        <v>5.88046360015869</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G228" t="n">
-        <v>5.56159687042236</v>
+        <v>5.56159639358521</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G229" t="n">
-        <v>5.62041711807251</v>
+        <v>5.62041664123535</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>7.27600002288818</v>
       </c>
       <c r="G231" t="n">
-        <v>5.63125228881836</v>
+        <v>5.63125276565552</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>6.93800020217896</v>
       </c>
       <c r="G232" t="n">
-        <v>5.36965703964233</v>
+        <v>5.36965751647949</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>6.86199998855591</v>
       </c>
       <c r="G233" t="n">
-        <v>5.31083726882935</v>
+        <v>5.3108377456665</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G236" t="n">
-        <v>5.2164158821106</v>
+        <v>5.21641540527344</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>6.67199993133545</v>
       </c>
       <c r="G237" t="n">
-        <v>5.16378688812256</v>
+        <v>5.16378736495972</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G238" t="n">
-        <v>5.36346673965454</v>
+        <v>5.36346578598022</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7.01200008392334</v>
       </c>
       <c r="G239" t="n">
-        <v>5.42692947387695</v>
+        <v>5.42692995071411</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G240" t="n">
-        <v>5.49813270568848</v>
+        <v>5.49813318252563</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503707885742</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G242" t="n">
-        <v>5.49813270568848</v>
+        <v>5.49813318252563</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>7.22200012207031</v>
       </c>
       <c r="G243" t="n">
-        <v>5.58945846557617</v>
+        <v>5.58945941925049</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G244" t="n">
-        <v>5.55695295333862</v>
+        <v>5.55695343017578</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>5.51051616668701</v>
+        <v>5.51051568984985</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>7.10599994659424</v>
       </c>
       <c r="G248" t="n">
-        <v>5.499680519104</v>
+        <v>5.49968099594116</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G249" t="n">
-        <v>5.4857497215271</v>
+        <v>5.48574924468994</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G250" t="n">
-        <v>5.56159687042236</v>
+        <v>5.56159639358521</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>7.25600004196167</v>
       </c>
       <c r="G251" t="n">
-        <v>5.61577320098877</v>
+        <v>5.61577367782593</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>7.22800016403198</v>
       </c>
       <c r="G252" t="n">
-        <v>5.59410285949707</v>
+        <v>5.59410333633423</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G253" t="n">
-        <v>5.5662407875061</v>
+        <v>5.56624031066895</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.99200010299683</v>
       </c>
       <c r="G254" t="n">
-        <v>5.41145086288452</v>
+        <v>5.41145133972168</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G255" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503707885742</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>6.86399984359741</v>
       </c>
       <c r="G256" t="n">
-        <v>5.31238508224487</v>
+        <v>5.31238555908203</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>6.56599998474121</v>
       </c>
       <c r="G258" t="n">
-        <v>5.08174896240234</v>
+        <v>5.08174848556519</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G259" t="n">
-        <v>5.17771863937378</v>
+        <v>5.17771911621094</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>4.86813831329346</v>
+        <v>4.86813879013062</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G261" t="n">
-        <v>4.73037624359131</v>
+        <v>4.73037576675415</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>4.99197006225586</v>
+        <v>4.99197053909302</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>6.24200010299683</v>
       </c>
       <c r="G265" t="n">
-        <v>4.83098936080933</v>
+        <v>4.83098888397217</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>4.78300476074219</v>
+        <v>4.78300428390503</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G268" t="n">
-        <v>4.57094287872314</v>
+        <v>4.57094240188599</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G269" t="n">
-        <v>4.53534126281738</v>
+        <v>4.53534078598022</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G270" t="n">
-        <v>4.53534126281738</v>
+        <v>4.53534078598022</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>6.53800010681152</v>
       </c>
       <c r="G274" t="n">
-        <v>5.06007814407349</v>
+        <v>5.06007766723633</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>6.44600009918213</v>
       </c>
       <c r="G276" t="n">
-        <v>4.98887491226196</v>
+        <v>4.9888744354248</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G277" t="n">
-        <v>4.94088935852051</v>
+        <v>4.94089031219482</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>5.01518869400024</v>
+        <v>5.01518964767456</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>6.33599996566772</v>
       </c>
       <c r="G281" t="n">
-        <v>4.90373992919922</v>
+        <v>4.90374040603638</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>6.2020001411438</v>
       </c>
       <c r="G286" t="n">
-        <v>4.8000316619873</v>
+        <v>4.80003023147583</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>6.29199981689453</v>
       </c>
       <c r="G288" t="n">
-        <v>4.8696870803833</v>
+        <v>4.86968660354614</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>6.23400020599365</v>
       </c>
       <c r="G289" t="n">
-        <v>4.82479763031006</v>
+        <v>4.8247971534729</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G290" t="n">
-        <v>4.93005466461182</v>
+        <v>4.93005418777466</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.42399978637695</v>
       </c>
       <c r="G292" t="n">
-        <v>4.97184801101685</v>
+        <v>4.971848487854</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.40799999237061</v>
       </c>
       <c r="G294" t="n">
-        <v>4.95946407318115</v>
+        <v>4.95946502685547</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G295" t="n">
-        <v>4.79848289489746</v>
+        <v>4.7984824180603</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>6.24399995803833</v>
       </c>
       <c r="G296" t="n">
-        <v>4.8325366973877</v>
+        <v>4.83253717422485</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>6.20599985122681</v>
       </c>
       <c r="G300" t="n">
-        <v>4.8031268119812</v>
+        <v>4.80312728881836</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G303" t="n">
-        <v>4.53534126281738</v>
+        <v>4.53534078598022</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.00799989700317</v>
       </c>
       <c r="G306" t="n">
-        <v>4.6498851776123</v>
+        <v>4.64988470077515</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>4.52760171890259</v>
+        <v>4.52760076522827</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.72599983215332</v>
       </c>
       <c r="G308" t="n">
-        <v>4.43163156509399</v>
+        <v>4.43163108825684</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G309" t="n">
-        <v>4.38674259185791</v>
+        <v>4.38674211502075</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>5.7480001449585</v>
       </c>
       <c r="G310" t="n">
-        <v>4.44865894317627</v>
+        <v>4.44865846633911</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G313" t="n">
-        <v>4.27529382705688</v>
+        <v>4.27529430389404</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>5.55399990081787</v>
       </c>
       <c r="G315" t="n">
-        <v>4.29851245880127</v>
+        <v>4.29851198196411</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.44600009918213</v>
       </c>
       <c r="G316" t="n">
-        <v>4.21492624282837</v>
+        <v>4.21492576599121</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G317" t="n">
-        <v>4.40531778335571</v>
+        <v>4.4053168296814</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.63800001144409</v>
       </c>
       <c r="G318" t="n">
-        <v>4.36352443695068</v>
+        <v>4.36352348327637</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G322" t="n">
-        <v>4.69013071060181</v>
+        <v>4.69013023376465</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>6.0460000038147</v>
       </c>
       <c r="G323" t="n">
-        <v>4.67929553985596</v>
+        <v>4.6792950630188</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>6.06199979782104</v>
       </c>
       <c r="G324" t="n">
-        <v>4.69167804718018</v>
+        <v>4.69167852401733</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>4.72108793258667</v>
+        <v>4.72108840942383</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.98199987411499</v>
       </c>
       <c r="G339" t="n">
-        <v>4.62976264953613</v>
+        <v>4.62976217269897</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.71799993515015</v>
       </c>
       <c r="G343" t="n">
-        <v>4.42543935775757</v>
+        <v>4.42543983459473</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>6.06799983978271</v>
       </c>
       <c r="G344" t="n">
-        <v>4.69632196426392</v>
+        <v>4.69632244110107</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>5.98400020599365</v>
       </c>
       <c r="G346" t="n">
-        <v>4.63131046295166</v>
+        <v>4.6313099861145</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G351" t="n">
-        <v>4.72108793258667</v>
+        <v>4.72108840942383</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G354" t="n">
-        <v>4.69477462768555</v>
+        <v>4.69477415084839</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>6.15399980545044</v>
       </c>
       <c r="G358" t="n">
-        <v>4.7628812789917</v>
+        <v>4.76288080215454</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>4.72108793258667</v>
+        <v>4.72108840942383</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G362" t="n">
-        <v>4.54772329330444</v>
+        <v>4.54772424697876</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G363" t="n">
-        <v>4.49509477615356</v>
+        <v>4.49509572982788</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.80600023269653</v>
       </c>
       <c r="G365" t="n">
-        <v>4.49354839324951</v>
+        <v>4.49354791641235</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.83799982070923</v>
       </c>
       <c r="G366" t="n">
-        <v>4.51831340789795</v>
+        <v>4.51831293106079</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>4.61273527145386</v>
+        <v>4.61273574829102</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.97200012207031</v>
       </c>
       <c r="G368" t="n">
-        <v>4.6220235824585</v>
+        <v>4.62202310562134</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G369" t="n">
-        <v>4.67000770568848</v>
+        <v>4.67000722885132</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G370" t="n">
-        <v>4.67000770568848</v>
+        <v>4.67000722885132</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G371" t="n">
-        <v>4.68548583984375</v>
+        <v>4.68548631668091</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.93400001525879</v>
       </c>
       <c r="G372" t="n">
-        <v>4.59261322021484</v>
+        <v>4.59261274337769</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G375" t="n">
-        <v>4.47342538833618</v>
+        <v>4.47342491149902</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>5.82800006866455</v>
       </c>
       <c r="G378" t="n">
-        <v>4.51057481765747</v>
+        <v>4.51057434082031</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G379" t="n">
-        <v>4.64059829711914</v>
+        <v>4.64059782028198</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G380" t="n">
-        <v>4.79848289489746</v>
+        <v>4.7984824180603</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G382" t="n">
-        <v>4.86813831329346</v>
+        <v>4.86813879013062</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.26800012588501</v>
       </c>
       <c r="G383" t="n">
-        <v>4.85111141204834</v>
+        <v>4.85111236572266</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G386" t="n">
-        <v>4.91612386703491</v>
+        <v>4.91612434387207</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.51200008392334</v>
       </c>
       <c r="G388" t="n">
-        <v>5.03995561599731</v>
+        <v>5.03995609283447</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G389" t="n">
-        <v>5.02757167816162</v>
+        <v>5.02757215499878</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.5</v>
       </c>
       <c r="G390" t="n">
-        <v>5.03066825866699</v>
+        <v>5.03066778182983</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>4.98423051834106</v>
+        <v>4.98423147201538</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G392" t="n">
-        <v>4.96875238418579</v>
+        <v>4.96875190734863</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.4060001373291</v>
       </c>
       <c r="G394" t="n">
-        <v>4.95791673660278</v>
+        <v>4.95791721343994</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G396" t="n">
-        <v>4.99971055984497</v>
+        <v>4.99971008300781</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.50799989700317</v>
       </c>
       <c r="G397" t="n">
-        <v>5.0368595123291</v>
+        <v>5.03685998916626</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.30600023269653</v>
       </c>
       <c r="G398" t="n">
-        <v>4.88052272796631</v>
+        <v>4.88052225112915</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>6.17799997329712</v>
       </c>
       <c r="G399" t="n">
-        <v>4.78145694732666</v>
+        <v>4.7814564704895</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>5.97399997711182</v>
       </c>
       <c r="G400" t="n">
-        <v>4.62357139587402</v>
+        <v>4.62357091903687</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G401" t="n">
-        <v>4.55081939697266</v>
+        <v>4.55081987380981</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>5.77799987792969</v>
       </c>
       <c r="G403" t="n">
-        <v>4.4718770980835</v>
+        <v>4.47187662124634</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>5.72800016403198</v>
       </c>
       <c r="G404" t="n">
-        <v>4.43317985534668</v>
+        <v>4.43317937850952</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G406" t="n">
-        <v>4.40376901626587</v>
+        <v>4.40376949310303</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G410" t="n">
-        <v>4.3749361038208</v>
+        <v>4.37493562698364</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>5.57600021362305</v>
       </c>
       <c r="G411" t="n">
-        <v>4.45157623291016</v>
+        <v>4.45157670974731</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G416" t="n">
-        <v>4.14660835266113</v>
+        <v>4.14660882949829</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5.17799997329712</v>
       </c>
       <c r="G422" t="n">
-        <v>4.13383531570435</v>
+        <v>4.1338357925415</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5.18800020217896</v>
       </c>
       <c r="G423" t="n">
-        <v>4.14181900024414</v>
+        <v>4.14181852340698</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G425" t="n">
-        <v>4.18972015380859</v>
+        <v>4.18971920013428</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.32800006866455</v>
       </c>
       <c r="G426" t="n">
-        <v>4.25358724594116</v>
+        <v>4.253586769104</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.29199981689453</v>
       </c>
       <c r="G429" t="n">
-        <v>4.22484636306763</v>
+        <v>4.22484683990479</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.2519998550415</v>
       </c>
       <c r="G430" t="n">
-        <v>4.19291305541992</v>
+        <v>4.19291257858276</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>5.2979998588562</v>
       </c>
       <c r="G431" t="n">
-        <v>4.22963619232178</v>
+        <v>4.22963666915894</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>5.47599983215332</v>
       </c>
       <c r="G433" t="n">
-        <v>4.371741771698</v>
+        <v>4.37174224853516</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G434" t="n">
-        <v>4.39249897003174</v>
+        <v>4.3924994468689</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G435" t="n">
-        <v>4.35577583312988</v>
+        <v>4.35577487945557</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G436" t="n">
-        <v>4.29829454421997</v>
+        <v>4.29829406738281</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>5.19799995422363</v>
       </c>
       <c r="G439" t="n">
-        <v>4.14980220794678</v>
+        <v>4.14980268478394</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>5.30600023269653</v>
       </c>
       <c r="G440" t="n">
-        <v>4.23602294921875</v>
+        <v>4.23602390289307</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>5.3439998626709</v>
       </c>
       <c r="G443" t="n">
-        <v>4.26636028289795</v>
+        <v>4.26636075973511</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G445" t="n">
-        <v>4.36056518554688</v>
+        <v>4.36056613922119</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G448" t="n">
-        <v>4.40367650985718</v>
+        <v>4.40367603302002</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54737854003906</v>
+        <v>4.5473780632019</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>5.36399984359741</v>
       </c>
       <c r="G452" t="n">
-        <v>4.28232717514038</v>
+        <v>4.28232765197754</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G453" t="n">
-        <v>4.1513991355896</v>
+        <v>4.15139865875244</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5.68200016021729</v>
       </c>
       <c r="G456" t="n">
-        <v>4.53620147705078</v>
+        <v>4.53620100021362</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G457" t="n">
-        <v>4.63359928131104</v>
+        <v>4.63359975814819</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.60799980163574</v>
       </c>
       <c r="G459" t="n">
-        <v>4.47712326049805</v>
+        <v>4.47712421417236</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.46799993515015</v>
       </c>
       <c r="G460" t="n">
-        <v>4.36535549163818</v>
+        <v>4.36535501480103</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.31400012969971</v>
       </c>
       <c r="G461" t="n">
-        <v>4.24241018295288</v>
+        <v>4.24241065979004</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.3439998626709</v>
       </c>
       <c r="G462" t="n">
-        <v>4.26636028289795</v>
+        <v>4.26636075973511</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.38800001144409</v>
       </c>
       <c r="G463" t="n">
-        <v>4.30148839950562</v>
+        <v>4.3014874458313</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>3.87197756767273</v>
+        <v>3.87197732925415</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G466" t="n">
-        <v>3.7681930065155</v>
+        <v>3.76819229125977</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.75299978256226</v>
       </c>
       <c r="G471" t="n">
-        <v>3.79453778266907</v>
+        <v>3.79453825950623</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G473" t="n">
-        <v>3.60533022880554</v>
+        <v>3.6053295135498</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G474" t="n">
-        <v>3.67957615852356</v>
+        <v>3.67957639694214</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.51300001144409</v>
       </c>
       <c r="G475" t="n">
-        <v>3.60293507575989</v>
+        <v>3.60293531417847</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G476" t="n">
-        <v>3.74264597892761</v>
+        <v>3.74264574050903</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.84700012207031</v>
       </c>
       <c r="G480" t="n">
-        <v>3.86958312988281</v>
+        <v>3.86958265304565</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.82407665252686</v>
+        <v>3.82407736778259</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.74025058746338</v>
+        <v>3.74025082588196</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>3.76020956039429</v>
+        <v>3.76020932197571</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>4.42283582687378</v>
+        <v>4.4228367805481</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G493" t="n">
-        <v>4.51863813400269</v>
+        <v>4.51863765716553</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G496" t="n">
-        <v>4.52183151245117</v>
+        <v>4.52183103561401</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G497" t="n">
-        <v>4.56973218917847</v>
+        <v>4.56973266601562</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G498" t="n">
-        <v>4.52183151245117</v>
+        <v>4.52183103561401</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G501" t="n">
-        <v>4.29510116577148</v>
+        <v>4.29510068893433</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>4.42283582687378</v>
+        <v>4.4228367805481</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G511" t="n">
-        <v>4.07954740524292</v>
+        <v>4.07954788208008</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G512" t="n">
-        <v>4.25518369674683</v>
+        <v>4.25518417358398</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G515" t="n">
-        <v>4.48510694503784</v>
+        <v>4.485107421875</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G517" t="n">
-        <v>4.43081998825073</v>
+        <v>4.43081951141357</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.4539999961853</v>
       </c>
       <c r="G519" t="n">
-        <v>4.35417890548706</v>
+        <v>4.3541784286499</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G520" t="n">
-        <v>4.40048313140869</v>
+        <v>4.40048265457153</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.4539999961853</v>
       </c>
       <c r="G522" t="n">
-        <v>4.35417890548706</v>
+        <v>4.3541784286499</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G525" t="n">
-        <v>4.63679361343384</v>
+        <v>4.63679313659668</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.18800020217896</v>
       </c>
       <c r="G526" t="n">
-        <v>4.14181900024414</v>
+        <v>4.14181852340698</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G528" t="n">
-        <v>4.18333292007446</v>
+        <v>4.1833324432373</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G529" t="n">
-        <v>4.32703495025635</v>
+        <v>4.32703447341919</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.28711700439453</v>
+        <v>4.28711748123169</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>4.3749361038208</v>
+        <v>4.37493562698364</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.44799995422363</v>
       </c>
       <c r="G533" t="n">
-        <v>4.34938907623291</v>
+        <v>4.34938859939575</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.4980001449585</v>
       </c>
       <c r="G534" t="n">
-        <v>4.38930559158325</v>
+        <v>4.38930606842041</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.41485261917114</v>
+        <v>4.41485357284546</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G536" t="n">
-        <v>4.28073072433472</v>
+        <v>4.28073120117188</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G537" t="n">
-        <v>4.22644329071045</v>
+        <v>4.22644424438477</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>5.21400022506714</v>
       </c>
       <c r="G540" t="n">
-        <v>4.16257572174072</v>
+        <v>4.16257619857788</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.18800020217896</v>
       </c>
       <c r="G542" t="n">
-        <v>4.14181900024414</v>
+        <v>4.14181852340698</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G543" t="n">
-        <v>4.13543176651001</v>
+        <v>4.13543128967285</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G546" t="n">
-        <v>4.22644329071045</v>
+        <v>4.22644424438477</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.26399993896484</v>
       </c>
       <c r="G547" t="n">
-        <v>4.20249319076538</v>
+        <v>4.20249271392822</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G548" t="n">
-        <v>4.11148118972778</v>
+        <v>4.11148166656494</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G549" t="n">
-        <v>4.06996726989746</v>
+        <v>4.06996822357178</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G550" t="n">
-        <v>4.03164672851562</v>
+        <v>4.03164720535278</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G551" t="n">
-        <v>4.06996726989746</v>
+        <v>4.06996822357178</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.07800006866455</v>
       </c>
       <c r="G552" t="n">
-        <v>4.05399990081787</v>
+        <v>4.05400085449219</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.14200019836426</v>
       </c>
       <c r="G553" t="n">
-        <v>4.10509443283081</v>
+        <v>4.10509490966797</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G555" t="n">
-        <v>4.10669136047363</v>
+        <v>4.10669088363647</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.28200006484985</v>
       </c>
       <c r="G557" t="n">
-        <v>4.21686267852783</v>
+        <v>4.21686315536499</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G560" t="n">
-        <v>4.20089673995972</v>
+        <v>4.20089626312256</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G561" t="n">
-        <v>4.16576862335205</v>
+        <v>4.16576910018921</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G562" t="n">
-        <v>4.09870767593384</v>
+        <v>4.098708152771</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G563" t="n">
-        <v>4.15778589248657</v>
+        <v>4.15778541564941</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.21600008010864</v>
       </c>
       <c r="G564" t="n">
-        <v>4.16417264938354</v>
+        <v>4.16417217254639</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G567" t="n">
-        <v>4.26795721054077</v>
+        <v>4.26795768737793</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.14599990844727</v>
       </c>
       <c r="G569" t="n">
-        <v>4.1082878112793</v>
+        <v>4.10828876495361</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G570" t="n">
-        <v>4.16576862335205</v>
+        <v>4.16576910018921</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G577" t="n">
-        <v>4.05080699920654</v>
+        <v>4.0508074760437</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G578" t="n">
-        <v>4.04761362075806</v>
+        <v>4.04761409759521</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>4.05559682846069</v>
+        <v>4.05559778213501</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G582" t="n">
-        <v>3.92147564888</v>
+        <v>3.92147541046143</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.78900003433228</v>
       </c>
       <c r="G583" t="n">
-        <v>3.82327842712402</v>
+        <v>3.8232786655426</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G584" t="n">
-        <v>3.64524745941162</v>
+        <v>3.64524722099304</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.58300018310547</v>
       </c>
       <c r="G585" t="n">
-        <v>3.65881967544556</v>
+        <v>3.6588191986084</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G587" t="n">
-        <v>3.62129688262939</v>
+        <v>3.62129664421082</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G588" t="n">
-        <v>3.4903678894043</v>
+        <v>3.49036812782288</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G589" t="n">
-        <v>3.50314164161682</v>
+        <v>3.5031418800354</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G591" t="n">
-        <v>3.68037462234497</v>
+        <v>3.68037486076355</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.59299993515015</v>
       </c>
       <c r="G592" t="n">
-        <v>3.66680288314819</v>
+        <v>3.66680264472961</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>3.62848210334778</v>
+        <v>3.62848258018494</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.45100021362305</v>
       </c>
       <c r="G595" t="n">
-        <v>3.55343794822693</v>
+        <v>3.55343723297119</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G596" t="n">
-        <v>3.67957615852356</v>
+        <v>3.67957639694214</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G597" t="n">
-        <v>3.60054039955139</v>
+        <v>3.60054016113281</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>3.60852336883545</v>
+        <v>3.60852360725403</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G599" t="n">
-        <v>3.7681930065155</v>
+        <v>3.76819229125977</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.70900011062622</v>
       </c>
       <c r="G600" t="n">
-        <v>3.7594108581543</v>
+        <v>3.75941133499146</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G602" t="n">
-        <v>3.86798572540283</v>
+        <v>3.86798548698425</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.75299978256226</v>
       </c>
       <c r="G603" t="n">
-        <v>3.79453778266907</v>
+        <v>3.79453825950623</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.45900011062622</v>
       </c>
       <c r="G604" t="n">
-        <v>3.55982494354248</v>
+        <v>3.5598247051239</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G607" t="n">
-        <v>3.44885444641113</v>
+        <v>3.44885420799255</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.25299978256226</v>
       </c>
       <c r="G608" t="n">
-        <v>3.39536476135254</v>
+        <v>3.39536499977112</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.01700019836426</v>
       </c>
       <c r="G611" t="n">
-        <v>3.20695567131042</v>
+        <v>3.20695543289185</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G613" t="n">
-        <v>3.1087589263916</v>
+        <v>3.10875916481018</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>2.95228290557861</v>
+        <v>2.95228338241577</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.81299996376038</v>
       </c>
       <c r="G616" t="n">
-        <v>3.04409289360046</v>
+        <v>3.04409265518188</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.13700008392334</v>
       </c>
       <c r="G617" t="n">
-        <v>2.50441122055054</v>
+        <v>2.50441098213196</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G619" t="n">
-        <v>2.54831981658936</v>
+        <v>2.54832029342651</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.61899995803833</v>
       </c>
       <c r="G621" t="n">
-        <v>2.88921403884888</v>
+        <v>2.8892138004303</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G623" t="n">
-        <v>2.8740451335907</v>
+        <v>2.87404537200928</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G625" t="n">
-        <v>2.86606168746948</v>
+        <v>2.86606192588806</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>3.34100008010864</v>
       </c>
       <c r="G629" t="n">
-        <v>2.6672739982605</v>
+        <v>2.66727352142334</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44134163856506</v>
+        <v>2.44134187698364</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>2.52676510810852</v>
+        <v>2.52676486968994</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>2.52676510810852</v>
+        <v>2.52676486968994</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.38199996948242</v>
       </c>
       <c r="G636" t="n">
-        <v>2.70000576972961</v>
+        <v>2.70000600814819</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G637" t="n">
-        <v>2.69681239128113</v>
+        <v>2.69681262969971</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G639" t="n">
-        <v>2.4908390045166</v>
+        <v>2.49083924293518</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>2.62655782699585</v>
+        <v>2.62655806541443</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G644" t="n">
-        <v>2.61857438087463</v>
+        <v>2.61857461929321</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G648" t="n">
-        <v>2.73513317108154</v>
+        <v>2.73513293266296</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G649" t="n">
-        <v>2.81816077232361</v>
+        <v>2.81816101074219</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3.55399990081787</v>
       </c>
       <c r="G650" t="n">
-        <v>2.83732128143311</v>
+        <v>2.83732151985168</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G651" t="n">
-        <v>2.81017732620239</v>
+        <v>2.81017780303955</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>3.66899991035461</v>
       </c>
       <c r="G655" t="n">
-        <v>2.92913126945496</v>
+        <v>2.92913103103638</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.60700011253357</v>
       </c>
       <c r="G656" t="n">
-        <v>2.87963390350342</v>
+        <v>2.87963366508484</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>2.90997076034546</v>
+        <v>2.90997099876404</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.59699988365173</v>
       </c>
       <c r="G660" t="n">
-        <v>2.87165021896362</v>
+        <v>2.87164998054504</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G661" t="n">
-        <v>2.92593741416931</v>
+        <v>2.92593765258789</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.45099997520447</v>
       </c>
       <c r="G662" t="n">
-        <v>2.75509166717529</v>
+        <v>2.75509142875671</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.58899998664856</v>
       </c>
       <c r="G664" t="n">
-        <v>2.86526370048523</v>
+        <v>2.86526346206665</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.57699990272522</v>
       </c>
       <c r="G665" t="n">
-        <v>2.85568332672119</v>
+        <v>2.85568284988403</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G666" t="n">
-        <v>2.89320540428162</v>
+        <v>2.89320588111877</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G671" t="n">
-        <v>3.21094703674316</v>
+        <v>3.21094727516174</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G673" t="n">
-        <v>3.37380981445312</v>
+        <v>3.37380957603455</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G675" t="n">
-        <v>3.53986573219299</v>
+        <v>3.53986597061157</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G678" t="n">
-        <v>3.36502814292908</v>
+        <v>3.3650279045105</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4</v>
       </c>
       <c r="G683" t="n">
-        <v>3.19338345527649</v>
+        <v>3.19338369369507</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G684" t="n">
-        <v>3.14069271087646</v>
+        <v>3.14069318771362</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.01100015640259</v>
       </c>
       <c r="G687" t="n">
-        <v>3.20216584205627</v>
+        <v>3.2021656036377</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G688" t="n">
-        <v>3.04010152816772</v>
+        <v>3.04010128974915</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G689" t="n">
-        <v>3.04808497428894</v>
+        <v>3.04808473587036</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>3.04010152816772</v>
+        <v>3.04010128974915</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G696" t="n">
-        <v>3.03211760520935</v>
+        <v>3.03211784362793</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>3.75</v>
       </c>
       <c r="G698" t="n">
-        <v>2.99379706382751</v>
+        <v>2.99379730224609</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.64100003242493</v>
       </c>
       <c r="G699" t="n">
-        <v>2.90677762031555</v>
+        <v>2.90677738189697</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G700" t="n">
-        <v>2.96585512161255</v>
+        <v>2.96585464477539</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G701" t="n">
-        <v>3.02094101905823</v>
+        <v>3.02094078063965</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G703" t="n">
-        <v>3.05287480354309</v>
+        <v>3.05287456512451</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G704" t="n">
-        <v>3.03371453285217</v>
+        <v>3.03371429443359</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G706" t="n">
-        <v>2.98581385612488</v>
+        <v>2.9858136177063</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>3.76699995994568</v>
       </c>
       <c r="G708" t="n">
-        <v>3.00736880302429</v>
+        <v>3.00736904144287</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>3.61899995803833</v>
       </c>
       <c r="G710" t="n">
-        <v>2.88921403884888</v>
+        <v>2.8892138004303</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G711" t="n">
-        <v>2.90997076034546</v>
+        <v>2.90997099876404</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>3.58899998664856</v>
       </c>
       <c r="G713" t="n">
-        <v>2.86526370048523</v>
+        <v>2.86526346206665</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.46399998664856</v>
       </c>
       <c r="G716" t="n">
-        <v>2.76547002792358</v>
+        <v>2.76547026634216</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G718" t="n">
-        <v>2.94908952713013</v>
+        <v>2.94908976554871</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G720" t="n">
-        <v>2.71118235588074</v>
+        <v>2.7111828327179</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G722" t="n">
-        <v>2.96825003623962</v>
+        <v>2.9682502746582</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G723" t="n">
-        <v>2.996990442276</v>
+        <v>2.99699068069458</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G724" t="n">
-        <v>2.98581385612488</v>
+        <v>2.9858136177063</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>3.71900010108948</v>
       </c>
       <c r="G725" t="n">
-        <v>2.96904850006104</v>
+        <v>2.96904826164246</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>3.71900010108948</v>
       </c>
       <c r="G726" t="n">
-        <v>2.96904850006104</v>
+        <v>2.96904826164246</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G727" t="n">
-        <v>2.96345973014832</v>
+        <v>2.96346020698547</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>3.73300004005432</v>
       </c>
       <c r="G728" t="n">
-        <v>2.98022556304932</v>
+        <v>2.98022532463074</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>3.6470000743866</v>
       </c>
       <c r="G729" t="n">
-        <v>2.9115674495697</v>
+        <v>2.91156768798828</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.69899988174438</v>
       </c>
       <c r="G731" t="n">
-        <v>2.9530816078186</v>
+        <v>2.95308136940002</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>3.66100001335144</v>
       </c>
       <c r="G732" t="n">
-        <v>2.9227442741394</v>
+        <v>2.92274451255798</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G733" t="n">
-        <v>2.95068621635437</v>
+        <v>2.95068669319153</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>2.96186327934265</v>
+        <v>2.96186351776123</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G740" t="n">
-        <v>2.95228290557861</v>
+        <v>2.95228338241577</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>3.67799997329712</v>
       </c>
       <c r="G741" t="n">
-        <v>2.93631601333618</v>
+        <v>2.93631649017334</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G743" t="n">
-        <v>3.07522869110107</v>
+        <v>3.0752284526825</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G747" t="n">
-        <v>3.06165671348572</v>
+        <v>3.06165647506714</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.95900011062622</v>
       </c>
       <c r="G750" t="n">
-        <v>3.16065144538879</v>
+        <v>3.16065168380737</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>3.81900000572205</v>
       </c>
       <c r="G753" t="n">
-        <v>3.04888319969177</v>
+        <v>3.04888296127319</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G754" t="n">
-        <v>2.98980522155762</v>
+        <v>2.9898054599762</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G758" t="n">
-        <v>2.92354226112366</v>
+        <v>2.92354273796082</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.53299999237061</v>
       </c>
       <c r="G760" t="n">
-        <v>2.82055616378784</v>
+        <v>2.82055592536926</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.82699990272522</v>
       </c>
       <c r="G763" t="n">
-        <v>3.05526971817017</v>
+        <v>3.05526947975159</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G766" t="n">
-        <v>3.11674237251282</v>
+        <v>3.1167426109314</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G768" t="n">
-        <v>3.0688419342041</v>
+        <v>3.06884169578552</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.67799997329712</v>
       </c>
       <c r="G769" t="n">
-        <v>2.93631601333618</v>
+        <v>2.93631649017334</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G770" t="n">
-        <v>2.93950939178467</v>
+        <v>2.93950963020325</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G772" t="n">
-        <v>3.06963992118835</v>
+        <v>3.06964015960693</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.68899989128113</v>
       </c>
       <c r="G773" t="n">
-        <v>2.94509792327881</v>
+        <v>2.94509768486023</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G778" t="n">
-        <v>2.7926139831543</v>
+        <v>2.79261374473572</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.4539999961853</v>
       </c>
       <c r="G779" t="n">
-        <v>2.75748682022095</v>
+        <v>2.75748705863953</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G780" t="n">
-        <v>2.85807824134827</v>
+        <v>2.85807847976685</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G781" t="n">
-        <v>2.91396236419678</v>
+        <v>2.91396260261536</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.86899995803833</v>
       </c>
       <c r="G782" t="n">
-        <v>3.08879995346069</v>
+        <v>3.08880019187927</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.71900010108948</v>
       </c>
       <c r="G784" t="n">
-        <v>2.96904850006104</v>
+        <v>2.96904826164246</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.69099998474121</v>
       </c>
       <c r="G785" t="n">
-        <v>2.94669485092163</v>
+        <v>2.94669461250305</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G786" t="n">
-        <v>3.36582684516907</v>
+        <v>3.36582636833191</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.23299980163574</v>
       </c>
       <c r="G787" t="n">
-        <v>3.37939834594727</v>
+        <v>3.37939786911011</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4</v>
       </c>
       <c r="G789" t="n">
-        <v>3.19338345527649</v>
+        <v>3.19338369369507</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G790" t="n">
-        <v>3.33708596229553</v>
+        <v>3.33708572387695</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.22900009155273</v>
       </c>
       <c r="G791" t="n">
-        <v>3.37620520591736</v>
+        <v>3.37620496749878</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G794" t="n">
-        <v>3.34666609764099</v>
+        <v>3.34666585922241</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G795" t="n">
-        <v>3.33708596229553</v>
+        <v>3.33708572387695</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G797" t="n">
-        <v>3.40734028816223</v>
+        <v>3.40734052658081</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G798" t="n">
-        <v>3.45843386650085</v>
+        <v>3.45843434333801</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G799" t="n">
-        <v>3.54146194458008</v>
+        <v>3.54146218299866</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.5</v>
       </c>
       <c r="G801" t="n">
-        <v>3.5925567150116</v>
+        <v>3.59255647659302</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.50099992752075</v>
       </c>
       <c r="G802" t="n">
-        <v>3.59335494041443</v>
+        <v>3.59335470199585</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.42199993133545</v>
       </c>
       <c r="G804" t="n">
-        <v>3.53028559684753</v>
+        <v>3.53028583526611</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>3.55663108825684</v>
+        <v>3.55663061141968</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.45900011062622</v>
       </c>
       <c r="G807" t="n">
-        <v>3.55982494354248</v>
+        <v>3.5598247051239</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.48899984359741</v>
       </c>
       <c r="G811" t="n">
-        <v>3.58377480506897</v>
+        <v>3.58377456665039</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G812" t="n">
-        <v>3.51272177696228</v>
+        <v>3.51272225379944</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G813" t="n">
-        <v>3.57259798049927</v>
+        <v>3.57259750366211</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G814" t="n">
-        <v>3.73945236206055</v>
+        <v>3.73945212364197</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G815" t="n">
-        <v>3.50793194770813</v>
+        <v>3.50793218612671</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.35099983215332</v>
       </c>
       <c r="G817" t="n">
-        <v>3.47360301017761</v>
+        <v>3.47360253334045</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.40299987792969</v>
       </c>
       <c r="G818" t="n">
-        <v>3.51511693000793</v>
+        <v>3.51511669158936</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.43300008773804</v>
       </c>
       <c r="G821" t="n">
-        <v>3.53906750679016</v>
+        <v>3.53906726837158</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.35900020599365</v>
       </c>
       <c r="G822" t="n">
-        <v>3.47999024391174</v>
+        <v>3.47998952865601</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.29300022125244</v>
       </c>
       <c r="G824" t="n">
-        <v>3.42729878425598</v>
+        <v>3.42729902267456</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G827" t="n">
-        <v>3.50633525848389</v>
+        <v>3.50633502006531</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G828" t="n">
-        <v>3.62129688262939</v>
+        <v>3.62129664421082</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G829" t="n">
-        <v>3.58297610282898</v>
+        <v>3.58297634124756</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G832" t="n">
-        <v>3.53667211532593</v>
+        <v>3.53667235374451</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G833" t="n">
-        <v>3.50793194770813</v>
+        <v>3.50793218612671</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.43100023269653</v>
       </c>
       <c r="G835" t="n">
-        <v>3.53747129440308</v>
+        <v>3.53747034072876</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.29099988937378</v>
       </c>
       <c r="G836" t="n">
-        <v>3.42570209503174</v>
+        <v>3.42570233345032</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G838" t="n">
-        <v>3.44885444641113</v>
+        <v>3.44885420799255</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.26900005340576</v>
       </c>
       <c r="G839" t="n">
-        <v>3.40813851356506</v>
+        <v>3.40813875198364</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G841" t="n">
-        <v>3.44087100028992</v>
+        <v>3.44087076187134</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G842" t="n">
-        <v>3.41692090034485</v>
+        <v>3.41692066192627</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.3730001449585</v>
       </c>
       <c r="G843" t="n">
-        <v>3.49116659164429</v>
+        <v>3.49116683006287</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G845" t="n">
-        <v>3.72029185295105</v>
+        <v>3.72029161453247</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.72300004959106</v>
       </c>
       <c r="G847" t="n">
-        <v>3.77058792114258</v>
+        <v>3.770587682724</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.69299983978271</v>
       </c>
       <c r="G848" t="n">
-        <v>3.74663710594177</v>
+        <v>3.74663686752319</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G849" t="n">
-        <v>3.71630072593689</v>
+        <v>3.71630048751831</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G850" t="n">
-        <v>3.73226714134216</v>
+        <v>3.73226690292358</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>3.78815054893494</v>
+        <v>3.78815102577209</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>3.76420116424561</v>
+        <v>3.76420092582703</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G854" t="n">
-        <v>3.68995475769043</v>
+        <v>3.68995499610901</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>3.7586133480072</v>
+        <v>3.75861263275146</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>3.90790319442749</v>
+        <v>3.90790295600891</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.81400012969971</v>
       </c>
       <c r="G859" t="n">
-        <v>3.84323716163635</v>
+        <v>3.84323740005493</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G860" t="n">
-        <v>3.81609392166138</v>
+        <v>3.81609320640564</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G861" t="n">
-        <v>3.81210160255432</v>
+        <v>3.8121018409729</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G863" t="n">
-        <v>3.86080121994019</v>
+        <v>3.86080074310303</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G864" t="n">
-        <v>3.89592814445496</v>
+        <v>3.89592862129211</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G865" t="n">
-        <v>3.84802770614624</v>
+        <v>3.84802722930908</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.75</v>
       </c>
       <c r="G866" t="n">
-        <v>3.79214286804199</v>
+        <v>3.79214310646057</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.9689998626709</v>
       </c>
       <c r="G867" t="n">
-        <v>3.96698045730591</v>
+        <v>3.96698093414307</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.94899988174438</v>
       </c>
       <c r="G869" t="n">
-        <v>3.95101356506348</v>
+        <v>3.95101428031921</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G870" t="n">
-        <v>3.91508841514587</v>
+        <v>3.91508817672729</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G872" t="n">
-        <v>3.96378707885742</v>
+        <v>3.96378803253174</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G873" t="n">
-        <v>3.91269302368164</v>
+        <v>3.9126935005188</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5</v>
       </c>
       <c r="G874" t="n">
-        <v>3.99172949790955</v>
+        <v>3.9917299747467</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>5.0939998626709</v>
       </c>
       <c r="G876" t="n">
-        <v>4.06677341461182</v>
+        <v>4.06677436828613</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.97700023651123</v>
       </c>
       <c r="G877" t="n">
-        <v>3.97336792945862</v>
+        <v>3.97336745262146</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.93599987030029</v>
       </c>
       <c r="G878" t="n">
-        <v>3.94063568115234</v>
+        <v>3.94063496589661</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G879" t="n">
-        <v>3.94622421264648</v>
+        <v>3.94622373580933</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>5.00799989700317</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99811625480652</v>
+        <v>3.9981164932251</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G881" t="n">
-        <v>3.9677791595459</v>
+        <v>3.96777868270874</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G882" t="n">
-        <v>4.00769662857056</v>
+        <v>4.0076961517334</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G885" t="n">
-        <v>3.9869396686554</v>
+        <v>3.98693943023682</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>5.05200004577637</v>
       </c>
       <c r="G887" t="n">
-        <v>4.03324365615845</v>
+        <v>4.03324317932129</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.94399976730347</v>
       </c>
       <c r="G890" t="n">
-        <v>3.94702243804932</v>
+        <v>3.94702172279358</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.9210000038147</v>
       </c>
       <c r="G892" t="n">
-        <v>3.92866015434265</v>
+        <v>3.92866063117981</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G894" t="n">
-        <v>3.99971318244934</v>
+        <v>3.99971342086792</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G896" t="n">
-        <v>3.84802770614624</v>
+        <v>3.84802722930908</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G897" t="n">
-        <v>3.91269302368164</v>
+        <v>3.9126935005188</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.96299982070923</v>
       </c>
       <c r="G898" t="n">
-        <v>3.96219062805176</v>
+        <v>3.96219038963318</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G901" t="n">
-        <v>3.94542551040649</v>
+        <v>3.94542598724365</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.79699993133545</v>
       </c>
       <c r="G902" t="n">
-        <v>3.829665184021</v>
+        <v>3.82966542243958</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G903" t="n">
-        <v>3.75701594352722</v>
+        <v>3.75701546669006</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.67700004577637</v>
       </c>
       <c r="G904" t="n">
-        <v>3.73386359214783</v>
+        <v>3.73386406898499</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.73299980163574</v>
       </c>
       <c r="G905" t="n">
-        <v>3.77857065200806</v>
+        <v>3.77857112884521</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G906" t="n">
-        <v>3.67638254165649</v>
+        <v>3.67638325691223</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G907" t="n">
-        <v>3.68436598777771</v>
+        <v>3.68436622619629</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G908" t="n">
-        <v>3.69155144691467</v>
+        <v>3.69155168533325</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.66099977493286</v>
       </c>
       <c r="G909" t="n">
-        <v>3.72109007835388</v>
+        <v>3.7210898399353</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G910" t="n">
-        <v>3.71630072593689</v>
+        <v>3.71630048751831</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>4.58099985122681</v>
       </c>
       <c r="G911" t="n">
-        <v>3.65722227096558</v>
+        <v>3.65722250938416</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G912" t="n">
-        <v>3.66839957237244</v>
+        <v>3.6683988571167</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>3.73945236206055</v>
+        <v>3.73945212364197</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G915" t="n">
-        <v>3.75222587585449</v>
+        <v>3.75222539901733</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>3.72029185295105</v>
+        <v>3.72029161453247</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.67700004577637</v>
       </c>
       <c r="G918" t="n">
-        <v>3.73386359214783</v>
+        <v>3.73386406898499</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G919" t="n">
-        <v>3.74823427200317</v>
+        <v>3.74823403358459</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G920" t="n">
-        <v>3.7649998664856</v>
+        <v>3.76499962806702</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.72900009155273</v>
       </c>
       <c r="G922" t="n">
-        <v>3.77537751197815</v>
+        <v>3.77537798881531</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.85200023651123</v>
       </c>
       <c r="G923" t="n">
-        <v>3.87357449531555</v>
+        <v>3.87357425689697</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G928" t="n">
-        <v>4.06517744064331</v>
+        <v>4.06517696380615</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.20599985122681</v>
       </c>
       <c r="G930" t="n">
-        <v>4.15618848800659</v>
+        <v>4.15618896484375</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>5.17799997329712</v>
       </c>
       <c r="G931" t="n">
-        <v>4.13383531570435</v>
+        <v>4.1338357925415</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>4.12744855880737</v>
+        <v>4.12744808197021</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>4.15345907211304</v>
+        <v>4.15345859527588</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G941" t="n">
-        <v>4.1339898109436</v>
+        <v>4.13398933410645</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G942" t="n">
-        <v>4.07558155059814</v>
+        <v>4.07558107376099</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>5.03399991989136</v>
       </c>
       <c r="G943" t="n">
-        <v>4.0836935043335</v>
+        <v>4.08369398117065</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.98299980163574</v>
       </c>
       <c r="G946" t="n">
-        <v>4.04232168197632</v>
+        <v>4.042320728302</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G947" t="n">
-        <v>3.97174525260925</v>
+        <v>3.97174477577209</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.9229998588562</v>
       </c>
       <c r="G948" t="n">
-        <v>3.99364805221558</v>
+        <v>3.99364829063416</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.86899995803833</v>
       </c>
       <c r="G953" t="n">
-        <v>3.94984197616577</v>
+        <v>3.94984269142151</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.97200012207031</v>
       </c>
       <c r="G954" t="n">
-        <v>4.03339862823486</v>
+        <v>4.03339767456055</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.93100023269653</v>
       </c>
       <c r="G955" t="n">
-        <v>4.00013828277588</v>
+        <v>4.00013780593872</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G956" t="n">
-        <v>4.00581645965576</v>
+        <v>4.00581693649292</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G958" t="n">
-        <v>3.9425413608551</v>
+        <v>3.94254159927368</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G959" t="n">
-        <v>3.9685001373291</v>
+        <v>3.96850037574768</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G960" t="n">
-        <v>3.85168433189392</v>
+        <v>3.85168409347534</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G961" t="n">
-        <v>3.914959192276</v>
+        <v>3.91495990753174</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.96099996566772</v>
       </c>
       <c r="G963" t="n">
-        <v>4.02447414398193</v>
+        <v>4.02447462081909</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G965" t="n">
-        <v>4.1339898109436</v>
+        <v>4.13398933410645</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G969" t="n">
-        <v>4.13561201095581</v>
+        <v>4.13561248779297</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G971" t="n">
-        <v>4.1064076423645</v>
+        <v>4.10640811920166</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G972" t="n">
-        <v>4.14534664154053</v>
+        <v>4.14534711837769</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G973" t="n">
-        <v>4.12263202667236</v>
+        <v>4.12263250350952</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G974" t="n">
-        <v>4.42116260528564</v>
+        <v>4.42116212844849</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>5.44399976730347</v>
       </c>
       <c r="G978" t="n">
-        <v>4.41629457473755</v>
+        <v>4.41629505157471</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>5.44600009918213</v>
       </c>
       <c r="G979" t="n">
-        <v>4.41791725158691</v>
+        <v>4.41791772842407</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G980" t="n">
-        <v>4.40007066726685</v>
+        <v>4.40007019042969</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>5.31400012969971</v>
       </c>
       <c r="G981" t="n">
-        <v>4.31083631515503</v>
+        <v>4.31083679199219</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G983" t="n">
-        <v>4.24756050109863</v>
+        <v>4.24756097793579</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G989" t="n">
-        <v>4.21348905563354</v>
+        <v>4.2134895324707</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G992" t="n">
-        <v>4.17292833328247</v>
+        <v>4.17292785644531</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G993" t="n">
-        <v>4.19888782501221</v>
+        <v>4.19888734817505</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>5.15399980545044</v>
       </c>
       <c r="G996" t="n">
-        <v>4.18104028701782</v>
+        <v>4.18104076385498</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>5.13600015640259</v>
       </c>
       <c r="G997" t="n">
-        <v>4.16643905639648</v>
+        <v>4.16643857955933</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G998" t="n">
-        <v>4.19888782501221</v>
+        <v>4.19888734817505</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G999" t="n">
-        <v>4.15345907211304</v>
+        <v>4.15345859527588</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>5.2519998550415</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.26054048538208</v>
+        <v>4.26054000854492</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>5.14599990844727</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.17455053329468</v>
+        <v>4.17455101013184</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.19888782501221</v>
+        <v>4.19888734817505</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.12263202667236</v>
+        <v>4.12263250350952</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.19564199447632</v>
+        <v>4.19564247131348</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.26703071594238</v>
+        <v>4.26703023910522</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.23782634735107</v>
+        <v>4.23782587051392</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.13074493408203</v>
+        <v>4.13074445724487</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.12100982666016</v>
+        <v>4.12101030349731</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>4.12100982666016</v>
+        <v>4.12101030349731</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.05205631256104</v>
+        <v>4.05205583572388</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.97661209106445</v>
+        <v>3.97661256790161</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.98699998855591</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.04556655883789</v>
+        <v>4.04556608200073</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.05124521255493</v>
+        <v>4.05124473571777</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.07233667373657</v>
+        <v>4.07233619689941</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.10478591918945</v>
+        <v>4.10478544235229</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>5.06799983978271</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.1112756729126</v>
+        <v>4.11127471923828</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.10478591918945</v>
+        <v>4.10478544235229</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.21348905563354</v>
+        <v>4.2134895324707</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.31894874572754</v>
+        <v>4.31894826889038</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.3205714225769</v>
+        <v>4.32057094573975</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.4665904045105</v>
+        <v>4.46659088134766</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.49579429626465</v>
+        <v>4.49579524993896</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.67264175415039</v>
+        <v>4.67264127731323</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.69860076904297</v>
+        <v>4.69860029220581</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.6969780921936</v>
+        <v>4.69697761535645</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.6596622467041</v>
+        <v>4.65966129302979</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G1054" t="n">
-        <v>4.4308967590332</v>
+        <v>4.43089723587036</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>5.40399980545044</v>
       </c>
       <c r="G1055" t="n">
-        <v>4.38384628295898</v>
+        <v>4.38384580612183</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1057" t="n">
-        <v>4.52824401855469</v>
+        <v>4.52824354171753</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>5.5460000038147</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.49903964996338</v>
+        <v>4.49904012680054</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1060" t="n">
-        <v>4.66128396987915</v>
+        <v>4.66128349304199</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>5.96400022506714</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.83813095092773</v>
+        <v>4.83813047409058</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.84299755096436</v>
+        <v>4.84299802780151</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>5.97399997711182</v>
       </c>
       <c r="G1065" t="n">
-        <v>4.84624242782593</v>
+        <v>4.84624290466309</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.84299755096436</v>
+        <v>4.84299802780151</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1068" t="n">
-        <v>4.85922241210938</v>
+        <v>4.85922193527222</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.85111045837402</v>
+        <v>4.85110998153687</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>5.95599985122681</v>
       </c>
       <c r="G1071" t="n">
-        <v>4.83164072036743</v>
+        <v>4.83164119720459</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G1072" t="n">
-        <v>4.87869167327881</v>
+        <v>4.87869215011597</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>6.10400009155273</v>
       </c>
       <c r="G1074" t="n">
-        <v>4.95170211791992</v>
+        <v>4.95170164108276</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>6.11600017547607</v>
       </c>
       <c r="G1076" t="n">
-        <v>4.96143627166748</v>
+        <v>4.9614372253418</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>6.10799980163574</v>
       </c>
       <c r="G1077" t="n">
-        <v>4.95494651794434</v>
+        <v>4.95494699478149</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>6.17600011825562</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.01010942459106</v>
+        <v>5.01010990142822</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>6.5</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.27294588088989</v>
+        <v>5.27294635772705</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>6.43800020217896</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.2226505279541</v>
+        <v>5.22265005111694</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>6.42600011825562</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.21291589736938</v>
+        <v>5.21291542053223</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.2891697883606</v>
+        <v>5.28917074203491</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6.58400011062622</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.34108829498291</v>
+        <v>5.34108877182007</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>6.59200000762939</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.34757804870605</v>
+        <v>5.34757900238037</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>6.67600011825562</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.41572093963623</v>
+        <v>5.41572141647339</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>6.62799978256226</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.37678194046021</v>
+        <v>5.37678241729736</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>6.56799983978271</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.32810878753662</v>
+        <v>5.32810926437378</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.26970052719116</v>
+        <v>5.26970100402832</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>6.08799982070923</v>
       </c>
       <c r="G1093" t="n">
-        <v>4.93872213363647</v>
+        <v>4.93872261047363</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.02957916259766</v>
+        <v>5.0295786857605</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.00037527084351</v>
+        <v>5.00037574768066</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.05553817749023</v>
+        <v>5.05553865432739</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>6.32200002670288</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.12854862213135</v>
+        <v>5.12854814529419</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>6.29199981689453</v>
       </c>
       <c r="G1100" t="n">
-        <v>5.10421133041382</v>
+        <v>5.10421180725098</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>6.24599981307983</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.06689500808716</v>
+        <v>5.06689548492432</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>6.13199996948242</v>
       </c>
       <c r="G1104" t="n">
-        <v>4.97441625595093</v>
+        <v>4.97441577911377</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>6.11800003051758</v>
       </c>
       <c r="G1105" t="n">
-        <v>4.96305894851685</v>
+        <v>4.96305847167969</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G1110" t="n">
-        <v>4.76025342941284</v>
+        <v>4.76025390625</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.76349830627441</v>
+        <v>4.76349878311157</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>5.61199998855591</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.55258083343506</v>
+        <v>4.5525803565979</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G1118" t="n">
-        <v>4.0098729133606</v>
+        <v>4.00987243652344</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.82248067855835</v>
+        <v>3.82248020172119</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>4.65700006484985</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.77786326408386</v>
+        <v>3.77786302566528</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.50772547721863</v>
+        <v>3.50772571563721</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.43796038627625</v>
+        <v>3.43796062469482</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.6870059967041</v>
+        <v>3.68700647354126</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.67402648925781</v>
+        <v>3.67402601242065</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>4.6710000038147</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.78922009468079</v>
+        <v>3.78921961784363</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.97661209106445</v>
+        <v>3.97661256790161</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>4.84700012207031</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.93199586868286</v>
+        <v>3.9319953918457</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>4.84899997711182</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.93361783027649</v>
+        <v>3.93361759185791</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.86953163146973</v>
+        <v>3.86953115463257</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.93767356872559</v>
+        <v>3.93767428398132</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.9311842918396</v>
+        <v>3.93118405342102</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.8938684463501</v>
+        <v>3.89386796951294</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>5.01800012588501</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.07071399688721</v>
+        <v>4.07071447372437</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G1140" t="n">
-        <v>4.0544900894165</v>
+        <v>4.05448961257935</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>4.93100023269653</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.00013828277588</v>
+        <v>4.00013780593872</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>4.9060001373291</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.97985768318176</v>
+        <v>3.97985816001892</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>4.8769998550415</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.95633125305176</v>
+        <v>3.95633172988892</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.8954906463623</v>
+        <v>3.89549040794373</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.68457221984863</v>
+        <v>3.68457269668579</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>4.41300010681152</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.57992458343506</v>
+        <v>3.57992482185364</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.61318492889404</v>
+        <v>3.61318516731262</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.59209275245667</v>
+        <v>3.59209322929382</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>4.52099990844727</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.66753697395325</v>
+        <v>3.66753649711609</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.73567914962769</v>
+        <v>3.73567962646484</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.84924983978271</v>
+        <v>3.84925055503845</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>4.5770001411438</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.71296525001526</v>
+        <v>3.71296501159668</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>4.66599988937378</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.78516364097595</v>
+        <v>3.78516435623169</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.85006141662598</v>
+        <v>3.85006189346313</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.85168433189392</v>
+        <v>3.85168409347534</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>4.61700010299683</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.7454137802124</v>
+        <v>3.74541401863098</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.71377658843994</v>
+        <v>3.71377682685852</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.71215438842773</v>
+        <v>3.71215415000916</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.60831737518311</v>
+        <v>3.60831761360168</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.45100021362305</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.61075139045715</v>
+        <v>3.61075091362</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>4.30100011825562</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.48906779289246</v>
+        <v>3.48906803131104</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>4.4689998626709</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.62535285949707</v>
+        <v>3.62535309791565</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>4.56799983978271</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.70566439628601</v>
+        <v>3.70566415786743</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>4.63899993896484</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.76326107978821</v>
+        <v>3.76326036453247</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.75</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.85330653190613</v>
+        <v>3.85330700874329</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.71134281158447</v>
+        <v>3.71134233474731</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.68781709671021</v>
+        <v>3.68781757354736</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>4.42899990081787</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.72579169273376</v>
+        <v>3.72579121589661</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.85449886322021</v>
+        <v>3.85449910163879</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.86543464660645</v>
+        <v>3.86543440818787</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>4.66699981689453</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.92600297927856</v>
+        <v>3.92600274085999</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.87132334709167</v>
+        <v>3.87132382392883</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>4.65100002288818</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.91254353523254</v>
+        <v>3.91254377365112</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.84861040115356</v>
+        <v>3.84860992431641</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.92852711677551</v>
+        <v>3.92852735519409</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.58900022506714</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.86038780212402</v>
+        <v>3.8603880405426</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.80402517318726</v>
+        <v>3.80402541160583</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>4.32299995422363</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.63662123680115</v>
+        <v>3.63662147521973</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.42379117012024</v>
+        <v>3.4237916469574</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.37752366065979</v>
+        <v>3.37752342224121</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.21299982070923</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.54408645629883</v>
+        <v>3.54408621788025</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.56679940223694</v>
+        <v>3.56679916381836</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.53483319282532</v>
+        <v>3.53483271598816</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.41117238998413</v>
+        <v>3.41117262840271</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.4019193649292</v>
+        <v>3.40191960334778</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>4.08300018310547</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.43472719192505</v>
+        <v>3.43472743034363</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.26059293746948</v>
+        <v>3.26059341430664</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.93700003623962</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.31190824508667</v>
+        <v>3.31190800666809</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>3.90300011634827</v>
       </c>
       <c r="G1206" t="n">
-        <v>3.28330636024475</v>
+        <v>3.28330659866333</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.17478799819946</v>
+        <v>3.17478823661804</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>4.07100009918213</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.42463231086731</v>
+        <v>3.42463254928589</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>4.08699989318848</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.43809199333191</v>
+        <v>3.43809175491333</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.875</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.25975179672241</v>
+        <v>3.25975203514099</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>4.16900014877319</v>
       </c>
       <c r="G1218" t="n">
-        <v>3.50707292556763</v>
+        <v>3.50707268714905</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>4.12099981307983</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.46669340133667</v>
+        <v>3.46669363975525</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.11700010299683</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.46332907676697</v>
+        <v>3.46332883834839</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.35649275779724</v>
+        <v>3.3564932346344</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>4.20800018310547</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.53988027572632</v>
+        <v>3.53988075256348</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G1227" t="n">
-        <v>3.44566345214844</v>
+        <v>3.44566321372986</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>4.43900012969971</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.73420357704163</v>
+        <v>3.73420381546021</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>4.40700006484985</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.70728445053101</v>
+        <v>3.70728397369385</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>4.29099988937378</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.60970187187195</v>
+        <v>3.60970211029053</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.62400269508362</v>
+        <v>3.62400317192078</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.46164631843567</v>
+        <v>3.46164608001709</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.27068781852722</v>
+        <v>3.2706880569458</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1241" t="n">
-        <v>3.28078269958496</v>
+        <v>3.28078293800354</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>3.87899994850159</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.26311683654785</v>
+        <v>3.26311707496643</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.26059293746948</v>
+        <v>3.26059341430664</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>3.70900011062622</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.12010836601257</v>
+        <v>3.12010860443115</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.17983531951904</v>
+        <v>3.17983555793762</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.23872137069702</v>
+        <v>3.2387216091156</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.07468223571777</v>
+        <v>3.07468199729919</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.16721725463867</v>
+        <v>3.16721701622009</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.7590000629425</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.16216969490051</v>
+        <v>3.16216993331909</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.297607421875</v>
+        <v>3.29760718345642</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.20507216453552</v>
+        <v>3.2050724029541</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.13609170913696</v>
+        <v>3.13609147071838</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.15964603424072</v>
+        <v>3.1596462726593</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G1263" t="n">
-        <v>3.0469217300415</v>
+        <v>3.04692196846008</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.90223097801208</v>
+        <v>2.90223073959351</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.75081014633179</v>
+        <v>2.75080990791321</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.86858201026917</v>
+        <v>2.86858177185059</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.84839248657227</v>
+        <v>2.84839224815369</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>3.40400004386902</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.86353445053101</v>
+        <v>2.86353468894958</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>3.41899991035461</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.87615275382996</v>
+        <v>2.87615251541138</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1283" t="n">
-        <v>3.01579618453979</v>
+        <v>3.01579642295837</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.95775175094604</v>
+        <v>2.95775198936462</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.11085486412048</v>
+        <v>3.11085510253906</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1286" t="n">
-        <v>3.17983531951904</v>
+        <v>3.17983555793762</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.17478799819946</v>
+        <v>3.17478823661804</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.13272666931152</v>
+        <v>3.1327269077301</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1292" t="n">
-        <v>3.16301083564758</v>
+        <v>3.16301107406616</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1296" t="n">
-        <v>3.38593626022339</v>
+        <v>3.38593602180481</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.52053189277649</v>
+        <v>3.52053213119507</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.5112783908844</v>
+        <v>3.51127862930298</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.4658522605896</v>
+        <v>3.46585249900818</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.5011842250824</v>
+        <v>3.50118374824524</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>4.12099981307983</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.46669340133667</v>
+        <v>3.46669363975525</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.519690990448</v>
+        <v>3.51969075202942</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>4.22300004959106</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.55249881744385</v>
+        <v>3.55249905586243</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.55838704109192</v>
+        <v>3.55838751792908</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.5264208316803</v>
+        <v>3.52642059326172</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.56679940223694</v>
+        <v>3.56679916381836</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>4.32600021362305</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.63914513587952</v>
+        <v>3.6391453742981</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.56343460083008</v>
+        <v>3.56343483924866</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.14300012588501</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.48520064353943</v>
+        <v>3.48520088195801</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.4389328956604</v>
+        <v>3.43893313407898</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>4.16900014877319</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.50707292556763</v>
+        <v>3.50707268714905</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>4.02899980545044</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.38930082321167</v>
+        <v>3.38930058479309</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.35985803604126</v>
+        <v>3.35985827445984</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.38593626022339</v>
+        <v>3.38593602180481</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>4.00699996948242</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.37079381942749</v>
+        <v>3.37079405784607</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>4.09299993515015</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.44313955307007</v>
+        <v>3.44313931465149</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>4.4229998588562</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.72074413299561</v>
+        <v>3.72074365615845</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G1338" t="n">
-        <v>3.82926225662231</v>
+        <v>3.82926201820374</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.82926225662231</v>
+        <v>3.82926201820374</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1340" t="n">
-        <v>3.81916761398315</v>
+        <v>3.819167137146</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.84019804000854</v>
+        <v>3.84019827842712</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.87721180915833</v>
+        <v>3.87721252441406</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.90329003334045</v>
+        <v>3.90329027175903</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.94366908073425</v>
+        <v>3.94366931915283</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>4.59100008010864</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.86207032203674</v>
+        <v>3.86206984519958</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>4.53700017929077</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.81664419174194</v>
+        <v>3.81664395332336</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>4.60300016403198</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.8721649646759</v>
+        <v>3.87216472625732</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>4.56899976730347</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.84356307983398</v>
+        <v>3.84356284141541</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>4.58599996566772</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.85786366462708</v>
+        <v>3.85786390304565</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.06059980392456</v>
+        <v>4.0605993270874</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>4.75899982452393</v>
       </c>
       <c r="G1359" t="n">
-        <v>4.00339603424072</v>
+        <v>4.00339555740356</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>4.65399980545044</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.91506719589233</v>
+        <v>3.91506743431091</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.95208096504211</v>
+        <v>3.95208168029785</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.83767437934875</v>
+        <v>3.83767414093018</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.90917825698853</v>
+        <v>3.9091784954071</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.95376372337341</v>
+        <v>3.95376348495483</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G1368" t="n">
-        <v>4.08331251144409</v>
+        <v>4.08331298828125</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.11359596252441</v>
+        <v>4.11359643936157</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.05639314651489</v>
+        <v>4.05639362335205</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>4.89099979400635</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.1144380569458</v>
+        <v>4.11443758010864</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G1377" t="n">
-        <v>4.12285041809082</v>
+        <v>4.12284994125366</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>4.94700002670288</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.16154718399048</v>
+        <v>4.16154670715332</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G1382" t="n">
-        <v>4.07574129104614</v>
+        <v>4.0757417678833</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.74900007247925</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.99498414993286</v>
+        <v>3.99498438835144</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>4.50299978256226</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.78804206848145</v>
+        <v>3.78804159164429</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.86627650260925</v>
+        <v>3.86627674102783</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.74682211875916</v>
+        <v>3.74682235717773</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.79561352729797</v>
+        <v>3.79561305046082</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>4.45699977874756</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.74934577941895</v>
+        <v>3.74934554100037</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.76448774337769</v>
+        <v>3.76448750495911</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.88814806938171</v>
+        <v>3.88814854621887</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>4.62599992752075</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.89151263237</v>
+        <v>3.89151310920715</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>4.48299980163574</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.77121758460999</v>
+        <v>3.77121734619141</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.61700010299683</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.88394212722778</v>
+        <v>3.8839418888092</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.88141798973083</v>
+        <v>3.88141822814941</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.95208096504211</v>
+        <v>3.95208168029785</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.95796942710876</v>
+        <v>3.9579701423645</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.97563505172729</v>
+        <v>3.97563552856445</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1409" t="n">
-        <v>4.02442693710327</v>
+        <v>4.02442646026611</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.91843199729919</v>
+        <v>3.91843247413635</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>4.63899993896484</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.90244889259338</v>
+        <v>3.90244841575623</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.84861040115356</v>
+        <v>3.84860992431641</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.88814806938171</v>
+        <v>3.88814854621887</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>4.63700008392334</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.90076637268066</v>
+        <v>3.90076661109924</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.99246001243591</v>
+        <v>3.99246025085449</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.91843199729919</v>
+        <v>3.91843247413635</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.99414277076721</v>
+        <v>3.99414253234863</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>4.72100019454956</v>
       </c>
       <c r="G1419" t="n">
-        <v>3.9714298248291</v>
+        <v>3.97142958641052</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.12285041809082</v>
+        <v>4.12284994125366</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>4.88199996948242</v>
       </c>
       <c r="G1422" t="n">
-        <v>4.10686683654785</v>
+        <v>4.10686731338501</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.90299987792969</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.12453269958496</v>
+        <v>4.1245322227478</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G1424" t="n">
-        <v>4.0235857963562</v>
+        <v>4.02358531951904</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>4.83099985122681</v>
       </c>
       <c r="G1427" t="n">
-        <v>4.06396436691284</v>
+        <v>4.06396389007568</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G1428" t="n">
-        <v>4.06059980392456</v>
+        <v>4.0605993270874</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G1429" t="n">
-        <v>4.08331251144409</v>
+        <v>4.08331298828125</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>4.88399982452393</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.10854911804199</v>
+        <v>4.10854959487915</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>4.89400005340576</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.11696147918701</v>
+        <v>4.11696195602417</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>4.58699989318848</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.85870552062988</v>
+        <v>3.85870480537415</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>4.51900005340576</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.80150151252747</v>
+        <v>3.80150175094604</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.87468862533569</v>
+        <v>3.87468838691711</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.83262729644775</v>
+        <v>3.83262753486633</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.70812606811523</v>
+        <v>3.70812559127808</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.87468862533569</v>
+        <v>3.87468838691711</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.82337379455566</v>
+        <v>3.82337403297424</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>4.49900007247925</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.78467750549316</v>
+        <v>3.78467702865601</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>4.64300012588501</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.90581369400024</v>
+        <v>3.90581345558167</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>4.68100023269653</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.93778014183044</v>
+        <v>3.93778085708618</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.90917825698853</v>
+        <v>3.9091784954071</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>4.61899995803833</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.88562440872192</v>
+        <v>3.88562417030334</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.77710580825806</v>
+        <v>3.77710604667664</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.43300008773804</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.72915649414062</v>
+        <v>3.72915601730347</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.70307803153992</v>
+        <v>3.70307850837708</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.73504495620728</v>
+        <v>3.7350447177887</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.78131246566772</v>
+        <v>3.78131222724915</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.78383612632751</v>
+        <v>3.78383636474609</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>4.57100009918213</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.84524583816528</v>
+        <v>3.8452455997467</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.72999739646912</v>
+        <v>3.7299976348877</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>4.47599983215332</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.76532912254333</v>
+        <v>3.76532888412476</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.81411981582642</v>
+        <v>3.814120054245</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>4.63700008392334</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.90076637268066</v>
+        <v>3.90076661109924</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.95544624328613</v>
+        <v>3.95544648170471</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.90917825698853</v>
+        <v>3.9091784954071</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.96890568733215</v>
+        <v>3.96890592575073</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>4.91699981689453</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.33140182495117</v>
+        <v>4.33140230178833</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G1486" t="n">
-        <v>4.11558103561401</v>
+        <v>4.11558055877686</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>4.56899976730347</v>
       </c>
       <c r="G1492" t="n">
-        <v>4.02484750747681</v>
+        <v>4.02484703063965</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1494" t="n">
-        <v>4.00458669662476</v>
+        <v>4.00458717346191</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>4.51700019836426</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.97904062271118</v>
+        <v>3.97904086112976</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>4.50699996948242</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.97023153305054</v>
+        <v>3.97023129463196</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.94997096061707</v>
+        <v>3.94997119903564</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>4.49300003051758</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.95789909362793</v>
+        <v>3.95789885520935</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.99401569366455</v>
+        <v>3.99401545524597</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>4.73299980163574</v>
       </c>
       <c r="G1506" t="n">
-        <v>4.16931581497192</v>
+        <v>4.16931533813477</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>4.7039999961853</v>
       </c>
       <c r="G1509" t="n">
-        <v>4.14376926422119</v>
+        <v>4.14376974105835</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1513" t="n">
-        <v>4.18252897262573</v>
+        <v>4.18252944946289</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>4.68900012969971</v>
       </c>
       <c r="G1515" t="n">
-        <v>4.13055658340454</v>
+        <v>4.13055610656738</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>4.71299982070923</v>
       </c>
       <c r="G1520" t="n">
-        <v>4.15169715881348</v>
+        <v>4.15169763565063</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.94468545913696</v>
+        <v>3.94468593597412</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>4.44399976730347</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.91473436355591</v>
+        <v>3.91473460197449</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>4.44299983978271</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.91385340690613</v>
+        <v>3.91385364532471</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>4.47100019454956</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.93851947784424</v>
+        <v>3.93851923942566</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.96230363845825</v>
+        <v>3.96230340003967</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.95349454879761</v>
+        <v>3.95349431037903</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.92530536651611</v>
+        <v>3.92530512809753</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.62051320075989</v>
+        <v>3.62051296234131</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>4.39300012588501</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.8698091506958</v>
+        <v>3.86980891227722</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>4.44700002670288</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.91737723350525</v>
+        <v>3.91737747192383</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>4.44099998474121</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.91209173202515</v>
+        <v>3.9120922088623</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.98961114883423</v>
+        <v>3.98961138725281</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.98961114883423</v>
+        <v>3.98961138725281</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1559" t="n">
-        <v>4.00458669662476</v>
+        <v>4.00458717346191</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>4.46099996566772</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.92970991134644</v>
+        <v>3.92971014976501</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.94997096061707</v>
+        <v>3.94997119903564</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.95173263549805</v>
+        <v>3.95173287391663</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>4.54899978637695</v>
       </c>
       <c r="G1565" t="n">
-        <v>4.00722932815552</v>
+        <v>4.00722885131836</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G1566" t="n">
-        <v>4.0133957862854</v>
+        <v>4.01339626312256</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G1571" t="n">
-        <v>4.18957614898682</v>
+        <v>4.18957662582397</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G1572" t="n">
-        <v>4.18957614898682</v>
+        <v>4.18957662582397</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.2063136100769</v>
+        <v>4.20631313323975</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>4.80700016021729</v>
       </c>
       <c r="G1576" t="n">
-        <v>4.23450231552124</v>
+        <v>4.2345027923584</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>4.86100006103516</v>
       </c>
       <c r="G1578" t="n">
-        <v>4.28207111358643</v>
+        <v>4.28207159042358</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G1579" t="n">
-        <v>4.25123929977417</v>
+        <v>4.25123977661133</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>4.78700017929077</v>
       </c>
       <c r="G1580" t="n">
-        <v>4.21688461303711</v>
+        <v>4.21688508987427</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>4.84899997711182</v>
       </c>
       <c r="G1582" t="n">
-        <v>4.27150058746338</v>
+        <v>4.27150106430054</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G1591" t="n">
-        <v>4.26181077957153</v>
+        <v>4.26181030273438</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.39042282104492</v>
+        <v>4.39042234420776</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1594" t="n">
-        <v>4.56307888031006</v>
+        <v>4.56307935714722</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G1596" t="n">
-        <v>4.67231178283691</v>
+        <v>4.67231130599976</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G1599" t="n">
-        <v>4.48555994033813</v>
+        <v>4.48556041717529</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1600" t="n">
-        <v>4.47498893737793</v>
+        <v>4.47498941421509</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G1601" t="n">
-        <v>4.50317764282227</v>
+        <v>4.50317811965942</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1602" t="n">
-        <v>4.47498893737793</v>
+        <v>4.47498941421509</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G1605" t="n">
-        <v>4.50317764282227</v>
+        <v>4.50317811965942</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>5.2039999961853</v>
       </c>
       <c r="G1606" t="n">
-        <v>4.58422136306763</v>
+        <v>4.58422088623047</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1607" t="n">
-        <v>4.55427026748657</v>
+        <v>4.55427074432373</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>5.01399993896484</v>
       </c>
       <c r="G1610" t="n">
-        <v>4.41684913635254</v>
+        <v>4.4168496131897</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1616" t="n">
-        <v>4.70402431488037</v>
+        <v>4.70402383804321</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>5.41800022125244</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.77273511886597</v>
+        <v>4.77273464202881</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G1632" t="n">
-        <v>4.99472236633301</v>
+        <v>4.99472188949585</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1633" t="n">
-        <v>5.05638551712036</v>
+        <v>5.0563850402832</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1634" t="n">
-        <v>4.88020467758179</v>
+        <v>4.88020420074463</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>5.41400003433228</v>
       </c>
       <c r="G1635" t="n">
-        <v>4.76921081542969</v>
+        <v>4.76921033859253</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G1636" t="n">
-        <v>4.72868919372559</v>
+        <v>4.72868967056274</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G1638" t="n">
-        <v>4.71459531784058</v>
+        <v>4.71459484100342</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>5.33799982070923</v>
       </c>
       <c r="G1639" t="n">
-        <v>4.70226240158081</v>
+        <v>4.70226192474365</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1642" t="n">
-        <v>4.8713960647583</v>
+        <v>4.87139558792114</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1643" t="n">
-        <v>4.91720294952393</v>
+        <v>4.91720247268677</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G1644" t="n">
-        <v>4.89606094360352</v>
+        <v>4.89606142044067</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1648" t="n">
-        <v>4.9735803604126</v>
+        <v>4.97358083724976</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G1649" t="n">
-        <v>4.99472236633301</v>
+        <v>4.99472188949585</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1651" t="n">
-        <v>4.9735803604126</v>
+        <v>4.97358083724976</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1652" t="n">
-        <v>5.07576513290405</v>
+        <v>5.07576560974121</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1660" t="n">
-        <v>5.15328502655029</v>
+        <v>5.15328454971313</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>5.80200004577637</v>
       </c>
       <c r="G1661" t="n">
-        <v>5.11100149154663</v>
+        <v>5.11100101470947</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1663" t="n">
-        <v>5.17090320587158</v>
+        <v>5.17090272903442</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1664" t="n">
-        <v>5.1233344078064</v>
+        <v>5.12333393096924</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G1666" t="n">
-        <v>5.27484893798828</v>
+        <v>5.27484941482544</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>5.97800016403198</v>
       </c>
       <c r="G1667" t="n">
-        <v>5.26604032516479</v>
+        <v>5.26604080200195</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>5.96799993515015</v>
       </c>
       <c r="G1671" t="n">
-        <v>5.25723123550415</v>
+        <v>5.25723171234131</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G1672" t="n">
-        <v>5.36646318435669</v>
+        <v>5.36646366119385</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>6.17799997329712</v>
       </c>
       <c r="G1675" t="n">
-        <v>5.44222068786621</v>
+        <v>5.44222116470337</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G1676" t="n">
-        <v>5.29951477050781</v>
+        <v>5.29951429367065</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>6.23400020599365</v>
       </c>
       <c r="G1678" t="n">
-        <v>5.49155187606812</v>
+        <v>5.49155235290527</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>6.08599996566772</v>
       </c>
       <c r="G1687" t="n">
-        <v>5.36117792129517</v>
+        <v>5.36117744445801</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G1689" t="n">
-        <v>5.41403245925903</v>
+        <v>5.41403198242188</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G1691" t="n">
-        <v>5.45279216766357</v>
+        <v>5.45279169082642</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1692" t="n">
-        <v>5.20613861083984</v>
+        <v>5.206139087677</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G1701" t="n">
-        <v>5.29951477050781</v>
+        <v>5.29951429367065</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>5.96799993515015</v>
       </c>
       <c r="G1702" t="n">
-        <v>5.25723123550415</v>
+        <v>5.25723171234131</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>5.86600017547607</v>
       </c>
       <c r="G1703" t="n">
-        <v>5.1673789024353</v>
+        <v>5.16737937927246</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1706" t="n">
-        <v>5.13566637039185</v>
+        <v>5.135666847229</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1713" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1714" t="n">
-        <v>5.12169647216797</v>
+        <v>5.12169694900513</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1715" t="n">
-        <v>5.02137899398804</v>
+        <v>5.02137851715088</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G1718" t="n">
-        <v>5.16547155380249</v>
+        <v>5.16547203063965</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>5.57399988174438</v>
       </c>
       <c r="G1720" t="n">
-        <v>5.08339309692383</v>
+        <v>5.08339357376099</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1721" t="n">
-        <v>5.14905595779419</v>
+        <v>5.14905643463135</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1723" t="n">
-        <v>5.22931051254272</v>
+        <v>5.22931098937988</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1725" t="n">
-        <v>5.25484609603882</v>
+        <v>5.25484657287598</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>5.75</v>
       </c>
       <c r="G1732" t="n">
-        <v>5.2439022064209</v>
+        <v>5.24390268325806</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1733" t="n">
-        <v>5.30774116516113</v>
+        <v>5.30774164199829</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1734" t="n">
-        <v>5.26578998565674</v>
+        <v>5.2657904624939</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1737" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1738" t="n">
-        <v>4.97760343551636</v>
+        <v>4.97760391235352</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G1740" t="n">
-        <v>4.74960803985596</v>
+        <v>4.7496075630188</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G1744" t="n">
-        <v>4.78426313400269</v>
+        <v>4.78426265716553</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>5.38199996948242</v>
       </c>
       <c r="G1748" t="n">
-        <v>4.90829277038574</v>
+        <v>4.90829229354858</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1750" t="n">
-        <v>4.94294834136963</v>
+        <v>4.94294786453247</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>5.43200016021729</v>
       </c>
       <c r="G1753" t="n">
-        <v>4.95389175415039</v>
+        <v>4.95389223098755</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>5.52799987792969</v>
       </c>
       <c r="G1758" t="n">
-        <v>5.04144191741943</v>
+        <v>5.04144239425659</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1760" t="n">
-        <v>4.99584341049194</v>
+        <v>4.99584293365479</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1767" t="n">
-        <v>4.96118783950806</v>
+        <v>4.9611873626709</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G1769" t="n">
-        <v>4.92106056213379</v>
+        <v>4.92106008529663</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1777" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>5.21199989318848</v>
       </c>
       <c r="G1780" t="n">
-        <v>4.75325536727905</v>
+        <v>4.75325584411621</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G1785" t="n">
-        <v>4.8955249786377</v>
+        <v>4.89552450180054</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G1791" t="n">
-        <v>4.87546110153198</v>
+        <v>4.87546157836914</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>5.24399995803833</v>
       </c>
       <c r="G1795" t="n">
-        <v>4.7824387550354</v>
+        <v>4.78243923187256</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1797" t="n">
-        <v>4.71677589416504</v>
+        <v>4.7167763710022</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>5.15799999237061</v>
       </c>
       <c r="G1798" t="n">
-        <v>4.70400810241699</v>
+        <v>4.70400857925415</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1799" t="n">
-        <v>4.62010622024536</v>
+        <v>4.6201057434082</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1802" t="n">
-        <v>4.62010622024536</v>
+        <v>4.6201057434082</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>5.10400009155273</v>
       </c>
       <c r="G1807" t="n">
-        <v>4.65476179122925</v>
+        <v>4.65476131439209</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1808" t="n">
-        <v>4.71677589416504</v>
+        <v>4.7167763710022</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>4.96700000762939</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.52981996536255</v>
+        <v>4.52981948852539</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G1811" t="n">
-        <v>4.63469743728638</v>
+        <v>4.63469791412354</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>5.16599988937378</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.71130466461182</v>
+        <v>4.71130418777466</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.71677589416504</v>
+        <v>4.7167763710022</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G1822" t="n">
-        <v>4.68212032318115</v>
+        <v>4.68212080001831</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G1825" t="n">
-        <v>4.78426313400269</v>
+        <v>4.78426265716553</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.87546110153198</v>
+        <v>4.87546157836914</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G1828" t="n">
-        <v>4.92106056213379</v>
+        <v>4.92106008529663</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1834" t="n">
-        <v>5.02137899398804</v>
+        <v>5.02137851715088</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1835" t="n">
-        <v>5.04326677322388</v>
+        <v>5.04326629638672</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.97760343551636</v>
+        <v>4.97760391235352</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.99219465255737</v>
+        <v>4.99219512939453</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1846" t="n">
-        <v>5.09068918228149</v>
+        <v>5.09068870544434</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1847" t="n">
-        <v>5.09616088867188</v>
+        <v>5.09616136550903</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1848" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1849" t="n">
-        <v>5.18006372451782</v>
+        <v>5.18006324768066</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1851" t="n">
-        <v>5.22931051254272</v>
+        <v>5.22931098937988</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1854" t="n">
-        <v>5.23843050003052</v>
+        <v>5.23843002319336</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>5.82800006866455</v>
       </c>
       <c r="G1856" t="n">
-        <v>5.3150372505188</v>
+        <v>5.31503677368164</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>5.85200023651123</v>
       </c>
       <c r="G1857" t="n">
-        <v>5.33692455291748</v>
+        <v>5.33692502975464</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>5.78200006484985</v>
       </c>
       <c r="G1860" t="n">
-        <v>5.27308559417725</v>
+        <v>5.2730860710144</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1863" t="n">
-        <v>5.13264036178589</v>
+        <v>5.13263988494873</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1864" t="n">
-        <v>5.10710477828979</v>
+        <v>5.10710525512695</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>5.53800010681152</v>
       </c>
       <c r="G1865" t="n">
-        <v>5.05056238174438</v>
+        <v>5.05056190490723</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1866" t="n">
-        <v>5.10710477828979</v>
+        <v>5.10710525512695</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1868" t="n">
-        <v>5.10710477828979</v>
+        <v>5.10710525512695</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1869" t="n">
-        <v>5.14358377456665</v>
+        <v>5.14358425140381</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G1871" t="n">
-        <v>5.24572658538818</v>
+        <v>5.24572610855103</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>5.72800016403198</v>
       </c>
       <c r="G1876" t="n">
-        <v>5.2238392829895</v>
+        <v>5.22383880615234</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1880" t="n">
-        <v>5.30774116516113</v>
+        <v>5.30774164199829</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G1882" t="n">
-        <v>5.50290536880493</v>
+        <v>5.50290584564209</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>5.75</v>
       </c>
       <c r="G1884" t="n">
-        <v>5.2439022064209</v>
+        <v>5.24390268325806</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1886" t="n">
-        <v>5.30774116516113</v>
+        <v>5.30774164199829</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49431,7 +49431,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1887" t="n">
-        <v>5.14905595779419</v>
+        <v>5.14905643463135</v>
       </c>
       <c r="H1887" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>5.66599988937378</v>
       </c>
       <c r="G1888" t="n">
-        <v>5.16729593276978</v>
+        <v>5.16729545593262</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1889" t="n">
-        <v>5.12169647216797</v>
+        <v>5.12169694900513</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1891" t="n">
-        <v>5.25484609603882</v>
+        <v>5.25484657287598</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G1892" t="n">
-        <v>5.40258693695068</v>
+        <v>5.40258741378784</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1894" t="n">
-        <v>5.40441179275513</v>
+        <v>5.40441131591797</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1895" t="n">
-        <v>5.40441179275513</v>
+        <v>5.40441131591797</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1897" t="n">
-        <v>5.36246061325073</v>
+        <v>5.36246013641357</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G1899" t="n">
-        <v>5.24572658538818</v>
+        <v>5.24572610855103</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1900" t="n">
-        <v>5.09616088867188</v>
+        <v>5.09616136550903</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.99219465255737</v>
+        <v>4.99219512939453</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G1905" t="n">
-        <v>4.97577905654907</v>
+        <v>4.97577953338623</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.84262990951538</v>
+        <v>4.84262943267822</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>4.80299997329712</v>
       </c>
       <c r="G1911" t="n">
-        <v>4.38025426864624</v>
+        <v>4.3802547454834</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G1913" t="n">
-        <v>4.50793218612671</v>
+        <v>4.50793170928955</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.56903505325317</v>
+        <v>4.56903553009033</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G1916" t="n">
-        <v>4.58909893035889</v>
+        <v>4.58909845352173</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>5.36399984359741</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.89187717437744</v>
+        <v>4.89187669754028</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>5.53599977493286</v>
       </c>
       <c r="G1926" t="n">
-        <v>5.04873752593994</v>
+        <v>5.0487380027771</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G1930" t="n">
-        <v>5.40258693695068</v>
+        <v>5.40258741378784</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>5.91800022125244</v>
       </c>
       <c r="G1934" t="n">
-        <v>5.39711570739746</v>
+        <v>5.39711618423462</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1935" t="n">
-        <v>5.45365810394287</v>
+        <v>5.45365858078003</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G1936" t="n">
-        <v>5.57403993606567</v>
+        <v>5.57404041290283</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1937" t="n">
-        <v>5.62693500518799</v>
+        <v>5.62693548202515</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>6.13800001144409</v>
       </c>
       <c r="G1939" t="n">
-        <v>5.59775161743164</v>
+        <v>5.5977520942688</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1943" t="n">
-        <v>5.73637342453003</v>
+        <v>5.73637294769287</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1946" t="n">
-        <v>5.69077348709106</v>
+        <v>5.69077396392822</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>6.18599987030029</v>
       </c>
       <c r="G1952" t="n">
-        <v>5.64152717590332</v>
+        <v>5.64152669906616</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1959" t="n">
-        <v>5.53208875656128</v>
+        <v>5.53208923339844</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -59704,6 +59704,32 @@
         <v>6.59499979019165</v>
       </c>
       <c r="H2282" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2283" t="n">
+        <v>2329370</v>
+      </c>
+      <c r="C2283" t="n">
+        <v>6.71500015258789</v>
+      </c>
+      <c r="D2283" t="n">
+        <v>6.61999988555908</v>
+      </c>
+      <c r="E2283" t="n">
+        <v>6.61999988555908</v>
+      </c>
+      <c r="F2283" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="G2283" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="H2283" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -52943,8 +52943,31 @@
       <c r="E2286" t="n">
         <v>6.55000019073486</v>
       </c>
-      <c r="F2286"/>
+      <c r="F2286" t="n">
+        <v>6.63000011444092</v>
+      </c>
       <c r="G2286" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2287" t="n">
+        <v>1053713</v>
+      </c>
+      <c r="C2287" t="n">
+        <v>6.7350001335144</v>
+      </c>
+      <c r="D2287" t="n">
+        <v>6.64499998092651</v>
+      </c>
+      <c r="E2287" t="n">
+        <v>6.69500017166138</v>
+      </c>
+      <c r="F2287"/>
+      <c r="G2287" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -52966,8 +52966,31 @@
       <c r="E2287" t="n">
         <v>6.69500017166138</v>
       </c>
-      <c r="F2287"/>
+      <c r="F2287" t="n">
+        <v>6.72499990463257</v>
+      </c>
       <c r="G2287" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2288" t="n">
+        <v>1505494</v>
+      </c>
+      <c r="C2288" t="n">
+        <v>6.78499984741211</v>
+      </c>
+      <c r="D2288" t="n">
+        <v>6.65500020980835</v>
+      </c>
+      <c r="E2288" t="n">
+        <v>6.65500020980835</v>
+      </c>
+      <c r="F2288"/>
+      <c r="G2288" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -52989,8 +52989,31 @@
       <c r="E2288" t="n">
         <v>6.65500020980835</v>
       </c>
-      <c r="F2288"/>
+      <c r="F2288" t="n">
+        <v>6.67000007629395</v>
+      </c>
       <c r="G2288" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2289" t="n">
+        <v>1249923</v>
+      </c>
+      <c r="C2289" t="n">
+        <v>6.63500022888184</v>
+      </c>
+      <c r="D2289" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E2289" t="n">
+        <v>6.6100001335144</v>
+      </c>
+      <c r="F2289"/>
+      <c r="G2289" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -53012,8 +53012,31 @@
       <c r="E2289" t="n">
         <v>6.6100001335144</v>
       </c>
-      <c r="F2289"/>
+      <c r="F2289" t="n">
+        <v>6.59499979019165</v>
+      </c>
       <c r="G2289" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2290" t="n">
+        <v>799865</v>
+      </c>
+      <c r="C2290" t="n">
+        <v>6.67000007629395</v>
+      </c>
+      <c r="D2290" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E2290" t="n">
+        <v>6.6100001335144</v>
+      </c>
+      <c r="F2290"/>
+      <c r="G2290" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -53042,6 +53042,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2291">
+      <c r="A2291" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2291" t="n">
+        <v>1725136</v>
+      </c>
+      <c r="C2291" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="D2291" t="n">
+        <v>6.6100001335144</v>
+      </c>
+      <c r="E2291" t="n">
+        <v>6.61499977111816</v>
+      </c>
+      <c r="F2291" t="n">
+        <v>6.63000011444092</v>
+      </c>
+      <c r="G2291" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G2" t="n">
-        <v>5.00744962692261</v>
+        <v>5.00744915008545</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>5.19319725036621</v>
+        <v>5.19319772720337</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G5" t="n">
-        <v>5.0771050453186</v>
+        <v>5.07710456848145</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G6" t="n">
-        <v>5.10419225692749</v>
+        <v>5.10419321060181</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G7" t="n">
-        <v>5.1119327545166</v>
+        <v>5.11193323135376</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>6.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.03066778182983</v>
+        <v>5.03066825866699</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>5.02679824829102</v>
+        <v>5.02679777145386</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>4.99971008300781</v>
+        <v>4.99970960617065</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>4.98423051834106</v>
+        <v>4.98423194885254</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>5.02679824829102</v>
+        <v>5.02679777145386</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G15" t="n">
-        <v>5.04227733612061</v>
+        <v>5.04227685928345</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>6.5</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03066778182983</v>
+        <v>5.03066825866699</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G18" t="n">
-        <v>5.04227733612061</v>
+        <v>5.04227685928345</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G19" t="n">
-        <v>5.10806322097778</v>
+        <v>5.10806226730347</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G20" t="n">
-        <v>5.11580228805542</v>
+        <v>5.11580276489258</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G23" t="n">
-        <v>5.37507486343384</v>
+        <v>5.375075340271</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G24" t="n">
-        <v>5.3325080871582</v>
+        <v>5.33250761032104</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>5.41764211654663</v>
+        <v>5.41764259338379</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G27" t="n">
-        <v>5.3673357963562</v>
+        <v>5.36733627319336</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>5.44860076904297</v>
+        <v>5.44860029220581</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G38" t="n">
-        <v>5.45247030258179</v>
+        <v>5.45246982574463</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>5.44860076904297</v>
+        <v>5.44860029220581</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>5.47955846786499</v>
+        <v>5.47955799102783</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G42" t="n">
-        <v>5.46407985687256</v>
+        <v>5.4640793800354</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>5.34024810791016</v>
+        <v>5.340247631073</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>5.42925214767456</v>
+        <v>5.42925119400024</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G46" t="n">
-        <v>5.39442443847656</v>
+        <v>5.39442348480225</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G47" t="n">
-        <v>5.37120532989502</v>
+        <v>5.37120580673218</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G50" t="n">
-        <v>5.61886930465698</v>
+        <v>5.61886882781982</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G53" t="n">
-        <v>5.59178066253662</v>
+        <v>5.59178161621094</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G56" t="n">
-        <v>5.4718189239502</v>
+        <v>5.47181940078735</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>5.47955846786499</v>
+        <v>5.47955799102783</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G58" t="n">
-        <v>5.52986478805542</v>
+        <v>5.52986526489258</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>5.54921388626099</v>
+        <v>5.54921340942383</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>5.59565019607544</v>
+        <v>5.5956506729126</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.25</v>
       </c>
       <c r="G62" t="n">
-        <v>5.61112928390503</v>
+        <v>5.61113023757935</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G65" t="n">
-        <v>5.84718418121338</v>
+        <v>5.84718370437622</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>6.04840993881226</v>
+        <v>6.04841089248657</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>6.14902400970459</v>
+        <v>6.14902448654175</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>7.75</v>
       </c>
       <c r="G69" t="n">
-        <v>5.99810361862183</v>
+        <v>5.99810409545898</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>7.86499977111816</v>
       </c>
       <c r="G71" t="n">
-        <v>6.08710813522339</v>
+        <v>6.08710765838623</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G72" t="n">
-        <v>6.09097766876221</v>
+        <v>6.09097814559937</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G73" t="n">
-        <v>6.13741540908813</v>
+        <v>6.13741493225098</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G76" t="n">
-        <v>6.09097766876221</v>
+        <v>6.09097814559937</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>5.98262453079224</v>
+        <v>5.98262500762939</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G79" t="n">
-        <v>5.97101593017578</v>
+        <v>5.9710168838501</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>5.94392728805542</v>
+        <v>5.94392776489258</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G82" t="n">
-        <v>6.06930732727051</v>
+        <v>6.06930780410767</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G83" t="n">
-        <v>6.00584411621094</v>
+        <v>6.00584363937378</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G84" t="n">
-        <v>6.00584411621094</v>
+        <v>6.00584363937378</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7.76399993896484</v>
       </c>
       <c r="G85" t="n">
-        <v>6.00893974304199</v>
+        <v>6.00894021987915</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G86" t="n">
-        <v>5.88201093673706</v>
+        <v>5.88201141357422</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G87" t="n">
-        <v>5.72722244262695</v>
+        <v>5.72722148895264</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.55800008773804</v>
       </c>
       <c r="G89" t="n">
-        <v>5.84950590133667</v>
+        <v>5.84950542449951</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>7.32800006866455</v>
       </c>
       <c r="G90" t="n">
-        <v>5.67149782180786</v>
+        <v>5.6714973449707</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G99" t="n">
-        <v>5.73186540603638</v>
+        <v>5.73186588287354</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>7.28800010681152</v>
       </c>
       <c r="G104" t="n">
-        <v>5.64053916931152</v>
+        <v>5.64053964614868</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>7.0479998588562</v>
       </c>
       <c r="G105" t="n">
-        <v>5.45479154586792</v>
+        <v>5.45479249954224</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>6.91200017929077</v>
       </c>
       <c r="G106" t="n">
-        <v>5.34953498840332</v>
+        <v>5.34953546524048</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>6.89200019836426</v>
       </c>
       <c r="G107" t="n">
-        <v>5.33405590057373</v>
+        <v>5.33405637741089</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G108" t="n">
-        <v>5.4857497215271</v>
+        <v>5.48575019836426</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>7.26599979400635</v>
       </c>
       <c r="G112" t="n">
-        <v>5.62351322174072</v>
+        <v>5.62351274490356</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G113" t="n">
-        <v>5.52754354476929</v>
+        <v>5.52754306793213</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G114" t="n">
-        <v>5.4718189239502</v>
+        <v>5.47181940078735</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>5.51051616668701</v>
+        <v>5.51051664352417</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>7.08199977874756</v>
       </c>
       <c r="G117" t="n">
-        <v>5.48110675811768</v>
+        <v>5.48110628128052</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>7.19799995422363</v>
       </c>
       <c r="G118" t="n">
-        <v>5.57088470458984</v>
+        <v>5.57088375091553</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G119" t="n">
-        <v>5.61886930465698</v>
+        <v>5.61886882781982</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G120" t="n">
-        <v>5.51051616668701</v>
+        <v>5.51051664352417</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>5.46407985687256</v>
+        <v>5.4640793800354</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G123" t="n">
-        <v>5.42538213729858</v>
+        <v>5.42538261413574</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>7.03599977493286</v>
       </c>
       <c r="G124" t="n">
-        <v>5.4455041885376</v>
+        <v>5.44550466537476</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>5.57243251800537</v>
+        <v>5.57243204116821</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>7.16800022125244</v>
       </c>
       <c r="G126" t="n">
-        <v>5.54766654968262</v>
+        <v>5.5476655960083</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G128" t="n">
-        <v>5.5554051399231</v>
+        <v>5.55540561676025</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>5.54147386550903</v>
+        <v>5.54147434234619</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>7.11199998855591</v>
       </c>
       <c r="G130" t="n">
-        <v>5.5043249130249</v>
+        <v>5.50432538986206</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503707885742</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G134" t="n">
-        <v>5.61886930465698</v>
+        <v>5.61886882781982</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>7.25</v>
       </c>
       <c r="G135" t="n">
-        <v>5.61112928390503</v>
+        <v>5.61113023757935</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>5.54921388626099</v>
+        <v>5.54921340942383</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G138" t="n">
-        <v>5.44086074829102</v>
+        <v>5.44086122512817</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>7.02400016784668</v>
       </c>
       <c r="G139" t="n">
-        <v>5.43621778488159</v>
+        <v>5.43621730804443</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G141" t="n">
-        <v>5.57243251800537</v>
+        <v>5.57243204116821</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.13600015640259</v>
       </c>
       <c r="G142" t="n">
-        <v>5.52289962768555</v>
+        <v>5.52289915084839</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7.19600009918213</v>
       </c>
       <c r="G144" t="n">
-        <v>5.56933689117432</v>
+        <v>5.56933641433716</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>7.2039999961853</v>
       </c>
       <c r="G145" t="n">
-        <v>5.57552766799927</v>
+        <v>5.57552814483643</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.28200006484985</v>
       </c>
       <c r="G147" t="n">
-        <v>5.63589668273926</v>
+        <v>5.6358962059021</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.32800006866455</v>
       </c>
       <c r="G149" t="n">
-        <v>5.67149782180786</v>
+        <v>5.6714973449707</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503707885742</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>7.01200008392334</v>
       </c>
       <c r="G152" t="n">
-        <v>5.42693042755127</v>
+        <v>5.42692947387695</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.14400005340576</v>
       </c>
       <c r="G154" t="n">
-        <v>5.52909088134766</v>
+        <v>5.52909135818481</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.5479998588562</v>
       </c>
       <c r="G157" t="n">
-        <v>5.84176588058472</v>
+        <v>5.84176635742188</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>7.61199998855591</v>
       </c>
       <c r="G158" t="n">
-        <v>5.8912992477417</v>
+        <v>5.89129877090454</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7.67799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>5.94237995147705</v>
+        <v>5.94238042831421</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>5.89749050140381</v>
+        <v>5.89749097824097</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G163" t="n">
-        <v>5.75044012069702</v>
+        <v>5.75044059753418</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G164" t="n">
-        <v>5.69626379013062</v>
+        <v>5.69626474380493</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>7.31799983978271</v>
       </c>
       <c r="G167" t="n">
-        <v>5.66375827789307</v>
+        <v>5.66375875473022</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>7.32800006866455</v>
       </c>
       <c r="G168" t="n">
-        <v>5.67149782180786</v>
+        <v>5.6714973449707</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7.47599983215332</v>
       </c>
       <c r="G170" t="n">
-        <v>5.78604125976562</v>
+        <v>5.78604221343994</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>7.52400016784668</v>
       </c>
       <c r="G174" t="n">
-        <v>5.82319211959839</v>
+        <v>5.82319116592407</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G176" t="n">
-        <v>5.75044012069702</v>
+        <v>5.75044059753418</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>5.72722244262695</v>
+        <v>5.72722148895264</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G178" t="n">
-        <v>5.76591968536377</v>
+        <v>5.76591920852661</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G179" t="n">
-        <v>5.72257900238037</v>
+        <v>5.72257852554321</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.64982748031616</v>
+        <v>5.649827003479</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G182" t="n">
-        <v>5.60339021682739</v>
+        <v>5.60338973999023</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G183" t="n">
-        <v>5.69316911697388</v>
+        <v>5.69316816329956</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>7.25</v>
       </c>
       <c r="G184" t="n">
-        <v>5.61112928390503</v>
+        <v>5.61113023757935</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>7.29199981689453</v>
       </c>
       <c r="G186" t="n">
-        <v>5.64363527297974</v>
+        <v>5.64363574981689</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>7.24200010299683</v>
       </c>
       <c r="G190" t="n">
-        <v>5.60493850708008</v>
+        <v>5.60493803024292</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G191" t="n">
-        <v>5.5554051399231</v>
+        <v>5.55540561676025</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>7.2960000038147</v>
       </c>
       <c r="G192" t="n">
-        <v>5.64673137664795</v>
+        <v>5.64673185348511</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7.13600015640259</v>
       </c>
       <c r="G193" t="n">
-        <v>5.52289962768555</v>
+        <v>5.52289915084839</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7.15799999237061</v>
       </c>
       <c r="G195" t="n">
-        <v>5.53992605209351</v>
+        <v>5.53992652893066</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7</v>
       </c>
       <c r="G196" t="n">
-        <v>5.41764211654663</v>
+        <v>5.41764259338379</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="n">
-        <v>5.41764211654663</v>
+        <v>5.41764259338379</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>5.47955846786499</v>
+        <v>5.47955799102783</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G203" t="n">
-        <v>5.52754354476929</v>
+        <v>5.52754306793213</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G204" t="n">
-        <v>5.4718189239502</v>
+        <v>5.47181940078735</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>7.44600009918213</v>
       </c>
       <c r="G207" t="n">
-        <v>5.76282405853271</v>
+        <v>5.76282358169556</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>7.46600008010864</v>
       </c>
       <c r="G208" t="n">
-        <v>5.7783031463623</v>
+        <v>5.77830266952515</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>7.47200012207031</v>
       </c>
       <c r="G210" t="n">
-        <v>5.78294658660889</v>
+        <v>5.78294610977173</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7.19799995422363</v>
       </c>
       <c r="G212" t="n">
-        <v>5.57088470458984</v>
+        <v>5.57088375091553</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>7.48799991607666</v>
       </c>
       <c r="G215" t="n">
-        <v>5.79532957077026</v>
+        <v>5.79532909393311</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.60400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>5.88510799407959</v>
+        <v>5.88510751724243</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>5.88201093673706</v>
+        <v>5.88201141357422</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>7.63800001144409</v>
       </c>
       <c r="G221" t="n">
-        <v>5.91142129898071</v>
+        <v>5.91142177581787</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>7.59800004959106</v>
       </c>
       <c r="G224" t="n">
-        <v>5.88046407699585</v>
+        <v>5.88046360015869</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>7.25</v>
       </c>
       <c r="G225" t="n">
-        <v>5.61112928390503</v>
+        <v>5.61113023757935</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G226" t="n">
-        <v>5.69626379013062</v>
+        <v>5.69626474380493</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>7.1560001373291</v>
       </c>
       <c r="G227" t="n">
-        <v>5.53837823867798</v>
+        <v>5.53837871551514</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G229" t="n">
-        <v>5.62041759490967</v>
+        <v>5.62041711807251</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.25</v>
       </c>
       <c r="G230" t="n">
-        <v>5.61112928390503</v>
+        <v>5.61113023757935</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>6.93800020217896</v>
       </c>
       <c r="G232" t="n">
-        <v>5.36965799331665</v>
+        <v>5.36965751647949</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>6.86199998855591</v>
       </c>
       <c r="G233" t="n">
-        <v>5.31083726882935</v>
+        <v>5.3108377456665</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>6.92799997329712</v>
       </c>
       <c r="G234" t="n">
-        <v>5.3619179725647</v>
+        <v>5.36191749572754</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>6.92799997329712</v>
       </c>
       <c r="G235" t="n">
-        <v>5.3619179725647</v>
+        <v>5.36191749572754</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G236" t="n">
-        <v>5.2164158821106</v>
+        <v>5.21641540527344</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>6.67199993133545</v>
       </c>
       <c r="G237" t="n">
-        <v>5.16378784179688</v>
+        <v>5.16378736495972</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7.01200008392334</v>
       </c>
       <c r="G239" t="n">
-        <v>5.42693042755127</v>
+        <v>5.42692947387695</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503707885742</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>7.22200012207031</v>
       </c>
       <c r="G243" t="n">
-        <v>5.58945941925049</v>
+        <v>5.58945894241333</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>7.18800020217896</v>
       </c>
       <c r="G245" t="n">
-        <v>5.56314468383789</v>
+        <v>5.56314516067505</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>5.51051616668701</v>
+        <v>5.51051664352417</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G249" t="n">
-        <v>5.4857497215271</v>
+        <v>5.48575019836426</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>7.25600004196167</v>
       </c>
       <c r="G251" t="n">
-        <v>5.61577320098877</v>
+        <v>5.61577272415161</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>7.22800016403198</v>
       </c>
       <c r="G252" t="n">
-        <v>5.59410333633423</v>
+        <v>5.59410285949707</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G253" t="n">
-        <v>5.5662407875061</v>
+        <v>5.56624031066895</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.99200010299683</v>
       </c>
       <c r="G254" t="n">
-        <v>5.41145086288452</v>
+        <v>5.41145038604736</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G255" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503707885742</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>5.25511264801025</v>
+        <v>5.25511312484741</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>6.56599998474121</v>
       </c>
       <c r="G258" t="n">
-        <v>5.08174800872803</v>
+        <v>5.08174848556519</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G259" t="n">
-        <v>5.17771863937378</v>
+        <v>5.17771816253662</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G261" t="n">
-        <v>4.73037576675415</v>
+        <v>4.73037624359131</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>4.87587881088257</v>
+        <v>4.87587833404541</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>4.99197006225586</v>
+        <v>4.99197053909302</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>4.78300380706787</v>
+        <v>4.78300428390503</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>6.2480001449585</v>
       </c>
       <c r="G272" t="n">
-        <v>4.83563375473022</v>
+        <v>4.83563280105591</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G273" t="n">
-        <v>4.91457557678223</v>
+        <v>4.91457605361938</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G275" t="n">
-        <v>5.02602386474609</v>
+        <v>5.02602434158325</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>6.44600009918213</v>
       </c>
       <c r="G276" t="n">
-        <v>4.98887491226196</v>
+        <v>4.9888744354248</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.34600019454956</v>
       </c>
       <c r="G278" t="n">
-        <v>4.91148042678833</v>
+        <v>4.91147994995117</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>6.26599979400635</v>
       </c>
       <c r="G279" t="n">
-        <v>4.84956407546997</v>
+        <v>4.84956359863281</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>5.0151891708374</v>
+        <v>5.01518869400024</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>6.33599996566772</v>
       </c>
       <c r="G281" t="n">
-        <v>4.90374040603638</v>
+        <v>4.90373992919922</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G282" t="n">
-        <v>4.79074478149414</v>
+        <v>4.79074382781982</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>5.89200019836426</v>
       </c>
       <c r="G283" t="n">
-        <v>4.56010723114014</v>
+        <v>4.56010770797729</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>6.12400007247925</v>
       </c>
       <c r="G285" t="n">
-        <v>4.73966312408447</v>
+        <v>4.73966360092163</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>6.2020001411438</v>
       </c>
       <c r="G286" t="n">
-        <v>4.80003118515015</v>
+        <v>4.8000316619873</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G287" t="n">
-        <v>4.80467462539673</v>
+        <v>4.80467557907104</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>6.29199981689453</v>
       </c>
       <c r="G288" t="n">
-        <v>4.86968660354614</v>
+        <v>4.8696870803833</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>6.23400020599365</v>
       </c>
       <c r="G289" t="n">
-        <v>4.82479810714722</v>
+        <v>4.8247971534729</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G290" t="n">
-        <v>4.93005466461182</v>
+        <v>4.93005418777466</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>6.32600021362305</v>
       </c>
       <c r="G291" t="n">
-        <v>4.89600038528442</v>
+        <v>4.89600133895874</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.42399978637695</v>
       </c>
       <c r="G292" t="n">
-        <v>4.97184705734253</v>
+        <v>4.97184801101685</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G293" t="n">
-        <v>5.02602386474609</v>
+        <v>5.02602434158325</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G295" t="n">
-        <v>4.79848337173462</v>
+        <v>4.79848289489746</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>6.24399995803833</v>
       </c>
       <c r="G296" t="n">
-        <v>4.83253717422485</v>
+        <v>4.8325366973877</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G297" t="n">
-        <v>4.80467462539673</v>
+        <v>4.80467557907104</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>6.43400001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>4.97958755493164</v>
+        <v>4.97958707809448</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>6.20599985122681</v>
       </c>
       <c r="G300" t="n">
-        <v>4.80312728881836</v>
+        <v>4.8031268119812</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G304" t="n">
-        <v>4.55855941772461</v>
+        <v>4.55855894088745</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>4.58487272262573</v>
+        <v>4.58487319946289</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.00799989700317</v>
       </c>
       <c r="G306" t="n">
-        <v>4.64988565444946</v>
+        <v>4.6498851776123</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>4.52760076522827</v>
+        <v>4.52760124206543</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.72599983215332</v>
       </c>
       <c r="G308" t="n">
-        <v>4.43163156509399</v>
+        <v>4.43163108825684</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>5.7480001449585</v>
       </c>
       <c r="G310" t="n">
-        <v>4.44865894317627</v>
+        <v>4.44865846633911</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.44600009918213</v>
       </c>
       <c r="G316" t="n">
-        <v>4.21492576599121</v>
+        <v>4.21492528915405</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G317" t="n">
-        <v>4.40531730651855</v>
+        <v>4.4053168296814</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.63800001144409</v>
       </c>
       <c r="G318" t="n">
-        <v>4.36352491378784</v>
+        <v>4.36352396011353</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G319" t="n">
-        <v>4.48116397857666</v>
+        <v>4.48116445541382</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.96600008010864</v>
       </c>
       <c r="G320" t="n">
-        <v>4.61737871170044</v>
+        <v>4.6173791885376</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G322" t="n">
-        <v>4.69013071060181</v>
+        <v>4.69013023376465</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>6.0460000038147</v>
       </c>
       <c r="G323" t="n">
-        <v>4.67929601669312</v>
+        <v>4.6792950630188</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>6.05200004577637</v>
       </c>
       <c r="G327" t="n">
-        <v>4.68393850326538</v>
+        <v>4.68393898010254</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>6.02799987792969</v>
       </c>
       <c r="G329" t="n">
-        <v>4.66536426544189</v>
+        <v>4.66536378860474</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G331" t="n">
-        <v>4.71489715576172</v>
+        <v>4.71489667892456</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>5.81199979782104</v>
       </c>
       <c r="G334" t="n">
-        <v>4.49818992614746</v>
+        <v>4.49819040298462</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>4.55855941772461</v>
+        <v>4.55855894088745</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>5.69799995422363</v>
       </c>
       <c r="G337" t="n">
-        <v>4.40996026992798</v>
+        <v>4.40996074676514</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.77600002288818</v>
       </c>
       <c r="G338" t="n">
-        <v>4.47032928466797</v>
+        <v>4.47032880783081</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.98199987411499</v>
       </c>
       <c r="G339" t="n">
-        <v>4.62976217269897</v>
+        <v>4.62976264953613</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.71799993515015</v>
       </c>
       <c r="G343" t="n">
-        <v>4.42543983459473</v>
+        <v>4.42544031143188</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G345" t="n">
-        <v>4.71489715576172</v>
+        <v>4.71489667892456</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G348" t="n">
-        <v>4.65452861785889</v>
+        <v>4.65452909469604</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G349" t="n">
-        <v>4.55855941772461</v>
+        <v>4.55855894088745</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>6.11600017547607</v>
       </c>
       <c r="G350" t="n">
-        <v>4.73347187042236</v>
+        <v>4.73347234725952</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G354" t="n">
-        <v>4.69477367401123</v>
+        <v>4.69477415084839</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G355" t="n">
-        <v>4.5043830871582</v>
+        <v>4.50438356399536</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>6.07600021362305</v>
       </c>
       <c r="G357" t="n">
-        <v>4.70251417160034</v>
+        <v>4.70251369476318</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G363" t="n">
-        <v>4.49509572982788</v>
+        <v>4.49509525299072</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.76800012588501</v>
       </c>
       <c r="G364" t="n">
-        <v>4.46413707733154</v>
+        <v>4.4641375541687</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.83799982070923</v>
       </c>
       <c r="G366" t="n">
-        <v>4.51831388473511</v>
+        <v>4.51831340789795</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>4.61273622512817</v>
+        <v>4.61273574829102</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.97200012207031</v>
       </c>
       <c r="G368" t="n">
-        <v>4.62202262878418</v>
+        <v>4.6220235824585</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G371" t="n">
-        <v>4.68548679351807</v>
+        <v>4.68548631668091</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.93400001525879</v>
       </c>
       <c r="G372" t="n">
-        <v>4.59261274337769</v>
+        <v>4.59261322021484</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G374" t="n">
-        <v>4.53069639205933</v>
+        <v>4.53069686889648</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.73799991607666</v>
       </c>
       <c r="G377" t="n">
-        <v>4.44091892242432</v>
+        <v>4.44091844558716</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>5.82800006866455</v>
       </c>
       <c r="G378" t="n">
-        <v>4.51057386398315</v>
+        <v>4.51057434082031</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G380" t="n">
-        <v>4.79848337173462</v>
+        <v>4.79848289489746</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>4.79074478149414</v>
+        <v>4.79074382781982</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G385" t="n">
-        <v>4.84492063522339</v>
+        <v>4.84492015838623</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G386" t="n">
-        <v>4.91612434387207</v>
+        <v>4.91612386703491</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.60200023651123</v>
       </c>
       <c r="G387" t="n">
-        <v>5.10961103439331</v>
+        <v>5.10961151123047</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.51200008392334</v>
       </c>
       <c r="G388" t="n">
-        <v>5.03995561599731</v>
+        <v>5.03995609283447</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G389" t="n">
-        <v>5.02757167816162</v>
+        <v>5.02757263183594</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.5</v>
       </c>
       <c r="G390" t="n">
-        <v>5.03066778182983</v>
+        <v>5.03066825866699</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>4.98423051834106</v>
+        <v>4.98423194885254</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>6.44199991226196</v>
       </c>
       <c r="G393" t="n">
-        <v>4.98577880859375</v>
+        <v>4.98577833175659</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.4060001373291</v>
       </c>
       <c r="G394" t="n">
-        <v>4.95791625976562</v>
+        <v>4.95791673660278</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G395" t="n">
-        <v>5.02602386474609</v>
+        <v>5.02602434158325</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G396" t="n">
-        <v>4.99971008300781</v>
+        <v>4.99970960617065</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.50799989700317</v>
       </c>
       <c r="G397" t="n">
-        <v>5.0368595123291</v>
+        <v>5.03685998916626</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>6.17799997329712</v>
       </c>
       <c r="G399" t="n">
-        <v>4.7814564704895</v>
+        <v>4.78145599365234</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>5.97399997711182</v>
       </c>
       <c r="G400" t="n">
-        <v>4.62357091903687</v>
+        <v>4.62356996536255</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>5.77799987792969</v>
       </c>
       <c r="G403" t="n">
-        <v>4.47187662124634</v>
+        <v>4.4718770980835</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G407" t="n">
-        <v>4.53069639205933</v>
+        <v>4.53069686889648</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G410" t="n">
-        <v>4.37493562698364</v>
+        <v>4.37493515014648</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>5.57600021362305</v>
       </c>
       <c r="G411" t="n">
-        <v>4.45157670974731</v>
+        <v>4.45157718658447</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.34800004959106</v>
       </c>
       <c r="G413" t="n">
-        <v>4.26955413818359</v>
+        <v>4.26955366134644</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G414" t="n">
-        <v>4.25039386749268</v>
+        <v>4.25039339065552</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.23400020599365</v>
       </c>
       <c r="G415" t="n">
-        <v>4.17854261398315</v>
+        <v>4.178542137146</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G417" t="n">
-        <v>4.07635450363159</v>
+        <v>4.07635402679443</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G419" t="n">
-        <v>4.07635450363159</v>
+        <v>4.07635402679443</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G420" t="n">
-        <v>4.08114433288574</v>
+        <v>4.0811448097229</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5.17799997329712</v>
       </c>
       <c r="G422" t="n">
-        <v>4.13383531570435</v>
+        <v>4.13383483886719</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.32800006866455</v>
       </c>
       <c r="G426" t="n">
-        <v>4.253586769104</v>
+        <v>4.25358772277832</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.25</v>
       </c>
       <c r="G428" t="n">
-        <v>4.1913161277771</v>
+        <v>4.19131565093994</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.2519998550415</v>
       </c>
       <c r="G430" t="n">
-        <v>4.19291257858276</v>
+        <v>4.19291210174561</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>5.2979998588562</v>
       </c>
       <c r="G431" t="n">
-        <v>4.22963619232178</v>
+        <v>4.22963666915894</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>5.47599983215332</v>
       </c>
       <c r="G433" t="n">
-        <v>4.37174224853516</v>
+        <v>4.371741771698</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G434" t="n">
-        <v>4.3924994468689</v>
+        <v>4.39249897003174</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5.19600009918213</v>
       </c>
       <c r="G438" t="n">
-        <v>4.14820575714111</v>
+        <v>4.14820528030396</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>5.30600023269653</v>
       </c>
       <c r="G440" t="n">
-        <v>4.23602342605591</v>
+        <v>4.23602390289307</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>4.15938234329224</v>
+        <v>4.15938138961792</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5.25</v>
       </c>
       <c r="G442" t="n">
-        <v>4.1913161277771</v>
+        <v>4.19131565093994</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G446" t="n">
-        <v>4.25039386749268</v>
+        <v>4.25039339065552</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>5.39400005340576</v>
       </c>
       <c r="G447" t="n">
-        <v>4.30627822875977</v>
+        <v>4.30627775192261</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G448" t="n">
-        <v>4.40367555618286</v>
+        <v>4.40367603302002</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5.67799997329712</v>
       </c>
       <c r="G449" t="n">
-        <v>4.53300809860229</v>
+        <v>4.53300762176514</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>5.55399990081787</v>
       </c>
       <c r="G451" t="n">
-        <v>4.43401288986206</v>
+        <v>4.43401336669922</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G453" t="n">
-        <v>4.15139865875244</v>
+        <v>4.1513991355896</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G454" t="n">
-        <v>4.14022159576416</v>
+        <v>4.14022207260132</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5.68200016021729</v>
       </c>
       <c r="G456" t="n">
-        <v>4.53620147705078</v>
+        <v>4.53620100021362</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G457" t="n">
-        <v>4.63359975814819</v>
+        <v>4.63359928131104</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G458" t="n">
-        <v>4.55057191848755</v>
+        <v>4.55057144165039</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.31400012969971</v>
       </c>
       <c r="G461" t="n">
-        <v>4.24241018295288</v>
+        <v>4.24241065979004</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.38800001144409</v>
       </c>
       <c r="G463" t="n">
-        <v>4.30148792266846</v>
+        <v>4.3014874458313</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.01599979400635</v>
       </c>
       <c r="G464" t="n">
-        <v>4.00450325012207</v>
+        <v>4.00450277328491</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>3.87197756767273</v>
+        <v>3.87197709083557</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G466" t="n">
-        <v>3.76819252967834</v>
+        <v>3.76819229125977</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>4.85699987411499</v>
       </c>
       <c r="G468" t="n">
-        <v>3.87756609916687</v>
+        <v>3.87756586074829</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>3.70831680297852</v>
+        <v>3.70831656455994</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.75299978256226</v>
       </c>
       <c r="G471" t="n">
-        <v>3.79453825950623</v>
+        <v>3.79453802108765</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G472" t="n">
-        <v>3.64444947242737</v>
+        <v>3.64444899559021</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G473" t="n">
-        <v>3.60532999038696</v>
+        <v>3.60532975196838</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G474" t="n">
-        <v>3.67957639694214</v>
+        <v>3.67957663536072</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.51300001144409</v>
       </c>
       <c r="G475" t="n">
-        <v>3.60293531417847</v>
+        <v>3.60293507575989</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G476" t="n">
-        <v>3.74264574050903</v>
+        <v>3.74264550209045</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.81300020217896</v>
       </c>
       <c r="G477" t="n">
-        <v>3.84243869781494</v>
+        <v>3.84243893623352</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.74100017547607</v>
       </c>
       <c r="G479" t="n">
-        <v>3.78495788574219</v>
+        <v>3.78495764732361</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.84700012207031</v>
       </c>
       <c r="G480" t="n">
-        <v>3.86958265304565</v>
+        <v>3.86958289146423</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.82407689094543</v>
+        <v>3.82407665252686</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.74025011062622</v>
+        <v>3.74025106430054</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G487" t="n">
-        <v>4.06837034225464</v>
+        <v>4.0683708190918</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.13199996948242</v>
       </c>
       <c r="G488" t="n">
-        <v>4.09711122512817</v>
+        <v>4.09711074829102</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G491" t="n">
-        <v>4.26316738128662</v>
+        <v>4.26316690444946</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>4.4228367805481</v>
+        <v>4.42283630371094</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G493" t="n">
-        <v>4.51863765716553</v>
+        <v>4.51863718032837</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>4.55057191848755</v>
+        <v>4.55057144165039</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G495" t="n">
-        <v>4.49468755722046</v>
+        <v>4.49468803405762</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G496" t="n">
-        <v>4.52183151245117</v>
+        <v>4.52183103561401</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G497" t="n">
-        <v>4.56973218917847</v>
+        <v>4.56973171234131</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G498" t="n">
-        <v>4.52183151245117</v>
+        <v>4.52183103561401</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>5.44199991226196</v>
       </c>
       <c r="G499" t="n">
-        <v>4.34459829330444</v>
+        <v>4.3445987701416</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>4.4228367805481</v>
+        <v>4.42283630371094</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G504" t="n">
-        <v>4.33342123031616</v>
+        <v>4.33342170715332</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.25</v>
       </c>
       <c r="G506" t="n">
-        <v>4.1913161277771</v>
+        <v>4.19131565093994</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G507" t="n">
-        <v>4.17055940628052</v>
+        <v>4.1705584526062</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G510" t="n">
-        <v>4.01727628707886</v>
+        <v>4.01727676391602</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G514" t="n">
-        <v>4.33342123031616</v>
+        <v>4.33342170715332</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G515" t="n">
-        <v>4.48510694503784</v>
+        <v>4.485107421875</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.69399976730347</v>
       </c>
       <c r="G516" t="n">
-        <v>4.54578113555908</v>
+        <v>4.54578161239624</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G517" t="n">
-        <v>4.43081951141357</v>
+        <v>4.43081998825073</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G520" t="n">
-        <v>4.40048313140869</v>
+        <v>4.40048265457153</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G521" t="n">
-        <v>4.31266498565674</v>
+        <v>4.31266450881958</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.82399988174438</v>
       </c>
       <c r="G524" t="n">
-        <v>4.64956617355347</v>
+        <v>4.64956665039062</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G525" t="n">
-        <v>4.636794090271</v>
+        <v>4.63679313659668</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G528" t="n">
-        <v>4.18333196640015</v>
+        <v>4.18333292007446</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G529" t="n">
-        <v>4.32703447341919</v>
+        <v>4.32703495025635</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G530" t="n">
-        <v>4.28552055358887</v>
+        <v>4.28552007675171</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.28711700439453</v>
+        <v>4.28711748123169</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>4.37493562698364</v>
+        <v>4.37493515014648</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.44799995422363</v>
       </c>
       <c r="G533" t="n">
-        <v>4.34938859939575</v>
+        <v>4.34938812255859</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.4980001449585</v>
       </c>
       <c r="G534" t="n">
-        <v>4.38930606842041</v>
+        <v>4.38930559158325</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.41485357284546</v>
+        <v>4.4148530960083</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G536" t="n">
-        <v>4.28073024749756</v>
+        <v>4.28073072433472</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G537" t="n">
-        <v>4.22644376754761</v>
+        <v>4.22644329071045</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G538" t="n">
-        <v>4.24879741668701</v>
+        <v>4.2487964630127</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>5.21400022506714</v>
       </c>
       <c r="G540" t="n">
-        <v>4.16257619857788</v>
+        <v>4.16257572174072</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G546" t="n">
-        <v>4.22644376754761</v>
+        <v>4.22644329071045</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G548" t="n">
-        <v>4.11148166656494</v>
+        <v>4.11148118972778</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G549" t="n">
-        <v>4.06996726989746</v>
+        <v>4.06996774673462</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G550" t="n">
-        <v>4.03164720535278</v>
+        <v>4.03164672851562</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G551" t="n">
-        <v>4.06996726989746</v>
+        <v>4.06996774673462</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.07800006866455</v>
       </c>
       <c r="G552" t="n">
-        <v>4.05400085449219</v>
+        <v>4.05400037765503</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G556" t="n">
-        <v>4.17055940628052</v>
+        <v>4.1705584526062</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G558" t="n">
-        <v>4.17055940628052</v>
+        <v>4.1705584526062</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G559" t="n">
-        <v>4.24560356140137</v>
+        <v>4.24560308456421</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G561" t="n">
-        <v>4.16576862335205</v>
+        <v>4.16576910018921</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G562" t="n">
-        <v>4.098708152771</v>
+        <v>4.09870719909668</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.21600008010864</v>
       </c>
       <c r="G564" t="n">
-        <v>4.16417264938354</v>
+        <v>4.1641731262207</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G565" t="n">
-        <v>4.15299558639526</v>
+        <v>4.15299606323242</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G567" t="n">
-        <v>4.26795768737793</v>
+        <v>4.26795721054077</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>4.15938234329224</v>
+        <v>4.15938138961792</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G570" t="n">
-        <v>4.16576862335205</v>
+        <v>4.16576910018921</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>5.28599977493286</v>
       </c>
       <c r="G572" t="n">
-        <v>4.22005701065063</v>
+        <v>4.22005653381348</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.25400018692017</v>
       </c>
       <c r="G574" t="n">
-        <v>4.19450950622559</v>
+        <v>4.19450902938843</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.02799987792969</v>
       </c>
       <c r="G576" t="n">
-        <v>4.01408290863037</v>
+        <v>4.01408338546753</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.1560001373291</v>
       </c>
       <c r="G579" t="n">
-        <v>4.11627101898193</v>
+        <v>4.11627149581909</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.03800010681152</v>
       </c>
       <c r="G581" t="n">
-        <v>4.02206611633301</v>
+        <v>4.02206707000732</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G582" t="n">
-        <v>3.92147517204285</v>
+        <v>3.92147541046143</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.78900003433228</v>
       </c>
       <c r="G583" t="n">
-        <v>3.82327914237976</v>
+        <v>3.82327890396118</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.58300018310547</v>
       </c>
       <c r="G585" t="n">
-        <v>3.65881967544556</v>
+        <v>3.6588191986084</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G586" t="n">
-        <v>3.75302457809448</v>
+        <v>3.75302410125732</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G587" t="n">
-        <v>3.62129640579224</v>
+        <v>3.62129712104797</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G588" t="n">
-        <v>3.49036836624146</v>
+        <v>3.49036812782288</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.36299991607666</v>
       </c>
       <c r="G590" t="n">
-        <v>3.48318314552307</v>
+        <v>3.48318290710449</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G591" t="n">
-        <v>3.68037509918213</v>
+        <v>3.68037486076355</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.59299993515015</v>
       </c>
       <c r="G592" t="n">
-        <v>3.66680312156677</v>
+        <v>3.66680264472961</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>3.62848234176636</v>
+        <v>3.62848258018494</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.45100021362305</v>
       </c>
       <c r="G595" t="n">
-        <v>3.55343770980835</v>
+        <v>3.55343794822693</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G596" t="n">
-        <v>3.67957639694214</v>
+        <v>3.67957663536072</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G597" t="n">
-        <v>3.60054016113281</v>
+        <v>3.60054039955139</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>3.60852360725403</v>
+        <v>3.60852336883545</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G599" t="n">
-        <v>3.76819252967834</v>
+        <v>3.76819229125977</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G602" t="n">
-        <v>3.86798524856567</v>
+        <v>3.86798596382141</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.75299978256226</v>
       </c>
       <c r="G603" t="n">
-        <v>3.79453825950623</v>
+        <v>3.79453802108765</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.45900011062622</v>
       </c>
       <c r="G604" t="n">
-        <v>3.55982398986816</v>
+        <v>3.5598247051239</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.36100006103516</v>
       </c>
       <c r="G605" t="n">
-        <v>3.48158621788025</v>
+        <v>3.48158645629883</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G607" t="n">
-        <v>3.44885420799255</v>
+        <v>3.44885444641113</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>3.27321839332581</v>
+        <v>3.27321815490723</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.81299996376038</v>
       </c>
       <c r="G616" t="n">
-        <v>3.04409313201904</v>
+        <v>3.04409265518188</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G619" t="n">
-        <v>2.54832005500793</v>
+        <v>2.54832029342651</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G620" t="n">
-        <v>2.68004751205444</v>
+        <v>2.68004703521729</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.61899995803833</v>
       </c>
       <c r="G621" t="n">
-        <v>2.8892138004303</v>
+        <v>2.88921403884888</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G622" t="n">
-        <v>3.04169797897339</v>
+        <v>3.04169821739197</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G624" t="n">
-        <v>2.76866340637207</v>
+        <v>2.76866364479065</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G625" t="n">
-        <v>2.86606168746948</v>
+        <v>2.86606192588806</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.45300006866455</v>
       </c>
       <c r="G626" t="n">
-        <v>2.75668835639954</v>
+        <v>2.75668859481812</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>3.34100008010864</v>
       </c>
       <c r="G629" t="n">
-        <v>2.66727352142334</v>
+        <v>2.66727375984192</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G630" t="n">
-        <v>2.60659956932068</v>
+        <v>2.6065993309021</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>2.52676486968994</v>
+        <v>2.52676439285278</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>2.52676486968994</v>
+        <v>2.52676439285278</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G635" t="n">
-        <v>2.56748056411743</v>
+        <v>2.56748032569885</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G637" t="n">
-        <v>2.69681262969971</v>
+        <v>2.69681239128113</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G639" t="n">
-        <v>2.4908390045166</v>
+        <v>2.49083924293518</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.28600001335144</v>
       </c>
       <c r="G640" t="n">
-        <v>2.62336444854736</v>
+        <v>2.62336468696594</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>2.62655806541443</v>
+        <v>2.62655782699585</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G643" t="n">
-        <v>2.65689516067505</v>
+        <v>2.65689539909363</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G646" t="n">
-        <v>2.68004751205444</v>
+        <v>2.68004703521729</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G647" t="n">
-        <v>2.70639276504517</v>
+        <v>2.70639252662659</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G651" t="n">
-        <v>2.81017780303955</v>
+        <v>2.81017732620239</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G652" t="n">
-        <v>2.83253145217896</v>
+        <v>2.83253121376038</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.60700011253357</v>
       </c>
       <c r="G656" t="n">
-        <v>2.87963390350342</v>
+        <v>2.87963366508484</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G658" t="n">
-        <v>2.87005352973938</v>
+        <v>2.87005376815796</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>3.58699989318848</v>
       </c>
       <c r="G659" t="n">
-        <v>2.86366653442383</v>
+        <v>2.86366677284241</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.59699988365173</v>
       </c>
       <c r="G660" t="n">
-        <v>2.87164998054504</v>
+        <v>2.87165021896362</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3.52699995040894</v>
       </c>
       <c r="G663" t="n">
-        <v>2.81576633453369</v>
+        <v>2.81576585769653</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.57699990272522</v>
       </c>
       <c r="G665" t="n">
-        <v>2.85568356513977</v>
+        <v>2.85568284988403</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G668" t="n">
-        <v>3.05127835273743</v>
+        <v>3.05127811431885</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G669" t="n">
-        <v>3.30116081237793</v>
+        <v>3.30116057395935</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>3.21733427047729</v>
+        <v>3.21733403205872</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G671" t="n">
-        <v>3.21094703674316</v>
+        <v>3.21094727516174</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.20699977874756</v>
       </c>
       <c r="G674" t="n">
-        <v>3.35864114761353</v>
+        <v>3.35864067077637</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G676" t="n">
-        <v>3.47919106483459</v>
+        <v>3.47919154167175</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G677" t="n">
-        <v>3.38498616218567</v>
+        <v>3.38498640060425</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G678" t="n">
-        <v>3.36502861976624</v>
+        <v>3.36502838134766</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G679" t="n">
-        <v>3.07762384414673</v>
+        <v>3.07762360572815</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G680" t="n">
-        <v>3.11354947090149</v>
+        <v>3.11354923248291</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.99300003051758</v>
       </c>
       <c r="G682" t="n">
-        <v>3.18779516220093</v>
+        <v>3.18779540061951</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4</v>
       </c>
       <c r="G683" t="n">
-        <v>3.19338345527649</v>
+        <v>3.19338369369507</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G684" t="n">
-        <v>3.14069271087646</v>
+        <v>3.14069294929504</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.11354947090149</v>
+        <v>3.11354923248291</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.01100015640259</v>
       </c>
       <c r="G687" t="n">
-        <v>3.2021656036377</v>
+        <v>3.20216536521912</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G688" t="n">
-        <v>3.04010128974915</v>
+        <v>3.04010152816772</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>3.04010128974915</v>
+        <v>3.04010152816772</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G692" t="n">
-        <v>3.01375579833984</v>
+        <v>3.01375603675842</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G693" t="n">
-        <v>2.937912940979</v>
+        <v>2.93791317939758</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G694" t="n">
-        <v>3.05447125434875</v>
+        <v>3.05447149276733</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G695" t="n">
-        <v>2.96505689620972</v>
+        <v>2.96505641937256</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.64100003242493</v>
       </c>
       <c r="G699" t="n">
-        <v>2.90677738189697</v>
+        <v>2.90677762031555</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G700" t="n">
-        <v>2.96585512161255</v>
+        <v>2.96585488319397</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G701" t="n">
-        <v>3.02094078063965</v>
+        <v>3.02094054222107</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G702" t="n">
-        <v>2.96026635169983</v>
+        <v>2.96026659011841</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>3.76900005340576</v>
       </c>
       <c r="G705" t="n">
-        <v>3.00896596908569</v>
+        <v>3.00896549224854</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>3.76699995994568</v>
       </c>
       <c r="G708" t="n">
-        <v>3.00736880302429</v>
+        <v>3.00736927986145</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>3.61899995803833</v>
       </c>
       <c r="G710" t="n">
-        <v>2.8892138004303</v>
+        <v>2.88921403884888</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.46399998664856</v>
       </c>
       <c r="G716" t="n">
-        <v>2.76547002792358</v>
+        <v>2.76547026634216</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G722" t="n">
-        <v>2.96825003623962</v>
+        <v>2.96825051307678</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G723" t="n">
-        <v>2.996990442276</v>
+        <v>2.99699068069458</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>3.71900010108948</v>
       </c>
       <c r="G725" t="n">
-        <v>2.96904873847961</v>
+        <v>2.96904850006104</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>3.71900010108948</v>
       </c>
       <c r="G726" t="n">
-        <v>2.96904873847961</v>
+        <v>2.96904850006104</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>3.73300004005432</v>
       </c>
       <c r="G728" t="n">
-        <v>2.98022556304932</v>
+        <v>2.98022532463074</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G730" t="n">
-        <v>2.85488486289978</v>
+        <v>2.85488510131836</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.69899988174438</v>
       </c>
       <c r="G731" t="n">
-        <v>2.95308113098145</v>
+        <v>2.95308136940002</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>3.66100001335144</v>
       </c>
       <c r="G732" t="n">
-        <v>2.9227442741394</v>
+        <v>2.92274451255798</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G733" t="n">
-        <v>2.95068621635437</v>
+        <v>2.95068669319153</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>2.96186327934265</v>
+        <v>2.96186351776123</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G738" t="n">
-        <v>2.87085175514221</v>
+        <v>2.87085199356079</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G742" t="n">
-        <v>3.04489135742188</v>
+        <v>3.04489088058472</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G744" t="n">
-        <v>3.11354947090149</v>
+        <v>3.11354923248291</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>3.88100004196167</v>
       </c>
       <c r="G745" t="n">
-        <v>3.09838056564331</v>
+        <v>3.09838032722473</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G746" t="n">
-        <v>3.08321189880371</v>
+        <v>3.08321166038513</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G748" t="n">
-        <v>3.07762384414673</v>
+        <v>3.07762360572815</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>3.94799995422363</v>
       </c>
       <c r="G749" t="n">
-        <v>3.15186977386475</v>
+        <v>3.15186953544617</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.75699996948242</v>
       </c>
       <c r="G751" t="n">
-        <v>2.99938535690308</v>
+        <v>2.99938559532166</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G752" t="n">
-        <v>2.98741054534912</v>
+        <v>2.98741030693054</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>3.81900000572205</v>
       </c>
       <c r="G753" t="n">
-        <v>3.04888296127319</v>
+        <v>3.04888319969177</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G756" t="n">
-        <v>3.01774764060974</v>
+        <v>3.01774740219116</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.58299994468689</v>
       </c>
       <c r="G759" t="n">
-        <v>2.86047315597534</v>
+        <v>2.8604736328125</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.53299999237061</v>
       </c>
       <c r="G760" t="n">
-        <v>2.82055592536926</v>
+        <v>2.82055616378784</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G762" t="n">
-        <v>3.07762384414673</v>
+        <v>3.07762360572815</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.82699990272522</v>
       </c>
       <c r="G763" t="n">
-        <v>3.05526995658875</v>
+        <v>3.05526947975159</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G766" t="n">
-        <v>3.1167426109314</v>
+        <v>3.11674237251282</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G767" t="n">
-        <v>3.06564831733704</v>
+        <v>3.06564807891846</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.68899989128113</v>
       </c>
       <c r="G773" t="n">
-        <v>2.94509792327881</v>
+        <v>2.94509816169739</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G775" t="n">
-        <v>3.2812020778656</v>
+        <v>3.28120183944702</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.94300007820129</v>
       </c>
       <c r="G776" t="n">
-        <v>3.14787817001343</v>
+        <v>3.14787793159485</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G778" t="n">
-        <v>2.79261374473572</v>
+        <v>2.7926139831543</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G780" t="n">
-        <v>2.85807824134827</v>
+        <v>2.85807847976685</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G783" t="n">
-        <v>2.96505689620972</v>
+        <v>2.96505641937256</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.71900010108948</v>
       </c>
       <c r="G784" t="n">
-        <v>2.96904873847961</v>
+        <v>2.96904850006104</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.69099998474121</v>
       </c>
       <c r="G785" t="n">
-        <v>2.94669485092163</v>
+        <v>2.94669461250305</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G786" t="n">
-        <v>3.36582636833191</v>
+        <v>3.36582612991333</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4</v>
       </c>
       <c r="G789" t="n">
-        <v>3.19338345527649</v>
+        <v>3.19338369369507</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.22900009155273</v>
       </c>
       <c r="G791" t="n">
-        <v>3.37620496749878</v>
+        <v>3.37620520591736</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G794" t="n">
-        <v>3.34666562080383</v>
+        <v>3.34666609764099</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G796" t="n">
-        <v>3.31792545318604</v>
+        <v>3.31792569160461</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G797" t="n">
-        <v>3.40734028816223</v>
+        <v>3.40734052658081</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G799" t="n">
-        <v>3.54146289825439</v>
+        <v>3.54146265983582</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.5</v>
       </c>
       <c r="G801" t="n">
-        <v>3.59255623817444</v>
+        <v>3.5925567150116</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.50099992752075</v>
       </c>
       <c r="G802" t="n">
-        <v>3.59335517883301</v>
+        <v>3.59335494041443</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.38100004196167</v>
       </c>
       <c r="G803" t="n">
-        <v>3.49755358695984</v>
+        <v>3.49755311012268</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G805" t="n">
-        <v>3.60213708877563</v>
+        <v>3.6021363735199</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>3.55663084983826</v>
+        <v>3.55663132667542</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.45900011062622</v>
       </c>
       <c r="G807" t="n">
-        <v>3.55982398986816</v>
+        <v>3.5598247051239</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.55299997329712</v>
       </c>
       <c r="G808" t="n">
-        <v>3.63486886024475</v>
+        <v>3.63486862182617</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.39699983596802</v>
       </c>
       <c r="G809" t="n">
-        <v>3.51032662391663</v>
+        <v>3.51032733917236</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.48899984359741</v>
       </c>
       <c r="G811" t="n">
-        <v>3.58377480506897</v>
+        <v>3.58377456665039</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G812" t="n">
-        <v>3.51272225379944</v>
+        <v>3.5127215385437</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G813" t="n">
-        <v>3.57259821891785</v>
+        <v>3.57259798049927</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G814" t="n">
-        <v>3.73945212364197</v>
+        <v>3.73945236206055</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G815" t="n">
-        <v>3.50793194770813</v>
+        <v>3.50793218612671</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>3.45683741569519</v>
+        <v>3.45683789253235</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.35099983215332</v>
       </c>
       <c r="G817" t="n">
-        <v>3.47360277175903</v>
+        <v>3.47360301017761</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.40299987792969</v>
       </c>
       <c r="G818" t="n">
-        <v>3.51511716842651</v>
+        <v>3.51511669158936</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G819" t="n">
-        <v>3.60453176498413</v>
+        <v>3.60453200340271</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>3.56062269210815</v>
+        <v>3.56062245368958</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.43300008773804</v>
       </c>
       <c r="G821" t="n">
-        <v>3.53906726837158</v>
+        <v>3.53906750679016</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.35900020599365</v>
       </c>
       <c r="G822" t="n">
-        <v>3.47999000549316</v>
+        <v>3.47999024391174</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G823" t="n">
-        <v>3.42330741882324</v>
+        <v>3.42330718040466</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>3.5446560382843</v>
+        <v>3.54465579986572</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G826" t="n">
-        <v>3.54944562911987</v>
+        <v>3.54944586753845</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G828" t="n">
-        <v>3.62129640579224</v>
+        <v>3.62129712104797</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G829" t="n">
-        <v>3.58297657966614</v>
+        <v>3.58297610282898</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G830" t="n">
-        <v>3.5446560382843</v>
+        <v>3.54465579986572</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G831" t="n">
-        <v>3.46322417259216</v>
+        <v>3.46322464942932</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G833" t="n">
-        <v>3.50793194770813</v>
+        <v>3.50793218612671</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.47900009155273</v>
       </c>
       <c r="G834" t="n">
-        <v>3.57579112052917</v>
+        <v>3.57579135894775</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.43100023269653</v>
       </c>
       <c r="G835" t="n">
-        <v>3.53747081756592</v>
+        <v>3.53747057914734</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.29099988937378</v>
       </c>
       <c r="G836" t="n">
-        <v>3.42570233345032</v>
+        <v>3.42570209503174</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.19399976730347</v>
       </c>
       <c r="G837" t="n">
-        <v>3.34826278686523</v>
+        <v>3.34826254844666</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G838" t="n">
-        <v>3.44885420799255</v>
+        <v>3.44885444641113</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G841" t="n">
-        <v>3.44087100028992</v>
+        <v>3.44087076187134</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.3730001449585</v>
       </c>
       <c r="G843" t="n">
-        <v>3.49116683006287</v>
+        <v>3.49116706848145</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G845" t="n">
-        <v>3.72029185295105</v>
+        <v>3.72029137611389</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.67600011825562</v>
       </c>
       <c r="G846" t="n">
-        <v>3.73306608200073</v>
+        <v>3.73306560516357</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.72300004959106</v>
       </c>
       <c r="G847" t="n">
-        <v>3.770587682724</v>
+        <v>3.77058720588684</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.69299983978271</v>
       </c>
       <c r="G848" t="n">
-        <v>3.74663710594177</v>
+        <v>3.74663758277893</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G849" t="n">
-        <v>3.71630096435547</v>
+        <v>3.71630024909973</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G850" t="n">
-        <v>3.73226714134216</v>
+        <v>3.73226737976074</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.68100023269653</v>
       </c>
       <c r="G851" t="n">
-        <v>3.73705744743347</v>
+        <v>3.73705697059631</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>3.78815150260925</v>
+        <v>3.78815126419067</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>3.76420140266418</v>
+        <v>3.76420116424561</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G854" t="n">
-        <v>3.68995523452759</v>
+        <v>3.68995499610901</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.60099983215332</v>
       </c>
       <c r="G855" t="n">
-        <v>3.67318916320801</v>
+        <v>3.67318940162659</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>3.75861287117004</v>
+        <v>3.75861310958862</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>3.90790367126465</v>
+        <v>3.90790271759033</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.77099990844727</v>
       </c>
       <c r="G858" t="n">
-        <v>3.80890846252441</v>
+        <v>3.80890822410583</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.81400012969971</v>
       </c>
       <c r="G859" t="n">
-        <v>3.84323740005493</v>
+        <v>3.84323716163635</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G861" t="n">
-        <v>3.81210160255432</v>
+        <v>3.81210207939148</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G862" t="n">
-        <v>3.86399364471436</v>
+        <v>3.86399412155151</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G863" t="n">
-        <v>3.86080121994019</v>
+        <v>3.86080074310303</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G864" t="n">
-        <v>3.89592862129211</v>
+        <v>3.89592838287354</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.75</v>
       </c>
       <c r="G866" t="n">
-        <v>3.79214310646057</v>
+        <v>3.79214358329773</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.9689998626709</v>
       </c>
       <c r="G867" t="n">
-        <v>3.96698069572449</v>
+        <v>3.96698093414307</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G868" t="n">
-        <v>3.95340943336487</v>
+        <v>3.95340919494629</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G870" t="n">
-        <v>3.91508769989014</v>
+        <v>3.91508841514587</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.90299987792969</v>
       </c>
       <c r="G871" t="n">
-        <v>3.9142894744873</v>
+        <v>3.91429018974304</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G873" t="n">
-        <v>3.9126935005188</v>
+        <v>3.91269373893738</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5</v>
       </c>
       <c r="G874" t="n">
-        <v>3.99172949790955</v>
+        <v>3.9917299747467</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G875" t="n">
-        <v>4.04441976547241</v>
+        <v>4.04442024230957</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.93599987030029</v>
       </c>
       <c r="G878" t="n">
-        <v>3.94063520431519</v>
+        <v>3.94063496589661</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G879" t="n">
-        <v>3.94622397422791</v>
+        <v>3.94622373580933</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>5.00799989700317</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99811625480652</v>
+        <v>3.99811553955078</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G881" t="n">
-        <v>3.96777892112732</v>
+        <v>3.9677791595459</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G882" t="n">
-        <v>4.00769662857056</v>
+        <v>4.0076961517334</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G883" t="n">
-        <v>4.14022159576416</v>
+        <v>4.14022207260132</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>5.02799987792969</v>
       </c>
       <c r="G886" t="n">
-        <v>4.01408290863037</v>
+        <v>4.01408338546753</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G888" t="n">
-        <v>3.99013328552246</v>
+        <v>3.9901328086853</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.9060001373291</v>
       </c>
       <c r="G889" t="n">
-        <v>3.91668462753296</v>
+        <v>3.9166853427887</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.94399976730347</v>
       </c>
       <c r="G890" t="n">
-        <v>3.94702219963074</v>
+        <v>3.94702172279358</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G891" t="n">
-        <v>3.92786192893982</v>
+        <v>3.92786145210266</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.9210000038147</v>
       </c>
       <c r="G892" t="n">
-        <v>3.92866063117981</v>
+        <v>3.92866015434265</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G893" t="n">
-        <v>3.92626547813416</v>
+        <v>3.92626452445984</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G894" t="n">
-        <v>3.9997136592865</v>
+        <v>3.99971342086792</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G895" t="n">
-        <v>3.95740079879761</v>
+        <v>3.95740032196045</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G897" t="n">
-        <v>3.9126935005188</v>
+        <v>3.91269373893738</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.96299982070923</v>
       </c>
       <c r="G898" t="n">
-        <v>3.96219062805176</v>
+        <v>3.96219038963318</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G901" t="n">
-        <v>3.94542527198792</v>
+        <v>3.94542551040649</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.79699993133545</v>
       </c>
       <c r="G902" t="n">
-        <v>3.82966542243958</v>
+        <v>3.829665184021</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G903" t="n">
-        <v>3.75701522827148</v>
+        <v>3.75701546669006</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.67700004577637</v>
       </c>
       <c r="G904" t="n">
-        <v>3.73386335372925</v>
+        <v>3.73386383056641</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G906" t="n">
-        <v>3.67638278007507</v>
+        <v>3.67638301849365</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G907" t="n">
-        <v>3.68436574935913</v>
+        <v>3.68436622619629</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G908" t="n">
-        <v>3.69155216217041</v>
+        <v>3.69155120849609</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.66099977493286</v>
       </c>
       <c r="G909" t="n">
-        <v>3.72109031677246</v>
+        <v>3.72109007835388</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G910" t="n">
-        <v>3.71630096435547</v>
+        <v>3.71630024909973</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.71299982070923</v>
       </c>
       <c r="G913" t="n">
-        <v>3.76260423660278</v>
+        <v>3.76260375976562</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>3.73945212364197</v>
+        <v>3.73945236206055</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G916" t="n">
-        <v>3.79533624649048</v>
+        <v>3.79533672332764</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>3.72029185295105</v>
+        <v>3.72029137611389</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.67700004577637</v>
       </c>
       <c r="G918" t="n">
-        <v>3.73386335372925</v>
+        <v>3.73386383056641</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G919" t="n">
-        <v>3.74823427200317</v>
+        <v>3.74823403358459</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G920" t="n">
-        <v>3.76499891281128</v>
+        <v>3.76499938964844</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G921" t="n">
-        <v>3.79054665565491</v>
+        <v>3.79054641723633</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.72900009155273</v>
       </c>
       <c r="G922" t="n">
-        <v>3.77537775039673</v>
+        <v>3.77537822723389</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.85200023651123</v>
       </c>
       <c r="G923" t="n">
-        <v>3.87357449531555</v>
+        <v>3.87357473373413</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G924" t="n">
-        <v>3.86399364471436</v>
+        <v>3.86399412155151</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.85699987411499</v>
       </c>
       <c r="G925" t="n">
-        <v>3.87756609916687</v>
+        <v>3.87756586074829</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G927" t="n">
-        <v>3.97097277641296</v>
+        <v>3.97097229957581</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G929" t="n">
-        <v>4.07635450363159</v>
+        <v>4.07635402679443</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.20599985122681</v>
       </c>
       <c r="G930" t="n">
-        <v>4.15618896484375</v>
+        <v>4.15618801116943</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>5.17799997329712</v>
       </c>
       <c r="G931" t="n">
-        <v>4.13383531570435</v>
+        <v>4.13383483886719</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>5.16599988937378</v>
       </c>
       <c r="G937" t="n">
-        <v>4.12425518035889</v>
+        <v>4.12425470352173</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>4.02366352081299</v>
+        <v>4.02366399765015</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>5.03399991989136</v>
       </c>
       <c r="G943" t="n">
-        <v>4.08369398117065</v>
+        <v>4.0836935043335</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.98299980163574</v>
       </c>
       <c r="G946" t="n">
-        <v>4.042320728302</v>
+        <v>4.04232120513916</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G947" t="n">
-        <v>3.97174501419067</v>
+        <v>3.97174525260925</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.9229998588562</v>
       </c>
       <c r="G948" t="n">
-        <v>3.99364829063416</v>
+        <v>3.99364805221558</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G949" t="n">
-        <v>4.00338268280029</v>
+        <v>4.00338315963745</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.93900012969971</v>
       </c>
       <c r="G951" t="n">
-        <v>4.00662803649902</v>
+        <v>4.00662755966187</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.86899995803833</v>
       </c>
       <c r="G953" t="n">
-        <v>3.94984221458435</v>
+        <v>3.94984197616577</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.93100023269653</v>
       </c>
       <c r="G955" t="n">
-        <v>4.00013780593872</v>
+        <v>4.00013828277588</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G957" t="n">
-        <v>3.99608182907104</v>
+        <v>3.99608206748962</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G958" t="n">
-        <v>3.94254088401794</v>
+        <v>3.94254112243652</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G959" t="n">
-        <v>3.96850061416626</v>
+        <v>3.96849989891052</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.96099996566772</v>
       </c>
       <c r="G963" t="n">
-        <v>4.02447414398193</v>
+        <v>4.02447462081909</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>5.07600021362305</v>
       </c>
       <c r="G967" t="n">
-        <v>4.1177659034729</v>
+        <v>4.11776494979858</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G969" t="n">
-        <v>4.13561201095581</v>
+        <v>4.13561248779297</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G970" t="n">
-        <v>4.16968297958374</v>
+        <v>4.1696834564209</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G971" t="n">
-        <v>4.10640811920166</v>
+        <v>4.1064076423645</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G973" t="n">
-        <v>4.12263202667236</v>
+        <v>4.12263250350952</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G974" t="n">
-        <v>4.42116212844849</v>
+        <v>4.42116260528564</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G975" t="n">
-        <v>4.38546848297119</v>
+        <v>4.38546895980835</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>5.44600009918213</v>
       </c>
       <c r="G979" t="n">
-        <v>4.41791725158691</v>
+        <v>4.41791772842407</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G980" t="n">
-        <v>4.40007066726685</v>
+        <v>4.40007019042969</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>5.31400012969971</v>
       </c>
       <c r="G981" t="n">
-        <v>4.31083583831787</v>
+        <v>4.31083679199219</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G982" t="n">
-        <v>4.35788726806641</v>
+        <v>4.35788679122925</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G984" t="n">
-        <v>4.20699977874756</v>
+        <v>4.20700025558472</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G986" t="n">
-        <v>4.21024417877197</v>
+        <v>4.21024465560913</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.14799976348877</v>
       </c>
       <c r="G990" t="n">
-        <v>4.17617273330688</v>
+        <v>4.17617321014404</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G991" t="n">
-        <v>4.11614274978638</v>
+        <v>4.11614227294922</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G992" t="n">
-        <v>4.17292785644531</v>
+        <v>4.17292881011963</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>5.15399980545044</v>
       </c>
       <c r="G996" t="n">
-        <v>4.18104028701782</v>
+        <v>4.18104076385498</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>5.14599990844727</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.17455101013184</v>
+        <v>4.17455053329468</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.12263202667236</v>
+        <v>4.12263250350952</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.19564199447632</v>
+        <v>4.19564247131348</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.26702976226807</v>
+        <v>4.26703071594238</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.15994882583618</v>
+        <v>4.15994834899902</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.13074493408203</v>
+        <v>4.13074445724487</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.05205631256104</v>
+        <v>4.05205583572388</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.98699998855591</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.04556655883789</v>
+        <v>4.04556608200073</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>5.03599977493286</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.08531618118286</v>
+        <v>4.0853157043457</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.10478544235229</v>
+        <v>4.10478591918945</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.06422472000122</v>
+        <v>4.06422519683838</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.11614274978638</v>
+        <v>4.11614227294922</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.10478544235229</v>
+        <v>4.10478591918945</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.31894826889038</v>
+        <v>4.31894874572754</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.33192825317383</v>
+        <v>4.33192729949951</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.38546848297119</v>
+        <v>4.38546895980835</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.42765188217163</v>
+        <v>4.42765235900879</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.46659088134766</v>
+        <v>4.4665904045105</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.51364231109619</v>
+        <v>4.51364183425903</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.69860029220581</v>
+        <v>4.69860076904297</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.73916149139404</v>
+        <v>4.7391619682312</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>5.84600019454956</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.74240636825562</v>
+        <v>4.74240684509277</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.68399858474731</v>
+        <v>4.68399906158447</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.7537636756897</v>
+        <v>4.75376415252686</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>5.78200006484985</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.6904878616333</v>
+        <v>4.69048833847046</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.6596622467041</v>
+        <v>4.65966176986694</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G1054" t="n">
-        <v>4.43089723587036</v>
+        <v>4.4308967590332</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>5.40399980545044</v>
       </c>
       <c r="G1055" t="n">
-        <v>4.38384580612183</v>
+        <v>4.38384628295898</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G1056" t="n">
-        <v>4.40331506729126</v>
+        <v>4.40331554412842</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1057" t="n">
-        <v>4.52824401855469</v>
+        <v>4.52824354171753</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>4.4941725730896</v>
+        <v>4.49417209625244</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1060" t="n">
-        <v>4.66128349304199</v>
+        <v>4.66128444671631</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.84299755096436</v>
+        <v>4.84299802780151</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>5.94399976730347</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.82190561294556</v>
+        <v>4.82190608978271</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.84299755096436</v>
+        <v>4.84299802780151</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.85110998153687</v>
+        <v>4.85111045837402</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>5.87400007247925</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.76512050628662</v>
+        <v>4.76512098312378</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>5.95599985122681</v>
       </c>
       <c r="G1071" t="n">
-        <v>4.83164119720459</v>
+        <v>4.83164072036743</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>6.09600019454956</v>
       </c>
       <c r="G1073" t="n">
-        <v>4.94521284103394</v>
+        <v>4.94521236419678</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G1075" t="n">
-        <v>4.94845724105835</v>
+        <v>4.94845676422119</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>6.10799980163574</v>
       </c>
       <c r="G1077" t="n">
-        <v>4.95494651794434</v>
+        <v>4.95494699478149</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>6.15199995040894</v>
       </c>
       <c r="G1078" t="n">
-        <v>4.99064016342163</v>
+        <v>4.99064111709595</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>6.5</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.27294540405273</v>
+        <v>5.27294635772705</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>6.42600011825562</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.21291494369507</v>
+        <v>5.21291589736938</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.28917074203491</v>
+        <v>5.2891697883606</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6.58400011062622</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.34108877182007</v>
+        <v>5.34108924865723</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>6.67600011825562</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.41572141647339</v>
+        <v>5.41572093963623</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.31350708007812</v>
+        <v>5.31350660324097</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>6.56799983978271</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.32810926437378</v>
+        <v>5.32810878753662</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.02957963943481</v>
+        <v>5.02957916259766</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>6.28599977493286</v>
       </c>
       <c r="G1096" t="n">
-        <v>5.09934425354004</v>
+        <v>5.09934377670288</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>6.32200002670288</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.12854814529419</v>
+        <v>5.12854862213135</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>6.24599981307983</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.06689548492432</v>
+        <v>5.06689500808716</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.89978361129761</v>
+        <v>4.89978313446045</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>6.13199996948242</v>
       </c>
       <c r="G1104" t="n">
-        <v>4.97441625595093</v>
+        <v>4.97441577911377</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>6.11800003051758</v>
       </c>
       <c r="G1105" t="n">
-        <v>4.96305894851685</v>
+        <v>4.96305847167969</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G1108" t="n">
-        <v>4.7488956451416</v>
+        <v>4.74889612197876</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>5.9980001449585</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.86571168899536</v>
+        <v>4.86571216583252</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G1110" t="n">
-        <v>4.76025342941284</v>
+        <v>4.76025295257568</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>5.75799989700317</v>
       </c>
       <c r="G1112" t="n">
-        <v>4.67101907730103</v>
+        <v>4.67101860046387</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>5.61199998855591</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.55257987976074</v>
+        <v>4.5525803565979</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>5.66200017929077</v>
       </c>
       <c r="G1114" t="n">
-        <v>4.59314107894897</v>
+        <v>4.59314203262329</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>5.65199995040894</v>
       </c>
       <c r="G1115" t="n">
-        <v>4.58502912521362</v>
+        <v>4.58502960205078</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>5.06400012969971</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.10803031921387</v>
+        <v>4.10803079605103</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.21024417877197</v>
+        <v>4.21024465560913</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G1118" t="n">
-        <v>4.0098729133606</v>
+        <v>4.00987195968628</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.82247996330261</v>
+        <v>3.82248020172119</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>4.32600021362305</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.50934886932373</v>
+        <v>3.50934839248657</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.50772571563721</v>
+        <v>3.50772595405579</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>4.67799997329712</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.79489850997925</v>
+        <v>3.79489874839783</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.67402601242065</v>
+        <v>3.67402648925781</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>4.66099977493286</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.7811074256897</v>
+        <v>3.78110814094543</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>4.6710000038147</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.78922009468079</v>
+        <v>3.78922033309937</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>4.84700012207031</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.9319953918457</v>
+        <v>3.93199515342712</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.93767404556274</v>
+        <v>3.93767380714417</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.9311842918396</v>
+        <v>3.93118405342102</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.89386796951294</v>
+        <v>3.89386773109436</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>4.93100023269653</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.00013780593872</v>
+        <v>4.00013828277588</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>4.9060001373291</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.9798572063446</v>
+        <v>3.97985744476318</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>4.8769998550415</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.9563319683075</v>
+        <v>3.95633172988892</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.89548993110657</v>
+        <v>3.89549040794373</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.59209299087524</v>
+        <v>3.59209275245667</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.6066951751709</v>
+        <v>3.60669493675232</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>4.52099990844727</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.66753649711609</v>
+        <v>3.66753673553467</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>4.54300022125244</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.68538355827332</v>
+        <v>3.68538379669189</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.73567938804626</v>
+        <v>3.73567962646484</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.85817408561707</v>
+        <v>3.85817384719849</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>4.88100004196167</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.95957636833191</v>
+        <v>3.95957684516907</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>4.69600009918213</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.8095006942749</v>
+        <v>3.80950045585632</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>4.5770001411438</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.71296548843384</v>
+        <v>3.71296525001526</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.85006141662598</v>
+        <v>3.85006165504456</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>4.61700010299683</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.74541425704956</v>
+        <v>3.74541449546814</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.71215415000916</v>
+        <v>3.712153673172</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>4.56799983978271</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.70566368103027</v>
+        <v>3.70566391944885</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>4.63899993896484</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.76326131820679</v>
+        <v>3.76326060295105</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.75</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.85330677032471</v>
+        <v>3.85330700874329</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.81761288642883</v>
+        <v>3.81761264801025</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>4.68699979782104</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.8021993637085</v>
+        <v>3.80219960212708</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.71134257316589</v>
+        <v>3.71134281158447</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.68781733512878</v>
+        <v>3.68781709671021</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>4.51399993896484</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.66185784339905</v>
+        <v>3.66185808181763</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>4.51100015640259</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.79477190971375</v>
+        <v>3.79477214813232</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>4.40100002288818</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.70223689079285</v>
+        <v>3.70223712921143</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>4.42899990081787</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.72579145431519</v>
+        <v>3.72579121589661</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.85449886322021</v>
+        <v>3.85449910163879</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.86543488502502</v>
+        <v>3.86543440818787</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>4.66699981689453</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.92600321769714</v>
+        <v>3.92600297927856</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.87132358551025</v>
+        <v>3.87132334709167</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.92768573760986</v>
+        <v>3.92768549919128</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.84860968589783</v>
+        <v>3.84861040115356</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.80402517318726</v>
+        <v>3.80402565002441</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.74177479743958</v>
+        <v>3.741774559021</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.42379117012024</v>
+        <v>3.42379140853882</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.21299982070923</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.54408621788025</v>
+        <v>3.54408645629883</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.3901424407959</v>
+        <v>3.39014220237732</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.56848216056824</v>
+        <v>3.56848192214966</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.53483295440674</v>
+        <v>3.5348334312439</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.3363037109375</v>
+        <v>3.33630347251892</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.41117286682129</v>
+        <v>3.41117262840271</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.4019193649292</v>
+        <v>3.40191960334778</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>4.08300018310547</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.43472743034363</v>
+        <v>3.43472719192505</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.93700003623962</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.31190800666809</v>
+        <v>3.31190824508667</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>4.07100009918213</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.42463254928589</v>
+        <v>3.42463231086731</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.33125638961792</v>
+        <v>3.33125615119934</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.875</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.25975203514099</v>
+        <v>3.25975227355957</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>4.09100008010864</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.44145679473877</v>
+        <v>3.44145727157593</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.49950170516968</v>
+        <v>3.4995014667511</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>4.16900014877319</v>
       </c>
       <c r="G1218" t="n">
-        <v>3.50707268714905</v>
+        <v>3.50707244873047</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.11700010299683</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.46332907676697</v>
+        <v>3.46332883834839</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>4.02299976348877</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.38425326347351</v>
+        <v>3.38425350189209</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.2959246635437</v>
+        <v>3.29592490196228</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.35649299621582</v>
+        <v>3.3564932346344</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>4.17700004577637</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.51380252838135</v>
+        <v>3.51380228996277</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1228" t="n">
-        <v>3.60044860839844</v>
+        <v>3.6004490852356</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.58025908470154</v>
+        <v>3.58025932312012</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.58194184303284</v>
+        <v>3.58194160461426</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.66774702072144</v>
+        <v>3.66774654388428</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.59624242782593</v>
+        <v>3.59624266624451</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.3901424407959</v>
+        <v>3.39014220237732</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.2706880569458</v>
+        <v>3.27068781852722</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.14113926887512</v>
+        <v>3.14113879203796</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G1245" t="n">
-        <v>3.08393573760986</v>
+        <v>3.08393549919128</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>3.70900011062622</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.12010836601257</v>
+        <v>3.12010860443115</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.14113926887512</v>
+        <v>3.14113879203796</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.23872137069702</v>
+        <v>3.23872113227844</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.07468247413635</v>
+        <v>3.07468223571777</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.16721725463867</v>
+        <v>3.16721701622009</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.7590000629425</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.16216969490051</v>
+        <v>3.16216993331909</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.29760718345642</v>
+        <v>3.297607421875</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>3.78099989891052</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.18067669868469</v>
+        <v>3.18067646026611</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.13609170913696</v>
+        <v>3.13609147071838</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.16637563705444</v>
+        <v>3.16637587547302</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G1261" t="n">
-        <v>3.17647051811218</v>
+        <v>3.17647075653076</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.15964603424072</v>
+        <v>3.1596462726593</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G1263" t="n">
-        <v>3.0469217300415</v>
+        <v>3.04692196846008</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.87867665290833</v>
+        <v>2.87867641448975</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.75080990791321</v>
+        <v>2.75081014633179</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.82652020454407</v>
+        <v>2.82652044296265</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.82652020454407</v>
+        <v>2.82652044296265</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.86858177185059</v>
+        <v>2.86858201026917</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>3.40400004386902</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.86353421211243</v>
+        <v>2.86353445053101</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>3.41899991035461</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.87615275382996</v>
+        <v>2.87615251541138</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>3.62299990653992</v>
       </c>
       <c r="G1281" t="n">
-        <v>3.04776310920715</v>
+        <v>3.04776287078857</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>3.56900000572205</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.00233674049377</v>
+        <v>3.0023365020752</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.95775198936462</v>
+        <v>2.95775175094604</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.11085510253906</v>
+        <v>3.11085486412048</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>3.84100008010864</v>
       </c>
       <c r="G1288" t="n">
-        <v>3.23115038871765</v>
+        <v>3.23115015029907</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.2118022441864</v>
+        <v>3.21180200576782</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1296" t="n">
-        <v>3.38593578338623</v>
+        <v>3.38593602180481</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>4.04099988937378</v>
       </c>
       <c r="G1297" t="n">
-        <v>3.39939522743225</v>
+        <v>3.39939546585083</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>4.13299989700317</v>
       </c>
       <c r="G1298" t="n">
-        <v>3.47678852081299</v>
+        <v>3.47678804397583</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.47931218147278</v>
+        <v>3.47931241989136</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.5112783908844</v>
+        <v>3.51127862930298</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.4658522605896</v>
+        <v>3.46585249900818</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.4288387298584</v>
+        <v>3.42883896827698</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G1304" t="n">
-        <v>3.5062313079834</v>
+        <v>3.50623154640198</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.5011842250824</v>
+        <v>3.50118398666382</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.51969122886658</v>
+        <v>3.51969075202942</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>4.22300004959106</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.55249881744385</v>
+        <v>3.55249857902527</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.52642059326172</v>
+        <v>3.5264208316803</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>4.15399980545044</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.49445414543152</v>
+        <v>3.49445366859436</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.14300012588501</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.48520088195801</v>
+        <v>3.48520064353943</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.08799982070923</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.43893313407898</v>
+        <v>3.4389328956604</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.36658787727356</v>
+        <v>3.3665874004364</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>4.16900014877319</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.50707268714905</v>
+        <v>3.50707244873047</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>4.15100002288818</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.49193024635315</v>
+        <v>3.49193072319031</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>4.02899980545044</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.38930058479309</v>
+        <v>3.38930082321167</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.38593578338623</v>
+        <v>3.38593602180481</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.38677740097046</v>
+        <v>3.38677716255188</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>4.09299993515015</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.44313955307007</v>
+        <v>3.44313931465149</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.36827063560486</v>
+        <v>3.36827039718628</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>4.08900022506714</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.43977451324463</v>
+        <v>3.43977475166321</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>4.4229998588562</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.72074413299561</v>
+        <v>3.72074389457703</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>4.44099998474121</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.73588585853577</v>
+        <v>3.73588609695435</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G1338" t="n">
-        <v>3.82926249504089</v>
+        <v>3.82926273345947</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.82926249504089</v>
+        <v>3.82926273345947</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.87721228599548</v>
+        <v>3.8772120475769</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.90329027175903</v>
+        <v>3.90329003334045</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.97058796882629</v>
+        <v>3.97058820724487</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>4.60300016403198</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.87216520309448</v>
+        <v>3.8721649646759</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>4.56899976730347</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.84356307983398</v>
+        <v>3.84356260299683</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.90497279167175</v>
+        <v>3.90497303009033</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.85618209838867</v>
+        <v>3.85618185997009</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.82758045196533</v>
+        <v>3.82758021354675</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>4.58599996566772</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.85786414146423</v>
+        <v>3.85786366462708</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.85618209838867</v>
+        <v>3.85618185997009</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>4.75899982452393</v>
       </c>
       <c r="G1359" t="n">
-        <v>4.00339603424072</v>
+        <v>4.00339651107788</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.91590881347656</v>
+        <v>3.9159083366394</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.95208120346069</v>
+        <v>3.95208144187927</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.83767437934875</v>
+        <v>3.83767461776733</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.9091784954071</v>
+        <v>3.90917873382568</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.95376372337341</v>
+        <v>3.95376348495483</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.11359691619873</v>
+        <v>4.11359643936157</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>4.76700019836426</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.01012659072876</v>
+        <v>4.0101261138916</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>4.88299989700317</v>
       </c>
       <c r="G1374" t="n">
-        <v>4.10770797729492</v>
+        <v>4.10770750045776</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.05639314651489</v>
+        <v>4.05639362335205</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>4.89099979400635</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.1144380569458</v>
+        <v>4.11443758010864</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G1382" t="n">
-        <v>4.07574129104614</v>
+        <v>4.0757417678833</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.74900007247925</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.99498391151428</v>
+        <v>3.9949836730957</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>4.50299978256226</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.78804183006287</v>
+        <v>3.78804206848145</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.86627650260925</v>
+        <v>3.86627674102783</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.669429063797</v>
+        <v>3.66942930221558</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.73672747612</v>
+        <v>3.73672723770142</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.68961882591248</v>
+        <v>3.68961834907532</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.79561328887939</v>
+        <v>3.79561305046082</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.75607538223267</v>
+        <v>3.75607562065125</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>4.45699977874756</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.74934530258179</v>
+        <v>3.74934554100037</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>4.34899997711182</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.65849351882935</v>
+        <v>3.65849304199219</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.69634866714478</v>
+        <v>3.6963484287262</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.76448798179626</v>
+        <v>3.76448774337769</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>4.55900001525879</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.83515071868896</v>
+        <v>3.83515095710754</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>4.62599992752075</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.89151239395142</v>
+        <v>3.89151334762573</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.79056572914124</v>
+        <v>3.79056620597839</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.88141798973083</v>
+        <v>3.88141822814941</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.95208120346069</v>
+        <v>3.95208144187927</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.97563505172729</v>
+        <v>3.97563529014587</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1409" t="n">
-        <v>4.02442693710327</v>
+        <v>4.02442646026611</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.92768573760986</v>
+        <v>3.92768549919128</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.91843199729919</v>
+        <v>3.91843223571777</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>4.63899993896484</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.90244889259338</v>
+        <v>3.90244841575623</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.84860968589783</v>
+        <v>3.84861040115356</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>4.63700008392334</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.90076661109924</v>
+        <v>3.90076637268066</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.99245977401733</v>
+        <v>3.99246001243591</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.91843199729919</v>
+        <v>3.91843223571777</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.99414277076721</v>
+        <v>3.99414253234863</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>4.72100019454956</v>
       </c>
       <c r="G1419" t="n">
-        <v>3.97142934799194</v>
+        <v>3.9714298248291</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G1424" t="n">
-        <v>4.0235857963562</v>
+        <v>4.02358531951904</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>4.8289999961853</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.06228160858154</v>
+        <v>4.0622820854187</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>4.83099985122681</v>
       </c>
       <c r="G1427" t="n">
-        <v>4.06396389007568</v>
+        <v>4.06396436691284</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>4.88399982452393</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.10854959487915</v>
+        <v>4.10854911804199</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>4.58699989318848</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.85870504379272</v>
+        <v>3.8587052822113</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.87468862533569</v>
+        <v>3.87468838691711</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.83262705802917</v>
+        <v>3.83262729644775</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.82758045196533</v>
+        <v>3.82758021354675</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.70812559127808</v>
+        <v>3.70812582969666</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.87468862533569</v>
+        <v>3.87468838691711</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>4.58300018310547</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.85534048080444</v>
+        <v>3.85534024238586</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.82337379455566</v>
+        <v>3.82337403297424</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.83178567886353</v>
+        <v>3.8317859172821</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>4.56099987030029</v>
       </c>
       <c r="G1445" t="n">
-        <v>3.83683276176453</v>
+        <v>3.83683323860168</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>4.68100023269653</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.93778109550476</v>
+        <v>3.9377806186676</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.9091784954071</v>
+        <v>3.90917873382568</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>4.61899995803833</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.88562417030334</v>
+        <v>3.8856246471405</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.77710604667664</v>
+        <v>3.77710652351379</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.43300008773804</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.72915649414062</v>
+        <v>3.72915625572205</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.74345707893372</v>
+        <v>3.74345684051514</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.7030782699585</v>
+        <v>3.70307803153992</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.73504519462585</v>
+        <v>3.73504495620728</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.74345707893372</v>
+        <v>3.74345684051514</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.78131222724915</v>
+        <v>3.78131198883057</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.80570769309998</v>
+        <v>3.80570793151855</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>4.56400012969971</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.83935689926147</v>
+        <v>3.83935737609863</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>4.57100009918213</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.8452455997467</v>
+        <v>3.84524583816528</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.82085013389587</v>
+        <v>3.82084965705872</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>4.47599983215332</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.76532912254333</v>
+        <v>3.76532936096191</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.76364636421204</v>
+        <v>3.76364660263062</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>4.63700008392334</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.90076661109924</v>
+        <v>3.90076637268066</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.97058796882629</v>
+        <v>3.97058820724487</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.95544624328613</v>
+        <v>3.95544648170471</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.9091784954071</v>
+        <v>3.90917873382568</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.96890592575073</v>
+        <v>3.96890568733215</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.97058796882629</v>
+        <v>3.97058820724487</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>4.82399988174438</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.05807542800903</v>
+        <v>4.05807590484619</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.07153558731079</v>
+        <v>4.07153606414795</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.18869590759277</v>
+        <v>4.18869543075562</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G1478" t="n">
-        <v>4.15081644058228</v>
+        <v>4.15081691741943</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1481" t="n">
-        <v>4.27238178253174</v>
+        <v>4.27238082885742</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.29880809783936</v>
+        <v>4.29880905151367</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1483" t="n">
-        <v>4.27238178253174</v>
+        <v>4.27238082885742</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>4.76800012588501</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.20014715194702</v>
+        <v>4.20014762878418</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.07858324050903</v>
+        <v>4.07858228683472</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07065391540527</v>
+        <v>4.07065439224243</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>4.51399993896484</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.97639775276184</v>
+        <v>3.97639751434326</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>4.56899976730347</v>
       </c>
       <c r="G1492" t="n">
-        <v>4.02484750747681</v>
+        <v>4.02484703063965</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>4.55100011825562</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.00899124145508</v>
+        <v>4.00899171829224</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1494" t="n">
-        <v>4.00458669662476</v>
+        <v>4.0045862197876</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>4.51700019836426</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.97904062271118</v>
+        <v>3.97904086112976</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>4.50699996948242</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.97023153305054</v>
+        <v>3.97023129463196</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>4.49700021743774</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.96142268180847</v>
+        <v>3.96142244338989</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.99401617050171</v>
+        <v>3.99401593208313</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>4.58099985122681</v>
       </c>
       <c r="G1502" t="n">
-        <v>4.03541851043701</v>
+        <v>4.03541803359985</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>4.60699987411499</v>
       </c>
       <c r="G1503" t="n">
-        <v>4.05832147598267</v>
+        <v>4.05832195281982</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>4.73299980163574</v>
       </c>
       <c r="G1506" t="n">
-        <v>4.16931581497192</v>
+        <v>4.16931533813477</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1513" t="n">
-        <v>4.18252944946289</v>
+        <v>4.18252897262573</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>4.68900012969971</v>
       </c>
       <c r="G1515" t="n">
-        <v>4.13055658340454</v>
+        <v>4.13055610656738</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>4.85300016403198</v>
       </c>
       <c r="G1517" t="n">
-        <v>4.27502393722534</v>
+        <v>4.2750244140625</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G1518" t="n">
-        <v>4.26004886627197</v>
+        <v>4.26004934310913</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1523" t="n">
-        <v>4.01868104934692</v>
+        <v>4.01868152618408</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>4.56099987030029</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.01779985427856</v>
+        <v>4.01780033111572</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.94468545913696</v>
+        <v>3.94468569755554</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>4.44399976730347</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.91473436355591</v>
+        <v>3.91473412513733</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.87157011032104</v>
+        <v>3.87157034873962</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>4.44299983978271</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.91385388374329</v>
+        <v>3.91385364532471</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>4.47100019454956</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.93851900100708</v>
+        <v>3.93851947784424</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.87597513198853</v>
+        <v>3.87597489356995</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.95349454879761</v>
+        <v>3.95349407196045</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.92530536651611</v>
+        <v>3.92530512809753</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.84073901176453</v>
+        <v>3.84073853492737</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.66455817222595</v>
+        <v>3.66455793380737</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.58175325393677</v>
+        <v>3.58175301551819</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.62051320075989</v>
+        <v>3.62051296234131</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.58527684211731</v>
+        <v>3.58527708053589</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>4.23299980163574</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.72886395454407</v>
+        <v>3.72886371612549</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.88302206993103</v>
+        <v>3.88302230834961</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.84073901176453</v>
+        <v>3.84073853492737</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>4.44700002670288</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.91737723350525</v>
+        <v>3.91737747192383</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.88302206993103</v>
+        <v>3.88302230834961</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>4.44099998474121</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.91209173202515</v>
+        <v>3.9120922088623</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.98961114883423</v>
+        <v>3.98961138725281</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.98961114883423</v>
+        <v>3.98961138725281</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.93587589263916</v>
+        <v>3.93587613105774</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1559" t="n">
-        <v>4.00458669662476</v>
+        <v>4.0045862197876</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>4.46099996566772</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.92970991134644</v>
+        <v>3.92970967292786</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G1566" t="n">
-        <v>4.0133957862854</v>
+        <v>4.01339626312256</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G1568" t="n">
-        <v>4.01515769958496</v>
+        <v>4.0151572227478</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.01868104934692</v>
+        <v>4.01868152618408</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>4.53299999237061</v>
       </c>
       <c r="G1570" t="n">
-        <v>3.99313521385193</v>
+        <v>3.99313497543335</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1575" t="n">
-        <v>4.2459545135498</v>
+        <v>4.24595403671265</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>4.86100006103516</v>
       </c>
       <c r="G1578" t="n">
-        <v>4.28207111358643</v>
+        <v>4.28207159042358</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G1579" t="n">
-        <v>4.25123929977417</v>
+        <v>4.25123977661133</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G1581" t="n">
-        <v>4.23009777069092</v>
+        <v>4.23009824752808</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G1585" t="n">
-        <v>4.28823757171631</v>
+        <v>4.28823804855347</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G1588" t="n">
-        <v>4.34990167617798</v>
+        <v>4.34990119934082</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>4.83099985122681</v>
       </c>
       <c r="G1589" t="n">
-        <v>4.25564384460449</v>
+        <v>4.25564432144165</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>4.8439998626709</v>
       </c>
       <c r="G1590" t="n">
-        <v>4.26709604263306</v>
+        <v>4.2670955657959</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G1591" t="n">
-        <v>4.26181077957153</v>
+        <v>4.26181030273438</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.39042234420776</v>
+        <v>4.39042282104492</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1594" t="n">
-        <v>4.56307888031006</v>
+        <v>4.56307935714722</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1595" t="n">
-        <v>4.69169187545776</v>
+        <v>4.69169139862061</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G1596" t="n">
-        <v>4.67231178283691</v>
+        <v>4.67231130599976</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1607" t="n">
-        <v>4.55427026748657</v>
+        <v>4.55427074432373</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G1608" t="n">
-        <v>4.52255725860596</v>
+        <v>4.52255773544312</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>5.03800010681152</v>
       </c>
       <c r="G1609" t="n">
-        <v>4.43799161911011</v>
+        <v>4.43799114227295</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>5.01399993896484</v>
       </c>
       <c r="G1610" t="n">
-        <v>4.41684913635254</v>
+        <v>4.4168496131897</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>4.95800018310547</v>
       </c>
       <c r="G1612" t="n">
-        <v>4.36751890182495</v>
+        <v>4.36751937866211</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1616" t="n">
-        <v>4.70402383804321</v>
+        <v>4.70402431488037</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.74278354644775</v>
+        <v>4.74278402328491</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>5.41800022125244</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.77273464202881</v>
+        <v>4.77273511886597</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G1622" t="n">
-        <v>4.68464422225952</v>
+        <v>4.68464374542236</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1625" t="n">
-        <v>4.77449655532837</v>
+        <v>4.77449607849121</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G1626" t="n">
-        <v>4.80268573760986</v>
+        <v>4.80268526077271</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.80620861053467</v>
+        <v>4.80620908737183</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1631" t="n">
-        <v>4.95948600769043</v>
+        <v>4.95948648452759</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G1638" t="n">
-        <v>4.71459531784058</v>
+        <v>4.71459484100342</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>5.54400014877319</v>
       </c>
       <c r="G1641" t="n">
-        <v>4.88372802734375</v>
+        <v>4.88372850418091</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1643" t="n">
-        <v>4.91720247268677</v>
+        <v>4.91720199584961</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G1644" t="n">
-        <v>4.89606094360352</v>
+        <v>4.89606142044067</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1645" t="n">
-        <v>4.9330587387085</v>
+        <v>4.93305921554565</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>5.58599996566772</v>
       </c>
       <c r="G1646" t="n">
-        <v>4.92072629928589</v>
+        <v>4.92072677612305</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>5.65399980545044</v>
       </c>
       <c r="G1647" t="n">
-        <v>4.98062753677368</v>
+        <v>4.98062705993652</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1648" t="n">
-        <v>4.97357988357544</v>
+        <v>4.97358083724976</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1651" t="n">
-        <v>4.97357988357544</v>
+        <v>4.97358083724976</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1663" t="n">
-        <v>5.17090320587158</v>
+        <v>5.17090272903442</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1664" t="n">
-        <v>5.1233344078064</v>
+        <v>5.12333345413208</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G1666" t="n">
-        <v>5.27484893798828</v>
+        <v>5.27484941482544</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>6</v>
       </c>
       <c r="G1670" t="n">
-        <v>5.28541994094849</v>
+        <v>5.28542041778564</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>6.00400018692017</v>
       </c>
       <c r="G1673" t="n">
-        <v>5.28894376754761</v>
+        <v>5.28894424438477</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G1676" t="n">
-        <v>5.29951477050781</v>
+        <v>5.29951429367065</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>6.06799983978271</v>
       </c>
       <c r="G1677" t="n">
-        <v>5.34532165527344</v>
+        <v>5.34532117843628</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1679" t="n">
-        <v>5.4616003036499</v>
+        <v>5.46160078048706</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>6.11399984359741</v>
       </c>
       <c r="G1682" t="n">
-        <v>5.38584327697754</v>
+        <v>5.38584280014038</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>6</v>
       </c>
       <c r="G1685" t="n">
-        <v>5.28541994094849</v>
+        <v>5.28542041778564</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G1686" t="n">
-        <v>5.36470174789429</v>
+        <v>5.36470127105713</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G1689" t="n">
-        <v>5.41403198242188</v>
+        <v>5.41403150558472</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>6.17399978637695</v>
       </c>
       <c r="G1690" t="n">
-        <v>5.43869733810425</v>
+        <v>5.43869686126709</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G1694" t="n">
-        <v>5.29775333404541</v>
+        <v>5.29775285720825</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>5.97599983215332</v>
       </c>
       <c r="G1695" t="n">
-        <v>5.26427841186523</v>
+        <v>5.26427888870239</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>5.94399976730347</v>
       </c>
       <c r="G1696" t="n">
-        <v>5.23608922958374</v>
+        <v>5.2360897064209</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>6.0460000038147</v>
       </c>
       <c r="G1697" t="n">
-        <v>5.32594203948975</v>
+        <v>5.32594156265259</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1698" t="n">
-        <v>5.32946538925171</v>
+        <v>5.32946586608887</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G1701" t="n">
-        <v>5.29951477050781</v>
+        <v>5.29951429367065</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>5.86199998855591</v>
       </c>
       <c r="G1705" t="n">
-        <v>5.1638560295105</v>
+        <v>5.16385555267334</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1706" t="n">
-        <v>5.135666847229</v>
+        <v>5.13566637039185</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1713" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1714" t="n">
-        <v>5.12169647216797</v>
+        <v>5.12169694900513</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1715" t="n">
-        <v>5.02137899398804</v>
+        <v>5.02137851715088</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G1718" t="n">
-        <v>5.16547155380249</v>
+        <v>5.16547203063965</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>5.57399988174438</v>
       </c>
       <c r="G1720" t="n">
-        <v>5.08339309692383</v>
+        <v>5.08339357376099</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1721" t="n">
-        <v>5.14905595779419</v>
+        <v>5.14905643463135</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1723" t="n">
-        <v>5.22931051254272</v>
+        <v>5.22931098937988</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1725" t="n">
-        <v>5.25484609603882</v>
+        <v>5.25484657287598</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>5.75</v>
       </c>
       <c r="G1732" t="n">
-        <v>5.2439022064209</v>
+        <v>5.24390268325806</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1733" t="n">
-        <v>5.30774116516113</v>
+        <v>5.30774164199829</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1734" t="n">
-        <v>5.26578998565674</v>
+        <v>5.2657904624939</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1737" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1738" t="n">
-        <v>4.97760343551636</v>
+        <v>4.97760391235352</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G1740" t="n">
-        <v>4.74960803985596</v>
+        <v>4.7496075630188</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G1744" t="n">
-        <v>4.78426313400269</v>
+        <v>4.78426265716553</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>5.38199996948242</v>
       </c>
       <c r="G1748" t="n">
-        <v>4.90829277038574</v>
+        <v>4.90829229354858</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1750" t="n">
-        <v>4.94294834136963</v>
+        <v>4.94294786453247</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>5.43200016021729</v>
       </c>
       <c r="G1753" t="n">
-        <v>4.95389175415039</v>
+        <v>4.95389223098755</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>5.52799987792969</v>
       </c>
       <c r="G1758" t="n">
-        <v>5.04144191741943</v>
+        <v>5.04144239425659</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1760" t="n">
-        <v>4.99584341049194</v>
+        <v>4.99584293365479</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1767" t="n">
-        <v>4.96118783950806</v>
+        <v>4.9611873626709</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G1769" t="n">
-        <v>4.92106056213379</v>
+        <v>4.92106008529663</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1777" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>5.21199989318848</v>
       </c>
       <c r="G1780" t="n">
-        <v>4.75325536727905</v>
+        <v>4.75325584411621</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G1785" t="n">
-        <v>4.8955249786377</v>
+        <v>4.89552450180054</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G1791" t="n">
-        <v>4.87546110153198</v>
+        <v>4.87546157836914</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>5.24399995803833</v>
       </c>
       <c r="G1795" t="n">
-        <v>4.7824387550354</v>
+        <v>4.78243923187256</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1797" t="n">
-        <v>4.71677589416504</v>
+        <v>4.7167763710022</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>5.15799999237061</v>
       </c>
       <c r="G1798" t="n">
-        <v>4.70400810241699</v>
+        <v>4.70400857925415</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1799" t="n">
-        <v>4.62010622024536</v>
+        <v>4.6201057434082</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1802" t="n">
-        <v>4.62010622024536</v>
+        <v>4.6201057434082</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>5.10400009155273</v>
       </c>
       <c r="G1807" t="n">
-        <v>4.65476179122925</v>
+        <v>4.65476131439209</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1808" t="n">
-        <v>4.71677589416504</v>
+        <v>4.7167763710022</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>4.96700000762939</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.52981996536255</v>
+        <v>4.52981948852539</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G1811" t="n">
-        <v>4.63469743728638</v>
+        <v>4.63469791412354</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>5.16599988937378</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.71130466461182</v>
+        <v>4.71130418777466</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.71677589416504</v>
+        <v>4.7167763710022</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G1822" t="n">
-        <v>4.68212032318115</v>
+        <v>4.68212080001831</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G1825" t="n">
-        <v>4.78426313400269</v>
+        <v>4.78426265716553</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.87546110153198</v>
+        <v>4.87546157836914</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G1828" t="n">
-        <v>4.92106056213379</v>
+        <v>4.92106008529663</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1834" t="n">
-        <v>5.02137899398804</v>
+        <v>5.02137851715088</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1835" t="n">
-        <v>5.04326677322388</v>
+        <v>5.04326629638672</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.97760343551636</v>
+        <v>4.97760391235352</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.99219465255737</v>
+        <v>4.99219512939453</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1846" t="n">
-        <v>5.09068918228149</v>
+        <v>5.09068870544434</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1847" t="n">
-        <v>5.09616088867188</v>
+        <v>5.09616136550903</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1848" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1849" t="n">
-        <v>5.18006372451782</v>
+        <v>5.18006324768066</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1851" t="n">
-        <v>5.22931051254272</v>
+        <v>5.22931098937988</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1854" t="n">
-        <v>5.23843050003052</v>
+        <v>5.23843002319336</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>5.82800006866455</v>
       </c>
       <c r="G1856" t="n">
-        <v>5.3150372505188</v>
+        <v>5.31503677368164</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>5.85200023651123</v>
       </c>
       <c r="G1857" t="n">
-        <v>5.33692455291748</v>
+        <v>5.33692502975464</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>5.78200006484985</v>
       </c>
       <c r="G1860" t="n">
-        <v>5.27308559417725</v>
+        <v>5.2730860710144</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1863" t="n">
-        <v>5.13264036178589</v>
+        <v>5.13263988494873</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1864" t="n">
-        <v>5.10710477828979</v>
+        <v>5.10710525512695</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>5.53800010681152</v>
       </c>
       <c r="G1865" t="n">
-        <v>5.05056238174438</v>
+        <v>5.05056190490723</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1866" t="n">
-        <v>5.10710477828979</v>
+        <v>5.10710525512695</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1868" t="n">
-        <v>5.10710477828979</v>
+        <v>5.10710525512695</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1869" t="n">
-        <v>5.14358377456665</v>
+        <v>5.14358425140381</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G1871" t="n">
-        <v>5.24572658538818</v>
+        <v>5.24572610855103</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>5.72800016403198</v>
       </c>
       <c r="G1876" t="n">
-        <v>5.2238392829895</v>
+        <v>5.22383880615234</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1880" t="n">
-        <v>5.30774116516113</v>
+        <v>5.30774164199829</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G1882" t="n">
-        <v>5.50290536880493</v>
+        <v>5.50290584564209</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>5.75</v>
       </c>
       <c r="G1884" t="n">
-        <v>5.2439022064209</v>
+        <v>5.24390268325806</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1886" t="n">
-        <v>5.30774116516113</v>
+        <v>5.30774164199829</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49431,7 +49431,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1887" t="n">
-        <v>5.14905595779419</v>
+        <v>5.14905643463135</v>
       </c>
       <c r="H1887" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>5.66599988937378</v>
       </c>
       <c r="G1888" t="n">
-        <v>5.16729593276978</v>
+        <v>5.16729545593262</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1889" t="n">
-        <v>5.12169647216797</v>
+        <v>5.12169694900513</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1891" t="n">
-        <v>5.25484609603882</v>
+        <v>5.25484657287598</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G1892" t="n">
-        <v>5.40258693695068</v>
+        <v>5.40258741378784</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1894" t="n">
-        <v>5.40441179275513</v>
+        <v>5.40441131591797</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1895" t="n">
-        <v>5.40441179275513</v>
+        <v>5.40441131591797</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1897" t="n">
-        <v>5.36246061325073</v>
+        <v>5.36246013641357</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G1899" t="n">
-        <v>5.24572658538818</v>
+        <v>5.24572610855103</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1900" t="n">
-        <v>5.09616088867188</v>
+        <v>5.09616136550903</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.99219465255737</v>
+        <v>4.99219512939453</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G1905" t="n">
-        <v>4.97577905654907</v>
+        <v>4.97577953338623</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.84262990951538</v>
+        <v>4.84262943267822</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>4.80299997329712</v>
       </c>
       <c r="G1911" t="n">
-        <v>4.38025426864624</v>
+        <v>4.3802547454834</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G1913" t="n">
-        <v>4.50793218612671</v>
+        <v>4.50793170928955</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.56903505325317</v>
+        <v>4.56903553009033</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G1916" t="n">
-        <v>4.58909893035889</v>
+        <v>4.58909845352173</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>5.36399984359741</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.89187717437744</v>
+        <v>4.89187669754028</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>5.53599977493286</v>
       </c>
       <c r="G1926" t="n">
-        <v>5.04873752593994</v>
+        <v>5.0487380027771</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G1930" t="n">
-        <v>5.40258693695068</v>
+        <v>5.40258741378784</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>5.91800022125244</v>
       </c>
       <c r="G1934" t="n">
-        <v>5.39711570739746</v>
+        <v>5.39711618423462</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1935" t="n">
-        <v>5.45365810394287</v>
+        <v>5.45365858078003</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G1936" t="n">
-        <v>5.57403993606567</v>
+        <v>5.57404041290283</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1937" t="n">
-        <v>5.62693500518799</v>
+        <v>5.62693548202515</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>6.13800001144409</v>
       </c>
       <c r="G1939" t="n">
-        <v>5.59775161743164</v>
+        <v>5.5977520942688</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1943" t="n">
-        <v>5.73637342453003</v>
+        <v>5.73637294769287</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1946" t="n">
-        <v>5.69077348709106</v>
+        <v>5.69077396392822</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>6.18599987030029</v>
       </c>
       <c r="G1952" t="n">
-        <v>5.64152717590332</v>
+        <v>5.64152669906616</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1959" t="n">
-        <v>5.53208875656128</v>
+        <v>5.53208923339844</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -59990,6 +59990,32 @@
         <v>6.69000005722046</v>
       </c>
       <c r="H2293" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2294" t="n">
+        <v>1646565</v>
+      </c>
+      <c r="C2294" t="n">
+        <v>6.78000020980835</v>
+      </c>
+      <c r="D2294" t="n">
+        <v>6.6399998664856</v>
+      </c>
+      <c r="E2294" t="n">
+        <v>6.6399998664856</v>
+      </c>
+      <c r="F2294" t="n">
+        <v>6.72499990463257</v>
+      </c>
+      <c r="G2294" t="n">
+        <v>6.72499990463257</v>
+      </c>
+      <c r="H2294" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G2" t="n">
-        <v>5.00744915008545</v>
+        <v>5.00744962692261</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>5.19319772720337</v>
+        <v>5.19319725036621</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G5" t="n">
-        <v>5.07710456848145</v>
+        <v>5.0771050453186</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G6" t="n">
-        <v>5.10419321060181</v>
+        <v>5.10419273376465</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G7" t="n">
-        <v>5.11193323135376</v>
+        <v>5.1119327545166</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>6.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.03066825866699</v>
+        <v>5.03066778182983</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>5.02679777145386</v>
+        <v>5.02679872512817</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>4.98423194885254</v>
+        <v>4.98423051834106</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>5.02679777145386</v>
+        <v>5.02679872512817</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G15" t="n">
-        <v>5.04227685928345</v>
+        <v>5.04227733612061</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>6.5</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03066825866699</v>
+        <v>5.03066778182983</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G18" t="n">
-        <v>5.04227685928345</v>
+        <v>5.04227733612061</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G19" t="n">
-        <v>5.10806226730347</v>
+        <v>5.10806179046631</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>6.75</v>
       </c>
       <c r="G21" t="n">
-        <v>5.22415494918823</v>
+        <v>5.22415590286255</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>5.23189544677734</v>
+        <v>5.23189401626587</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>5.29381084442139</v>
+        <v>5.29381132125854</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G32" t="n">
-        <v>5.26285314559937</v>
+        <v>5.26285219192505</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>5.26285314559937</v>
+        <v>5.26285219192505</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>5.29381084442139</v>
+        <v>5.29381132125854</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>5.28994083404541</v>
+        <v>5.28994131088257</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>5.44860029220581</v>
+        <v>5.44860076904297</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>5.44860029220581</v>
+        <v>5.44860076904297</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>5.47955799102783</v>
+        <v>5.47955846786499</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G42" t="n">
-        <v>5.4640793800354</v>
+        <v>5.46407890319824</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>5.42151212692261</v>
+        <v>5.42151260375977</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>5.42925119400024</v>
+        <v>5.4292516708374</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G46" t="n">
-        <v>5.39442348480225</v>
+        <v>5.3944239616394</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G47" t="n">
-        <v>5.37120580673218</v>
+        <v>5.37120532989502</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G50" t="n">
-        <v>5.61886882781982</v>
+        <v>5.61886930465698</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G51" t="n">
-        <v>5.5879111289978</v>
+        <v>5.58791065216064</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G53" t="n">
-        <v>5.59178161621094</v>
+        <v>5.59178066253662</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>5.53373527526855</v>
+        <v>5.5337347984314</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>5.47955799102783</v>
+        <v>5.47955846786499</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G58" t="n">
-        <v>5.52986526489258</v>
+        <v>5.52986478805542</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>5.53373527526855</v>
+        <v>5.5337347984314</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>5.54921340942383</v>
+        <v>5.54921388626099</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>7.25</v>
       </c>
       <c r="G62" t="n">
-        <v>5.61113023757935</v>
+        <v>5.61112928390503</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G65" t="n">
-        <v>5.84718370437622</v>
+        <v>5.84718418121338</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G67" t="n">
-        <v>6.04841089248657</v>
+        <v>6.04841041564941</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>6.14902448654175</v>
+        <v>6.14902496337891</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>7.86499977111816</v>
       </c>
       <c r="G71" t="n">
-        <v>6.08710765838623</v>
+        <v>6.08710813522339</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>6.03680181503296</v>
+        <v>6.03680229187012</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>5.98262500762939</v>
+        <v>5.98262548446655</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G79" t="n">
-        <v>5.9710168838501</v>
+        <v>5.97101640701294</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>5.94392776489258</v>
+        <v>5.94392681121826</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G83" t="n">
-        <v>6.00584363937378</v>
+        <v>6.00584411621094</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G84" t="n">
-        <v>6.00584363937378</v>
+        <v>6.00584411621094</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>7.76399993896484</v>
       </c>
       <c r="G85" t="n">
-        <v>6.00894021987915</v>
+        <v>6.00893974304199</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G86" t="n">
-        <v>5.88201141357422</v>
+        <v>5.88201189041138</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G87" t="n">
-        <v>5.72722148895264</v>
+        <v>5.72722196578979</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>7.55800008773804</v>
       </c>
       <c r="G89" t="n">
-        <v>5.84950542449951</v>
+        <v>5.84950637817383</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>7.32800006866455</v>
       </c>
       <c r="G90" t="n">
-        <v>5.6714973449707</v>
+        <v>5.67149829864502</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G92" t="n">
-        <v>5.69007301330566</v>
+        <v>5.69007253646851</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>7.43400001525879</v>
       </c>
       <c r="G94" t="n">
-        <v>5.75353574752808</v>
+        <v>5.75353622436523</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>7.67600011825562</v>
       </c>
       <c r="G96" t="n">
-        <v>5.94083213806152</v>
+        <v>5.94083166122437</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>7.52199983596802</v>
       </c>
       <c r="G97" t="n">
-        <v>5.8216438293457</v>
+        <v>5.82164430618286</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>5.71174335479736</v>
+        <v>5.71174287796021</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G101" t="n">
-        <v>5.79687738418579</v>
+        <v>5.79687690734863</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G102" t="n">
-        <v>5.79687738418579</v>
+        <v>5.79687690734863</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G103" t="n">
-        <v>5.79687738418579</v>
+        <v>5.79687690734863</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>7.0479998588562</v>
       </c>
       <c r="G105" t="n">
-        <v>5.45479249954224</v>
+        <v>5.45479154586792</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>6.91200017929077</v>
       </c>
       <c r="G106" t="n">
-        <v>5.34953546524048</v>
+        <v>5.34953498840332</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>6.89200019836426</v>
       </c>
       <c r="G107" t="n">
-        <v>5.33405637741089</v>
+        <v>5.33405590057373</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G108" t="n">
-        <v>5.48575019836426</v>
+        <v>5.4857497215271</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G109" t="n">
-        <v>5.56159639358521</v>
+        <v>5.56159687042236</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>7.31599998474121</v>
       </c>
       <c r="G110" t="n">
-        <v>5.66220998764038</v>
+        <v>5.66221046447754</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>5.62660837173462</v>
+        <v>5.62660884857178</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>5.51051664352417</v>
+        <v>5.51051616668701</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>7.08199977874756</v>
       </c>
       <c r="G117" t="n">
-        <v>5.48110628128052</v>
+        <v>5.48110675811768</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>7.19799995422363</v>
       </c>
       <c r="G118" t="n">
-        <v>5.57088375091553</v>
+        <v>5.57088470458984</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G119" t="n">
-        <v>5.61886882781982</v>
+        <v>5.61886930465698</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G120" t="n">
-        <v>5.51051664352417</v>
+        <v>5.51051616668701</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>5.4640793800354</v>
+        <v>5.46407890319824</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>7.03599977493286</v>
       </c>
       <c r="G124" t="n">
-        <v>5.44550466537476</v>
+        <v>5.44550514221191</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>7.16800022125244</v>
       </c>
       <c r="G126" t="n">
-        <v>5.5476655960083</v>
+        <v>5.54766654968262</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G128" t="n">
-        <v>5.55540561676025</v>
+        <v>5.5554051399231</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>5.54147434234619</v>
+        <v>5.54147386550903</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>7.11199998855591</v>
       </c>
       <c r="G130" t="n">
-        <v>5.50432538986206</v>
+        <v>5.5043249130249</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G131" t="n">
-        <v>5.56159639358521</v>
+        <v>5.56159687042236</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>5.49503707885742</v>
+        <v>5.49503755569458</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>5.53373527526855</v>
+        <v>5.5337347984314</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G134" t="n">
-        <v>5.61886882781982</v>
+        <v>5.61886930465698</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>7.25</v>
       </c>
       <c r="G135" t="n">
-        <v>5.61113023757935</v>
+        <v>5.61112928390503</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>5.54921340942383</v>
+        <v>5.54921388626099</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G138" t="n">
-        <v>5.44086122512817</v>
+        <v>5.44086074829102</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>7.02400016784668</v>
       </c>
       <c r="G139" t="n">
-        <v>5.43621730804443</v>
+        <v>5.43621683120728</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>7.13600015640259</v>
       </c>
       <c r="G142" t="n">
-        <v>5.52289915084839</v>
+        <v>5.52289962768555</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>7.19600009918213</v>
       </c>
       <c r="G144" t="n">
-        <v>5.56933641433716</v>
+        <v>5.56933689117432</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G146" t="n">
-        <v>5.69007301330566</v>
+        <v>5.69007253646851</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.32800006866455</v>
       </c>
       <c r="G149" t="n">
-        <v>5.6714973449707</v>
+        <v>5.67149829864502</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>7.26800012588501</v>
       </c>
       <c r="G150" t="n">
-        <v>5.62506103515625</v>
+        <v>5.62506055831909</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>5.49503707885742</v>
+        <v>5.49503755569458</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>7.01200008392334</v>
       </c>
       <c r="G152" t="n">
-        <v>5.42692947387695</v>
+        <v>5.42692995071411</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G153" t="n">
-        <v>5.38823223114014</v>
+        <v>5.38823175430298</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7.67799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>5.94238042831421</v>
+        <v>5.94237947463989</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G163" t="n">
-        <v>5.75044059753418</v>
+        <v>5.75044012069702</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G164" t="n">
-        <v>5.69626474380493</v>
+        <v>5.69626426696777</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>7.26399993896484</v>
       </c>
       <c r="G166" t="n">
-        <v>5.6219654083252</v>
+        <v>5.62196493148804</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>7.31799983978271</v>
       </c>
       <c r="G167" t="n">
-        <v>5.66375875473022</v>
+        <v>5.66375780105591</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>7.32800006866455</v>
       </c>
       <c r="G168" t="n">
-        <v>5.6714973449707</v>
+        <v>5.67149829864502</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7.47599983215332</v>
       </c>
       <c r="G170" t="n">
-        <v>5.78604221343994</v>
+        <v>5.78604173660278</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>7.43400001525879</v>
       </c>
       <c r="G172" t="n">
-        <v>5.75353574752808</v>
+        <v>5.75353622436523</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>7.52400016784668</v>
       </c>
       <c r="G174" t="n">
-        <v>5.82319116592407</v>
+        <v>5.82319164276123</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>5.77365875244141</v>
+        <v>5.77365922927856</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G176" t="n">
-        <v>5.75044059753418</v>
+        <v>5.75044012069702</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>5.72722148895264</v>
+        <v>5.72722196578979</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G178" t="n">
-        <v>5.76591920852661</v>
+        <v>5.76591873168945</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G179" t="n">
-        <v>5.72257852554321</v>
+        <v>5.72257900238037</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.649827003479</v>
+        <v>5.64982748031616</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G182" t="n">
-        <v>5.60338973999023</v>
+        <v>5.60339021682739</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>7.25</v>
       </c>
       <c r="G184" t="n">
-        <v>5.61113023757935</v>
+        <v>5.61112928390503</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>7.12400007247925</v>
       </c>
       <c r="G187" t="n">
-        <v>5.51361227035522</v>
+        <v>5.51361179351807</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G191" t="n">
-        <v>5.55540561676025</v>
+        <v>5.5554051399231</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>7.2960000038147</v>
       </c>
       <c r="G192" t="n">
-        <v>5.64673185348511</v>
+        <v>5.64673137664795</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7.13600015640259</v>
       </c>
       <c r="G193" t="n">
-        <v>5.52289915084839</v>
+        <v>5.52289962768555</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7.15799999237061</v>
       </c>
       <c r="G195" t="n">
-        <v>5.53992652893066</v>
+        <v>5.53992605209351</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>5.47955799102783</v>
+        <v>5.47955846786499</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.0460000038147</v>
       </c>
       <c r="G201" t="n">
-        <v>5.45324373245239</v>
+        <v>5.45324420928955</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.13399982452393</v>
       </c>
       <c r="G205" t="n">
-        <v>5.52135181427002</v>
+        <v>5.52135229110718</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>5.53373527526855</v>
+        <v>5.5337347984314</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>7.44600009918213</v>
       </c>
       <c r="G207" t="n">
-        <v>5.76282358169556</v>
+        <v>5.76282405853271</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>7.46600008010864</v>
       </c>
       <c r="G208" t="n">
-        <v>5.77830266952515</v>
+        <v>5.7783031463623</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>7.52199983596802</v>
       </c>
       <c r="G209" t="n">
-        <v>5.8216438293457</v>
+        <v>5.82164430618286</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G211" t="n">
-        <v>5.69007301330566</v>
+        <v>5.69007253646851</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7.19799995422363</v>
       </c>
       <c r="G212" t="n">
-        <v>5.57088375091553</v>
+        <v>5.57088470458984</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>7.48799991607666</v>
       </c>
       <c r="G215" t="n">
-        <v>5.79532909393311</v>
+        <v>5.79533004760742</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.66599988937378</v>
       </c>
       <c r="G216" t="n">
-        <v>5.93309211730957</v>
+        <v>5.93309259414673</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.66599988937378</v>
       </c>
       <c r="G217" t="n">
-        <v>5.93309211730957</v>
+        <v>5.93309259414673</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.60400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>5.88510751724243</v>
+        <v>5.88510704040527</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>5.88201141357422</v>
+        <v>5.88201189041138</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>7.60200023651123</v>
       </c>
       <c r="G222" t="n">
-        <v>5.8835597038269</v>
+        <v>5.88356018066406</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>7.59800004959106</v>
       </c>
       <c r="G224" t="n">
-        <v>5.88046360015869</v>
+        <v>5.88046407699585</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>7.25</v>
       </c>
       <c r="G225" t="n">
-        <v>5.61113023757935</v>
+        <v>5.61112928390503</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G226" t="n">
-        <v>5.69626474380493</v>
+        <v>5.69626426696777</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>7.1560001373291</v>
       </c>
       <c r="G227" t="n">
-        <v>5.53837871551514</v>
+        <v>5.53837823867798</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G228" t="n">
-        <v>5.56159639358521</v>
+        <v>5.56159687042236</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.25</v>
       </c>
       <c r="G230" t="n">
-        <v>5.61113023757935</v>
+        <v>5.61112928390503</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>6.93800020217896</v>
       </c>
       <c r="G232" t="n">
-        <v>5.36965751647949</v>
+        <v>5.36965799331665</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>6.92799997329712</v>
       </c>
       <c r="G234" t="n">
-        <v>5.36191749572754</v>
+        <v>5.3619179725647</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>6.92799997329712</v>
       </c>
       <c r="G235" t="n">
-        <v>5.36191749572754</v>
+        <v>5.3619179725647</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G236" t="n">
-        <v>5.21641540527344</v>
+        <v>5.2164158821106</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G238" t="n">
-        <v>5.36346626281738</v>
+        <v>5.36346578598022</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7.01200008392334</v>
       </c>
       <c r="G239" t="n">
-        <v>5.42692947387695</v>
+        <v>5.42692995071411</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G240" t="n">
-        <v>5.49813318252563</v>
+        <v>5.49813365936279</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>5.49503707885742</v>
+        <v>5.49503755569458</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G242" t="n">
-        <v>5.49813318252563</v>
+        <v>5.49813365936279</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G244" t="n">
-        <v>5.55695295333862</v>
+        <v>5.55695343017578</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>7.18800020217896</v>
       </c>
       <c r="G245" t="n">
-        <v>5.56314516067505</v>
+        <v>5.56314468383789</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>5.51051664352417</v>
+        <v>5.51051616668701</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>7.10599994659424</v>
       </c>
       <c r="G248" t="n">
-        <v>5.49968099594116</v>
+        <v>5.49968147277832</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G249" t="n">
-        <v>5.48575019836426</v>
+        <v>5.4857497215271</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G250" t="n">
-        <v>5.56159639358521</v>
+        <v>5.56159687042236</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.99200010299683</v>
       </c>
       <c r="G254" t="n">
-        <v>5.41145038604736</v>
+        <v>5.41145086288452</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G255" t="n">
-        <v>5.49503707885742</v>
+        <v>5.49503755569458</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>6.56599998474121</v>
       </c>
       <c r="G258" t="n">
-        <v>5.08174848556519</v>
+        <v>5.08174800872803</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G259" t="n">
-        <v>5.17771816253662</v>
+        <v>5.17771768569946</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>4.86813831329346</v>
+        <v>4.86813926696777</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G261" t="n">
-        <v>4.73037624359131</v>
+        <v>4.73037576675415</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G263" t="n">
-        <v>4.84646797180176</v>
+        <v>4.84646844863892</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>4.99197053909302</v>
+        <v>4.99197101593018</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>6.24200010299683</v>
       </c>
       <c r="G265" t="n">
-        <v>4.83098936080933</v>
+        <v>4.83098888397217</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G268" t="n">
-        <v>4.57094240188599</v>
+        <v>4.57094192504883</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>6.2480001449585</v>
       </c>
       <c r="G272" t="n">
-        <v>4.83563280105591</v>
+        <v>4.83563327789307</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G273" t="n">
-        <v>4.91457605361938</v>
+        <v>4.91457557678223</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G275" t="n">
-        <v>5.02602434158325</v>
+        <v>5.02602386474609</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G277" t="n">
-        <v>4.94088983535767</v>
+        <v>4.94089031219482</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.34600019454956</v>
       </c>
       <c r="G278" t="n">
-        <v>4.91147994995117</v>
+        <v>4.91148042678833</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>6.26599979400635</v>
       </c>
       <c r="G279" t="n">
-        <v>4.84956359863281</v>
+        <v>4.84956407546997</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>5.01518869400024</v>
+        <v>5.0151891708374</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G282" t="n">
-        <v>4.79074382781982</v>
+        <v>4.79074430465698</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>5.89200019836426</v>
       </c>
       <c r="G283" t="n">
-        <v>4.56010770797729</v>
+        <v>4.56010723114014</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G284" t="n">
-        <v>4.63440608978271</v>
+        <v>4.63440656661987</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G287" t="n">
-        <v>4.80467557907104</v>
+        <v>4.80467510223389</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>6.29199981689453</v>
       </c>
       <c r="G288" t="n">
-        <v>4.8696870803833</v>
+        <v>4.86968660354614</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>6.23400020599365</v>
       </c>
       <c r="G289" t="n">
-        <v>4.8247971534729</v>
+        <v>4.82479763031006</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.42399978637695</v>
       </c>
       <c r="G292" t="n">
-        <v>4.97184801101685</v>
+        <v>4.97184753417969</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G293" t="n">
-        <v>5.02602434158325</v>
+        <v>5.02602386474609</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.40799999237061</v>
       </c>
       <c r="G294" t="n">
-        <v>4.95946455001831</v>
+        <v>4.95946502685547</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G297" t="n">
-        <v>4.80467557907104</v>
+        <v>4.80467510223389</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G304" t="n">
-        <v>4.55855894088745</v>
+        <v>4.55855941772461</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>4.58487319946289</v>
+        <v>4.58487367630005</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.00799989700317</v>
       </c>
       <c r="G306" t="n">
-        <v>4.6498851776123</v>
+        <v>4.64988470077515</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>4.52760124206543</v>
+        <v>4.52760076522827</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.72599983215332</v>
       </c>
       <c r="G308" t="n">
-        <v>4.43163108825684</v>
+        <v>4.43163156509399</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G309" t="n">
-        <v>4.38674211502075</v>
+        <v>4.38674259185791</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.60799980163574</v>
       </c>
       <c r="G311" t="n">
-        <v>4.34030485153198</v>
+        <v>4.34030532836914</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G313" t="n">
-        <v>4.27529430389404</v>
+        <v>4.27529382705688</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.44600009918213</v>
       </c>
       <c r="G316" t="n">
-        <v>4.21492528915405</v>
+        <v>4.21492576599121</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G317" t="n">
-        <v>4.4053168296814</v>
+        <v>4.40531730651855</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G322" t="n">
-        <v>4.69013023376465</v>
+        <v>4.69013071060181</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>6.06199979782104</v>
       </c>
       <c r="G324" t="n">
-        <v>4.69167852401733</v>
+        <v>4.69167804718018</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>4.65917205810547</v>
+        <v>4.65917253494263</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>4.72108840942383</v>
+        <v>4.72108793258667</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G330" t="n">
-        <v>4.63440608978271</v>
+        <v>4.63440656661987</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G331" t="n">
-        <v>4.71489667892456</v>
+        <v>4.71489715576172</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>6.04400014877319</v>
       </c>
       <c r="G332" t="n">
-        <v>4.67774772644043</v>
+        <v>4.67774724960327</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>4.55855894088745</v>
+        <v>4.55855941772461</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.77600002288818</v>
       </c>
       <c r="G338" t="n">
-        <v>4.47032880783081</v>
+        <v>4.47032928466797</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.98199987411499</v>
       </c>
       <c r="G339" t="n">
-        <v>4.62976264953613</v>
+        <v>4.62976169586182</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>6.06799983978271</v>
       </c>
       <c r="G344" t="n">
-        <v>4.69632196426392</v>
+        <v>4.69632244110107</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G345" t="n">
-        <v>4.71489667892456</v>
+        <v>4.71489715576172</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>5.98400020599365</v>
       </c>
       <c r="G346" t="n">
-        <v>4.63131046295166</v>
+        <v>4.63131093978882</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G348" t="n">
-        <v>4.65452909469604</v>
+        <v>4.65452861785889</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G349" t="n">
-        <v>4.55855894088745</v>
+        <v>4.55855941772461</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>6.11600017547607</v>
       </c>
       <c r="G350" t="n">
-        <v>4.73347234725952</v>
+        <v>4.73347187042236</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G351" t="n">
-        <v>4.72108840942383</v>
+        <v>4.72108793258667</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>6.05800008773804</v>
       </c>
       <c r="G353" t="n">
-        <v>4.68858242034912</v>
+        <v>4.68858289718628</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G355" t="n">
-        <v>4.50438356399536</v>
+        <v>4.50438261032104</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>6.07600021362305</v>
       </c>
       <c r="G357" t="n">
-        <v>4.70251369476318</v>
+        <v>4.70251321792603</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>4.72108840942383</v>
+        <v>4.72108793258667</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>4.65917205810547</v>
+        <v>4.65917253494263</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G362" t="n">
-        <v>4.5477237701416</v>
+        <v>4.54772329330444</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G363" t="n">
-        <v>4.49509525299072</v>
+        <v>4.49509572982788</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>4.61273574829102</v>
+        <v>4.61273622512817</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.97200012207031</v>
       </c>
       <c r="G368" t="n">
-        <v>4.6220235824585</v>
+        <v>4.62202262878418</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G371" t="n">
-        <v>4.68548631668091</v>
+        <v>4.68548727035522</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>5.84600019454956</v>
       </c>
       <c r="G373" t="n">
-        <v>4.52450561523438</v>
+        <v>4.52450513839722</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G374" t="n">
-        <v>4.53069686889648</v>
+        <v>4.53069639205933</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G375" t="n">
-        <v>4.47342491149902</v>
+        <v>4.47342538833618</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G376" t="n">
-        <v>4.41150856018066</v>
+        <v>4.41150903701782</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.73799991607666</v>
       </c>
       <c r="G377" t="n">
-        <v>4.44091844558716</v>
+        <v>4.44091892242432</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G382" t="n">
-        <v>4.86813831329346</v>
+        <v>4.86813926696777</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.26800012588501</v>
       </c>
       <c r="G383" t="n">
-        <v>4.8511118888855</v>
+        <v>4.85111141204834</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>4.79074382781982</v>
+        <v>4.79074430465698</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.60200023651123</v>
       </c>
       <c r="G387" t="n">
-        <v>5.10961151123047</v>
+        <v>5.10961103439331</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.51200008392334</v>
       </c>
       <c r="G388" t="n">
-        <v>5.03995609283447</v>
+        <v>5.03995561599731</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G389" t="n">
-        <v>5.02757263183594</v>
+        <v>5.02757215499878</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.5</v>
       </c>
       <c r="G390" t="n">
-        <v>5.03066825866699</v>
+        <v>5.03066778182983</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>4.98423194885254</v>
+        <v>4.98423051834106</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G395" t="n">
-        <v>5.02602434158325</v>
+        <v>5.02602386474609</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.50799989700317</v>
       </c>
       <c r="G397" t="n">
-        <v>5.03685998916626</v>
+        <v>5.0368595123291</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.30600023269653</v>
       </c>
       <c r="G398" t="n">
-        <v>4.88052225112915</v>
+        <v>4.88052129745483</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>5.97399997711182</v>
       </c>
       <c r="G400" t="n">
-        <v>4.62356996536255</v>
+        <v>4.62357044219971</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>5.77799987792969</v>
       </c>
       <c r="G403" t="n">
-        <v>4.4718770980835</v>
+        <v>4.47187662124634</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>5.72800016403198</v>
       </c>
       <c r="G404" t="n">
-        <v>4.43317985534668</v>
+        <v>4.43317937850952</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G407" t="n">
-        <v>4.53069686889648</v>
+        <v>4.53069639205933</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G409" t="n">
-        <v>4.48271226882935</v>
+        <v>4.48271179199219</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>5.57600021362305</v>
       </c>
       <c r="G411" t="n">
-        <v>4.45157718658447</v>
+        <v>4.45157670974731</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G412" t="n">
-        <v>4.36695194244385</v>
+        <v>4.36695241928101</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.23400020599365</v>
       </c>
       <c r="G415" t="n">
-        <v>4.178542137146</v>
+        <v>4.17854261398315</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G417" t="n">
-        <v>4.07635402679443</v>
+        <v>4.07635450363159</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G419" t="n">
-        <v>4.07635402679443</v>
+        <v>4.07635450363159</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G420" t="n">
-        <v>4.0811448097229</v>
+        <v>4.08114433288574</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.25600004196167</v>
       </c>
       <c r="G421" t="n">
-        <v>4.19610643386841</v>
+        <v>4.19610595703125</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5.18800020217896</v>
       </c>
       <c r="G423" t="n">
-        <v>4.14181852340698</v>
+        <v>4.14181900024414</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.32800006866455</v>
       </c>
       <c r="G426" t="n">
-        <v>4.25358772277832</v>
+        <v>4.25358724594116</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G427" t="n">
-        <v>4.13223838806152</v>
+        <v>4.13223886489868</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.29199981689453</v>
       </c>
       <c r="G429" t="n">
-        <v>4.22484636306763</v>
+        <v>4.22484588623047</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.2519998550415</v>
       </c>
       <c r="G430" t="n">
-        <v>4.19291210174561</v>
+        <v>4.19291305541992</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>5.2979998588562</v>
       </c>
       <c r="G431" t="n">
-        <v>4.22963666915894</v>
+        <v>4.22963619232178</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>5.47599983215332</v>
       </c>
       <c r="G433" t="n">
-        <v>4.371741771698</v>
+        <v>4.37174224853516</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5.19600009918213</v>
       </c>
       <c r="G438" t="n">
-        <v>4.14820528030396</v>
+        <v>4.14820575714111</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>5.19799995422363</v>
       </c>
       <c r="G439" t="n">
-        <v>4.14980268478394</v>
+        <v>4.14980220794678</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>4.15938138961792</v>
+        <v>4.15938186645508</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5.67799997329712</v>
       </c>
       <c r="G449" t="n">
-        <v>4.53300762176514</v>
+        <v>4.53300809860229</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G450" t="n">
-        <v>4.5473780632019</v>
+        <v>4.54737854003906</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>5.36399984359741</v>
       </c>
       <c r="G452" t="n">
-        <v>4.28232717514038</v>
+        <v>4.28232765197754</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G453" t="n">
-        <v>4.1513991355896</v>
+        <v>4.15139865875244</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G454" t="n">
-        <v>4.14022207260132</v>
+        <v>4.14022159576416</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5.68200016021729</v>
       </c>
       <c r="G456" t="n">
-        <v>4.53620100021362</v>
+        <v>4.53620147705078</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G457" t="n">
-        <v>4.63359928131104</v>
+        <v>4.63359975814819</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G458" t="n">
-        <v>4.55057144165039</v>
+        <v>4.55057191848755</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.01599979400635</v>
       </c>
       <c r="G464" t="n">
-        <v>4.00450277328491</v>
+        <v>4.00450372695923</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>3.87197709083557</v>
+        <v>3.87197756767273</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>4.85699987411499</v>
       </c>
       <c r="G468" t="n">
-        <v>3.87756586074829</v>
+        <v>3.87756633758545</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G472" t="n">
-        <v>3.64444899559021</v>
+        <v>3.64444947242737</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G473" t="n">
-        <v>3.60532975196838</v>
+        <v>3.60533022880554</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.74100017547607</v>
       </c>
       <c r="G479" t="n">
-        <v>3.78495764732361</v>
+        <v>3.78495812416077</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.84700012207031</v>
       </c>
       <c r="G480" t="n">
-        <v>3.86958289146423</v>
+        <v>3.86958193778992</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.74025106430054</v>
+        <v>3.74025058746338</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>3.76020908355713</v>
+        <v>3.76020956039429</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G491" t="n">
-        <v>4.26316690444946</v>
+        <v>4.26316738128662</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>4.42283630371094</v>
+        <v>4.42283582687378</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>4.55057144165039</v>
+        <v>4.55057191848755</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G495" t="n">
-        <v>4.49468803405762</v>
+        <v>4.49468755722046</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G496" t="n">
-        <v>4.52183103561401</v>
+        <v>4.52183151245117</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G497" t="n">
-        <v>4.56973171234131</v>
+        <v>4.56973218917847</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G498" t="n">
-        <v>4.52183103561401</v>
+        <v>4.52183151245117</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G500" t="n">
-        <v>4.28871440887451</v>
+        <v>4.28871488571167</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G501" t="n">
-        <v>4.29510116577148</v>
+        <v>4.29510068893433</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>4.42283630371094</v>
+        <v>4.42283582687378</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G507" t="n">
-        <v>4.1705584526062</v>
+        <v>4.17055940628052</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G510" t="n">
-        <v>4.01727676391602</v>
+        <v>4.01727628707886</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G511" t="n">
-        <v>4.07954740524292</v>
+        <v>4.07954788208008</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G512" t="n">
-        <v>4.25518369674683</v>
+        <v>4.25518417358398</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.69399976730347</v>
       </c>
       <c r="G516" t="n">
-        <v>4.54578161239624</v>
+        <v>4.54578113555908</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G517" t="n">
-        <v>4.43081998825073</v>
+        <v>4.43081951141357</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G520" t="n">
-        <v>4.40048265457153</v>
+        <v>4.40048313140869</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>4.4627537727356</v>
+        <v>4.46275329589844</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.82399988174438</v>
       </c>
       <c r="G524" t="n">
-        <v>4.64956665039062</v>
+        <v>4.64956712722778</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G525" t="n">
-        <v>4.63679313659668</v>
+        <v>4.63679361343384</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.18800020217896</v>
       </c>
       <c r="G526" t="n">
-        <v>4.14181852340698</v>
+        <v>4.14181900024414</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.18200016021729</v>
       </c>
       <c r="G527" t="n">
-        <v>4.13702821731567</v>
+        <v>4.13702869415283</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G530" t="n">
-        <v>4.28552007675171</v>
+        <v>4.28552055358887</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.44799995422363</v>
       </c>
       <c r="G533" t="n">
-        <v>4.34938812255859</v>
+        <v>4.34938859939575</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.4148530960083</v>
+        <v>4.41485357284546</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G536" t="n">
-        <v>4.28073072433472</v>
+        <v>4.28073024749756</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G537" t="n">
-        <v>4.22644329071045</v>
+        <v>4.22644376754761</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G538" t="n">
-        <v>4.2487964630127</v>
+        <v>4.24879693984985</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.18800020217896</v>
       </c>
       <c r="G542" t="n">
-        <v>4.14181852340698</v>
+        <v>4.14181900024414</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G546" t="n">
-        <v>4.22644329071045</v>
+        <v>4.22644376754761</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G549" t="n">
-        <v>4.06996774673462</v>
+        <v>4.06996726989746</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G551" t="n">
-        <v>4.06996774673462</v>
+        <v>4.06996726989746</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>4.07156419754028</v>
+        <v>4.07156467437744</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G555" t="n">
-        <v>4.10669183731079</v>
+        <v>4.10669136047363</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G556" t="n">
-        <v>4.1705584526062</v>
+        <v>4.17055940628052</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G558" t="n">
-        <v>4.1705584526062</v>
+        <v>4.17055940628052</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G560" t="n">
-        <v>4.20089626312256</v>
+        <v>4.2008957862854</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G562" t="n">
-        <v>4.09870719909668</v>
+        <v>4.098708152771</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G563" t="n">
-        <v>4.15778541564941</v>
+        <v>4.15778493881226</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.21600008010864</v>
       </c>
       <c r="G564" t="n">
-        <v>4.1641731262207</v>
+        <v>4.16417264938354</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G565" t="n">
-        <v>4.15299606323242</v>
+        <v>4.15299558639526</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G566" t="n">
-        <v>4.1034984588623</v>
+        <v>4.10349798202515</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>4.15938138961792</v>
+        <v>4.15938186645508</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G571" t="n">
-        <v>4.24720048904419</v>
+        <v>4.24720001220703</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.25400018692017</v>
       </c>
       <c r="G574" t="n">
-        <v>4.19450902938843</v>
+        <v>4.19450950622559</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G577" t="n">
-        <v>4.05080699920654</v>
+        <v>4.05080652236938</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.03800010681152</v>
       </c>
       <c r="G581" t="n">
-        <v>4.02206707000732</v>
+        <v>4.02206659317017</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G584" t="n">
-        <v>3.64524745941162</v>
+        <v>3.64524722099304</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.58300018310547</v>
       </c>
       <c r="G585" t="n">
-        <v>3.6588191986084</v>
+        <v>3.65881967544556</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G587" t="n">
-        <v>3.62129712104797</v>
+        <v>3.62129688262939</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G588" t="n">
-        <v>3.49036812782288</v>
+        <v>3.49036860466003</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.36299991607666</v>
       </c>
       <c r="G590" t="n">
-        <v>3.48318290710449</v>
+        <v>3.48318314552307</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.59299993515015</v>
       </c>
       <c r="G592" t="n">
-        <v>3.66680264472961</v>
+        <v>3.66680335998535</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>3.62848258018494</v>
+        <v>3.6284818649292</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.50899982452393</v>
       </c>
       <c r="G594" t="n">
-        <v>3.59974145889282</v>
+        <v>3.5997416973114</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G597" t="n">
-        <v>3.60054039955139</v>
+        <v>3.60054016113281</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>3.60852336883545</v>
+        <v>3.60852360725403</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.86600017547607</v>
       </c>
       <c r="G601" t="n">
-        <v>3.88475179672241</v>
+        <v>3.88475131988525</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G602" t="n">
-        <v>3.86798596382141</v>
+        <v>3.86798548698425</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.45900011062622</v>
       </c>
       <c r="G604" t="n">
-        <v>3.5598247051239</v>
+        <v>3.55982422828674</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.36100006103516</v>
       </c>
       <c r="G605" t="n">
-        <v>3.48158645629883</v>
+        <v>3.48158621788025</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G606" t="n">
-        <v>3.55742907524109</v>
+        <v>3.55742883682251</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G607" t="n">
-        <v>3.44885444641113</v>
+        <v>3.44885396957397</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.25299978256226</v>
       </c>
       <c r="G608" t="n">
-        <v>3.39536499977112</v>
+        <v>3.39536476135254</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>3.27321815490723</v>
+        <v>3.27321839332581</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.01399993896484</v>
       </c>
       <c r="G610" t="n">
-        <v>3.20456051826477</v>
+        <v>3.20456027984619</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.01700019836426</v>
       </c>
       <c r="G611" t="n">
-        <v>3.20695567131042</v>
+        <v>3.20695543289185</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>3.12951612472534</v>
+        <v>3.12951588630676</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G613" t="n">
-        <v>3.1087589263916</v>
+        <v>3.10875916481018</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.81299996376038</v>
       </c>
       <c r="G616" t="n">
-        <v>3.04409265518188</v>
+        <v>3.04409289360046</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G620" t="n">
-        <v>2.68004703521729</v>
+        <v>2.68004727363586</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G622" t="n">
-        <v>3.04169821739197</v>
+        <v>3.04169797897339</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.45300006866455</v>
       </c>
       <c r="G626" t="n">
-        <v>2.75668859481812</v>
+        <v>2.75668835639954</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G634" t="n">
-        <v>2.55790042877197</v>
+        <v>2.55790066719055</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G635" t="n">
-        <v>2.56748032569885</v>
+        <v>2.56748056411743</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G638" t="n">
-        <v>2.64731502532959</v>
+        <v>2.64731526374817</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G639" t="n">
-        <v>2.49083924293518</v>
+        <v>2.4908390045166</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.28600001335144</v>
       </c>
       <c r="G640" t="n">
-        <v>2.62336468696594</v>
+        <v>2.62336421012878</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>2.62655782699585</v>
+        <v>2.62655806541443</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>2.71437621116638</v>
+        <v>2.7143759727478</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G643" t="n">
-        <v>2.65689539909363</v>
+        <v>2.65689516067505</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G645" t="n">
-        <v>2.64731502532959</v>
+        <v>2.64731526374817</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G646" t="n">
-        <v>2.68004703521729</v>
+        <v>2.68004727363586</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G647" t="n">
-        <v>2.70639252662659</v>
+        <v>2.70639276504517</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G651" t="n">
-        <v>2.81017732620239</v>
+        <v>2.81017756462097</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>3.66899991035461</v>
       </c>
       <c r="G655" t="n">
-        <v>2.92913126945496</v>
+        <v>2.92913103103638</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3.52699995040894</v>
       </c>
       <c r="G663" t="n">
-        <v>2.81576585769653</v>
+        <v>2.81576609611511</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.57699990272522</v>
       </c>
       <c r="G665" t="n">
-        <v>2.85568284988403</v>
+        <v>2.85568332672119</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>3.21733403205872</v>
+        <v>3.21733450889587</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G671" t="n">
-        <v>3.21094727516174</v>
+        <v>3.21094703674316</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G673" t="n">
-        <v>3.37380957603455</v>
+        <v>3.37380933761597</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.20699977874756</v>
       </c>
       <c r="G674" t="n">
-        <v>3.35864067077637</v>
+        <v>3.35864114761353</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G675" t="n">
-        <v>3.53986573219299</v>
+        <v>3.53986549377441</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G676" t="n">
-        <v>3.47919154167175</v>
+        <v>3.47919106483459</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G677" t="n">
-        <v>3.38498640060425</v>
+        <v>3.38498592376709</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G680" t="n">
-        <v>3.11354923248291</v>
+        <v>3.11354947090149</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.9210000038147</v>
       </c>
       <c r="G681" t="n">
-        <v>3.13031435012817</v>
+        <v>3.13031458854675</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.99300003051758</v>
       </c>
       <c r="G682" t="n">
-        <v>3.18779540061951</v>
+        <v>3.18779516220093</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G684" t="n">
-        <v>3.14069294929504</v>
+        <v>3.14069271087646</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.11354923248291</v>
+        <v>3.11354947090149</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.01100015640259</v>
       </c>
       <c r="G687" t="n">
-        <v>3.20216536521912</v>
+        <v>3.2021656036377</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G688" t="n">
-        <v>3.04010152816772</v>
+        <v>3.04010128974915</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>3.04010152816772</v>
+        <v>3.04010128974915</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G691" t="n">
-        <v>3.0975821018219</v>
+        <v>3.09758234024048</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G693" t="n">
-        <v>2.93791317939758</v>
+        <v>2.937912940979</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G694" t="n">
-        <v>3.05447149276733</v>
+        <v>3.05447125434875</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G695" t="n">
-        <v>2.96505641937256</v>
+        <v>2.96505665779114</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G696" t="n">
-        <v>3.03211784362793</v>
+        <v>3.03211760520935</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.78099989891052</v>
       </c>
       <c r="G697" t="n">
-        <v>3.01854586601257</v>
+        <v>3.01854562759399</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.64100003242493</v>
       </c>
       <c r="G699" t="n">
-        <v>2.90677762031555</v>
+        <v>2.90677738189697</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G704" t="n">
-        <v>3.03371429443359</v>
+        <v>3.03371453285217</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>3.76900005340576</v>
       </c>
       <c r="G705" t="n">
-        <v>3.00896549224854</v>
+        <v>3.00896573066711</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G707" t="n">
-        <v>3.0975821018219</v>
+        <v>3.09758234024048</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>3.76699995994568</v>
       </c>
       <c r="G708" t="n">
-        <v>3.00736927986145</v>
+        <v>3.00736904144287</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>3.78099989891052</v>
       </c>
       <c r="G709" t="n">
-        <v>3.01854586601257</v>
+        <v>3.01854562759399</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G718" t="n">
-        <v>2.94908976554871</v>
+        <v>2.94908952713013</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G719" t="n">
-        <v>2.80858087539673</v>
+        <v>2.80858111381531</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G722" t="n">
-        <v>2.96825051307678</v>
+        <v>2.9682502746582</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>3.6470000743866</v>
       </c>
       <c r="G729" t="n">
-        <v>2.9115674495697</v>
+        <v>2.91156768798828</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>2.96186351776123</v>
+        <v>2.96186327934265</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G742" t="n">
-        <v>3.04489088058472</v>
+        <v>3.04489135742188</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G744" t="n">
-        <v>3.11354923248291</v>
+        <v>3.11354947090149</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>3.88100004196167</v>
       </c>
       <c r="G745" t="n">
-        <v>3.09838032722473</v>
+        <v>3.09838056564331</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G746" t="n">
-        <v>3.08321166038513</v>
+        <v>3.08321189880371</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G747" t="n">
-        <v>3.06165647506714</v>
+        <v>3.06165671348572</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.95900011062622</v>
       </c>
       <c r="G750" t="n">
-        <v>3.16065144538879</v>
+        <v>3.16065168380737</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.75699996948242</v>
       </c>
       <c r="G751" t="n">
-        <v>2.99938559532166</v>
+        <v>2.99938535690308</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G752" t="n">
-        <v>2.98741030693054</v>
+        <v>2.98741054534912</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>3.81900000572205</v>
       </c>
       <c r="G753" t="n">
-        <v>3.04888319969177</v>
+        <v>3.04888296127319</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G754" t="n">
-        <v>2.9898054599762</v>
+        <v>2.98980522155762</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.58299994468689</v>
       </c>
       <c r="G759" t="n">
-        <v>2.8604736328125</v>
+        <v>2.86047339439392</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.53299999237061</v>
       </c>
       <c r="G760" t="n">
-        <v>2.82055616378784</v>
+        <v>2.82055592536926</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.82699990272522</v>
       </c>
       <c r="G763" t="n">
-        <v>3.05526947975159</v>
+        <v>3.05526971817017</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G768" t="n">
-        <v>3.06884169578552</v>
+        <v>3.0688419342041</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G771" t="n">
-        <v>2.9570734500885</v>
+        <v>2.95707321166992</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G775" t="n">
-        <v>3.28120183944702</v>
+        <v>3.2812020778656</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.94300007820129</v>
       </c>
       <c r="G776" t="n">
-        <v>3.14787793159485</v>
+        <v>3.14787817001343</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G777" t="n">
-        <v>3.00577235221863</v>
+        <v>3.00577259063721</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G778" t="n">
-        <v>2.7926139831543</v>
+        <v>2.79261374473572</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.4539999961853</v>
       </c>
       <c r="G779" t="n">
-        <v>2.75748705863953</v>
+        <v>2.75748682022095</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G780" t="n">
-        <v>2.85807847976685</v>
+        <v>2.85807824134827</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.86899995803833</v>
       </c>
       <c r="G782" t="n">
-        <v>3.08880019187927</v>
+        <v>3.08879995346069</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G783" t="n">
-        <v>2.96505641937256</v>
+        <v>2.96505665779114</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G786" t="n">
-        <v>3.36582612991333</v>
+        <v>3.36582636833191</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.27899980545044</v>
       </c>
       <c r="G788" t="n">
-        <v>3.41612195968628</v>
+        <v>3.41612219810486</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G790" t="n">
-        <v>3.33708596229553</v>
+        <v>3.33708620071411</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.22900009155273</v>
       </c>
       <c r="G791" t="n">
-        <v>3.37620520591736</v>
+        <v>3.37620496749878</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.26300001144409</v>
       </c>
       <c r="G792" t="n">
-        <v>3.40334844589233</v>
+        <v>3.40334868431091</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.28700017929077</v>
       </c>
       <c r="G793" t="n">
-        <v>3.42250919342041</v>
+        <v>3.42250943183899</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G794" t="n">
-        <v>3.34666609764099</v>
+        <v>3.34666585922241</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G795" t="n">
-        <v>3.33708596229553</v>
+        <v>3.33708620071411</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G797" t="n">
-        <v>3.40734052658081</v>
+        <v>3.40734028816223</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G798" t="n">
-        <v>3.45843434333801</v>
+        <v>3.45843410491943</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.5</v>
       </c>
       <c r="G801" t="n">
-        <v>3.5925567150116</v>
+        <v>3.59255623817444</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.38100004196167</v>
       </c>
       <c r="G803" t="n">
-        <v>3.49755311012268</v>
+        <v>3.49755358695984</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G805" t="n">
-        <v>3.6021363735199</v>
+        <v>3.60213661193848</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>3.55663132667542</v>
+        <v>3.55663084983826</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.45900011062622</v>
       </c>
       <c r="G807" t="n">
-        <v>3.5598247051239</v>
+        <v>3.55982422828674</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.55299997329712</v>
       </c>
       <c r="G808" t="n">
-        <v>3.63486862182617</v>
+        <v>3.63486886024475</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.39699983596802</v>
       </c>
       <c r="G809" t="n">
-        <v>3.51032733917236</v>
+        <v>3.51032638549805</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G812" t="n">
-        <v>3.5127215385437</v>
+        <v>3.51272201538086</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G813" t="n">
-        <v>3.57259798049927</v>
+        <v>3.57259821891785</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G814" t="n">
-        <v>3.73945236206055</v>
+        <v>3.73945188522339</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G815" t="n">
-        <v>3.50793218612671</v>
+        <v>3.50793194770813</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>3.45683789253235</v>
+        <v>3.45683741569519</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G819" t="n">
-        <v>3.60453200340271</v>
+        <v>3.60453152656555</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>3.56062245368958</v>
+        <v>3.56062316894531</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.43300008773804</v>
       </c>
       <c r="G821" t="n">
-        <v>3.53906750679016</v>
+        <v>3.53906726837158</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G823" t="n">
-        <v>3.42330718040466</v>
+        <v>3.42330741882324</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.29300022125244</v>
       </c>
       <c r="G824" t="n">
-        <v>3.42729902267456</v>
+        <v>3.42729926109314</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G828" t="n">
-        <v>3.62129712104797</v>
+        <v>3.62129688262939</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G829" t="n">
-        <v>3.58297610282898</v>
+        <v>3.58297657966614</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G831" t="n">
-        <v>3.46322464942932</v>
+        <v>3.46322417259216</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G832" t="n">
-        <v>3.53667211532593</v>
+        <v>3.53667235374451</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G833" t="n">
-        <v>3.50793218612671</v>
+        <v>3.50793194770813</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.47900009155273</v>
       </c>
       <c r="G834" t="n">
-        <v>3.57579135894775</v>
+        <v>3.57579112052917</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.43100023269653</v>
       </c>
       <c r="G835" t="n">
-        <v>3.53747057914734</v>
+        <v>3.53747081756592</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.29099988937378</v>
       </c>
       <c r="G836" t="n">
-        <v>3.42570209503174</v>
+        <v>3.42570233345032</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G838" t="n">
-        <v>3.44885444641113</v>
+        <v>3.44885396957397</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.27899980545044</v>
       </c>
       <c r="G840" t="n">
-        <v>3.41612195968628</v>
+        <v>3.41612219810486</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.3730001449585</v>
       </c>
       <c r="G843" t="n">
-        <v>3.49116706848145</v>
+        <v>3.49116683006287</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G845" t="n">
-        <v>3.72029137611389</v>
+        <v>3.72029185295105</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.69299983978271</v>
       </c>
       <c r="G848" t="n">
-        <v>3.74663758277893</v>
+        <v>3.74663734436035</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G849" t="n">
-        <v>3.71630024909973</v>
+        <v>3.71630072593689</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G850" t="n">
-        <v>3.73226737976074</v>
+        <v>3.73226690292358</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>3.76420116424561</v>
+        <v>3.76420092582703</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>3.75861310958862</v>
+        <v>3.75861263275146</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>3.90790271759033</v>
+        <v>3.90790367126465</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G860" t="n">
-        <v>3.81609344482422</v>
+        <v>3.81609392166138</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G861" t="n">
-        <v>3.81210207939148</v>
+        <v>3.81210160255432</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G863" t="n">
-        <v>3.86080074310303</v>
+        <v>3.86080121994019</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.75</v>
       </c>
       <c r="G866" t="n">
-        <v>3.79214358329773</v>
+        <v>3.79214310646057</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.94899988174438</v>
       </c>
       <c r="G869" t="n">
-        <v>3.95101380348206</v>
+        <v>3.95101428031921</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.90299987792969</v>
       </c>
       <c r="G871" t="n">
-        <v>3.91429018974304</v>
+        <v>3.91428971290588</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G872" t="n">
-        <v>3.96378755569458</v>
+        <v>3.96378707885742</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5</v>
       </c>
       <c r="G874" t="n">
-        <v>3.9917299747467</v>
+        <v>3.99172949790955</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>5.0939998626709</v>
       </c>
       <c r="G876" t="n">
-        <v>4.06677341461182</v>
+        <v>4.06677389144897</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.93599987030029</v>
       </c>
       <c r="G878" t="n">
-        <v>3.94063496589661</v>
+        <v>3.94063544273376</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G879" t="n">
-        <v>3.94622373580933</v>
+        <v>3.94622397422791</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>5.00799989700317</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99811553955078</v>
+        <v>3.99811601638794</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G883" t="n">
-        <v>4.14022207260132</v>
+        <v>4.14022159576416</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G885" t="n">
-        <v>3.98693895339966</v>
+        <v>3.98693943023682</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>5.05200004577637</v>
       </c>
       <c r="G887" t="n">
-        <v>4.03324317932129</v>
+        <v>4.03324365615845</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G888" t="n">
-        <v>3.9901328086853</v>
+        <v>3.99013328552246</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G893" t="n">
-        <v>3.92626452445984</v>
+        <v>3.92626547813416</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G895" t="n">
-        <v>3.95740032196045</v>
+        <v>3.95740079879761</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G901" t="n">
-        <v>3.94542551040649</v>
+        <v>3.94542503356934</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.79699993133545</v>
       </c>
       <c r="G902" t="n">
-        <v>3.829665184021</v>
+        <v>3.82966566085815</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G906" t="n">
-        <v>3.67638301849365</v>
+        <v>3.67638254165649</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G908" t="n">
-        <v>3.69155120849609</v>
+        <v>3.69155168533325</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G910" t="n">
-        <v>3.71630024909973</v>
+        <v>3.71630072593689</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>4.58099985122681</v>
       </c>
       <c r="G911" t="n">
-        <v>3.65722250938416</v>
+        <v>3.65722274780273</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G912" t="n">
-        <v>3.66839933395386</v>
+        <v>3.66839909553528</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.71299982070923</v>
       </c>
       <c r="G913" t="n">
-        <v>3.76260375976562</v>
+        <v>3.76260423660278</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>3.73945236206055</v>
+        <v>3.73945188522339</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G916" t="n">
-        <v>3.79533672332764</v>
+        <v>3.79533624649048</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>3.72029137611389</v>
+        <v>3.72029185295105</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.72900009155273</v>
       </c>
       <c r="G922" t="n">
-        <v>3.77537822723389</v>
+        <v>3.77537727355957</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.85200023651123</v>
       </c>
       <c r="G923" t="n">
-        <v>3.87357473373413</v>
+        <v>3.87357425689697</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.85699987411499</v>
       </c>
       <c r="G925" t="n">
-        <v>3.87756586074829</v>
+        <v>3.87756633758545</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G926" t="n">
-        <v>3.93185377120972</v>
+        <v>3.93185424804688</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G927" t="n">
-        <v>3.97097229957581</v>
+        <v>3.97097277641296</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G929" t="n">
-        <v>4.07635402679443</v>
+        <v>4.07635450363159</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.20599985122681</v>
       </c>
       <c r="G930" t="n">
-        <v>4.15618801116943</v>
+        <v>4.15618848800659</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G932" t="n">
-        <v>4.1034984588623</v>
+        <v>4.10349798202515</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G936" t="n">
-        <v>4.1034984588623</v>
+        <v>4.10349798202515</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>4.02366399765015</v>
+        <v>4.02366352081299</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>5.03399991989136</v>
       </c>
       <c r="G943" t="n">
-        <v>4.0836935043335</v>
+        <v>4.08369398117065</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.9229998588562</v>
       </c>
       <c r="G948" t="n">
-        <v>3.99364805221558</v>
+        <v>3.99364852905273</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G957" t="n">
-        <v>3.99608206748962</v>
+        <v>3.99608159065247</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G959" t="n">
-        <v>3.96849989891052</v>
+        <v>3.96850037574768</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G960" t="n">
-        <v>3.85168433189392</v>
+        <v>3.85168480873108</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G961" t="n">
-        <v>3.91495990753174</v>
+        <v>3.91495943069458</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.96099996566772</v>
       </c>
       <c r="G963" t="n">
-        <v>4.02447462081909</v>
+        <v>4.02447414398193</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>5.07600021362305</v>
       </c>
       <c r="G967" t="n">
-        <v>4.11776494979858</v>
+        <v>4.11776542663574</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G971" t="n">
-        <v>4.1064076423645</v>
+        <v>4.10640811920166</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G973" t="n">
-        <v>4.12263250350952</v>
+        <v>4.12263202667236</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G980" t="n">
-        <v>4.40007019042969</v>
+        <v>4.40007066726685</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>5.31400012969971</v>
       </c>
       <c r="G981" t="n">
-        <v>4.31083679199219</v>
+        <v>4.31083631515503</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G983" t="n">
-        <v>4.24756097793579</v>
+        <v>4.24756145477295</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G984" t="n">
-        <v>4.20700025558472</v>
+        <v>4.20699977874756</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>5.15199995040894</v>
       </c>
       <c r="G988" t="n">
-        <v>4.17941808700562</v>
+        <v>4.17941856384277</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.14799976348877</v>
       </c>
       <c r="G990" t="n">
-        <v>4.17617321014404</v>
+        <v>4.17617273330688</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G992" t="n">
-        <v>4.17292881011963</v>
+        <v>4.17292833328247</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>5.15199995040894</v>
       </c>
       <c r="G995" t="n">
-        <v>4.17941808700562</v>
+        <v>4.17941856384277</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>5.15399980545044</v>
       </c>
       <c r="G996" t="n">
-        <v>4.18104076385498</v>
+        <v>4.18104028701782</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>5.14599990844727</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.17455053329468</v>
+        <v>4.17455101013184</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.12263250350952</v>
+        <v>4.12263202667236</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.26703071594238</v>
+        <v>4.26703023910522</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.23782587051392</v>
+        <v>4.23782634735107</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.98699998855591</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.04556608200073</v>
+        <v>4.04556655883789</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>5.03599977493286</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.0853157043457</v>
+        <v>4.08531618118286</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.10478591918945</v>
+        <v>4.10478544235229</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>5.08400011062622</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.12425518035889</v>
+        <v>4.12425470352173</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.06422519683838</v>
+        <v>4.06422472000122</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>5.06799983978271</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.11127519607544</v>
+        <v>4.1112756729126</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.10478591918945</v>
+        <v>4.10478544235229</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.33192729949951</v>
+        <v>4.33192777633667</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.42765235900879</v>
+        <v>4.42765188217163</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.68399906158447</v>
+        <v>4.68399810791016</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.75376415252686</v>
+        <v>4.7537636756897</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>5.78200006484985</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.69048833847046</v>
+        <v>4.69048881530762</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G1056" t="n">
-        <v>4.40331554412842</v>
+        <v>4.40331506729126</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1060" t="n">
-        <v>4.66128444671631</v>
+        <v>4.66128396987915</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>5.92799997329712</v>
       </c>
       <c r="G1061" t="n">
-        <v>4.80892658233643</v>
+        <v>4.80892705917358</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>5.96400022506714</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.83813095092773</v>
+        <v>4.83813047409058</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>5.97399997711182</v>
       </c>
       <c r="G1065" t="n">
-        <v>4.84624290466309</v>
+        <v>4.84624338150024</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>5.94399976730347</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.82190608978271</v>
+        <v>4.82190561294556</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.85111045837402</v>
+        <v>4.85110998153687</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>5.87400007247925</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.76512098312378</v>
+        <v>4.76512050628662</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G1075" t="n">
-        <v>4.94845676422119</v>
+        <v>4.94845724105835</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>6.5</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.27294635772705</v>
+        <v>5.27294588088989</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>6.42600011825562</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.21291589736938</v>
+        <v>5.21291542053223</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.2891697883606</v>
+        <v>5.28917026519775</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6.58400011062622</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.34108924865723</v>
+        <v>5.34108877182007</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>6.59200000762939</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.34757804870605</v>
+        <v>5.34757852554321</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>6.69600009918213</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.43194532394409</v>
+        <v>5.43194580078125</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>6.67600011825562</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.41572093963623</v>
+        <v>5.41572141647339</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.02957916259766</v>
+        <v>5.0295786857605</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.00037527084351</v>
+        <v>5.00037574768066</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.99712991714478</v>
+        <v>4.99713039398193</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.05553817749023</v>
+        <v>5.05553770065308</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>6.32200002670288</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.12854862213135</v>
+        <v>5.12854814529419</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>6.29199981689453</v>
       </c>
       <c r="G1100" t="n">
-        <v>5.10421180725098</v>
+        <v>5.10421133041382</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.89978313446045</v>
+        <v>4.89978361129761</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>6.11800003051758</v>
       </c>
       <c r="G1105" t="n">
-        <v>4.96305847167969</v>
+        <v>4.96305894851685</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.76349830627441</v>
+        <v>4.76349878311157</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>5.75799989700317</v>
       </c>
       <c r="G1112" t="n">
-        <v>4.67101860046387</v>
+        <v>4.67101907730103</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>5.66200017929077</v>
       </c>
       <c r="G1114" t="n">
-        <v>4.59314203262329</v>
+        <v>4.59314155578613</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>5.65199995040894</v>
       </c>
       <c r="G1115" t="n">
-        <v>4.58502960205078</v>
+        <v>4.58502912521362</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G1118" t="n">
-        <v>4.00987195968628</v>
+        <v>4.00987243652344</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.82248020172119</v>
+        <v>3.82247972488403</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>4.32600021362305</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.50934839248657</v>
+        <v>3.50934863090515</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.50772595405579</v>
+        <v>3.50772571563721</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.43796062469482</v>
+        <v>3.4379608631134</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.68700647354126</v>
+        <v>3.6870059967041</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.67402648925781</v>
+        <v>3.67402625083923</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>4.66099977493286</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.78110814094543</v>
+        <v>3.78110766410828</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>4.6710000038147</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.78922033309937</v>
+        <v>3.78921985626221</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.93767380714417</v>
+        <v>3.93767428398132</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.93118405342102</v>
+        <v>3.93118357658386</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.89386773109436</v>
+        <v>3.89386820793152</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.8735876083374</v>
+        <v>3.87358713150024</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>4.8769998550415</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.95633172988892</v>
+        <v>3.95633220672607</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.89549040794373</v>
+        <v>3.89548993110657</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>4.41300010681152</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.57992482185364</v>
+        <v>3.57992458343506</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.61318492889404</v>
+        <v>3.61318469047546</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.59209275245667</v>
+        <v>3.59209299087524</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.60669493675232</v>
+        <v>3.6066951751709</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>4.52099990844727</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.66753673553467</v>
+        <v>3.66753697395325</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.73567962646484</v>
+        <v>3.73567938804626</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.85817384719849</v>
+        <v>3.85817432403564</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.84925055503845</v>
+        <v>3.84925007820129</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.85168433189392</v>
+        <v>3.85168480873108</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>4.61700010299683</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.74541449546814</v>
+        <v>3.74541401863098</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.71377658843994</v>
+        <v>3.71377635002136</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.712153673172</v>
+        <v>3.71215438842773</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.60831761360168</v>
+        <v>3.60831713676453</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.45100021362305</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.61075139045715</v>
+        <v>3.61075162887573</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>4.4689998626709</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.62535309791565</v>
+        <v>3.62535285949707</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>4.56799983978271</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.70566391944885</v>
+        <v>3.70566368103027</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>4.63899993896484</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.76326060295105</v>
+        <v>3.76326107978821</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.75</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.85330700874329</v>
+        <v>3.85330653190613</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.81761264801025</v>
+        <v>3.81761312484741</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.68781709671021</v>
+        <v>3.68781757354736</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>4.51399993896484</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.66185808181763</v>
+        <v>3.66185784339905</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>4.51100015640259</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.79477214813232</v>
+        <v>3.79477262496948</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.85449910163879</v>
+        <v>3.85449862480164</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.87132334709167</v>
+        <v>3.87132382392883</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.92768549919128</v>
+        <v>3.92768597602844</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.84861040115356</v>
+        <v>3.84861016273499</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>4.32299995422363</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.63662123680115</v>
+        <v>3.63662147521973</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.21299982070923</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.54408645629883</v>
+        <v>3.54408621788025</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.39014220237732</v>
+        <v>3.39014196395874</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.56679916381836</v>
+        <v>3.56679940223694</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>4.25899982452393</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.58278274536133</v>
+        <v>3.58278250694275</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.5348334312439</v>
+        <v>3.53483295440674</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.25218081474304</v>
+        <v>3.25218105316162</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.48267674446106</v>
+        <v>3.48267698287964</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.33125615119934</v>
+        <v>3.33125638961792</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>4.16900014877319</v>
       </c>
       <c r="G1218" t="n">
-        <v>3.50707244873047</v>
+        <v>3.50707268714905</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.11700010299683</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.46332883834839</v>
+        <v>3.46332907676697</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.3564932346344</v>
+        <v>3.35649299621582</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>4.20800018310547</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.5398805141449</v>
+        <v>3.53988075256348</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>4.17700004577637</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.51380228996277</v>
+        <v>3.51380252838135</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.58025932312012</v>
+        <v>3.5802595615387</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>4.40700006484985</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.70728445053101</v>
+        <v>3.70728397369385</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.58194160461426</v>
+        <v>3.58194184303284</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.66774654388428</v>
+        <v>3.66774678230286</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>4.29099988937378</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.60970187187195</v>
+        <v>3.60970234870911</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.47847104072571</v>
+        <v>3.47847080230713</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.39014220237732</v>
+        <v>3.39014196395874</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>3.87899994850159</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.26311683654785</v>
+        <v>3.26311707496643</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.14113879203796</v>
+        <v>3.14113903045654</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>3.70900011062622</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.12010860443115</v>
+        <v>3.12010836601257</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.17983531951904</v>
+        <v>3.17983555793762</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.14113879203796</v>
+        <v>3.14113903045654</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.23872113227844</v>
+        <v>3.23872137069702</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.2050724029541</v>
+        <v>3.20507216453552</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.16637587547302</v>
+        <v>3.16637563705444</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G1261" t="n">
-        <v>3.17647075653076</v>
+        <v>3.17647051811218</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.90223097801208</v>
+        <v>2.90223073959351</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.3659999370575</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.83156776428223</v>
+        <v>2.83156752586365</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.5</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.94429230690002</v>
+        <v>2.94429206848145</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1283" t="n">
-        <v>3.01579642295837</v>
+        <v>3.01579666137695</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1286" t="n">
-        <v>3.17983531951904</v>
+        <v>3.17983555793762</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>3.84100008010864</v>
       </c>
       <c r="G1288" t="n">
-        <v>3.23115015029907</v>
+        <v>3.23115038871765</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.1327269077301</v>
+        <v>3.13272666931152</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1296" t="n">
-        <v>3.38593602180481</v>
+        <v>3.38593626022339</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>4.13299989700317</v>
       </c>
       <c r="G1298" t="n">
-        <v>3.47678804397583</v>
+        <v>3.47678828239441</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.47931241989136</v>
+        <v>3.47931218147278</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.51127862930298</v>
+        <v>3.5112783908844</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.42883896827698</v>
+        <v>3.4288387298584</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>4.18400001525879</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.51969075202942</v>
+        <v>3.519690990448</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>4.22300004959106</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.55249857902527</v>
+        <v>3.55249905586243</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.55838704109192</v>
+        <v>3.55838751792908</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.56679916381836</v>
+        <v>3.56679940223694</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>4.32600021362305</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.63914513587952</v>
+        <v>3.6391453742981</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>4.15399980545044</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.49445366859436</v>
+        <v>3.49445390701294</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>4.16900014877319</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.50707244873047</v>
+        <v>3.50707268714905</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>4.02899980545044</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.38930082321167</v>
+        <v>3.38930058479309</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.35985779762268</v>
+        <v>3.35985803604126</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.38593602180481</v>
+        <v>3.38593626022339</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>4.0789999961853</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.43136215209961</v>
+        <v>3.43136239051819</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>4.09299993515015</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.44313931465149</v>
+        <v>3.44313955307007</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.36827039718628</v>
+        <v>3.3682701587677</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G1338" t="n">
-        <v>3.82926273345947</v>
+        <v>3.82926225662231</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.82926273345947</v>
+        <v>3.82926225662231</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.84019804000854</v>
+        <v>3.84019827842712</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.8772120475769</v>
+        <v>3.87721252441406</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>4.53700017929077</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.81664395332336</v>
+        <v>3.81664443016052</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.85618185997009</v>
+        <v>3.85618138313293</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.85618185997009</v>
+        <v>3.85618138313293</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.0605993270874</v>
+        <v>4.06059980392456</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>4.75899982452393</v>
       </c>
       <c r="G1359" t="n">
-        <v>4.00339651107788</v>
+        <v>4.00339603424072</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.9159083366394</v>
+        <v>3.91590881347656</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.83767461776733</v>
+        <v>3.83767414093018</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.90917873382568</v>
+        <v>3.90917825698853</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>4.78900003433228</v>
       </c>
       <c r="G1366" t="n">
-        <v>4.02863311767578</v>
+        <v>4.02863264083862</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G1368" t="n">
-        <v>4.08331251144409</v>
+        <v>4.08331203460693</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.11359643936157</v>
+        <v>4.11359691619873</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G1371" t="n">
-        <v>4.04209232330322</v>
+        <v>4.04209184646606</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>4.88299989700317</v>
       </c>
       <c r="G1374" t="n">
-        <v>4.10770750045776</v>
+        <v>4.10770797729492</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.05639362335205</v>
+        <v>4.05639314651489</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.74900007247925</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.9949836730957</v>
+        <v>3.99498414993286</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.66942930221558</v>
+        <v>3.669429063797</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.68961834907532</v>
+        <v>3.68961882591248</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.6963484287262</v>
+        <v>3.69634819030762</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>4.40899991989136</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.70896673202515</v>
+        <v>3.70896625518799</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.79056620597839</v>
+        <v>3.79056572914124</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.88141822814941</v>
+        <v>3.88141775131226</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1409" t="n">
-        <v>4.02442646026611</v>
+        <v>4.02442693710327</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.92768549919128</v>
+        <v>3.92768597602844</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>4.63899993896484</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.90244841575623</v>
+        <v>3.90244889259338</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.84861040115356</v>
+        <v>3.84861016273499</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G1428" t="n">
-        <v>4.0605993270874</v>
+        <v>4.06059980392456</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G1429" t="n">
-        <v>4.08331251144409</v>
+        <v>4.08331203460693</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.87468838691711</v>
+        <v>3.87468791007996</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.87468838691711</v>
+        <v>3.87468791007996</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>4.58300018310547</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.85534024238586</v>
+        <v>3.85534071922302</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.82337403297424</v>
+        <v>3.82337355613708</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>4.49900007247925</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.78467750549316</v>
+        <v>3.78467702865601</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.90917873382568</v>
+        <v>3.90917825698853</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>4.61899995803833</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.8856246471405</v>
+        <v>3.88562417030334</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1451" t="n">
-        <v>3.84440422058105</v>
+        <v>3.84440469741821</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.77710652351379</v>
+        <v>3.77710604667664</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.43300008773804</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.72915625572205</v>
+        <v>3.72915601730347</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.70307803153992</v>
+        <v>3.70307850837708</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.78383612632751</v>
+        <v>3.78383660316467</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.80570793151855</v>
+        <v>3.80570840835571</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>4.56400012969971</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.83935737609863</v>
+        <v>3.83935689926147</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>4.57100009918213</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.84524583816528</v>
+        <v>3.84524536132812</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.82084965705872</v>
+        <v>3.82085013389587</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>4.47599983215332</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.76532936096191</v>
+        <v>3.76532888412476</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.81412029266357</v>
+        <v>3.81411981582642</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.90917873382568</v>
+        <v>3.90917825698853</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>4.82399988174438</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.05807590484619</v>
+        <v>4.05807542800903</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -60016,6 +60016,32 @@
         <v>6.72499990463257</v>
       </c>
       <c r="H2294" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2295" t="n">
+        <v>1821645</v>
+      </c>
+      <c r="C2295" t="n">
+        <v>6.81500005722046</v>
+      </c>
+      <c r="D2295" t="n">
+        <v>6.71999979019165</v>
+      </c>
+      <c r="E2295" t="n">
+        <v>6.73000001907349</v>
+      </c>
+      <c r="F2295" t="n">
+        <v>6.73999977111816</v>
+      </c>
+      <c r="G2295" t="n">
+        <v>6.73999977111816</v>
+      </c>
+      <c r="H2295" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -456,7 +456,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>5.19319772720337</v>
+        <v>5.19319725036621</v>
       </c>
       <c r="H3" t="n">
         <v>24993644</v>
@@ -485,7 +485,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>5.18545818328857</v>
+        <v>5.18545770645142</v>
       </c>
       <c r="H4" t="n">
         <v>10381356</v>
@@ -630,7 +630,7 @@
         <v>6.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.03066825866699</v>
+        <v>5.03066778182983</v>
       </c>
       <c r="H9" t="n">
         <v>1559429</v>
@@ -659,7 +659,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>5.02679824829102</v>
+        <v>5.02679777145386</v>
       </c>
       <c r="H10" t="n">
         <v>4863908</v>
@@ -775,7 +775,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>5.02679824829102</v>
+        <v>5.02679777145386</v>
       </c>
       <c r="H14" t="n">
         <v>2519007</v>
@@ -833,7 +833,7 @@
         <v>6.5</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03066825866699</v>
+        <v>5.03066778182983</v>
       </c>
       <c r="H16" t="n">
         <v>1266116</v>
@@ -862,7 +862,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G17" t="n">
-        <v>5.02292823791504</v>
+        <v>5.02292776107788</v>
       </c>
       <c r="H17" t="n">
         <v>941108</v>
@@ -949,7 +949,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G20" t="n">
-        <v>5.11580228805542</v>
+        <v>5.11580276489258</v>
       </c>
       <c r="H20" t="n">
         <v>778081</v>
@@ -1442,7 +1442,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>5.44860076904297</v>
+        <v>5.44860029220581</v>
       </c>
       <c r="H37" t="n">
         <v>1554481</v>
@@ -1471,7 +1471,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G38" t="n">
-        <v>5.45247030258179</v>
+        <v>5.45246934890747</v>
       </c>
       <c r="H38" t="n">
         <v>874776</v>
@@ -1529,7 +1529,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G40" t="n">
-        <v>5.44860076904297</v>
+        <v>5.44860029220581</v>
       </c>
       <c r="H40" t="n">
         <v>903020</v>
@@ -1558,7 +1558,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>5.47955894470215</v>
+        <v>5.47955846786499</v>
       </c>
       <c r="H41" t="n">
         <v>1316822</v>
@@ -1645,7 +1645,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>5.340247631073</v>
+        <v>5.34024810791016</v>
       </c>
       <c r="H44" t="n">
         <v>1806362</v>
@@ -1703,7 +1703,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G46" t="n">
-        <v>5.39442348480225</v>
+        <v>5.3944239616394</v>
       </c>
       <c r="H46" t="n">
         <v>1348979</v>
@@ -1732,7 +1732,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G47" t="n">
-        <v>5.37120580673218</v>
+        <v>5.37120532989502</v>
       </c>
       <c r="H47" t="n">
         <v>1757181</v>
@@ -1790,7 +1790,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G49" t="n">
-        <v>5.56469297409058</v>
+        <v>5.56469249725342</v>
       </c>
       <c r="H49" t="n">
         <v>1856608</v>
@@ -1819,7 +1819,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G50" t="n">
-        <v>5.61886930465698</v>
+        <v>5.61886978149414</v>
       </c>
       <c r="H50" t="n">
         <v>1356581</v>
@@ -1877,7 +1877,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>5.62273931503296</v>
+        <v>5.6227388381958</v>
       </c>
       <c r="H52" t="n">
         <v>2277506</v>
@@ -1906,7 +1906,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G53" t="n">
-        <v>5.59178066253662</v>
+        <v>5.59178018569946</v>
       </c>
       <c r="H53" t="n">
         <v>2419795</v>
@@ -1964,7 +1964,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>5.48342847824097</v>
+        <v>5.48342800140381</v>
       </c>
       <c r="H55" t="n">
         <v>2428996</v>
@@ -2022,7 +2022,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>5.47955894470215</v>
+        <v>5.47955846786499</v>
       </c>
       <c r="H57" t="n">
         <v>1498021</v>
@@ -2109,7 +2109,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>5.54921436309814</v>
+        <v>5.54921388626099</v>
       </c>
       <c r="H60" t="n">
         <v>575911</v>
@@ -2138,7 +2138,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>5.59565114974976</v>
+        <v>5.5956506729126</v>
       </c>
       <c r="H61" t="n">
         <v>1027455</v>
@@ -2254,7 +2254,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G65" t="n">
-        <v>5.84718322753906</v>
+        <v>5.84718370437622</v>
       </c>
       <c r="H65" t="n">
         <v>2115620</v>
@@ -2370,7 +2370,7 @@
         <v>7.75</v>
       </c>
       <c r="G69" t="n">
-        <v>5.99810361862183</v>
+        <v>5.99810457229614</v>
       </c>
       <c r="H69" t="n">
         <v>2947971</v>
@@ -2428,7 +2428,7 @@
         <v>7.86499977111816</v>
       </c>
       <c r="G71" t="n">
-        <v>6.08710813522339</v>
+        <v>6.08710861206055</v>
       </c>
       <c r="H71" t="n">
         <v>1712288</v>
@@ -2486,7 +2486,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G73" t="n">
-        <v>6.13741445541382</v>
+        <v>6.13741493225098</v>
       </c>
       <c r="H73" t="n">
         <v>1143990</v>
@@ -2515,7 +2515,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G74" t="n">
-        <v>6.05228090286255</v>
+        <v>6.05228042602539</v>
       </c>
       <c r="H74" t="n">
         <v>2266592</v>
@@ -2544,7 +2544,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>6.03680229187012</v>
+        <v>6.03680181503296</v>
       </c>
       <c r="H75" t="n">
         <v>1814794</v>
@@ -2602,7 +2602,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G77" t="n">
-        <v>6.05228090286255</v>
+        <v>6.05228042602539</v>
       </c>
       <c r="H77" t="n">
         <v>1103493</v>
@@ -2660,7 +2660,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G79" t="n">
-        <v>5.97101593017578</v>
+        <v>5.97101640701294</v>
       </c>
       <c r="H79" t="n">
         <v>1358430</v>
@@ -2718,7 +2718,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G81" t="n">
-        <v>6.05228090286255</v>
+        <v>6.05228042602539</v>
       </c>
       <c r="H81" t="n">
         <v>1375872</v>
@@ -2776,7 +2776,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G83" t="n">
-        <v>6.00584411621094</v>
+        <v>6.00584363937378</v>
       </c>
       <c r="H83" t="n">
         <v>1192678</v>
@@ -2805,7 +2805,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G84" t="n">
-        <v>6.00584411621094</v>
+        <v>6.00584363937378</v>
       </c>
       <c r="H84" t="n">
         <v>1034704</v>
@@ -2834,7 +2834,7 @@
         <v>7.76399993896484</v>
       </c>
       <c r="G85" t="n">
-        <v>6.00893926620483</v>
+        <v>6.00893974304199</v>
       </c>
       <c r="H85" t="n">
         <v>1196110</v>
@@ -2863,7 +2863,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G86" t="n">
-        <v>5.88201189041138</v>
+        <v>5.88201236724854</v>
       </c>
       <c r="H86" t="n">
         <v>2172088</v>
@@ -3037,7 +3037,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G92" t="n">
-        <v>5.69007205963135</v>
+        <v>5.69007301330566</v>
       </c>
       <c r="H92" t="n">
         <v>1784953</v>
@@ -3095,7 +3095,7 @@
         <v>7.43400001525879</v>
       </c>
       <c r="G94" t="n">
-        <v>5.75353574752808</v>
+        <v>5.75353622436523</v>
       </c>
       <c r="H94" t="n">
         <v>1691292</v>
@@ -3124,7 +3124,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G95" t="n">
-        <v>5.7813982963562</v>
+        <v>5.78139877319336</v>
       </c>
       <c r="H95" t="n">
         <v>1798735</v>
@@ -3182,7 +3182,7 @@
         <v>7.52199983596802</v>
       </c>
       <c r="G97" t="n">
-        <v>5.82164335250854</v>
+        <v>5.8216438293457</v>
       </c>
       <c r="H97" t="n">
         <v>766003</v>
@@ -3269,7 +3269,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G100" t="n">
-        <v>5.71174335479736</v>
+        <v>5.71174287796021</v>
       </c>
       <c r="H100" t="n">
         <v>2305834</v>
@@ -3298,7 +3298,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G101" t="n">
-        <v>5.79687738418579</v>
+        <v>5.79687643051147</v>
       </c>
       <c r="H101" t="n">
         <v>1741178</v>
@@ -3327,7 +3327,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G102" t="n">
-        <v>5.79687738418579</v>
+        <v>5.79687643051147</v>
       </c>
       <c r="H102" t="n">
         <v>4646214</v>
@@ -3356,7 +3356,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G103" t="n">
-        <v>5.79687738418579</v>
+        <v>5.79687643051147</v>
       </c>
       <c r="H103" t="n">
         <v>2511181</v>
@@ -3385,7 +3385,7 @@
         <v>7.28800010681152</v>
       </c>
       <c r="G104" t="n">
-        <v>5.640540599823</v>
+        <v>5.64054012298584</v>
       </c>
       <c r="H104" t="n">
         <v>1988206</v>
@@ -3472,7 +3472,7 @@
         <v>6.89200019836426</v>
       </c>
       <c r="G107" t="n">
-        <v>5.33405590057373</v>
+        <v>5.33405542373657</v>
       </c>
       <c r="H107" t="n">
         <v>2889957</v>
@@ -3501,7 +3501,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G108" t="n">
-        <v>5.4857497215271</v>
+        <v>5.48574876785278</v>
       </c>
       <c r="H108" t="n">
         <v>2296418</v>
@@ -3559,7 +3559,7 @@
         <v>7.31599998474121</v>
       </c>
       <c r="G110" t="n">
-        <v>5.66220998764038</v>
+        <v>5.66221046447754</v>
       </c>
       <c r="H110" t="n">
         <v>2111123</v>
@@ -3617,7 +3617,7 @@
         <v>7.26599979400635</v>
       </c>
       <c r="G112" t="n">
-        <v>5.62351274490356</v>
+        <v>5.62351322174072</v>
       </c>
       <c r="H112" t="n">
         <v>1188881</v>
@@ -3646,7 +3646,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G113" t="n">
-        <v>5.52754306793213</v>
+        <v>5.52754354476929</v>
       </c>
       <c r="H113" t="n">
         <v>1568885</v>
@@ -3733,7 +3733,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>5.58017158508301</v>
+        <v>5.58017206192017</v>
       </c>
       <c r="H116" t="n">
         <v>3945713</v>
@@ -3820,7 +3820,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G119" t="n">
-        <v>5.61886930465698</v>
+        <v>5.61886978149414</v>
       </c>
       <c r="H119" t="n">
         <v>1697131</v>
@@ -3907,7 +3907,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>5.40216398239136</v>
+        <v>5.4021635055542</v>
       </c>
       <c r="H122" t="n">
         <v>1605771</v>
@@ -3965,7 +3965,7 @@
         <v>7.03599977493286</v>
       </c>
       <c r="G124" t="n">
-        <v>5.4455041885376</v>
+        <v>5.44550466537476</v>
       </c>
       <c r="H124" t="n">
         <v>2485435</v>
@@ -4081,7 +4081,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G128" t="n">
-        <v>5.5554051399231</v>
+        <v>5.55540561676025</v>
       </c>
       <c r="H128" t="n">
         <v>2509350</v>
@@ -4110,7 +4110,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>5.54147434234619</v>
+        <v>5.54147386550903</v>
       </c>
       <c r="H129" t="n">
         <v>1457912</v>
@@ -4255,7 +4255,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G134" t="n">
-        <v>5.61886930465698</v>
+        <v>5.61886978149414</v>
       </c>
       <c r="H134" t="n">
         <v>3548151</v>
@@ -4313,7 +4313,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>5.54921436309814</v>
+        <v>5.54921388626099</v>
       </c>
       <c r="H136" t="n">
         <v>4094123</v>
@@ -4342,7 +4342,7 @@
         <v>7.02199983596802</v>
       </c>
       <c r="G137" t="n">
-        <v>5.43466901779175</v>
+        <v>5.43466949462891</v>
       </c>
       <c r="H137" t="n">
         <v>8167240</v>
@@ -4371,7 +4371,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G138" t="n">
-        <v>5.44086074829102</v>
+        <v>5.44086122512817</v>
       </c>
       <c r="H138" t="n">
         <v>4304794</v>
@@ -4400,7 +4400,7 @@
         <v>7.02400016784668</v>
       </c>
       <c r="G139" t="n">
-        <v>5.43621730804443</v>
+        <v>5.43621778488159</v>
       </c>
       <c r="H139" t="n">
         <v>4830708</v>
@@ -4429,7 +4429,7 @@
         <v>7.08400011062622</v>
       </c>
       <c r="G140" t="n">
-        <v>5.48265409469604</v>
+        <v>5.4826545715332</v>
       </c>
       <c r="H140" t="n">
         <v>1915810</v>
@@ -4574,7 +4574,7 @@
         <v>7.2039999961853</v>
       </c>
       <c r="G145" t="n">
-        <v>5.57552766799927</v>
+        <v>5.57552862167358</v>
       </c>
       <c r="H145" t="n">
         <v>1195513</v>
@@ -4603,7 +4603,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G146" t="n">
-        <v>5.69007205963135</v>
+        <v>5.69007301330566</v>
       </c>
       <c r="H146" t="n">
         <v>3640962</v>
@@ -4632,7 +4632,7 @@
         <v>7.28200006484985</v>
       </c>
       <c r="G147" t="n">
-        <v>5.63589668273926</v>
+        <v>5.6358962059021</v>
       </c>
       <c r="H147" t="n">
         <v>1337297</v>
@@ -4719,7 +4719,7 @@
         <v>7.26800012588501</v>
       </c>
       <c r="G150" t="n">
-        <v>5.62506103515625</v>
+        <v>5.62506008148193</v>
       </c>
       <c r="H150" t="n">
         <v>2888493</v>
@@ -4806,7 +4806,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G153" t="n">
-        <v>5.38823223114014</v>
+        <v>5.38823270797729</v>
       </c>
       <c r="H153" t="n">
         <v>3075765</v>
@@ -4835,7 +4835,7 @@
         <v>7.14400005340576</v>
       </c>
       <c r="G154" t="n">
-        <v>5.52909135818481</v>
+        <v>5.52909088134766</v>
       </c>
       <c r="H154" t="n">
         <v>3363964</v>
@@ -4864,7 +4864,7 @@
         <v>7.4539999961853</v>
       </c>
       <c r="G155" t="n">
-        <v>5.76901531219482</v>
+        <v>5.76901483535767</v>
       </c>
       <c r="H155" t="n">
         <v>12483969</v>
@@ -5009,7 +5009,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>5.89749050140381</v>
+        <v>5.89749097824097</v>
       </c>
       <c r="H160" t="n">
         <v>3125732</v>
@@ -5125,7 +5125,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G164" t="n">
-        <v>5.69626426696777</v>
+        <v>5.69626474380493</v>
       </c>
       <c r="H164" t="n">
         <v>2880645</v>
@@ -5154,7 +5154,7 @@
         <v>7.20800018310547</v>
       </c>
       <c r="G165" t="n">
-        <v>5.57862377166748</v>
+        <v>5.5786247253418</v>
       </c>
       <c r="H165" t="n">
         <v>5358633</v>
@@ -5183,7 +5183,7 @@
         <v>7.26399993896484</v>
       </c>
       <c r="G166" t="n">
-        <v>5.62196445465088</v>
+        <v>5.62196493148804</v>
       </c>
       <c r="H166" t="n">
         <v>4341174</v>
@@ -5212,7 +5212,7 @@
         <v>7.31799983978271</v>
       </c>
       <c r="G167" t="n">
-        <v>5.66375827789307</v>
+        <v>5.66375780105591</v>
       </c>
       <c r="H167" t="n">
         <v>43240003</v>
@@ -5270,7 +5270,7 @@
         <v>7.36199998855591</v>
       </c>
       <c r="G169" t="n">
-        <v>5.69781160354614</v>
+        <v>5.6978120803833</v>
       </c>
       <c r="H169" t="n">
         <v>2575130</v>
@@ -5299,7 +5299,7 @@
         <v>7.47599983215332</v>
       </c>
       <c r="G170" t="n">
-        <v>5.78604173660278</v>
+        <v>5.7860426902771</v>
       </c>
       <c r="H170" t="n">
         <v>4178875</v>
@@ -5357,7 +5357,7 @@
         <v>7.43400001525879</v>
       </c>
       <c r="G172" t="n">
-        <v>5.75353574752808</v>
+        <v>5.75353622436523</v>
       </c>
       <c r="H172" t="n">
         <v>2045405</v>
@@ -5444,7 +5444,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>5.77365970611572</v>
+        <v>5.77365922927856</v>
       </c>
       <c r="H175" t="n">
         <v>1681767</v>
@@ -5531,7 +5531,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G178" t="n">
-        <v>5.76591920852661</v>
+        <v>5.76591968536377</v>
       </c>
       <c r="H178" t="n">
         <v>3012342</v>
@@ -5560,7 +5560,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G179" t="n">
-        <v>5.72257900238037</v>
+        <v>5.72257852554321</v>
       </c>
       <c r="H179" t="n">
         <v>930343</v>
@@ -5589,7 +5589,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>5.67304515838623</v>
+        <v>5.67304563522339</v>
       </c>
       <c r="H180" t="n">
         <v>1468023</v>
@@ -5618,7 +5618,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.649827003479</v>
+        <v>5.64982652664185</v>
       </c>
       <c r="H181" t="n">
         <v>1631020</v>
@@ -5676,7 +5676,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G183" t="n">
-        <v>5.69316864013672</v>
+        <v>5.6931676864624</v>
       </c>
       <c r="H183" t="n">
         <v>1521415</v>
@@ -5763,7 +5763,7 @@
         <v>7.29199981689453</v>
       </c>
       <c r="G186" t="n">
-        <v>5.64363527297974</v>
+        <v>5.64363574981689</v>
       </c>
       <c r="H186" t="n">
         <v>2057580</v>
@@ -5821,7 +5821,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G188" t="n">
-        <v>5.53528213500977</v>
+        <v>5.53528261184692</v>
       </c>
       <c r="H188" t="n">
         <v>1687495</v>
@@ -5850,7 +5850,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G189" t="n">
-        <v>5.53528213500977</v>
+        <v>5.53528261184692</v>
       </c>
       <c r="H189" t="n">
         <v>2030021</v>
@@ -5908,7 +5908,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G191" t="n">
-        <v>5.5554051399231</v>
+        <v>5.55540561676025</v>
       </c>
       <c r="H191" t="n">
         <v>1748330</v>
@@ -5995,7 +5995,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G194" t="n">
-        <v>5.56469297409058</v>
+        <v>5.56469249725342</v>
       </c>
       <c r="H194" t="n">
         <v>2271355</v>
@@ -6024,7 +6024,7 @@
         <v>7.15799999237061</v>
       </c>
       <c r="G195" t="n">
-        <v>5.53992605209351</v>
+        <v>5.53992652893066</v>
       </c>
       <c r="H195" t="n">
         <v>2685820</v>
@@ -6169,7 +6169,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>5.47955894470215</v>
+        <v>5.47955846786499</v>
       </c>
       <c r="H200" t="n">
         <v>1257767</v>
@@ -6198,7 +6198,7 @@
         <v>7.0460000038147</v>
       </c>
       <c r="G201" t="n">
-        <v>5.45324373245239</v>
+        <v>5.45324420928955</v>
       </c>
       <c r="H201" t="n">
         <v>1269104</v>
@@ -6256,7 +6256,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G203" t="n">
-        <v>5.52754306793213</v>
+        <v>5.52754354476929</v>
       </c>
       <c r="H203" t="n">
         <v>1657489</v>
@@ -6314,7 +6314,7 @@
         <v>7.13399982452393</v>
       </c>
       <c r="G205" t="n">
-        <v>5.52135133743286</v>
+        <v>5.52135181427002</v>
       </c>
       <c r="H205" t="n">
         <v>1601027</v>
@@ -6372,7 +6372,7 @@
         <v>7.44600009918213</v>
       </c>
       <c r="G207" t="n">
-        <v>5.76282405853271</v>
+        <v>5.76282453536987</v>
       </c>
       <c r="H207" t="n">
         <v>2963238</v>
@@ -6401,7 +6401,7 @@
         <v>7.46600008010864</v>
       </c>
       <c r="G208" t="n">
-        <v>5.77830219268799</v>
+        <v>5.7783031463623</v>
       </c>
       <c r="H208" t="n">
         <v>1423117</v>
@@ -6430,7 +6430,7 @@
         <v>7.52199983596802</v>
       </c>
       <c r="G209" t="n">
-        <v>5.82164335250854</v>
+        <v>5.8216438293457</v>
       </c>
       <c r="H209" t="n">
         <v>1510800</v>
@@ -6488,7 +6488,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G211" t="n">
-        <v>5.69007205963135</v>
+        <v>5.69007301330566</v>
       </c>
       <c r="H211" t="n">
         <v>1609011</v>
@@ -6546,7 +6546,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>5.51825618743896</v>
+        <v>5.51825571060181</v>
       </c>
       <c r="H213" t="n">
         <v>1073404</v>
@@ -6575,7 +6575,7 @@
         <v>7.20800018310547</v>
       </c>
       <c r="G214" t="n">
-        <v>5.57862377166748</v>
+        <v>5.5786247253418</v>
       </c>
       <c r="H214" t="n">
         <v>1044217</v>
@@ -6691,7 +6691,7 @@
         <v>7.60400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>5.88510799407959</v>
+        <v>5.88510751724243</v>
       </c>
       <c r="H218" t="n">
         <v>1267206</v>
@@ -6720,7 +6720,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>5.88201189041138</v>
+        <v>5.88201236724854</v>
       </c>
       <c r="H219" t="n">
         <v>1419114</v>
@@ -6923,7 +6923,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G226" t="n">
-        <v>5.69626426696777</v>
+        <v>5.69626474380493</v>
       </c>
       <c r="H226" t="n">
         <v>2153061</v>
@@ -6952,7 +6952,7 @@
         <v>7.1560001373291</v>
       </c>
       <c r="G227" t="n">
-        <v>5.53837871551514</v>
+        <v>5.53837823867798</v>
       </c>
       <c r="H227" t="n">
         <v>2180122</v>
@@ -7010,7 +7010,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G229" t="n">
-        <v>5.62041711807251</v>
+        <v>5.62041616439819</v>
       </c>
       <c r="H229" t="n">
         <v>2755940</v>
@@ -7126,7 +7126,7 @@
         <v>6.86199998855591</v>
       </c>
       <c r="G233" t="n">
-        <v>5.3108377456665</v>
+        <v>5.31083726882935</v>
       </c>
       <c r="H233" t="n">
         <v>1785974</v>
@@ -7242,7 +7242,7 @@
         <v>6.67199993133545</v>
       </c>
       <c r="G237" t="n">
-        <v>5.16378736495972</v>
+        <v>5.16378784179688</v>
       </c>
       <c r="H237" t="n">
         <v>1786947</v>
@@ -7271,7 +7271,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G238" t="n">
-        <v>5.36346626281738</v>
+        <v>5.36346673965454</v>
       </c>
       <c r="H238" t="n">
         <v>2787477</v>
@@ -7329,7 +7329,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G240" t="n">
-        <v>5.49813318252563</v>
+        <v>5.49813270568848</v>
       </c>
       <c r="H240" t="n">
         <v>2318680</v>
@@ -7387,7 +7387,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G242" t="n">
-        <v>5.49813318252563</v>
+        <v>5.49813270568848</v>
       </c>
       <c r="H242" t="n">
         <v>1618816</v>
@@ -7416,7 +7416,7 @@
         <v>7.22200012207031</v>
       </c>
       <c r="G243" t="n">
-        <v>5.58945941925049</v>
+        <v>5.58945846557617</v>
       </c>
       <c r="H243" t="n">
         <v>2092114</v>
@@ -7445,7 +7445,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G244" t="n">
-        <v>5.55695247650146</v>
+        <v>5.55695343017578</v>
       </c>
       <c r="H244" t="n">
         <v>1426893</v>
@@ -7474,7 +7474,7 @@
         <v>7.18800020217896</v>
       </c>
       <c r="G245" t="n">
-        <v>5.56314420700073</v>
+        <v>5.56314516067505</v>
       </c>
       <c r="H245" t="n">
         <v>1349255</v>
@@ -7503,7 +7503,7 @@
         <v>7.20599985122681</v>
       </c>
       <c r="G246" t="n">
-        <v>5.57707595825195</v>
+        <v>5.57707500457764</v>
       </c>
       <c r="H246" t="n">
         <v>1630112</v>
@@ -7590,7 +7590,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G249" t="n">
-        <v>5.4857497215271</v>
+        <v>5.48574876785278</v>
       </c>
       <c r="H249" t="n">
         <v>1354493</v>
@@ -7706,7 +7706,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G253" t="n">
-        <v>5.56624126434326</v>
+        <v>5.5662407875061</v>
       </c>
       <c r="H253" t="n">
         <v>1107860</v>
@@ -7851,7 +7851,7 @@
         <v>6.56599998474121</v>
       </c>
       <c r="G258" t="n">
-        <v>5.0817494392395</v>
+        <v>5.08174848556519</v>
       </c>
       <c r="H258" t="n">
         <v>2220756</v>
@@ -7996,7 +7996,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G263" t="n">
-        <v>4.84646844863892</v>
+        <v>4.84646797180176</v>
       </c>
       <c r="H263" t="n">
         <v>1904690</v>
@@ -8025,7 +8025,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>4.99197053909302</v>
+        <v>4.99197006225586</v>
       </c>
       <c r="H264" t="n">
         <v>2054662</v>
@@ -8054,7 +8054,7 @@
         <v>6.24200010299683</v>
       </c>
       <c r="G265" t="n">
-        <v>4.83098983764648</v>
+        <v>4.83098936080933</v>
       </c>
       <c r="H265" t="n">
         <v>1949193</v>
@@ -8141,7 +8141,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G268" t="n">
-        <v>4.57094240188599</v>
+        <v>4.57094287872314</v>
       </c>
       <c r="H268" t="n">
         <v>3844094</v>
@@ -8170,7 +8170,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G269" t="n">
-        <v>4.53534030914307</v>
+        <v>4.53534078598022</v>
       </c>
       <c r="H269" t="n">
         <v>2387790</v>
@@ -8199,7 +8199,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G270" t="n">
-        <v>4.53534030914307</v>
+        <v>4.53534078598022</v>
       </c>
       <c r="H270" t="n">
         <v>3415835</v>
@@ -8257,7 +8257,7 @@
         <v>6.2480001449585</v>
       </c>
       <c r="G272" t="n">
-        <v>4.83563327789307</v>
+        <v>4.83563280105591</v>
       </c>
       <c r="H272" t="n">
         <v>2873517</v>
@@ -8286,7 +8286,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G273" t="n">
-        <v>4.91457557678223</v>
+        <v>4.91457605361938</v>
       </c>
       <c r="H273" t="n">
         <v>3077722</v>
@@ -8315,7 +8315,7 @@
         <v>6.53800010681152</v>
       </c>
       <c r="G274" t="n">
-        <v>5.06007862091064</v>
+        <v>5.06007814407349</v>
       </c>
       <c r="H274" t="n">
         <v>2925266</v>
@@ -8344,7 +8344,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G275" t="n">
-        <v>5.02602434158325</v>
+        <v>5.02602386474609</v>
       </c>
       <c r="H275" t="n">
         <v>3419765</v>
@@ -8373,7 +8373,7 @@
         <v>6.44600009918213</v>
       </c>
       <c r="G276" t="n">
-        <v>4.98887395858765</v>
+        <v>4.98887491226196</v>
       </c>
       <c r="H276" t="n">
         <v>1300076</v>
@@ -8402,7 +8402,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G277" t="n">
-        <v>4.94088983535767</v>
+        <v>4.94088935852051</v>
       </c>
       <c r="H277" t="n">
         <v>2480733</v>
@@ -8431,7 +8431,7 @@
         <v>6.34600019454956</v>
       </c>
       <c r="G278" t="n">
-        <v>4.91148042678833</v>
+        <v>4.91147947311401</v>
       </c>
       <c r="H278" t="n">
         <v>2104958</v>
@@ -8489,7 +8489,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>5.0151891708374</v>
+        <v>5.01518869400024</v>
       </c>
       <c r="H280" t="n">
         <v>1181822</v>
@@ -8518,7 +8518,7 @@
         <v>6.33599996566772</v>
       </c>
       <c r="G281" t="n">
-        <v>4.90374088287354</v>
+        <v>4.90374040603638</v>
       </c>
       <c r="H281" t="n">
         <v>1475144</v>
@@ -8605,7 +8605,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G284" t="n">
-        <v>4.63440561294556</v>
+        <v>4.63440608978271</v>
       </c>
       <c r="H284" t="n">
         <v>2793354</v>
@@ -8692,7 +8692,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G287" t="n">
-        <v>4.80467462539673</v>
+        <v>4.80467510223389</v>
       </c>
       <c r="H287" t="n">
         <v>1577631</v>
@@ -8721,7 +8721,7 @@
         <v>6.29199981689453</v>
       </c>
       <c r="G288" t="n">
-        <v>4.8696870803833</v>
+        <v>4.86968660354614</v>
       </c>
       <c r="H288" t="n">
         <v>1424566</v>
@@ -8837,7 +8837,7 @@
         <v>6.42399978637695</v>
       </c>
       <c r="G292" t="n">
-        <v>4.97184801101685</v>
+        <v>4.97184753417969</v>
       </c>
       <c r="H292" t="n">
         <v>854708</v>
@@ -8866,7 +8866,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G293" t="n">
-        <v>5.02602434158325</v>
+        <v>5.02602386474609</v>
       </c>
       <c r="H293" t="n">
         <v>2085690</v>
@@ -8924,7 +8924,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G295" t="n">
-        <v>4.79848289489746</v>
+        <v>4.79848337173462</v>
       </c>
       <c r="H295" t="n">
         <v>2235148</v>
@@ -8953,7 +8953,7 @@
         <v>6.24399995803833</v>
       </c>
       <c r="G296" t="n">
-        <v>4.8325366973877</v>
+        <v>4.83253717422485</v>
       </c>
       <c r="H296" t="n">
         <v>1047482</v>
@@ -8982,7 +8982,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G297" t="n">
-        <v>4.80467462539673</v>
+        <v>4.80467510223389</v>
       </c>
       <c r="H297" t="n">
         <v>2974670</v>
@@ -9011,7 +9011,7 @@
         <v>6.43400001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>4.97958755493164</v>
+        <v>4.97958707809448</v>
       </c>
       <c r="H298" t="n">
         <v>2398005</v>
@@ -9098,7 +9098,7 @@
         <v>6.00400018692017</v>
       </c>
       <c r="G301" t="n">
-        <v>4.64678955078125</v>
+        <v>4.64678907394409</v>
       </c>
       <c r="H301" t="n">
         <v>2292669</v>
@@ -9156,7 +9156,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G303" t="n">
-        <v>4.53534030914307</v>
+        <v>4.53534078598022</v>
       </c>
       <c r="H303" t="n">
         <v>1541621</v>
@@ -9185,7 +9185,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G304" t="n">
-        <v>4.55855894088745</v>
+        <v>4.55855941772461</v>
       </c>
       <c r="H304" t="n">
         <v>2287721</v>
@@ -9214,7 +9214,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>4.58487367630005</v>
+        <v>4.58487272262573</v>
       </c>
       <c r="H305" t="n">
         <v>1600933</v>
@@ -9301,7 +9301,7 @@
         <v>5.72599983215332</v>
       </c>
       <c r="G308" t="n">
-        <v>4.43163061141968</v>
+        <v>4.43163108825684</v>
       </c>
       <c r="H308" t="n">
         <v>1935193</v>
@@ -9330,7 +9330,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G309" t="n">
-        <v>4.38674211502075</v>
+        <v>4.38674306869507</v>
       </c>
       <c r="H309" t="n">
         <v>2277365</v>
@@ -9388,7 +9388,7 @@
         <v>5.60799980163574</v>
       </c>
       <c r="G311" t="n">
-        <v>4.34030485153198</v>
+        <v>4.3403058052063</v>
       </c>
       <c r="H311" t="n">
         <v>1673261</v>
@@ -9475,7 +9475,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G314" t="n">
-        <v>4.34185409545898</v>
+        <v>4.34185314178467</v>
       </c>
       <c r="H314" t="n">
         <v>1120253</v>
@@ -9533,7 +9533,7 @@
         <v>5.44600009918213</v>
       </c>
       <c r="G316" t="n">
-        <v>4.21492624282837</v>
+        <v>4.21492576599121</v>
       </c>
       <c r="H316" t="n">
         <v>1823690</v>
@@ -9591,7 +9591,7 @@
         <v>5.63800001144409</v>
       </c>
       <c r="G318" t="n">
-        <v>4.36352396011353</v>
+        <v>4.36352491378784</v>
       </c>
       <c r="H318" t="n">
         <v>2183353</v>
@@ -9794,7 +9794,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>4.65917205810547</v>
+        <v>4.65917253494263</v>
       </c>
       <c r="H325" t="n">
         <v>2339314</v>
@@ -9910,7 +9910,7 @@
         <v>6.02799987792969</v>
       </c>
       <c r="G329" t="n">
-        <v>4.66536331176758</v>
+        <v>4.66536426544189</v>
       </c>
       <c r="H329" t="n">
         <v>1011597</v>
@@ -9939,7 +9939,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G330" t="n">
-        <v>4.63440561294556</v>
+        <v>4.63440608978271</v>
       </c>
       <c r="H330" t="n">
         <v>914177</v>
@@ -9997,7 +9997,7 @@
         <v>6.04400014877319</v>
       </c>
       <c r="G332" t="n">
-        <v>4.67774772644043</v>
+        <v>4.67774724960327</v>
       </c>
       <c r="H332" t="n">
         <v>2309782</v>
@@ -10084,7 +10084,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>4.55855894088745</v>
+        <v>4.55855941772461</v>
       </c>
       <c r="H335" t="n">
         <v>1559842</v>
@@ -10142,7 +10142,7 @@
         <v>5.69799995422363</v>
       </c>
       <c r="G337" t="n">
-        <v>4.40996074676514</v>
+        <v>4.40996122360229</v>
       </c>
       <c r="H337" t="n">
         <v>2706905</v>
@@ -10171,7 +10171,7 @@
         <v>5.77600002288818</v>
       </c>
       <c r="G338" t="n">
-        <v>4.47032928466797</v>
+        <v>4.47032880783081</v>
       </c>
       <c r="H338" t="n">
         <v>1791028</v>
@@ -10200,7 +10200,7 @@
         <v>5.98199987411499</v>
       </c>
       <c r="G339" t="n">
-        <v>4.62976169586182</v>
+        <v>4.62976264953613</v>
       </c>
       <c r="H339" t="n">
         <v>2743128</v>
@@ -10229,7 +10229,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G340" t="n">
-        <v>4.68239068984985</v>
+        <v>4.68239116668701</v>
       </c>
       <c r="H340" t="n">
         <v>2404799</v>
@@ -10258,7 +10258,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G341" t="n">
-        <v>4.49199962615967</v>
+        <v>4.49200010299683</v>
       </c>
       <c r="H341" t="n">
         <v>3253843</v>
@@ -10345,7 +10345,7 @@
         <v>6.06799983978271</v>
       </c>
       <c r="G344" t="n">
-        <v>4.69632244110107</v>
+        <v>4.69632196426392</v>
       </c>
       <c r="H344" t="n">
         <v>4045783</v>
@@ -10432,7 +10432,7 @@
         <v>6.07399988174438</v>
       </c>
       <c r="G347" t="n">
-        <v>4.70096635818481</v>
+        <v>4.7009654045105</v>
       </c>
       <c r="H347" t="n">
         <v>3636485</v>
@@ -10490,7 +10490,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G349" t="n">
-        <v>4.55855894088745</v>
+        <v>4.55855941772461</v>
       </c>
       <c r="H349" t="n">
         <v>1804076</v>
@@ -10606,7 +10606,7 @@
         <v>6.05800008773804</v>
       </c>
       <c r="G353" t="n">
-        <v>4.68858242034912</v>
+        <v>4.68858289718628</v>
       </c>
       <c r="H353" t="n">
         <v>1813455</v>
@@ -10809,7 +10809,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G360" t="n">
-        <v>4.67465114593506</v>
+        <v>4.67465162277222</v>
       </c>
       <c r="H360" t="n">
         <v>1624225</v>
@@ -10838,7 +10838,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>4.65917205810547</v>
+        <v>4.65917253494263</v>
       </c>
       <c r="H361" t="n">
         <v>2666267</v>
@@ -10867,7 +10867,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G362" t="n">
-        <v>4.54772329330444</v>
+        <v>4.5477237701416</v>
       </c>
       <c r="H362" t="n">
         <v>1919771</v>
@@ -10925,7 +10925,7 @@
         <v>5.76800012588501</v>
       </c>
       <c r="G364" t="n">
-        <v>4.4641375541687</v>
+        <v>4.46413707733154</v>
       </c>
       <c r="H364" t="n">
         <v>3500087</v>
@@ -10954,7 +10954,7 @@
         <v>5.80600023269653</v>
       </c>
       <c r="G365" t="n">
-        <v>4.49354791641235</v>
+        <v>4.49354696273804</v>
       </c>
       <c r="H365" t="n">
         <v>2427346</v>
@@ -10983,7 +10983,7 @@
         <v>5.83799982070923</v>
       </c>
       <c r="G366" t="n">
-        <v>4.51831388473511</v>
+        <v>4.51831340789795</v>
       </c>
       <c r="H366" t="n">
         <v>2273085</v>
@@ -11041,7 +11041,7 @@
         <v>5.97200012207031</v>
       </c>
       <c r="G368" t="n">
-        <v>4.62202262878418</v>
+        <v>4.6220235824585</v>
       </c>
       <c r="H368" t="n">
         <v>1871770</v>
@@ -11070,7 +11070,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G369" t="n">
-        <v>4.67000722885132</v>
+        <v>4.67000770568848</v>
       </c>
       <c r="H369" t="n">
         <v>2627829</v>
@@ -11099,7 +11099,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G370" t="n">
-        <v>4.67000722885132</v>
+        <v>4.67000770568848</v>
       </c>
       <c r="H370" t="n">
         <v>1424349</v>
@@ -11157,7 +11157,7 @@
         <v>5.93400001525879</v>
       </c>
       <c r="G372" t="n">
-        <v>4.59261322021484</v>
+        <v>4.59261274337769</v>
       </c>
       <c r="H372" t="n">
         <v>2169132</v>
@@ -11215,7 +11215,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G374" t="n">
-        <v>4.53069734573364</v>
+        <v>4.53069686889648</v>
       </c>
       <c r="H374" t="n">
         <v>1872965</v>
@@ -11244,7 +11244,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G375" t="n">
-        <v>4.47342443466187</v>
+        <v>4.47342491149902</v>
       </c>
       <c r="H375" t="n">
         <v>2288738</v>
@@ -11302,7 +11302,7 @@
         <v>5.73799991607666</v>
       </c>
       <c r="G377" t="n">
-        <v>4.44091892242432</v>
+        <v>4.44091844558716</v>
       </c>
       <c r="H377" t="n">
         <v>2321157</v>
@@ -11331,7 +11331,7 @@
         <v>5.82800006866455</v>
       </c>
       <c r="G378" t="n">
-        <v>4.51057434082031</v>
+        <v>4.51057481765747</v>
       </c>
       <c r="H378" t="n">
         <v>3033773</v>
@@ -11389,7 +11389,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G380" t="n">
-        <v>4.79848289489746</v>
+        <v>4.79848337173462</v>
       </c>
       <c r="H380" t="n">
         <v>4188895</v>
@@ -11418,7 +11418,7 @@
         <v>6.24599981307983</v>
       </c>
       <c r="G381" t="n">
-        <v>4.83408498764038</v>
+        <v>4.83408451080322</v>
       </c>
       <c r="H381" t="n">
         <v>2344904</v>
@@ -11563,7 +11563,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G386" t="n">
-        <v>4.91612386703491</v>
+        <v>4.91612339019775</v>
       </c>
       <c r="H386" t="n">
         <v>2103203</v>
@@ -11592,7 +11592,7 @@
         <v>6.60200023651123</v>
       </c>
       <c r="G387" t="n">
-        <v>5.10961103439331</v>
+        <v>5.10961151123047</v>
       </c>
       <c r="H387" t="n">
         <v>3211150</v>
@@ -11650,7 +11650,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G389" t="n">
-        <v>5.02757215499878</v>
+        <v>5.02757167816162</v>
       </c>
       <c r="H389" t="n">
         <v>1436659</v>
@@ -11679,7 +11679,7 @@
         <v>6.5</v>
       </c>
       <c r="G390" t="n">
-        <v>5.03066825866699</v>
+        <v>5.03066778182983</v>
       </c>
       <c r="H390" t="n">
         <v>1844285</v>
@@ -11737,7 +11737,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G392" t="n">
-        <v>4.96875190734863</v>
+        <v>4.96875238418579</v>
       </c>
       <c r="H392" t="n">
         <v>2044749</v>
@@ -11766,7 +11766,7 @@
         <v>6.44199991226196</v>
       </c>
       <c r="G393" t="n">
-        <v>4.98577928543091</v>
+        <v>4.98577880859375</v>
       </c>
       <c r="H393" t="n">
         <v>2979080</v>
@@ -11795,7 +11795,7 @@
         <v>6.4060001373291</v>
       </c>
       <c r="G394" t="n">
-        <v>4.95791673660278</v>
+        <v>4.95791721343994</v>
       </c>
       <c r="H394" t="n">
         <v>1161802</v>
@@ -11824,7 +11824,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G395" t="n">
-        <v>5.02602434158325</v>
+        <v>5.02602386474609</v>
       </c>
       <c r="H395" t="n">
         <v>1755876</v>
@@ -11911,7 +11911,7 @@
         <v>6.30600023269653</v>
       </c>
       <c r="G398" t="n">
-        <v>4.88052225112915</v>
+        <v>4.88052177429199</v>
       </c>
       <c r="H398" t="n">
         <v>1489174</v>
@@ -11940,7 +11940,7 @@
         <v>6.17799997329712</v>
       </c>
       <c r="G399" t="n">
-        <v>4.78145599365234</v>
+        <v>4.7814564704895</v>
       </c>
       <c r="H399" t="n">
         <v>2777477</v>
@@ -11998,7 +11998,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G401" t="n">
-        <v>4.55081987380981</v>
+        <v>4.55081939697266</v>
       </c>
       <c r="H401" t="n">
         <v>2736466</v>
@@ -12085,7 +12085,7 @@
         <v>5.72800016403198</v>
       </c>
       <c r="G404" t="n">
-        <v>4.43318033218384</v>
+        <v>4.43317937850952</v>
       </c>
       <c r="H404" t="n">
         <v>2771135</v>
@@ -12114,7 +12114,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G405" t="n">
-        <v>4.34185409545898</v>
+        <v>4.34185314178467</v>
       </c>
       <c r="H405" t="n">
         <v>2818219</v>
@@ -12143,7 +12143,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G406" t="n">
-        <v>4.40376949310303</v>
+        <v>4.40376901626587</v>
       </c>
       <c r="H406" t="n">
         <v>2618707</v>
@@ -12172,7 +12172,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G407" t="n">
-        <v>4.53069734573364</v>
+        <v>4.53069686889648</v>
       </c>
       <c r="H407" t="n">
         <v>6401824</v>
@@ -12259,7 +12259,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G410" t="n">
-        <v>4.37493562698364</v>
+        <v>4.3749361038208</v>
       </c>
       <c r="H410" t="n">
         <v>2918482</v>
@@ -12288,7 +12288,7 @@
         <v>5.57600021362305</v>
       </c>
       <c r="G411" t="n">
-        <v>4.45157718658447</v>
+        <v>4.45157670974731</v>
       </c>
       <c r="H411" t="n">
         <v>2546416</v>
@@ -12317,7 +12317,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G412" t="n">
-        <v>4.36695194244385</v>
+        <v>4.36695241928101</v>
       </c>
       <c r="H412" t="n">
         <v>1777324</v>
@@ -12346,7 +12346,7 @@
         <v>5.34800004959106</v>
       </c>
       <c r="G413" t="n">
-        <v>4.26955413818359</v>
+        <v>4.26955366134644</v>
       </c>
       <c r="H413" t="n">
         <v>2649682</v>
@@ -12375,7 +12375,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G414" t="n">
-        <v>4.25039291381836</v>
+        <v>4.25039386749268</v>
       </c>
       <c r="H414" t="n">
         <v>1953616</v>
@@ -12404,7 +12404,7 @@
         <v>5.23400020599365</v>
       </c>
       <c r="G415" t="n">
-        <v>4.17854261398315</v>
+        <v>4.17854309082031</v>
       </c>
       <c r="H415" t="n">
         <v>1839026</v>
@@ -12433,7 +12433,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G416" t="n">
-        <v>4.14660882949829</v>
+        <v>4.14660835266113</v>
       </c>
       <c r="H416" t="n">
         <v>3138975</v>
@@ -12491,7 +12491,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G418" t="n">
-        <v>4.14341592788696</v>
+        <v>4.1434154510498</v>
       </c>
       <c r="H418" t="n">
         <v>2326150</v>
@@ -12549,7 +12549,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G420" t="n">
-        <v>4.08114433288574</v>
+        <v>4.08114385604858</v>
       </c>
       <c r="H420" t="n">
         <v>2549135</v>
@@ -12665,7 +12665,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G424" t="n">
-        <v>4.14341592788696</v>
+        <v>4.1434154510498</v>
       </c>
       <c r="H424" t="n">
         <v>1701343</v>
@@ -12723,7 +12723,7 @@
         <v>5.32800006866455</v>
       </c>
       <c r="G426" t="n">
-        <v>4.25358724594116</v>
+        <v>4.253586769104</v>
       </c>
       <c r="H426" t="n">
         <v>1782929</v>
@@ -12752,7 +12752,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G427" t="n">
-        <v>4.13223886489868</v>
+        <v>4.13223838806152</v>
       </c>
       <c r="H427" t="n">
         <v>2230171</v>
@@ -12810,7 +12810,7 @@
         <v>5.29199981689453</v>
       </c>
       <c r="G429" t="n">
-        <v>4.22484588623047</v>
+        <v>4.22484636306763</v>
       </c>
       <c r="H429" t="n">
         <v>2364383</v>
@@ -12839,7 +12839,7 @@
         <v>5.2519998550415</v>
       </c>
       <c r="G430" t="n">
-        <v>4.19291210174561</v>
+        <v>4.19291257858276</v>
       </c>
       <c r="H430" t="n">
         <v>1071567</v>
@@ -12926,7 +12926,7 @@
         <v>5.47599983215332</v>
       </c>
       <c r="G433" t="n">
-        <v>4.37174224853516</v>
+        <v>4.371741771698</v>
       </c>
       <c r="H433" t="n">
         <v>2847131</v>
@@ -13042,7 +13042,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>4.23123264312744</v>
+        <v>4.23123359680176</v>
       </c>
       <c r="H437" t="n">
         <v>3128652</v>
@@ -13100,7 +13100,7 @@
         <v>5.19799995422363</v>
       </c>
       <c r="G439" t="n">
-        <v>4.14980220794678</v>
+        <v>4.14980173110962</v>
       </c>
       <c r="H439" t="n">
         <v>3592521</v>
@@ -13129,7 +13129,7 @@
         <v>5.30600023269653</v>
       </c>
       <c r="G440" t="n">
-        <v>4.23602294921875</v>
+        <v>4.23602342605591</v>
       </c>
       <c r="H440" t="n">
         <v>3874778</v>
@@ -13216,7 +13216,7 @@
         <v>5.3439998626709</v>
       </c>
       <c r="G443" t="n">
-        <v>4.26635980606079</v>
+        <v>4.26636028289795</v>
       </c>
       <c r="H443" t="n">
         <v>2105073</v>
@@ -13245,7 +13245,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>4.23123264312744</v>
+        <v>4.23123359680176</v>
       </c>
       <c r="H444" t="n">
         <v>2016439</v>
@@ -13303,7 +13303,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G446" t="n">
-        <v>4.25039291381836</v>
+        <v>4.25039386749268</v>
       </c>
       <c r="H446" t="n">
         <v>4262357</v>
@@ -13361,7 +13361,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G448" t="n">
-        <v>4.40367555618286</v>
+        <v>4.40367603302002</v>
       </c>
       <c r="H448" t="n">
         <v>3767418</v>
@@ -13419,7 +13419,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54737901687622</v>
+        <v>4.54737854003906</v>
       </c>
       <c r="H450" t="n">
         <v>4693010</v>
@@ -13506,7 +13506,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G453" t="n">
-        <v>4.15139818191528</v>
+        <v>4.15139865875244</v>
       </c>
       <c r="H453" t="n">
         <v>4787912</v>
@@ -13535,7 +13535,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G454" t="n">
-        <v>4.14022159576416</v>
+        <v>4.14022207260132</v>
       </c>
       <c r="H454" t="n">
         <v>4361773</v>
@@ -13564,7 +13564,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G455" t="n">
-        <v>4.17534971237183</v>
+        <v>4.17534923553467</v>
       </c>
       <c r="H455" t="n">
         <v>2187865</v>
@@ -13593,7 +13593,7 @@
         <v>5.68200016021729</v>
       </c>
       <c r="G456" t="n">
-        <v>4.53620195388794</v>
+        <v>4.53620147705078</v>
       </c>
       <c r="H456" t="n">
         <v>11735893</v>
@@ -13680,7 +13680,7 @@
         <v>5.60799980163574</v>
       </c>
       <c r="G459" t="n">
-        <v>4.47712326049805</v>
+        <v>4.47712373733521</v>
       </c>
       <c r="H459" t="n">
         <v>3761167</v>
@@ -13767,7 +13767,7 @@
         <v>5.3439998626709</v>
       </c>
       <c r="G462" t="n">
-        <v>4.26635980606079</v>
+        <v>4.26636028289795</v>
       </c>
       <c r="H462" t="n">
         <v>2651816</v>
@@ -13825,7 +13825,7 @@
         <v>5.01599979400635</v>
       </c>
       <c r="G464" t="n">
-        <v>4.00450372695923</v>
+        <v>4.00450277328491</v>
       </c>
       <c r="H464" t="n">
         <v>10393285</v>
@@ -13912,7 +13912,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G467" t="n">
-        <v>3.79373955726624</v>
+        <v>3.79373931884766</v>
       </c>
       <c r="H467" t="n">
         <v>3659216</v>
@@ -13941,7 +13941,7 @@
         <v>4.85699987411499</v>
       </c>
       <c r="G468" t="n">
-        <v>3.87756609916687</v>
+        <v>3.87756562232971</v>
       </c>
       <c r="H468" t="n">
         <v>1900796</v>
@@ -13970,7 +13970,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>3.70831704139709</v>
+        <v>3.70831656455994</v>
       </c>
       <c r="H469" t="n">
         <v>4777891</v>
@@ -14028,7 +14028,7 @@
         <v>4.75299978256226</v>
       </c>
       <c r="G471" t="n">
-        <v>3.79453802108765</v>
+        <v>3.79453825950623</v>
       </c>
       <c r="H471" t="n">
         <v>4709323</v>
@@ -14057,7 +14057,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G472" t="n">
-        <v>3.64444899559021</v>
+        <v>3.64444947242737</v>
       </c>
       <c r="H472" t="n">
         <v>2861060</v>
@@ -14086,7 +14086,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G473" t="n">
-        <v>3.60532975196838</v>
+        <v>3.60532999038696</v>
       </c>
       <c r="H473" t="n">
         <v>4311711</v>
@@ -14115,7 +14115,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G474" t="n">
-        <v>3.67957639694214</v>
+        <v>3.67957663536072</v>
       </c>
       <c r="H474" t="n">
         <v>2548271</v>
@@ -14202,7 +14202,7 @@
         <v>4.81300020217896</v>
       </c>
       <c r="G477" t="n">
-        <v>3.84243869781494</v>
+        <v>3.8424391746521</v>
       </c>
       <c r="H477" t="n">
         <v>2898616</v>
@@ -14231,7 +14231,7 @@
         <v>4.6729998588562</v>
       </c>
       <c r="G478" t="n">
-        <v>3.73067045211792</v>
+        <v>3.73067021369934</v>
       </c>
       <c r="H478" t="n">
         <v>2579458</v>
@@ -14260,7 +14260,7 @@
         <v>4.74100017547607</v>
       </c>
       <c r="G479" t="n">
-        <v>3.78495788574219</v>
+        <v>3.78495812416077</v>
       </c>
       <c r="H479" t="n">
         <v>1283763</v>
@@ -14318,7 +14318,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.82407736778259</v>
+        <v>3.82407689094543</v>
       </c>
       <c r="H481" t="n">
         <v>1581513</v>
@@ -14405,7 +14405,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>3.76020908355713</v>
+        <v>3.76020956039429</v>
       </c>
       <c r="H484" t="n">
         <v>1701361</v>
@@ -14434,7 +14434,7 @@
         <v>4.6729998588562</v>
       </c>
       <c r="G485" t="n">
-        <v>3.73067045211792</v>
+        <v>3.73067021369934</v>
       </c>
       <c r="H485" t="n">
         <v>1812903</v>
@@ -14492,7 +14492,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G487" t="n">
-        <v>4.0683708190918</v>
+        <v>4.06837129592896</v>
       </c>
       <c r="H487" t="n">
         <v>4111709</v>
@@ -14521,7 +14521,7 @@
         <v>5.13199996948242</v>
       </c>
       <c r="G488" t="n">
-        <v>4.09711074829102</v>
+        <v>4.09711170196533</v>
       </c>
       <c r="H488" t="n">
         <v>4550769</v>
@@ -14637,7 +14637,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>4.42283630371094</v>
+        <v>4.42283582687378</v>
       </c>
       <c r="H492" t="n">
         <v>5033717</v>
@@ -14666,7 +14666,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G493" t="n">
-        <v>4.51863765716553</v>
+        <v>4.51863813400269</v>
       </c>
       <c r="H493" t="n">
         <v>5379056</v>
@@ -14724,7 +14724,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G495" t="n">
-        <v>4.49468803405762</v>
+        <v>4.49468755722046</v>
       </c>
       <c r="H495" t="n">
         <v>4049726</v>
@@ -14782,7 +14782,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G497" t="n">
-        <v>4.56973171234131</v>
+        <v>4.56973218917847</v>
       </c>
       <c r="H497" t="n">
         <v>2885842</v>
@@ -14956,7 +14956,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>4.42283630371094</v>
+        <v>4.42283582687378</v>
       </c>
       <c r="H503" t="n">
         <v>2428806</v>
@@ -14985,7 +14985,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G504" t="n">
-        <v>4.33342170715332</v>
+        <v>4.33342123031616</v>
       </c>
       <c r="H504" t="n">
         <v>3521555</v>
@@ -15014,7 +15014,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G505" t="n">
-        <v>4.33022785186768</v>
+        <v>4.33022832870483</v>
       </c>
       <c r="H505" t="n">
         <v>3746928</v>
@@ -15275,7 +15275,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G514" t="n">
-        <v>4.33342170715332</v>
+        <v>4.33342123031616</v>
       </c>
       <c r="H514" t="n">
         <v>1809786</v>
@@ -15333,7 +15333,7 @@
         <v>5.69399976730347</v>
       </c>
       <c r="G516" t="n">
-        <v>4.54578113555908</v>
+        <v>4.54578161239624</v>
       </c>
       <c r="H516" t="n">
         <v>2588388</v>
@@ -15565,7 +15565,7 @@
         <v>5.82399988174438</v>
       </c>
       <c r="G524" t="n">
-        <v>4.64956617355347</v>
+        <v>4.64956665039062</v>
       </c>
       <c r="H524" t="n">
         <v>9256252</v>
@@ -15594,7 +15594,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G525" t="n">
-        <v>4.63679313659668</v>
+        <v>4.63679265975952</v>
       </c>
       <c r="H525" t="n">
         <v>3552700</v>
@@ -15710,7 +15710,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G529" t="n">
-        <v>4.32703495025635</v>
+        <v>4.32703447341919</v>
       </c>
       <c r="H529" t="n">
         <v>6851432</v>
@@ -15797,7 +15797,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>4.37493562698364</v>
+        <v>4.3749361038208</v>
       </c>
       <c r="H532" t="n">
         <v>6191056</v>
@@ -15913,7 +15913,7 @@
         <v>5.36199998855591</v>
       </c>
       <c r="G536" t="n">
-        <v>4.28073120117188</v>
+        <v>4.28073072433472</v>
       </c>
       <c r="H536" t="n">
         <v>3783144</v>
@@ -15942,7 +15942,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G537" t="n">
-        <v>4.22644376754761</v>
+        <v>4.22644233703613</v>
       </c>
       <c r="H537" t="n">
         <v>3102583</v>
@@ -16029,7 +16029,7 @@
         <v>5.21400022506714</v>
       </c>
       <c r="G540" t="n">
-        <v>4.16257572174072</v>
+        <v>4.16257619857788</v>
       </c>
       <c r="H540" t="n">
         <v>4373570</v>
@@ -16058,7 +16058,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>4.14341592788696</v>
+        <v>4.1434154510498</v>
       </c>
       <c r="H541" t="n">
         <v>3194214</v>
@@ -16116,7 +16116,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G543" t="n">
-        <v>4.13543128967285</v>
+        <v>4.13543176651001</v>
       </c>
       <c r="H543" t="n">
         <v>2630136</v>
@@ -16174,7 +16174,7 @@
         <v>5.39200019836426</v>
       </c>
       <c r="G545" t="n">
-        <v>4.30468082427979</v>
+        <v>4.30468130111694</v>
       </c>
       <c r="H545" t="n">
         <v>5095042</v>
@@ -16203,7 +16203,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G546" t="n">
-        <v>4.22644376754761</v>
+        <v>4.22644233703613</v>
       </c>
       <c r="H546" t="n">
         <v>3708846</v>
@@ -16232,7 +16232,7 @@
         <v>5.26399993896484</v>
       </c>
       <c r="G547" t="n">
-        <v>4.20249319076538</v>
+        <v>4.20249271392822</v>
       </c>
       <c r="H547" t="n">
         <v>2102478</v>
@@ -16319,7 +16319,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G550" t="n">
-        <v>4.03164720535278</v>
+        <v>4.03164672851562</v>
       </c>
       <c r="H550" t="n">
         <v>2770919</v>
@@ -16377,7 +16377,7 @@
         <v>5.07800006866455</v>
       </c>
       <c r="G552" t="n">
-        <v>4.05400037765503</v>
+        <v>4.05400085449219</v>
       </c>
       <c r="H552" t="n">
         <v>2112005</v>
@@ -16406,7 +16406,7 @@
         <v>5.14200019836426</v>
       </c>
       <c r="G553" t="n">
-        <v>4.10509443283081</v>
+        <v>4.10509538650513</v>
       </c>
       <c r="H553" t="n">
         <v>1526086</v>
@@ -16464,7 +16464,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G555" t="n">
-        <v>4.10669183731079</v>
+        <v>4.10669136047363</v>
       </c>
       <c r="H555" t="n">
         <v>2487463</v>
@@ -16522,7 +16522,7 @@
         <v>5.28200006484985</v>
       </c>
       <c r="G557" t="n">
-        <v>4.21686315536499</v>
+        <v>4.21686267852783</v>
       </c>
       <c r="H557" t="n">
         <v>3347161</v>
@@ -16580,7 +16580,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G559" t="n">
-        <v>4.24560356140137</v>
+        <v>4.24560308456421</v>
       </c>
       <c r="H559" t="n">
         <v>1914778</v>
@@ -16609,7 +16609,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G560" t="n">
-        <v>4.20089673995972</v>
+        <v>4.20089626312256</v>
       </c>
       <c r="H560" t="n">
         <v>1839922</v>
@@ -16638,7 +16638,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G561" t="n">
-        <v>4.16576910018921</v>
+        <v>4.16576862335205</v>
       </c>
       <c r="H561" t="n">
         <v>2216343</v>
@@ -16667,7 +16667,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G562" t="n">
-        <v>4.09870719909668</v>
+        <v>4.09870767593384</v>
       </c>
       <c r="H562" t="n">
         <v>3351858</v>
@@ -16696,7 +16696,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G563" t="n">
-        <v>4.15778589248657</v>
+        <v>4.15778541564941</v>
       </c>
       <c r="H563" t="n">
         <v>4069219</v>
@@ -16754,7 +16754,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G565" t="n">
-        <v>4.15299510955811</v>
+        <v>4.15299558639526</v>
       </c>
       <c r="H565" t="n">
         <v>1322873</v>
@@ -16899,7 +16899,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G570" t="n">
-        <v>4.16576910018921</v>
+        <v>4.16576862335205</v>
       </c>
       <c r="H570" t="n">
         <v>3604289</v>
@@ -16928,7 +16928,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G571" t="n">
-        <v>4.24720001220703</v>
+        <v>4.24720048904419</v>
       </c>
       <c r="H571" t="n">
         <v>3827018</v>
@@ -16957,7 +16957,7 @@
         <v>5.28599977493286</v>
       </c>
       <c r="G572" t="n">
-        <v>4.22005558013916</v>
+        <v>4.22005605697632</v>
       </c>
       <c r="H572" t="n">
         <v>2205631</v>
@@ -16986,7 +16986,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G573" t="n">
-        <v>4.23123264312744</v>
+        <v>4.23123359680176</v>
       </c>
       <c r="H573" t="n">
         <v>1225817</v>
@@ -17102,7 +17102,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G577" t="n">
-        <v>4.05080699920654</v>
+        <v>4.05080652236938</v>
       </c>
       <c r="H577" t="n">
         <v>5524918</v>
@@ -17160,7 +17160,7 @@
         <v>5.1560001373291</v>
       </c>
       <c r="G579" t="n">
-        <v>4.11627101898193</v>
+        <v>4.11627149581909</v>
       </c>
       <c r="H579" t="n">
         <v>4812294</v>
@@ -17247,7 +17247,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G582" t="n">
-        <v>3.92147493362427</v>
+        <v>3.92147541046143</v>
       </c>
       <c r="H582" t="n">
         <v>4658611</v>
@@ -17334,7 +17334,7 @@
         <v>4.58300018310547</v>
       </c>
       <c r="G585" t="n">
-        <v>3.65881943702698</v>
+        <v>3.65881967544556</v>
       </c>
       <c r="H585" t="n">
         <v>5364133</v>
@@ -17363,7 +17363,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G586" t="n">
-        <v>3.75302457809448</v>
+        <v>3.75302410125732</v>
       </c>
       <c r="H586" t="n">
         <v>6044732</v>
@@ -17392,7 +17392,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G587" t="n">
-        <v>3.62129688262939</v>
+        <v>3.62129640579224</v>
       </c>
       <c r="H587" t="n">
         <v>4501239</v>
@@ -17450,7 +17450,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G589" t="n">
-        <v>3.5031418800354</v>
+        <v>3.50314164161682</v>
       </c>
       <c r="H589" t="n">
         <v>3275117</v>
@@ -17479,7 +17479,7 @@
         <v>4.36299991607666</v>
       </c>
       <c r="G590" t="n">
-        <v>3.48318266868591</v>
+        <v>3.48318290710449</v>
       </c>
       <c r="H590" t="n">
         <v>6428207</v>
@@ -17508,7 +17508,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G591" t="n">
-        <v>3.68037462234497</v>
+        <v>3.68037486076355</v>
       </c>
       <c r="H591" t="n">
         <v>8091443</v>
@@ -17537,7 +17537,7 @@
         <v>4.59299993515015</v>
       </c>
       <c r="G592" t="n">
-        <v>3.66680335998535</v>
+        <v>3.66680288314819</v>
       </c>
       <c r="H592" t="n">
         <v>6212543</v>
@@ -17595,7 +17595,7 @@
         <v>4.50899982452393</v>
       </c>
       <c r="G594" t="n">
-        <v>3.5997416973114</v>
+        <v>3.59974145889282</v>
       </c>
       <c r="H594" t="n">
         <v>2408795</v>
@@ -17653,7 +17653,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G596" t="n">
-        <v>3.67957639694214</v>
+        <v>3.67957663536072</v>
       </c>
       <c r="H596" t="n">
         <v>4652125</v>
@@ -17682,7 +17682,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G597" t="n">
-        <v>3.60054016113281</v>
+        <v>3.60054039955139</v>
       </c>
       <c r="H597" t="n">
         <v>6336601</v>
@@ -17711,7 +17711,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>3.60852336883545</v>
+        <v>3.60852384567261</v>
       </c>
       <c r="H598" t="n">
         <v>3399120</v>
@@ -17769,7 +17769,7 @@
         <v>4.70900011062622</v>
       </c>
       <c r="G600" t="n">
-        <v>3.75941061973572</v>
+        <v>3.75941133499146</v>
       </c>
       <c r="H600" t="n">
         <v>4447046</v>
@@ -17798,7 +17798,7 @@
         <v>4.86600017547607</v>
       </c>
       <c r="G601" t="n">
-        <v>3.88475131988525</v>
+        <v>3.8847508430481</v>
       </c>
       <c r="H601" t="n">
         <v>10983974</v>
@@ -17827,7 +17827,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G602" t="n">
-        <v>3.86798572540283</v>
+        <v>3.86798620223999</v>
       </c>
       <c r="H602" t="n">
         <v>5651003</v>
@@ -17856,7 +17856,7 @@
         <v>4.75299978256226</v>
       </c>
       <c r="G603" t="n">
-        <v>3.79453802108765</v>
+        <v>3.79453825950623</v>
       </c>
       <c r="H603" t="n">
         <v>4205571</v>
@@ -17885,7 +17885,7 @@
         <v>4.45900011062622</v>
       </c>
       <c r="G604" t="n">
-        <v>3.5598247051239</v>
+        <v>3.55982422828674</v>
       </c>
       <c r="H604" t="n">
         <v>8229899</v>
@@ -17914,7 +17914,7 @@
         <v>4.36100006103516</v>
       </c>
       <c r="G605" t="n">
-        <v>3.48158621788025</v>
+        <v>3.48158669471741</v>
       </c>
       <c r="H605" t="n">
         <v>6810047</v>
@@ -17943,7 +17943,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G606" t="n">
-        <v>3.55742955207825</v>
+        <v>3.55742931365967</v>
       </c>
       <c r="H606" t="n">
         <v>5214931</v>
@@ -18146,7 +18146,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G613" t="n">
-        <v>3.1087589263916</v>
+        <v>3.10875868797302</v>
       </c>
       <c r="H613" t="n">
         <v>8219341</v>
@@ -18204,7 +18204,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G615" t="n">
-        <v>2.95228338241577</v>
+        <v>2.95228290557861</v>
       </c>
       <c r="H615" t="n">
         <v>8688676</v>
@@ -18320,7 +18320,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G619" t="n">
-        <v>2.54832029342651</v>
+        <v>2.54832005500793</v>
       </c>
       <c r="H619" t="n">
         <v>9672937</v>
@@ -18349,7 +18349,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G620" t="n">
-        <v>2.68004751205444</v>
+        <v>2.68004727363586</v>
       </c>
       <c r="H620" t="n">
         <v>6043852</v>
@@ -18436,7 +18436,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G623" t="n">
-        <v>2.8740451335907</v>
+        <v>2.87404537200928</v>
       </c>
       <c r="H623" t="n">
         <v>16884906</v>
@@ -18494,7 +18494,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G625" t="n">
-        <v>2.86606168746948</v>
+        <v>2.86606192588806</v>
       </c>
       <c r="H625" t="n">
         <v>9063322</v>
@@ -18523,7 +18523,7 @@
         <v>3.45300006866455</v>
       </c>
       <c r="G626" t="n">
-        <v>2.75668859481812</v>
+        <v>2.75668835639954</v>
       </c>
       <c r="H626" t="n">
         <v>8623249</v>
@@ -18610,7 +18610,7 @@
         <v>3.34100008010864</v>
       </c>
       <c r="G629" t="n">
-        <v>2.66727352142334</v>
+        <v>2.66727375984192</v>
       </c>
       <c r="H629" t="n">
         <v>3510090</v>
@@ -18697,7 +18697,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>2.52676486968994</v>
+        <v>2.52676463127136</v>
       </c>
       <c r="H632" t="n">
         <v>7636312</v>
@@ -18726,7 +18726,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>2.52676486968994</v>
+        <v>2.52676463127136</v>
       </c>
       <c r="H633" t="n">
         <v>3202966</v>
@@ -18755,7 +18755,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G634" t="n">
-        <v>2.55790042877197</v>
+        <v>2.55790066719055</v>
       </c>
       <c r="H634" t="n">
         <v>5933108</v>
@@ -18813,7 +18813,7 @@
         <v>3.38199996948242</v>
       </c>
       <c r="G636" t="n">
-        <v>2.70000576972961</v>
+        <v>2.70000553131104</v>
       </c>
       <c r="H636" t="n">
         <v>4018148</v>
@@ -18929,7 +18929,7 @@
         <v>3.28600001335144</v>
       </c>
       <c r="G640" t="n">
-        <v>2.62336444854736</v>
+        <v>2.62336468696594</v>
       </c>
       <c r="H640" t="n">
         <v>4401473</v>
@@ -19016,7 +19016,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G643" t="n">
-        <v>2.65689516067505</v>
+        <v>2.65689539909363</v>
       </c>
       <c r="H643" t="n">
         <v>2058256</v>
@@ -19045,7 +19045,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G644" t="n">
-        <v>2.61857461929321</v>
+        <v>2.61857438087463</v>
       </c>
       <c r="H644" t="n">
         <v>2275737</v>
@@ -19103,7 +19103,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G646" t="n">
-        <v>2.68004751205444</v>
+        <v>2.68004727363586</v>
       </c>
       <c r="H646" t="n">
         <v>1543079</v>
@@ -19132,7 +19132,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G647" t="n">
-        <v>2.70639276504517</v>
+        <v>2.70639252662659</v>
       </c>
       <c r="H647" t="n">
         <v>1698132</v>
@@ -19190,7 +19190,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G649" t="n">
-        <v>2.81816124916077</v>
+        <v>2.81816101074219</v>
       </c>
       <c r="H649" t="n">
         <v>3163107</v>
@@ -19277,7 +19277,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G652" t="n">
-        <v>2.83253145217896</v>
+        <v>2.83253121376038</v>
       </c>
       <c r="H652" t="n">
         <v>1841416</v>
@@ -19364,7 +19364,7 @@
         <v>3.66899991035461</v>
       </c>
       <c r="G655" t="n">
-        <v>2.9291307926178</v>
+        <v>2.92913126945496</v>
       </c>
       <c r="H655" t="n">
         <v>2340026</v>
@@ -19451,7 +19451,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G658" t="n">
-        <v>2.87005400657654</v>
+        <v>2.87005376815796</v>
       </c>
       <c r="H658" t="n">
         <v>2233494</v>
@@ -19567,7 +19567,7 @@
         <v>3.45099997520447</v>
       </c>
       <c r="G662" t="n">
-        <v>2.75509190559387</v>
+        <v>2.75509166717529</v>
       </c>
       <c r="H662" t="n">
         <v>5786998</v>
@@ -19596,7 +19596,7 @@
         <v>3.52699995040894</v>
       </c>
       <c r="G663" t="n">
-        <v>2.81576585769653</v>
+        <v>2.81576609611511</v>
       </c>
       <c r="H663" t="n">
         <v>2848991</v>
@@ -19625,7 +19625,7 @@
         <v>3.58899998664856</v>
       </c>
       <c r="G664" t="n">
-        <v>2.86526346206665</v>
+        <v>2.86526370048523</v>
       </c>
       <c r="H664" t="n">
         <v>5340228</v>
@@ -19683,7 +19683,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G666" t="n">
-        <v>2.89320540428162</v>
+        <v>2.8932056427002</v>
       </c>
       <c r="H666" t="n">
         <v>1922555</v>
@@ -19828,7 +19828,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G671" t="n">
-        <v>3.21094727516174</v>
+        <v>3.21094679832458</v>
       </c>
       <c r="H671" t="n">
         <v>2761689</v>
@@ -19886,7 +19886,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G673" t="n">
-        <v>3.3738100528717</v>
+        <v>3.37380957603455</v>
       </c>
       <c r="H673" t="n">
         <v>3421967</v>
@@ -19915,7 +19915,7 @@
         <v>4.20699977874756</v>
       </c>
       <c r="G674" t="n">
-        <v>3.35864114761353</v>
+        <v>3.3586413860321</v>
       </c>
       <c r="H674" t="n">
         <v>3781899</v>
@@ -19944,7 +19944,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G675" t="n">
-        <v>3.53986573219299</v>
+        <v>3.53986549377441</v>
       </c>
       <c r="H675" t="n">
         <v>5982928</v>
@@ -20002,7 +20002,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G677" t="n">
-        <v>3.38498640060425</v>
+        <v>3.38498592376709</v>
       </c>
       <c r="H677" t="n">
         <v>3819140</v>
@@ -20031,7 +20031,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G678" t="n">
-        <v>3.36502838134766</v>
+        <v>3.36502814292908</v>
       </c>
       <c r="H678" t="n">
         <v>3499100</v>
@@ -20060,7 +20060,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G679" t="n">
-        <v>3.07762360572815</v>
+        <v>3.07762384414673</v>
       </c>
       <c r="H679" t="n">
         <v>6114529</v>
@@ -20118,7 +20118,7 @@
         <v>3.9210000038147</v>
       </c>
       <c r="G681" t="n">
-        <v>3.13031435012817</v>
+        <v>3.13031411170959</v>
       </c>
       <c r="H681" t="n">
         <v>2399572</v>
@@ -20147,7 +20147,7 @@
         <v>3.99300003051758</v>
       </c>
       <c r="G682" t="n">
-        <v>3.18779492378235</v>
+        <v>3.18779516220093</v>
       </c>
       <c r="H682" t="n">
         <v>2842957</v>
@@ -20234,7 +20234,7 @@
         <v>3.89100003242493</v>
       </c>
       <c r="G685" t="n">
-        <v>3.10636377334595</v>
+        <v>3.10636401176453</v>
       </c>
       <c r="H685" t="n">
         <v>5461032</v>
@@ -20292,7 +20292,7 @@
         <v>4.01100015640259</v>
       </c>
       <c r="G687" t="n">
-        <v>3.2021656036377</v>
+        <v>3.20216536521912</v>
       </c>
       <c r="H687" t="n">
         <v>3725678</v>
@@ -20350,7 +20350,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G689" t="n">
-        <v>3.04808473587036</v>
+        <v>3.04808497428894</v>
       </c>
       <c r="H689" t="n">
         <v>2951291</v>
@@ -20466,7 +20466,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G693" t="n">
-        <v>2.93791317939758</v>
+        <v>2.937912940979</v>
       </c>
       <c r="H693" t="n">
         <v>3582961</v>
@@ -20524,7 +20524,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G695" t="n">
-        <v>2.96505689620972</v>
+        <v>2.96505665779114</v>
       </c>
       <c r="H695" t="n">
         <v>2579475</v>
@@ -20553,7 +20553,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G696" t="n">
-        <v>3.03211784362793</v>
+        <v>3.03211760520935</v>
       </c>
       <c r="H696" t="n">
         <v>2919023</v>
@@ -20582,7 +20582,7 @@
         <v>3.78099989891052</v>
       </c>
       <c r="G697" t="n">
-        <v>3.01854562759399</v>
+        <v>3.01854586601257</v>
       </c>
       <c r="H697" t="n">
         <v>1681574</v>
@@ -20611,7 +20611,7 @@
         <v>3.75</v>
       </c>
       <c r="G698" t="n">
-        <v>2.99379730224609</v>
+        <v>2.99379706382751</v>
       </c>
       <c r="H698" t="n">
         <v>2714801</v>
@@ -20640,7 +20640,7 @@
         <v>3.64100003242493</v>
       </c>
       <c r="G699" t="n">
-        <v>2.90677738189697</v>
+        <v>2.90677762031555</v>
       </c>
       <c r="H699" t="n">
         <v>2147732</v>
@@ -20669,7 +20669,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G700" t="n">
-        <v>2.96585512161255</v>
+        <v>2.96585488319397</v>
       </c>
       <c r="H700" t="n">
         <v>3333759</v>
@@ -20785,7 +20785,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G704" t="n">
-        <v>3.03371405601501</v>
+        <v>3.03371453285217</v>
       </c>
       <c r="H704" t="n">
         <v>2133351</v>
@@ -20901,7 +20901,7 @@
         <v>3.76699995994568</v>
       </c>
       <c r="G708" t="n">
-        <v>3.00736904144287</v>
+        <v>3.00736880302429</v>
       </c>
       <c r="H708" t="n">
         <v>2567828</v>
@@ -20930,7 +20930,7 @@
         <v>3.78099989891052</v>
       </c>
       <c r="G709" t="n">
-        <v>3.01854562759399</v>
+        <v>3.01854586601257</v>
       </c>
       <c r="H709" t="n">
         <v>2822705</v>
@@ -21017,7 +21017,7 @@
         <v>3.63599991798401</v>
       </c>
       <c r="G712" t="n">
-        <v>2.90278553962708</v>
+        <v>2.90278577804565</v>
       </c>
       <c r="H712" t="n">
         <v>2006688</v>
@@ -21046,7 +21046,7 @@
         <v>3.58899998664856</v>
       </c>
       <c r="G713" t="n">
-        <v>2.86526346206665</v>
+        <v>2.86526370048523</v>
       </c>
       <c r="H713" t="n">
         <v>2594843</v>
@@ -21075,7 +21075,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G714" t="n">
-        <v>2.77345371246338</v>
+        <v>2.7734534740448</v>
       </c>
       <c r="H714" t="n">
         <v>3493137</v>
@@ -21104,7 +21104,7 @@
         <v>3.36299991607666</v>
       </c>
       <c r="G715" t="n">
-        <v>2.68483710289001</v>
+        <v>2.68483734130859</v>
       </c>
       <c r="H715" t="n">
         <v>2932370</v>
@@ -21220,7 +21220,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G719" t="n">
-        <v>2.80858063697815</v>
+        <v>2.80858087539673</v>
       </c>
       <c r="H719" t="n">
         <v>8851149</v>
@@ -21307,7 +21307,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G722" t="n">
-        <v>2.96825003623962</v>
+        <v>2.9682502746582</v>
       </c>
       <c r="H722" t="n">
         <v>3797095</v>
@@ -21336,7 +21336,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G723" t="n">
-        <v>2.99699020385742</v>
+        <v>2.996990442276</v>
       </c>
       <c r="H723" t="n">
         <v>2769659</v>
@@ -21452,7 +21452,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G727" t="n">
-        <v>2.96345973014832</v>
+        <v>2.96345996856689</v>
       </c>
       <c r="H727" t="n">
         <v>2416775</v>
@@ -21481,7 +21481,7 @@
         <v>3.73300004005432</v>
       </c>
       <c r="G728" t="n">
-        <v>2.98022532463074</v>
+        <v>2.98022556304932</v>
       </c>
       <c r="H728" t="n">
         <v>1181940</v>
@@ -21510,7 +21510,7 @@
         <v>3.6470000743866</v>
       </c>
       <c r="G729" t="n">
-        <v>2.91156768798828</v>
+        <v>2.9115674495697</v>
       </c>
       <c r="H729" t="n">
         <v>1509920</v>
@@ -21568,7 +21568,7 @@
         <v>3.69899988174438</v>
       </c>
       <c r="G731" t="n">
-        <v>2.95308136940002</v>
+        <v>2.9530816078186</v>
       </c>
       <c r="H731" t="n">
         <v>1412914</v>
@@ -21655,7 +21655,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>2.96186351776123</v>
+        <v>2.96186327934265</v>
       </c>
       <c r="H734" t="n">
         <v>1213470</v>
@@ -21742,7 +21742,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G737" t="n">
-        <v>2.85408687591553</v>
+        <v>2.85408663749695</v>
       </c>
       <c r="H737" t="n">
         <v>1946139</v>
@@ -21829,7 +21829,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G740" t="n">
-        <v>2.95228338241577</v>
+        <v>2.95228290557861</v>
       </c>
       <c r="H740" t="n">
         <v>2594794</v>
@@ -22003,7 +22003,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G746" t="n">
-        <v>3.08321189880371</v>
+        <v>3.08321166038513</v>
       </c>
       <c r="H746" t="n">
         <v>2806919</v>
@@ -22061,7 +22061,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G748" t="n">
-        <v>3.07762360572815</v>
+        <v>3.07762384414673</v>
       </c>
       <c r="H748" t="n">
         <v>1301407</v>
@@ -22090,7 +22090,7 @@
         <v>3.94799995422363</v>
       </c>
       <c r="G749" t="n">
-        <v>3.15186929702759</v>
+        <v>3.15186953544617</v>
       </c>
       <c r="H749" t="n">
         <v>3187840</v>
@@ -22119,7 +22119,7 @@
         <v>3.95900011062622</v>
       </c>
       <c r="G750" t="n">
-        <v>3.16065192222595</v>
+        <v>3.16065168380737</v>
       </c>
       <c r="H750" t="n">
         <v>4618724</v>
@@ -22148,7 +22148,7 @@
         <v>3.75699996948242</v>
       </c>
       <c r="G751" t="n">
-        <v>2.99938559532166</v>
+        <v>2.99938535690308</v>
       </c>
       <c r="H751" t="n">
         <v>3188876</v>
@@ -22235,7 +22235,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G754" t="n">
-        <v>2.9898054599762</v>
+        <v>2.98980522155762</v>
       </c>
       <c r="H754" t="n">
         <v>2049209</v>
@@ -22293,7 +22293,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G756" t="n">
-        <v>3.01774716377258</v>
+        <v>3.01774740219116</v>
       </c>
       <c r="H756" t="n">
         <v>3433454</v>
@@ -22380,7 +22380,7 @@
         <v>3.58299994468689</v>
       </c>
       <c r="G759" t="n">
-        <v>2.8604736328125</v>
+        <v>2.86047339439392</v>
       </c>
       <c r="H759" t="n">
         <v>3222216</v>
@@ -22467,7 +22467,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G762" t="n">
-        <v>3.07762360572815</v>
+        <v>3.07762384414673</v>
       </c>
       <c r="H762" t="n">
         <v>4804396</v>
@@ -22496,7 +22496,7 @@
         <v>3.82699990272522</v>
       </c>
       <c r="G763" t="n">
-        <v>3.05526995658875</v>
+        <v>3.05526971817017</v>
       </c>
       <c r="H763" t="n">
         <v>2346346</v>
@@ -22583,7 +22583,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G766" t="n">
-        <v>3.11674237251282</v>
+        <v>3.11674213409424</v>
       </c>
       <c r="H766" t="n">
         <v>4213016</v>
@@ -22641,7 +22641,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G768" t="n">
-        <v>3.0688419342041</v>
+        <v>3.06884169578552</v>
       </c>
       <c r="H768" t="n">
         <v>1475717</v>
@@ -22728,7 +22728,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G771" t="n">
-        <v>2.95707321166992</v>
+        <v>2.9570734500885</v>
       </c>
       <c r="H771" t="n">
         <v>2285002</v>
@@ -22757,7 +22757,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G772" t="n">
-        <v>3.06964015960693</v>
+        <v>3.06964039802551</v>
       </c>
       <c r="H772" t="n">
         <v>4101570</v>
@@ -22786,7 +22786,7 @@
         <v>3.68899989128113</v>
       </c>
       <c r="G773" t="n">
-        <v>2.94509768486023</v>
+        <v>2.94509792327881</v>
       </c>
       <c r="H773" t="n">
         <v>3433440</v>
@@ -22815,7 +22815,7 @@
         <v>3.78299999237061</v>
       </c>
       <c r="G774" t="n">
-        <v>3.02014231681824</v>
+        <v>3.02014255523682</v>
       </c>
       <c r="H774" t="n">
         <v>3457710</v>
@@ -22873,7 +22873,7 @@
         <v>3.94300007820129</v>
       </c>
       <c r="G776" t="n">
-        <v>3.14787817001343</v>
+        <v>3.14787793159485</v>
       </c>
       <c r="H776" t="n">
         <v>4608842</v>
@@ -22902,7 +22902,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G777" t="n">
-        <v>3.00577259063721</v>
+        <v>3.00577235221863</v>
       </c>
       <c r="H777" t="n">
         <v>6184054</v>
@@ -22989,7 +22989,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G780" t="n">
-        <v>2.85807824134827</v>
+        <v>2.85807800292969</v>
       </c>
       <c r="H780" t="n">
         <v>4129192</v>
@@ -23047,7 +23047,7 @@
         <v>3.86899995803833</v>
       </c>
       <c r="G782" t="n">
-        <v>3.08879995346069</v>
+        <v>3.08880019187927</v>
       </c>
       <c r="H782" t="n">
         <v>3534221</v>
@@ -23076,7 +23076,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G783" t="n">
-        <v>2.96505689620972</v>
+        <v>2.96505665779114</v>
       </c>
       <c r="H783" t="n">
         <v>6191479</v>
@@ -23192,7 +23192,7 @@
         <v>4.23299980163574</v>
       </c>
       <c r="G787" t="n">
-        <v>3.37939810752869</v>
+        <v>3.37939834594727</v>
       </c>
       <c r="H787" t="n">
         <v>6292817</v>
@@ -23279,7 +23279,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G790" t="n">
-        <v>3.33708596229553</v>
+        <v>3.33708572387695</v>
       </c>
       <c r="H790" t="n">
         <v>6357335</v>
@@ -23308,7 +23308,7 @@
         <v>4.22900009155273</v>
       </c>
       <c r="G791" t="n">
-        <v>3.3762047290802</v>
+        <v>3.37620496749878</v>
       </c>
       <c r="H791" t="n">
         <v>5593742</v>
@@ -23337,7 +23337,7 @@
         <v>4.26300001144409</v>
       </c>
       <c r="G792" t="n">
-        <v>3.40334868431091</v>
+        <v>3.40334844589233</v>
       </c>
       <c r="H792" t="n">
         <v>3038372</v>
@@ -23366,7 +23366,7 @@
         <v>4.28700017929077</v>
       </c>
       <c r="G793" t="n">
-        <v>3.42250919342041</v>
+        <v>3.42250943183899</v>
       </c>
       <c r="H793" t="n">
         <v>4231809</v>
@@ -23424,7 +23424,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G795" t="n">
-        <v>3.33708596229553</v>
+        <v>3.33708572387695</v>
       </c>
       <c r="H795" t="n">
         <v>3638320</v>
@@ -23453,7 +23453,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G796" t="n">
-        <v>3.31792569160461</v>
+        <v>3.31792545318604</v>
       </c>
       <c r="H796" t="n">
         <v>3693940</v>
@@ -23482,7 +23482,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G797" t="n">
-        <v>3.40734052658081</v>
+        <v>3.40734028816223</v>
       </c>
       <c r="H797" t="n">
         <v>4608848</v>
@@ -23511,7 +23511,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G798" t="n">
-        <v>3.45843434333801</v>
+        <v>3.45843458175659</v>
       </c>
       <c r="H798" t="n">
         <v>4749283</v>
@@ -23569,7 +23569,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G800" t="n">
-        <v>3.46881294250488</v>
+        <v>3.46881246566772</v>
       </c>
       <c r="H800" t="n">
         <v>8062494</v>
@@ -23598,7 +23598,7 @@
         <v>4.5</v>
       </c>
       <c r="G801" t="n">
-        <v>3.59255599975586</v>
+        <v>3.59255647659302</v>
       </c>
       <c r="H801" t="n">
         <v>42409919</v>
@@ -23627,7 +23627,7 @@
         <v>4.50099992752075</v>
       </c>
       <c r="G802" t="n">
-        <v>3.59335517883301</v>
+        <v>3.59335470199585</v>
       </c>
       <c r="H802" t="n">
         <v>3709710</v>
@@ -23656,7 +23656,7 @@
         <v>4.38100004196167</v>
       </c>
       <c r="G803" t="n">
-        <v>3.49755358695984</v>
+        <v>3.49755334854126</v>
       </c>
       <c r="H803" t="n">
         <v>3568279</v>
@@ -23685,7 +23685,7 @@
         <v>4.42199993133545</v>
       </c>
       <c r="G804" t="n">
-        <v>3.53028583526611</v>
+        <v>3.53028535842896</v>
       </c>
       <c r="H804" t="n">
         <v>2373246</v>
@@ -23772,7 +23772,7 @@
         <v>4.45900011062622</v>
       </c>
       <c r="G807" t="n">
-        <v>3.5598247051239</v>
+        <v>3.55982422828674</v>
       </c>
       <c r="H807" t="n">
         <v>1453180</v>
@@ -23801,7 +23801,7 @@
         <v>4.55299997329712</v>
       </c>
       <c r="G808" t="n">
-        <v>3.63486909866333</v>
+        <v>3.63486886024475</v>
       </c>
       <c r="H808" t="n">
         <v>4469524</v>
@@ -23830,7 +23830,7 @@
         <v>4.39699983596802</v>
       </c>
       <c r="G809" t="n">
-        <v>3.51032686233521</v>
+        <v>3.51032710075378</v>
       </c>
       <c r="H809" t="n">
         <v>4785540</v>
@@ -23888,7 +23888,7 @@
         <v>4.48899984359741</v>
       </c>
       <c r="G811" t="n">
-        <v>3.58377456665039</v>
+        <v>3.58377432823181</v>
       </c>
       <c r="H811" t="n">
         <v>3097950</v>
@@ -23917,7 +23917,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G812" t="n">
-        <v>3.51272225379944</v>
+        <v>3.51272177696228</v>
       </c>
       <c r="H812" t="n">
         <v>7525445</v>
@@ -23946,7 +23946,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G813" t="n">
-        <v>3.57259845733643</v>
+        <v>3.57259821891785</v>
       </c>
       <c r="H813" t="n">
         <v>6334167</v>
@@ -23975,7 +23975,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G814" t="n">
-        <v>3.73945260047913</v>
+        <v>3.73945283889771</v>
       </c>
       <c r="H814" t="n">
         <v>8208133</v>
@@ -24033,7 +24033,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>3.45683789253235</v>
+        <v>3.45683765411377</v>
       </c>
       <c r="H816" t="n">
         <v>5256319</v>
@@ -24062,7 +24062,7 @@
         <v>4.35099983215332</v>
       </c>
       <c r="G817" t="n">
-        <v>3.47360277175903</v>
+        <v>3.47360348701477</v>
       </c>
       <c r="H817" t="n">
         <v>2573619</v>
@@ -24091,7 +24091,7 @@
         <v>4.40299987792969</v>
       </c>
       <c r="G818" t="n">
-        <v>3.51511669158936</v>
+        <v>3.51511693000793</v>
       </c>
       <c r="H818" t="n">
         <v>2717001</v>
@@ -24149,7 +24149,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>3.56062269210815</v>
+        <v>3.56062316894531</v>
       </c>
       <c r="H820" t="n">
         <v>1970058</v>
@@ -24236,7 +24236,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G823" t="n">
-        <v>3.42330718040466</v>
+        <v>3.42330741882324</v>
       </c>
       <c r="H823" t="n">
         <v>5898709</v>
@@ -24265,7 +24265,7 @@
         <v>4.29300022125244</v>
       </c>
       <c r="G824" t="n">
-        <v>3.42729949951172</v>
+        <v>3.42729926109314</v>
       </c>
       <c r="H824" t="n">
         <v>4293764</v>
@@ -24294,7 +24294,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>3.5446560382843</v>
+        <v>3.54465627670288</v>
       </c>
       <c r="H825" t="n">
         <v>4749576</v>
@@ -24323,7 +24323,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G826" t="n">
-        <v>3.54944586753845</v>
+        <v>3.54944610595703</v>
       </c>
       <c r="H826" t="n">
         <v>4809149</v>
@@ -24381,7 +24381,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G828" t="n">
-        <v>3.62129688262939</v>
+        <v>3.62129640579224</v>
       </c>
       <c r="H828" t="n">
         <v>4573879</v>
@@ -24410,7 +24410,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G829" t="n">
-        <v>3.58297657966614</v>
+        <v>3.58297610282898</v>
       </c>
       <c r="H829" t="n">
         <v>2831592</v>
@@ -24439,7 +24439,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G830" t="n">
-        <v>3.5446560382843</v>
+        <v>3.54465627670288</v>
       </c>
       <c r="H830" t="n">
         <v>2051814</v>
@@ -24497,7 +24497,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G832" t="n">
-        <v>3.53667211532593</v>
+        <v>3.53667259216309</v>
       </c>
       <c r="H832" t="n">
         <v>2577762</v>
@@ -24613,7 +24613,7 @@
         <v>4.29099988937378</v>
       </c>
       <c r="G836" t="n">
-        <v>3.42570209503174</v>
+        <v>3.4257025718689</v>
       </c>
       <c r="H836" t="n">
         <v>3192309</v>
@@ -24700,7 +24700,7 @@
         <v>4.26900005340576</v>
       </c>
       <c r="G839" t="n">
-        <v>3.40813899040222</v>
+        <v>3.40813875198364</v>
       </c>
       <c r="H839" t="n">
         <v>8596223</v>
@@ -24758,7 +24758,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G841" t="n">
-        <v>3.44087100028992</v>
+        <v>3.44087076187134</v>
       </c>
       <c r="H841" t="n">
         <v>3106643</v>
@@ -24961,7 +24961,7 @@
         <v>4.69299983978271</v>
       </c>
       <c r="G848" t="n">
-        <v>3.74663710594177</v>
+        <v>3.74663686752319</v>
       </c>
       <c r="H848" t="n">
         <v>4481975</v>
@@ -24990,7 +24990,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G849" t="n">
-        <v>3.71630024909973</v>
+        <v>3.71630072593689</v>
       </c>
       <c r="H849" t="n">
         <v>2569243</v>
@@ -25019,7 +25019,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G850" t="n">
-        <v>3.73226714134216</v>
+        <v>3.73226761817932</v>
       </c>
       <c r="H850" t="n">
         <v>1985783</v>
@@ -25048,7 +25048,7 @@
         <v>4.68100023269653</v>
       </c>
       <c r="G851" t="n">
-        <v>3.73705792427063</v>
+        <v>3.73705720901489</v>
       </c>
       <c r="H851" t="n">
         <v>1646366</v>
@@ -25077,7 +25077,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>3.78815126419067</v>
+        <v>3.78815078735352</v>
       </c>
       <c r="H852" t="n">
         <v>2450719</v>
@@ -25106,7 +25106,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>3.76420140266418</v>
+        <v>3.76420116424561</v>
       </c>
       <c r="H853" t="n">
         <v>2607308</v>
@@ -25135,7 +25135,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G854" t="n">
-        <v>3.68995475769043</v>
+        <v>3.68995428085327</v>
       </c>
       <c r="H854" t="n">
         <v>3076913</v>
@@ -25164,7 +25164,7 @@
         <v>4.60099983215332</v>
       </c>
       <c r="G855" t="n">
-        <v>3.67318964004517</v>
+        <v>3.67318940162659</v>
       </c>
       <c r="H855" t="n">
         <v>1427684</v>
@@ -25193,7 +25193,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>3.75861287117004</v>
+        <v>3.75861239433289</v>
       </c>
       <c r="H856" t="n">
         <v>1816097</v>
@@ -25222,7 +25222,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>3.90790343284607</v>
+        <v>3.90790295600891</v>
       </c>
       <c r="H857" t="n">
         <v>4999525</v>
@@ -25251,7 +25251,7 @@
         <v>4.77099990844727</v>
       </c>
       <c r="G858" t="n">
-        <v>3.80890846252441</v>
+        <v>3.80890798568726</v>
       </c>
       <c r="H858" t="n">
         <v>3010730</v>
@@ -25367,7 +25367,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G862" t="n">
-        <v>3.86399412155151</v>
+        <v>3.86399459838867</v>
       </c>
       <c r="H862" t="n">
         <v>2024564</v>
@@ -25396,7 +25396,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G863" t="n">
-        <v>3.86080098152161</v>
+        <v>3.86080050468445</v>
       </c>
       <c r="H863" t="n">
         <v>2711307</v>
@@ -25483,7 +25483,7 @@
         <v>4.75</v>
       </c>
       <c r="G866" t="n">
-        <v>3.79214310646057</v>
+        <v>3.79214286804199</v>
       </c>
       <c r="H866" t="n">
         <v>2152373</v>
@@ -25512,7 +25512,7 @@
         <v>4.9689998626709</v>
       </c>
       <c r="G867" t="n">
-        <v>3.96698093414307</v>
+        <v>3.96698045730591</v>
       </c>
       <c r="H867" t="n">
         <v>3957020</v>
@@ -25541,7 +25541,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G868" t="n">
-        <v>3.95340871810913</v>
+        <v>3.95340919494629</v>
       </c>
       <c r="H868" t="n">
         <v>3882618</v>
@@ -25570,7 +25570,7 @@
         <v>4.94899988174438</v>
       </c>
       <c r="G869" t="n">
-        <v>3.95101404190063</v>
+        <v>3.95101356506348</v>
       </c>
       <c r="H869" t="n">
         <v>2692109</v>
@@ -25599,7 +25599,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G870" t="n">
-        <v>3.91508793830872</v>
+        <v>3.91508817672729</v>
       </c>
       <c r="H870" t="n">
         <v>7781306</v>
@@ -25686,7 +25686,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G873" t="n">
-        <v>3.91269326210022</v>
+        <v>3.91269373893738</v>
       </c>
       <c r="H873" t="n">
         <v>2975747</v>
@@ -25802,7 +25802,7 @@
         <v>4.97700023651123</v>
       </c>
       <c r="G877" t="n">
-        <v>3.97336745262146</v>
+        <v>3.97336792945862</v>
       </c>
       <c r="H877" t="n">
         <v>2915800</v>
@@ -25947,7 +25947,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G882" t="n">
-        <v>4.00769710540771</v>
+        <v>4.00769662857056</v>
       </c>
       <c r="H882" t="n">
         <v>1377373</v>
@@ -25976,7 +25976,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G883" t="n">
-        <v>4.14022159576416</v>
+        <v>4.14022207260132</v>
       </c>
       <c r="H883" t="n">
         <v>5129041</v>
@@ -26005,7 +26005,7 @@
         <v>5.0019998550415</v>
       </c>
       <c r="G884" t="n">
-        <v>3.99332642555237</v>
+        <v>3.99332594871521</v>
       </c>
       <c r="H884" t="n">
         <v>8991183</v>
@@ -26121,7 +26121,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G888" t="n">
-        <v>3.99013257026672</v>
+        <v>3.99013304710388</v>
       </c>
       <c r="H888" t="n">
         <v>2928960</v>
@@ -26266,7 +26266,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G893" t="n">
-        <v>3.92626523971558</v>
+        <v>3.92626571655273</v>
       </c>
       <c r="H893" t="n">
         <v>1526999</v>
@@ -26324,7 +26324,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G895" t="n">
-        <v>3.95740032196045</v>
+        <v>3.95740079879761</v>
       </c>
       <c r="H895" t="n">
         <v>1966290</v>
@@ -26382,7 +26382,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G897" t="n">
-        <v>3.91269326210022</v>
+        <v>3.91269373893738</v>
       </c>
       <c r="H897" t="n">
         <v>2075739</v>
@@ -26411,7 +26411,7 @@
         <v>4.96299982070923</v>
       </c>
       <c r="G898" t="n">
-        <v>3.96219062805176</v>
+        <v>3.96219110488892</v>
       </c>
       <c r="H898" t="n">
         <v>2780569</v>
@@ -26440,7 +26440,7 @@
         <v>5.0019998550415</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99332642555237</v>
+        <v>3.99332594871521</v>
       </c>
       <c r="H899" t="n">
         <v>2294402</v>
@@ -26469,7 +26469,7 @@
         <v>5.02600002288818</v>
       </c>
       <c r="G900" t="n">
-        <v>4.01248693466187</v>
+        <v>4.01248598098755</v>
       </c>
       <c r="H900" t="n">
         <v>2165187</v>
@@ -26498,7 +26498,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G901" t="n">
-        <v>3.94542503356934</v>
+        <v>3.94542551040649</v>
       </c>
       <c r="H901" t="n">
         <v>4957834</v>
@@ -26527,7 +26527,7 @@
         <v>4.79699993133545</v>
       </c>
       <c r="G902" t="n">
-        <v>3.829665184021</v>
+        <v>3.82966470718384</v>
       </c>
       <c r="H902" t="n">
         <v>5237550</v>
@@ -26556,7 +26556,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G903" t="n">
-        <v>3.75701594352722</v>
+        <v>3.7570161819458</v>
       </c>
       <c r="H903" t="n">
         <v>5125936</v>
@@ -26585,7 +26585,7 @@
         <v>4.67700004577637</v>
       </c>
       <c r="G904" t="n">
-        <v>3.73386359214783</v>
+        <v>3.73386406898499</v>
       </c>
       <c r="H904" t="n">
         <v>2835308</v>
@@ -26614,7 +26614,7 @@
         <v>4.73299980163574</v>
       </c>
       <c r="G905" t="n">
-        <v>3.77857089042664</v>
+        <v>3.77857112884521</v>
       </c>
       <c r="H905" t="n">
         <v>2260456</v>
@@ -26643,7 +26643,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G906" t="n">
-        <v>3.67638254165649</v>
+        <v>3.67638278007507</v>
       </c>
       <c r="H906" t="n">
         <v>4445808</v>
@@ -26672,7 +26672,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G907" t="n">
-        <v>3.68436598777771</v>
+        <v>3.68436646461487</v>
       </c>
       <c r="H907" t="n">
         <v>4336143</v>
@@ -26701,7 +26701,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G908" t="n">
-        <v>3.69155120849609</v>
+        <v>3.69155144691467</v>
       </c>
       <c r="H908" t="n">
         <v>4131045</v>
@@ -26730,7 +26730,7 @@
         <v>4.66099977493286</v>
       </c>
       <c r="G909" t="n">
-        <v>3.7210898399353</v>
+        <v>3.72109007835388</v>
       </c>
       <c r="H909" t="n">
         <v>2888364</v>
@@ -26759,7 +26759,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G910" t="n">
-        <v>3.71630024909973</v>
+        <v>3.71630072593689</v>
       </c>
       <c r="H910" t="n">
         <v>2630457</v>
@@ -26788,7 +26788,7 @@
         <v>4.58099985122681</v>
       </c>
       <c r="G911" t="n">
-        <v>3.65722274780273</v>
+        <v>3.65722250938416</v>
       </c>
       <c r="H911" t="n">
         <v>3464484</v>
@@ -26817,7 +26817,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G912" t="n">
-        <v>3.66839981079102</v>
+        <v>3.66839933395386</v>
       </c>
       <c r="H912" t="n">
         <v>1942781</v>
@@ -26846,7 +26846,7 @@
         <v>4.71299982070923</v>
       </c>
       <c r="G913" t="n">
-        <v>3.76260423660278</v>
+        <v>3.7626039981842</v>
       </c>
       <c r="H913" t="n">
         <v>5449345</v>
@@ -26875,7 +26875,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>3.73945260047913</v>
+        <v>3.73945283889771</v>
       </c>
       <c r="H914" t="n">
         <v>3729259</v>
@@ -26904,7 +26904,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G915" t="n">
-        <v>3.75222611427307</v>
+        <v>3.75222587585449</v>
       </c>
       <c r="H915" t="n">
         <v>1728510</v>
@@ -26933,7 +26933,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G916" t="n">
-        <v>3.79533624649048</v>
+        <v>3.79533672332764</v>
       </c>
       <c r="H916" t="n">
         <v>2356522</v>
@@ -26991,7 +26991,7 @@
         <v>4.67700004577637</v>
       </c>
       <c r="G918" t="n">
-        <v>3.73386359214783</v>
+        <v>3.73386406898499</v>
       </c>
       <c r="H918" t="n">
         <v>2074454</v>
@@ -27020,7 +27020,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G919" t="n">
-        <v>3.74823379516602</v>
+        <v>3.74823427200317</v>
       </c>
       <c r="H919" t="n">
         <v>2245847</v>
@@ -27078,7 +27078,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G921" t="n">
-        <v>3.79054641723633</v>
+        <v>3.79054689407349</v>
       </c>
       <c r="H921" t="n">
         <v>2892437</v>
@@ -27107,7 +27107,7 @@
         <v>4.72900009155273</v>
       </c>
       <c r="G922" t="n">
-        <v>3.77537775039673</v>
+        <v>3.77537798881531</v>
       </c>
       <c r="H922" t="n">
         <v>2553622</v>
@@ -27165,7 +27165,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G924" t="n">
-        <v>3.86399412155151</v>
+        <v>3.86399459838867</v>
       </c>
       <c r="H924" t="n">
         <v>1783174</v>
@@ -27194,7 +27194,7 @@
         <v>4.85699987411499</v>
       </c>
       <c r="G925" t="n">
-        <v>3.87756609916687</v>
+        <v>3.87756562232971</v>
       </c>
       <c r="H925" t="n">
         <v>1032853</v>
@@ -27223,7 +27223,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G926" t="n">
-        <v>3.93185353279114</v>
+        <v>3.93185329437256</v>
       </c>
       <c r="H926" t="n">
         <v>2913802</v>
@@ -27281,7 +27281,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G928" t="n">
-        <v>4.06517744064331</v>
+        <v>4.06517696380615</v>
       </c>
       <c r="H928" t="n">
         <v>5038431</v>
@@ -27426,7 +27426,7 @@
         <v>5.16200017929077</v>
       </c>
       <c r="G933" t="n">
-        <v>4.12106132507324</v>
+        <v>4.1210618019104</v>
       </c>
       <c r="H933" t="n">
         <v>2361572</v>
@@ -27455,7 +27455,7 @@
         <v>5.16200017929077</v>
       </c>
       <c r="G934" t="n">
-        <v>4.12106132507324</v>
+        <v>4.1210618019104</v>
       </c>
       <c r="H934" t="n">
         <v>1419462</v>
@@ -27571,7 +27571,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>4.12744855880737</v>
+        <v>4.12744808197021</v>
       </c>
       <c r="H938" t="n">
         <v>2099142</v>
@@ -27600,7 +27600,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>4.02366352081299</v>
+        <v>4.02366304397583</v>
       </c>
       <c r="H939" t="n">
         <v>3026829</v>
@@ -27629,7 +27629,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>4.15345907211304</v>
+        <v>4.15345859527588</v>
       </c>
       <c r="H940" t="n">
         <v>2848192</v>
@@ -27658,7 +27658,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G941" t="n">
-        <v>4.1339898109436</v>
+        <v>4.13399028778076</v>
       </c>
       <c r="H941" t="n">
         <v>1763484</v>
@@ -27687,7 +27687,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G942" t="n">
-        <v>4.07558155059814</v>
+        <v>4.0755820274353</v>
       </c>
       <c r="H942" t="n">
         <v>1599756</v>
@@ -27774,7 +27774,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G945" t="n">
-        <v>4.01717329025269</v>
+        <v>4.01717376708984</v>
       </c>
       <c r="H945" t="n">
         <v>2334336</v>
@@ -27861,7 +27861,7 @@
         <v>4.9229998588562</v>
       </c>
       <c r="G948" t="n">
-        <v>3.99364805221558</v>
+        <v>3.99364852905273</v>
       </c>
       <c r="H948" t="n">
         <v>1782081</v>
@@ -27948,7 +27948,7 @@
         <v>4.93900012969971</v>
       </c>
       <c r="G951" t="n">
-        <v>4.00662708282471</v>
+        <v>4.00662755966187</v>
       </c>
       <c r="H951" t="n">
         <v>1594357</v>
@@ -27977,7 +27977,7 @@
         <v>4.99200010299683</v>
       </c>
       <c r="G952" t="n">
-        <v>4.04962205886841</v>
+        <v>4.04962253570557</v>
       </c>
       <c r="H952" t="n">
         <v>1481995</v>
@@ -28035,7 +28035,7 @@
         <v>4.97200012207031</v>
       </c>
       <c r="G954" t="n">
-        <v>4.03339815139771</v>
+        <v>4.03339862823486</v>
       </c>
       <c r="H954" t="n">
         <v>1838472</v>
@@ -28209,7 +28209,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G960" t="n">
-        <v>3.85168433189392</v>
+        <v>3.85168480873108</v>
       </c>
       <c r="H960" t="n">
         <v>4116007</v>
@@ -28267,7 +28267,7 @@
         <v>4.99900007247925</v>
       </c>
       <c r="G962" t="n">
-        <v>4.05530166625977</v>
+        <v>4.05530118942261</v>
       </c>
       <c r="H962" t="n">
         <v>5465593</v>
@@ -28296,7 +28296,7 @@
         <v>4.96099996566772</v>
       </c>
       <c r="G963" t="n">
-        <v>4.02447509765625</v>
+        <v>4.02447414398193</v>
       </c>
       <c r="H963" t="n">
         <v>2320311</v>
@@ -28354,7 +28354,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G965" t="n">
-        <v>4.1339898109436</v>
+        <v>4.13399028778076</v>
       </c>
       <c r="H965" t="n">
         <v>2048703</v>
@@ -28383,7 +28383,7 @@
         <v>5.02199983596802</v>
       </c>
       <c r="G966" t="n">
-        <v>4.07395887374878</v>
+        <v>4.07395935058594</v>
       </c>
       <c r="H966" t="n">
         <v>2792244</v>
@@ -28412,7 +28412,7 @@
         <v>5.07600021362305</v>
       </c>
       <c r="G967" t="n">
-        <v>4.11776494979858</v>
+        <v>4.11776542663574</v>
       </c>
       <c r="H967" t="n">
         <v>2243989</v>
@@ -28528,7 +28528,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G971" t="n">
-        <v>4.1064076423645</v>
+        <v>4.10640811920166</v>
       </c>
       <c r="H971" t="n">
         <v>1962976</v>
@@ -28586,7 +28586,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G973" t="n">
-        <v>4.12263250350952</v>
+        <v>4.12263202667236</v>
       </c>
       <c r="H973" t="n">
         <v>1912199</v>
@@ -28615,7 +28615,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G974" t="n">
-        <v>4.42116212844849</v>
+        <v>4.42116260528564</v>
       </c>
       <c r="H974" t="n">
         <v>11030734</v>
@@ -28731,7 +28731,7 @@
         <v>5.44399976730347</v>
       </c>
       <c r="G978" t="n">
-        <v>4.41629457473755</v>
+        <v>4.41629505157471</v>
       </c>
       <c r="H978" t="n">
         <v>1130398</v>
@@ -28789,7 +28789,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G980" t="n">
-        <v>4.40007019042969</v>
+        <v>4.40007066726685</v>
       </c>
       <c r="H980" t="n">
         <v>869534</v>
@@ -28876,7 +28876,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G983" t="n">
-        <v>4.24756097793579</v>
+        <v>4.24756145477295</v>
       </c>
       <c r="H983" t="n">
         <v>2469703</v>
@@ -28905,7 +28905,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G984" t="n">
-        <v>4.2069993019104</v>
+        <v>4.20699977874756</v>
       </c>
       <c r="H984" t="n">
         <v>1342414</v>
@@ -28934,7 +28934,7 @@
         <v>5.16800022125244</v>
       </c>
       <c r="G985" t="n">
-        <v>4.1923975944519</v>
+        <v>4.19239807128906</v>
       </c>
       <c r="H985" t="n">
         <v>1123987</v>
@@ -28963,7 +28963,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G986" t="n">
-        <v>4.21024513244629</v>
+        <v>4.21024465560913</v>
       </c>
       <c r="H986" t="n">
         <v>1166057</v>
@@ -28992,7 +28992,7 @@
         <v>5.16200017929077</v>
       </c>
       <c r="G987" t="n">
-        <v>4.18753004074097</v>
+        <v>4.18753051757812</v>
       </c>
       <c r="H987" t="n">
         <v>818470</v>
@@ -29021,7 +29021,7 @@
         <v>5.15199995040894</v>
       </c>
       <c r="G988" t="n">
-        <v>4.17941808700562</v>
+        <v>4.17941856384277</v>
       </c>
       <c r="H988" t="n">
         <v>1033644</v>
@@ -29050,7 +29050,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G989" t="n">
-        <v>4.2134895324707</v>
+        <v>4.21348905563354</v>
       </c>
       <c r="H989" t="n">
         <v>1226933</v>
@@ -29108,7 +29108,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G991" t="n">
-        <v>4.11614274978638</v>
+        <v>4.11614227294922</v>
       </c>
       <c r="H991" t="n">
         <v>2172480</v>
@@ -29137,7 +29137,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G992" t="n">
-        <v>4.17292881011963</v>
+        <v>4.17292833328247</v>
       </c>
       <c r="H992" t="n">
         <v>1736802</v>
@@ -29166,7 +29166,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G993" t="n">
-        <v>4.19888782501221</v>
+        <v>4.19888734817505</v>
       </c>
       <c r="H993" t="n">
         <v>1028145</v>
@@ -29224,7 +29224,7 @@
         <v>5.15199995040894</v>
       </c>
       <c r="G995" t="n">
-        <v>4.17941808700562</v>
+        <v>4.17941856384277</v>
       </c>
       <c r="H995" t="n">
         <v>679524</v>
@@ -29282,7 +29282,7 @@
         <v>5.13600015640259</v>
       </c>
       <c r="G997" t="n">
-        <v>4.16643905639648</v>
+        <v>4.16643857955933</v>
       </c>
       <c r="H997" t="n">
         <v>3304160</v>
@@ -29311,7 +29311,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G998" t="n">
-        <v>4.19888782501221</v>
+        <v>4.19888734817505</v>
       </c>
       <c r="H998" t="n">
         <v>2479222</v>
@@ -29340,7 +29340,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G999" t="n">
-        <v>4.15345907211304</v>
+        <v>4.15345859527588</v>
       </c>
       <c r="H999" t="n">
         <v>2065863</v>
@@ -29369,7 +29369,7 @@
         <v>5.2519998550415</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.26053953170776</v>
+        <v>4.26054000854492</v>
       </c>
       <c r="H1000" t="n">
         <v>4074072</v>
@@ -29456,7 +29456,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.20213174819946</v>
+        <v>4.20213222503662</v>
       </c>
       <c r="H1003" t="n">
         <v>2224645</v>
@@ -29485,7 +29485,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.19888782501221</v>
+        <v>4.19888734817505</v>
       </c>
       <c r="H1004" t="n">
         <v>4814465</v>
@@ -29514,7 +29514,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.12263250350952</v>
+        <v>4.12263202667236</v>
       </c>
       <c r="H1005" t="n">
         <v>2689543</v>
@@ -29717,7 +29717,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.13074493408203</v>
+        <v>4.13074445724487</v>
       </c>
       <c r="H1012" t="n">
         <v>1475971</v>
@@ -29804,7 +29804,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.05205631256104</v>
+        <v>4.05205583572388</v>
       </c>
       <c r="H1015" t="n">
         <v>1874139</v>
@@ -29833,7 +29833,7 @@
         <v>5.02199983596802</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.07395887374878</v>
+        <v>4.07395935058594</v>
       </c>
       <c r="H1016" t="n">
         <v>2197359</v>
@@ -29891,7 +29891,7 @@
         <v>4.98699998855591</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.04556608200073</v>
+        <v>4.04556655883789</v>
       </c>
       <c r="H1018" t="n">
         <v>1803434</v>
@@ -29978,7 +29978,7 @@
         <v>5.03599977493286</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.0853157043457</v>
+        <v>4.08531618118286</v>
       </c>
       <c r="H1021" t="n">
         <v>2181807</v>
@@ -30007,7 +30007,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.07233715057373</v>
+        <v>4.07233667373657</v>
       </c>
       <c r="H1022" t="n">
         <v>1012542</v>
@@ -30123,7 +30123,7 @@
         <v>5.00600004196167</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.06097984313965</v>
+        <v>4.06097936630249</v>
       </c>
       <c r="H1026" t="n">
         <v>952568</v>
@@ -30152,7 +30152,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.11614274978638</v>
+        <v>4.11614227294922</v>
       </c>
       <c r="H1027" t="n">
         <v>1747743</v>
@@ -30181,7 +30181,7 @@
         <v>5.06799983978271</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.11127519607544</v>
+        <v>4.1112756729126</v>
       </c>
       <c r="H1028" t="n">
         <v>1982566</v>
@@ -30239,7 +30239,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.2134895324707</v>
+        <v>4.21348905563354</v>
       </c>
       <c r="H1030" t="n">
         <v>2386015</v>
@@ -30268,7 +30268,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.31894779205322</v>
+        <v>4.31894874572754</v>
       </c>
       <c r="H1031" t="n">
         <v>3608828</v>
@@ -30413,7 +30413,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.31570339202881</v>
+        <v>4.31570386886597</v>
       </c>
       <c r="H1036" t="n">
         <v>1033265</v>
@@ -30500,7 +30500,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.54284524917603</v>
+        <v>4.54284572601318</v>
       </c>
       <c r="H1039" t="n">
         <v>3675186</v>
@@ -30529,7 +30529,7 @@
         <v>5.53800010681152</v>
       </c>
       <c r="G1040" t="n">
-        <v>4.49255084991455</v>
+        <v>4.49255037307739</v>
       </c>
       <c r="H1040" t="n">
         <v>1209926</v>
@@ -30558,7 +30558,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.46659088134766</v>
+        <v>4.4665904045105</v>
       </c>
       <c r="H1041" t="n">
         <v>985475</v>
@@ -30703,7 +30703,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.73916149139404</v>
+        <v>4.7391619682312</v>
       </c>
       <c r="H1046" t="n">
         <v>2599366</v>
@@ -30761,7 +30761,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.69697761535645</v>
+        <v>4.6969780921936</v>
       </c>
       <c r="H1048" t="n">
         <v>2389181</v>
@@ -30790,7 +30790,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.68399858474731</v>
+        <v>4.68399810791016</v>
       </c>
       <c r="H1049" t="n">
         <v>2601645</v>
@@ -30848,7 +30848,7 @@
         <v>5.78200006484985</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.69048833847046</v>
+        <v>4.69048881530762</v>
       </c>
       <c r="H1051" t="n">
         <v>1522914</v>
@@ -30993,7 +30993,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G1056" t="n">
-        <v>4.40331554412842</v>
+        <v>4.40331506729126</v>
       </c>
       <c r="H1056" t="n">
         <v>2173376</v>
@@ -31051,7 +31051,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>4.4941725730896</v>
+        <v>4.49417209625244</v>
       </c>
       <c r="H1058" t="n">
         <v>1269316</v>
@@ -31196,7 +31196,7 @@
         <v>5.96400022506714</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.83813095092773</v>
+        <v>4.83813047409058</v>
       </c>
       <c r="H1063" t="n">
         <v>1383343</v>
@@ -31254,7 +31254,7 @@
         <v>5.97399997711182</v>
       </c>
       <c r="G1065" t="n">
-        <v>4.84624290466309</v>
+        <v>4.84624338150024</v>
       </c>
       <c r="H1065" t="n">
         <v>2235634</v>
@@ -31283,7 +31283,7 @@
         <v>5.94399976730347</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.82190608978271</v>
+        <v>4.82190561294556</v>
       </c>
       <c r="H1066" t="n">
         <v>2592587</v>
@@ -31399,7 +31399,7 @@
         <v>5.87400007247925</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.76512098312378</v>
+        <v>4.76512050628662</v>
       </c>
       <c r="H1070" t="n">
         <v>1622984</v>
@@ -31457,7 +31457,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G1072" t="n">
-        <v>4.87869215011597</v>
+        <v>4.87869167327881</v>
       </c>
       <c r="H1072" t="n">
         <v>1042404</v>
@@ -31515,7 +31515,7 @@
         <v>6.10400009155273</v>
       </c>
       <c r="G1074" t="n">
-        <v>4.95170211791992</v>
+        <v>4.95170164108276</v>
       </c>
       <c r="H1074" t="n">
         <v>1199147</v>
@@ -31631,7 +31631,7 @@
         <v>6.15199995040894</v>
       </c>
       <c r="G1078" t="n">
-        <v>4.99064064025879</v>
+        <v>4.99064111709595</v>
       </c>
       <c r="H1078" t="n">
         <v>1736834</v>
@@ -31689,7 +31689,7 @@
         <v>6.5</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.27294635772705</v>
+        <v>5.27294588088989</v>
       </c>
       <c r="H1080" t="n">
         <v>10512927</v>
@@ -31718,7 +31718,7 @@
         <v>6.43800020217896</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.22265005111694</v>
+        <v>5.2226505279541</v>
       </c>
       <c r="H1081" t="n">
         <v>3172913</v>
@@ -31776,7 +31776,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.28917074203491</v>
+        <v>5.28917026519775</v>
       </c>
       <c r="H1083" t="n">
         <v>3042107</v>
@@ -31950,7 +31950,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.31350708007812</v>
+        <v>5.31350660324097</v>
       </c>
       <c r="H1089" t="n">
         <v>1843261</v>
@@ -32124,7 +32124,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.00037479400635</v>
+        <v>5.00037574768066</v>
       </c>
       <c r="H1095" t="n">
         <v>1842897</v>
@@ -32182,7 +32182,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1097" t="n">
-        <v>4.99712991714478</v>
+        <v>4.99713039398193</v>
       </c>
       <c r="H1097" t="n">
         <v>2246446</v>
@@ -32211,7 +32211,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.05553817749023</v>
+        <v>5.05553770065308</v>
       </c>
       <c r="H1098" t="n">
         <v>1921905</v>
@@ -32269,7 +32269,7 @@
         <v>6.29199981689453</v>
       </c>
       <c r="G1100" t="n">
-        <v>5.10421180725098</v>
+        <v>5.10421133041382</v>
       </c>
       <c r="H1100" t="n">
         <v>1028986</v>
@@ -32327,7 +32327,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.89978313446045</v>
+        <v>4.89978361129761</v>
       </c>
       <c r="H1102" t="n">
         <v>2730930</v>
@@ -32385,7 +32385,7 @@
         <v>6.13199996948242</v>
       </c>
       <c r="G1104" t="n">
-        <v>4.97441625595093</v>
+        <v>4.97441577911377</v>
       </c>
       <c r="H1104" t="n">
         <v>1543094</v>
@@ -32443,7 +32443,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.04580402374268</v>
+        <v>5.04580354690552</v>
       </c>
       <c r="H1106" t="n">
         <v>1943608</v>
@@ -32472,7 +32472,7 @@
         <v>6.01200008392334</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.87706995010376</v>
+        <v>4.8770694732666</v>
       </c>
       <c r="H1107" t="n">
         <v>2841431</v>
@@ -32501,7 +32501,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G1108" t="n">
-        <v>4.74889659881592</v>
+        <v>4.74889612197876</v>
       </c>
       <c r="H1108" t="n">
         <v>3881959</v>
@@ -32530,7 +32530,7 @@
         <v>5.9980001449585</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.86571264266968</v>
+        <v>4.86571216583252</v>
       </c>
       <c r="H1109" t="n">
         <v>2265679</v>
@@ -32617,7 +32617,7 @@
         <v>5.75799989700317</v>
       </c>
       <c r="G1112" t="n">
-        <v>4.67101860046387</v>
+        <v>4.67101907730103</v>
       </c>
       <c r="H1112" t="n">
         <v>2110850</v>
@@ -32675,7 +32675,7 @@
         <v>5.66200017929077</v>
       </c>
       <c r="G1114" t="n">
-        <v>4.59314203262329</v>
+        <v>4.59314155578613</v>
       </c>
       <c r="H1114" t="n">
         <v>2046864</v>
@@ -32762,7 +32762,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.21024513244629</v>
+        <v>4.21024465560913</v>
       </c>
       <c r="H1117" t="n">
         <v>7442160</v>
@@ -32820,7 +32820,7 @@
         <v>4.60099983215332</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.73243451118469</v>
+        <v>3.73243427276611</v>
       </c>
       <c r="H1119" t="n">
         <v>5550087</v>
@@ -32849,7 +32849,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.82247996330261</v>
+        <v>3.82247972488403</v>
       </c>
       <c r="H1120" t="n">
         <v>5287521</v>
@@ -33081,7 +33081,7 @@
         <v>4.66099977493286</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.7811074256897</v>
+        <v>3.78110766410828</v>
       </c>
       <c r="H1128" t="n">
         <v>3248155</v>
@@ -33110,7 +33110,7 @@
         <v>4.6710000038147</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.78922009468079</v>
+        <v>3.78921985626221</v>
       </c>
       <c r="H1129" t="n">
         <v>3429484</v>
@@ -33226,7 +33226,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.86953139305115</v>
+        <v>3.86953091621399</v>
       </c>
       <c r="H1133" t="n">
         <v>1636489</v>
@@ -33255,7 +33255,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.93767333030701</v>
+        <v>3.93767428398132</v>
       </c>
       <c r="H1134" t="n">
         <v>1588173</v>
@@ -33284,7 +33284,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.93118405342102</v>
+        <v>3.93118357658386</v>
       </c>
       <c r="H1135" t="n">
         <v>1943279</v>
@@ -33342,7 +33342,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.89386773109436</v>
+        <v>3.89386820793152</v>
       </c>
       <c r="H1137" t="n">
         <v>1417907</v>
@@ -33429,7 +33429,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G1140" t="n">
-        <v>4.05448961257935</v>
+        <v>4.0544900894165</v>
       </c>
       <c r="H1140" t="n">
         <v>2539969</v>
@@ -33516,7 +33516,7 @@
         <v>4.8769998550415</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.95633172988892</v>
+        <v>3.95633220672607</v>
       </c>
       <c r="H1143" t="n">
         <v>1366405</v>
@@ -33603,7 +33603,7 @@
         <v>4.41300010681152</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.57992482185364</v>
+        <v>3.57992458343506</v>
       </c>
       <c r="H1146" t="n">
         <v>3363384</v>
@@ -33632,7 +33632,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.61318445205688</v>
+        <v>3.61318469047546</v>
       </c>
       <c r="H1147" t="n">
         <v>3241105</v>
@@ -33661,7 +33661,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.59209251403809</v>
+        <v>3.59209299087524</v>
       </c>
       <c r="H1148" t="n">
         <v>2403733</v>
@@ -33690,7 +33690,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.60669493675232</v>
+        <v>3.6066951751709</v>
       </c>
       <c r="H1149" t="n">
         <v>2415234</v>
@@ -33719,7 +33719,7 @@
         <v>4.52099990844727</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.66753673553467</v>
+        <v>3.66753697395325</v>
       </c>
       <c r="H1150" t="n">
         <v>1575910</v>
@@ -33748,7 +33748,7 @@
         <v>4.54300022125244</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.68538355827332</v>
+        <v>3.68538379669189</v>
       </c>
       <c r="H1151" t="n">
         <v>2039720</v>
@@ -33777,7 +33777,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.73567914962769</v>
+        <v>3.73567938804626</v>
       </c>
       <c r="H1152" t="n">
         <v>1172764</v>
@@ -33806,7 +33806,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.85817408561707</v>
+        <v>3.85817432403564</v>
       </c>
       <c r="H1153" t="n">
         <v>3842670</v>
@@ -33864,7 +33864,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.84925055503845</v>
+        <v>3.84925007820129</v>
       </c>
       <c r="H1155" t="n">
         <v>1572535</v>
@@ -33980,7 +33980,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.85006141662598</v>
+        <v>3.85006165504456</v>
       </c>
       <c r="H1159" t="n">
         <v>1808335</v>
@@ -34009,7 +34009,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.85168433189392</v>
+        <v>3.85168480873108</v>
       </c>
       <c r="H1160" t="n">
         <v>1917361</v>
@@ -34038,7 +34038,7 @@
         <v>4.61700010299683</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.74541449546814</v>
+        <v>3.74541401863098</v>
       </c>
       <c r="H1161" t="n">
         <v>2119596</v>
@@ -34125,7 +34125,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.60831737518311</v>
+        <v>3.60831713676453</v>
       </c>
       <c r="H1164" t="n">
         <v>1746404</v>
@@ -34212,7 +34212,7 @@
         <v>4.4689998626709</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.62535309791565</v>
+        <v>3.62535285949707</v>
       </c>
       <c r="H1167" t="n">
         <v>2099491</v>
@@ -34241,7 +34241,7 @@
         <v>4.56799983978271</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.70566415786743</v>
+        <v>3.70566368103027</v>
       </c>
       <c r="H1168" t="n">
         <v>2290244</v>
@@ -34270,7 +34270,7 @@
         <v>4.63899993896484</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.76326084136963</v>
+        <v>3.76326107978821</v>
       </c>
       <c r="H1169" t="n">
         <v>1807513</v>
@@ -34299,7 +34299,7 @@
         <v>4.75</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.85330677032471</v>
+        <v>3.85330653190613</v>
       </c>
       <c r="H1170" t="n">
         <v>1116248</v>
@@ -34328,7 +34328,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.81761288642883</v>
+        <v>3.81761312484741</v>
       </c>
       <c r="H1171" t="n">
         <v>885772</v>
@@ -34357,7 +34357,7 @@
         <v>4.68699979782104</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.80219912528992</v>
+        <v>3.80219960212708</v>
       </c>
       <c r="H1172" t="n">
         <v>1423396</v>
@@ -34415,7 +34415,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.68781709671021</v>
+        <v>3.68781757354736</v>
       </c>
       <c r="H1174" t="n">
         <v>1820197</v>
@@ -34444,7 +34444,7 @@
         <v>4.51399993896484</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.66185808181763</v>
+        <v>3.66185784339905</v>
       </c>
       <c r="H1175" t="n">
         <v>2396662</v>
@@ -34473,7 +34473,7 @@
         <v>4.51100015640259</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.79477214813232</v>
+        <v>3.79477262496948</v>
       </c>
       <c r="H1176" t="n">
         <v>1930235</v>
@@ -34531,7 +34531,7 @@
         <v>4.42899990081787</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.72579145431519</v>
+        <v>3.72579121589661</v>
       </c>
       <c r="H1178" t="n">
         <v>1352870</v>
@@ -34560,7 +34560,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.85449910163879</v>
+        <v>3.85449862480164</v>
       </c>
       <c r="H1179" t="n">
         <v>1272388</v>
@@ -34589,7 +34589,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.86543488502502</v>
+        <v>3.86543440818787</v>
       </c>
       <c r="H1180" t="n">
         <v>803294</v>
@@ -34618,7 +34618,7 @@
         <v>4.66699981689453</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.92600345611572</v>
+        <v>3.92600297927856</v>
       </c>
       <c r="H1181" t="n">
         <v>1236000</v>
@@ -34734,7 +34734,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.84861040115356</v>
+        <v>3.84861016273499</v>
       </c>
       <c r="H1185" t="n">
         <v>982607</v>
@@ -34792,7 +34792,7 @@
         <v>4.58900022506714</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.86038780212402</v>
+        <v>3.8603880405426</v>
       </c>
       <c r="H1187" t="n">
         <v>1054236</v>
@@ -34821,7 +34821,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.80402541160583</v>
+        <v>3.80402565002441</v>
       </c>
       <c r="H1188" t="n">
         <v>1390641</v>
@@ -34879,7 +34879,7 @@
         <v>4.32299995422363</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.63662123680115</v>
+        <v>3.63662147521973</v>
       </c>
       <c r="H1190" t="n">
         <v>2686190</v>
@@ -34966,7 +34966,7 @@
         <v>4.21299982070923</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.54408597946167</v>
+        <v>3.54408621788025</v>
       </c>
       <c r="H1193" t="n">
         <v>2162957</v>
@@ -34995,7 +34995,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.39014220237732</v>
+        <v>3.39014196395874</v>
       </c>
       <c r="H1194" t="n">
         <v>1378418</v>
@@ -35024,7 +35024,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.56679916381836</v>
+        <v>3.56679940223694</v>
       </c>
       <c r="H1195" t="n">
         <v>3470441</v>
@@ -35082,7 +35082,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.56848216056824</v>
+        <v>3.56848192214966</v>
       </c>
       <c r="H1197" t="n">
         <v>852460</v>
@@ -35111,7 +35111,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.53483319282532</v>
+        <v>3.53483295440674</v>
       </c>
       <c r="H1198" t="n">
         <v>853012</v>
@@ -35227,7 +35227,7 @@
         <v>4.08300018310547</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.43472743034363</v>
+        <v>3.43472719192505</v>
       </c>
       <c r="H1202" t="n">
         <v>1367751</v>
@@ -35372,7 +35372,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.17478799819946</v>
+        <v>3.17478823661804</v>
       </c>
       <c r="H1207" t="n">
         <v>2164862</v>
@@ -35401,7 +35401,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.25218081474304</v>
+        <v>3.25218105316162</v>
       </c>
       <c r="H1208" t="n">
         <v>1272968</v>
@@ -35459,7 +35459,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.48267674446106</v>
+        <v>3.48267698287964</v>
       </c>
       <c r="H1210" t="n">
         <v>1992624</v>
@@ -35488,7 +35488,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.41958475112915</v>
+        <v>3.41958498954773</v>
       </c>
       <c r="H1211" t="n">
         <v>1022124</v>
@@ -35546,7 +35546,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.33125615119934</v>
+        <v>3.33125638961792</v>
       </c>
       <c r="H1213" t="n">
         <v>1482347</v>
@@ -35575,7 +35575,7 @@
         <v>3.875</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.25975203514099</v>
+        <v>3.25975227355957</v>
       </c>
       <c r="H1214" t="n">
         <v>1737711</v>
@@ -35604,7 +35604,7 @@
         <v>4.09100008010864</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.44145703315735</v>
+        <v>3.44145727157593</v>
       </c>
       <c r="H1215" t="n">
         <v>2031711</v>
@@ -35691,7 +35691,7 @@
         <v>4.16900014877319</v>
       </c>
       <c r="G1218" t="n">
-        <v>3.50707292556763</v>
+        <v>3.50707268714905</v>
       </c>
       <c r="H1218" t="n">
         <v>1806984</v>
@@ -35720,7 +35720,7 @@
         <v>4.12099981307983</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.46669340133667</v>
+        <v>3.46669363975525</v>
       </c>
       <c r="H1219" t="n">
         <v>2020551</v>
@@ -35749,7 +35749,7 @@
         <v>4.11700010299683</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.46332883834839</v>
+        <v>3.46332907676697</v>
       </c>
       <c r="H1220" t="n">
         <v>780425</v>
@@ -35807,7 +35807,7 @@
         <v>4.02299976348877</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.38425326347351</v>
+        <v>3.38425350189209</v>
       </c>
       <c r="H1222" t="n">
         <v>1385705</v>
@@ -35836,7 +35836,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.2959246635437</v>
+        <v>3.29592490196228</v>
       </c>
       <c r="H1223" t="n">
         <v>2424724</v>
@@ -35894,7 +35894,7 @@
         <v>4.20800018310547</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.5398805141449</v>
+        <v>3.53988075256348</v>
       </c>
       <c r="H1225" t="n">
         <v>1809630</v>
@@ -35923,7 +35923,7 @@
         <v>4.17700004577637</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.51380228996277</v>
+        <v>3.51380252838135</v>
       </c>
       <c r="H1226" t="n">
         <v>1062850</v>
@@ -35952,7 +35952,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G1227" t="n">
-        <v>3.44566321372986</v>
+        <v>3.44566297531128</v>
       </c>
       <c r="H1227" t="n">
         <v>881224</v>
@@ -35981,7 +35981,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1228" t="n">
-        <v>3.60044884681702</v>
+        <v>3.6004490852356</v>
       </c>
       <c r="H1228" t="n">
         <v>1426287</v>
@@ -36010,7 +36010,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.58025908470154</v>
+        <v>3.5802595615387</v>
       </c>
       <c r="H1229" t="n">
         <v>1188294</v>
@@ -36068,7 +36068,7 @@
         <v>4.40700006484985</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.70728445053101</v>
+        <v>3.70728397369385</v>
       </c>
       <c r="H1231" t="n">
         <v>2232915</v>
@@ -36126,7 +36126,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.66774702072144</v>
+        <v>3.66774678230286</v>
       </c>
       <c r="H1233" t="n">
         <v>2584764</v>
@@ -36155,7 +36155,7 @@
         <v>4.29099988937378</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.60970211029053</v>
+        <v>3.60970234870911</v>
       </c>
       <c r="H1234" t="n">
         <v>2859774</v>
@@ -36213,7 +36213,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.59624242782593</v>
+        <v>3.59624266624451</v>
       </c>
       <c r="H1236" t="n">
         <v>1613160</v>
@@ -36271,7 +36271,7 @@
         <v>4.11499977111816</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.46164608001709</v>
+        <v>3.46164631843567</v>
       </c>
       <c r="H1238" t="n">
         <v>2417292</v>
@@ -36300,7 +36300,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.39014220237732</v>
+        <v>3.39014196395874</v>
       </c>
       <c r="H1239" t="n">
         <v>1972997</v>
@@ -36387,7 +36387,7 @@
         <v>3.87899994850159</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.26311683654785</v>
+        <v>3.26311707496643</v>
       </c>
       <c r="H1242" t="n">
         <v>2951087</v>
@@ -36532,7 +36532,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.17983531951904</v>
+        <v>3.17983555793762</v>
       </c>
       <c r="H1247" t="n">
         <v>4372863</v>
@@ -36648,7 +36648,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.16721749305725</v>
+        <v>3.16721701622009</v>
       </c>
       <c r="H1251" t="n">
         <v>2569808</v>
@@ -36677,7 +36677,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.1832001209259</v>
+        <v>3.18320035934448</v>
       </c>
       <c r="H1252" t="n">
         <v>1415765</v>
@@ -36909,7 +36909,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.16637587547302</v>
+        <v>3.16637563705444</v>
       </c>
       <c r="H1260" t="n">
         <v>1018012</v>
@@ -36996,7 +36996,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G1263" t="n">
-        <v>3.0469217300415</v>
+        <v>3.04692196846008</v>
       </c>
       <c r="H1263" t="n">
         <v>2294253</v>
@@ -37199,7 +37199,7 @@
         <v>3.3659999370575</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.83156776428223</v>
+        <v>2.83156752586365</v>
       </c>
       <c r="H1270" t="n">
         <v>2368766</v>
@@ -37431,7 +37431,7 @@
         <v>3.5</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.94429230690002</v>
+        <v>2.94429206848145</v>
       </c>
       <c r="H1278" t="n">
         <v>3129866</v>
@@ -37547,7 +37547,7 @@
         <v>3.56900000572205</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.00233674049377</v>
+        <v>3.0023365020752</v>
       </c>
       <c r="H1282" t="n">
         <v>1713888</v>
@@ -37605,7 +37605,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.95775198936462</v>
+        <v>2.95775175094604</v>
       </c>
       <c r="H1284" t="n">
         <v>2573864</v>
@@ -37634,7 +37634,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.11085510253906</v>
+        <v>3.11085486412048</v>
       </c>
       <c r="H1285" t="n">
         <v>3358682</v>
@@ -37663,7 +37663,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1286" t="n">
-        <v>3.17983531951904</v>
+        <v>3.17983555793762</v>
       </c>
       <c r="H1286" t="n">
         <v>2688752</v>
@@ -37692,7 +37692,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.17478799819946</v>
+        <v>3.17478823661804</v>
       </c>
       <c r="H1287" t="n">
         <v>1764647</v>
@@ -37779,7 +37779,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.2118022441864</v>
+        <v>3.21180200576782</v>
       </c>
       <c r="H1290" t="n">
         <v>1372350</v>
@@ -37866,7 +37866,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G1293" t="n">
-        <v>3.07552313804626</v>
+        <v>3.07552337646484</v>
       </c>
       <c r="H1293" t="n">
         <v>2217035</v>
@@ -37895,7 +37895,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G1294" t="n">
-        <v>3.41369676589966</v>
+        <v>3.41369652748108</v>
       </c>
       <c r="H1294" t="n">
         <v>8350860</v>
@@ -37953,7 +37953,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1296" t="n">
-        <v>3.38593602180481</v>
+        <v>3.38593626022339</v>
       </c>
       <c r="H1296" t="n">
         <v>1598547</v>
@@ -38156,7 +38156,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.42883849143982</v>
+        <v>3.4288387298584</v>
       </c>
       <c r="H1303" t="n">
         <v>1307714</v>
@@ -38243,7 +38243,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.5011842250824</v>
+        <v>3.50118398666382</v>
       </c>
       <c r="H1306" t="n">
         <v>995208</v>
@@ -38272,7 +38272,7 @@
         <v>4.12099981307983</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.46669340133667</v>
+        <v>3.46669363975525</v>
       </c>
       <c r="H1307" t="n">
         <v>1315283</v>
@@ -38359,7 +38359,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.5583872795105</v>
+        <v>3.55838751792908</v>
       </c>
       <c r="H1310" t="n">
         <v>1498119</v>
@@ -38417,7 +38417,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.56679916381836</v>
+        <v>3.56679940223694</v>
       </c>
       <c r="H1312" t="n">
         <v>1981212</v>
@@ -38446,7 +38446,7 @@
         <v>4.32600021362305</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.63914513587952</v>
+        <v>3.6391453742981</v>
       </c>
       <c r="H1313" t="n">
         <v>2960871</v>
@@ -38504,7 +38504,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.56343460083008</v>
+        <v>3.56343483924866</v>
       </c>
       <c r="H1315" t="n">
         <v>1887472</v>
@@ -38649,7 +38649,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.36658763885498</v>
+        <v>3.3665874004364</v>
       </c>
       <c r="H1320" t="n">
         <v>2636832</v>
@@ -38678,7 +38678,7 @@
         <v>4.16900014877319</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.50707292556763</v>
+        <v>3.50707268714905</v>
       </c>
       <c r="H1321" t="n">
         <v>3728189</v>
@@ -38707,7 +38707,7 @@
         <v>4.15100002288818</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.49193048477173</v>
+        <v>3.49193072319031</v>
       </c>
       <c r="H1322" t="n">
         <v>1434174</v>
@@ -38794,7 +38794,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.38593602180481</v>
+        <v>3.38593626022339</v>
       </c>
       <c r="H1325" t="n">
         <v>780175</v>
@@ -38823,7 +38823,7 @@
         <v>4.00699996948242</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.37079381942749</v>
+        <v>3.37079405784607</v>
       </c>
       <c r="H1326" t="n">
         <v>1016341</v>
@@ -38910,7 +38910,7 @@
         <v>4.0789999961853</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.43136215209961</v>
+        <v>3.43136239051819</v>
       </c>
       <c r="H1329" t="n">
         <v>929483</v>
@@ -39055,7 +39055,7 @@
         <v>4.08900022506714</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.43977451324463</v>
+        <v>3.43977475166321</v>
       </c>
       <c r="H1334" t="n">
         <v>1180250</v>
@@ -39142,7 +39142,7 @@
         <v>4.44099998474121</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.73588585853577</v>
+        <v>3.73588609695435</v>
       </c>
       <c r="H1337" t="n">
         <v>1610539</v>
@@ -39229,7 +39229,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1340" t="n">
-        <v>3.81916761398315</v>
+        <v>3.81916737556458</v>
       </c>
       <c r="H1340" t="n">
         <v>1362107</v>
@@ -39258,7 +39258,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.84019804000854</v>
+        <v>3.84019827842712</v>
       </c>
       <c r="H1341" t="n">
         <v>1203558</v>
@@ -39432,7 +39432,7 @@
         <v>4.59100008010864</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.86206984519958</v>
+        <v>3.86207032203674</v>
       </c>
       <c r="H1347" t="n">
         <v>1615322</v>
@@ -39461,7 +39461,7 @@
         <v>4.53700017929077</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.81664371490479</v>
+        <v>3.81664443016052</v>
       </c>
       <c r="H1348" t="n">
         <v>2276340</v>
@@ -39519,7 +39519,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.85113406181335</v>
+        <v>3.85113430023193</v>
       </c>
       <c r="H1350" t="n">
         <v>693551</v>
@@ -39548,7 +39548,7 @@
         <v>4.56899976730347</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.84356307983398</v>
+        <v>3.84356260299683</v>
       </c>
       <c r="H1351" t="n">
         <v>745424</v>
@@ -39577,7 +39577,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.90497255325317</v>
+        <v>3.90497303009033</v>
       </c>
       <c r="H1352" t="n">
         <v>1284008</v>
@@ -39606,7 +39606,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.85618162155151</v>
+        <v>3.85618138313293</v>
       </c>
       <c r="H1353" t="n">
         <v>1766336</v>
@@ -39664,7 +39664,7 @@
         <v>4.58599996566772</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.85786390304565</v>
+        <v>3.85786366462708</v>
       </c>
       <c r="H1355" t="n">
         <v>1795596</v>
@@ -39693,7 +39693,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.85618162155151</v>
+        <v>3.85618138313293</v>
       </c>
       <c r="H1356" t="n">
         <v>2609924</v>
@@ -39722,7 +39722,7 @@
         <v>4.65899991989136</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.919273853302</v>
+        <v>3.91927337646484</v>
       </c>
       <c r="H1357" t="n">
         <v>2680349</v>
@@ -39751,7 +39751,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.0605993270874</v>
+        <v>4.06059980392456</v>
       </c>
       <c r="H1358" t="n">
         <v>4196593</v>
@@ -39780,7 +39780,7 @@
         <v>4.75899982452393</v>
       </c>
       <c r="G1359" t="n">
-        <v>4.00339651107788</v>
+        <v>4.00339603424072</v>
       </c>
       <c r="H1359" t="n">
         <v>1911674</v>
@@ -39896,7 +39896,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.83767437934875</v>
+        <v>3.83767414093018</v>
       </c>
       <c r="H1363" t="n">
         <v>2263573</v>
@@ -39925,7 +39925,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.90917873382568</v>
+        <v>3.90917825698853</v>
       </c>
       <c r="H1364" t="n">
         <v>1819880</v>
@@ -39954,7 +39954,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.95376396179199</v>
+        <v>3.95376348495483</v>
       </c>
       <c r="H1365" t="n">
         <v>1904113</v>
@@ -39983,7 +39983,7 @@
         <v>4.78900003433228</v>
       </c>
       <c r="G1366" t="n">
-        <v>4.02863311767578</v>
+        <v>4.02863264083862</v>
       </c>
       <c r="H1366" t="n">
         <v>5871194</v>
@@ -40186,7 +40186,7 @@
         <v>4.76700019836426</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.01012659072876</v>
+        <v>4.0101261138916</v>
       </c>
       <c r="H1373" t="n">
         <v>3059807</v>
@@ -40244,7 +40244,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.05639362335205</v>
+        <v>4.05639314651489</v>
       </c>
       <c r="H1375" t="n">
         <v>1559692</v>
@@ -40418,7 +40418,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1381" t="n">
-        <v>4.16238832473755</v>
+        <v>4.16238784790039</v>
       </c>
       <c r="H1381" t="n">
         <v>1401021</v>
@@ -40447,7 +40447,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G1382" t="n">
-        <v>4.07574129104614</v>
+        <v>4.0757417678833</v>
       </c>
       <c r="H1382" t="n">
         <v>1297124</v>
@@ -40476,7 +40476,7 @@
         <v>4.74900007247925</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.9949836730957</v>
+        <v>3.99498414993286</v>
       </c>
       <c r="H1383" t="n">
         <v>2196345</v>
@@ -40534,7 +40534,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.86627626419067</v>
+        <v>3.86627674102783</v>
       </c>
       <c r="H1385" t="n">
         <v>2645603</v>
@@ -40563,7 +40563,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.66942930221558</v>
+        <v>3.669429063797</v>
       </c>
       <c r="H1386" t="n">
         <v>3488551</v>
@@ -40592,7 +40592,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.73672747612</v>
+        <v>3.73672723770142</v>
       </c>
       <c r="H1387" t="n">
         <v>1881833</v>
@@ -40650,7 +40650,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.746821641922</v>
+        <v>3.74682188034058</v>
       </c>
       <c r="H1389" t="n">
         <v>2366506</v>
@@ -40679,7 +40679,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.79561328887939</v>
+        <v>3.79561305046082</v>
       </c>
       <c r="H1390" t="n">
         <v>2003223</v>
@@ -40766,7 +40766,7 @@
         <v>4.34899997711182</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.65849351882935</v>
+        <v>3.65849304199219</v>
       </c>
       <c r="H1393" t="n">
         <v>1563435</v>
@@ -40795,7 +40795,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.6963484287262</v>
+        <v>3.69634819030762</v>
       </c>
       <c r="H1394" t="n">
         <v>1311955</v>
@@ -40824,7 +40824,7 @@
         <v>4.40899991989136</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.70896697044373</v>
+        <v>3.70896625518799</v>
       </c>
       <c r="H1395" t="n">
         <v>1151563</v>
@@ -40853,7 +40853,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.76448798179626</v>
+        <v>3.76448774337769</v>
       </c>
       <c r="H1396" t="n">
         <v>1206554</v>
@@ -40882,7 +40882,7 @@
         <v>4.55900001525879</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.83515048027039</v>
+        <v>3.83515095710754</v>
       </c>
       <c r="H1397" t="n">
         <v>1778437</v>
@@ -40940,7 +40940,7 @@
         <v>4.62599992752075</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.89151287078857</v>
+        <v>3.89151334762573</v>
       </c>
       <c r="H1399" t="n">
         <v>1320958</v>
@@ -40969,7 +40969,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.95460486412048</v>
+        <v>3.95460534095764</v>
       </c>
       <c r="H1400" t="n">
         <v>2792824</v>
@@ -40998,7 +40998,7 @@
         <v>4.48299980163574</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.77121758460999</v>
+        <v>3.77121782302856</v>
       </c>
       <c r="H1401" t="n">
         <v>4299498</v>
@@ -41085,7 +41085,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.88141846656799</v>
+        <v>3.88141775131226</v>
       </c>
       <c r="H1404" t="n">
         <v>1594098</v>
@@ -41172,7 +41172,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.97563576698303</v>
+        <v>3.97563529014587</v>
       </c>
       <c r="H1407" t="n">
         <v>1984155</v>
@@ -41230,7 +41230,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1409" t="n">
-        <v>4.02442646026611</v>
+        <v>4.02442693710327</v>
       </c>
       <c r="H1409" t="n">
         <v>1224894</v>
@@ -41346,7 +41346,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.84861040115356</v>
+        <v>3.84861016273499</v>
       </c>
       <c r="H1413" t="n">
         <v>2048783</v>
@@ -41433,7 +41433,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.99245953559875</v>
+        <v>3.99246001243591</v>
       </c>
       <c r="H1416" t="n">
         <v>2199392</v>
@@ -41578,7 +41578,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G1421" t="n">
-        <v>4.14303922653198</v>
+        <v>4.14303970336914</v>
       </c>
       <c r="H1421" t="n">
         <v>932185</v>
@@ -41636,7 +41636,7 @@
         <v>4.90299987792969</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.12453317642212</v>
+        <v>4.12453269958496</v>
       </c>
       <c r="H1423" t="n">
         <v>2276972</v>
@@ -41665,7 +41665,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G1424" t="n">
-        <v>4.02358627319336</v>
+        <v>4.02358531951904</v>
       </c>
       <c r="H1424" t="n">
         <v>2609423</v>
@@ -41781,7 +41781,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G1428" t="n">
-        <v>4.0605993270874</v>
+        <v>4.06059980392456</v>
       </c>
       <c r="H1428" t="n">
         <v>1388696</v>
@@ -41897,7 +41897,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1432" t="n">
-        <v>4.06312322616577</v>
+        <v>4.06312274932861</v>
       </c>
       <c r="H1432" t="n">
         <v>901576</v>
@@ -41984,7 +41984,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.87468886375427</v>
+        <v>3.87468791007996</v>
       </c>
       <c r="H1435" t="n">
         <v>1604844</v>
@@ -42100,7 +42100,7 @@
         <v>4.46700000762939</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.75775814056396</v>
+        <v>3.75775790214539</v>
       </c>
       <c r="H1439" t="n">
         <v>1252337</v>
@@ -42129,7 +42129,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.87468886375427</v>
+        <v>3.87468791007996</v>
       </c>
       <c r="H1440" t="n">
         <v>1471923</v>
@@ -42158,7 +42158,7 @@
         <v>4.58300018310547</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.85534048080444</v>
+        <v>3.85534071922302</v>
       </c>
       <c r="H1441" t="n">
         <v>1250531</v>
@@ -42187,7 +42187,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.82337331771851</v>
+        <v>3.82337355613708</v>
       </c>
       <c r="H1442" t="n">
         <v>2119319</v>
@@ -42216,7 +42216,7 @@
         <v>4.49900007247925</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.78467726707458</v>
+        <v>3.78467702865601</v>
       </c>
       <c r="H1443" t="n">
         <v>2947860</v>
@@ -42274,7 +42274,7 @@
         <v>4.56099987030029</v>
       </c>
       <c r="G1445" t="n">
-        <v>3.83683300018311</v>
+        <v>3.83683323860168</v>
       </c>
       <c r="H1445" t="n">
         <v>965363</v>
@@ -42361,7 +42361,7 @@
         <v>4.67899990081787</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.93609762191772</v>
+        <v>3.93609809875488</v>
       </c>
       <c r="H1448" t="n">
         <v>1534277</v>
@@ -42390,7 +42390,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.90917873382568</v>
+        <v>3.90917825698853</v>
       </c>
       <c r="H1449" t="n">
         <v>1323793</v>
@@ -42419,7 +42419,7 @@
         <v>4.61899995803833</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.8856246471405</v>
+        <v>3.88562417030334</v>
       </c>
       <c r="H1450" t="n">
         <v>3112143</v>
@@ -42448,7 +42448,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1451" t="n">
-        <v>3.84440445899963</v>
+        <v>3.84440469741821</v>
       </c>
       <c r="H1451" t="n">
         <v>1764816</v>
@@ -42506,7 +42506,7 @@
         <v>4.43300008773804</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.72915625572205</v>
+        <v>3.72915601730347</v>
       </c>
       <c r="H1453" t="n">
         <v>4104182</v>
@@ -42535,7 +42535,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.74345707893372</v>
+        <v>3.74345684051514</v>
       </c>
       <c r="H1454" t="n">
         <v>3310751</v>
@@ -42622,7 +42622,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.74345707893372</v>
+        <v>3.74345684051514</v>
       </c>
       <c r="H1457" t="n">
         <v>1671361</v>
@@ -42651,7 +42651,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.78131222724915</v>
+        <v>3.78131198883057</v>
       </c>
       <c r="H1458" t="n">
         <v>2078424</v>
@@ -42680,7 +42680,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.78383612632751</v>
+        <v>3.78383660316467</v>
       </c>
       <c r="H1459" t="n">
         <v>2243918</v>
@@ -42709,7 +42709,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.80570793151855</v>
+        <v>3.80570840835571</v>
       </c>
       <c r="H1460" t="n">
         <v>2202383</v>
@@ -42767,7 +42767,7 @@
         <v>4.57100009918213</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.8452455997467</v>
+        <v>3.84524536132812</v>
       </c>
       <c r="H1462" t="n">
         <v>1737710</v>
@@ -42825,7 +42825,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.72999739646912</v>
+        <v>3.7299976348877</v>
       </c>
       <c r="H1464" t="n">
         <v>3422951</v>
@@ -42883,7 +42883,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.76364636421204</v>
+        <v>3.76364660263062</v>
       </c>
       <c r="H1466" t="n">
         <v>1255557</v>
@@ -42912,7 +42912,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.81412029266357</v>
+        <v>3.81411981582642</v>
       </c>
       <c r="H1467" t="n">
         <v>1845430</v>
@@ -43028,7 +43028,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.90917873382568</v>
+        <v>3.90917825698853</v>
       </c>
       <c r="H1471" t="n">
         <v>2049781</v>
@@ -43057,7 +43057,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.96890616416931</v>
+        <v>3.96890568733215</v>
       </c>
       <c r="H1472" t="n">
         <v>1326059</v>
@@ -43115,7 +43115,7 @@
         <v>4.82399988174438</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.05807590484619</v>
+        <v>4.05807542800903</v>
       </c>
       <c r="H1474" t="n">
         <v>3200900</v>
@@ -43144,7 +43144,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.07153558731079</v>
+        <v>4.07153606414795</v>
       </c>
       <c r="H1475" t="n">
         <v>4038631</v>
@@ -43260,7 +43260,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1479" t="n">
-        <v>4.26357221603394</v>
+        <v>4.26357269287109</v>
       </c>
       <c r="H1479" t="n">
         <v>3637164</v>
@@ -43318,7 +43318,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1481" t="n">
-        <v>4.27238130569458</v>
+        <v>4.27238082885742</v>
       </c>
       <c r="H1481" t="n">
         <v>2743673</v>
@@ -43347,7 +43347,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.29880857467651</v>
+        <v>4.29880905151367</v>
       </c>
       <c r="H1482" t="n">
         <v>1983741</v>
@@ -43376,7 +43376,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1483" t="n">
-        <v>4.27238130569458</v>
+        <v>4.27238082885742</v>
       </c>
       <c r="H1483" t="n">
         <v>1777355</v>
@@ -43492,7 +43492,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.07858276367188</v>
+        <v>4.07858228683472</v>
       </c>
       <c r="H1487" t="n">
         <v>1319825</v>
@@ -43637,7 +43637,7 @@
         <v>4.56899976730347</v>
       </c>
       <c r="G1492" t="n">
-        <v>4.02484750747681</v>
+        <v>4.02484703063965</v>
       </c>
       <c r="H1492" t="n">
         <v>1283800</v>
@@ -43695,7 +43695,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1494" t="n">
-        <v>4.00458669662476</v>
+        <v>4.0045862197876</v>
       </c>
       <c r="H1494" t="n">
         <v>1374433</v>
@@ -43753,7 +43753,7 @@
         <v>4.50699996948242</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.97023177146912</v>
+        <v>3.97023129463196</v>
       </c>
       <c r="H1496" t="n">
         <v>930525</v>
@@ -44246,7 +44246,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1513" t="n">
-        <v>4.18252944946289</v>
+        <v>4.18252897262573</v>
       </c>
       <c r="H1513" t="n">
         <v>2073053</v>
@@ -44391,7 +44391,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G1518" t="n">
-        <v>4.26004886627197</v>
+        <v>4.26004934310913</v>
       </c>
       <c r="H1518" t="n">
         <v>2157314</v>
@@ -44536,7 +44536,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1523" t="n">
-        <v>4.01868104934692</v>
+        <v>4.01868152618408</v>
       </c>
       <c r="H1523" t="n">
         <v>3026688</v>
@@ -44594,7 +44594,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.94468522071838</v>
+        <v>3.94468569755554</v>
       </c>
       <c r="H1525" t="n">
         <v>1481934</v>
@@ -44681,7 +44681,7 @@
         <v>4.35099983215332</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.83281064033508</v>
+        <v>3.8328104019165</v>
       </c>
       <c r="H1528" t="n">
         <v>1313742</v>
@@ -44710,7 +44710,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.84778618812561</v>
+        <v>3.84778594970703</v>
       </c>
       <c r="H1529" t="n">
         <v>1296121</v>
@@ -44797,7 +44797,7 @@
         <v>4.47100019454956</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.93851900100708</v>
+        <v>3.93851947784424</v>
       </c>
       <c r="H1532" t="n">
         <v>1809355</v>
@@ -44913,7 +44913,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.95349454879761</v>
+        <v>3.95349407196045</v>
       </c>
       <c r="H1536" t="n">
         <v>1423494</v>
@@ -44942,7 +44942,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.92530560493469</v>
+        <v>3.92530512809753</v>
       </c>
       <c r="H1537" t="n">
         <v>1819378</v>
@@ -44971,7 +44971,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.84073901176453</v>
+        <v>3.84073853492737</v>
       </c>
       <c r="H1538" t="n">
         <v>1558430</v>
@@ -45029,7 +45029,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.66455817222595</v>
+        <v>3.66455793380737</v>
       </c>
       <c r="H1540" t="n">
         <v>4026623</v>
@@ -45116,7 +45116,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.62051320075989</v>
+        <v>3.62051296234131</v>
       </c>
       <c r="H1543" t="n">
         <v>2643345</v>
@@ -45174,7 +45174,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.63636875152588</v>
+        <v>3.63636898994446</v>
       </c>
       <c r="H1545" t="n">
         <v>1760575</v>
@@ -45232,7 +45232,7 @@
         <v>4.23299980163574</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.72886395454407</v>
+        <v>3.72886371612549</v>
       </c>
       <c r="H1547" t="n">
         <v>1519824</v>
@@ -45348,7 +45348,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.84073901176453</v>
+        <v>3.84073853492737</v>
       </c>
       <c r="H1551" t="n">
         <v>1258004</v>
@@ -45464,7 +45464,7 @@
         <v>4.44099998474121</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.91209173202515</v>
+        <v>3.9120922088623</v>
       </c>
       <c r="H1555" t="n">
         <v>1441226</v>
@@ -45493,7 +45493,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.98961091041565</v>
+        <v>3.98961138725281</v>
       </c>
       <c r="H1556" t="n">
         <v>2208333</v>
@@ -45522,7 +45522,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.98961091041565</v>
+        <v>3.98961138725281</v>
       </c>
       <c r="H1557" t="n">
         <v>1771099</v>
@@ -45580,7 +45580,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1559" t="n">
-        <v>4.00458669662476</v>
+        <v>4.0045862197876</v>
       </c>
       <c r="H1559" t="n">
         <v>1818131</v>
@@ -45638,7 +45638,7 @@
         <v>4.46099996566772</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.92971014976501</v>
+        <v>3.92970967292786</v>
       </c>
       <c r="H1561" t="n">
         <v>1580647</v>
@@ -45696,7 +45696,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.95173215866089</v>
+        <v>3.95173263549805</v>
       </c>
       <c r="H1563" t="n">
         <v>930940</v>
@@ -45841,7 +45841,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G1568" t="n">
-        <v>4.01515769958496</v>
+        <v>4.0151572227478</v>
       </c>
       <c r="H1568" t="n">
         <v>2517345</v>
@@ -45870,7 +45870,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.01868104934692</v>
+        <v>4.01868152618408</v>
       </c>
       <c r="H1569" t="n">
         <v>2341666</v>
@@ -46044,7 +46044,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1575" t="n">
-        <v>4.2459545135498</v>
+        <v>4.24595403671265</v>
       </c>
       <c r="H1575" t="n">
         <v>1850014</v>
@@ -46131,7 +46131,7 @@
         <v>4.86100006103516</v>
       </c>
       <c r="G1578" t="n">
-        <v>4.28207111358643</v>
+        <v>4.28207159042358</v>
       </c>
       <c r="H1578" t="n">
         <v>3296575</v>
@@ -46160,7 +46160,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G1579" t="n">
-        <v>4.25123929977417</v>
+        <v>4.25123977661133</v>
       </c>
       <c r="H1579" t="n">
         <v>3303443</v>
@@ -46305,7 +46305,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G1584" t="n">
-        <v>4.27942895889282</v>
+        <v>4.27942848205566</v>
       </c>
       <c r="H1584" t="n">
         <v>961055</v>
@@ -46479,7 +46479,7 @@
         <v>4.8439998626709</v>
       </c>
       <c r="G1590" t="n">
-        <v>4.26709604263306</v>
+        <v>4.2670955657959</v>
       </c>
       <c r="H1590" t="n">
         <v>892961</v>
@@ -46537,7 +46537,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.39042234420776</v>
+        <v>4.39042282104492</v>
       </c>
       <c r="H1592" t="n">
         <v>2796389</v>
@@ -46624,7 +46624,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1595" t="n">
-        <v>4.69169187545776</v>
+        <v>4.69169139862061</v>
       </c>
       <c r="H1595" t="n">
         <v>3747916</v>
@@ -46769,7 +46769,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1600" t="n">
-        <v>4.47498941421509</v>
+        <v>4.47498893737793</v>
       </c>
       <c r="H1600" t="n">
         <v>1413854</v>
@@ -46827,7 +46827,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1602" t="n">
-        <v>4.47498941421509</v>
+        <v>4.47498893737793</v>
       </c>
       <c r="H1602" t="n">
         <v>1825018</v>
@@ -47001,7 +47001,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G1608" t="n">
-        <v>4.52255725860596</v>
+        <v>4.52255773544312</v>
       </c>
       <c r="H1608" t="n">
         <v>4438145</v>
@@ -47262,7 +47262,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.74278354644775</v>
+        <v>4.74278402328491</v>
       </c>
       <c r="H1617" t="n">
         <v>1946543</v>
@@ -47349,7 +47349,7 @@
         <v>5.46799993515015</v>
       </c>
       <c r="G1620" t="n">
-        <v>4.81678009033203</v>
+        <v>4.81677961349487</v>
       </c>
       <c r="H1620" t="n">
         <v>1494974</v>
@@ -47378,7 +47378,7 @@
         <v>5.41800022125244</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.77273464202881</v>
+        <v>4.77273511886597</v>
       </c>
       <c r="H1621" t="n">
         <v>2110714</v>
@@ -47494,7 +47494,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1625" t="n">
-        <v>4.77449655532837</v>
+        <v>4.77449607849121</v>
       </c>
       <c r="H1625" t="n">
         <v>1615810</v>
@@ -47610,7 +47610,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.80620861053467</v>
+        <v>4.80620908737183</v>
       </c>
       <c r="H1629" t="n">
         <v>1140067</v>
@@ -47668,7 +47668,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1631" t="n">
-        <v>4.95948600769043</v>
+        <v>4.95948648452759</v>
       </c>
       <c r="H1631" t="n">
         <v>3400037</v>
@@ -47813,7 +47813,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G1636" t="n">
-        <v>4.72868967056274</v>
+        <v>4.72868919372559</v>
       </c>
       <c r="H1636" t="n">
         <v>2107962</v>
@@ -47987,7 +47987,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1642" t="n">
-        <v>4.87139654159546</v>
+        <v>4.8713960647583</v>
       </c>
       <c r="H1642" t="n">
         <v>1968871</v>
@@ -48016,7 +48016,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1643" t="n">
-        <v>4.91720247268677</v>
+        <v>4.91720199584961</v>
       </c>
       <c r="H1643" t="n">
         <v>1157047</v>
@@ -48074,7 +48074,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1645" t="n">
-        <v>4.9330587387085</v>
+        <v>4.93305921554565</v>
       </c>
       <c r="H1645" t="n">
         <v>1639165</v>
@@ -48161,7 +48161,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1648" t="n">
-        <v>4.9735803604126</v>
+        <v>4.97358083724976</v>
       </c>
       <c r="H1648" t="n">
         <v>1355402</v>
@@ -48248,7 +48248,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1651" t="n">
-        <v>4.9735803604126</v>
+        <v>4.97358083724976</v>
       </c>
       <c r="H1651" t="n">
         <v>1114962</v>
@@ -48277,7 +48277,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1652" t="n">
-        <v>5.07576513290405</v>
+        <v>5.07576560974121</v>
       </c>
       <c r="H1652" t="n">
         <v>1696803</v>
@@ -48335,7 +48335,7 @@
         <v>5.77600002288818</v>
       </c>
       <c r="G1654" t="n">
-        <v>5.08809852600098</v>
+        <v>5.08809804916382</v>
       </c>
       <c r="H1654" t="n">
         <v>1247410</v>
@@ -48596,7 +48596,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1663" t="n">
-        <v>5.17090320587158</v>
+        <v>5.17090272903442</v>
       </c>
       <c r="H1663" t="n">
         <v>1114408</v>
@@ -48625,7 +48625,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1664" t="n">
-        <v>5.12333393096924</v>
+        <v>5.12333345413208</v>
       </c>
       <c r="H1664" t="n">
         <v>1446906</v>
@@ -48886,7 +48886,7 @@
         <v>6.00400018692017</v>
       </c>
       <c r="G1673" t="n">
-        <v>5.28894376754761</v>
+        <v>5.28894424438477</v>
       </c>
       <c r="H1673" t="n">
         <v>1425999</v>
@@ -48944,7 +48944,7 @@
         <v>6.17799997329712</v>
       </c>
       <c r="G1675" t="n">
-        <v>5.44222164154053</v>
+        <v>5.44222116470337</v>
       </c>
       <c r="H1675" t="n">
         <v>1287114</v>
@@ -48973,7 +48973,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G1676" t="n">
-        <v>5.29951477050781</v>
+        <v>5.29951429367065</v>
       </c>
       <c r="H1676" t="n">
         <v>2412084</v>
@@ -49002,7 +49002,7 @@
         <v>6.06799983978271</v>
       </c>
       <c r="G1677" t="n">
-        <v>5.34532165527344</v>
+        <v>5.34532117843628</v>
       </c>
       <c r="H1677" t="n">
         <v>966171</v>
@@ -49031,7 +49031,7 @@
         <v>6.23400020599365</v>
       </c>
       <c r="G1678" t="n">
-        <v>5.49155235290527</v>
+        <v>5.49155187606812</v>
       </c>
       <c r="H1678" t="n">
         <v>4102798</v>
@@ -49321,7 +49321,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1688" t="n">
-        <v>5.43517351150513</v>
+        <v>5.43517398834229</v>
       </c>
       <c r="H1688" t="n">
         <v>2465072</v>
@@ -49524,7 +49524,7 @@
         <v>5.97599983215332</v>
       </c>
       <c r="G1695" t="n">
-        <v>5.26427841186523</v>
+        <v>5.26427888870239</v>
       </c>
       <c r="H1695" t="n">
         <v>3842448</v>
@@ -49640,7 +49640,7 @@
         <v>6.04400014877319</v>
       </c>
       <c r="G1699" t="n">
-        <v>5.32418060302734</v>
+        <v>5.32418012619019</v>
       </c>
       <c r="H1699" t="n">
         <v>1299410</v>
@@ -49669,7 +49669,7 @@
         <v>6.00799989700317</v>
       </c>
       <c r="G1700" t="n">
-        <v>5.29246711730957</v>
+        <v>5.29246759414673</v>
       </c>
       <c r="H1700" t="n">
         <v>2014704</v>
@@ -49698,7 +49698,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G1701" t="n">
-        <v>5.29951477050781</v>
+        <v>5.29951429367065</v>
       </c>
       <c r="H1701" t="n">
         <v>2215181</v>
@@ -49843,7 +49843,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1706" t="n">
-        <v>5.135666847229</v>
+        <v>5.13566637039185</v>
       </c>
       <c r="H1706" t="n">
         <v>1336134</v>
@@ -50046,7 +50046,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1713" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1713" t="n">
         <v>1930745</v>
@@ -50075,7 +50075,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1714" t="n">
-        <v>5.12169647216797</v>
+        <v>5.12169694900513</v>
       </c>
       <c r="H1714" t="n">
         <v>1367400</v>
@@ -50104,7 +50104,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1715" t="n">
-        <v>5.02137899398804</v>
+        <v>5.02137851715088</v>
       </c>
       <c r="H1715" t="n">
         <v>2554508</v>
@@ -50191,7 +50191,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G1718" t="n">
-        <v>5.16547155380249</v>
+        <v>5.16547203063965</v>
       </c>
       <c r="H1718" t="n">
         <v>1115062</v>
@@ -50249,7 +50249,7 @@
         <v>5.57399988174438</v>
       </c>
       <c r="G1720" t="n">
-        <v>5.08339309692383</v>
+        <v>5.08339357376099</v>
       </c>
       <c r="H1720" t="n">
         <v>1066536</v>
@@ -50278,7 +50278,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1721" t="n">
-        <v>5.14905595779419</v>
+        <v>5.14905643463135</v>
       </c>
       <c r="H1721" t="n">
         <v>1309301</v>
@@ -50336,7 +50336,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1723" t="n">
-        <v>5.22931051254272</v>
+        <v>5.22931098937988</v>
       </c>
       <c r="H1723" t="n">
         <v>1073822</v>
@@ -50394,7 +50394,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1725" t="n">
-        <v>5.25484609603882</v>
+        <v>5.25484657287598</v>
       </c>
       <c r="H1725" t="n">
         <v>1815362</v>
@@ -50597,7 +50597,7 @@
         <v>5.75</v>
       </c>
       <c r="G1732" t="n">
-        <v>5.2439022064209</v>
+        <v>5.24390268325806</v>
       </c>
       <c r="H1732" t="n">
         <v>2383059</v>
@@ -50626,7 +50626,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1733" t="n">
-        <v>5.30774116516113</v>
+        <v>5.30774164199829</v>
       </c>
       <c r="H1733" t="n">
         <v>1419417</v>
@@ -50655,7 +50655,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1734" t="n">
-        <v>5.26578998565674</v>
+        <v>5.2657904624939</v>
       </c>
       <c r="H1734" t="n">
         <v>1263754</v>
@@ -50742,7 +50742,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1737" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1737" t="n">
         <v>2008071</v>
@@ -50771,7 +50771,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1738" t="n">
-        <v>4.97760343551636</v>
+        <v>4.97760391235352</v>
       </c>
       <c r="H1738" t="n">
         <v>2945125</v>
@@ -50829,7 +50829,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G1740" t="n">
-        <v>4.74960803985596</v>
+        <v>4.7496075630188</v>
       </c>
       <c r="H1740" t="n">
         <v>1995582</v>
@@ -50945,7 +50945,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G1744" t="n">
-        <v>4.78426313400269</v>
+        <v>4.78426265716553</v>
       </c>
       <c r="H1744" t="n">
         <v>872180</v>
@@ -51061,7 +51061,7 @@
         <v>5.38199996948242</v>
       </c>
       <c r="G1748" t="n">
-        <v>4.90829277038574</v>
+        <v>4.90829229354858</v>
       </c>
       <c r="H1748" t="n">
         <v>707574</v>
@@ -51119,7 +51119,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1750" t="n">
-        <v>4.94294834136963</v>
+        <v>4.94294786453247</v>
       </c>
       <c r="H1750" t="n">
         <v>1233465</v>
@@ -51206,7 +51206,7 @@
         <v>5.43200016021729</v>
       </c>
       <c r="G1753" t="n">
-        <v>4.95389175415039</v>
+        <v>4.95389223098755</v>
       </c>
       <c r="H1753" t="n">
         <v>598372</v>
@@ -51351,7 +51351,7 @@
         <v>5.52799987792969</v>
       </c>
       <c r="G1758" t="n">
-        <v>5.04144191741943</v>
+        <v>5.04144239425659</v>
       </c>
       <c r="H1758" t="n">
         <v>749729</v>
@@ -51409,7 +51409,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1760" t="n">
-        <v>4.99584341049194</v>
+        <v>4.99584293365479</v>
       </c>
       <c r="H1760" t="n">
         <v>1110795</v>
@@ -51612,7 +51612,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1767" t="n">
-        <v>4.96118783950806</v>
+        <v>4.9611873626709</v>
       </c>
       <c r="H1767" t="n">
         <v>871216</v>
@@ -51670,7 +51670,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G1769" t="n">
-        <v>4.92106056213379</v>
+        <v>4.92106008529663</v>
       </c>
       <c r="H1769" t="n">
         <v>1142507</v>
@@ -51902,7 +51902,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1777" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1777" t="n">
         <v>1639161</v>
@@ -51989,7 +51989,7 @@
         <v>5.21199989318848</v>
       </c>
       <c r="G1780" t="n">
-        <v>4.75325536727905</v>
+        <v>4.75325584411621</v>
       </c>
       <c r="H1780" t="n">
         <v>7817931</v>
@@ -52134,7 +52134,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G1785" t="n">
-        <v>4.8955249786377</v>
+        <v>4.89552450180054</v>
       </c>
       <c r="H1785" t="n">
         <v>1946243</v>
@@ -52308,7 +52308,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G1791" t="n">
-        <v>4.87546110153198</v>
+        <v>4.87546157836914</v>
       </c>
       <c r="H1791" t="n">
         <v>1464698</v>
@@ -52424,7 +52424,7 @@
         <v>5.24399995803833</v>
       </c>
       <c r="G1795" t="n">
-        <v>4.7824387550354</v>
+        <v>4.78243923187256</v>
       </c>
       <c r="H1795" t="n">
         <v>1922209</v>
@@ -52482,7 +52482,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1797" t="n">
-        <v>4.71677589416504</v>
+        <v>4.7167763710022</v>
       </c>
       <c r="H1797" t="n">
         <v>1952792</v>
@@ -52511,7 +52511,7 @@
         <v>5.15799999237061</v>
       </c>
       <c r="G1798" t="n">
-        <v>4.70400810241699</v>
+        <v>4.70400857925415</v>
       </c>
       <c r="H1798" t="n">
         <v>2608346</v>
@@ -52540,7 +52540,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1799" t="n">
-        <v>4.62010622024536</v>
+        <v>4.6201057434082</v>
       </c>
       <c r="H1799" t="n">
         <v>2142638</v>
@@ -52627,7 +52627,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1802" t="n">
-        <v>4.62010622024536</v>
+        <v>4.6201057434082</v>
       </c>
       <c r="H1802" t="n">
         <v>1304150</v>
@@ -52772,7 +52772,7 @@
         <v>5.10400009155273</v>
       </c>
       <c r="G1807" t="n">
-        <v>4.65476179122925</v>
+        <v>4.65476131439209</v>
       </c>
       <c r="H1807" t="n">
         <v>7182672</v>
@@ -52801,7 +52801,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1808" t="n">
-        <v>4.71677589416504</v>
+        <v>4.7167763710022</v>
       </c>
       <c r="H1808" t="n">
         <v>3272568</v>
@@ -52859,7 +52859,7 @@
         <v>4.96700000762939</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.52981996536255</v>
+        <v>4.52981948852539</v>
       </c>
       <c r="H1810" t="n">
         <v>3621056</v>
@@ -52888,7 +52888,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G1811" t="n">
-        <v>4.63469743728638</v>
+        <v>4.63469791412354</v>
       </c>
       <c r="H1811" t="n">
         <v>2020220</v>
@@ -53004,7 +53004,7 @@
         <v>5.16599988937378</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.71130466461182</v>
+        <v>4.71130418777466</v>
       </c>
       <c r="H1815" t="n">
         <v>3075470</v>
@@ -53062,7 +53062,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.71677589416504</v>
+        <v>4.7167763710022</v>
       </c>
       <c r="H1817" t="n">
         <v>1675292</v>
@@ -53207,7 +53207,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G1822" t="n">
-        <v>4.68212032318115</v>
+        <v>4.68212080001831</v>
       </c>
       <c r="H1822" t="n">
         <v>1423087</v>
@@ -53294,7 +53294,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G1825" t="n">
-        <v>4.78426313400269</v>
+        <v>4.78426265716553</v>
       </c>
       <c r="H1825" t="n">
         <v>2341827</v>
@@ -53352,7 +53352,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.87546110153198</v>
+        <v>4.87546157836914</v>
       </c>
       <c r="H1827" t="n">
         <v>1570389</v>
@@ -53381,7 +53381,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G1828" t="n">
-        <v>4.92106056213379</v>
+        <v>4.92106008529663</v>
       </c>
       <c r="H1828" t="n">
         <v>1505172</v>
@@ -53555,7 +53555,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1834" t="n">
-        <v>5.02137899398804</v>
+        <v>5.02137851715088</v>
       </c>
       <c r="H1834" t="n">
         <v>2061632</v>
@@ -53584,7 +53584,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1835" t="n">
-        <v>5.04326677322388</v>
+        <v>5.04326629638672</v>
       </c>
       <c r="H1835" t="n">
         <v>1605046</v>
@@ -53671,7 +53671,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.97760343551636</v>
+        <v>4.97760391235352</v>
       </c>
       <c r="H1838" t="n">
         <v>1222379</v>
@@ -53729,7 +53729,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.99219465255737</v>
+        <v>4.99219512939453</v>
       </c>
       <c r="H1840" t="n">
         <v>1067550</v>
@@ -53903,7 +53903,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1846" t="n">
-        <v>5.09068918228149</v>
+        <v>5.09068870544434</v>
       </c>
       <c r="H1846" t="n">
         <v>2122240</v>
@@ -53932,7 +53932,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1847" t="n">
-        <v>5.09616088867188</v>
+        <v>5.09616136550903</v>
       </c>
       <c r="H1847" t="n">
         <v>1601324</v>
@@ -53961,7 +53961,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1848" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1848" t="n">
         <v>1113736</v>
@@ -53990,7 +53990,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1849" t="n">
-        <v>5.18006372451782</v>
+        <v>5.18006324768066</v>
       </c>
       <c r="H1849" t="n">
         <v>4393306</v>
@@ -54048,7 +54048,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1851" t="n">
-        <v>5.22931051254272</v>
+        <v>5.22931098937988</v>
       </c>
       <c r="H1851" t="n">
         <v>2082674</v>
@@ -54135,7 +54135,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1854" t="n">
-        <v>5.23843050003052</v>
+        <v>5.23843002319336</v>
       </c>
       <c r="H1854" t="n">
         <v>1638683</v>
@@ -54193,7 +54193,7 @@
         <v>5.82800006866455</v>
       </c>
       <c r="G1856" t="n">
-        <v>5.3150372505188</v>
+        <v>5.31503677368164</v>
       </c>
       <c r="H1856" t="n">
         <v>2461456</v>
@@ -54222,7 +54222,7 @@
         <v>5.85200023651123</v>
       </c>
       <c r="G1857" t="n">
-        <v>5.33692455291748</v>
+        <v>5.33692502975464</v>
       </c>
       <c r="H1857" t="n">
         <v>1917532</v>
@@ -54309,7 +54309,7 @@
         <v>5.78200006484985</v>
       </c>
       <c r="G1860" t="n">
-        <v>5.27308559417725</v>
+        <v>5.2730860710144</v>
       </c>
       <c r="H1860" t="n">
         <v>1153715</v>
@@ -54396,7 +54396,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1863" t="n">
-        <v>5.13264036178589</v>
+        <v>5.13263988494873</v>
       </c>
       <c r="H1863" t="n">
         <v>6863661</v>
@@ -54425,7 +54425,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1864" t="n">
-        <v>5.10710477828979</v>
+        <v>5.10710525512695</v>
       </c>
       <c r="H1864" t="n">
         <v>1749750</v>
@@ -54454,7 +54454,7 @@
         <v>5.53800010681152</v>
       </c>
       <c r="G1865" t="n">
-        <v>5.05056238174438</v>
+        <v>5.05056190490723</v>
       </c>
       <c r="H1865" t="n">
         <v>1856112</v>
@@ -54483,7 +54483,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1866" t="n">
-        <v>5.10710477828979</v>
+        <v>5.10710525512695</v>
       </c>
       <c r="H1866" t="n">
         <v>1134560</v>
@@ -54541,7 +54541,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1868" t="n">
-        <v>5.10710477828979</v>
+        <v>5.10710525512695</v>
       </c>
       <c r="H1868" t="n">
         <v>1623973</v>
@@ -54570,7 +54570,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1869" t="n">
-        <v>5.14358377456665</v>
+        <v>5.14358425140381</v>
       </c>
       <c r="H1869" t="n">
         <v>1888128</v>
@@ -54628,7 +54628,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G1871" t="n">
-        <v>5.24572658538818</v>
+        <v>5.24572610855103</v>
       </c>
       <c r="H1871" t="n">
         <v>2824097</v>
@@ -54773,7 +54773,7 @@
         <v>5.72800016403198</v>
       </c>
       <c r="G1876" t="n">
-        <v>5.2238392829895</v>
+        <v>5.22383880615234</v>
       </c>
       <c r="H1876" t="n">
         <v>1322234</v>
@@ -54889,7 +54889,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1880" t="n">
-        <v>5.30774116516113</v>
+        <v>5.30774164199829</v>
       </c>
       <c r="H1880" t="n">
         <v>1628098</v>
@@ -54947,7 +54947,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G1882" t="n">
-        <v>5.50290536880493</v>
+        <v>5.50290584564209</v>
       </c>
       <c r="H1882" t="n">
         <v>3694253</v>
@@ -55005,7 +55005,7 @@
         <v>5.75</v>
       </c>
       <c r="G1884" t="n">
-        <v>5.2439022064209</v>
+        <v>5.24390268325806</v>
       </c>
       <c r="H1884" t="n">
         <v>4531783</v>
@@ -55063,7 +55063,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1886" t="n">
-        <v>5.30774116516113</v>
+        <v>5.30774164199829</v>
       </c>
       <c r="H1886" t="n">
         <v>3842206</v>
@@ -55092,7 +55092,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1887" t="n">
-        <v>5.14905595779419</v>
+        <v>5.14905643463135</v>
       </c>
       <c r="H1887" t="n">
         <v>4539598</v>
@@ -55121,7 +55121,7 @@
         <v>5.66599988937378</v>
       </c>
       <c r="G1888" t="n">
-        <v>5.16729593276978</v>
+        <v>5.16729545593262</v>
       </c>
       <c r="H1888" t="n">
         <v>3363922</v>
@@ -55150,7 +55150,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1889" t="n">
-        <v>5.12169647216797</v>
+        <v>5.12169694900513</v>
       </c>
       <c r="H1889" t="n">
         <v>3102908</v>
@@ -55208,7 +55208,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1891" t="n">
-        <v>5.25484609603882</v>
+        <v>5.25484657287598</v>
       </c>
       <c r="H1891" t="n">
         <v>2244420</v>
@@ -55237,7 +55237,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G1892" t="n">
-        <v>5.40258693695068</v>
+        <v>5.40258741378784</v>
       </c>
       <c r="H1892" t="n">
         <v>2940061</v>
@@ -55295,7 +55295,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1894" t="n">
-        <v>5.40441179275513</v>
+        <v>5.40441131591797</v>
       </c>
       <c r="H1894" t="n">
         <v>1732424</v>
@@ -55324,7 +55324,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1895" t="n">
-        <v>5.40441179275513</v>
+        <v>5.40441131591797</v>
       </c>
       <c r="H1895" t="n">
         <v>1130769</v>
@@ -55382,7 +55382,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1897" t="n">
-        <v>5.36246061325073</v>
+        <v>5.36246013641357</v>
       </c>
       <c r="H1897" t="n">
         <v>3402608</v>
@@ -55440,7 +55440,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G1899" t="n">
-        <v>5.24572658538818</v>
+        <v>5.24572610855103</v>
       </c>
       <c r="H1899" t="n">
         <v>5097268</v>
@@ -55469,7 +55469,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1900" t="n">
-        <v>5.09616088867188</v>
+        <v>5.09616136550903</v>
       </c>
       <c r="H1900" t="n">
         <v>4791696</v>
@@ -55556,7 +55556,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.99219465255737</v>
+        <v>4.99219512939453</v>
       </c>
       <c r="H1903" t="n">
         <v>2656525</v>
@@ -55614,7 +55614,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G1905" t="n">
-        <v>4.97577905654907</v>
+        <v>4.97577953338623</v>
       </c>
       <c r="H1905" t="n">
         <v>1974649</v>
@@ -55643,7 +55643,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.84262990951538</v>
+        <v>4.84262943267822</v>
       </c>
       <c r="H1906" t="n">
         <v>2382236</v>
@@ -55788,7 +55788,7 @@
         <v>4.80299997329712</v>
       </c>
       <c r="G1911" t="n">
-        <v>4.38025426864624</v>
+        <v>4.3802547454834</v>
       </c>
       <c r="H1911" t="n">
         <v>3237721</v>
@@ -55846,7 +55846,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G1913" t="n">
-        <v>4.50793218612671</v>
+        <v>4.50793170928955</v>
       </c>
       <c r="H1913" t="n">
         <v>1902362</v>
@@ -55904,7 +55904,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.56903505325317</v>
+        <v>4.56903553009033</v>
       </c>
       <c r="H1915" t="n">
         <v>1697802</v>
@@ -55933,7 +55933,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G1916" t="n">
-        <v>4.58909893035889</v>
+        <v>4.58909845352173</v>
       </c>
       <c r="H1916" t="n">
         <v>1293197</v>
@@ -56078,7 +56078,7 @@
         <v>5.36399984359741</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.89187717437744</v>
+        <v>4.89187669754028</v>
       </c>
       <c r="H1921" t="n">
         <v>2120977</v>
@@ -56223,7 +56223,7 @@
         <v>5.53599977493286</v>
       </c>
       <c r="G1926" t="n">
-        <v>5.04873752593994</v>
+        <v>5.0487380027771</v>
       </c>
       <c r="H1926" t="n">
         <v>1676053</v>
@@ -56339,7 +56339,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G1930" t="n">
-        <v>5.40258693695068</v>
+        <v>5.40258741378784</v>
       </c>
       <c r="H1930" t="n">
         <v>2688995</v>
@@ -56455,7 +56455,7 @@
         <v>5.91800022125244</v>
       </c>
       <c r="G1934" t="n">
-        <v>5.39711570739746</v>
+        <v>5.39711618423462</v>
       </c>
       <c r="H1934" t="n">
         <v>2801870</v>
@@ -56484,7 +56484,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1935" t="n">
-        <v>5.45365810394287</v>
+        <v>5.45365858078003</v>
       </c>
       <c r="H1935" t="n">
         <v>1677316</v>
@@ -56513,7 +56513,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G1936" t="n">
-        <v>5.57403993606567</v>
+        <v>5.57404041290283</v>
       </c>
       <c r="H1936" t="n">
         <v>3612638</v>
@@ -56542,7 +56542,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1937" t="n">
-        <v>5.62693500518799</v>
+        <v>5.62693548202515</v>
       </c>
       <c r="H1937" t="n">
         <v>3227462</v>
@@ -56600,7 +56600,7 @@
         <v>6.13800001144409</v>
       </c>
       <c r="G1939" t="n">
-        <v>5.59775161743164</v>
+        <v>5.5977520942688</v>
       </c>
       <c r="H1939" t="n">
         <v>6063161</v>
@@ -56716,7 +56716,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1943" t="n">
-        <v>5.73637342453003</v>
+        <v>5.73637294769287</v>
       </c>
       <c r="H1943" t="n">
         <v>3058422</v>
@@ -56803,7 +56803,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1946" t="n">
-        <v>5.69077348709106</v>
+        <v>5.69077396392822</v>
       </c>
       <c r="H1946" t="n">
         <v>1535277</v>
@@ -56977,7 +56977,7 @@
         <v>6.18599987030029</v>
       </c>
       <c r="G1952" t="n">
-        <v>5.64152717590332</v>
+        <v>5.64152669906616</v>
       </c>
       <c r="H1952" t="n">
         <v>2276866</v>
@@ -57180,7 +57180,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1959" t="n">
-        <v>5.53208875656128</v>
+        <v>5.53208923339844</v>
       </c>
       <c r="H1959" t="n">
         <v>2753548</v>
@@ -66930,6 +66930,64 @@
         <v>1821645</v>
       </c>
       <c r="I2295" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2296" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2296" t="n">
+        <v>6.67000007629395</v>
+      </c>
+      <c r="D2296" t="n">
+        <v>6.67000007629395</v>
+      </c>
+      <c r="E2296" t="n">
+        <v>6.48999977111816</v>
+      </c>
+      <c r="F2296" t="n">
+        <v>6.63500022888184</v>
+      </c>
+      <c r="G2296" t="n">
+        <v>6.63500022888184</v>
+      </c>
+      <c r="H2296" t="n">
+        <v>1359725</v>
+      </c>
+      <c r="I2296" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2297" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2297" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="D2297" t="n">
+        <v>6.6399998664856</v>
+      </c>
+      <c r="E2297" t="n">
+        <v>6.53999996185303</v>
+      </c>
+      <c r="F2297" t="n">
+        <v>6.59000015258789</v>
+      </c>
+      <c r="G2297" t="n">
+        <v>6.59000015258789</v>
+      </c>
+      <c r="H2297" t="n">
+        <v>1098527</v>
+      </c>
+      <c r="I2297" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -456,7 +456,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>5.19319725036621</v>
+        <v>5.19319772720337</v>
       </c>
       <c r="H3" t="n">
         <v>24993644</v>
@@ -485,7 +485,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>5.18545770645142</v>
+        <v>5.18545818328857</v>
       </c>
       <c r="H4" t="n">
         <v>10381356</v>
@@ -514,7 +514,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G5" t="n">
-        <v>5.0771050453186</v>
+        <v>5.07710456848145</v>
       </c>
       <c r="H5" t="n">
         <v>5160664</v>
@@ -572,7 +572,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G7" t="n">
-        <v>5.11193227767944</v>
+        <v>5.1119327545166</v>
       </c>
       <c r="H7" t="n">
         <v>1858638</v>
@@ -601,7 +601,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G8" t="n">
-        <v>5.03453779220581</v>
+        <v>5.03453731536865</v>
       </c>
       <c r="H8" t="n">
         <v>1660176</v>
@@ -630,7 +630,7 @@
         <v>6.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.03066778182983</v>
+        <v>5.03066825866699</v>
       </c>
       <c r="H9" t="n">
         <v>1559429</v>
@@ -659,7 +659,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>5.02679777145386</v>
+        <v>5.02679872512817</v>
       </c>
       <c r="H10" t="n">
         <v>4863908</v>
@@ -688,7 +688,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>4.99971008300781</v>
+        <v>4.99971055984497</v>
       </c>
       <c r="H11" t="n">
         <v>2476184</v>
@@ -775,7 +775,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>5.02679777145386</v>
+        <v>5.02679872512817</v>
       </c>
       <c r="H14" t="n">
         <v>2519007</v>
@@ -804,7 +804,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G15" t="n">
-        <v>5.04227685928345</v>
+        <v>5.04227781295776</v>
       </c>
       <c r="H15" t="n">
         <v>2086712</v>
@@ -833,7 +833,7 @@
         <v>6.5</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03066778182983</v>
+        <v>5.03066825866699</v>
       </c>
       <c r="H16" t="n">
         <v>1266116</v>
@@ -862,7 +862,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G17" t="n">
-        <v>5.02292776107788</v>
+        <v>5.02292823791504</v>
       </c>
       <c r="H17" t="n">
         <v>941108</v>
@@ -891,7 +891,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G18" t="n">
-        <v>5.04227685928345</v>
+        <v>5.04227781295776</v>
       </c>
       <c r="H18" t="n">
         <v>1554901</v>
@@ -920,7 +920,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G19" t="n">
-        <v>5.10806274414062</v>
+        <v>5.10806226730347</v>
       </c>
       <c r="H19" t="n">
         <v>2506280</v>
@@ -978,7 +978,7 @@
         <v>6.75</v>
       </c>
       <c r="G21" t="n">
-        <v>5.22415542602539</v>
+        <v>5.22415494918823</v>
       </c>
       <c r="H21" t="n">
         <v>3151263</v>
@@ -1007,7 +1007,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G22" t="n">
-        <v>5.40990257263184</v>
+        <v>5.40990304946899</v>
       </c>
       <c r="H22" t="n">
         <v>3306513</v>
@@ -1065,7 +1065,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G24" t="n">
-        <v>5.33250856399536</v>
+        <v>5.3325080871582</v>
       </c>
       <c r="H24" t="n">
         <v>2075041</v>
@@ -1123,7 +1123,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G26" t="n">
-        <v>5.45633983612061</v>
+        <v>5.45634031295776</v>
       </c>
       <c r="H26" t="n">
         <v>3523859</v>
@@ -1268,7 +1268,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G31" t="n">
-        <v>5.30542039871216</v>
+        <v>5.305419921875</v>
       </c>
       <c r="H31" t="n">
         <v>842590</v>
@@ -1297,7 +1297,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G32" t="n">
-        <v>5.26285266876221</v>
+        <v>5.26285362243652</v>
       </c>
       <c r="H32" t="n">
         <v>771098</v>
@@ -1326,7 +1326,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>5.26285266876221</v>
+        <v>5.26285362243652</v>
       </c>
       <c r="H33" t="n">
         <v>532136</v>
@@ -1384,7 +1384,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>5.28994131088257</v>
+        <v>5.28994083404541</v>
       </c>
       <c r="H35" t="n">
         <v>599729</v>
@@ -1471,7 +1471,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G38" t="n">
-        <v>5.45246934890747</v>
+        <v>5.45246982574463</v>
       </c>
       <c r="H38" t="n">
         <v>874776</v>
@@ -1558,7 +1558,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>5.47955846786499</v>
+        <v>5.47955799102783</v>
       </c>
       <c r="H41" t="n">
         <v>1316822</v>
@@ -1587,7 +1587,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G42" t="n">
-        <v>5.4640793800354</v>
+        <v>5.46407890319824</v>
       </c>
       <c r="H42" t="n">
         <v>3264384</v>
@@ -1616,7 +1616,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>5.42151260375977</v>
+        <v>5.42151212692261</v>
       </c>
       <c r="H43" t="n">
         <v>2601318</v>
@@ -1645,7 +1645,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>5.34024810791016</v>
+        <v>5.340247631073</v>
       </c>
       <c r="H44" t="n">
         <v>1806362</v>
@@ -1674,7 +1674,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>5.42925119400024</v>
+        <v>5.42925262451172</v>
       </c>
       <c r="H45" t="n">
         <v>1351272</v>
@@ -1703,7 +1703,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G46" t="n">
-        <v>5.3944239616394</v>
+        <v>5.39442348480225</v>
       </c>
       <c r="H46" t="n">
         <v>1348979</v>
@@ -1790,7 +1790,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G49" t="n">
-        <v>5.56469249725342</v>
+        <v>5.56469297409058</v>
       </c>
       <c r="H49" t="n">
         <v>1856608</v>
@@ -1819,7 +1819,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G50" t="n">
-        <v>5.61886978149414</v>
+        <v>5.61886930465698</v>
       </c>
       <c r="H50" t="n">
         <v>1356581</v>
@@ -1906,7 +1906,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G53" t="n">
-        <v>5.59178018569946</v>
+        <v>5.59178113937378</v>
       </c>
       <c r="H53" t="n">
         <v>2419795</v>
@@ -1935,7 +1935,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>5.5337347984314</v>
+        <v>5.53373527526855</v>
       </c>
       <c r="H54" t="n">
         <v>14422327</v>
@@ -1964,7 +1964,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>5.48342800140381</v>
+        <v>5.48342847824097</v>
       </c>
       <c r="H55" t="n">
         <v>2428996</v>
@@ -2022,7 +2022,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>5.47955846786499</v>
+        <v>5.47955799102783</v>
       </c>
       <c r="H57" t="n">
         <v>1498021</v>
@@ -2051,7 +2051,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G58" t="n">
-        <v>5.52986526489258</v>
+        <v>5.52986478805542</v>
       </c>
       <c r="H58" t="n">
         <v>1284540</v>
@@ -2080,7 +2080,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>5.5337347984314</v>
+        <v>5.53373527526855</v>
       </c>
       <c r="H59" t="n">
         <v>976129</v>
@@ -2109,7 +2109,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>5.54921388626099</v>
+        <v>5.54921340942383</v>
       </c>
       <c r="H60" t="n">
         <v>575911</v>
@@ -2138,7 +2138,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>5.5956506729126</v>
+        <v>5.59565019607544</v>
       </c>
       <c r="H61" t="n">
         <v>1027455</v>
@@ -2196,7 +2196,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G63" t="n">
-        <v>5.68078517913818</v>
+        <v>5.68078565597534</v>
       </c>
       <c r="H63" t="n">
         <v>1436706</v>
@@ -2254,7 +2254,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G65" t="n">
-        <v>5.84718370437622</v>
+        <v>5.84718418121338</v>
       </c>
       <c r="H65" t="n">
         <v>2115620</v>
@@ -2341,7 +2341,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>6.14902448654175</v>
+        <v>6.14902400970459</v>
       </c>
       <c r="H68" t="n">
         <v>2619744</v>
@@ -2399,7 +2399,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G70" t="n">
-        <v>6.09871816635132</v>
+        <v>6.09871768951416</v>
       </c>
       <c r="H70" t="n">
         <v>2140774</v>
@@ -2428,7 +2428,7 @@
         <v>7.86499977111816</v>
       </c>
       <c r="G71" t="n">
-        <v>6.08710861206055</v>
+        <v>6.08710813522339</v>
       </c>
       <c r="H71" t="n">
         <v>1712288</v>
@@ -2515,7 +2515,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G74" t="n">
-        <v>6.05228042602539</v>
+        <v>6.05228090286255</v>
       </c>
       <c r="H74" t="n">
         <v>2266592</v>
@@ -2602,7 +2602,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G77" t="n">
-        <v>6.05228042602539</v>
+        <v>6.05228090286255</v>
       </c>
       <c r="H77" t="n">
         <v>1103493</v>
@@ -2631,7 +2631,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>5.98262548446655</v>
+        <v>5.98262500762939</v>
       </c>
       <c r="H78" t="n">
         <v>2070393</v>
@@ -2660,7 +2660,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G79" t="n">
-        <v>5.97101640701294</v>
+        <v>5.97101593017578</v>
       </c>
       <c r="H79" t="n">
         <v>1358430</v>
@@ -2718,7 +2718,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G81" t="n">
-        <v>6.05228042602539</v>
+        <v>6.05228090286255</v>
       </c>
       <c r="H81" t="n">
         <v>1375872</v>
@@ -2747,7 +2747,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G82" t="n">
-        <v>6.06930732727051</v>
+        <v>6.06930780410767</v>
       </c>
       <c r="H82" t="n">
         <v>2088672</v>
@@ -2834,7 +2834,7 @@
         <v>7.76399993896484</v>
       </c>
       <c r="G85" t="n">
-        <v>6.00893974304199</v>
+        <v>6.00893926620483</v>
       </c>
       <c r="H85" t="n">
         <v>1196110</v>
@@ -2863,7 +2863,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G86" t="n">
-        <v>5.88201236724854</v>
+        <v>5.88201141357422</v>
       </c>
       <c r="H86" t="n">
         <v>2172088</v>
@@ -2921,7 +2921,7 @@
         <v>7.28599977493286</v>
       </c>
       <c r="G88" t="n">
-        <v>5.638991355896</v>
+        <v>5.63899183273315</v>
       </c>
       <c r="H88" t="n">
         <v>3950924</v>
@@ -2950,7 +2950,7 @@
         <v>7.55800008773804</v>
       </c>
       <c r="G89" t="n">
-        <v>5.84950637817383</v>
+        <v>5.84950542449951</v>
       </c>
       <c r="H89" t="n">
         <v>2755965</v>
@@ -3037,7 +3037,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G92" t="n">
-        <v>5.69007301330566</v>
+        <v>5.69007349014282</v>
       </c>
       <c r="H92" t="n">
         <v>1784953</v>
@@ -3124,7 +3124,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G95" t="n">
-        <v>5.78139877319336</v>
+        <v>5.7813982963562</v>
       </c>
       <c r="H95" t="n">
         <v>1798735</v>
@@ -3240,7 +3240,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G99" t="n">
-        <v>5.73186540603638</v>
+        <v>5.73186588287354</v>
       </c>
       <c r="H99" t="n">
         <v>1618284</v>
@@ -3298,7 +3298,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G101" t="n">
-        <v>5.79687643051147</v>
+        <v>5.79687738418579</v>
       </c>
       <c r="H101" t="n">
         <v>1741178</v>
@@ -3327,7 +3327,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G102" t="n">
-        <v>5.79687643051147</v>
+        <v>5.79687738418579</v>
       </c>
       <c r="H102" t="n">
         <v>4646214</v>
@@ -3356,7 +3356,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G103" t="n">
-        <v>5.79687643051147</v>
+        <v>5.79687738418579</v>
       </c>
       <c r="H103" t="n">
         <v>2511181</v>
@@ -3385,7 +3385,7 @@
         <v>7.28800010681152</v>
       </c>
       <c r="G104" t="n">
-        <v>5.64054012298584</v>
+        <v>5.64053964614868</v>
       </c>
       <c r="H104" t="n">
         <v>1988206</v>
@@ -3443,7 +3443,7 @@
         <v>6.91200017929077</v>
       </c>
       <c r="G106" t="n">
-        <v>5.34953498840332</v>
+        <v>5.34953546524048</v>
       </c>
       <c r="H106" t="n">
         <v>2909725</v>
@@ -3472,7 +3472,7 @@
         <v>6.89200019836426</v>
       </c>
       <c r="G107" t="n">
-        <v>5.33405542373657</v>
+        <v>5.33405590057373</v>
       </c>
       <c r="H107" t="n">
         <v>2889957</v>
@@ -3501,7 +3501,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G108" t="n">
-        <v>5.48574876785278</v>
+        <v>5.4857497215271</v>
       </c>
       <c r="H108" t="n">
         <v>2296418</v>
@@ -3530,7 +3530,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G109" t="n">
-        <v>5.56159687042236</v>
+        <v>5.56159639358521</v>
       </c>
       <c r="H109" t="n">
         <v>2743718</v>
@@ -3559,7 +3559,7 @@
         <v>7.31599998474121</v>
       </c>
       <c r="G110" t="n">
-        <v>5.66221046447754</v>
+        <v>5.66220998764038</v>
       </c>
       <c r="H110" t="n">
         <v>2111123</v>
@@ -3588,7 +3588,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>5.62660884857178</v>
+        <v>5.62660837173462</v>
       </c>
       <c r="H111" t="n">
         <v>1667359</v>
@@ -3617,7 +3617,7 @@
         <v>7.26599979400635</v>
       </c>
       <c r="G112" t="n">
-        <v>5.62351322174072</v>
+        <v>5.62351274490356</v>
       </c>
       <c r="H112" t="n">
         <v>1188881</v>
@@ -3646,7 +3646,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G113" t="n">
-        <v>5.52754354476929</v>
+        <v>5.52754306793213</v>
       </c>
       <c r="H113" t="n">
         <v>1568885</v>
@@ -3762,7 +3762,7 @@
         <v>7.08199977874756</v>
       </c>
       <c r="G117" t="n">
-        <v>5.4811053276062</v>
+        <v>5.48110628128052</v>
       </c>
       <c r="H117" t="n">
         <v>1463476</v>
@@ -3791,7 +3791,7 @@
         <v>7.19799995422363</v>
       </c>
       <c r="G118" t="n">
-        <v>5.570885181427</v>
+        <v>5.57088470458984</v>
       </c>
       <c r="H118" t="n">
         <v>1960942</v>
@@ -3820,7 +3820,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G119" t="n">
-        <v>5.61886978149414</v>
+        <v>5.61886930465698</v>
       </c>
       <c r="H119" t="n">
         <v>1697131</v>
@@ -3878,7 +3878,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>5.4640793800354</v>
+        <v>5.46407890319824</v>
       </c>
       <c r="H121" t="n">
         <v>1962224</v>
@@ -3965,7 +3965,7 @@
         <v>7.03599977493286</v>
       </c>
       <c r="G124" t="n">
-        <v>5.44550466537476</v>
+        <v>5.4455041885376</v>
       </c>
       <c r="H124" t="n">
         <v>2485435</v>
@@ -3994,7 +3994,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>5.57243156433105</v>
+        <v>5.57243204116821</v>
       </c>
       <c r="H125" t="n">
         <v>2256527</v>
@@ -4081,7 +4081,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G128" t="n">
-        <v>5.55540561676025</v>
+        <v>5.5554051399231</v>
       </c>
       <c r="H128" t="n">
         <v>2509350</v>
@@ -4110,7 +4110,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>5.54147386550903</v>
+        <v>5.54147338867188</v>
       </c>
       <c r="H129" t="n">
         <v>1457912</v>
@@ -4139,7 +4139,7 @@
         <v>7.11199998855591</v>
       </c>
       <c r="G130" t="n">
-        <v>5.5043249130249</v>
+        <v>5.50432443618774</v>
       </c>
       <c r="H130" t="n">
         <v>1790452</v>
@@ -4168,7 +4168,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G131" t="n">
-        <v>5.56159687042236</v>
+        <v>5.56159639358521</v>
       </c>
       <c r="H131" t="n">
         <v>1483323</v>
@@ -4197,7 +4197,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503707885742</v>
       </c>
       <c r="H132" t="n">
         <v>1894031</v>
@@ -4226,7 +4226,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G133" t="n">
-        <v>5.5337347984314</v>
+        <v>5.53373527526855</v>
       </c>
       <c r="H133" t="n">
         <v>2155032</v>
@@ -4255,7 +4255,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G134" t="n">
-        <v>5.61886978149414</v>
+        <v>5.61886930465698</v>
       </c>
       <c r="H134" t="n">
         <v>3548151</v>
@@ -4313,7 +4313,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>5.54921388626099</v>
+        <v>5.54921340942383</v>
       </c>
       <c r="H136" t="n">
         <v>4094123</v>
@@ -4400,7 +4400,7 @@
         <v>7.02400016784668</v>
       </c>
       <c r="G139" t="n">
-        <v>5.43621778488159</v>
+        <v>5.43621730804443</v>
       </c>
       <c r="H139" t="n">
         <v>4830708</v>
@@ -4429,7 +4429,7 @@
         <v>7.08400011062622</v>
       </c>
       <c r="G140" t="n">
-        <v>5.4826545715332</v>
+        <v>5.48265504837036</v>
       </c>
       <c r="H140" t="n">
         <v>1915810</v>
@@ -4458,7 +4458,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G141" t="n">
-        <v>5.57243156433105</v>
+        <v>5.57243204116821</v>
       </c>
       <c r="H141" t="n">
         <v>3254579</v>
@@ -4487,7 +4487,7 @@
         <v>7.13600015640259</v>
       </c>
       <c r="G142" t="n">
-        <v>5.52289962768555</v>
+        <v>5.52290010452271</v>
       </c>
       <c r="H142" t="n">
         <v>3308006</v>
@@ -4516,7 +4516,7 @@
         <v>7.2519998550415</v>
       </c>
       <c r="G143" t="n">
-        <v>5.61267709732056</v>
+        <v>5.61267757415771</v>
       </c>
       <c r="H143" t="n">
         <v>1930956</v>
@@ -4574,7 +4574,7 @@
         <v>7.2039999961853</v>
       </c>
       <c r="G145" t="n">
-        <v>5.57552862167358</v>
+        <v>5.57552719116211</v>
       </c>
       <c r="H145" t="n">
         <v>1195513</v>
@@ -4603,7 +4603,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G146" t="n">
-        <v>5.69007301330566</v>
+        <v>5.69007349014282</v>
       </c>
       <c r="H146" t="n">
         <v>3640962</v>
@@ -4661,7 +4661,7 @@
         <v>7.28599977493286</v>
       </c>
       <c r="G148" t="n">
-        <v>5.638991355896</v>
+        <v>5.63899183273315</v>
       </c>
       <c r="H148" t="n">
         <v>2206570</v>
@@ -4719,7 +4719,7 @@
         <v>7.26800012588501</v>
       </c>
       <c r="G150" t="n">
-        <v>5.62506008148193</v>
+        <v>5.62506103515625</v>
       </c>
       <c r="H150" t="n">
         <v>2888493</v>
@@ -4748,7 +4748,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503707885742</v>
       </c>
       <c r="H151" t="n">
         <v>3273131</v>
@@ -4806,7 +4806,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G153" t="n">
-        <v>5.38823270797729</v>
+        <v>5.38823223114014</v>
       </c>
       <c r="H153" t="n">
         <v>3075765</v>
@@ -4864,7 +4864,7 @@
         <v>7.4539999961853</v>
       </c>
       <c r="G155" t="n">
-        <v>5.76901483535767</v>
+        <v>5.76901531219482</v>
       </c>
       <c r="H155" t="n">
         <v>12483969</v>
@@ -4922,7 +4922,7 @@
         <v>7.5479998588562</v>
       </c>
       <c r="G157" t="n">
-        <v>5.84176635742188</v>
+        <v>5.84176588058472</v>
       </c>
       <c r="H157" t="n">
         <v>4087859</v>
@@ -5009,7 +5009,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>5.89749097824097</v>
+        <v>5.89749050140381</v>
       </c>
       <c r="H160" t="n">
         <v>3125732</v>
@@ -5067,7 +5067,7 @@
         <v>7.28599977493286</v>
       </c>
       <c r="G162" t="n">
-        <v>5.638991355896</v>
+        <v>5.63899183273315</v>
       </c>
       <c r="H162" t="n">
         <v>3232347</v>
@@ -5096,7 +5096,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G163" t="n">
-        <v>5.75044059753418</v>
+        <v>5.75044012069702</v>
       </c>
       <c r="H163" t="n">
         <v>5190788</v>
@@ -5125,7 +5125,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G164" t="n">
-        <v>5.69626474380493</v>
+        <v>5.69626426696777</v>
       </c>
       <c r="H164" t="n">
         <v>2880645</v>
@@ -5154,7 +5154,7 @@
         <v>7.20800018310547</v>
       </c>
       <c r="G165" t="n">
-        <v>5.5786247253418</v>
+        <v>5.57862377166748</v>
       </c>
       <c r="H165" t="n">
         <v>5358633</v>
@@ -5212,7 +5212,7 @@
         <v>7.31799983978271</v>
       </c>
       <c r="G167" t="n">
-        <v>5.66375780105591</v>
+        <v>5.66375827789307</v>
       </c>
       <c r="H167" t="n">
         <v>43240003</v>
@@ -5299,7 +5299,7 @@
         <v>7.47599983215332</v>
       </c>
       <c r="G170" t="n">
-        <v>5.7860426902771</v>
+        <v>5.78604221343994</v>
       </c>
       <c r="H170" t="n">
         <v>4178875</v>
@@ -5328,7 +5328,7 @@
         <v>7.44199991226196</v>
       </c>
       <c r="G171" t="n">
-        <v>5.75972747802734</v>
+        <v>5.7597279548645</v>
       </c>
       <c r="H171" t="n">
         <v>2234904</v>
@@ -5415,7 +5415,7 @@
         <v>7.52400016784668</v>
       </c>
       <c r="G174" t="n">
-        <v>5.82319164276123</v>
+        <v>5.82319211959839</v>
       </c>
       <c r="H174" t="n">
         <v>2159098</v>
@@ -5473,7 +5473,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G176" t="n">
-        <v>5.75044059753418</v>
+        <v>5.75044012069702</v>
       </c>
       <c r="H176" t="n">
         <v>1089579</v>
@@ -5531,7 +5531,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G178" t="n">
-        <v>5.76591968536377</v>
+        <v>5.76591920852661</v>
       </c>
       <c r="H178" t="n">
         <v>3012342</v>
@@ -5589,7 +5589,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>5.67304563522339</v>
+        <v>5.67304515838623</v>
       </c>
       <c r="H180" t="n">
         <v>1468023</v>
@@ -5618,7 +5618,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.64982652664185</v>
+        <v>5.64982795715332</v>
       </c>
       <c r="H181" t="n">
         <v>1631020</v>
@@ -5676,7 +5676,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G183" t="n">
-        <v>5.6931676864624</v>
+        <v>5.69316864013672</v>
       </c>
       <c r="H183" t="n">
         <v>1521415</v>
@@ -5734,7 +5734,7 @@
         <v>7.2519998550415</v>
       </c>
       <c r="G185" t="n">
-        <v>5.61267709732056</v>
+        <v>5.61267757415771</v>
       </c>
       <c r="H185" t="n">
         <v>1519641</v>
@@ -5763,7 +5763,7 @@
         <v>7.29199981689453</v>
       </c>
       <c r="G186" t="n">
-        <v>5.64363574981689</v>
+        <v>5.64363527297974</v>
       </c>
       <c r="H186" t="n">
         <v>2057580</v>
@@ -5821,7 +5821,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G188" t="n">
-        <v>5.53528261184692</v>
+        <v>5.53528213500977</v>
       </c>
       <c r="H188" t="n">
         <v>1687495</v>
@@ -5850,7 +5850,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G189" t="n">
-        <v>5.53528261184692</v>
+        <v>5.53528213500977</v>
       </c>
       <c r="H189" t="n">
         <v>2030021</v>
@@ -5908,7 +5908,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G191" t="n">
-        <v>5.55540561676025</v>
+        <v>5.5554051399231</v>
       </c>
       <c r="H191" t="n">
         <v>1748330</v>
@@ -5966,7 +5966,7 @@
         <v>7.13600015640259</v>
       </c>
       <c r="G193" t="n">
-        <v>5.52289962768555</v>
+        <v>5.52290010452271</v>
       </c>
       <c r="H193" t="n">
         <v>1880138</v>
@@ -5995,7 +5995,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G194" t="n">
-        <v>5.56469249725342</v>
+        <v>5.56469297409058</v>
       </c>
       <c r="H194" t="n">
         <v>2271355</v>
@@ -6024,7 +6024,7 @@
         <v>7.15799999237061</v>
       </c>
       <c r="G195" t="n">
-        <v>5.53992652893066</v>
+        <v>5.53992700576782</v>
       </c>
       <c r="H195" t="n">
         <v>2685820</v>
@@ -6111,7 +6111,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>5.38668394088745</v>
+        <v>5.38668489456177</v>
       </c>
       <c r="H198" t="n">
         <v>1798402</v>
@@ -6169,7 +6169,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>5.47955846786499</v>
+        <v>5.47955799102783</v>
       </c>
       <c r="H200" t="n">
         <v>1257767</v>
@@ -6227,7 +6227,7 @@
         <v>7.13199996948242</v>
       </c>
       <c r="G202" t="n">
-        <v>5.51980352401733</v>
+        <v>5.51980400085449</v>
       </c>
       <c r="H202" t="n">
         <v>1113937</v>
@@ -6256,7 +6256,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G203" t="n">
-        <v>5.52754354476929</v>
+        <v>5.52754306793213</v>
       </c>
       <c r="H203" t="n">
         <v>1657489</v>
@@ -6314,7 +6314,7 @@
         <v>7.13399982452393</v>
       </c>
       <c r="G205" t="n">
-        <v>5.52135181427002</v>
+        <v>5.5213508605957</v>
       </c>
       <c r="H205" t="n">
         <v>1601027</v>
@@ -6343,7 +6343,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>5.5337347984314</v>
+        <v>5.53373527526855</v>
       </c>
       <c r="H206" t="n">
         <v>1972922</v>
@@ -6372,7 +6372,7 @@
         <v>7.44600009918213</v>
       </c>
       <c r="G207" t="n">
-        <v>5.76282453536987</v>
+        <v>5.76282358169556</v>
       </c>
       <c r="H207" t="n">
         <v>2963238</v>
@@ -6401,7 +6401,7 @@
         <v>7.46600008010864</v>
       </c>
       <c r="G208" t="n">
-        <v>5.7783031463623</v>
+        <v>5.77830266952515</v>
       </c>
       <c r="H208" t="n">
         <v>1423117</v>
@@ -6459,7 +6459,7 @@
         <v>7.47200012207031</v>
       </c>
       <c r="G210" t="n">
-        <v>5.78294658660889</v>
+        <v>5.78294610977173</v>
       </c>
       <c r="H210" t="n">
         <v>1742076</v>
@@ -6488,7 +6488,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G211" t="n">
-        <v>5.69007301330566</v>
+        <v>5.69007349014282</v>
       </c>
       <c r="H211" t="n">
         <v>1609011</v>
@@ -6517,7 +6517,7 @@
         <v>7.19799995422363</v>
       </c>
       <c r="G212" t="n">
-        <v>5.570885181427</v>
+        <v>5.57088470458984</v>
       </c>
       <c r="H212" t="n">
         <v>2297120</v>
@@ -6575,7 +6575,7 @@
         <v>7.20800018310547</v>
       </c>
       <c r="G214" t="n">
-        <v>5.5786247253418</v>
+        <v>5.57862377166748</v>
       </c>
       <c r="H214" t="n">
         <v>1044217</v>
@@ -6691,7 +6691,7 @@
         <v>7.60400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>5.88510751724243</v>
+        <v>5.88510799407959</v>
       </c>
       <c r="H218" t="n">
         <v>1267206</v>
@@ -6720,7 +6720,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>5.88201236724854</v>
+        <v>5.88201141357422</v>
       </c>
       <c r="H219" t="n">
         <v>1419114</v>
@@ -6749,7 +6749,7 @@
         <v>7.62200021743774</v>
       </c>
       <c r="G220" t="n">
-        <v>5.89903879165649</v>
+        <v>5.89903926849365</v>
       </c>
       <c r="H220" t="n">
         <v>1328680</v>
@@ -6778,7 +6778,7 @@
         <v>7.63800001144409</v>
       </c>
       <c r="G221" t="n">
-        <v>5.91142177581787</v>
+        <v>5.91142225265503</v>
       </c>
       <c r="H221" t="n">
         <v>957497</v>
@@ -6807,7 +6807,7 @@
         <v>7.60200023651123</v>
       </c>
       <c r="G222" t="n">
-        <v>5.8835597038269</v>
+        <v>5.88356018066406</v>
       </c>
       <c r="H222" t="n">
         <v>1290829</v>
@@ -6836,7 +6836,7 @@
         <v>7.57800006866455</v>
       </c>
       <c r="G223" t="n">
-        <v>5.86498498916626</v>
+        <v>5.86498546600342</v>
       </c>
       <c r="H223" t="n">
         <v>1266692</v>
@@ -6865,7 +6865,7 @@
         <v>7.59800004959106</v>
       </c>
       <c r="G224" t="n">
-        <v>5.88046360015869</v>
+        <v>5.88046407699585</v>
       </c>
       <c r="H224" t="n">
         <v>869374</v>
@@ -6923,7 +6923,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G226" t="n">
-        <v>5.69626474380493</v>
+        <v>5.69626426696777</v>
       </c>
       <c r="H226" t="n">
         <v>2153061</v>
@@ -6952,7 +6952,7 @@
         <v>7.1560001373291</v>
       </c>
       <c r="G227" t="n">
-        <v>5.53837823867798</v>
+        <v>5.53837871551514</v>
       </c>
       <c r="H227" t="n">
         <v>2180122</v>
@@ -6981,7 +6981,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G228" t="n">
-        <v>5.56159687042236</v>
+        <v>5.56159639358521</v>
       </c>
       <c r="H228" t="n">
         <v>1290570</v>
@@ -7010,7 +7010,7 @@
         <v>7.26200008392334</v>
       </c>
       <c r="G229" t="n">
-        <v>5.62041616439819</v>
+        <v>5.62041711807251</v>
       </c>
       <c r="H229" t="n">
         <v>2755940</v>
@@ -7155,7 +7155,7 @@
         <v>6.92799997329712</v>
       </c>
       <c r="G234" t="n">
-        <v>5.3619179725647</v>
+        <v>5.36191844940186</v>
       </c>
       <c r="H234" t="n">
         <v>2011130</v>
@@ -7184,7 +7184,7 @@
         <v>6.92799997329712</v>
       </c>
       <c r="G235" t="n">
-        <v>5.3619179725647</v>
+        <v>5.36191844940186</v>
       </c>
       <c r="H235" t="n">
         <v>3181112</v>
@@ -7213,7 +7213,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G236" t="n">
-        <v>5.2164158821106</v>
+        <v>5.21641540527344</v>
       </c>
       <c r="H236" t="n">
         <v>2473197</v>
@@ -7242,7 +7242,7 @@
         <v>6.67199993133545</v>
       </c>
       <c r="G237" t="n">
-        <v>5.16378784179688</v>
+        <v>5.16378736495972</v>
       </c>
       <c r="H237" t="n">
         <v>1786947</v>
@@ -7271,7 +7271,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G238" t="n">
-        <v>5.36346673965454</v>
+        <v>5.36346578598022</v>
       </c>
       <c r="H238" t="n">
         <v>2787477</v>
@@ -7329,7 +7329,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G240" t="n">
-        <v>5.49813270568848</v>
+        <v>5.49813318252563</v>
       </c>
       <c r="H240" t="n">
         <v>2318680</v>
@@ -7358,7 +7358,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503707885742</v>
       </c>
       <c r="H241" t="n">
         <v>2076514</v>
@@ -7387,7 +7387,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G242" t="n">
-        <v>5.49813270568848</v>
+        <v>5.49813318252563</v>
       </c>
       <c r="H242" t="n">
         <v>1618816</v>
@@ -7416,7 +7416,7 @@
         <v>7.22200012207031</v>
       </c>
       <c r="G243" t="n">
-        <v>5.58945846557617</v>
+        <v>5.58945894241333</v>
       </c>
       <c r="H243" t="n">
         <v>2092114</v>
@@ -7445,7 +7445,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G244" t="n">
-        <v>5.55695343017578</v>
+        <v>5.55695295333862</v>
       </c>
       <c r="H244" t="n">
         <v>1426893</v>
@@ -7474,7 +7474,7 @@
         <v>7.18800020217896</v>
       </c>
       <c r="G245" t="n">
-        <v>5.56314516067505</v>
+        <v>5.56314468383789</v>
       </c>
       <c r="H245" t="n">
         <v>1349255</v>
@@ -7503,7 +7503,7 @@
         <v>7.20599985122681</v>
       </c>
       <c r="G246" t="n">
-        <v>5.57707500457764</v>
+        <v>5.57707595825195</v>
       </c>
       <c r="H246" t="n">
         <v>1630112</v>
@@ -7561,7 +7561,7 @@
         <v>7.10599994659424</v>
       </c>
       <c r="G248" t="n">
-        <v>5.49968099594116</v>
+        <v>5.49968147277832</v>
       </c>
       <c r="H248" t="n">
         <v>1099500</v>
@@ -7590,7 +7590,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G249" t="n">
-        <v>5.48574876785278</v>
+        <v>5.4857497215271</v>
       </c>
       <c r="H249" t="n">
         <v>1354493</v>
@@ -7619,7 +7619,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G250" t="n">
-        <v>5.56159687042236</v>
+        <v>5.56159639358521</v>
       </c>
       <c r="H250" t="n">
         <v>1511622</v>
@@ -7706,7 +7706,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G253" t="n">
-        <v>5.5662407875061</v>
+        <v>5.56624126434326</v>
       </c>
       <c r="H253" t="n">
         <v>1107860</v>
@@ -7735,7 +7735,7 @@
         <v>6.99200010299683</v>
       </c>
       <c r="G254" t="n">
-        <v>5.41145133972168</v>
+        <v>5.41144990921021</v>
       </c>
       <c r="H254" t="n">
         <v>2263864</v>
@@ -7764,7 +7764,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G255" t="n">
-        <v>5.49503755569458</v>
+        <v>5.49503707885742</v>
       </c>
       <c r="H255" t="n">
         <v>1071753</v>
@@ -7793,7 +7793,7 @@
         <v>6.86399984359741</v>
       </c>
       <c r="G256" t="n">
-        <v>5.31238508224487</v>
+        <v>5.31238460540771</v>
       </c>
       <c r="H256" t="n">
         <v>3890851</v>
@@ -7822,7 +7822,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>5.25511360168457</v>
+        <v>5.25511264801025</v>
       </c>
       <c r="H257" t="n">
         <v>2167315</v>
@@ -7851,7 +7851,7 @@
         <v>6.56599998474121</v>
       </c>
       <c r="G258" t="n">
-        <v>5.08174848556519</v>
+        <v>5.08174896240234</v>
       </c>
       <c r="H258" t="n">
         <v>2220756</v>
@@ -7938,7 +7938,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G261" t="n">
-        <v>4.73037576675415</v>
+        <v>4.73037528991699</v>
       </c>
       <c r="H261" t="n">
         <v>4291834</v>
@@ -7996,7 +7996,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G263" t="n">
-        <v>4.84646797180176</v>
+        <v>4.84646844863892</v>
       </c>
       <c r="H263" t="n">
         <v>1904690</v>
@@ -8054,7 +8054,7 @@
         <v>6.24200010299683</v>
       </c>
       <c r="G265" t="n">
-        <v>4.83098936080933</v>
+        <v>4.83098888397217</v>
       </c>
       <c r="H265" t="n">
         <v>1949193</v>
@@ -8083,7 +8083,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>4.78300476074219</v>
+        <v>4.78300333023071</v>
       </c>
       <c r="H266" t="n">
         <v>1727102</v>
@@ -8112,7 +8112,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G267" t="n">
-        <v>4.54153251647949</v>
+        <v>4.54153156280518</v>
       </c>
       <c r="H267" t="n">
         <v>4649771</v>
@@ -8228,7 +8228,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G271" t="n">
-        <v>4.75204658508301</v>
+        <v>4.75204610824585</v>
       </c>
       <c r="H271" t="n">
         <v>2954519</v>
@@ -8257,7 +8257,7 @@
         <v>6.2480001449585</v>
       </c>
       <c r="G272" t="n">
-        <v>4.83563280105591</v>
+        <v>4.83563327789307</v>
       </c>
       <c r="H272" t="n">
         <v>2873517</v>
@@ -8286,7 +8286,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G273" t="n">
-        <v>4.91457605361938</v>
+        <v>4.91457509994507</v>
       </c>
       <c r="H273" t="n">
         <v>3077722</v>
@@ -8315,7 +8315,7 @@
         <v>6.53800010681152</v>
       </c>
       <c r="G274" t="n">
-        <v>5.06007814407349</v>
+        <v>5.06007766723633</v>
       </c>
       <c r="H274" t="n">
         <v>2925266</v>
@@ -8344,7 +8344,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G275" t="n">
-        <v>5.02602386474609</v>
+        <v>5.02602434158325</v>
       </c>
       <c r="H275" t="n">
         <v>3419765</v>
@@ -8373,7 +8373,7 @@
         <v>6.44600009918213</v>
       </c>
       <c r="G276" t="n">
-        <v>4.98887491226196</v>
+        <v>4.98887538909912</v>
       </c>
       <c r="H276" t="n">
         <v>1300076</v>
@@ -8431,7 +8431,7 @@
         <v>6.34600019454956</v>
       </c>
       <c r="G278" t="n">
-        <v>4.91147947311401</v>
+        <v>4.91148042678833</v>
       </c>
       <c r="H278" t="n">
         <v>2104958</v>
@@ -8489,7 +8489,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>5.01518869400024</v>
+        <v>5.0151891708374</v>
       </c>
       <c r="H280" t="n">
         <v>1181822</v>
@@ -8518,7 +8518,7 @@
         <v>6.33599996566772</v>
       </c>
       <c r="G281" t="n">
-        <v>4.90374040603638</v>
+        <v>4.90373992919922</v>
       </c>
       <c r="H281" t="n">
         <v>1475144</v>
@@ -8605,7 +8605,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G284" t="n">
-        <v>4.63440608978271</v>
+        <v>4.63440656661987</v>
       </c>
       <c r="H284" t="n">
         <v>2793354</v>
@@ -8663,7 +8663,7 @@
         <v>6.2020001411438</v>
       </c>
       <c r="G286" t="n">
-        <v>4.8000316619873</v>
+        <v>4.80003118515015</v>
       </c>
       <c r="H286" t="n">
         <v>3630673</v>
@@ -8692,7 +8692,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G287" t="n">
-        <v>4.80467510223389</v>
+        <v>4.80467462539673</v>
       </c>
       <c r="H287" t="n">
         <v>1577631</v>
@@ -8750,7 +8750,7 @@
         <v>6.23400020599365</v>
       </c>
       <c r="G289" t="n">
-        <v>4.82479763031006</v>
+        <v>4.82479810714722</v>
       </c>
       <c r="H289" t="n">
         <v>1177221</v>
@@ -8837,7 +8837,7 @@
         <v>6.42399978637695</v>
       </c>
       <c r="G292" t="n">
-        <v>4.97184753417969</v>
+        <v>4.97184801101685</v>
       </c>
       <c r="H292" t="n">
         <v>854708</v>
@@ -8866,7 +8866,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G293" t="n">
-        <v>5.02602386474609</v>
+        <v>5.02602434158325</v>
       </c>
       <c r="H293" t="n">
         <v>2085690</v>
@@ -8895,7 +8895,7 @@
         <v>6.40799999237061</v>
       </c>
       <c r="G294" t="n">
-        <v>4.95946455001831</v>
+        <v>4.95946502685547</v>
       </c>
       <c r="H294" t="n">
         <v>1622501</v>
@@ -8982,7 +8982,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G297" t="n">
-        <v>4.80467510223389</v>
+        <v>4.80467462539673</v>
       </c>
       <c r="H297" t="n">
         <v>2974670</v>
@@ -9011,7 +9011,7 @@
         <v>6.43400001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>4.97958707809448</v>
+        <v>4.97958755493164</v>
       </c>
       <c r="H298" t="n">
         <v>2398005</v>
@@ -9040,7 +9040,7 @@
         <v>6.22599983215332</v>
       </c>
       <c r="G299" t="n">
-        <v>4.81860637664795</v>
+        <v>4.81860589981079</v>
       </c>
       <c r="H299" t="n">
         <v>1316365</v>
@@ -9214,7 +9214,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>4.58487272262573</v>
+        <v>4.58487319946289</v>
       </c>
       <c r="H305" t="n">
         <v>1600933</v>
@@ -9272,7 +9272,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>4.52760124206543</v>
+        <v>4.52760076522827</v>
       </c>
       <c r="H307" t="n">
         <v>1240333</v>
@@ -9301,7 +9301,7 @@
         <v>5.72599983215332</v>
       </c>
       <c r="G308" t="n">
-        <v>4.43163108825684</v>
+        <v>4.43163061141968</v>
       </c>
       <c r="H308" t="n">
         <v>1935193</v>
@@ -9330,7 +9330,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G309" t="n">
-        <v>4.38674306869507</v>
+        <v>4.38674211502075</v>
       </c>
       <c r="H309" t="n">
         <v>2277365</v>
@@ -9359,7 +9359,7 @@
         <v>5.7480001449585</v>
       </c>
       <c r="G310" t="n">
-        <v>4.44865846633911</v>
+        <v>4.44865894317627</v>
       </c>
       <c r="H310" t="n">
         <v>2514403</v>
@@ -9417,7 +9417,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>4.34804534912109</v>
+        <v>4.34804487228394</v>
       </c>
       <c r="H312" t="n">
         <v>2312898</v>
@@ -9475,7 +9475,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G314" t="n">
-        <v>4.34185314178467</v>
+        <v>4.34185409545898</v>
       </c>
       <c r="H314" t="n">
         <v>1120253</v>
@@ -9533,7 +9533,7 @@
         <v>5.44600009918213</v>
       </c>
       <c r="G316" t="n">
-        <v>4.21492576599121</v>
+        <v>4.21492624282837</v>
       </c>
       <c r="H316" t="n">
         <v>1823690</v>
@@ -9591,7 +9591,7 @@
         <v>5.63800001144409</v>
       </c>
       <c r="G318" t="n">
-        <v>4.36352491378784</v>
+        <v>4.36352396011353</v>
       </c>
       <c r="H318" t="n">
         <v>2183353</v>
@@ -9620,7 +9620,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G319" t="n">
-        <v>4.48116397857666</v>
+        <v>4.48116493225098</v>
       </c>
       <c r="H319" t="n">
         <v>2117640</v>
@@ -9649,7 +9649,7 @@
         <v>5.96600008010864</v>
       </c>
       <c r="G320" t="n">
-        <v>4.61737966537476</v>
+        <v>4.6173791885376</v>
       </c>
       <c r="H320" t="n">
         <v>2084581</v>
@@ -9678,7 +9678,7 @@
         <v>5.9980001449585</v>
       </c>
       <c r="G321" t="n">
-        <v>4.64214563369751</v>
+        <v>4.64214611053467</v>
       </c>
       <c r="H321" t="n">
         <v>1109326</v>
@@ -9707,7 +9707,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G322" t="n">
-        <v>4.69013023376465</v>
+        <v>4.69013071060181</v>
       </c>
       <c r="H322" t="n">
         <v>2666205</v>
@@ -9736,7 +9736,7 @@
         <v>6.0460000038147</v>
       </c>
       <c r="G323" t="n">
-        <v>4.67929553985596</v>
+        <v>4.6792950630188</v>
       </c>
       <c r="H323" t="n">
         <v>1558020</v>
@@ -9765,7 +9765,7 @@
         <v>6.06199979782104</v>
       </c>
       <c r="G324" t="n">
-        <v>4.69167852401733</v>
+        <v>4.69167804718018</v>
       </c>
       <c r="H324" t="n">
         <v>2672651</v>
@@ -9852,7 +9852,7 @@
         <v>6.05200004577637</v>
       </c>
       <c r="G327" t="n">
-        <v>4.6839394569397</v>
+        <v>4.68393850326538</v>
       </c>
       <c r="H327" t="n">
         <v>1956207</v>
@@ -9910,7 +9910,7 @@
         <v>6.02799987792969</v>
       </c>
       <c r="G329" t="n">
-        <v>4.66536426544189</v>
+        <v>4.66536378860474</v>
       </c>
       <c r="H329" t="n">
         <v>1011597</v>
@@ -9939,7 +9939,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G330" t="n">
-        <v>4.63440608978271</v>
+        <v>4.63440656661987</v>
       </c>
       <c r="H330" t="n">
         <v>914177</v>
@@ -9968,7 +9968,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G331" t="n">
-        <v>4.71489667892456</v>
+        <v>4.71489715576172</v>
       </c>
       <c r="H331" t="n">
         <v>1629330</v>
@@ -10055,7 +10055,7 @@
         <v>5.81199979782104</v>
       </c>
       <c r="G334" t="n">
-        <v>4.49819135665894</v>
+        <v>4.49819087982178</v>
       </c>
       <c r="H334" t="n">
         <v>2327837</v>
@@ -10142,7 +10142,7 @@
         <v>5.69799995422363</v>
       </c>
       <c r="G337" t="n">
-        <v>4.40996122360229</v>
+        <v>4.40996026992798</v>
       </c>
       <c r="H337" t="n">
         <v>2706905</v>
@@ -10200,7 +10200,7 @@
         <v>5.98199987411499</v>
       </c>
       <c r="G339" t="n">
-        <v>4.62976264953613</v>
+        <v>4.62976169586182</v>
       </c>
       <c r="H339" t="n">
         <v>2743128</v>
@@ -10229,7 +10229,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G340" t="n">
-        <v>4.68239116668701</v>
+        <v>4.68239164352417</v>
       </c>
       <c r="H340" t="n">
         <v>2404799</v>
@@ -10287,7 +10287,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G342" t="n">
-        <v>4.34804534912109</v>
+        <v>4.34804487228394</v>
       </c>
       <c r="H342" t="n">
         <v>1737668</v>
@@ -10345,7 +10345,7 @@
         <v>6.06799983978271</v>
       </c>
       <c r="G344" t="n">
-        <v>4.69632196426392</v>
+        <v>4.69632244110107</v>
       </c>
       <c r="H344" t="n">
         <v>4045783</v>
@@ -10374,7 +10374,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G345" t="n">
-        <v>4.71489667892456</v>
+        <v>4.71489715576172</v>
       </c>
       <c r="H345" t="n">
         <v>2457900</v>
@@ -10432,7 +10432,7 @@
         <v>6.07399988174438</v>
       </c>
       <c r="G347" t="n">
-        <v>4.7009654045105</v>
+        <v>4.70096588134766</v>
       </c>
       <c r="H347" t="n">
         <v>3636485</v>
@@ -10461,7 +10461,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G348" t="n">
-        <v>4.65452861785889</v>
+        <v>4.65452909469604</v>
       </c>
       <c r="H348" t="n">
         <v>1808439</v>
@@ -10635,7 +10635,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G354" t="n">
-        <v>4.69477367401123</v>
+        <v>4.69477415084839</v>
       </c>
       <c r="H354" t="n">
         <v>1178760</v>
@@ -10722,7 +10722,7 @@
         <v>6.07600021362305</v>
       </c>
       <c r="G357" t="n">
-        <v>4.70251369476318</v>
+        <v>4.70251417160034</v>
       </c>
       <c r="H357" t="n">
         <v>3568457</v>
@@ -10751,7 +10751,7 @@
         <v>6.15399980545044</v>
       </c>
       <c r="G358" t="n">
-        <v>4.76288175582886</v>
+        <v>4.7628812789917</v>
       </c>
       <c r="H358" t="n">
         <v>2611739</v>
@@ -10896,7 +10896,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G363" t="n">
-        <v>4.49509525299072</v>
+        <v>4.49509572982788</v>
       </c>
       <c r="H363" t="n">
         <v>3344560</v>
@@ -10925,7 +10925,7 @@
         <v>5.76800012588501</v>
       </c>
       <c r="G364" t="n">
-        <v>4.46413707733154</v>
+        <v>4.4641375541687</v>
       </c>
       <c r="H364" t="n">
         <v>3500087</v>
@@ -10954,7 +10954,7 @@
         <v>5.80600023269653</v>
       </c>
       <c r="G365" t="n">
-        <v>4.49354696273804</v>
+        <v>4.4935474395752</v>
       </c>
       <c r="H365" t="n">
         <v>2427346</v>
@@ -10983,7 +10983,7 @@
         <v>5.83799982070923</v>
       </c>
       <c r="G366" t="n">
-        <v>4.51831340789795</v>
+        <v>4.51831436157227</v>
       </c>
       <c r="H366" t="n">
         <v>2273085</v>
@@ -11012,7 +11012,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>4.61273527145386</v>
+        <v>4.61273574829102</v>
       </c>
       <c r="H367" t="n">
         <v>4059024</v>
@@ -11041,7 +11041,7 @@
         <v>5.97200012207031</v>
       </c>
       <c r="G368" t="n">
-        <v>4.6220235824585</v>
+        <v>4.62202310562134</v>
       </c>
       <c r="H368" t="n">
         <v>1871770</v>
@@ -11128,7 +11128,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G371" t="n">
-        <v>4.68548631668091</v>
+        <v>4.68548679351807</v>
       </c>
       <c r="H371" t="n">
         <v>1948144</v>
@@ -11186,7 +11186,7 @@
         <v>5.84600019454956</v>
       </c>
       <c r="G373" t="n">
-        <v>4.52450513839722</v>
+        <v>4.52450561523438</v>
       </c>
       <c r="H373" t="n">
         <v>2166296</v>
@@ -11273,7 +11273,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G376" t="n">
-        <v>4.41150903701782</v>
+        <v>4.41150856018066</v>
       </c>
       <c r="H376" t="n">
         <v>1761142</v>
@@ -11302,7 +11302,7 @@
         <v>5.73799991607666</v>
       </c>
       <c r="G377" t="n">
-        <v>4.44091844558716</v>
+        <v>4.44091939926147</v>
       </c>
       <c r="H377" t="n">
         <v>2321157</v>
@@ -11331,7 +11331,7 @@
         <v>5.82800006866455</v>
       </c>
       <c r="G378" t="n">
-        <v>4.51057481765747</v>
+        <v>4.51057434082031</v>
       </c>
       <c r="H378" t="n">
         <v>3033773</v>
@@ -11360,7 +11360,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G379" t="n">
-        <v>4.64059782028198</v>
+        <v>4.64059686660767</v>
       </c>
       <c r="H379" t="n">
         <v>5437759</v>
@@ -11534,7 +11534,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G385" t="n">
-        <v>4.84492063522339</v>
+        <v>4.84492015838623</v>
       </c>
       <c r="H385" t="n">
         <v>1864595</v>
@@ -11563,7 +11563,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G386" t="n">
-        <v>4.91612339019775</v>
+        <v>4.91612386703491</v>
       </c>
       <c r="H386" t="n">
         <v>2103203</v>
@@ -11621,7 +11621,7 @@
         <v>6.51200008392334</v>
       </c>
       <c r="G388" t="n">
-        <v>5.03995513916016</v>
+        <v>5.03995561599731</v>
       </c>
       <c r="H388" t="n">
         <v>1515195</v>
@@ -11650,7 +11650,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G389" t="n">
-        <v>5.02757167816162</v>
+        <v>5.02757215499878</v>
       </c>
       <c r="H389" t="n">
         <v>1436659</v>
@@ -11679,7 +11679,7 @@
         <v>6.5</v>
       </c>
       <c r="G390" t="n">
-        <v>5.03066778182983</v>
+        <v>5.03066825866699</v>
       </c>
       <c r="H390" t="n">
         <v>1844285</v>
@@ -11737,7 +11737,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G392" t="n">
-        <v>4.96875238418579</v>
+        <v>4.96875190734863</v>
       </c>
       <c r="H392" t="n">
         <v>2044749</v>
@@ -11795,7 +11795,7 @@
         <v>6.4060001373291</v>
       </c>
       <c r="G394" t="n">
-        <v>4.95791721343994</v>
+        <v>4.95791673660278</v>
       </c>
       <c r="H394" t="n">
         <v>1161802</v>
@@ -11824,7 +11824,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G395" t="n">
-        <v>5.02602386474609</v>
+        <v>5.02602434158325</v>
       </c>
       <c r="H395" t="n">
         <v>1755876</v>
@@ -11853,7 +11853,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G396" t="n">
-        <v>4.99971008300781</v>
+        <v>4.99971055984497</v>
       </c>
       <c r="H396" t="n">
         <v>1301218</v>
@@ -11882,7 +11882,7 @@
         <v>6.50799989700317</v>
       </c>
       <c r="G397" t="n">
-        <v>5.03685998916626</v>
+        <v>5.0368595123291</v>
       </c>
       <c r="H397" t="n">
         <v>2084969</v>
@@ -11911,7 +11911,7 @@
         <v>6.30600023269653</v>
       </c>
       <c r="G398" t="n">
-        <v>4.88052177429199</v>
+        <v>4.88052225112915</v>
       </c>
       <c r="H398" t="n">
         <v>1489174</v>
@@ -11940,7 +11940,7 @@
         <v>6.17799997329712</v>
       </c>
       <c r="G399" t="n">
-        <v>4.7814564704895</v>
+        <v>4.78145694732666</v>
       </c>
       <c r="H399" t="n">
         <v>2777477</v>
@@ -11998,7 +11998,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G401" t="n">
-        <v>4.55081939697266</v>
+        <v>4.55081987380981</v>
       </c>
       <c r="H401" t="n">
         <v>2736466</v>
@@ -12114,7 +12114,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G405" t="n">
-        <v>4.34185314178467</v>
+        <v>4.34185409545898</v>
       </c>
       <c r="H405" t="n">
         <v>2818219</v>
@@ -12143,7 +12143,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G406" t="n">
-        <v>4.40376901626587</v>
+        <v>4.40376949310303</v>
       </c>
       <c r="H406" t="n">
         <v>2618707</v>
@@ -12201,7 +12201,7 @@
         <v>5.78399991989136</v>
       </c>
       <c r="G408" t="n">
-        <v>4.47652053833008</v>
+        <v>4.47652006149292</v>
       </c>
       <c r="H408" t="n">
         <v>3475457</v>
@@ -12230,7 +12230,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G409" t="n">
-        <v>4.48271226882935</v>
+        <v>4.48271131515503</v>
       </c>
       <c r="H409" t="n">
         <v>2991538</v>
@@ -12259,7 +12259,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G410" t="n">
-        <v>4.3749361038208</v>
+        <v>4.37493562698364</v>
       </c>
       <c r="H410" t="n">
         <v>2918482</v>
@@ -12317,7 +12317,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G412" t="n">
-        <v>4.36695241928101</v>
+        <v>4.36695146560669</v>
       </c>
       <c r="H412" t="n">
         <v>1777324</v>
@@ -12404,7 +12404,7 @@
         <v>5.23400020599365</v>
       </c>
       <c r="G415" t="n">
-        <v>4.17854309082031</v>
+        <v>4.17854261398315</v>
       </c>
       <c r="H415" t="n">
         <v>1839026</v>
@@ -12491,7 +12491,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G418" t="n">
-        <v>4.1434154510498</v>
+        <v>4.14341497421265</v>
       </c>
       <c r="H418" t="n">
         <v>2326150</v>
@@ -12549,7 +12549,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G420" t="n">
-        <v>4.08114385604858</v>
+        <v>4.08114433288574</v>
       </c>
       <c r="H420" t="n">
         <v>2549135</v>
@@ -12665,7 +12665,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G424" t="n">
-        <v>4.1434154510498</v>
+        <v>4.14341497421265</v>
       </c>
       <c r="H424" t="n">
         <v>1701343</v>
@@ -12723,7 +12723,7 @@
         <v>5.32800006866455</v>
       </c>
       <c r="G426" t="n">
-        <v>4.253586769104</v>
+        <v>4.25358724594116</v>
       </c>
       <c r="H426" t="n">
         <v>1782929</v>
@@ -12781,7 +12781,7 @@
         <v>5.25</v>
       </c>
       <c r="G428" t="n">
-        <v>4.1913161277771</v>
+        <v>4.19131565093994</v>
       </c>
       <c r="H428" t="n">
         <v>1872527</v>
@@ -12839,7 +12839,7 @@
         <v>5.2519998550415</v>
       </c>
       <c r="G430" t="n">
-        <v>4.19291257858276</v>
+        <v>4.19291305541992</v>
       </c>
       <c r="H430" t="n">
         <v>1071567</v>
@@ -12868,7 +12868,7 @@
         <v>5.2979998588562</v>
       </c>
       <c r="G431" t="n">
-        <v>4.22963619232178</v>
+        <v>4.22963666915894</v>
       </c>
       <c r="H431" t="n">
         <v>1833402</v>
@@ -12897,7 +12897,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G432" t="n">
-        <v>4.27913427352905</v>
+        <v>4.27913475036621</v>
       </c>
       <c r="H432" t="n">
         <v>1674854</v>
@@ -12926,7 +12926,7 @@
         <v>5.47599983215332</v>
       </c>
       <c r="G433" t="n">
-        <v>4.371741771698</v>
+        <v>4.37174224853516</v>
       </c>
       <c r="H433" t="n">
         <v>2847131</v>
@@ -13013,7 +13013,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G436" t="n">
-        <v>4.29829406738281</v>
+        <v>4.29829454421997</v>
       </c>
       <c r="H436" t="n">
         <v>1263878</v>
@@ -13129,7 +13129,7 @@
         <v>5.30600023269653</v>
       </c>
       <c r="G440" t="n">
-        <v>4.23602342605591</v>
+        <v>4.23602390289307</v>
       </c>
       <c r="H440" t="n">
         <v>3874778</v>
@@ -13187,7 +13187,7 @@
         <v>5.25</v>
       </c>
       <c r="G442" t="n">
-        <v>4.1913161277771</v>
+        <v>4.19131565093994</v>
       </c>
       <c r="H442" t="n">
         <v>2076406</v>
@@ -13448,7 +13448,7 @@
         <v>5.55399990081787</v>
       </c>
       <c r="G451" t="n">
-        <v>4.43401288986206</v>
+        <v>4.43401336669922</v>
       </c>
       <c r="H451" t="n">
         <v>4935845</v>
@@ -13506,7 +13506,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G453" t="n">
-        <v>4.15139865875244</v>
+        <v>4.15139818191528</v>
       </c>
       <c r="H453" t="n">
         <v>4787912</v>
@@ -13535,7 +13535,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G454" t="n">
-        <v>4.14022207260132</v>
+        <v>4.14022159576416</v>
       </c>
       <c r="H454" t="n">
         <v>4361773</v>
@@ -13622,7 +13622,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G457" t="n">
-        <v>4.63359928131104</v>
+        <v>4.63359975814819</v>
       </c>
       <c r="H457" t="n">
         <v>7038921</v>
@@ -13651,7 +13651,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G458" t="n">
-        <v>4.55057144165039</v>
+        <v>4.55057191848755</v>
       </c>
       <c r="H458" t="n">
         <v>5385901</v>
@@ -13680,7 +13680,7 @@
         <v>5.60799980163574</v>
       </c>
       <c r="G459" t="n">
-        <v>4.47712373733521</v>
+        <v>4.47712421417236</v>
       </c>
       <c r="H459" t="n">
         <v>3761167</v>
@@ -13738,7 +13738,7 @@
         <v>5.31400012969971</v>
       </c>
       <c r="G461" t="n">
-        <v>4.24241018295288</v>
+        <v>4.24241065979004</v>
       </c>
       <c r="H461" t="n">
         <v>4723842</v>
@@ -13796,7 +13796,7 @@
         <v>5.38800001144409</v>
       </c>
       <c r="G463" t="n">
-        <v>4.30148792266846</v>
+        <v>4.30148839950562</v>
       </c>
       <c r="H463" t="n">
         <v>2317291</v>
@@ -13825,7 +13825,7 @@
         <v>5.01599979400635</v>
       </c>
       <c r="G464" t="n">
-        <v>4.00450277328491</v>
+        <v>4.00450325012207</v>
       </c>
       <c r="H464" t="n">
         <v>10393285</v>
@@ -13854,7 +13854,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>3.87197756767273</v>
+        <v>3.87197804450989</v>
       </c>
       <c r="H465" t="n">
         <v>5847939</v>
@@ -13883,7 +13883,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G466" t="n">
-        <v>3.76819276809692</v>
+        <v>3.76819229125977</v>
       </c>
       <c r="H466" t="n">
         <v>4448449</v>
@@ -13912,7 +13912,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G467" t="n">
-        <v>3.79373931884766</v>
+        <v>3.79373955726624</v>
       </c>
       <c r="H467" t="n">
         <v>3659216</v>
@@ -13941,7 +13941,7 @@
         <v>4.85699987411499</v>
       </c>
       <c r="G468" t="n">
-        <v>3.87756562232971</v>
+        <v>3.87756609916687</v>
       </c>
       <c r="H468" t="n">
         <v>1900796</v>
@@ -13970,7 +13970,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>3.70831656455994</v>
+        <v>3.70831680297852</v>
       </c>
       <c r="H469" t="n">
         <v>4777891</v>
@@ -13999,7 +13999,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G470" t="n">
-        <v>3.673987865448</v>
+        <v>3.67398810386658</v>
       </c>
       <c r="H470" t="n">
         <v>1796893</v>
@@ -14057,7 +14057,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G472" t="n">
-        <v>3.64444947242737</v>
+        <v>3.64444875717163</v>
       </c>
       <c r="H472" t="n">
         <v>2861060</v>
@@ -14115,7 +14115,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G474" t="n">
-        <v>3.67957663536072</v>
+        <v>3.67957639694214</v>
       </c>
       <c r="H474" t="n">
         <v>2548271</v>
@@ -14144,7 +14144,7 @@
         <v>4.51300001144409</v>
       </c>
       <c r="G475" t="n">
-        <v>3.60293459892273</v>
+        <v>3.60293531417847</v>
       </c>
       <c r="H475" t="n">
         <v>2278675</v>
@@ -14173,7 +14173,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G476" t="n">
-        <v>3.74264574050903</v>
+        <v>3.74264550209045</v>
       </c>
       <c r="H476" t="n">
         <v>5137879</v>
@@ -14231,7 +14231,7 @@
         <v>4.6729998588562</v>
       </c>
       <c r="G478" t="n">
-        <v>3.73067021369934</v>
+        <v>3.73067045211792</v>
       </c>
       <c r="H478" t="n">
         <v>2579458</v>
@@ -14260,7 +14260,7 @@
         <v>4.74100017547607</v>
       </c>
       <c r="G479" t="n">
-        <v>3.78495812416077</v>
+        <v>3.78495836257935</v>
       </c>
       <c r="H479" t="n">
         <v>1283763</v>
@@ -14289,7 +14289,7 @@
         <v>4.84700012207031</v>
       </c>
       <c r="G480" t="n">
-        <v>3.86958265304565</v>
+        <v>3.86958241462708</v>
       </c>
       <c r="H480" t="n">
         <v>2567620</v>
@@ -14318,7 +14318,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.82407689094543</v>
+        <v>3.82407736778259</v>
       </c>
       <c r="H481" t="n">
         <v>1581513</v>
@@ -14347,7 +14347,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.74025082588196</v>
+        <v>3.74025058746338</v>
       </c>
       <c r="H482" t="n">
         <v>5781269</v>
@@ -14376,7 +14376,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>3.77218437194824</v>
+        <v>3.7721848487854</v>
       </c>
       <c r="H483" t="n">
         <v>3715855</v>
@@ -14405,7 +14405,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>3.76020956039429</v>
+        <v>3.76020908355713</v>
       </c>
       <c r="H484" t="n">
         <v>1701361</v>
@@ -14434,7 +14434,7 @@
         <v>4.6729998588562</v>
       </c>
       <c r="G485" t="n">
-        <v>3.73067021369934</v>
+        <v>3.73067045211792</v>
       </c>
       <c r="H485" t="n">
         <v>1812903</v>
@@ -14463,7 +14463,7 @@
         <v>4.97300004959106</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97017455101013</v>
+        <v>3.97017407417297</v>
       </c>
       <c r="H486" t="n">
         <v>6818273</v>
@@ -14492,7 +14492,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G487" t="n">
-        <v>4.06837129592896</v>
+        <v>4.0683708190918</v>
       </c>
       <c r="H487" t="n">
         <v>4111709</v>
@@ -14521,7 +14521,7 @@
         <v>5.13199996948242</v>
       </c>
       <c r="G488" t="n">
-        <v>4.09711170196533</v>
+        <v>4.09711122512817</v>
       </c>
       <c r="H488" t="n">
         <v>4550769</v>
@@ -14550,7 +14550,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G489" t="n">
-        <v>4.27274751663208</v>
+        <v>4.27274799346924</v>
       </c>
       <c r="H489" t="n">
         <v>6002211</v>
@@ -14579,7 +14579,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G490" t="n">
-        <v>4.31585836410522</v>
+        <v>4.31585788726807</v>
       </c>
       <c r="H490" t="n">
         <v>4931862</v>
@@ -14637,7 +14637,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>4.42283582687378</v>
+        <v>4.4228367805481</v>
       </c>
       <c r="H492" t="n">
         <v>5033717</v>
@@ -14666,7 +14666,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G493" t="n">
-        <v>4.51863813400269</v>
+        <v>4.51863765716553</v>
       </c>
       <c r="H493" t="n">
         <v>5379056</v>
@@ -14695,7 +14695,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>4.55057144165039</v>
+        <v>4.55057191848755</v>
       </c>
       <c r="H494" t="n">
         <v>4943046</v>
@@ -14753,7 +14753,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G496" t="n">
-        <v>4.52183151245117</v>
+        <v>4.52183103561401</v>
       </c>
       <c r="H496" t="n">
         <v>3180033</v>
@@ -14811,7 +14811,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G498" t="n">
-        <v>4.52183151245117</v>
+        <v>4.52183103561401</v>
       </c>
       <c r="H498" t="n">
         <v>3193617</v>
@@ -14840,7 +14840,7 @@
         <v>5.44199991226196</v>
       </c>
       <c r="G499" t="n">
-        <v>4.34459829330444</v>
+        <v>4.3445987701416</v>
       </c>
       <c r="H499" t="n">
         <v>3591458</v>
@@ -14869,7 +14869,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G500" t="n">
-        <v>4.28871393203735</v>
+        <v>4.2887134552002</v>
       </c>
       <c r="H500" t="n">
         <v>3137057</v>
@@ -14927,7 +14927,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G502" t="n">
-        <v>4.31585836410522</v>
+        <v>4.31585788726807</v>
       </c>
       <c r="H502" t="n">
         <v>2362505</v>
@@ -14956,7 +14956,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>4.42283582687378</v>
+        <v>4.4228367805481</v>
       </c>
       <c r="H503" t="n">
         <v>2428806</v>
@@ -14985,7 +14985,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G504" t="n">
-        <v>4.33342123031616</v>
+        <v>4.33342170715332</v>
       </c>
       <c r="H504" t="n">
         <v>3521555</v>
@@ -15043,7 +15043,7 @@
         <v>5.25</v>
       </c>
       <c r="G506" t="n">
-        <v>4.1913161277771</v>
+        <v>4.19131565093994</v>
       </c>
       <c r="H506" t="n">
         <v>4996046</v>
@@ -15072,7 +15072,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G507" t="n">
-        <v>4.17055940628052</v>
+        <v>4.17055892944336</v>
       </c>
       <c r="H507" t="n">
         <v>2153129</v>
@@ -15130,7 +15130,7 @@
         <v>5.12200021743774</v>
       </c>
       <c r="G509" t="n">
-        <v>4.08912801742554</v>
+        <v>4.08912754058838</v>
       </c>
       <c r="H509" t="n">
         <v>2419720</v>
@@ -15188,7 +15188,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G511" t="n">
-        <v>4.07954740524292</v>
+        <v>4.07954835891724</v>
       </c>
       <c r="H511" t="n">
         <v>2798919</v>
@@ -15217,7 +15217,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G512" t="n">
-        <v>4.25518321990967</v>
+        <v>4.25518369674683</v>
       </c>
       <c r="H512" t="n">
         <v>4570455</v>
@@ -15246,7 +15246,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G513" t="n">
-        <v>4.31585836410522</v>
+        <v>4.31585788726807</v>
       </c>
       <c r="H513" t="n">
         <v>3182774</v>
@@ -15275,7 +15275,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G514" t="n">
-        <v>4.33342123031616</v>
+        <v>4.33342170715332</v>
       </c>
       <c r="H514" t="n">
         <v>1809786</v>
@@ -15362,7 +15362,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G517" t="n">
-        <v>4.43081951141357</v>
+        <v>4.43082046508789</v>
       </c>
       <c r="H517" t="n">
         <v>5183857</v>
@@ -15391,7 +15391,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G518" t="n">
-        <v>4.31585836410522</v>
+        <v>4.31585788726807</v>
       </c>
       <c r="H518" t="n">
         <v>4792657</v>
@@ -15420,7 +15420,7 @@
         <v>5.4539999961853</v>
       </c>
       <c r="G519" t="n">
-        <v>4.35417890548706</v>
+        <v>4.3541784286499</v>
       </c>
       <c r="H519" t="n">
         <v>4000499</v>
@@ -15507,7 +15507,7 @@
         <v>5.4539999961853</v>
       </c>
       <c r="G522" t="n">
-        <v>4.35417890548706</v>
+        <v>4.3541784286499</v>
       </c>
       <c r="H522" t="n">
         <v>2878305</v>
@@ -15594,7 +15594,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G525" t="n">
-        <v>4.63679265975952</v>
+        <v>4.63679313659668</v>
       </c>
       <c r="H525" t="n">
         <v>3552700</v>
@@ -15681,7 +15681,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G528" t="n">
-        <v>4.18333292007446</v>
+        <v>4.18333196640015</v>
       </c>
       <c r="H528" t="n">
         <v>2888851</v>
@@ -15797,7 +15797,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>4.3749361038208</v>
+        <v>4.37493562698364</v>
       </c>
       <c r="H532" t="n">
         <v>6191056</v>
@@ -15884,7 +15884,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.41485261917114</v>
+        <v>4.4148530960083</v>
       </c>
       <c r="H535" t="n">
         <v>4053856</v>
@@ -15942,7 +15942,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G537" t="n">
-        <v>4.22644233703613</v>
+        <v>4.22644329071045</v>
       </c>
       <c r="H537" t="n">
         <v>3102583</v>
@@ -16000,7 +16000,7 @@
         <v>5.27600002288818</v>
       </c>
       <c r="G539" t="n">
-        <v>4.21207332611084</v>
+        <v>4.21207284927368</v>
       </c>
       <c r="H539" t="n">
         <v>3407347</v>
@@ -16029,7 +16029,7 @@
         <v>5.21400022506714</v>
       </c>
       <c r="G540" t="n">
-        <v>4.16257619857788</v>
+        <v>4.16257572174072</v>
       </c>
       <c r="H540" t="n">
         <v>4373570</v>
@@ -16058,7 +16058,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>4.1434154510498</v>
+        <v>4.14341497421265</v>
       </c>
       <c r="H541" t="n">
         <v>3194214</v>
@@ -16145,7 +16145,7 @@
         <v>5.27600002288818</v>
       </c>
       <c r="G544" t="n">
-        <v>4.21207332611084</v>
+        <v>4.21207284927368</v>
       </c>
       <c r="H544" t="n">
         <v>2108071</v>
@@ -16174,7 +16174,7 @@
         <v>5.39200019836426</v>
       </c>
       <c r="G545" t="n">
-        <v>4.30468130111694</v>
+        <v>4.30468082427979</v>
       </c>
       <c r="H545" t="n">
         <v>5095042</v>
@@ -16203,7 +16203,7 @@
         <v>5.29400014877319</v>
       </c>
       <c r="G546" t="n">
-        <v>4.22644233703613</v>
+        <v>4.22644329071045</v>
       </c>
       <c r="H546" t="n">
         <v>3708846</v>
@@ -16261,7 +16261,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G548" t="n">
-        <v>4.11148166656494</v>
+        <v>4.11148118972778</v>
       </c>
       <c r="H548" t="n">
         <v>3196759</v>
@@ -16290,7 +16290,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G549" t="n">
-        <v>4.06996774673462</v>
+        <v>4.0699667930603</v>
       </c>
       <c r="H549" t="n">
         <v>3624315</v>
@@ -16319,7 +16319,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G550" t="n">
-        <v>4.03164672851562</v>
+        <v>4.03164720535278</v>
       </c>
       <c r="H550" t="n">
         <v>2770919</v>
@@ -16348,7 +16348,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G551" t="n">
-        <v>4.06996774673462</v>
+        <v>4.0699667930603</v>
       </c>
       <c r="H551" t="n">
         <v>2173884</v>
@@ -16406,7 +16406,7 @@
         <v>5.14200019836426</v>
       </c>
       <c r="G553" t="n">
-        <v>4.10509538650513</v>
+        <v>4.10509490966797</v>
       </c>
       <c r="H553" t="n">
         <v>1526086</v>
@@ -16435,7 +16435,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>4.07156419754028</v>
+        <v>4.07156372070312</v>
       </c>
       <c r="H554" t="n">
         <v>1997489</v>
@@ -16493,7 +16493,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G556" t="n">
-        <v>4.17055940628052</v>
+        <v>4.17055892944336</v>
       </c>
       <c r="H556" t="n">
         <v>2796533</v>
@@ -16522,7 +16522,7 @@
         <v>5.28200006484985</v>
       </c>
       <c r="G557" t="n">
-        <v>4.21686267852783</v>
+        <v>4.21686315536499</v>
       </c>
       <c r="H557" t="n">
         <v>3347161</v>
@@ -16551,7 +16551,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G558" t="n">
-        <v>4.17055940628052</v>
+        <v>4.17055892944336</v>
       </c>
       <c r="H558" t="n">
         <v>4025623</v>
@@ -16580,7 +16580,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G559" t="n">
-        <v>4.24560308456421</v>
+        <v>4.24560356140137</v>
       </c>
       <c r="H559" t="n">
         <v>1914778</v>
@@ -16667,7 +16667,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G562" t="n">
-        <v>4.09870767593384</v>
+        <v>4.098708152771</v>
       </c>
       <c r="H562" t="n">
         <v>3351858</v>
@@ -16725,7 +16725,7 @@
         <v>5.21600008010864</v>
       </c>
       <c r="G564" t="n">
-        <v>4.16417264938354</v>
+        <v>4.16417217254639</v>
       </c>
       <c r="H564" t="n">
         <v>1011107</v>
@@ -16870,7 +16870,7 @@
         <v>5.14599990844727</v>
       </c>
       <c r="G569" t="n">
-        <v>4.10828828811646</v>
+        <v>4.1082878112793</v>
       </c>
       <c r="H569" t="n">
         <v>4795887</v>
@@ -17015,7 +17015,7 @@
         <v>5.25400018692017</v>
       </c>
       <c r="G574" t="n">
-        <v>4.19450950622559</v>
+        <v>4.19450902938843</v>
       </c>
       <c r="H574" t="n">
         <v>2166563</v>
@@ -17073,7 +17073,7 @@
         <v>5.02799987792969</v>
       </c>
       <c r="G576" t="n">
-        <v>4.01408290863037</v>
+        <v>4.01408243179321</v>
       </c>
       <c r="H576" t="n">
         <v>3884688</v>
@@ -17102,7 +17102,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G577" t="n">
-        <v>4.05080652236938</v>
+        <v>4.0508074760437</v>
       </c>
       <c r="H577" t="n">
         <v>5524918</v>
@@ -17131,7 +17131,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G578" t="n">
-        <v>4.0476131439209</v>
+        <v>4.04761362075806</v>
       </c>
       <c r="H578" t="n">
         <v>3863560</v>
@@ -17218,7 +17218,7 @@
         <v>5.03800010681152</v>
       </c>
       <c r="G581" t="n">
-        <v>4.02206611633301</v>
+        <v>4.02206659317017</v>
       </c>
       <c r="H581" t="n">
         <v>2078074</v>
@@ -17247,7 +17247,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G582" t="n">
-        <v>3.92147541046143</v>
+        <v>3.92147564888</v>
       </c>
       <c r="H582" t="n">
         <v>4658611</v>
@@ -17276,7 +17276,7 @@
         <v>4.78900003433228</v>
       </c>
       <c r="G583" t="n">
-        <v>3.8232786655426</v>
+        <v>3.82327890396118</v>
       </c>
       <c r="H583" t="n">
         <v>11701850</v>
@@ -17334,7 +17334,7 @@
         <v>4.58300018310547</v>
       </c>
       <c r="G585" t="n">
-        <v>3.65881967544556</v>
+        <v>3.65881943702698</v>
       </c>
       <c r="H585" t="n">
         <v>5364133</v>
@@ -17363,7 +17363,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G586" t="n">
-        <v>3.75302410125732</v>
+        <v>3.75302457809448</v>
       </c>
       <c r="H586" t="n">
         <v>6044732</v>
@@ -17392,7 +17392,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G587" t="n">
-        <v>3.62129640579224</v>
+        <v>3.62129688262939</v>
       </c>
       <c r="H587" t="n">
         <v>4501239</v>
@@ -17421,7 +17421,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G588" t="n">
-        <v>3.49036860466003</v>
+        <v>3.49036884307861</v>
       </c>
       <c r="H588" t="n">
         <v>6889328</v>
@@ -17450,7 +17450,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G589" t="n">
-        <v>3.50314164161682</v>
+        <v>3.5031418800354</v>
       </c>
       <c r="H589" t="n">
         <v>3275117</v>
@@ -17479,7 +17479,7 @@
         <v>4.36299991607666</v>
       </c>
       <c r="G590" t="n">
-        <v>3.48318290710449</v>
+        <v>3.48318314552307</v>
       </c>
       <c r="H590" t="n">
         <v>6428207</v>
@@ -17537,7 +17537,7 @@
         <v>4.59299993515015</v>
       </c>
       <c r="G592" t="n">
-        <v>3.66680288314819</v>
+        <v>3.66680312156677</v>
       </c>
       <c r="H592" t="n">
         <v>6212543</v>
@@ -17566,7 +17566,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>3.62848210334778</v>
+        <v>3.62848234176636</v>
       </c>
       <c r="H593" t="n">
         <v>2432519</v>
@@ -17595,7 +17595,7 @@
         <v>4.50899982452393</v>
       </c>
       <c r="G594" t="n">
-        <v>3.59974145889282</v>
+        <v>3.59974193572998</v>
       </c>
       <c r="H594" t="n">
         <v>2408795</v>
@@ -17653,7 +17653,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G596" t="n">
-        <v>3.67957663536072</v>
+        <v>3.67957639694214</v>
       </c>
       <c r="H596" t="n">
         <v>4652125</v>
@@ -17682,7 +17682,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G597" t="n">
-        <v>3.60054039955139</v>
+        <v>3.60054016113281</v>
       </c>
       <c r="H597" t="n">
         <v>6336601</v>
@@ -17711,7 +17711,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>3.60852384567261</v>
+        <v>3.60852336883545</v>
       </c>
       <c r="H598" t="n">
         <v>3399120</v>
@@ -17740,7 +17740,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G599" t="n">
-        <v>3.76819276809692</v>
+        <v>3.76819229125977</v>
       </c>
       <c r="H599" t="n">
         <v>7494823</v>
@@ -17769,7 +17769,7 @@
         <v>4.70900011062622</v>
       </c>
       <c r="G600" t="n">
-        <v>3.75941133499146</v>
+        <v>3.75941109657288</v>
       </c>
       <c r="H600" t="n">
         <v>4447046</v>
@@ -17798,7 +17798,7 @@
         <v>4.86600017547607</v>
       </c>
       <c r="G601" t="n">
-        <v>3.8847508430481</v>
+        <v>3.88475179672241</v>
       </c>
       <c r="H601" t="n">
         <v>10983974</v>
@@ -17827,7 +17827,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G602" t="n">
-        <v>3.86798620223999</v>
+        <v>3.86798572540283</v>
       </c>
       <c r="H602" t="n">
         <v>5651003</v>
@@ -17885,7 +17885,7 @@
         <v>4.45900011062622</v>
       </c>
       <c r="G604" t="n">
-        <v>3.55982422828674</v>
+        <v>3.5598247051239</v>
       </c>
       <c r="H604" t="n">
         <v>8229899</v>
@@ -17914,7 +17914,7 @@
         <v>4.36100006103516</v>
       </c>
       <c r="G605" t="n">
-        <v>3.48158669471741</v>
+        <v>3.48158621788025</v>
       </c>
       <c r="H605" t="n">
         <v>6810047</v>
@@ -17943,7 +17943,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G606" t="n">
-        <v>3.55742931365967</v>
+        <v>3.55742883682251</v>
       </c>
       <c r="H606" t="n">
         <v>5214931</v>
@@ -17972,7 +17972,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G607" t="n">
-        <v>3.44885420799255</v>
+        <v>3.44885396957397</v>
       </c>
       <c r="H607" t="n">
         <v>7650637</v>
@@ -18001,7 +18001,7 @@
         <v>4.25299978256226</v>
       </c>
       <c r="G608" t="n">
-        <v>3.39536476135254</v>
+        <v>3.3953652381897</v>
       </c>
       <c r="H608" t="n">
         <v>7078011</v>
@@ -18030,7 +18030,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>3.27321815490723</v>
+        <v>3.27321839332581</v>
       </c>
       <c r="H609" t="n">
         <v>5545729</v>
@@ -18059,7 +18059,7 @@
         <v>4.01399993896484</v>
       </c>
       <c r="G610" t="n">
-        <v>3.20456051826477</v>
+        <v>3.20456027984619</v>
       </c>
       <c r="H610" t="n">
         <v>6984815</v>
@@ -18088,7 +18088,7 @@
         <v>4.01700019836426</v>
       </c>
       <c r="G611" t="n">
-        <v>3.20695543289185</v>
+        <v>3.20695567131042</v>
       </c>
       <c r="H611" t="n">
         <v>5862624</v>
@@ -18117,7 +18117,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>3.12951612472534</v>
+        <v>3.12951564788818</v>
       </c>
       <c r="H612" t="n">
         <v>6435404</v>
@@ -18146,7 +18146,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G613" t="n">
-        <v>3.10875868797302</v>
+        <v>3.1087589263916</v>
       </c>
       <c r="H613" t="n">
         <v>8219341</v>
@@ -18175,7 +18175,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G614" t="n">
-        <v>2.97304034233093</v>
+        <v>2.97304010391235</v>
       </c>
       <c r="H614" t="n">
         <v>10888234</v>
@@ -18233,7 +18233,7 @@
         <v>3.81299996376038</v>
       </c>
       <c r="G616" t="n">
-        <v>3.04409313201904</v>
+        <v>3.04409265518188</v>
       </c>
       <c r="H616" t="n">
         <v>7465288</v>
@@ -18291,7 +18291,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G618" t="n">
-        <v>2.79740405082703</v>
+        <v>2.79740381240845</v>
       </c>
       <c r="H618" t="n">
         <v>10288588</v>
@@ -18320,7 +18320,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G619" t="n">
-        <v>2.54832005500793</v>
+        <v>2.54832029342651</v>
       </c>
       <c r="H619" t="n">
         <v>9672937</v>
@@ -18349,7 +18349,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G620" t="n">
-        <v>2.68004727363586</v>
+        <v>2.68004751205444</v>
       </c>
       <c r="H620" t="n">
         <v>6043852</v>
@@ -18407,7 +18407,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G622" t="n">
-        <v>3.04169797897339</v>
+        <v>3.04169774055481</v>
       </c>
       <c r="H622" t="n">
         <v>5816562</v>
@@ -18436,7 +18436,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G623" t="n">
-        <v>2.87404537200928</v>
+        <v>2.8740451335907</v>
       </c>
       <c r="H623" t="n">
         <v>16884906</v>
@@ -18494,7 +18494,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G625" t="n">
-        <v>2.86606192588806</v>
+        <v>2.86606168746948</v>
       </c>
       <c r="H625" t="n">
         <v>9063322</v>
@@ -18552,7 +18552,7 @@
         <v>3.38100004196167</v>
       </c>
       <c r="G627" t="n">
-        <v>2.69920754432678</v>
+        <v>2.6992073059082</v>
       </c>
       <c r="H627" t="n">
         <v>9943300</v>
@@ -18581,7 +18581,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G628" t="n">
-        <v>2.65450000762939</v>
+        <v>2.65450048446655</v>
       </c>
       <c r="H628" t="n">
         <v>6000213</v>
@@ -18610,7 +18610,7 @@
         <v>3.34100008010864</v>
       </c>
       <c r="G629" t="n">
-        <v>2.66727375984192</v>
+        <v>2.6672739982605</v>
       </c>
       <c r="H629" t="n">
         <v>3510090</v>
@@ -18639,7 +18639,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G630" t="n">
-        <v>2.6065993309021</v>
+        <v>2.60659980773926</v>
       </c>
       <c r="H630" t="n">
         <v>6322881</v>
@@ -18697,7 +18697,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>2.52676463127136</v>
+        <v>2.52676486968994</v>
       </c>
       <c r="H632" t="n">
         <v>7636312</v>
@@ -18726,7 +18726,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>2.52676463127136</v>
+        <v>2.52676486968994</v>
       </c>
       <c r="H633" t="n">
         <v>3202966</v>
@@ -18755,7 +18755,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G634" t="n">
-        <v>2.55790066719055</v>
+        <v>2.55790042877197</v>
       </c>
       <c r="H634" t="n">
         <v>5933108</v>
@@ -18842,7 +18842,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G637" t="n">
-        <v>2.69681262969971</v>
+        <v>2.69681239128113</v>
       </c>
       <c r="H637" t="n">
         <v>5445633</v>
@@ -18871,7 +18871,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G638" t="n">
-        <v>2.64731502532959</v>
+        <v>2.64731526374817</v>
       </c>
       <c r="H638" t="n">
         <v>3349455</v>
@@ -18900,7 +18900,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G639" t="n">
-        <v>2.49083948135376</v>
+        <v>2.4908390045166</v>
       </c>
       <c r="H639" t="n">
         <v>4097145</v>
@@ -18929,7 +18929,7 @@
         <v>3.28600001335144</v>
       </c>
       <c r="G640" t="n">
-        <v>2.62336468696594</v>
+        <v>2.62336421012878</v>
       </c>
       <c r="H640" t="n">
         <v>4401473</v>
@@ -18958,7 +18958,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>2.62655806541443</v>
+        <v>2.62655782699585</v>
       </c>
       <c r="H641" t="n">
         <v>3511058</v>
@@ -18987,7 +18987,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G642" t="n">
-        <v>2.71437621116638</v>
+        <v>2.71437644958496</v>
       </c>
       <c r="H642" t="n">
         <v>2930726</v>
@@ -19016,7 +19016,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G643" t="n">
-        <v>2.65689539909363</v>
+        <v>2.65689516067505</v>
       </c>
       <c r="H643" t="n">
         <v>2058256</v>
@@ -19045,7 +19045,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G644" t="n">
-        <v>2.61857438087463</v>
+        <v>2.61857461929321</v>
       </c>
       <c r="H644" t="n">
         <v>2275737</v>
@@ -19074,7 +19074,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G645" t="n">
-        <v>2.64731502532959</v>
+        <v>2.64731526374817</v>
       </c>
       <c r="H645" t="n">
         <v>1198096</v>
@@ -19103,7 +19103,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G646" t="n">
-        <v>2.68004727363586</v>
+        <v>2.68004751205444</v>
       </c>
       <c r="H646" t="n">
         <v>1543079</v>
@@ -19132,7 +19132,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G647" t="n">
-        <v>2.70639252662659</v>
+        <v>2.70639276504517</v>
       </c>
       <c r="H647" t="n">
         <v>1698132</v>
@@ -19219,7 +19219,7 @@
         <v>3.55399990081787</v>
       </c>
       <c r="G650" t="n">
-        <v>2.83732128143311</v>
+        <v>2.83732151985168</v>
       </c>
       <c r="H650" t="n">
         <v>5429729</v>
@@ -19248,7 +19248,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G651" t="n">
-        <v>2.81017756462097</v>
+        <v>2.81017780303955</v>
       </c>
       <c r="H651" t="n">
         <v>2071239</v>
@@ -19306,7 +19306,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G653" t="n">
-        <v>2.95388007164001</v>
+        <v>2.95387983322144</v>
       </c>
       <c r="H653" t="n">
         <v>3265251</v>
@@ -19335,7 +19335,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G654" t="n">
-        <v>2.95388007164001</v>
+        <v>2.95387983322144</v>
       </c>
       <c r="H654" t="n">
         <v>2287711</v>
@@ -19393,7 +19393,7 @@
         <v>3.60700011253357</v>
       </c>
       <c r="G656" t="n">
-        <v>2.87963390350342</v>
+        <v>2.87963366508484</v>
       </c>
       <c r="H656" t="n">
         <v>2692353</v>
@@ -19422,7 +19422,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>2.90997076034546</v>
+        <v>2.90997099876404</v>
       </c>
       <c r="H657" t="n">
         <v>2184909</v>
@@ -19451,7 +19451,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G658" t="n">
-        <v>2.87005376815796</v>
+        <v>2.87005352973938</v>
       </c>
       <c r="H658" t="n">
         <v>2233494</v>
@@ -19480,7 +19480,7 @@
         <v>3.58699989318848</v>
       </c>
       <c r="G659" t="n">
-        <v>2.86366677284241</v>
+        <v>2.86366653442383</v>
       </c>
       <c r="H659" t="n">
         <v>3081090</v>
@@ -19509,7 +19509,7 @@
         <v>3.59699988365173</v>
       </c>
       <c r="G660" t="n">
-        <v>2.87165021896362</v>
+        <v>2.87164998054504</v>
       </c>
       <c r="H660" t="n">
         <v>3173757</v>
@@ -19538,7 +19538,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G661" t="n">
-        <v>2.92593741416931</v>
+        <v>2.92593765258789</v>
       </c>
       <c r="H661" t="n">
         <v>2163727</v>
@@ -19625,7 +19625,7 @@
         <v>3.58899998664856</v>
       </c>
       <c r="G664" t="n">
-        <v>2.86526370048523</v>
+        <v>2.86526346206665</v>
       </c>
       <c r="H664" t="n">
         <v>5340228</v>
@@ -19712,7 +19712,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>2.95388007164001</v>
+        <v>2.95387983322144</v>
       </c>
       <c r="H667" t="n">
         <v>3682124</v>
@@ -19770,7 +19770,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G669" t="n">
-        <v>3.30116033554077</v>
+        <v>3.30116057395935</v>
       </c>
       <c r="H669" t="n">
         <v>6165273</v>
@@ -19799,7 +19799,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>3.21733427047729</v>
+        <v>3.21733403205872</v>
       </c>
       <c r="H670" t="n">
         <v>9621540</v>
@@ -19828,7 +19828,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G671" t="n">
-        <v>3.21094679832458</v>
+        <v>3.21094727516174</v>
       </c>
       <c r="H671" t="n">
         <v>2761689</v>
@@ -19857,7 +19857,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G672" t="n">
-        <v>3.25565457344055</v>
+        <v>3.25565481185913</v>
       </c>
       <c r="H672" t="n">
         <v>3468706</v>
@@ -19915,7 +19915,7 @@
         <v>4.20699977874756</v>
       </c>
       <c r="G674" t="n">
-        <v>3.3586413860321</v>
+        <v>3.35864114761353</v>
       </c>
       <c r="H674" t="n">
         <v>3781899</v>
@@ -19944,7 +19944,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G675" t="n">
-        <v>3.53986549377441</v>
+        <v>3.53986573219299</v>
       </c>
       <c r="H675" t="n">
         <v>5982928</v>
@@ -20002,7 +20002,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G677" t="n">
-        <v>3.38498592376709</v>
+        <v>3.38498640060425</v>
       </c>
       <c r="H677" t="n">
         <v>3819140</v>
@@ -20089,7 +20089,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G680" t="n">
-        <v>3.11354923248291</v>
+        <v>3.11354947090149</v>
       </c>
       <c r="H680" t="n">
         <v>3936480</v>
@@ -20176,7 +20176,7 @@
         <v>4</v>
       </c>
       <c r="G683" t="n">
-        <v>3.19338345527649</v>
+        <v>3.19338369369507</v>
       </c>
       <c r="H683" t="n">
         <v>2791331</v>
@@ -20263,7 +20263,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.11354923248291</v>
+        <v>3.11354947090149</v>
       </c>
       <c r="H686" t="n">
         <v>2395917</v>
@@ -20292,7 +20292,7 @@
         <v>4.01100015640259</v>
       </c>
       <c r="G687" t="n">
-        <v>3.20216536521912</v>
+        <v>3.20216584205627</v>
       </c>
       <c r="H687" t="n">
         <v>3725678</v>
@@ -20350,7 +20350,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G689" t="n">
-        <v>3.04808497428894</v>
+        <v>3.04808473587036</v>
       </c>
       <c r="H689" t="n">
         <v>2951291</v>
@@ -20495,7 +20495,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G694" t="n">
-        <v>3.05447125434875</v>
+        <v>3.05447149276733</v>
       </c>
       <c r="H694" t="n">
         <v>4711399</v>
@@ -20582,7 +20582,7 @@
         <v>3.78099989891052</v>
       </c>
       <c r="G697" t="n">
-        <v>3.01854586601257</v>
+        <v>3.01854562759399</v>
       </c>
       <c r="H697" t="n">
         <v>1681574</v>
@@ -20640,7 +20640,7 @@
         <v>3.64100003242493</v>
       </c>
       <c r="G699" t="n">
-        <v>2.90677762031555</v>
+        <v>2.90677738189697</v>
       </c>
       <c r="H699" t="n">
         <v>2147732</v>
@@ -20669,7 +20669,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G700" t="n">
-        <v>2.96585488319397</v>
+        <v>2.96585464477539</v>
       </c>
       <c r="H700" t="n">
         <v>3333759</v>
@@ -20727,7 +20727,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G702" t="n">
-        <v>2.96026635169983</v>
+        <v>2.96026682853699</v>
       </c>
       <c r="H702" t="n">
         <v>2786641</v>
@@ -20901,7 +20901,7 @@
         <v>3.76699995994568</v>
       </c>
       <c r="G708" t="n">
-        <v>3.00736880302429</v>
+        <v>3.00736904144287</v>
       </c>
       <c r="H708" t="n">
         <v>2567828</v>
@@ -20930,7 +20930,7 @@
         <v>3.78099989891052</v>
       </c>
       <c r="G709" t="n">
-        <v>3.01854586601257</v>
+        <v>3.01854562759399</v>
       </c>
       <c r="H709" t="n">
         <v>2822705</v>
@@ -20988,7 +20988,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G711" t="n">
-        <v>2.90997076034546</v>
+        <v>2.90997099876404</v>
       </c>
       <c r="H711" t="n">
         <v>2116166</v>
@@ -21046,7 +21046,7 @@
         <v>3.58899998664856</v>
       </c>
       <c r="G713" t="n">
-        <v>2.86526370048523</v>
+        <v>2.86526346206665</v>
       </c>
       <c r="H713" t="n">
         <v>2594843</v>
@@ -21104,7 +21104,7 @@
         <v>3.36299991607666</v>
       </c>
       <c r="G715" t="n">
-        <v>2.68483734130859</v>
+        <v>2.68483710289001</v>
       </c>
       <c r="H715" t="n">
         <v>2932370</v>
@@ -21191,7 +21191,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G718" t="n">
-        <v>2.94908976554871</v>
+        <v>2.94909000396729</v>
       </c>
       <c r="H718" t="n">
         <v>2816589</v>
@@ -21220,7 +21220,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G719" t="n">
-        <v>2.80858087539673</v>
+        <v>2.80858063697815</v>
       </c>
       <c r="H719" t="n">
         <v>8851149</v>
@@ -21249,7 +21249,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G720" t="n">
-        <v>2.71118259429932</v>
+        <v>2.71118235588074</v>
       </c>
       <c r="H720" t="n">
         <v>4221054</v>
@@ -21336,7 +21336,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G723" t="n">
-        <v>2.996990442276</v>
+        <v>2.99699068069458</v>
       </c>
       <c r="H723" t="n">
         <v>2769659</v>
@@ -21394,7 +21394,7 @@
         <v>3.71900010108948</v>
       </c>
       <c r="G725" t="n">
-        <v>2.96904873847961</v>
+        <v>2.96904850006104</v>
       </c>
       <c r="H725" t="n">
         <v>1180559</v>
@@ -21423,7 +21423,7 @@
         <v>3.71900010108948</v>
       </c>
       <c r="G726" t="n">
-        <v>2.96904873847961</v>
+        <v>2.96904850006104</v>
       </c>
       <c r="H726" t="n">
         <v>1136621</v>
@@ -21481,7 +21481,7 @@
         <v>3.73300004005432</v>
       </c>
       <c r="G728" t="n">
-        <v>2.98022556304932</v>
+        <v>2.98022532463074</v>
       </c>
       <c r="H728" t="n">
         <v>1181940</v>
@@ -21510,7 +21510,7 @@
         <v>3.6470000743866</v>
       </c>
       <c r="G729" t="n">
-        <v>2.9115674495697</v>
+        <v>2.91156768798828</v>
       </c>
       <c r="H729" t="n">
         <v>1509920</v>
@@ -21568,7 +21568,7 @@
         <v>3.69899988174438</v>
       </c>
       <c r="G731" t="n">
-        <v>2.9530816078186</v>
+        <v>2.95308136940002</v>
       </c>
       <c r="H731" t="n">
         <v>1412914</v>
@@ -21597,7 +21597,7 @@
         <v>3.66100001335144</v>
       </c>
       <c r="G732" t="n">
-        <v>2.92274451255798</v>
+        <v>2.9227442741394</v>
       </c>
       <c r="H732" t="n">
         <v>1451808</v>
@@ -21684,7 +21684,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G735" t="n">
-        <v>2.9075756072998</v>
+        <v>2.90757584571838</v>
       </c>
       <c r="H735" t="n">
         <v>1203332</v>
@@ -21771,7 +21771,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G738" t="n">
-        <v>2.87085199356079</v>
+        <v>2.87085175514221</v>
       </c>
       <c r="H738" t="n">
         <v>2247121</v>
@@ -21916,7 +21916,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G743" t="n">
-        <v>3.0752284526825</v>
+        <v>3.07522821426392</v>
       </c>
       <c r="H743" t="n">
         <v>2215232</v>
@@ -21945,7 +21945,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G744" t="n">
-        <v>3.11354923248291</v>
+        <v>3.11354947090149</v>
       </c>
       <c r="H744" t="n">
         <v>4111384</v>
@@ -21974,7 +21974,7 @@
         <v>3.88100004196167</v>
       </c>
       <c r="G745" t="n">
-        <v>3.09838032722473</v>
+        <v>3.09838056564331</v>
       </c>
       <c r="H745" t="n">
         <v>2318010</v>
@@ -22003,7 +22003,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G746" t="n">
-        <v>3.08321166038513</v>
+        <v>3.08321189880371</v>
       </c>
       <c r="H746" t="n">
         <v>2806919</v>
@@ -22032,7 +22032,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G747" t="n">
-        <v>3.06165671348572</v>
+        <v>3.06165647506714</v>
       </c>
       <c r="H747" t="n">
         <v>2132412</v>
@@ -22148,7 +22148,7 @@
         <v>3.75699996948242</v>
       </c>
       <c r="G751" t="n">
-        <v>2.99938535690308</v>
+        <v>2.99938559532166</v>
       </c>
       <c r="H751" t="n">
         <v>3188876</v>
@@ -22206,7 +22206,7 @@
         <v>3.81900000572205</v>
       </c>
       <c r="G753" t="n">
-        <v>3.04888296127319</v>
+        <v>3.04888319969177</v>
       </c>
       <c r="H753" t="n">
         <v>2498213</v>
@@ -22235,7 +22235,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G754" t="n">
-        <v>2.98980522155762</v>
+        <v>2.9898054599762</v>
       </c>
       <c r="H754" t="n">
         <v>2049209</v>
@@ -22293,7 +22293,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G756" t="n">
-        <v>3.01774740219116</v>
+        <v>3.01774764060974</v>
       </c>
       <c r="H756" t="n">
         <v>3433454</v>
@@ -22322,7 +22322,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G757" t="n">
-        <v>2.97304034233093</v>
+        <v>2.97304010391235</v>
       </c>
       <c r="H757" t="n">
         <v>1792877</v>
@@ -22351,7 +22351,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G758" t="n">
-        <v>2.92354273796082</v>
+        <v>2.92354297637939</v>
       </c>
       <c r="H758" t="n">
         <v>2329517</v>
@@ -22525,7 +22525,7 @@
         <v>3.9909999370575</v>
       </c>
       <c r="G764" t="n">
-        <v>3.18619823455811</v>
+        <v>3.18619847297668</v>
       </c>
       <c r="H764" t="n">
         <v>8427170</v>
@@ -22583,7 +22583,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G766" t="n">
-        <v>3.11674213409424</v>
+        <v>3.11674237251282</v>
       </c>
       <c r="H766" t="n">
         <v>4213016</v>
@@ -22757,7 +22757,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G772" t="n">
-        <v>3.06964039802551</v>
+        <v>3.06963992118835</v>
       </c>
       <c r="H772" t="n">
         <v>4101570</v>
@@ -22786,7 +22786,7 @@
         <v>3.68899989128113</v>
       </c>
       <c r="G773" t="n">
-        <v>2.94509792327881</v>
+        <v>2.94509768486023</v>
       </c>
       <c r="H773" t="n">
         <v>3433440</v>
@@ -22815,7 +22815,7 @@
         <v>3.78299999237061</v>
       </c>
       <c r="G774" t="n">
-        <v>3.02014255523682</v>
+        <v>3.02014231681824</v>
       </c>
       <c r="H774" t="n">
         <v>3457710</v>
@@ -22844,7 +22844,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G775" t="n">
-        <v>3.28120183944702</v>
+        <v>3.2812020778656</v>
       </c>
       <c r="H775" t="n">
         <v>13906345</v>
@@ -23018,7 +23018,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G781" t="n">
-        <v>2.91396260261536</v>
+        <v>2.91396284103394</v>
       </c>
       <c r="H781" t="n">
         <v>2954324</v>
@@ -23105,7 +23105,7 @@
         <v>3.71900010108948</v>
       </c>
       <c r="G784" t="n">
-        <v>2.96904873847961</v>
+        <v>2.96904850006104</v>
       </c>
       <c r="H784" t="n">
         <v>6586083</v>
@@ -23134,7 +23134,7 @@
         <v>3.69099998474121</v>
       </c>
       <c r="G785" t="n">
-        <v>2.94669485092163</v>
+        <v>2.94669461250305</v>
       </c>
       <c r="H785" t="n">
         <v>4668244</v>
@@ -23192,7 +23192,7 @@
         <v>4.23299980163574</v>
       </c>
       <c r="G787" t="n">
-        <v>3.37939834594727</v>
+        <v>3.37939810752869</v>
       </c>
       <c r="H787" t="n">
         <v>6292817</v>
@@ -23221,7 +23221,7 @@
         <v>4.27899980545044</v>
       </c>
       <c r="G788" t="n">
-        <v>3.4161217212677</v>
+        <v>3.41612219810486</v>
       </c>
       <c r="H788" t="n">
         <v>5193817</v>
@@ -23250,7 +23250,7 @@
         <v>4</v>
       </c>
       <c r="G789" t="n">
-        <v>3.19338345527649</v>
+        <v>3.19338369369507</v>
       </c>
       <c r="H789" t="n">
         <v>10622676</v>
@@ -23337,7 +23337,7 @@
         <v>4.26300001144409</v>
       </c>
       <c r="G792" t="n">
-        <v>3.40334844589233</v>
+        <v>3.40334868431091</v>
       </c>
       <c r="H792" t="n">
         <v>3038372</v>
@@ -23366,7 +23366,7 @@
         <v>4.28700017929077</v>
       </c>
       <c r="G793" t="n">
-        <v>3.42250943183899</v>
+        <v>3.42250919342041</v>
       </c>
       <c r="H793" t="n">
         <v>4231809</v>
@@ -23395,7 +23395,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G794" t="n">
-        <v>3.34666609764099</v>
+        <v>3.34666585922241</v>
       </c>
       <c r="H794" t="n">
         <v>4331361</v>
@@ -23453,7 +23453,7 @@
         <v>4.1560001373291</v>
       </c>
       <c r="G796" t="n">
-        <v>3.31792545318604</v>
+        <v>3.31792593002319</v>
       </c>
       <c r="H796" t="n">
         <v>3693940</v>
@@ -23482,7 +23482,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G797" t="n">
-        <v>3.40734028816223</v>
+        <v>3.40734004974365</v>
       </c>
       <c r="H797" t="n">
         <v>4608848</v>
@@ -23511,7 +23511,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G798" t="n">
-        <v>3.45843458175659</v>
+        <v>3.45843410491943</v>
       </c>
       <c r="H798" t="n">
         <v>4749283</v>
@@ -23540,7 +23540,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G799" t="n">
-        <v>3.54146242141724</v>
+        <v>3.54146218299866</v>
       </c>
       <c r="H799" t="n">
         <v>4839665</v>
@@ -23569,7 +23569,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G800" t="n">
-        <v>3.46881246566772</v>
+        <v>3.4688127040863</v>
       </c>
       <c r="H800" t="n">
         <v>8062494</v>
@@ -23656,7 +23656,7 @@
         <v>4.38100004196167</v>
       </c>
       <c r="G803" t="n">
-        <v>3.49755334854126</v>
+        <v>3.49755358695984</v>
       </c>
       <c r="H803" t="n">
         <v>3568279</v>
@@ -23685,7 +23685,7 @@
         <v>4.42199993133545</v>
       </c>
       <c r="G804" t="n">
-        <v>3.53028535842896</v>
+        <v>3.53028559684753</v>
       </c>
       <c r="H804" t="n">
         <v>2373246</v>
@@ -23714,7 +23714,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G805" t="n">
-        <v>3.60213661193848</v>
+        <v>3.60213685035706</v>
       </c>
       <c r="H805" t="n">
         <v>3144898</v>
@@ -23743,7 +23743,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>3.55663108825684</v>
+        <v>3.55663084983826</v>
       </c>
       <c r="H806" t="n">
         <v>2012341</v>
@@ -23772,7 +23772,7 @@
         <v>4.45900011062622</v>
       </c>
       <c r="G807" t="n">
-        <v>3.55982422828674</v>
+        <v>3.5598247051239</v>
       </c>
       <c r="H807" t="n">
         <v>1453180</v>
@@ -23830,7 +23830,7 @@
         <v>4.39699983596802</v>
       </c>
       <c r="G809" t="n">
-        <v>3.51032710075378</v>
+        <v>3.51032686233521</v>
       </c>
       <c r="H809" t="n">
         <v>4785540</v>
@@ -23888,7 +23888,7 @@
         <v>4.48899984359741</v>
       </c>
       <c r="G811" t="n">
-        <v>3.58377432823181</v>
+        <v>3.58377480506897</v>
       </c>
       <c r="H811" t="n">
         <v>3097950</v>
@@ -23917,7 +23917,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G812" t="n">
-        <v>3.51272177696228</v>
+        <v>3.51272201538086</v>
       </c>
       <c r="H812" t="n">
         <v>7525445</v>
@@ -23975,7 +23975,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G814" t="n">
-        <v>3.73945283889771</v>
+        <v>3.73945212364197</v>
       </c>
       <c r="H814" t="n">
         <v>8208133</v>
@@ -24062,7 +24062,7 @@
         <v>4.35099983215332</v>
       </c>
       <c r="G817" t="n">
-        <v>3.47360348701477</v>
+        <v>3.47360277175903</v>
       </c>
       <c r="H817" t="n">
         <v>2573619</v>
@@ -24120,7 +24120,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G819" t="n">
-        <v>3.60453176498413</v>
+        <v>3.60453128814697</v>
       </c>
       <c r="H819" t="n">
         <v>4056509</v>
@@ -24149,7 +24149,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>3.56062316894531</v>
+        <v>3.56062245368958</v>
       </c>
       <c r="H820" t="n">
         <v>1970058</v>
@@ -24178,7 +24178,7 @@
         <v>4.43300008773804</v>
       </c>
       <c r="G821" t="n">
-        <v>3.53906726837158</v>
+        <v>3.53906750679016</v>
       </c>
       <c r="H821" t="n">
         <v>1238847</v>
@@ -24265,7 +24265,7 @@
         <v>4.29300022125244</v>
       </c>
       <c r="G824" t="n">
-        <v>3.42729926109314</v>
+        <v>3.42729902267456</v>
       </c>
       <c r="H824" t="n">
         <v>4293764</v>
@@ -24294,7 +24294,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>3.54465627670288</v>
+        <v>3.54465579986572</v>
       </c>
       <c r="H825" t="n">
         <v>4749576</v>
@@ -24323,7 +24323,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G826" t="n">
-        <v>3.54944610595703</v>
+        <v>3.54944586753845</v>
       </c>
       <c r="H826" t="n">
         <v>4809149</v>
@@ -24381,7 +24381,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G828" t="n">
-        <v>3.62129640579224</v>
+        <v>3.62129688262939</v>
       </c>
       <c r="H828" t="n">
         <v>4573879</v>
@@ -24439,7 +24439,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G830" t="n">
-        <v>3.54465627670288</v>
+        <v>3.54465579986572</v>
       </c>
       <c r="H830" t="n">
         <v>2051814</v>
@@ -24468,7 +24468,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G831" t="n">
-        <v>3.46322464942932</v>
+        <v>3.46322441101074</v>
       </c>
       <c r="H831" t="n">
         <v>2158544</v>
@@ -24497,7 +24497,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G832" t="n">
-        <v>3.53667259216309</v>
+        <v>3.53667235374451</v>
       </c>
       <c r="H832" t="n">
         <v>2577762</v>
@@ -24584,7 +24584,7 @@
         <v>4.43100023269653</v>
       </c>
       <c r="G835" t="n">
-        <v>3.5374710559845</v>
+        <v>3.53747081756592</v>
       </c>
       <c r="H835" t="n">
         <v>2675578</v>
@@ -24613,7 +24613,7 @@
         <v>4.29099988937378</v>
       </c>
       <c r="G836" t="n">
-        <v>3.4257025718689</v>
+        <v>3.42570209503174</v>
       </c>
       <c r="H836" t="n">
         <v>3192309</v>
@@ -24642,7 +24642,7 @@
         <v>4.19399976730347</v>
       </c>
       <c r="G837" t="n">
-        <v>3.34826254844666</v>
+        <v>3.34826278686523</v>
       </c>
       <c r="H837" t="n">
         <v>3446031</v>
@@ -24671,7 +24671,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G838" t="n">
-        <v>3.44885420799255</v>
+        <v>3.44885396957397</v>
       </c>
       <c r="H838" t="n">
         <v>2820049</v>
@@ -24729,7 +24729,7 @@
         <v>4.27899980545044</v>
       </c>
       <c r="G840" t="n">
-        <v>3.4161217212677</v>
+        <v>3.41612219810486</v>
       </c>
       <c r="H840" t="n">
         <v>4085081</v>
@@ -24787,7 +24787,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G842" t="n">
-        <v>3.41692042350769</v>
+        <v>3.41692090034485</v>
       </c>
       <c r="H842" t="n">
         <v>3962212</v>
@@ -24816,7 +24816,7 @@
         <v>4.3730001449585</v>
       </c>
       <c r="G843" t="n">
-        <v>3.49116683006287</v>
+        <v>3.49116706848145</v>
       </c>
       <c r="H843" t="n">
         <v>3072358</v>
@@ -24874,7 +24874,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G845" t="n">
-        <v>3.72029209136963</v>
+        <v>3.72029137611389</v>
       </c>
       <c r="H845" t="n">
         <v>8839185</v>
@@ -24932,7 +24932,7 @@
         <v>4.72300004959106</v>
       </c>
       <c r="G847" t="n">
-        <v>3.770587682724</v>
+        <v>3.77058744430542</v>
       </c>
       <c r="H847" t="n">
         <v>3796397</v>
@@ -24961,7 +24961,7 @@
         <v>4.69299983978271</v>
       </c>
       <c r="G848" t="n">
-        <v>3.74663686752319</v>
+        <v>3.74663710594177</v>
       </c>
       <c r="H848" t="n">
         <v>4481975</v>
@@ -25019,7 +25019,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G850" t="n">
-        <v>3.73226761817932</v>
+        <v>3.73226714134216</v>
       </c>
       <c r="H850" t="n">
         <v>1985783</v>
@@ -25048,7 +25048,7 @@
         <v>4.68100023269653</v>
       </c>
       <c r="G851" t="n">
-        <v>3.73705720901489</v>
+        <v>3.73705744743347</v>
       </c>
       <c r="H851" t="n">
         <v>1646366</v>
@@ -25077,7 +25077,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>3.78815078735352</v>
+        <v>3.78815150260925</v>
       </c>
       <c r="H852" t="n">
         <v>2450719</v>
@@ -25135,7 +25135,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G854" t="n">
-        <v>3.68995428085327</v>
+        <v>3.68995499610901</v>
       </c>
       <c r="H854" t="n">
         <v>3076913</v>
@@ -25164,7 +25164,7 @@
         <v>4.60099983215332</v>
       </c>
       <c r="G855" t="n">
-        <v>3.67318940162659</v>
+        <v>3.67318964004517</v>
       </c>
       <c r="H855" t="n">
         <v>1427684</v>
@@ -25193,7 +25193,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>3.75861239433289</v>
+        <v>3.75861287117004</v>
       </c>
       <c r="H856" t="n">
         <v>1816097</v>
@@ -25222,7 +25222,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>3.90790295600891</v>
+        <v>3.90790367126465</v>
       </c>
       <c r="H857" t="n">
         <v>4999525</v>
@@ -25251,7 +25251,7 @@
         <v>4.77099990844727</v>
       </c>
       <c r="G858" t="n">
-        <v>3.80890798568726</v>
+        <v>3.80890822410583</v>
       </c>
       <c r="H858" t="n">
         <v>3010730</v>
@@ -25280,7 +25280,7 @@
         <v>4.81400012969971</v>
       </c>
       <c r="G859" t="n">
-        <v>3.84323740005493</v>
+        <v>3.84323692321777</v>
       </c>
       <c r="H859" t="n">
         <v>3514103</v>
@@ -25309,7 +25309,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G860" t="n">
-        <v>3.8160936832428</v>
+        <v>3.81609392166138</v>
       </c>
       <c r="H860" t="n">
         <v>2057831</v>
@@ -25338,7 +25338,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G861" t="n">
-        <v>3.81210160255432</v>
+        <v>3.8121018409729</v>
       </c>
       <c r="H861" t="n">
         <v>2749850</v>
@@ -25396,7 +25396,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G863" t="n">
-        <v>3.86080050468445</v>
+        <v>3.86080074310303</v>
       </c>
       <c r="H863" t="n">
         <v>2711307</v>
@@ -25425,7 +25425,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G864" t="n">
-        <v>3.89592790603638</v>
+        <v>3.89592814445496</v>
       </c>
       <c r="H864" t="n">
         <v>2497242</v>
@@ -25483,7 +25483,7 @@
         <v>4.75</v>
       </c>
       <c r="G866" t="n">
-        <v>3.79214286804199</v>
+        <v>3.79214262962341</v>
       </c>
       <c r="H866" t="n">
         <v>2152373</v>
@@ -25541,7 +25541,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G868" t="n">
-        <v>3.95340919494629</v>
+        <v>3.95340895652771</v>
       </c>
       <c r="H868" t="n">
         <v>3882618</v>
@@ -25570,7 +25570,7 @@
         <v>4.94899988174438</v>
       </c>
       <c r="G869" t="n">
-        <v>3.95101356506348</v>
+        <v>3.95101380348206</v>
       </c>
       <c r="H869" t="n">
         <v>2692109</v>
@@ -25628,7 +25628,7 @@
         <v>4.90299987792969</v>
       </c>
       <c r="G871" t="n">
-        <v>3.91428995132446</v>
+        <v>3.9142894744873</v>
       </c>
       <c r="H871" t="n">
         <v>2979867</v>
@@ -25657,7 +25657,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G872" t="n">
-        <v>3.96378803253174</v>
+        <v>3.96378755569458</v>
       </c>
       <c r="H872" t="n">
         <v>3998285</v>
@@ -25686,7 +25686,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G873" t="n">
-        <v>3.91269373893738</v>
+        <v>3.91269302368164</v>
       </c>
       <c r="H873" t="n">
         <v>2975747</v>
@@ -25715,7 +25715,7 @@
         <v>5</v>
       </c>
       <c r="G874" t="n">
-        <v>3.99172949790955</v>
+        <v>3.99172902107239</v>
       </c>
       <c r="H874" t="n">
         <v>3316196</v>
@@ -25773,7 +25773,7 @@
         <v>5.0939998626709</v>
       </c>
       <c r="G876" t="n">
-        <v>4.06677341461182</v>
+        <v>4.06677389144897</v>
       </c>
       <c r="H876" t="n">
         <v>3117812</v>
@@ -25802,7 +25802,7 @@
         <v>4.97700023651123</v>
       </c>
       <c r="G877" t="n">
-        <v>3.97336792945862</v>
+        <v>3.97336745262146</v>
       </c>
       <c r="H877" t="n">
         <v>2915800</v>
@@ -25860,7 +25860,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G879" t="n">
-        <v>3.94622373580933</v>
+        <v>3.94622397422791</v>
       </c>
       <c r="H879" t="n">
         <v>1729053</v>
@@ -25918,7 +25918,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G881" t="n">
-        <v>3.9677791595459</v>
+        <v>3.96777892112732</v>
       </c>
       <c r="H881" t="n">
         <v>1672411</v>
@@ -25947,7 +25947,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G882" t="n">
-        <v>4.00769662857056</v>
+        <v>4.00769710540771</v>
       </c>
       <c r="H882" t="n">
         <v>1377373</v>
@@ -25976,7 +25976,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G883" t="n">
-        <v>4.14022207260132</v>
+        <v>4.14022159576416</v>
       </c>
       <c r="H883" t="n">
         <v>5129041</v>
@@ -26005,7 +26005,7 @@
         <v>5.0019998550415</v>
       </c>
       <c r="G884" t="n">
-        <v>3.99332594871521</v>
+        <v>3.99332642555237</v>
       </c>
       <c r="H884" t="n">
         <v>8991183</v>
@@ -26034,7 +26034,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G885" t="n">
-        <v>3.98693919181824</v>
+        <v>3.98693943023682</v>
       </c>
       <c r="H885" t="n">
         <v>7344136</v>
@@ -26063,7 +26063,7 @@
         <v>5.02799987792969</v>
       </c>
       <c r="G886" t="n">
-        <v>4.01408290863037</v>
+        <v>4.01408243179321</v>
       </c>
       <c r="H886" t="n">
         <v>3542178</v>
@@ -26092,7 +26092,7 @@
         <v>5.05200004577637</v>
       </c>
       <c r="G887" t="n">
-        <v>4.03324365615845</v>
+        <v>4.03324317932129</v>
       </c>
       <c r="H887" t="n">
         <v>1906884</v>
@@ -26121,7 +26121,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G888" t="n">
-        <v>3.99013304710388</v>
+        <v>3.9901328086853</v>
       </c>
       <c r="H888" t="n">
         <v>2928960</v>
@@ -26150,7 +26150,7 @@
         <v>4.9060001373291</v>
       </c>
       <c r="G889" t="n">
-        <v>3.91668510437012</v>
+        <v>3.91668462753296</v>
       </c>
       <c r="H889" t="n">
         <v>3235553</v>
@@ -26179,7 +26179,7 @@
         <v>4.94399976730347</v>
       </c>
       <c r="G890" t="n">
-        <v>3.94702196121216</v>
+        <v>3.94702219963074</v>
       </c>
       <c r="H890" t="n">
         <v>1804736</v>
@@ -26208,7 +26208,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G891" t="n">
-        <v>3.92786169052124</v>
+        <v>3.92786192893982</v>
       </c>
       <c r="H891" t="n">
         <v>1315006</v>
@@ -26237,7 +26237,7 @@
         <v>4.9210000038147</v>
       </c>
       <c r="G892" t="n">
-        <v>3.92866039276123</v>
+        <v>3.92866015434265</v>
       </c>
       <c r="H892" t="n">
         <v>1270074</v>
@@ -26266,7 +26266,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G893" t="n">
-        <v>3.92626571655273</v>
+        <v>3.92626547813416</v>
       </c>
       <c r="H893" t="n">
         <v>1526999</v>
@@ -26295,7 +26295,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G894" t="n">
-        <v>3.99971318244934</v>
+        <v>3.99971270561218</v>
       </c>
       <c r="H894" t="n">
         <v>4210348</v>
@@ -26324,7 +26324,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G895" t="n">
-        <v>3.95740079879761</v>
+        <v>3.95740032196045</v>
       </c>
       <c r="H895" t="n">
         <v>1966290</v>
@@ -26382,7 +26382,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G897" t="n">
-        <v>3.91269373893738</v>
+        <v>3.91269302368164</v>
       </c>
       <c r="H897" t="n">
         <v>2075739</v>
@@ -26411,7 +26411,7 @@
         <v>4.96299982070923</v>
       </c>
       <c r="G898" t="n">
-        <v>3.96219110488892</v>
+        <v>3.96219062805176</v>
       </c>
       <c r="H898" t="n">
         <v>2780569</v>
@@ -26440,7 +26440,7 @@
         <v>5.0019998550415</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99332594871521</v>
+        <v>3.99332642555237</v>
       </c>
       <c r="H899" t="n">
         <v>2294402</v>
@@ -26469,7 +26469,7 @@
         <v>5.02600002288818</v>
       </c>
       <c r="G900" t="n">
-        <v>4.01248598098755</v>
+        <v>4.01248645782471</v>
       </c>
       <c r="H900" t="n">
         <v>2165187</v>
@@ -26498,7 +26498,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G901" t="n">
-        <v>3.94542551040649</v>
+        <v>3.94542527198792</v>
       </c>
       <c r="H901" t="n">
         <v>4957834</v>
@@ -26527,7 +26527,7 @@
         <v>4.79699993133545</v>
       </c>
       <c r="G902" t="n">
-        <v>3.82966470718384</v>
+        <v>3.82966542243958</v>
       </c>
       <c r="H902" t="n">
         <v>5237550</v>
@@ -26556,7 +26556,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G903" t="n">
-        <v>3.7570161819458</v>
+        <v>3.75701522827148</v>
       </c>
       <c r="H903" t="n">
         <v>5125936</v>
@@ -26585,7 +26585,7 @@
         <v>4.67700004577637</v>
       </c>
       <c r="G904" t="n">
-        <v>3.73386406898499</v>
+        <v>3.73386359214783</v>
       </c>
       <c r="H904" t="n">
         <v>2835308</v>
@@ -26614,7 +26614,7 @@
         <v>4.73299980163574</v>
       </c>
       <c r="G905" t="n">
-        <v>3.77857112884521</v>
+        <v>3.77857041358948</v>
       </c>
       <c r="H905" t="n">
         <v>2260456</v>
@@ -26672,7 +26672,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G907" t="n">
-        <v>3.68436646461487</v>
+        <v>3.68436598777771</v>
       </c>
       <c r="H907" t="n">
         <v>4336143</v>
@@ -26701,7 +26701,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G908" t="n">
-        <v>3.69155144691467</v>
+        <v>3.69155168533325</v>
       </c>
       <c r="H908" t="n">
         <v>4131045</v>
@@ -26730,7 +26730,7 @@
         <v>4.66099977493286</v>
       </c>
       <c r="G909" t="n">
-        <v>3.72109007835388</v>
+        <v>3.7210898399353</v>
       </c>
       <c r="H909" t="n">
         <v>2888364</v>
@@ -26788,7 +26788,7 @@
         <v>4.58099985122681</v>
       </c>
       <c r="G911" t="n">
-        <v>3.65722250938416</v>
+        <v>3.65722227096558</v>
       </c>
       <c r="H911" t="n">
         <v>3464484</v>
@@ -26846,7 +26846,7 @@
         <v>4.71299982070923</v>
       </c>
       <c r="G913" t="n">
-        <v>3.7626039981842</v>
+        <v>3.76260423660278</v>
       </c>
       <c r="H913" t="n">
         <v>5449345</v>
@@ -26875,7 +26875,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G914" t="n">
-        <v>3.73945283889771</v>
+        <v>3.73945212364197</v>
       </c>
       <c r="H914" t="n">
         <v>3729259</v>
@@ -26904,7 +26904,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G915" t="n">
-        <v>3.75222587585449</v>
+        <v>3.75222563743591</v>
       </c>
       <c r="H915" t="n">
         <v>1728510</v>
@@ -26933,7 +26933,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G916" t="n">
-        <v>3.79533672332764</v>
+        <v>3.79533624649048</v>
       </c>
       <c r="H916" t="n">
         <v>2356522</v>
@@ -26962,7 +26962,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>3.72029209136963</v>
+        <v>3.72029137611389</v>
       </c>
       <c r="H917" t="n">
         <v>3313504</v>
@@ -26991,7 +26991,7 @@
         <v>4.67700004577637</v>
       </c>
       <c r="G918" t="n">
-        <v>3.73386406898499</v>
+        <v>3.73386359214783</v>
       </c>
       <c r="H918" t="n">
         <v>2074454</v>
@@ -27020,7 +27020,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G919" t="n">
-        <v>3.74823427200317</v>
+        <v>3.74823451042175</v>
       </c>
       <c r="H919" t="n">
         <v>2245847</v>
@@ -27049,7 +27049,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G920" t="n">
-        <v>3.76499962806702</v>
+        <v>3.76499938964844</v>
       </c>
       <c r="H920" t="n">
         <v>964384</v>
@@ -27078,7 +27078,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G921" t="n">
-        <v>3.79054689407349</v>
+        <v>3.79054665565491</v>
       </c>
       <c r="H921" t="n">
         <v>2892437</v>
@@ -27107,7 +27107,7 @@
         <v>4.72900009155273</v>
       </c>
       <c r="G922" t="n">
-        <v>3.77537798881531</v>
+        <v>3.77537775039673</v>
       </c>
       <c r="H922" t="n">
         <v>2553622</v>
@@ -27194,7 +27194,7 @@
         <v>4.85699987411499</v>
       </c>
       <c r="G925" t="n">
-        <v>3.87756562232971</v>
+        <v>3.87756609916687</v>
       </c>
       <c r="H925" t="n">
         <v>1032853</v>
@@ -27223,7 +27223,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G926" t="n">
-        <v>3.93185329437256</v>
+        <v>3.9318540096283</v>
       </c>
       <c r="H926" t="n">
         <v>2913802</v>
@@ -27252,7 +27252,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G927" t="n">
-        <v>3.97097229957581</v>
+        <v>3.97097277641296</v>
       </c>
       <c r="H927" t="n">
         <v>2943156</v>
@@ -27281,7 +27281,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G928" t="n">
-        <v>4.06517696380615</v>
+        <v>4.06517744064331</v>
       </c>
       <c r="H928" t="n">
         <v>5038431</v>
@@ -27426,7 +27426,7 @@
         <v>5.16200017929077</v>
       </c>
       <c r="G933" t="n">
-        <v>4.1210618019104</v>
+        <v>4.12106132507324</v>
       </c>
       <c r="H933" t="n">
         <v>2361572</v>
@@ -27455,7 +27455,7 @@
         <v>5.16200017929077</v>
       </c>
       <c r="G934" t="n">
-        <v>4.1210618019104</v>
+        <v>4.12106132507324</v>
       </c>
       <c r="H934" t="n">
         <v>1419462</v>
@@ -27484,7 +27484,7 @@
         <v>5.12200021743774</v>
       </c>
       <c r="G935" t="n">
-        <v>4.08912801742554</v>
+        <v>4.08912754058838</v>
       </c>
       <c r="H935" t="n">
         <v>1858836</v>
@@ -27542,7 +27542,7 @@
         <v>5.16599988937378</v>
       </c>
       <c r="G937" t="n">
-        <v>4.12425470352173</v>
+        <v>4.12425518035889</v>
       </c>
       <c r="H937" t="n">
         <v>1132810</v>
@@ -27571,7 +27571,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>4.12744808197021</v>
+        <v>4.12744855880737</v>
       </c>
       <c r="H938" t="n">
         <v>2099142</v>
@@ -27600,7 +27600,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>4.02366304397583</v>
+        <v>4.02366352081299</v>
       </c>
       <c r="H939" t="n">
         <v>3026829</v>
@@ -27658,7 +27658,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G941" t="n">
-        <v>4.13399028778076</v>
+        <v>4.1339898109436</v>
       </c>
       <c r="H941" t="n">
         <v>1763484</v>
@@ -27687,7 +27687,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G942" t="n">
-        <v>4.0755820274353</v>
+        <v>4.07558107376099</v>
       </c>
       <c r="H942" t="n">
         <v>1599756</v>
@@ -27803,7 +27803,7 @@
         <v>4.98299980163574</v>
       </c>
       <c r="G946" t="n">
-        <v>4.04232120513916</v>
+        <v>4.04232168197632</v>
       </c>
       <c r="H946" t="n">
         <v>1307809</v>
@@ -27832,7 +27832,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G947" t="n">
-        <v>3.97174525260925</v>
+        <v>3.97174477577209</v>
       </c>
       <c r="H947" t="n">
         <v>2427802</v>
@@ -27861,7 +27861,7 @@
         <v>4.9229998588562</v>
       </c>
       <c r="G948" t="n">
-        <v>3.99364852905273</v>
+        <v>3.99364805221558</v>
       </c>
       <c r="H948" t="n">
         <v>1782081</v>
@@ -27890,7 +27890,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G949" t="n">
-        <v>4.00338315963745</v>
+        <v>4.00338268280029</v>
       </c>
       <c r="H949" t="n">
         <v>2677698</v>
@@ -27977,7 +27977,7 @@
         <v>4.99200010299683</v>
       </c>
       <c r="G952" t="n">
-        <v>4.04962253570557</v>
+        <v>4.04962205886841</v>
       </c>
       <c r="H952" t="n">
         <v>1481995</v>
@@ -28006,7 +28006,7 @@
         <v>4.86899995803833</v>
       </c>
       <c r="G953" t="n">
-        <v>3.94984197616577</v>
+        <v>3.94984245300293</v>
       </c>
       <c r="H953" t="n">
         <v>3232585</v>
@@ -28035,7 +28035,7 @@
         <v>4.97200012207031</v>
       </c>
       <c r="G954" t="n">
-        <v>4.03339862823486</v>
+        <v>4.03339815139771</v>
       </c>
       <c r="H954" t="n">
         <v>1838472</v>
@@ -28064,7 +28064,7 @@
         <v>4.93100023269653</v>
       </c>
       <c r="G955" t="n">
-        <v>4.00013828277588</v>
+        <v>4.00013780593872</v>
       </c>
       <c r="H955" t="n">
         <v>1526660</v>
@@ -28122,7 +28122,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G957" t="n">
-        <v>3.99608159065247</v>
+        <v>3.99608135223389</v>
       </c>
       <c r="H957" t="n">
         <v>925785</v>
@@ -28151,7 +28151,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G958" t="n">
-        <v>3.94254112243652</v>
+        <v>3.94254183769226</v>
       </c>
       <c r="H958" t="n">
         <v>1551769</v>
@@ -28180,7 +28180,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G959" t="n">
-        <v>3.96850037574768</v>
+        <v>3.96850061416626</v>
       </c>
       <c r="H959" t="n">
         <v>2942863</v>
@@ -28209,7 +28209,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G960" t="n">
-        <v>3.85168480873108</v>
+        <v>3.85168433189392</v>
       </c>
       <c r="H960" t="n">
         <v>4116007</v>
@@ -28238,7 +28238,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G961" t="n">
-        <v>3.91495943069458</v>
+        <v>3.91495966911316</v>
       </c>
       <c r="H961" t="n">
         <v>4637553</v>
@@ -28354,7 +28354,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G965" t="n">
-        <v>4.13399028778076</v>
+        <v>4.1339898109436</v>
       </c>
       <c r="H965" t="n">
         <v>2048703</v>
@@ -28383,7 +28383,7 @@
         <v>5.02199983596802</v>
       </c>
       <c r="G966" t="n">
-        <v>4.07395935058594</v>
+        <v>4.07395887374878</v>
       </c>
       <c r="H966" t="n">
         <v>2792244</v>
@@ -28412,7 +28412,7 @@
         <v>5.07600021362305</v>
       </c>
       <c r="G967" t="n">
-        <v>4.11776542663574</v>
+        <v>4.1177659034729</v>
       </c>
       <c r="H967" t="n">
         <v>2243989</v>
@@ -28499,7 +28499,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G970" t="n">
-        <v>4.1696834564209</v>
+        <v>4.16968297958374</v>
       </c>
       <c r="H970" t="n">
         <v>2263761</v>
@@ -28528,7 +28528,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G971" t="n">
-        <v>4.10640811920166</v>
+        <v>4.1064076423645</v>
       </c>
       <c r="H971" t="n">
         <v>1962976</v>
@@ -28586,7 +28586,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G973" t="n">
-        <v>4.12263202667236</v>
+        <v>4.12263250350952</v>
       </c>
       <c r="H973" t="n">
         <v>1912199</v>
@@ -28615,7 +28615,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G974" t="n">
-        <v>4.42116260528564</v>
+        <v>4.42116212844849</v>
       </c>
       <c r="H974" t="n">
         <v>11030734</v>
@@ -28644,7 +28644,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G975" t="n">
-        <v>4.38546895980835</v>
+        <v>4.38546848297119</v>
       </c>
       <c r="H975" t="n">
         <v>4745665</v>
@@ -28789,7 +28789,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G980" t="n">
-        <v>4.40007066726685</v>
+        <v>4.40007019042969</v>
       </c>
       <c r="H980" t="n">
         <v>869534</v>
@@ -28847,7 +28847,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G982" t="n">
-        <v>4.35788679122925</v>
+        <v>4.35788774490356</v>
       </c>
       <c r="H982" t="n">
         <v>1372294</v>
@@ -28876,7 +28876,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G983" t="n">
-        <v>4.24756145477295</v>
+        <v>4.24756050109863</v>
       </c>
       <c r="H983" t="n">
         <v>2469703</v>
@@ -28934,7 +28934,7 @@
         <v>5.16800022125244</v>
       </c>
       <c r="G985" t="n">
-        <v>4.19239807128906</v>
+        <v>4.1923975944519</v>
       </c>
       <c r="H985" t="n">
         <v>1123987</v>
@@ -29021,7 +29021,7 @@
         <v>5.15199995040894</v>
       </c>
       <c r="G988" t="n">
-        <v>4.17941856384277</v>
+        <v>4.17941808700562</v>
       </c>
       <c r="H988" t="n">
         <v>1033644</v>
@@ -29050,7 +29050,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G989" t="n">
-        <v>4.21348905563354</v>
+        <v>4.2134895324707</v>
       </c>
       <c r="H989" t="n">
         <v>1226933</v>
@@ -29108,7 +29108,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G991" t="n">
-        <v>4.11614227294922</v>
+        <v>4.11614322662354</v>
       </c>
       <c r="H991" t="n">
         <v>2172480</v>
@@ -29166,7 +29166,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G993" t="n">
-        <v>4.19888734817505</v>
+        <v>4.19888782501221</v>
       </c>
       <c r="H993" t="n">
         <v>1028145</v>
@@ -29224,7 +29224,7 @@
         <v>5.15199995040894</v>
       </c>
       <c r="G995" t="n">
-        <v>4.17941856384277</v>
+        <v>4.17941808700562</v>
       </c>
       <c r="H995" t="n">
         <v>679524</v>
@@ -29253,7 +29253,7 @@
         <v>5.15399980545044</v>
       </c>
       <c r="G996" t="n">
-        <v>4.18104028701782</v>
+        <v>4.18104076385498</v>
       </c>
       <c r="H996" t="n">
         <v>802669</v>
@@ -29282,7 +29282,7 @@
         <v>5.13600015640259</v>
       </c>
       <c r="G997" t="n">
-        <v>4.16643857955933</v>
+        <v>4.16643905639648</v>
       </c>
       <c r="H997" t="n">
         <v>3304160</v>
@@ -29311,7 +29311,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G998" t="n">
-        <v>4.19888734817505</v>
+        <v>4.19888782501221</v>
       </c>
       <c r="H998" t="n">
         <v>2479222</v>
@@ -29369,7 +29369,7 @@
         <v>5.2519998550415</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.26054000854492</v>
+        <v>4.26054048538208</v>
       </c>
       <c r="H1000" t="n">
         <v>4074072</v>
@@ -29427,7 +29427,7 @@
         <v>5.14599990844727</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.17455101013184</v>
+        <v>4.17455148696899</v>
       </c>
       <c r="H1002" t="n">
         <v>1333298</v>
@@ -29456,7 +29456,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.20213222503662</v>
+        <v>4.20213174819946</v>
       </c>
       <c r="H1003" t="n">
         <v>2224645</v>
@@ -29485,7 +29485,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.19888734817505</v>
+        <v>4.19888782501221</v>
       </c>
       <c r="H1004" t="n">
         <v>4814465</v>
@@ -29514,7 +29514,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.12263202667236</v>
+        <v>4.12263250350952</v>
       </c>
       <c r="H1005" t="n">
         <v>2689543</v>
@@ -29572,7 +29572,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.19564247131348</v>
+        <v>4.19564294815063</v>
       </c>
       <c r="H1007" t="n">
         <v>1233191</v>
@@ -29717,7 +29717,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.13074445724487</v>
+        <v>4.13074493408203</v>
       </c>
       <c r="H1012" t="n">
         <v>1475971</v>
@@ -29804,7 +29804,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.05205583572388</v>
+        <v>4.05205631256104</v>
       </c>
       <c r="H1015" t="n">
         <v>1874139</v>
@@ -29833,7 +29833,7 @@
         <v>5.02199983596802</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.07395935058594</v>
+        <v>4.07395887374878</v>
       </c>
       <c r="H1016" t="n">
         <v>2197359</v>
@@ -29862,7 +29862,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.97661232948303</v>
+        <v>3.97661256790161</v>
       </c>
       <c r="H1017" t="n">
         <v>2260225</v>
@@ -29891,7 +29891,7 @@
         <v>4.98699998855591</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.04556655883789</v>
+        <v>4.04556608200073</v>
       </c>
       <c r="H1018" t="n">
         <v>1803434</v>
@@ -30007,7 +30007,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.07233667373657</v>
+        <v>4.07233715057373</v>
       </c>
       <c r="H1022" t="n">
         <v>1012542</v>
@@ -30036,7 +30036,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.10478544235229</v>
+        <v>4.10478591918945</v>
       </c>
       <c r="H1023" t="n">
         <v>839666</v>
@@ -30065,7 +30065,7 @@
         <v>5.08400011062622</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.12425470352173</v>
+        <v>4.12425518035889</v>
       </c>
       <c r="H1024" t="n">
         <v>1170127</v>
@@ -30123,7 +30123,7 @@
         <v>5.00600004196167</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.06097936630249</v>
+        <v>4.06097984313965</v>
       </c>
       <c r="H1026" t="n">
         <v>952568</v>
@@ -30152,7 +30152,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.11614227294922</v>
+        <v>4.11614322662354</v>
       </c>
       <c r="H1027" t="n">
         <v>1747743</v>
@@ -30181,7 +30181,7 @@
         <v>5.06799983978271</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.1112756729126</v>
+        <v>4.11127519607544</v>
       </c>
       <c r="H1028" t="n">
         <v>1982566</v>
@@ -30210,7 +30210,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.10478544235229</v>
+        <v>4.10478591918945</v>
       </c>
       <c r="H1029" t="n">
         <v>1426503</v>
@@ -30239,7 +30239,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.21348905563354</v>
+        <v>4.2134895324707</v>
       </c>
       <c r="H1030" t="n">
         <v>2386015</v>
@@ -30268,7 +30268,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.31894874572754</v>
+        <v>4.31894826889038</v>
       </c>
       <c r="H1031" t="n">
         <v>3608828</v>
@@ -30297,7 +30297,7 @@
         <v>5.31199979782104</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.30921363830566</v>
+        <v>4.30921268463135</v>
       </c>
       <c r="H1032" t="n">
         <v>2330998</v>
@@ -30326,7 +30326,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.33192777633667</v>
+        <v>4.33192825317383</v>
       </c>
       <c r="H1033" t="n">
         <v>1351883</v>
@@ -30355,7 +30355,7 @@
         <v>5.31199979782104</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.30921363830566</v>
+        <v>4.30921268463135</v>
       </c>
       <c r="H1034" t="n">
         <v>1389460</v>
@@ -30442,7 +30442,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.38546895980835</v>
+        <v>4.38546848297119</v>
       </c>
       <c r="H1037" t="n">
         <v>2484385</v>
@@ -30471,7 +30471,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.42765188217163</v>
+        <v>4.42765235900879</v>
       </c>
       <c r="H1038" t="n">
         <v>2747939</v>
@@ -30529,7 +30529,7 @@
         <v>5.53800010681152</v>
       </c>
       <c r="G1040" t="n">
-        <v>4.49255037307739</v>
+        <v>4.49254989624023</v>
       </c>
       <c r="H1040" t="n">
         <v>1209926</v>
@@ -30587,7 +30587,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.49579477310181</v>
+        <v>4.49579524993896</v>
       </c>
       <c r="H1042" t="n">
         <v>1640358</v>
@@ -30674,7 +30674,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.69860076904297</v>
+        <v>4.69860029220581</v>
       </c>
       <c r="H1045" t="n">
         <v>2320901</v>
@@ -30703,7 +30703,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.7391619682312</v>
+        <v>4.73916149139404</v>
       </c>
       <c r="H1046" t="n">
         <v>2599366</v>
@@ -30761,7 +30761,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.6969780921936</v>
+        <v>4.69697761535645</v>
       </c>
       <c r="H1048" t="n">
         <v>2389181</v>
@@ -30790,7 +30790,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.68399810791016</v>
+        <v>4.68399906158447</v>
       </c>
       <c r="H1049" t="n">
         <v>2601645</v>
@@ -30848,7 +30848,7 @@
         <v>5.78200006484985</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.69048881530762</v>
+        <v>4.69048833847046</v>
       </c>
       <c r="H1051" t="n">
         <v>1522914</v>
@@ -30935,7 +30935,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G1054" t="n">
-        <v>4.4308967590332</v>
+        <v>4.43089723587036</v>
       </c>
       <c r="H1054" t="n">
         <v>4035150</v>
@@ -31022,7 +31022,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1057" t="n">
-        <v>4.52824354171753</v>
+        <v>4.52824401855469</v>
       </c>
       <c r="H1057" t="n">
         <v>1470691</v>
@@ -31109,7 +31109,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1060" t="n">
-        <v>4.66128396987915</v>
+        <v>4.66128444671631</v>
       </c>
       <c r="H1060" t="n">
         <v>1523485</v>
@@ -31138,7 +31138,7 @@
         <v>5.92799997329712</v>
       </c>
       <c r="G1061" t="n">
-        <v>4.80892705917358</v>
+        <v>4.80892658233643</v>
       </c>
       <c r="H1061" t="n">
         <v>3912689</v>
@@ -31167,7 +31167,7 @@
         <v>5.9520001411438</v>
       </c>
       <c r="G1062" t="n">
-        <v>4.82839632034302</v>
+        <v>4.82839584350586</v>
       </c>
       <c r="H1062" t="n">
         <v>1625771</v>
@@ -31225,7 +31225,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.84299802780151</v>
+        <v>4.84299850463867</v>
       </c>
       <c r="H1064" t="n">
         <v>2344019</v>
@@ -31254,7 +31254,7 @@
         <v>5.97399997711182</v>
       </c>
       <c r="G1065" t="n">
-        <v>4.84624338150024</v>
+        <v>4.84624290466309</v>
       </c>
       <c r="H1065" t="n">
         <v>2235634</v>
@@ -31283,7 +31283,7 @@
         <v>5.94399976730347</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.82190561294556</v>
+        <v>4.82190608978271</v>
       </c>
       <c r="H1066" t="n">
         <v>2592587</v>
@@ -31312,7 +31312,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.84299802780151</v>
+        <v>4.84299850463867</v>
       </c>
       <c r="H1067" t="n">
         <v>1471367</v>
@@ -31370,7 +31370,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.85110998153687</v>
+        <v>4.85111045837402</v>
       </c>
       <c r="H1069" t="n">
         <v>3844834</v>
@@ -31399,7 +31399,7 @@
         <v>5.87400007247925</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.76512050628662</v>
+        <v>4.76512098312378</v>
       </c>
       <c r="H1070" t="n">
         <v>1622984</v>
@@ -31428,7 +31428,7 @@
         <v>5.95599985122681</v>
       </c>
       <c r="G1071" t="n">
-        <v>4.83164072036743</v>
+        <v>4.83164119720459</v>
       </c>
       <c r="H1071" t="n">
         <v>1049521</v>
@@ -31457,7 +31457,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G1072" t="n">
-        <v>4.87869167327881</v>
+        <v>4.87869215011597</v>
       </c>
       <c r="H1072" t="n">
         <v>1042404</v>
@@ -31515,7 +31515,7 @@
         <v>6.10400009155273</v>
       </c>
       <c r="G1074" t="n">
-        <v>4.95170164108276</v>
+        <v>4.95170211791992</v>
       </c>
       <c r="H1074" t="n">
         <v>1199147</v>
@@ -31544,7 +31544,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G1075" t="n">
-        <v>4.94845724105835</v>
+        <v>4.94845676422119</v>
       </c>
       <c r="H1075" t="n">
         <v>1049826</v>
@@ -31602,7 +31602,7 @@
         <v>6.10799980163574</v>
       </c>
       <c r="G1077" t="n">
-        <v>4.95494699478149</v>
+        <v>4.95494651794434</v>
       </c>
       <c r="H1077" t="n">
         <v>871315</v>
@@ -31631,7 +31631,7 @@
         <v>6.15199995040894</v>
       </c>
       <c r="G1078" t="n">
-        <v>4.99064111709595</v>
+        <v>4.99064064025879</v>
       </c>
       <c r="H1078" t="n">
         <v>1736834</v>
@@ -31660,7 +31660,7 @@
         <v>6.17600011825562</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.01010990142822</v>
+        <v>5.01010942459106</v>
       </c>
       <c r="H1079" t="n">
         <v>3017051</v>
@@ -31689,7 +31689,7 @@
         <v>6.5</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.27294588088989</v>
+        <v>5.27294635772705</v>
       </c>
       <c r="H1080" t="n">
         <v>10512927</v>
@@ -31718,7 +31718,7 @@
         <v>6.43800020217896</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.2226505279541</v>
+        <v>5.22265005111694</v>
       </c>
       <c r="H1081" t="n">
         <v>3172913</v>
@@ -31747,7 +31747,7 @@
         <v>6.42600011825562</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.21291542053223</v>
+        <v>5.21291589736938</v>
       </c>
       <c r="H1082" t="n">
         <v>2010109</v>
@@ -31863,7 +31863,7 @@
         <v>6.69600009918213</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.43194580078125</v>
+        <v>5.43194627761841</v>
       </c>
       <c r="H1086" t="n">
         <v>2633796</v>
@@ -31892,7 +31892,7 @@
         <v>6.67600011825562</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.41572141647339</v>
+        <v>5.41572093963623</v>
       </c>
       <c r="H1087" t="n">
         <v>2462914</v>
@@ -31921,7 +31921,7 @@
         <v>6.62799978256226</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.37678241729736</v>
+        <v>5.37678194046021</v>
       </c>
       <c r="H1088" t="n">
         <v>1446547</v>
@@ -31950,7 +31950,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.31350660324097</v>
+        <v>5.31350708007812</v>
       </c>
       <c r="H1089" t="n">
         <v>1843261</v>
@@ -31979,7 +31979,7 @@
         <v>6.56799983978271</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.32810878753662</v>
+        <v>5.32810926437378</v>
       </c>
       <c r="H1090" t="n">
         <v>976130</v>
@@ -32124,7 +32124,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.00037574768066</v>
+        <v>5.00037527084351</v>
       </c>
       <c r="H1095" t="n">
         <v>1842897</v>
@@ -32153,7 +32153,7 @@
         <v>6.28599977493286</v>
       </c>
       <c r="G1096" t="n">
-        <v>5.09934377670288</v>
+        <v>5.09934425354004</v>
       </c>
       <c r="H1096" t="n">
         <v>1786524</v>
@@ -32211,7 +32211,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.05553770065308</v>
+        <v>5.05553865432739</v>
       </c>
       <c r="H1098" t="n">
         <v>1921905</v>
@@ -32501,7 +32501,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G1108" t="n">
-        <v>4.74889612197876</v>
+        <v>4.74889659881592</v>
       </c>
       <c r="H1108" t="n">
         <v>3881959</v>
@@ -32530,7 +32530,7 @@
         <v>5.9980001449585</v>
       </c>
       <c r="G1109" t="n">
-        <v>4.86571216583252</v>
+        <v>4.86571264266968</v>
       </c>
       <c r="H1109" t="n">
         <v>2265679</v>
@@ -32559,7 +32559,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G1110" t="n">
-        <v>4.76025295257568</v>
+        <v>4.76025342941284</v>
       </c>
       <c r="H1110" t="n">
         <v>1735712</v>
@@ -32617,7 +32617,7 @@
         <v>5.75799989700317</v>
       </c>
       <c r="G1112" t="n">
-        <v>4.67101907730103</v>
+        <v>4.67101860046387</v>
       </c>
       <c r="H1112" t="n">
         <v>2110850</v>
@@ -32733,7 +32733,7 @@
         <v>5.06400012969971</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.10803079605103</v>
+        <v>4.10803031921387</v>
       </c>
       <c r="H1116" t="n">
         <v>8091389</v>
@@ -32791,7 +32791,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G1118" t="n">
-        <v>4.00987243652344</v>
+        <v>4.0098729133606</v>
       </c>
       <c r="H1118" t="n">
         <v>5179774</v>
@@ -32849,7 +32849,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.82247972488403</v>
+        <v>3.82248020172119</v>
       </c>
       <c r="H1120" t="n">
         <v>5287521</v>
@@ -32878,7 +32878,7 @@
         <v>4.65700006484985</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.77786302566528</v>
+        <v>3.77786350250244</v>
       </c>
       <c r="H1121" t="n">
         <v>4897326</v>
@@ -32907,7 +32907,7 @@
         <v>4.32600021362305</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.50934863090515</v>
+        <v>3.50934886932373</v>
       </c>
       <c r="H1122" t="n">
         <v>5387349</v>
@@ -32965,7 +32965,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.4379608631134</v>
+        <v>3.43796062469482</v>
       </c>
       <c r="H1124" t="n">
         <v>4500750</v>
@@ -33023,7 +33023,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.6870059967041</v>
+        <v>3.68700623512268</v>
       </c>
       <c r="H1126" t="n">
         <v>3168181</v>
@@ -33081,7 +33081,7 @@
         <v>4.66099977493286</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.78110766410828</v>
+        <v>3.78110790252686</v>
       </c>
       <c r="H1128" t="n">
         <v>3248155</v>
@@ -33110,7 +33110,7 @@
         <v>4.6710000038147</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.78921985626221</v>
+        <v>3.78922009468079</v>
       </c>
       <c r="H1129" t="n">
         <v>3429484</v>
@@ -33139,7 +33139,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.97661232948303</v>
+        <v>3.97661256790161</v>
       </c>
       <c r="H1130" t="n">
         <v>4326966</v>
@@ -33168,7 +33168,7 @@
         <v>4.84700012207031</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.93199515342712</v>
+        <v>3.9319953918457</v>
       </c>
       <c r="H1131" t="n">
         <v>4300476</v>
@@ -33226,7 +33226,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.86953091621399</v>
+        <v>3.86953067779541</v>
       </c>
       <c r="H1133" t="n">
         <v>1636489</v>
@@ -33255,7 +33255,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.93767428398132</v>
+        <v>3.93767356872559</v>
       </c>
       <c r="H1134" t="n">
         <v>1588173</v>
@@ -33284,7 +33284,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.93118357658386</v>
+        <v>3.93118381500244</v>
       </c>
       <c r="H1135" t="n">
         <v>1943279</v>
@@ -33313,7 +33313,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.86628603935242</v>
+        <v>3.86628651618958</v>
       </c>
       <c r="H1136" t="n">
         <v>1878893</v>
@@ -33342,7 +33342,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.89386820793152</v>
+        <v>3.89386749267578</v>
       </c>
       <c r="H1137" t="n">
         <v>1417907</v>
@@ -33458,7 +33458,7 @@
         <v>4.93100023269653</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.00013828277588</v>
+        <v>4.00013780593872</v>
       </c>
       <c r="H1141" t="n">
         <v>2150012</v>
@@ -33487,7 +33487,7 @@
         <v>4.9060001373291</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.97985744476318</v>
+        <v>3.97985768318176</v>
       </c>
       <c r="H1142" t="n">
         <v>1512137</v>
@@ -33516,7 +33516,7 @@
         <v>4.8769998550415</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.95633220672607</v>
+        <v>3.95633172988892</v>
       </c>
       <c r="H1143" t="n">
         <v>1366405</v>
@@ -33545,7 +33545,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.89548993110657</v>
+        <v>3.8954906463623</v>
       </c>
       <c r="H1144" t="n">
         <v>2905567</v>
@@ -33603,7 +33603,7 @@
         <v>4.41300010681152</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.57992458343506</v>
+        <v>3.57992506027222</v>
       </c>
       <c r="H1146" t="n">
         <v>3363384</v>
@@ -33632,7 +33632,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.61318469047546</v>
+        <v>3.61318492889404</v>
       </c>
       <c r="H1147" t="n">
         <v>3241105</v>
@@ -33690,7 +33690,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.6066951751709</v>
+        <v>3.60669469833374</v>
       </c>
       <c r="H1149" t="n">
         <v>2415234</v>
@@ -33719,7 +33719,7 @@
         <v>4.52099990844727</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.66753697395325</v>
+        <v>3.66753649711609</v>
       </c>
       <c r="H1150" t="n">
         <v>1575910</v>
@@ -33777,7 +33777,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.73567938804626</v>
+        <v>3.73567962646484</v>
       </c>
       <c r="H1152" t="n">
         <v>1172764</v>
@@ -33806,7 +33806,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.85817432403564</v>
+        <v>3.85817360877991</v>
       </c>
       <c r="H1153" t="n">
         <v>3842670</v>
@@ -33864,7 +33864,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.84925007820129</v>
+        <v>3.84924983978271</v>
       </c>
       <c r="H1155" t="n">
         <v>1572535</v>
@@ -33893,7 +33893,7 @@
         <v>4.69600009918213</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.80950045585632</v>
+        <v>3.80950093269348</v>
       </c>
       <c r="H1156" t="n">
         <v>1043439</v>
@@ -33922,7 +33922,7 @@
         <v>4.5770001411438</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.71296525001526</v>
+        <v>3.71296501159668</v>
       </c>
       <c r="H1157" t="n">
         <v>1271329</v>
@@ -33980,7 +33980,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.85006165504456</v>
+        <v>3.85006189346313</v>
       </c>
       <c r="H1159" t="n">
         <v>1808335</v>
@@ -34009,7 +34009,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.85168480873108</v>
+        <v>3.85168433189392</v>
       </c>
       <c r="H1160" t="n">
         <v>1917361</v>
@@ -34038,7 +34038,7 @@
         <v>4.61700010299683</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.74541401863098</v>
+        <v>3.74541425704956</v>
       </c>
       <c r="H1161" t="n">
         <v>2119596</v>
@@ -34125,7 +34125,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.60831713676453</v>
+        <v>3.60831761360168</v>
       </c>
       <c r="H1164" t="n">
         <v>1746404</v>
@@ -34154,7 +34154,7 @@
         <v>4.45100021362305</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.61075162887573</v>
+        <v>3.61075115203857</v>
       </c>
       <c r="H1165" t="n">
         <v>1855446</v>
@@ -34183,7 +34183,7 @@
         <v>4.30100011825562</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.48906803131104</v>
+        <v>3.48906779289246</v>
       </c>
       <c r="H1166" t="n">
         <v>2111708</v>
@@ -34212,7 +34212,7 @@
         <v>4.4689998626709</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.62535285949707</v>
+        <v>3.62535333633423</v>
       </c>
       <c r="H1167" t="n">
         <v>2099491</v>
@@ -34241,7 +34241,7 @@
         <v>4.56799983978271</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.70566368103027</v>
+        <v>3.70566415786743</v>
       </c>
       <c r="H1168" t="n">
         <v>2290244</v>
@@ -34270,7 +34270,7 @@
         <v>4.63899993896484</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.76326107978821</v>
+        <v>3.76326131820679</v>
       </c>
       <c r="H1169" t="n">
         <v>1807513</v>
@@ -34328,7 +34328,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.81761312484741</v>
+        <v>3.81761264801025</v>
       </c>
       <c r="H1171" t="n">
         <v>885772</v>
@@ -34357,7 +34357,7 @@
         <v>4.68699979782104</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.80219960212708</v>
+        <v>3.8021993637085</v>
       </c>
       <c r="H1172" t="n">
         <v>1423396</v>
@@ -34386,7 +34386,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.71134281158447</v>
+        <v>3.71134233474731</v>
       </c>
       <c r="H1173" t="n">
         <v>2215369</v>
@@ -34473,7 +34473,7 @@
         <v>4.51100015640259</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.79477262496948</v>
+        <v>3.7947723865509</v>
       </c>
       <c r="H1176" t="n">
         <v>1930235</v>
@@ -34560,7 +34560,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.85449862480164</v>
+        <v>3.85449838638306</v>
       </c>
       <c r="H1179" t="n">
         <v>1272388</v>
@@ -34589,7 +34589,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.86543440818787</v>
+        <v>3.86543464660645</v>
       </c>
       <c r="H1180" t="n">
         <v>803294</v>
@@ -34676,7 +34676,7 @@
         <v>4.65100002288818</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.91254377365112</v>
+        <v>3.9125440120697</v>
       </c>
       <c r="H1183" t="n">
         <v>1244046</v>
@@ -34705,7 +34705,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.92768597602844</v>
+        <v>3.92768549919128</v>
       </c>
       <c r="H1184" t="n">
         <v>429704</v>
@@ -34734,7 +34734,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.84861016273499</v>
+        <v>3.84861040115356</v>
       </c>
       <c r="H1185" t="n">
         <v>982607</v>
@@ -34763,7 +34763,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.92852687835693</v>
+        <v>3.92852711677551</v>
       </c>
       <c r="H1186" t="n">
         <v>661346</v>
@@ -34792,7 +34792,7 @@
         <v>4.58900022506714</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.8603880405426</v>
+        <v>3.86038780212402</v>
       </c>
       <c r="H1187" t="n">
         <v>1054236</v>
@@ -34821,7 +34821,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.80402565002441</v>
+        <v>3.80402541160583</v>
       </c>
       <c r="H1188" t="n">
         <v>1390641</v>
@@ -34850,7 +34850,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.741774559021</v>
+        <v>3.74177503585815</v>
       </c>
       <c r="H1189" t="n">
         <v>1501746</v>
@@ -34937,7 +34937,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.37752366065979</v>
+        <v>3.37752342224121</v>
       </c>
       <c r="H1192" t="n">
         <v>2426396</v>
@@ -34966,7 +34966,7 @@
         <v>4.21299982070923</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.54408621788025</v>
+        <v>3.54408645629883</v>
       </c>
       <c r="H1193" t="n">
         <v>2162957</v>
@@ -34995,7 +34995,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.39014196395874</v>
+        <v>3.3901424407959</v>
       </c>
       <c r="H1194" t="n">
         <v>1378418</v>
@@ -35198,7 +35198,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.40191960334778</v>
+        <v>3.4019193649292</v>
       </c>
       <c r="H1201" t="n">
         <v>1282641</v>
@@ -35372,7 +35372,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.17478823661804</v>
+        <v>3.17478799819946</v>
       </c>
       <c r="H1207" t="n">
         <v>2164862</v>
@@ -35488,7 +35488,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.41958498954773</v>
+        <v>3.41958475112915</v>
       </c>
       <c r="H1211" t="n">
         <v>1022124</v>
@@ -35546,7 +35546,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.33125638961792</v>
+        <v>3.33125615119934</v>
       </c>
       <c r="H1213" t="n">
         <v>1482347</v>
@@ -35575,7 +35575,7 @@
         <v>3.875</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.25975227355957</v>
+        <v>3.25975203514099</v>
       </c>
       <c r="H1214" t="n">
         <v>1737711</v>
@@ -35604,7 +35604,7 @@
         <v>4.09100008010864</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.44145727157593</v>
+        <v>3.44145703315735</v>
       </c>
       <c r="H1215" t="n">
         <v>2031711</v>
@@ -35633,7 +35633,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.4995014667511</v>
+        <v>3.49950122833252</v>
       </c>
       <c r="H1216" t="n">
         <v>1700718</v>
@@ -35662,7 +35662,7 @@
         <v>4.20300006866455</v>
       </c>
       <c r="G1217" t="n">
-        <v>3.53567409515381</v>
+        <v>3.53567433357239</v>
       </c>
       <c r="H1217" t="n">
         <v>1914171</v>
@@ -35778,7 +35778,7 @@
         <v>4.12900018692017</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.47342371940613</v>
+        <v>3.47342395782471</v>
       </c>
       <c r="H1221" t="n">
         <v>1023382</v>
@@ -35807,7 +35807,7 @@
         <v>4.02299976348877</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.38425350189209</v>
+        <v>3.38425326347351</v>
       </c>
       <c r="H1222" t="n">
         <v>1385705</v>
@@ -35836,7 +35836,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.29592490196228</v>
+        <v>3.2959246635437</v>
       </c>
       <c r="H1223" t="n">
         <v>2424724</v>
@@ -35952,7 +35952,7 @@
         <v>4.09600019454956</v>
       </c>
       <c r="G1227" t="n">
-        <v>3.44566297531128</v>
+        <v>3.44566321372986</v>
       </c>
       <c r="H1227" t="n">
         <v>881224</v>
@@ -35981,7 +35981,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1228" t="n">
-        <v>3.6004490852356</v>
+        <v>3.60044884681702</v>
       </c>
       <c r="H1228" t="n">
         <v>1426287</v>
@@ -36039,7 +36039,7 @@
         <v>4.43900012969971</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.73420381546021</v>
+        <v>3.73420357704163</v>
       </c>
       <c r="H1230" t="n">
         <v>4970115</v>
@@ -36068,7 +36068,7 @@
         <v>4.40700006484985</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.70728397369385</v>
+        <v>3.70728445053101</v>
       </c>
       <c r="H1231" t="n">
         <v>2232915</v>
@@ -36126,7 +36126,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.66774678230286</v>
+        <v>3.66774702072144</v>
       </c>
       <c r="H1233" t="n">
         <v>2584764</v>
@@ -36184,7 +36184,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.6240029335022</v>
+        <v>3.62400317192078</v>
       </c>
       <c r="H1235" t="n">
         <v>1326998</v>
@@ -36242,7 +36242,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.47847080230713</v>
+        <v>3.47847104072571</v>
       </c>
       <c r="H1237" t="n">
         <v>2906892</v>
@@ -36300,7 +36300,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.39014196395874</v>
+        <v>3.3901424407959</v>
       </c>
       <c r="H1239" t="n">
         <v>1972997</v>
@@ -36329,7 +36329,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.27068781852722</v>
+        <v>3.2706880569458</v>
       </c>
       <c r="H1240" t="n">
         <v>3268196</v>
@@ -36387,7 +36387,7 @@
         <v>3.87899994850159</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.26311707496643</v>
+        <v>3.26311683654785</v>
       </c>
       <c r="H1242" t="n">
         <v>2951087</v>
@@ -36445,7 +36445,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.14113903045654</v>
+        <v>3.14113926887512</v>
       </c>
       <c r="H1244" t="n">
         <v>2752657</v>
@@ -36561,7 +36561,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.14113903045654</v>
+        <v>3.14113926887512</v>
       </c>
       <c r="H1248" t="n">
         <v>1774378</v>
@@ -36619,7 +36619,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.07468223571777</v>
+        <v>3.07468199729919</v>
       </c>
       <c r="H1250" t="n">
         <v>2295669</v>
@@ -36648,7 +36648,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.16721701622009</v>
+        <v>3.16721725463867</v>
       </c>
       <c r="H1251" t="n">
         <v>2569808</v>
@@ -36764,7 +36764,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.297607421875</v>
+        <v>3.29760718345642</v>
       </c>
       <c r="H1255" t="n">
         <v>2198505</v>
@@ -36851,7 +36851,7 @@
         <v>3.78099989891052</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.18067646026611</v>
+        <v>3.18067669868469</v>
       </c>
       <c r="H1258" t="n">
         <v>1132165</v>
@@ -36880,7 +36880,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.13609147071838</v>
+        <v>3.13609170913696</v>
       </c>
       <c r="H1259" t="n">
         <v>2664565</v>
@@ -36967,7 +36967,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.1596462726593</v>
+        <v>3.15964603424072</v>
       </c>
       <c r="H1262" t="n">
         <v>1131519</v>
@@ -36996,7 +36996,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G1263" t="n">
-        <v>3.04692196846008</v>
+        <v>3.0469217300415</v>
       </c>
       <c r="H1263" t="n">
         <v>2294253</v>
@@ -37112,7 +37112,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.87867641448975</v>
+        <v>2.87867665290833</v>
       </c>
       <c r="H1267" t="n">
         <v>1918944</v>
@@ -37199,7 +37199,7 @@
         <v>3.3659999370575</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.83156752586365</v>
+        <v>2.83156776428223</v>
       </c>
       <c r="H1270" t="n">
         <v>2368766</v>
@@ -37228,7 +37228,7 @@
         <v>3.50300002098083</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.94681572914124</v>
+        <v>2.94681596755981</v>
       </c>
       <c r="H1271" t="n">
         <v>2192771</v>
@@ -37315,7 +37315,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.84839224815369</v>
+        <v>2.84839248657227</v>
       </c>
       <c r="H1274" t="n">
         <v>2266722</v>
@@ -37373,7 +37373,7 @@
         <v>3.40400004386902</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.86353445053101</v>
+        <v>2.86353468894958</v>
       </c>
       <c r="H1276" t="n">
         <v>2153043</v>
@@ -37402,7 +37402,7 @@
         <v>3.41899991035461</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.87615251541138</v>
+        <v>2.87615275382996</v>
       </c>
       <c r="H1277" t="n">
         <v>3459188</v>
@@ -37547,7 +37547,7 @@
         <v>3.56900000572205</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.0023365020752</v>
+        <v>3.00233697891235</v>
       </c>
       <c r="H1282" t="n">
         <v>1713888</v>
@@ -37576,7 +37576,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1283" t="n">
-        <v>3.01579666137695</v>
+        <v>3.01579642295837</v>
       </c>
       <c r="H1283" t="n">
         <v>1883074</v>
@@ -37634,7 +37634,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.11085486412048</v>
+        <v>3.11085510253906</v>
       </c>
       <c r="H1285" t="n">
         <v>3358682</v>
@@ -37692,7 +37692,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.17478823661804</v>
+        <v>3.17478799819946</v>
       </c>
       <c r="H1287" t="n">
         <v>1764647</v>
@@ -37779,7 +37779,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.21180200576782</v>
+        <v>3.2118022441864</v>
       </c>
       <c r="H1290" t="n">
         <v>1372350</v>
@@ -37837,7 +37837,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1292" t="n">
-        <v>3.16301107406616</v>
+        <v>3.16301083564758</v>
       </c>
       <c r="H1292" t="n">
         <v>2531218</v>
@@ -37953,7 +37953,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1296" t="n">
-        <v>3.38593626022339</v>
+        <v>3.38593602180481</v>
       </c>
       <c r="H1296" t="n">
         <v>1598547</v>
@@ -38011,7 +38011,7 @@
         <v>4.13299989700317</v>
       </c>
       <c r="G1298" t="n">
-        <v>3.47678828239441</v>
+        <v>3.47678852081299</v>
       </c>
       <c r="H1298" t="n">
         <v>2693788</v>
@@ -38069,7 +38069,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.52053213119507</v>
+        <v>3.52053189277649</v>
       </c>
       <c r="H1300" t="n">
         <v>1535495</v>
@@ -38127,7 +38127,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.46585249900818</v>
+        <v>3.4658522605896</v>
       </c>
       <c r="H1302" t="n">
         <v>1865038</v>
@@ -38156,7 +38156,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.4288387298584</v>
+        <v>3.42883849143982</v>
       </c>
       <c r="H1303" t="n">
         <v>1307714</v>
@@ -38330,7 +38330,7 @@
         <v>4.22300004959106</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.55249905586243</v>
+        <v>3.55249881744385</v>
       </c>
       <c r="H1309" t="n">
         <v>1179788</v>
@@ -38504,7 +38504,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.56343483924866</v>
+        <v>3.56343460083008</v>
       </c>
       <c r="H1315" t="n">
         <v>1887472</v>
@@ -38707,7 +38707,7 @@
         <v>4.15100002288818</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.49193072319031</v>
+        <v>3.49193048477173</v>
       </c>
       <c r="H1322" t="n">
         <v>1434174</v>
@@ -38794,7 +38794,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.38593626022339</v>
+        <v>3.38593602180481</v>
       </c>
       <c r="H1325" t="n">
         <v>780175</v>
@@ -38852,7 +38852,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.4271559715271</v>
+        <v>3.42715573310852</v>
       </c>
       <c r="H1327" t="n">
         <v>995271</v>
@@ -38997,7 +38997,7 @@
         <v>4.09299993515015</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.44313955307007</v>
+        <v>3.44313931465149</v>
       </c>
       <c r="H1332" t="n">
         <v>859323</v>
@@ -39026,7 +39026,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.3682701587677</v>
+        <v>3.36827039718628</v>
       </c>
       <c r="H1333" t="n">
         <v>740202</v>
@@ -39055,7 +39055,7 @@
         <v>4.08900022506714</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.43977475166321</v>
+        <v>3.43977451324463</v>
       </c>
       <c r="H1334" t="n">
         <v>1180250</v>
@@ -39113,7 +39113,7 @@
         <v>4.4229998588562</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.72074389457703</v>
+        <v>3.72074413299561</v>
       </c>
       <c r="H1336" t="n">
         <v>2901452</v>
@@ -39142,7 +39142,7 @@
         <v>4.44099998474121</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.73588609695435</v>
+        <v>3.73588633537292</v>
       </c>
       <c r="H1337" t="n">
         <v>1610539</v>
@@ -39229,7 +39229,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1340" t="n">
-        <v>3.81916737556458</v>
+        <v>3.819167137146</v>
       </c>
       <c r="H1340" t="n">
         <v>1362107</v>
@@ -39258,7 +39258,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.84019827842712</v>
+        <v>3.84019804000854</v>
       </c>
       <c r="H1341" t="n">
         <v>1203558</v>
@@ -39287,7 +39287,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.90749645233154</v>
+        <v>3.90749621391296</v>
       </c>
       <c r="H1342" t="n">
         <v>2514140</v>
@@ -39316,7 +39316,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.87721252441406</v>
+        <v>3.87721276283264</v>
       </c>
       <c r="H1343" t="n">
         <v>1423586</v>
@@ -39374,7 +39374,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.94366931915283</v>
+        <v>3.94366955757141</v>
       </c>
       <c r="H1345" t="n">
         <v>1481884</v>
@@ -39461,7 +39461,7 @@
         <v>4.53700017929077</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.81664443016052</v>
+        <v>3.81664419174194</v>
       </c>
       <c r="H1348" t="n">
         <v>2276340</v>
@@ -39519,7 +39519,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.85113430023193</v>
+        <v>3.85113406181335</v>
       </c>
       <c r="H1350" t="n">
         <v>693551</v>
@@ -39606,7 +39606,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.85618138313293</v>
+        <v>3.85618185997009</v>
       </c>
       <c r="H1353" t="n">
         <v>1766336</v>
@@ -39635,7 +39635,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.82758021354675</v>
+        <v>3.82757997512817</v>
       </c>
       <c r="H1354" t="n">
         <v>1519001</v>
@@ -39693,7 +39693,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.85618138313293</v>
+        <v>3.85618185997009</v>
       </c>
       <c r="H1356" t="n">
         <v>2609924</v>
@@ -39722,7 +39722,7 @@
         <v>4.65899991989136</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.91927337646484</v>
+        <v>3.919273853302</v>
       </c>
       <c r="H1357" t="n">
         <v>2680349</v>
@@ -39896,7 +39896,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.83767414093018</v>
+        <v>3.83767437934875</v>
       </c>
       <c r="H1363" t="n">
         <v>2263573</v>
@@ -39925,7 +39925,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.90917825698853</v>
+        <v>3.90917873382568</v>
       </c>
       <c r="H1364" t="n">
         <v>1819880</v>
@@ -39954,7 +39954,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.95376348495483</v>
+        <v>3.95376324653625</v>
       </c>
       <c r="H1365" t="n">
         <v>1904113</v>
@@ -39983,7 +39983,7 @@
         <v>4.78900003433228</v>
       </c>
       <c r="G1366" t="n">
-        <v>4.02863264083862</v>
+        <v>4.02863311767578</v>
       </c>
       <c r="H1366" t="n">
         <v>5871194</v>
@@ -40012,7 +40012,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.16407012939453</v>
+        <v>4.16406965255737</v>
       </c>
       <c r="H1367" t="n">
         <v>10998509</v>
@@ -40041,7 +40041,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G1368" t="n">
-        <v>4.08331203460693</v>
+        <v>4.08331251144409</v>
       </c>
       <c r="H1368" t="n">
         <v>2911998</v>
@@ -40070,7 +40070,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.11359691619873</v>
+        <v>4.11359643936157</v>
       </c>
       <c r="H1369" t="n">
         <v>1669141</v>
@@ -40128,7 +40128,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G1371" t="n">
-        <v>4.04209184646606</v>
+        <v>4.04209232330322</v>
       </c>
       <c r="H1371" t="n">
         <v>1614868</v>
@@ -40157,7 +40157,7 @@
         <v>4.95300006866455</v>
       </c>
       <c r="G1372" t="n">
-        <v>4.1665940284729</v>
+        <v>4.16659450531006</v>
       </c>
       <c r="H1372" t="n">
         <v>5809624</v>
@@ -40186,7 +40186,7 @@
         <v>4.76700019836426</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.0101261138916</v>
+        <v>4.01012563705444</v>
       </c>
       <c r="H1373" t="n">
         <v>3059807</v>
@@ -40273,7 +40273,7 @@
         <v>4.89099979400635</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.11443758010864</v>
+        <v>4.1144380569458</v>
       </c>
       <c r="H1376" t="n">
         <v>2478173</v>
@@ -40302,7 +40302,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G1377" t="n">
-        <v>4.12285041809082</v>
+        <v>4.12284994125366</v>
       </c>
       <c r="H1377" t="n">
         <v>1954631</v>
@@ -40331,7 +40331,7 @@
         <v>4.94399976730347</v>
       </c>
       <c r="G1378" t="n">
-        <v>4.15902280807495</v>
+        <v>4.15902233123779</v>
       </c>
       <c r="H1378" t="n">
         <v>1603382</v>
@@ -40360,7 +40360,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.22295618057251</v>
+        <v>4.22295570373535</v>
       </c>
       <c r="H1379" t="n">
         <v>1843000</v>
@@ -40418,7 +40418,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1381" t="n">
-        <v>4.16238784790039</v>
+        <v>4.16238737106323</v>
       </c>
       <c r="H1381" t="n">
         <v>1401021</v>
@@ -40534,7 +40534,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.86627674102783</v>
+        <v>3.86627650260925</v>
       </c>
       <c r="H1385" t="n">
         <v>2645603</v>
@@ -40592,7 +40592,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.73672723770142</v>
+        <v>3.73672699928284</v>
       </c>
       <c r="H1387" t="n">
         <v>1881833</v>
@@ -40650,7 +40650,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.74682188034058</v>
+        <v>3.74682211875916</v>
       </c>
       <c r="H1389" t="n">
         <v>2366506</v>
@@ -40679,7 +40679,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.79561305046082</v>
+        <v>3.79561328887939</v>
       </c>
       <c r="H1390" t="n">
         <v>2003223</v>
@@ -40708,7 +40708,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.75607562065125</v>
+        <v>3.7560760974884</v>
       </c>
       <c r="H1391" t="n">
         <v>1114169</v>
@@ -40737,7 +40737,7 @@
         <v>4.45699977874756</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.74934554100037</v>
+        <v>3.74934530258179</v>
       </c>
       <c r="H1392" t="n">
         <v>1090790</v>
@@ -40766,7 +40766,7 @@
         <v>4.34899997711182</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.65849304199219</v>
+        <v>3.65849328041077</v>
       </c>
       <c r="H1393" t="n">
         <v>1563435</v>
@@ -40795,7 +40795,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.69634819030762</v>
+        <v>3.6963484287262</v>
       </c>
       <c r="H1394" t="n">
         <v>1311955</v>
@@ -40824,7 +40824,7 @@
         <v>4.40899991989136</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.70896625518799</v>
+        <v>3.70896649360657</v>
       </c>
       <c r="H1395" t="n">
         <v>1151563</v>
@@ -40853,7 +40853,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.76448774337769</v>
+        <v>3.76448750495911</v>
       </c>
       <c r="H1396" t="n">
         <v>1206554</v>
@@ -40882,7 +40882,7 @@
         <v>4.55900001525879</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.83515095710754</v>
+        <v>3.83515071868896</v>
       </c>
       <c r="H1397" t="n">
         <v>1778437</v>
@@ -40911,7 +40911,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.88814830780029</v>
+        <v>3.88814854621887</v>
       </c>
       <c r="H1398" t="n">
         <v>1770472</v>
@@ -40940,7 +40940,7 @@
         <v>4.62599992752075</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.89151334762573</v>
+        <v>3.89151310920715</v>
       </c>
       <c r="H1399" t="n">
         <v>1320958</v>
@@ -40969,7 +40969,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.95460534095764</v>
+        <v>3.95460557937622</v>
       </c>
       <c r="H1400" t="n">
         <v>2792824</v>
@@ -41085,7 +41085,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.88141775131226</v>
+        <v>3.88141798973083</v>
       </c>
       <c r="H1404" t="n">
         <v>1594098</v>
@@ -41172,7 +41172,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.97563529014587</v>
+        <v>3.97563552856445</v>
       </c>
       <c r="H1407" t="n">
         <v>1984155</v>
@@ -41201,7 +41201,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1408" t="n">
-        <v>4.03788661956787</v>
+        <v>4.03788614273071</v>
       </c>
       <c r="H1408" t="n">
         <v>3190468</v>
@@ -41259,7 +41259,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.92768597602844</v>
+        <v>3.92768549919128</v>
       </c>
       <c r="H1410" t="n">
         <v>3075239</v>
@@ -41288,7 +41288,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.91843223571777</v>
+        <v>3.91843199729919</v>
       </c>
       <c r="H1411" t="n">
         <v>1704307</v>
@@ -41346,7 +41346,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.84861016273499</v>
+        <v>3.84861040115356</v>
       </c>
       <c r="H1413" t="n">
         <v>2048783</v>
@@ -41375,7 +41375,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.88814830780029</v>
+        <v>3.88814854621887</v>
       </c>
       <c r="H1414" t="n">
         <v>1677966</v>
@@ -41462,7 +41462,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.91843223571777</v>
+        <v>3.91843199729919</v>
       </c>
       <c r="H1417" t="n">
         <v>1704997</v>
@@ -41491,7 +41491,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.99414253234863</v>
+        <v>3.99414277076721</v>
       </c>
       <c r="H1418" t="n">
         <v>1526178</v>
@@ -41520,7 +41520,7 @@
         <v>4.72100019454956</v>
       </c>
       <c r="G1419" t="n">
-        <v>3.9714298248291</v>
+        <v>3.97142934799194</v>
       </c>
       <c r="H1419" t="n">
         <v>1366810</v>
@@ -41549,7 +41549,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.12285041809082</v>
+        <v>4.12284994125366</v>
       </c>
       <c r="H1420" t="n">
         <v>2875219</v>
@@ -41636,7 +41636,7 @@
         <v>4.90299987792969</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.12453269958496</v>
+        <v>4.12453317642212</v>
       </c>
       <c r="H1423" t="n">
         <v>2276972</v>
@@ -41665,7 +41665,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G1424" t="n">
-        <v>4.02358531951904</v>
+        <v>4.0235857963562</v>
       </c>
       <c r="H1424" t="n">
         <v>2609423</v>
@@ -41694,7 +41694,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.15145206451416</v>
+        <v>4.151451587677</v>
       </c>
       <c r="H1425" t="n">
         <v>3827861</v>
@@ -41723,7 +41723,7 @@
         <v>4.8289999961853</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.0622820854187</v>
+        <v>4.06228160858154</v>
       </c>
       <c r="H1426" t="n">
         <v>2187359</v>
@@ -41752,7 +41752,7 @@
         <v>4.83099985122681</v>
       </c>
       <c r="G1427" t="n">
-        <v>4.06396436691284</v>
+        <v>4.06396484375</v>
       </c>
       <c r="H1427" t="n">
         <v>1218784</v>
@@ -41810,7 +41810,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G1429" t="n">
-        <v>4.08331203460693</v>
+        <v>4.08331251144409</v>
       </c>
       <c r="H1429" t="n">
         <v>1540854</v>
@@ -41926,7 +41926,7 @@
         <v>4.58699989318848</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.8587052822113</v>
+        <v>3.85870552062988</v>
       </c>
       <c r="H1433" t="n">
         <v>4586945</v>
@@ -41955,7 +41955,7 @@
         <v>4.51900005340576</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.80150175094604</v>
+        <v>3.80150151252747</v>
       </c>
       <c r="H1434" t="n">
         <v>2626813</v>
@@ -41984,7 +41984,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.87468791007996</v>
+        <v>3.87468814849854</v>
       </c>
       <c r="H1435" t="n">
         <v>1604844</v>
@@ -42013,7 +42013,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.83262729644775</v>
+        <v>3.83262705802917</v>
       </c>
       <c r="H1436" t="n">
         <v>884691</v>
@@ -42042,7 +42042,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.82758021354675</v>
+        <v>3.82757997512817</v>
       </c>
       <c r="H1437" t="n">
         <v>765125</v>
@@ -42071,7 +42071,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.70812582969666</v>
+        <v>3.70812559127808</v>
       </c>
       <c r="H1438" t="n">
         <v>3983574</v>
@@ -42100,7 +42100,7 @@
         <v>4.46700000762939</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.75775790214539</v>
+        <v>3.75775814056396</v>
       </c>
       <c r="H1439" t="n">
         <v>1252337</v>
@@ -42129,7 +42129,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.87468791007996</v>
+        <v>3.87468814849854</v>
       </c>
       <c r="H1440" t="n">
         <v>1471923</v>
@@ -42158,7 +42158,7 @@
         <v>4.58300018310547</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.85534071922302</v>
+        <v>3.85534048080444</v>
       </c>
       <c r="H1441" t="n">
         <v>1250531</v>
@@ -42187,7 +42187,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.82337355613708</v>
+        <v>3.82337403297424</v>
       </c>
       <c r="H1442" t="n">
         <v>2119319</v>
@@ -42216,7 +42216,7 @@
         <v>4.49900007247925</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.78467702865601</v>
+        <v>3.78467726707458</v>
       </c>
       <c r="H1443" t="n">
         <v>2947860</v>
@@ -42303,7 +42303,7 @@
         <v>4.64300012588501</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.90581393241882</v>
+        <v>3.90581369400024</v>
       </c>
       <c r="H1446" t="n">
         <v>2353807</v>
@@ -42361,7 +42361,7 @@
         <v>4.67899990081787</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.93609809875488</v>
+        <v>3.93609762191772</v>
       </c>
       <c r="H1448" t="n">
         <v>1534277</v>
@@ -42390,7 +42390,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.90917825698853</v>
+        <v>3.90917873382568</v>
       </c>
       <c r="H1449" t="n">
         <v>1323793</v>
@@ -42419,7 +42419,7 @@
         <v>4.61899995803833</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.88562417030334</v>
+        <v>3.88562393188477</v>
       </c>
       <c r="H1450" t="n">
         <v>3112143</v>
@@ -42535,7 +42535,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.74345684051514</v>
+        <v>3.74345707893372</v>
       </c>
       <c r="H1454" t="n">
         <v>3310751</v>
@@ -42564,7 +42564,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.70307850837708</v>
+        <v>3.7030782699585</v>
       </c>
       <c r="H1455" t="n">
         <v>1346674</v>
@@ -42622,7 +42622,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.74345684051514</v>
+        <v>3.74345707893372</v>
       </c>
       <c r="H1457" t="n">
         <v>1671361</v>
@@ -42651,7 +42651,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.78131198883057</v>
+        <v>3.78131246566772</v>
       </c>
       <c r="H1458" t="n">
         <v>2078424</v>
@@ -42680,7 +42680,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.78383660316467</v>
+        <v>3.78383612632751</v>
       </c>
       <c r="H1459" t="n">
         <v>2243918</v>
@@ -42709,7 +42709,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.80570840835571</v>
+        <v>3.80570816993713</v>
       </c>
       <c r="H1460" t="n">
         <v>2202383</v>
@@ -42883,7 +42883,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.76364660263062</v>
+        <v>3.76364684104919</v>
       </c>
       <c r="H1466" t="n">
         <v>1255557</v>
@@ -42912,7 +42912,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.81411981582642</v>
+        <v>3.814120054245</v>
       </c>
       <c r="H1467" t="n">
         <v>1845430</v>
@@ -42999,7 +42999,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.95544648170471</v>
+        <v>3.95544624328613</v>
       </c>
       <c r="H1470" t="n">
         <v>1507196</v>
@@ -43028,7 +43028,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.90917825698853</v>
+        <v>3.90917873382568</v>
       </c>
       <c r="H1471" t="n">
         <v>2049781</v>
@@ -43144,7 +43144,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.07153606414795</v>
+        <v>4.07153558731079</v>
       </c>
       <c r="H1475" t="n">
         <v>4038631</v>
@@ -43202,7 +43202,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.18869543075562</v>
+        <v>4.18869590759277</v>
       </c>
       <c r="H1477" t="n">
         <v>2499975</v>
@@ -43231,7 +43231,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G1478" t="n">
-        <v>4.15081691741943</v>
+        <v>4.15081644058228</v>
       </c>
       <c r="H1478" t="n">
         <v>2122933</v>
@@ -43318,7 +43318,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1481" t="n">
-        <v>4.27238082885742</v>
+        <v>4.27238178253174</v>
       </c>
       <c r="H1481" t="n">
         <v>2743673</v>
@@ -43347,7 +43347,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.29880905151367</v>
+        <v>4.29880809783936</v>
       </c>
       <c r="H1482" t="n">
         <v>1983741</v>
@@ -43376,7 +43376,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1483" t="n">
-        <v>4.27238082885742</v>
+        <v>4.27238178253174</v>
       </c>
       <c r="H1483" t="n">
         <v>1777355</v>
@@ -43405,7 +43405,7 @@
         <v>4.76800012588501</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.20014762878418</v>
+        <v>4.20014715194702</v>
       </c>
       <c r="H1484" t="n">
         <v>1653824</v>
@@ -43492,7 +43492,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.07858228683472</v>
+        <v>4.07858324050903</v>
       </c>
       <c r="H1487" t="n">
         <v>1319825</v>
@@ -43521,7 +43521,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07065439224243</v>
+        <v>4.07065391540527</v>
       </c>
       <c r="H1488" t="n">
         <v>1702173</v>
@@ -43579,7 +43579,7 @@
         <v>4.51399993896484</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.97639751434326</v>
+        <v>3.97639775276184</v>
       </c>
       <c r="H1490" t="n">
         <v>1662173</v>
@@ -43637,7 +43637,7 @@
         <v>4.56899976730347</v>
       </c>
       <c r="G1492" t="n">
-        <v>4.02484703063965</v>
+        <v>4.02484750747681</v>
       </c>
       <c r="H1492" t="n">
         <v>1283800</v>
@@ -43666,7 +43666,7 @@
         <v>4.55100011825562</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.00899171829224</v>
+        <v>4.00899124145508</v>
       </c>
       <c r="H1493" t="n">
         <v>1228749</v>
@@ -43695,7 +43695,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1494" t="n">
-        <v>4.0045862197876</v>
+        <v>4.00458669662476</v>
       </c>
       <c r="H1494" t="n">
         <v>1374433</v>
@@ -43724,7 +43724,7 @@
         <v>4.51700019836426</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.97904086112976</v>
+        <v>3.97904062271118</v>
       </c>
       <c r="H1495" t="n">
         <v>1434114</v>
@@ -43753,7 +43753,7 @@
         <v>4.50699996948242</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.97023129463196</v>
+        <v>3.97023153305054</v>
       </c>
       <c r="H1496" t="n">
         <v>930525</v>
@@ -43782,7 +43782,7 @@
         <v>4.49700021743774</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.96142244338989</v>
+        <v>3.96142268180847</v>
       </c>
       <c r="H1497" t="n">
         <v>1277113</v>
@@ -43869,7 +43869,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.99401593208313</v>
+        <v>3.99401617050171</v>
       </c>
       <c r="H1500" t="n">
         <v>794751</v>
@@ -43927,7 +43927,7 @@
         <v>4.58099985122681</v>
       </c>
       <c r="G1502" t="n">
-        <v>4.03541803359985</v>
+        <v>4.03541851043701</v>
       </c>
       <c r="H1502" t="n">
         <v>1449451</v>
@@ -43956,7 +43956,7 @@
         <v>4.60699987411499</v>
       </c>
       <c r="G1503" t="n">
-        <v>4.05832195281982</v>
+        <v>4.05832147598267</v>
       </c>
       <c r="H1503" t="n">
         <v>1868954</v>
@@ -44043,7 +44043,7 @@
         <v>4.73299980163574</v>
       </c>
       <c r="G1506" t="n">
-        <v>4.16931533813477</v>
+        <v>4.16931581497192</v>
       </c>
       <c r="H1506" t="n">
         <v>2129245</v>
@@ -44246,7 +44246,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1513" t="n">
-        <v>4.18252897262573</v>
+        <v>4.18252944946289</v>
       </c>
       <c r="H1513" t="n">
         <v>2073053</v>
@@ -44304,7 +44304,7 @@
         <v>4.68900012969971</v>
       </c>
       <c r="G1515" t="n">
-        <v>4.13055610656738</v>
+        <v>4.13055658340454</v>
       </c>
       <c r="H1515" t="n">
         <v>1251667</v>
@@ -44362,7 +44362,7 @@
         <v>4.85300016403198</v>
       </c>
       <c r="G1517" t="n">
-        <v>4.2750244140625</v>
+        <v>4.27502393722534</v>
       </c>
       <c r="H1517" t="n">
         <v>2245748</v>
@@ -44391,7 +44391,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G1518" t="n">
-        <v>4.26004934310913</v>
+        <v>4.26004886627197</v>
       </c>
       <c r="H1518" t="n">
         <v>2157314</v>
@@ -44536,7 +44536,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1523" t="n">
-        <v>4.01868152618408</v>
+        <v>4.01868104934692</v>
       </c>
       <c r="H1523" t="n">
         <v>3026688</v>
@@ -44565,7 +44565,7 @@
         <v>4.56099987030029</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.01780033111572</v>
+        <v>4.01779985427856</v>
       </c>
       <c r="H1524" t="n">
         <v>1977623</v>
@@ -44594,7 +44594,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.94468569755554</v>
+        <v>3.94468545913696</v>
       </c>
       <c r="H1525" t="n">
         <v>1481934</v>
@@ -44623,7 +44623,7 @@
         <v>4.44399976730347</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.91473412513733</v>
+        <v>3.91473436355591</v>
       </c>
       <c r="H1526" t="n">
         <v>1426451</v>
@@ -44652,7 +44652,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.87157034873962</v>
+        <v>3.87157011032104</v>
       </c>
       <c r="H1527" t="n">
         <v>1882131</v>
@@ -44768,7 +44768,7 @@
         <v>4.44299983978271</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.91385364532471</v>
+        <v>3.91385388374329</v>
       </c>
       <c r="H1531" t="n">
         <v>2329729</v>
@@ -44797,7 +44797,7 @@
         <v>4.47100019454956</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.93851947784424</v>
+        <v>3.93851900100708</v>
       </c>
       <c r="H1532" t="n">
         <v>1809355</v>
@@ -44855,7 +44855,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.87597489356995</v>
+        <v>3.87597513198853</v>
       </c>
       <c r="H1534" t="n">
         <v>2153280</v>
@@ -44913,7 +44913,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.95349407196045</v>
+        <v>3.95349454879761</v>
       </c>
       <c r="H1536" t="n">
         <v>1423494</v>
@@ -44942,7 +44942,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.92530512809753</v>
+        <v>3.92530536651611</v>
       </c>
       <c r="H1537" t="n">
         <v>1819378</v>
@@ -44971,7 +44971,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.84073853492737</v>
+        <v>3.84073901176453</v>
       </c>
       <c r="H1538" t="n">
         <v>1558430</v>
@@ -45029,7 +45029,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.66455793380737</v>
+        <v>3.66455817222595</v>
       </c>
       <c r="H1540" t="n">
         <v>4026623</v>
@@ -45087,7 +45087,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.58175301551819</v>
+        <v>3.58175325393677</v>
       </c>
       <c r="H1542" t="n">
         <v>2173862</v>
@@ -45116,7 +45116,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.62051296234131</v>
+        <v>3.62051320075989</v>
       </c>
       <c r="H1543" t="n">
         <v>2643345</v>
@@ -45145,7 +45145,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.58527708053589</v>
+        <v>3.58527684211731</v>
       </c>
       <c r="H1544" t="n">
         <v>2170665</v>
@@ -45232,7 +45232,7 @@
         <v>4.23299980163574</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.72886371612549</v>
+        <v>3.72886395454407</v>
       </c>
       <c r="H1547" t="n">
         <v>1519824</v>
@@ -45319,7 +45319,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.88302230834961</v>
+        <v>3.88302206993103</v>
       </c>
       <c r="H1550" t="n">
         <v>2097912</v>
@@ -45348,7 +45348,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.84073853492737</v>
+        <v>3.84073901176453</v>
       </c>
       <c r="H1551" t="n">
         <v>1258004</v>
@@ -45377,7 +45377,7 @@
         <v>4.44700002670288</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.91737747192383</v>
+        <v>3.91737723350525</v>
       </c>
       <c r="H1552" t="n">
         <v>1655213</v>
@@ -45435,7 +45435,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.88302230834961</v>
+        <v>3.88302206993103</v>
       </c>
       <c r="H1554" t="n">
         <v>2272215</v>
@@ -45464,7 +45464,7 @@
         <v>4.44099998474121</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.9120922088623</v>
+        <v>3.91209173202515</v>
       </c>
       <c r="H1555" t="n">
         <v>1441226</v>
@@ -45493,7 +45493,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.98961138725281</v>
+        <v>3.98961114883423</v>
       </c>
       <c r="H1556" t="n">
         <v>2208333</v>
@@ -45522,7 +45522,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.98961138725281</v>
+        <v>3.98961114883423</v>
       </c>
       <c r="H1557" t="n">
         <v>1771099</v>
@@ -45551,7 +45551,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.93587613105774</v>
+        <v>3.93587589263916</v>
       </c>
       <c r="H1558" t="n">
         <v>1690561</v>
@@ -45580,7 +45580,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1559" t="n">
-        <v>4.0045862197876</v>
+        <v>4.00458669662476</v>
       </c>
       <c r="H1559" t="n">
         <v>1818131</v>
@@ -45638,7 +45638,7 @@
         <v>4.46099996566772</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.92970967292786</v>
+        <v>3.92970991134644</v>
       </c>
       <c r="H1561" t="n">
         <v>1580647</v>
@@ -45783,7 +45783,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G1566" t="n">
-        <v>4.01339626312256</v>
+        <v>4.0133957862854</v>
       </c>
       <c r="H1566" t="n">
         <v>1288155</v>
@@ -45841,7 +45841,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G1568" t="n">
-        <v>4.0151572227478</v>
+        <v>4.01515769958496</v>
       </c>
       <c r="H1568" t="n">
         <v>2517345</v>
@@ -45870,7 +45870,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.01868152618408</v>
+        <v>4.01868104934692</v>
       </c>
       <c r="H1569" t="n">
         <v>2341666</v>
@@ -45899,7 +45899,7 @@
         <v>4.53299999237061</v>
       </c>
       <c r="G1570" t="n">
-        <v>3.99313497543335</v>
+        <v>3.99313521385193</v>
       </c>
       <c r="H1570" t="n">
         <v>2185657</v>
@@ -46044,7 +46044,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1575" t="n">
-        <v>4.24595403671265</v>
+        <v>4.2459545135498</v>
       </c>
       <c r="H1575" t="n">
         <v>1850014</v>
@@ -46131,7 +46131,7 @@
         <v>4.86100006103516</v>
       </c>
       <c r="G1578" t="n">
-        <v>4.28207159042358</v>
+        <v>4.28207111358643</v>
       </c>
       <c r="H1578" t="n">
         <v>3296575</v>
@@ -46160,7 +46160,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G1579" t="n">
-        <v>4.25123977661133</v>
+        <v>4.25123929977417</v>
       </c>
       <c r="H1579" t="n">
         <v>3303443</v>
@@ -46218,7 +46218,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G1581" t="n">
-        <v>4.23009824752808</v>
+        <v>4.23009777069092</v>
       </c>
       <c r="H1581" t="n">
         <v>1650758</v>
@@ -46334,7 +46334,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G1585" t="n">
-        <v>4.28823804855347</v>
+        <v>4.28823757171631</v>
       </c>
       <c r="H1585" t="n">
         <v>1267698</v>
@@ -46421,7 +46421,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G1588" t="n">
-        <v>4.34990119934082</v>
+        <v>4.34990167617798</v>
       </c>
       <c r="H1588" t="n">
         <v>1909391</v>
@@ -46450,7 +46450,7 @@
         <v>4.83099985122681</v>
       </c>
       <c r="G1589" t="n">
-        <v>4.25564432144165</v>
+        <v>4.25564384460449</v>
       </c>
       <c r="H1589" t="n">
         <v>1549886</v>
@@ -46479,7 +46479,7 @@
         <v>4.8439998626709</v>
       </c>
       <c r="G1590" t="n">
-        <v>4.2670955657959</v>
+        <v>4.26709604263306</v>
       </c>
       <c r="H1590" t="n">
         <v>892961</v>
@@ -46508,7 +46508,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G1591" t="n">
-        <v>4.26181030273438</v>
+        <v>4.26181077957153</v>
       </c>
       <c r="H1591" t="n">
         <v>1494436</v>
@@ -46537,7 +46537,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.39042282104492</v>
+        <v>4.39042234420776</v>
       </c>
       <c r="H1592" t="n">
         <v>2796389</v>
@@ -46595,7 +46595,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1594" t="n">
-        <v>4.56307935714722</v>
+        <v>4.56307888031006</v>
       </c>
       <c r="H1594" t="n">
         <v>2130981</v>
@@ -46624,7 +46624,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1595" t="n">
-        <v>4.69169139862061</v>
+        <v>4.69169187545776</v>
       </c>
       <c r="H1595" t="n">
         <v>3747916</v>
@@ -46653,7 +46653,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G1596" t="n">
-        <v>4.67231130599976</v>
+        <v>4.67231178283691</v>
       </c>
       <c r="H1596" t="n">
         <v>2803424</v>
@@ -46972,7 +46972,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1607" t="n">
-        <v>4.55427074432373</v>
+        <v>4.55427026748657</v>
       </c>
       <c r="H1607" t="n">
         <v>1167250</v>
@@ -47001,7 +47001,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G1608" t="n">
-        <v>4.52255773544312</v>
+        <v>4.52255725860596</v>
       </c>
       <c r="H1608" t="n">
         <v>4438145</v>
@@ -47030,7 +47030,7 @@
         <v>5.03800010681152</v>
       </c>
       <c r="G1609" t="n">
-        <v>4.43799114227295</v>
+        <v>4.43799161911011</v>
       </c>
       <c r="H1609" t="n">
         <v>3851369</v>
@@ -47059,7 +47059,7 @@
         <v>5.01399993896484</v>
       </c>
       <c r="G1610" t="n">
-        <v>4.4168496131897</v>
+        <v>4.41684913635254</v>
       </c>
       <c r="H1610" t="n">
         <v>1491742</v>
@@ -47117,7 +47117,7 @@
         <v>4.95800018310547</v>
       </c>
       <c r="G1612" t="n">
-        <v>4.36751937866211</v>
+        <v>4.36751890182495</v>
       </c>
       <c r="H1612" t="n">
         <v>1940262</v>
@@ -47233,7 +47233,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1616" t="n">
-        <v>4.70402431488037</v>
+        <v>4.70402383804321</v>
       </c>
       <c r="H1616" t="n">
         <v>1657968</v>
@@ -47262,7 +47262,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.74278402328491</v>
+        <v>4.74278354644775</v>
       </c>
       <c r="H1617" t="n">
         <v>1946543</v>
@@ -47378,7 +47378,7 @@
         <v>5.41800022125244</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.77273511886597</v>
+        <v>4.77273464202881</v>
       </c>
       <c r="H1621" t="n">
         <v>2110714</v>
@@ -47407,7 +47407,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G1622" t="n">
-        <v>4.68464374542236</v>
+        <v>4.68464422225952</v>
       </c>
       <c r="H1622" t="n">
         <v>1490417</v>
@@ -47494,7 +47494,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1625" t="n">
-        <v>4.77449607849121</v>
+        <v>4.77449655532837</v>
       </c>
       <c r="H1625" t="n">
         <v>1615810</v>
@@ -47523,7 +47523,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G1626" t="n">
-        <v>4.80268526077271</v>
+        <v>4.80268573760986</v>
       </c>
       <c r="H1626" t="n">
         <v>1557790</v>
@@ -47610,7 +47610,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.80620908737183</v>
+        <v>4.80620861053467</v>
       </c>
       <c r="H1629" t="n">
         <v>1140067</v>
@@ -47668,7 +47668,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1631" t="n">
-        <v>4.95948648452759</v>
+        <v>4.95948600769043</v>
       </c>
       <c r="H1631" t="n">
         <v>3400037</v>
@@ -47871,7 +47871,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G1638" t="n">
-        <v>4.71459484100342</v>
+        <v>4.71459531784058</v>
       </c>
       <c r="H1638" t="n">
         <v>2512138</v>
@@ -47958,7 +47958,7 @@
         <v>5.54400014877319</v>
       </c>
       <c r="G1641" t="n">
-        <v>4.88372850418091</v>
+        <v>4.88372802734375</v>
       </c>
       <c r="H1641" t="n">
         <v>4579164</v>
@@ -48016,7 +48016,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1643" t="n">
-        <v>4.91720199584961</v>
+        <v>4.91720247268677</v>
       </c>
       <c r="H1643" t="n">
         <v>1157047</v>
@@ -48045,7 +48045,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G1644" t="n">
-        <v>4.89606142044067</v>
+        <v>4.89606094360352</v>
       </c>
       <c r="H1644" t="n">
         <v>1403328</v>
@@ -48074,7 +48074,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1645" t="n">
-        <v>4.93305921554565</v>
+        <v>4.9330587387085</v>
       </c>
       <c r="H1645" t="n">
         <v>1639165</v>
@@ -48103,7 +48103,7 @@
         <v>5.58599996566772</v>
       </c>
       <c r="G1646" t="n">
-        <v>4.92072677612305</v>
+        <v>4.92072629928589</v>
       </c>
       <c r="H1646" t="n">
         <v>1267120</v>
@@ -48132,7 +48132,7 @@
         <v>5.65399980545044</v>
       </c>
       <c r="G1647" t="n">
-        <v>4.98062705993652</v>
+        <v>4.98062753677368</v>
       </c>
       <c r="H1647" t="n">
         <v>1454661</v>
@@ -48161,7 +48161,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1648" t="n">
-        <v>4.97358083724976</v>
+        <v>4.97357988357544</v>
       </c>
       <c r="H1648" t="n">
         <v>1355402</v>
@@ -48248,7 +48248,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1651" t="n">
-        <v>4.97358083724976</v>
+        <v>4.97357988357544</v>
       </c>
       <c r="H1651" t="n">
         <v>1114962</v>
@@ -48596,7 +48596,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1663" t="n">
-        <v>5.17090272903442</v>
+        <v>5.17090320587158</v>
       </c>
       <c r="H1663" t="n">
         <v>1114408</v>
@@ -48625,7 +48625,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1664" t="n">
-        <v>5.12333345413208</v>
+        <v>5.1233344078064</v>
       </c>
       <c r="H1664" t="n">
         <v>1446906</v>
@@ -48683,7 +48683,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G1666" t="n">
-        <v>5.27484941482544</v>
+        <v>5.27484893798828</v>
       </c>
       <c r="H1666" t="n">
         <v>1580963</v>
@@ -48799,7 +48799,7 @@
         <v>6</v>
       </c>
       <c r="G1670" t="n">
-        <v>5.28542041778564</v>
+        <v>5.28541994094849</v>
       </c>
       <c r="H1670" t="n">
         <v>1014951</v>
@@ -48886,7 +48886,7 @@
         <v>6.00400018692017</v>
       </c>
       <c r="G1673" t="n">
-        <v>5.28894424438477</v>
+        <v>5.28894376754761</v>
       </c>
       <c r="H1673" t="n">
         <v>1425999</v>
@@ -48973,7 +48973,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G1676" t="n">
-        <v>5.29951429367065</v>
+        <v>5.29951477050781</v>
       </c>
       <c r="H1676" t="n">
         <v>2412084</v>
@@ -49002,7 +49002,7 @@
         <v>6.06799983978271</v>
       </c>
       <c r="G1677" t="n">
-        <v>5.34532117843628</v>
+        <v>5.34532165527344</v>
       </c>
       <c r="H1677" t="n">
         <v>966171</v>
@@ -49060,7 +49060,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1679" t="n">
-        <v>5.46160078048706</v>
+        <v>5.4616003036499</v>
       </c>
       <c r="H1679" t="n">
         <v>1683821</v>
@@ -49147,7 +49147,7 @@
         <v>6.11399984359741</v>
       </c>
       <c r="G1682" t="n">
-        <v>5.38584280014038</v>
+        <v>5.38584327697754</v>
       </c>
       <c r="H1682" t="n">
         <v>1142528</v>
@@ -49234,7 +49234,7 @@
         <v>6</v>
       </c>
       <c r="G1685" t="n">
-        <v>5.28542041778564</v>
+        <v>5.28541994094849</v>
       </c>
       <c r="H1685" t="n">
         <v>2107517</v>
@@ -49263,7 +49263,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G1686" t="n">
-        <v>5.36470127105713</v>
+        <v>5.36470174789429</v>
       </c>
       <c r="H1686" t="n">
         <v>2071456</v>
@@ -49350,7 +49350,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G1689" t="n">
-        <v>5.41403150558472</v>
+        <v>5.41403198242188</v>
       </c>
       <c r="H1689" t="n">
         <v>818217</v>
@@ -49379,7 +49379,7 @@
         <v>6.17399978637695</v>
       </c>
       <c r="G1690" t="n">
-        <v>5.43869686126709</v>
+        <v>5.43869733810425</v>
       </c>
       <c r="H1690" t="n">
         <v>1569252</v>
@@ -49495,7 +49495,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G1694" t="n">
-        <v>5.29775285720825</v>
+        <v>5.29775333404541</v>
       </c>
       <c r="H1694" t="n">
         <v>3090297</v>
@@ -49524,7 +49524,7 @@
         <v>5.97599983215332</v>
       </c>
       <c r="G1695" t="n">
-        <v>5.26427888870239</v>
+        <v>5.26427841186523</v>
       </c>
       <c r="H1695" t="n">
         <v>3842448</v>
@@ -49553,7 +49553,7 @@
         <v>5.94399976730347</v>
       </c>
       <c r="G1696" t="n">
-        <v>5.2360897064209</v>
+        <v>5.23608922958374</v>
       </c>
       <c r="H1696" t="n">
         <v>3447151</v>
@@ -49582,7 +49582,7 @@
         <v>6.0460000038147</v>
       </c>
       <c r="G1697" t="n">
-        <v>5.32594156265259</v>
+        <v>5.32594203948975</v>
       </c>
       <c r="H1697" t="n">
         <v>2203107</v>
@@ -49611,7 +49611,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1698" t="n">
-        <v>5.32946586608887</v>
+        <v>5.32946538925171</v>
       </c>
       <c r="H1698" t="n">
         <v>1405206</v>
@@ -49698,7 +49698,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G1701" t="n">
-        <v>5.29951429367065</v>
+        <v>5.29951477050781</v>
       </c>
       <c r="H1701" t="n">
         <v>2215181</v>
@@ -49814,7 +49814,7 @@
         <v>5.86199998855591</v>
       </c>
       <c r="G1705" t="n">
-        <v>5.16385555267334</v>
+        <v>5.1638560295105</v>
       </c>
       <c r="H1705" t="n">
         <v>2675380</v>
@@ -49843,7 +49843,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1706" t="n">
-        <v>5.13566637039185</v>
+        <v>5.135666847229</v>
       </c>
       <c r="H1706" t="n">
         <v>1336134</v>
@@ -50046,7 +50046,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1713" t="n">
-        <v>5.07062578201294</v>
+        <v>5.07062530517578</v>
       </c>
       <c r="H1713" t="n">
         <v>1930745</v>
@@ -50075,7 +50075,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1714" t="n">
-        <v>5.12169694900513</v>
+        <v>5.12169647216797</v>
       </c>
       <c r="H1714" t="n">
         <v>1367400</v>
@@ -50104,7 +50104,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1715" t="n">
-        <v>5.02137851715088</v>
+        <v>5.02137899398804</v>
       </c>
       <c r="H1715" t="n">
         <v>2554508</v>
@@ -50191,7 +50191,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G1718" t="n">
-        <v>5.16547203063965</v>
+        <v>5.16547155380249</v>
       </c>
       <c r="H1718" t="n">
         <v>1115062</v>
@@ -50249,7 +50249,7 @@
         <v>5.57399988174438</v>
       </c>
       <c r="G1720" t="n">
-        <v>5.08339357376099</v>
+        <v>5.08339309692383</v>
       </c>
       <c r="H1720" t="n">
         <v>1066536</v>
@@ -50278,7 +50278,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1721" t="n">
-        <v>5.14905643463135</v>
+        <v>5.14905595779419</v>
       </c>
       <c r="H1721" t="n">
         <v>1309301</v>
@@ -50336,7 +50336,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1723" t="n">
-        <v>5.22931098937988</v>
+        <v>5.22931051254272</v>
       </c>
       <c r="H1723" t="n">
         <v>1073822</v>
@@ -50394,7 +50394,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1725" t="n">
-        <v>5.25484657287598</v>
+        <v>5.25484609603882</v>
       </c>
       <c r="H1725" t="n">
         <v>1815362</v>
@@ -50597,7 +50597,7 @@
         <v>5.75</v>
       </c>
       <c r="G1732" t="n">
-        <v>5.24390268325806</v>
+        <v>5.2439022064209</v>
       </c>
       <c r="H1732" t="n">
         <v>2383059</v>
@@ -50626,7 +50626,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1733" t="n">
-        <v>5.30774164199829</v>
+        <v>5.30774116516113</v>
       </c>
       <c r="H1733" t="n">
         <v>1419417</v>
@@ -50655,7 +50655,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1734" t="n">
-        <v>5.2657904624939</v>
+        <v>5.26578998565674</v>
       </c>
       <c r="H1734" t="n">
         <v>1263754</v>
@@ -50742,7 +50742,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1737" t="n">
-        <v>5.07062578201294</v>
+        <v>5.07062530517578</v>
       </c>
       <c r="H1737" t="n">
         <v>2008071</v>
@@ -50771,7 +50771,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1738" t="n">
-        <v>4.97760391235352</v>
+        <v>4.97760343551636</v>
       </c>
       <c r="H1738" t="n">
         <v>2945125</v>
@@ -50829,7 +50829,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G1740" t="n">
-        <v>4.7496075630188</v>
+        <v>4.74960803985596</v>
       </c>
       <c r="H1740" t="n">
         <v>1995582</v>
@@ -50945,7 +50945,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G1744" t="n">
-        <v>4.78426265716553</v>
+        <v>4.78426313400269</v>
       </c>
       <c r="H1744" t="n">
         <v>872180</v>
@@ -51061,7 +51061,7 @@
         <v>5.38199996948242</v>
       </c>
       <c r="G1748" t="n">
-        <v>4.90829229354858</v>
+        <v>4.90829277038574</v>
       </c>
       <c r="H1748" t="n">
         <v>707574</v>
@@ -51119,7 +51119,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1750" t="n">
-        <v>4.94294786453247</v>
+        <v>4.94294834136963</v>
       </c>
       <c r="H1750" t="n">
         <v>1233465</v>
@@ -51206,7 +51206,7 @@
         <v>5.43200016021729</v>
       </c>
       <c r="G1753" t="n">
-        <v>4.95389223098755</v>
+        <v>4.95389175415039</v>
       </c>
       <c r="H1753" t="n">
         <v>598372</v>
@@ -51351,7 +51351,7 @@
         <v>5.52799987792969</v>
       </c>
       <c r="G1758" t="n">
-        <v>5.04144239425659</v>
+        <v>5.04144191741943</v>
       </c>
       <c r="H1758" t="n">
         <v>749729</v>
@@ -51409,7 +51409,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1760" t="n">
-        <v>4.99584293365479</v>
+        <v>4.99584341049194</v>
       </c>
       <c r="H1760" t="n">
         <v>1110795</v>
@@ -51612,7 +51612,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1767" t="n">
-        <v>4.9611873626709</v>
+        <v>4.96118783950806</v>
       </c>
       <c r="H1767" t="n">
         <v>871216</v>
@@ -51670,7 +51670,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G1769" t="n">
-        <v>4.92106008529663</v>
+        <v>4.92106056213379</v>
       </c>
       <c r="H1769" t="n">
         <v>1142507</v>
@@ -51902,7 +51902,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1777" t="n">
-        <v>5.07062578201294</v>
+        <v>5.07062530517578</v>
       </c>
       <c r="H1777" t="n">
         <v>1639161</v>
@@ -51989,7 +51989,7 @@
         <v>5.21199989318848</v>
       </c>
       <c r="G1780" t="n">
-        <v>4.75325584411621</v>
+        <v>4.75325536727905</v>
       </c>
       <c r="H1780" t="n">
         <v>7817931</v>
@@ -52134,7 +52134,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G1785" t="n">
-        <v>4.89552450180054</v>
+        <v>4.8955249786377</v>
       </c>
       <c r="H1785" t="n">
         <v>1946243</v>
@@ -52308,7 +52308,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G1791" t="n">
-        <v>4.87546157836914</v>
+        <v>4.87546110153198</v>
       </c>
       <c r="H1791" t="n">
         <v>1464698</v>
@@ -52424,7 +52424,7 @@
         <v>5.24399995803833</v>
       </c>
       <c r="G1795" t="n">
-        <v>4.78243923187256</v>
+        <v>4.7824387550354</v>
       </c>
       <c r="H1795" t="n">
         <v>1922209</v>
@@ -52482,7 +52482,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1797" t="n">
-        <v>4.7167763710022</v>
+        <v>4.71677589416504</v>
       </c>
       <c r="H1797" t="n">
         <v>1952792</v>
@@ -52511,7 +52511,7 @@
         <v>5.15799999237061</v>
       </c>
       <c r="G1798" t="n">
-        <v>4.70400857925415</v>
+        <v>4.70400810241699</v>
       </c>
       <c r="H1798" t="n">
         <v>2608346</v>
@@ -52540,7 +52540,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1799" t="n">
-        <v>4.6201057434082</v>
+        <v>4.62010622024536</v>
       </c>
       <c r="H1799" t="n">
         <v>2142638</v>
@@ -52627,7 +52627,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1802" t="n">
-        <v>4.6201057434082</v>
+        <v>4.62010622024536</v>
       </c>
       <c r="H1802" t="n">
         <v>1304150</v>
@@ -52772,7 +52772,7 @@
         <v>5.10400009155273</v>
       </c>
       <c r="G1807" t="n">
-        <v>4.65476131439209</v>
+        <v>4.65476179122925</v>
       </c>
       <c r="H1807" t="n">
         <v>7182672</v>
@@ -52801,7 +52801,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1808" t="n">
-        <v>4.7167763710022</v>
+        <v>4.71677589416504</v>
       </c>
       <c r="H1808" t="n">
         <v>3272568</v>
@@ -52859,7 +52859,7 @@
         <v>4.96700000762939</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.52981948852539</v>
+        <v>4.52981996536255</v>
       </c>
       <c r="H1810" t="n">
         <v>3621056</v>
@@ -52888,7 +52888,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G1811" t="n">
-        <v>4.63469791412354</v>
+        <v>4.63469743728638</v>
       </c>
       <c r="H1811" t="n">
         <v>2020220</v>
@@ -53004,7 +53004,7 @@
         <v>5.16599988937378</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.71130418777466</v>
+        <v>4.71130466461182</v>
       </c>
       <c r="H1815" t="n">
         <v>3075470</v>
@@ -53062,7 +53062,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.7167763710022</v>
+        <v>4.71677589416504</v>
       </c>
       <c r="H1817" t="n">
         <v>1675292</v>
@@ -53207,7 +53207,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G1822" t="n">
-        <v>4.68212080001831</v>
+        <v>4.68212032318115</v>
       </c>
       <c r="H1822" t="n">
         <v>1423087</v>
@@ -53294,7 +53294,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G1825" t="n">
-        <v>4.78426265716553</v>
+        <v>4.78426313400269</v>
       </c>
       <c r="H1825" t="n">
         <v>2341827</v>
@@ -53352,7 +53352,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.87546157836914</v>
+        <v>4.87546110153198</v>
       </c>
       <c r="H1827" t="n">
         <v>1570389</v>
@@ -53381,7 +53381,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G1828" t="n">
-        <v>4.92106008529663</v>
+        <v>4.92106056213379</v>
       </c>
       <c r="H1828" t="n">
         <v>1505172</v>
@@ -53555,7 +53555,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1834" t="n">
-        <v>5.02137851715088</v>
+        <v>5.02137899398804</v>
       </c>
       <c r="H1834" t="n">
         <v>2061632</v>
@@ -53584,7 +53584,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1835" t="n">
-        <v>5.04326629638672</v>
+        <v>5.04326677322388</v>
       </c>
       <c r="H1835" t="n">
         <v>1605046</v>
@@ -53671,7 +53671,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.97760391235352</v>
+        <v>4.97760343551636</v>
       </c>
       <c r="H1838" t="n">
         <v>1222379</v>
@@ -53729,7 +53729,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.99219512939453</v>
+        <v>4.99219465255737</v>
       </c>
       <c r="H1840" t="n">
         <v>1067550</v>
@@ -53903,7 +53903,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1846" t="n">
-        <v>5.09068870544434</v>
+        <v>5.09068918228149</v>
       </c>
       <c r="H1846" t="n">
         <v>2122240</v>
@@ -53932,7 +53932,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1847" t="n">
-        <v>5.09616136550903</v>
+        <v>5.09616088867188</v>
       </c>
       <c r="H1847" t="n">
         <v>1601324</v>
@@ -53961,7 +53961,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1848" t="n">
-        <v>5.07062578201294</v>
+        <v>5.07062530517578</v>
       </c>
       <c r="H1848" t="n">
         <v>1113736</v>
@@ -53990,7 +53990,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1849" t="n">
-        <v>5.18006324768066</v>
+        <v>5.18006372451782</v>
       </c>
       <c r="H1849" t="n">
         <v>4393306</v>
@@ -54048,7 +54048,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1851" t="n">
-        <v>5.22931098937988</v>
+        <v>5.22931051254272</v>
       </c>
       <c r="H1851" t="n">
         <v>2082674</v>
@@ -54135,7 +54135,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1854" t="n">
-        <v>5.23843002319336</v>
+        <v>5.23843050003052</v>
       </c>
       <c r="H1854" t="n">
         <v>1638683</v>
@@ -54193,7 +54193,7 @@
         <v>5.82800006866455</v>
       </c>
       <c r="G1856" t="n">
-        <v>5.31503677368164</v>
+        <v>5.3150372505188</v>
       </c>
       <c r="H1856" t="n">
         <v>2461456</v>
@@ -54222,7 +54222,7 @@
         <v>5.85200023651123</v>
       </c>
       <c r="G1857" t="n">
-        <v>5.33692502975464</v>
+        <v>5.33692455291748</v>
       </c>
       <c r="H1857" t="n">
         <v>1917532</v>
@@ -54309,7 +54309,7 @@
         <v>5.78200006484985</v>
       </c>
       <c r="G1860" t="n">
-        <v>5.2730860710144</v>
+        <v>5.27308559417725</v>
       </c>
       <c r="H1860" t="n">
         <v>1153715</v>
@@ -54396,7 +54396,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1863" t="n">
-        <v>5.13263988494873</v>
+        <v>5.13264036178589</v>
       </c>
       <c r="H1863" t="n">
         <v>6863661</v>
@@ -54425,7 +54425,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1864" t="n">
-        <v>5.10710525512695</v>
+        <v>5.10710477828979</v>
       </c>
       <c r="H1864" t="n">
         <v>1749750</v>
@@ -54454,7 +54454,7 @@
         <v>5.53800010681152</v>
       </c>
       <c r="G1865" t="n">
-        <v>5.05056190490723</v>
+        <v>5.05056238174438</v>
       </c>
       <c r="H1865" t="n">
         <v>1856112</v>
@@ -54483,7 +54483,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1866" t="n">
-        <v>5.10710525512695</v>
+        <v>5.10710477828979</v>
       </c>
       <c r="H1866" t="n">
         <v>1134560</v>
@@ -54541,7 +54541,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1868" t="n">
-        <v>5.10710525512695</v>
+        <v>5.10710477828979</v>
       </c>
       <c r="H1868" t="n">
         <v>1623973</v>
@@ -54570,7 +54570,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1869" t="n">
-        <v>5.14358425140381</v>
+        <v>5.14358377456665</v>
       </c>
       <c r="H1869" t="n">
         <v>1888128</v>
@@ -54628,7 +54628,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G1871" t="n">
-        <v>5.24572610855103</v>
+        <v>5.24572658538818</v>
       </c>
       <c r="H1871" t="n">
         <v>2824097</v>
@@ -54773,7 +54773,7 @@
         <v>5.72800016403198</v>
       </c>
       <c r="G1876" t="n">
-        <v>5.22383880615234</v>
+        <v>5.2238392829895</v>
       </c>
       <c r="H1876" t="n">
         <v>1322234</v>
@@ -54889,7 +54889,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1880" t="n">
-        <v>5.30774164199829</v>
+        <v>5.30774116516113</v>
       </c>
       <c r="H1880" t="n">
         <v>1628098</v>
@@ -54947,7 +54947,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G1882" t="n">
-        <v>5.50290584564209</v>
+        <v>5.50290536880493</v>
       </c>
       <c r="H1882" t="n">
         <v>3694253</v>
@@ -55005,7 +55005,7 @@
         <v>5.75</v>
       </c>
       <c r="G1884" t="n">
-        <v>5.24390268325806</v>
+        <v>5.2439022064209</v>
       </c>
       <c r="H1884" t="n">
         <v>4531783</v>
@@ -55063,7 +55063,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1886" t="n">
-        <v>5.30774164199829</v>
+        <v>5.30774116516113</v>
       </c>
       <c r="H1886" t="n">
         <v>3842206</v>
@@ -55092,7 +55092,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1887" t="n">
-        <v>5.14905643463135</v>
+        <v>5.14905595779419</v>
       </c>
       <c r="H1887" t="n">
         <v>4539598</v>
@@ -55121,7 +55121,7 @@
         <v>5.66599988937378</v>
       </c>
       <c r="G1888" t="n">
-        <v>5.16729545593262</v>
+        <v>5.16729593276978</v>
       </c>
       <c r="H1888" t="n">
         <v>3363922</v>
@@ -55150,7 +55150,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1889" t="n">
-        <v>5.12169694900513</v>
+        <v>5.12169647216797</v>
       </c>
       <c r="H1889" t="n">
         <v>3102908</v>
@@ -55208,7 +55208,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1891" t="n">
-        <v>5.25484657287598</v>
+        <v>5.25484609603882</v>
       </c>
       <c r="H1891" t="n">
         <v>2244420</v>
@@ -55237,7 +55237,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G1892" t="n">
-        <v>5.40258741378784</v>
+        <v>5.40258693695068</v>
       </c>
       <c r="H1892" t="n">
         <v>2940061</v>
@@ -55295,7 +55295,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1894" t="n">
-        <v>5.40441131591797</v>
+        <v>5.40441179275513</v>
       </c>
       <c r="H1894" t="n">
         <v>1732424</v>
@@ -55324,7 +55324,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1895" t="n">
-        <v>5.40441131591797</v>
+        <v>5.40441179275513</v>
       </c>
       <c r="H1895" t="n">
         <v>1130769</v>
@@ -55382,7 +55382,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1897" t="n">
-        <v>5.36246013641357</v>
+        <v>5.36246061325073</v>
       </c>
       <c r="H1897" t="n">
         <v>3402608</v>
@@ -55440,7 +55440,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G1899" t="n">
-        <v>5.24572610855103</v>
+        <v>5.24572658538818</v>
       </c>
       <c r="H1899" t="n">
         <v>5097268</v>
@@ -55469,7 +55469,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1900" t="n">
-        <v>5.09616136550903</v>
+        <v>5.09616088867188</v>
       </c>
       <c r="H1900" t="n">
         <v>4791696</v>
@@ -55556,7 +55556,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.99219512939453</v>
+        <v>4.99219465255737</v>
       </c>
       <c r="H1903" t="n">
         <v>2656525</v>
@@ -55614,7 +55614,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G1905" t="n">
-        <v>4.97577953338623</v>
+        <v>4.97577905654907</v>
       </c>
       <c r="H1905" t="n">
         <v>1974649</v>
@@ -55643,7 +55643,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.84262943267822</v>
+        <v>4.84262990951538</v>
       </c>
       <c r="H1906" t="n">
         <v>2382236</v>
@@ -55788,7 +55788,7 @@
         <v>4.80299997329712</v>
       </c>
       <c r="G1911" t="n">
-        <v>4.3802547454834</v>
+        <v>4.38025426864624</v>
       </c>
       <c r="H1911" t="n">
         <v>3237721</v>
@@ -55846,7 +55846,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G1913" t="n">
-        <v>4.50793170928955</v>
+        <v>4.50793218612671</v>
       </c>
       <c r="H1913" t="n">
         <v>1902362</v>
@@ -55904,7 +55904,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.56903553009033</v>
+        <v>4.56903505325317</v>
       </c>
       <c r="H1915" t="n">
         <v>1697802</v>
@@ -55933,7 +55933,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G1916" t="n">
-        <v>4.58909845352173</v>
+        <v>4.58909893035889</v>
       </c>
       <c r="H1916" t="n">
         <v>1293197</v>
@@ -56078,7 +56078,7 @@
         <v>5.36399984359741</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.89187669754028</v>
+        <v>4.89187717437744</v>
       </c>
       <c r="H1921" t="n">
         <v>2120977</v>
@@ -56223,7 +56223,7 @@
         <v>5.53599977493286</v>
       </c>
       <c r="G1926" t="n">
-        <v>5.0487380027771</v>
+        <v>5.04873752593994</v>
       </c>
       <c r="H1926" t="n">
         <v>1676053</v>
@@ -56339,7 +56339,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G1930" t="n">
-        <v>5.40258741378784</v>
+        <v>5.40258693695068</v>
       </c>
       <c r="H1930" t="n">
         <v>2688995</v>
@@ -56455,7 +56455,7 @@
         <v>5.91800022125244</v>
       </c>
       <c r="G1934" t="n">
-        <v>5.39711618423462</v>
+        <v>5.39711570739746</v>
       </c>
       <c r="H1934" t="n">
         <v>2801870</v>
@@ -56484,7 +56484,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1935" t="n">
-        <v>5.45365858078003</v>
+        <v>5.45365810394287</v>
       </c>
       <c r="H1935" t="n">
         <v>1677316</v>
@@ -56513,7 +56513,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G1936" t="n">
-        <v>5.57404041290283</v>
+        <v>5.57403993606567</v>
       </c>
       <c r="H1936" t="n">
         <v>3612638</v>
@@ -56542,7 +56542,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1937" t="n">
-        <v>5.62693548202515</v>
+        <v>5.62693500518799</v>
       </c>
       <c r="H1937" t="n">
         <v>3227462</v>
@@ -56600,7 +56600,7 @@
         <v>6.13800001144409</v>
       </c>
       <c r="G1939" t="n">
-        <v>5.5977520942688</v>
+        <v>5.59775161743164</v>
       </c>
       <c r="H1939" t="n">
         <v>6063161</v>
@@ -56716,7 +56716,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1943" t="n">
-        <v>5.73637294769287</v>
+        <v>5.73637342453003</v>
       </c>
       <c r="H1943" t="n">
         <v>3058422</v>
@@ -56803,7 +56803,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1946" t="n">
-        <v>5.69077396392822</v>
+        <v>5.69077348709106</v>
       </c>
       <c r="H1946" t="n">
         <v>1535277</v>
@@ -56977,7 +56977,7 @@
         <v>6.18599987030029</v>
       </c>
       <c r="G1952" t="n">
-        <v>5.64152669906616</v>
+        <v>5.64152717590332</v>
       </c>
       <c r="H1952" t="n">
         <v>2276866</v>
@@ -57180,7 +57180,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1959" t="n">
-        <v>5.53208923339844</v>
+        <v>5.53208875656128</v>
       </c>
       <c r="H1959" t="n">
         <v>2753548</v>
@@ -66988,6 +66988,35 @@
         <v>1098527</v>
       </c>
       <c r="I2297" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2298" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2298" t="n">
+        <v>6.56500005722046</v>
+      </c>
+      <c r="D2298" t="n">
+        <v>6.63000011444092</v>
+      </c>
+      <c r="E2298" t="n">
+        <v>6.4850001335144</v>
+      </c>
+      <c r="F2298" t="n">
+        <v>6.6100001335144</v>
+      </c>
+      <c r="G2298" t="n">
+        <v>6.6100001335144</v>
+      </c>
+      <c r="H2298" t="n">
+        <v>1226000</v>
+      </c>
+      <c r="I2298" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -485,7 +485,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>5.18545818328857</v>
+        <v>5.18545770645142</v>
       </c>
       <c r="H4" t="n">
         <v>10381356</v>
@@ -543,7 +543,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G6" t="n">
-        <v>5.10419273376465</v>
+        <v>5.10419321060181</v>
       </c>
       <c r="H6" t="n">
         <v>11557809</v>
@@ -572,7 +572,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G7" t="n">
-        <v>5.1119327545166</v>
+        <v>5.11193227767944</v>
       </c>
       <c r="H7" t="n">
         <v>1858638</v>
@@ -601,7 +601,7 @@
         <v>6.50500011444092</v>
       </c>
       <c r="G8" t="n">
-        <v>5.03453731536865</v>
+        <v>5.03453779220581</v>
       </c>
       <c r="H8" t="n">
         <v>1660176</v>
@@ -630,7 +630,7 @@
         <v>6.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.03066825866699</v>
+        <v>5.03066778182983</v>
       </c>
       <c r="H9" t="n">
         <v>1559429</v>
@@ -659,7 +659,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G10" t="n">
-        <v>5.02679872512817</v>
+        <v>5.02679824829102</v>
       </c>
       <c r="H10" t="n">
         <v>4863908</v>
@@ -688,7 +688,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>4.99971055984497</v>
+        <v>4.99970960617065</v>
       </c>
       <c r="H11" t="n">
         <v>2476184</v>
@@ -775,7 +775,7 @@
         <v>6.49499988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>5.02679872512817</v>
+        <v>5.02679824829102</v>
       </c>
       <c r="H14" t="n">
         <v>2519007</v>
@@ -804,7 +804,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G15" t="n">
-        <v>5.04227781295776</v>
+        <v>5.04227685928345</v>
       </c>
       <c r="H15" t="n">
         <v>2086712</v>
@@ -833,7 +833,7 @@
         <v>6.5</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03066825866699</v>
+        <v>5.03066778182983</v>
       </c>
       <c r="H16" t="n">
         <v>1266116</v>
@@ -891,7 +891,7 @@
         <v>6.5149998664856</v>
       </c>
       <c r="G18" t="n">
-        <v>5.04227781295776</v>
+        <v>5.04227685928345</v>
       </c>
       <c r="H18" t="n">
         <v>1554901</v>
@@ -920,7 +920,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G19" t="n">
-        <v>5.10806226730347</v>
+        <v>5.10806274414062</v>
       </c>
       <c r="H19" t="n">
         <v>2506280</v>
@@ -978,7 +978,7 @@
         <v>6.75</v>
       </c>
       <c r="G21" t="n">
-        <v>5.22415494918823</v>
+        <v>5.22415542602539</v>
       </c>
       <c r="H21" t="n">
         <v>3151263</v>
@@ -1007,7 +1007,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G22" t="n">
-        <v>5.40990304946899</v>
+        <v>5.40990257263184</v>
       </c>
       <c r="H22" t="n">
         <v>3306513</v>
@@ -1036,7 +1036,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G23" t="n">
-        <v>5.375075340271</v>
+        <v>5.37507581710815</v>
       </c>
       <c r="H23" t="n">
         <v>4122333</v>
@@ -1094,7 +1094,7 @@
         <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>5.41764259338379</v>
+        <v>5.41764211654663</v>
       </c>
       <c r="H25" t="n">
         <v>3819227</v>
@@ -1123,7 +1123,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G26" t="n">
-        <v>5.45634031295776</v>
+        <v>5.45633983612061</v>
       </c>
       <c r="H26" t="n">
         <v>3523859</v>
@@ -1152,7 +1152,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G27" t="n">
-        <v>5.3673357963562</v>
+        <v>5.36733531951904</v>
       </c>
       <c r="H27" t="n">
         <v>1969234</v>
@@ -1210,7 +1210,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>5.23189449310303</v>
+        <v>5.23189544677734</v>
       </c>
       <c r="H29" t="n">
         <v>1893614</v>
@@ -1239,7 +1239,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>5.29381084442139</v>
+        <v>5.29381036758423</v>
       </c>
       <c r="H30" t="n">
         <v>1171585</v>
@@ -1297,7 +1297,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G32" t="n">
-        <v>5.26285362243652</v>
+        <v>5.26285266876221</v>
       </c>
       <c r="H32" t="n">
         <v>771098</v>
@@ -1326,7 +1326,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>5.26285362243652</v>
+        <v>5.26285266876221</v>
       </c>
       <c r="H33" t="n">
         <v>532136</v>
@@ -1355,7 +1355,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>5.29381084442139</v>
+        <v>5.29381036758423</v>
       </c>
       <c r="H34" t="n">
         <v>764504</v>
@@ -1471,7 +1471,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G38" t="n">
-        <v>5.45246982574463</v>
+        <v>5.45247030258179</v>
       </c>
       <c r="H38" t="n">
         <v>874776</v>
@@ -1616,7 +1616,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>5.42151212692261</v>
+        <v>5.42151260375977</v>
       </c>
       <c r="H43" t="n">
         <v>2601318</v>
@@ -1674,7 +1674,7 @@
         <v>7.0149998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>5.42925262451172</v>
+        <v>5.4292516708374</v>
       </c>
       <c r="H45" t="n">
         <v>1351272</v>
@@ -1761,7 +1761,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G48" t="n">
-        <v>5.53760480880737</v>
+        <v>5.53760433197021</v>
       </c>
       <c r="H48" t="n">
         <v>1804427</v>
@@ -1819,7 +1819,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G50" t="n">
-        <v>5.61886930465698</v>
+        <v>5.61886978149414</v>
       </c>
       <c r="H50" t="n">
         <v>1356581</v>
@@ -1848,7 +1848,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G51" t="n">
-        <v>5.5879111289978</v>
+        <v>5.58791017532349</v>
       </c>
       <c r="H51" t="n">
         <v>1553449</v>
@@ -1877,7 +1877,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>5.6227388381958</v>
+        <v>5.62273836135864</v>
       </c>
       <c r="H52" t="n">
         <v>2277506</v>
@@ -1906,7 +1906,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G53" t="n">
-        <v>5.59178113937378</v>
+        <v>5.59178066253662</v>
       </c>
       <c r="H53" t="n">
         <v>2419795</v>
@@ -1993,7 +1993,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G56" t="n">
-        <v>5.47181940078735</v>
+        <v>5.4718189239502</v>
       </c>
       <c r="H56" t="n">
         <v>2048330</v>
@@ -2051,7 +2051,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G58" t="n">
-        <v>5.52986478805542</v>
+        <v>5.52986526489258</v>
       </c>
       <c r="H58" t="n">
         <v>1284540</v>
@@ -2109,7 +2109,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>5.54921340942383</v>
+        <v>5.54921388626099</v>
       </c>
       <c r="H60" t="n">
         <v>575911</v>
@@ -2138,7 +2138,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>5.59565019607544</v>
+        <v>5.59565114974976</v>
       </c>
       <c r="H61" t="n">
         <v>1027455</v>
@@ -2341,7 +2341,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>6.14902400970459</v>
+        <v>6.14902448654175</v>
       </c>
       <c r="H68" t="n">
         <v>2619744</v>
@@ -2544,7 +2544,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>6.03680181503296</v>
+        <v>6.03680229187012</v>
       </c>
       <c r="H75" t="n">
         <v>1814794</v>
@@ -2631,7 +2631,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>5.98262500762939</v>
+        <v>5.98262548446655</v>
       </c>
       <c r="H78" t="n">
         <v>2070393</v>
@@ -2747,7 +2747,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G82" t="n">
-        <v>6.06930780410767</v>
+        <v>6.06930732727051</v>
       </c>
       <c r="H82" t="n">
         <v>2088672</v>
@@ -2776,7 +2776,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G83" t="n">
-        <v>6.00584363937378</v>
+        <v>6.00584411621094</v>
       </c>
       <c r="H83" t="n">
         <v>1192678</v>
@@ -2805,7 +2805,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G84" t="n">
-        <v>6.00584363937378</v>
+        <v>6.00584411621094</v>
       </c>
       <c r="H84" t="n">
         <v>1034704</v>
@@ -2834,7 +2834,7 @@
         <v>7.76399993896484</v>
       </c>
       <c r="G85" t="n">
-        <v>6.00893926620483</v>
+        <v>6.00893974304199</v>
       </c>
       <c r="H85" t="n">
         <v>1196110</v>
@@ -2892,7 +2892,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G87" t="n">
-        <v>5.72722196578979</v>
+        <v>5.72722244262695</v>
       </c>
       <c r="H87" t="n">
         <v>3378154</v>
@@ -2950,7 +2950,7 @@
         <v>7.55800008773804</v>
       </c>
       <c r="G89" t="n">
-        <v>5.84950542449951</v>
+        <v>5.84950590133667</v>
       </c>
       <c r="H89" t="n">
         <v>2755965</v>
@@ -2979,7 +2979,7 @@
         <v>7.32800006866455</v>
       </c>
       <c r="G90" t="n">
-        <v>5.67149782180786</v>
+        <v>5.67149829864502</v>
       </c>
       <c r="H90" t="n">
         <v>2134999</v>
@@ -3037,7 +3037,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G92" t="n">
-        <v>5.69007349014282</v>
+        <v>5.69007301330566</v>
       </c>
       <c r="H92" t="n">
         <v>1784953</v>
@@ -3124,7 +3124,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G95" t="n">
-        <v>5.7813982963562</v>
+        <v>5.78139877319336</v>
       </c>
       <c r="H95" t="n">
         <v>1798735</v>
@@ -3211,7 +3211,7 @@
         <v>7.41599988937378</v>
       </c>
       <c r="G98" t="n">
-        <v>5.73960494995117</v>
+        <v>5.73960447311401</v>
       </c>
       <c r="H98" t="n">
         <v>1049117</v>
@@ -3240,7 +3240,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G99" t="n">
-        <v>5.73186588287354</v>
+        <v>5.73186540603638</v>
       </c>
       <c r="H99" t="n">
         <v>1618284</v>
@@ -3298,7 +3298,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G101" t="n">
-        <v>5.79687738418579</v>
+        <v>5.79687690734863</v>
       </c>
       <c r="H101" t="n">
         <v>1741178</v>
@@ -3327,7 +3327,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G102" t="n">
-        <v>5.79687738418579</v>
+        <v>5.79687690734863</v>
       </c>
       <c r="H102" t="n">
         <v>4646214</v>
@@ -3356,7 +3356,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G103" t="n">
-        <v>5.79687738418579</v>
+        <v>5.79687690734863</v>
       </c>
       <c r="H103" t="n">
         <v>2511181</v>
@@ -3501,7 +3501,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G108" t="n">
-        <v>5.4857497215271</v>
+        <v>5.48574924468994</v>
       </c>
       <c r="H108" t="n">
         <v>2296418</v>
@@ -3588,7 +3588,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>5.62660837173462</v>
+        <v>5.62660884857178</v>
       </c>
       <c r="H111" t="n">
         <v>1667359</v>
@@ -3675,7 +3675,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G114" t="n">
-        <v>5.47181940078735</v>
+        <v>5.4718189239502</v>
       </c>
       <c r="H114" t="n">
         <v>1348439</v>
@@ -3704,7 +3704,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G115" t="n">
-        <v>5.51051616668701</v>
+        <v>5.51051664352417</v>
       </c>
       <c r="H115" t="n">
         <v>1237587</v>
@@ -3762,7 +3762,7 @@
         <v>7.08199977874756</v>
       </c>
       <c r="G117" t="n">
-        <v>5.48110628128052</v>
+        <v>5.48110675811768</v>
       </c>
       <c r="H117" t="n">
         <v>1463476</v>
@@ -3791,7 +3791,7 @@
         <v>7.19799995422363</v>
       </c>
       <c r="G118" t="n">
-        <v>5.57088470458984</v>
+        <v>5.57088375091553</v>
       </c>
       <c r="H118" t="n">
         <v>1960942</v>
@@ -3820,7 +3820,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G119" t="n">
-        <v>5.61886930465698</v>
+        <v>5.61886978149414</v>
       </c>
       <c r="H119" t="n">
         <v>1697131</v>
@@ -3849,7 +3849,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G120" t="n">
-        <v>5.51051616668701</v>
+        <v>5.51051664352417</v>
       </c>
       <c r="H120" t="n">
         <v>2424098</v>
@@ -3936,7 +3936,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G123" t="n">
-        <v>5.42538166046143</v>
+        <v>5.42538213729858</v>
       </c>
       <c r="H123" t="n">
         <v>2355501</v>
@@ -3965,7 +3965,7 @@
         <v>7.03599977493286</v>
       </c>
       <c r="G124" t="n">
-        <v>5.4455041885376</v>
+        <v>5.44550466537476</v>
       </c>
       <c r="H124" t="n">
         <v>2485435</v>
@@ -3994,7 +3994,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>5.57243204116821</v>
+        <v>5.57243251800537</v>
       </c>
       <c r="H125" t="n">
         <v>2256527</v>
@@ -4023,7 +4023,7 @@
         <v>7.16800022125244</v>
       </c>
       <c r="G126" t="n">
-        <v>5.54766607284546</v>
+        <v>5.5476655960083</v>
       </c>
       <c r="H126" t="n">
         <v>1469569</v>
@@ -4052,7 +4052,7 @@
         <v>7.02799987792969</v>
       </c>
       <c r="G127" t="n">
-        <v>5.43931293487549</v>
+        <v>5.43931245803833</v>
       </c>
       <c r="H127" t="n">
         <v>2020676</v>
@@ -4110,7 +4110,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>5.54147338867188</v>
+        <v>5.54147434234619</v>
       </c>
       <c r="H129" t="n">
         <v>1457912</v>
@@ -4139,7 +4139,7 @@
         <v>7.11199998855591</v>
       </c>
       <c r="G130" t="n">
-        <v>5.50432443618774</v>
+        <v>5.50432538986206</v>
       </c>
       <c r="H130" t="n">
         <v>1790452</v>
@@ -4255,7 +4255,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G134" t="n">
-        <v>5.61886930465698</v>
+        <v>5.61886978149414</v>
       </c>
       <c r="H134" t="n">
         <v>3548151</v>
@@ -4313,7 +4313,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>5.54921340942383</v>
+        <v>5.54921388626099</v>
       </c>
       <c r="H136" t="n">
         <v>4094123</v>
@@ -4342,7 +4342,7 @@
         <v>7.02199983596802</v>
       </c>
       <c r="G137" t="n">
-        <v>5.43466949462891</v>
+        <v>5.43466997146606</v>
       </c>
       <c r="H137" t="n">
         <v>8167240</v>
@@ -4400,7 +4400,7 @@
         <v>7.02400016784668</v>
       </c>
       <c r="G139" t="n">
-        <v>5.43621730804443</v>
+        <v>5.43621683120728</v>
       </c>
       <c r="H139" t="n">
         <v>4830708</v>
@@ -4429,7 +4429,7 @@
         <v>7.08400011062622</v>
       </c>
       <c r="G140" t="n">
-        <v>5.48265504837036</v>
+        <v>5.48265361785889</v>
       </c>
       <c r="H140" t="n">
         <v>1915810</v>
@@ -4458,7 +4458,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G141" t="n">
-        <v>5.57243204116821</v>
+        <v>5.57243251800537</v>
       </c>
       <c r="H141" t="n">
         <v>3254579</v>
@@ -4545,7 +4545,7 @@
         <v>7.19600009918213</v>
       </c>
       <c r="G144" t="n">
-        <v>5.56933641433716</v>
+        <v>5.56933689117432</v>
       </c>
       <c r="H144" t="n">
         <v>1599656</v>
@@ -4574,7 +4574,7 @@
         <v>7.2039999961853</v>
       </c>
       <c r="G145" t="n">
-        <v>5.57552719116211</v>
+        <v>5.57552814483643</v>
       </c>
       <c r="H145" t="n">
         <v>1195513</v>
@@ -4603,7 +4603,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G146" t="n">
-        <v>5.69007349014282</v>
+        <v>5.69007301330566</v>
       </c>
       <c r="H146" t="n">
         <v>3640962</v>
@@ -4690,7 +4690,7 @@
         <v>7.32800006866455</v>
       </c>
       <c r="G149" t="n">
-        <v>5.67149782180786</v>
+        <v>5.67149829864502</v>
       </c>
       <c r="H149" t="n">
         <v>933654</v>
@@ -4719,7 +4719,7 @@
         <v>7.26800012588501</v>
       </c>
       <c r="G150" t="n">
-        <v>5.62506103515625</v>
+        <v>5.62506055831909</v>
       </c>
       <c r="H150" t="n">
         <v>2888493</v>
@@ -4864,7 +4864,7 @@
         <v>7.4539999961853</v>
       </c>
       <c r="G155" t="n">
-        <v>5.76901531219482</v>
+        <v>5.76901578903198</v>
       </c>
       <c r="H155" t="n">
         <v>12483969</v>
@@ -4922,7 +4922,7 @@
         <v>7.5479998588562</v>
       </c>
       <c r="G157" t="n">
-        <v>5.84176588058472</v>
+        <v>5.84176683425903</v>
       </c>
       <c r="H157" t="n">
         <v>4087859</v>
@@ -4980,7 +4980,7 @@
         <v>7.67799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>5.94237995147705</v>
+        <v>5.94237947463989</v>
       </c>
       <c r="H159" t="n">
         <v>2586916</v>
@@ -5038,7 +5038,7 @@
         <v>7.41599988937378</v>
       </c>
       <c r="G161" t="n">
-        <v>5.73960494995117</v>
+        <v>5.73960447311401</v>
       </c>
       <c r="H161" t="n">
         <v>2822860</v>
@@ -5096,7 +5096,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G163" t="n">
-        <v>5.75044012069702</v>
+        <v>5.75044059753418</v>
       </c>
       <c r="H163" t="n">
         <v>5190788</v>
@@ -5154,7 +5154,7 @@
         <v>7.20800018310547</v>
       </c>
       <c r="G165" t="n">
-        <v>5.57862377166748</v>
+        <v>5.57862424850464</v>
       </c>
       <c r="H165" t="n">
         <v>5358633</v>
@@ -5183,7 +5183,7 @@
         <v>7.26399993896484</v>
       </c>
       <c r="G166" t="n">
-        <v>5.62196493148804</v>
+        <v>5.62196445465088</v>
       </c>
       <c r="H166" t="n">
         <v>4341174</v>
@@ -5241,7 +5241,7 @@
         <v>7.32800006866455</v>
       </c>
       <c r="G168" t="n">
-        <v>5.67149782180786</v>
+        <v>5.67149829864502</v>
       </c>
       <c r="H168" t="n">
         <v>2311280</v>
@@ -5270,7 +5270,7 @@
         <v>7.36199998855591</v>
       </c>
       <c r="G169" t="n">
-        <v>5.6978120803833</v>
+        <v>5.69781112670898</v>
       </c>
       <c r="H169" t="n">
         <v>2575130</v>
@@ -5299,7 +5299,7 @@
         <v>7.47599983215332</v>
       </c>
       <c r="G170" t="n">
-        <v>5.78604221343994</v>
+        <v>5.78604173660278</v>
       </c>
       <c r="H170" t="n">
         <v>4178875</v>
@@ -5415,7 +5415,7 @@
         <v>7.52400016784668</v>
       </c>
       <c r="G174" t="n">
-        <v>5.82319211959839</v>
+        <v>5.82319164276123</v>
       </c>
       <c r="H174" t="n">
         <v>2159098</v>
@@ -5444,7 +5444,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>5.77365922927856</v>
+        <v>5.77365827560425</v>
       </c>
       <c r="H175" t="n">
         <v>1681767</v>
@@ -5473,7 +5473,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G176" t="n">
-        <v>5.75044012069702</v>
+        <v>5.75044059753418</v>
       </c>
       <c r="H176" t="n">
         <v>1089579</v>
@@ -5502,7 +5502,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>5.72722196578979</v>
+        <v>5.72722244262695</v>
       </c>
       <c r="H177" t="n">
         <v>3472853</v>
@@ -5589,7 +5589,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>5.67304515838623</v>
+        <v>5.67304563522339</v>
       </c>
       <c r="H180" t="n">
         <v>1468023</v>
@@ -5618,7 +5618,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>5.64982795715332</v>
+        <v>5.649827003479</v>
       </c>
       <c r="H181" t="n">
         <v>1631020</v>
@@ -5763,7 +5763,7 @@
         <v>7.29199981689453</v>
       </c>
       <c r="G186" t="n">
-        <v>5.64363527297974</v>
+        <v>5.64363479614258</v>
       </c>
       <c r="H186" t="n">
         <v>2057580</v>
@@ -5821,7 +5821,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G188" t="n">
-        <v>5.53528213500977</v>
+        <v>5.53528261184692</v>
       </c>
       <c r="H188" t="n">
         <v>1687495</v>
@@ -5850,7 +5850,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G189" t="n">
-        <v>5.53528213500977</v>
+        <v>5.53528261184692</v>
       </c>
       <c r="H189" t="n">
         <v>2030021</v>
@@ -5879,7 +5879,7 @@
         <v>7.24200010299683</v>
       </c>
       <c r="G190" t="n">
-        <v>5.60493803024292</v>
+        <v>5.60493850708008</v>
       </c>
       <c r="H190" t="n">
         <v>1380536</v>
@@ -6024,7 +6024,7 @@
         <v>7.15799999237061</v>
       </c>
       <c r="G195" t="n">
-        <v>5.53992700576782</v>
+        <v>5.53992605209351</v>
       </c>
       <c r="H195" t="n">
         <v>2685820</v>
@@ -6053,7 +6053,7 @@
         <v>7</v>
       </c>
       <c r="G196" t="n">
-        <v>5.41764259338379</v>
+        <v>5.41764211654663</v>
       </c>
       <c r="H196" t="n">
         <v>1482253</v>
@@ -6082,7 +6082,7 @@
         <v>7</v>
       </c>
       <c r="G197" t="n">
-        <v>5.41764259338379</v>
+        <v>5.41764211654663</v>
       </c>
       <c r="H197" t="n">
         <v>1456578</v>
@@ -6111,7 +6111,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>5.38668489456177</v>
+        <v>5.38668441772461</v>
       </c>
       <c r="H198" t="n">
         <v>1798402</v>
@@ -6140,7 +6140,7 @@
         <v>7.02799987792969</v>
       </c>
       <c r="G199" t="n">
-        <v>5.43931293487549</v>
+        <v>5.43931245803833</v>
       </c>
       <c r="H199" t="n">
         <v>1259885</v>
@@ -6198,7 +6198,7 @@
         <v>7.0460000038147</v>
       </c>
       <c r="G201" t="n">
-        <v>5.45324420928955</v>
+        <v>5.45324468612671</v>
       </c>
       <c r="H201" t="n">
         <v>1269104</v>
@@ -6227,7 +6227,7 @@
         <v>7.13199996948242</v>
       </c>
       <c r="G202" t="n">
-        <v>5.51980400085449</v>
+        <v>5.51980352401733</v>
       </c>
       <c r="H202" t="n">
         <v>1113937</v>
@@ -6285,7 +6285,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G204" t="n">
-        <v>5.47181940078735</v>
+        <v>5.4718189239502</v>
       </c>
       <c r="H204" t="n">
         <v>966199</v>
@@ -6372,7 +6372,7 @@
         <v>7.44600009918213</v>
       </c>
       <c r="G207" t="n">
-        <v>5.76282358169556</v>
+        <v>5.76282405853271</v>
       </c>
       <c r="H207" t="n">
         <v>2963238</v>
@@ -6488,7 +6488,7 @@
         <v>7.35200023651123</v>
       </c>
       <c r="G211" t="n">
-        <v>5.69007349014282</v>
+        <v>5.69007301330566</v>
       </c>
       <c r="H211" t="n">
         <v>1609011</v>
@@ -6517,7 +6517,7 @@
         <v>7.19799995422363</v>
       </c>
       <c r="G212" t="n">
-        <v>5.57088470458984</v>
+        <v>5.57088375091553</v>
       </c>
       <c r="H212" t="n">
         <v>2297120</v>
@@ -6546,7 +6546,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>5.51825571060181</v>
+        <v>5.51825618743896</v>
       </c>
       <c r="H213" t="n">
         <v>1073404</v>
@@ -6575,7 +6575,7 @@
         <v>7.20800018310547</v>
       </c>
       <c r="G214" t="n">
-        <v>5.57862377166748</v>
+        <v>5.57862424850464</v>
       </c>
       <c r="H214" t="n">
         <v>1044217</v>
@@ -6691,7 +6691,7 @@
         <v>7.60400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>5.88510799407959</v>
+        <v>5.88510751724243</v>
       </c>
       <c r="H218" t="n">
         <v>1267206</v>
@@ -6749,7 +6749,7 @@
         <v>7.62200021743774</v>
       </c>
       <c r="G220" t="n">
-        <v>5.89903926849365</v>
+        <v>5.89903879165649</v>
       </c>
       <c r="H220" t="n">
         <v>1328680</v>
@@ -6778,7 +6778,7 @@
         <v>7.63800001144409</v>
       </c>
       <c r="G221" t="n">
-        <v>5.91142225265503</v>
+        <v>5.91142129898071</v>
       </c>
       <c r="H221" t="n">
         <v>957497</v>
@@ -6807,7 +6807,7 @@
         <v>7.60200023651123</v>
       </c>
       <c r="G222" t="n">
-        <v>5.88356018066406</v>
+        <v>5.8835597038269</v>
       </c>
       <c r="H222" t="n">
         <v>1290829</v>
@@ -6836,7 +6836,7 @@
         <v>7.57800006866455</v>
       </c>
       <c r="G223" t="n">
-        <v>5.86498546600342</v>
+        <v>5.8649845123291</v>
       </c>
       <c r="H223" t="n">
         <v>1266692</v>
@@ -6952,7 +6952,7 @@
         <v>7.1560001373291</v>
       </c>
       <c r="G227" t="n">
-        <v>5.53837871551514</v>
+        <v>5.53837919235229</v>
       </c>
       <c r="H227" t="n">
         <v>2180122</v>
@@ -7126,7 +7126,7 @@
         <v>6.86199998855591</v>
       </c>
       <c r="G233" t="n">
-        <v>5.31083726882935</v>
+        <v>5.3108377456665</v>
       </c>
       <c r="H233" t="n">
         <v>1785974</v>
@@ -7155,7 +7155,7 @@
         <v>6.92799997329712</v>
       </c>
       <c r="G234" t="n">
-        <v>5.36191844940186</v>
+        <v>5.3619179725647</v>
       </c>
       <c r="H234" t="n">
         <v>2011130</v>
@@ -7184,7 +7184,7 @@
         <v>6.92799997329712</v>
       </c>
       <c r="G235" t="n">
-        <v>5.36191844940186</v>
+        <v>5.3619179725647</v>
       </c>
       <c r="H235" t="n">
         <v>3181112</v>
@@ -7242,7 +7242,7 @@
         <v>6.67199993133545</v>
       </c>
       <c r="G237" t="n">
-        <v>5.16378736495972</v>
+        <v>5.16378688812256</v>
       </c>
       <c r="H237" t="n">
         <v>1786947</v>
@@ -7329,7 +7329,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G240" t="n">
-        <v>5.49813318252563</v>
+        <v>5.49813270568848</v>
       </c>
       <c r="H240" t="n">
         <v>2318680</v>
@@ -7387,7 +7387,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G242" t="n">
-        <v>5.49813318252563</v>
+        <v>5.49813270568848</v>
       </c>
       <c r="H242" t="n">
         <v>1618816</v>
@@ -7416,7 +7416,7 @@
         <v>7.22200012207031</v>
       </c>
       <c r="G243" t="n">
-        <v>5.58945894241333</v>
+        <v>5.58945941925049</v>
       </c>
       <c r="H243" t="n">
         <v>2092114</v>
@@ -7445,7 +7445,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G244" t="n">
-        <v>5.55695295333862</v>
+        <v>5.55695343017578</v>
       </c>
       <c r="H244" t="n">
         <v>1426893</v>
@@ -7503,7 +7503,7 @@
         <v>7.20599985122681</v>
       </c>
       <c r="G246" t="n">
-        <v>5.57707595825195</v>
+        <v>5.57707548141479</v>
       </c>
       <c r="H246" t="n">
         <v>1630112</v>
@@ -7532,7 +7532,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G247" t="n">
-        <v>5.51051616668701</v>
+        <v>5.51051664352417</v>
       </c>
       <c r="H247" t="n">
         <v>4398932</v>
@@ -7561,7 +7561,7 @@
         <v>7.10599994659424</v>
       </c>
       <c r="G248" t="n">
-        <v>5.49968147277832</v>
+        <v>5.49968099594116</v>
       </c>
       <c r="H248" t="n">
         <v>1099500</v>
@@ -7590,7 +7590,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G249" t="n">
-        <v>5.4857497215271</v>
+        <v>5.48574924468994</v>
       </c>
       <c r="H249" t="n">
         <v>1354493</v>
@@ -7706,7 +7706,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G253" t="n">
-        <v>5.56624126434326</v>
+        <v>5.5662407875061</v>
       </c>
       <c r="H253" t="n">
         <v>1107860</v>
@@ -7735,7 +7735,7 @@
         <v>6.99200010299683</v>
       </c>
       <c r="G254" t="n">
-        <v>5.41144990921021</v>
+        <v>5.41145086288452</v>
       </c>
       <c r="H254" t="n">
         <v>2263864</v>
@@ -7793,7 +7793,7 @@
         <v>6.86399984359741</v>
       </c>
       <c r="G256" t="n">
-        <v>5.31238460540771</v>
+        <v>5.31238508224487</v>
       </c>
       <c r="H256" t="n">
         <v>3890851</v>
@@ -7822,7 +7822,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>5.25511264801025</v>
+        <v>5.25511360168457</v>
       </c>
       <c r="H257" t="n">
         <v>2167315</v>
@@ -7880,7 +7880,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G259" t="n">
-        <v>5.17771816253662</v>
+        <v>5.17771863937378</v>
       </c>
       <c r="H259" t="n">
         <v>1767287</v>
@@ -7909,7 +7909,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>4.86813879013062</v>
+        <v>4.86813831329346</v>
       </c>
       <c r="H260" t="n">
         <v>2892526</v>
@@ -7938,7 +7938,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G261" t="n">
-        <v>4.73037528991699</v>
+        <v>4.73037624359131</v>
       </c>
       <c r="H261" t="n">
         <v>4291834</v>
@@ -7967,7 +7967,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>4.87587833404541</v>
+        <v>4.87587881088257</v>
       </c>
       <c r="H262" t="n">
         <v>2856462</v>
@@ -8083,7 +8083,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>4.78300333023071</v>
+        <v>4.78300380706787</v>
       </c>
       <c r="H266" t="n">
         <v>1727102</v>
@@ -8112,7 +8112,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G267" t="n">
-        <v>4.54153156280518</v>
+        <v>4.54153251647949</v>
       </c>
       <c r="H267" t="n">
         <v>4649771</v>
@@ -8141,7 +8141,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G268" t="n">
-        <v>4.57094287872314</v>
+        <v>4.57094192504883</v>
       </c>
       <c r="H268" t="n">
         <v>3844094</v>
@@ -8228,7 +8228,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G271" t="n">
-        <v>4.75204610824585</v>
+        <v>4.75204658508301</v>
       </c>
       <c r="H271" t="n">
         <v>2954519</v>
@@ -8257,7 +8257,7 @@
         <v>6.2480001449585</v>
       </c>
       <c r="G272" t="n">
-        <v>4.83563327789307</v>
+        <v>4.83563280105591</v>
       </c>
       <c r="H272" t="n">
         <v>2873517</v>
@@ -8344,7 +8344,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G275" t="n">
-        <v>5.02602434158325</v>
+        <v>5.02602386474609</v>
       </c>
       <c r="H275" t="n">
         <v>3419765</v>
@@ -8373,7 +8373,7 @@
         <v>6.44600009918213</v>
       </c>
       <c r="G276" t="n">
-        <v>4.98887538909912</v>
+        <v>4.9888744354248</v>
       </c>
       <c r="H276" t="n">
         <v>1300076</v>
@@ -8431,7 +8431,7 @@
         <v>6.34600019454956</v>
       </c>
       <c r="G278" t="n">
-        <v>4.91148042678833</v>
+        <v>4.91147994995117</v>
       </c>
       <c r="H278" t="n">
         <v>2104958</v>
@@ -8518,7 +8518,7 @@
         <v>6.33599996566772</v>
       </c>
       <c r="G281" t="n">
-        <v>4.90373992919922</v>
+        <v>4.90374040603638</v>
       </c>
       <c r="H281" t="n">
         <v>1475144</v>
@@ -8605,7 +8605,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G284" t="n">
-        <v>4.63440656661987</v>
+        <v>4.63440608978271</v>
       </c>
       <c r="H284" t="n">
         <v>2793354</v>
@@ -8663,7 +8663,7 @@
         <v>6.2020001411438</v>
       </c>
       <c r="G286" t="n">
-        <v>4.80003118515015</v>
+        <v>4.8000316619873</v>
       </c>
       <c r="H286" t="n">
         <v>3630673</v>
@@ -8750,7 +8750,7 @@
         <v>6.23400020599365</v>
       </c>
       <c r="G289" t="n">
-        <v>4.82479810714722</v>
+        <v>4.82479763031006</v>
       </c>
       <c r="H289" t="n">
         <v>1177221</v>
@@ -8837,7 +8837,7 @@
         <v>6.42399978637695</v>
       </c>
       <c r="G292" t="n">
-        <v>4.97184801101685</v>
+        <v>4.97184753417969</v>
       </c>
       <c r="H292" t="n">
         <v>854708</v>
@@ -8866,7 +8866,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G293" t="n">
-        <v>5.02602434158325</v>
+        <v>5.02602386474609</v>
       </c>
       <c r="H293" t="n">
         <v>2085690</v>
@@ -8895,7 +8895,7 @@
         <v>6.40799999237061</v>
       </c>
       <c r="G294" t="n">
-        <v>4.95946502685547</v>
+        <v>4.95946455001831</v>
       </c>
       <c r="H294" t="n">
         <v>1622501</v>
@@ -9011,7 +9011,7 @@
         <v>6.43400001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>4.97958755493164</v>
+        <v>4.97958707809448</v>
       </c>
       <c r="H298" t="n">
         <v>2398005</v>
@@ -9040,7 +9040,7 @@
         <v>6.22599983215332</v>
       </c>
       <c r="G299" t="n">
-        <v>4.81860589981079</v>
+        <v>4.81860637664795</v>
       </c>
       <c r="H299" t="n">
         <v>1316365</v>
@@ -9069,7 +9069,7 @@
         <v>6.20599985122681</v>
       </c>
       <c r="G300" t="n">
-        <v>4.8031268119812</v>
+        <v>4.80312633514404</v>
       </c>
       <c r="H300" t="n">
         <v>1098983</v>
@@ -9185,7 +9185,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G304" t="n">
-        <v>4.55855941772461</v>
+        <v>4.55855894088745</v>
       </c>
       <c r="H304" t="n">
         <v>2287721</v>
@@ -9301,7 +9301,7 @@
         <v>5.72599983215332</v>
       </c>
       <c r="G308" t="n">
-        <v>4.43163061141968</v>
+        <v>4.43163108825684</v>
       </c>
       <c r="H308" t="n">
         <v>1935193</v>
@@ -9330,7 +9330,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G309" t="n">
-        <v>4.38674211502075</v>
+        <v>4.38674306869507</v>
       </c>
       <c r="H309" t="n">
         <v>2277365</v>
@@ -9388,7 +9388,7 @@
         <v>5.60799980163574</v>
       </c>
       <c r="G311" t="n">
-        <v>4.3403058052063</v>
+        <v>4.34030532836914</v>
       </c>
       <c r="H311" t="n">
         <v>1673261</v>
@@ -9475,7 +9475,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G314" t="n">
-        <v>4.34185409545898</v>
+        <v>4.34185361862183</v>
       </c>
       <c r="H314" t="n">
         <v>1120253</v>
@@ -9533,7 +9533,7 @@
         <v>5.44600009918213</v>
       </c>
       <c r="G316" t="n">
-        <v>4.21492624282837</v>
+        <v>4.21492576599121</v>
       </c>
       <c r="H316" t="n">
         <v>1823690</v>
@@ -9620,7 +9620,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G319" t="n">
-        <v>4.48116493225098</v>
+        <v>4.48116445541382</v>
       </c>
       <c r="H319" t="n">
         <v>2117640</v>
@@ -9649,7 +9649,7 @@
         <v>5.96600008010864</v>
       </c>
       <c r="G320" t="n">
-        <v>4.6173791885376</v>
+        <v>4.61737966537476</v>
       </c>
       <c r="H320" t="n">
         <v>2084581</v>
@@ -9736,7 +9736,7 @@
         <v>6.0460000038147</v>
       </c>
       <c r="G323" t="n">
-        <v>4.6792950630188</v>
+        <v>4.67929458618164</v>
       </c>
       <c r="H323" t="n">
         <v>1558020</v>
@@ -9794,7 +9794,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>4.65917253494263</v>
+        <v>4.65917205810547</v>
       </c>
       <c r="H325" t="n">
         <v>2339314</v>
@@ -9852,7 +9852,7 @@
         <v>6.05200004577637</v>
       </c>
       <c r="G327" t="n">
-        <v>4.68393850326538</v>
+        <v>4.68393898010254</v>
       </c>
       <c r="H327" t="n">
         <v>1956207</v>
@@ -9881,7 +9881,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>4.72108840942383</v>
+        <v>4.72108888626099</v>
       </c>
       <c r="H328" t="n">
         <v>654265</v>
@@ -9910,7 +9910,7 @@
         <v>6.02799987792969</v>
       </c>
       <c r="G329" t="n">
-        <v>4.66536378860474</v>
+        <v>4.66536331176758</v>
       </c>
       <c r="H329" t="n">
         <v>1011597</v>
@@ -9939,7 +9939,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G330" t="n">
-        <v>4.63440656661987</v>
+        <v>4.63440608978271</v>
       </c>
       <c r="H330" t="n">
         <v>914177</v>
@@ -9968,7 +9968,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G331" t="n">
-        <v>4.71489715576172</v>
+        <v>4.71489667892456</v>
       </c>
       <c r="H331" t="n">
         <v>1629330</v>
@@ -10084,7 +10084,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G335" t="n">
-        <v>4.55855941772461</v>
+        <v>4.55855894088745</v>
       </c>
       <c r="H335" t="n">
         <v>1559842</v>
@@ -10142,7 +10142,7 @@
         <v>5.69799995422363</v>
       </c>
       <c r="G337" t="n">
-        <v>4.40996026992798</v>
+        <v>4.40996074676514</v>
       </c>
       <c r="H337" t="n">
         <v>2706905</v>
@@ -10200,7 +10200,7 @@
         <v>5.98199987411499</v>
       </c>
       <c r="G339" t="n">
-        <v>4.62976169586182</v>
+        <v>4.62976312637329</v>
       </c>
       <c r="H339" t="n">
         <v>2743128</v>
@@ -10229,7 +10229,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G340" t="n">
-        <v>4.68239164352417</v>
+        <v>4.68239116668701</v>
       </c>
       <c r="H340" t="n">
         <v>2404799</v>
@@ -10258,7 +10258,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G341" t="n">
-        <v>4.49200010299683</v>
+        <v>4.49199962615967</v>
       </c>
       <c r="H341" t="n">
         <v>3253843</v>
@@ -10316,7 +10316,7 @@
         <v>5.71799993515015</v>
       </c>
       <c r="G343" t="n">
-        <v>4.42543983459473</v>
+        <v>4.42543935775757</v>
       </c>
       <c r="H343" t="n">
         <v>1859747</v>
@@ -10374,7 +10374,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G345" t="n">
-        <v>4.71489715576172</v>
+        <v>4.71489667892456</v>
       </c>
       <c r="H345" t="n">
         <v>2457900</v>
@@ -10403,7 +10403,7 @@
         <v>5.98400020599365</v>
       </c>
       <c r="G346" t="n">
-        <v>4.63131093978882</v>
+        <v>4.63131046295166</v>
       </c>
       <c r="H346" t="n">
         <v>1886450</v>
@@ -10432,7 +10432,7 @@
         <v>6.07399988174438</v>
       </c>
       <c r="G347" t="n">
-        <v>4.70096588134766</v>
+        <v>4.7009654045105</v>
       </c>
       <c r="H347" t="n">
         <v>3636485</v>
@@ -10461,7 +10461,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G348" t="n">
-        <v>4.65452909469604</v>
+        <v>4.65452861785889</v>
       </c>
       <c r="H348" t="n">
         <v>1808439</v>
@@ -10490,7 +10490,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G349" t="n">
-        <v>4.55855941772461</v>
+        <v>4.55855894088745</v>
       </c>
       <c r="H349" t="n">
         <v>1804076</v>
@@ -10548,7 +10548,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G351" t="n">
-        <v>4.72108840942383</v>
+        <v>4.72108888626099</v>
       </c>
       <c r="H351" t="n">
         <v>1185777</v>
@@ -10606,7 +10606,7 @@
         <v>6.05800008773804</v>
       </c>
       <c r="G353" t="n">
-        <v>4.68858289718628</v>
+        <v>4.68858242034912</v>
       </c>
       <c r="H353" t="n">
         <v>1813455</v>
@@ -10664,7 +10664,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G355" t="n">
-        <v>4.5043830871582</v>
+        <v>4.50438261032104</v>
       </c>
       <c r="H355" t="n">
         <v>8649771</v>
@@ -10751,7 +10751,7 @@
         <v>6.15399980545044</v>
       </c>
       <c r="G358" t="n">
-        <v>4.7628812789917</v>
+        <v>4.76288175582886</v>
       </c>
       <c r="H358" t="n">
         <v>2611739</v>
@@ -10780,7 +10780,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>4.72108840942383</v>
+        <v>4.72108888626099</v>
       </c>
       <c r="H359" t="n">
         <v>1704799</v>
@@ -10838,7 +10838,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G361" t="n">
-        <v>4.65917253494263</v>
+        <v>4.65917205810547</v>
       </c>
       <c r="H361" t="n">
         <v>2666267</v>
@@ -10867,7 +10867,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G362" t="n">
-        <v>4.5477237701416</v>
+        <v>4.54772329330444</v>
       </c>
       <c r="H362" t="n">
         <v>1919771</v>
@@ -10896,7 +10896,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G363" t="n">
-        <v>4.49509572982788</v>
+        <v>4.49509525299072</v>
       </c>
       <c r="H363" t="n">
         <v>3344560</v>
@@ -10925,7 +10925,7 @@
         <v>5.76800012588501</v>
       </c>
       <c r="G364" t="n">
-        <v>4.4641375541687</v>
+        <v>4.46413803100586</v>
       </c>
       <c r="H364" t="n">
         <v>3500087</v>
@@ -11012,7 +11012,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>4.61273574829102</v>
+        <v>4.61273527145386</v>
       </c>
       <c r="H367" t="n">
         <v>4059024</v>
@@ -11070,7 +11070,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G369" t="n">
-        <v>4.67000770568848</v>
+        <v>4.67000818252563</v>
       </c>
       <c r="H369" t="n">
         <v>2627829</v>
@@ -11099,7 +11099,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G370" t="n">
-        <v>4.67000770568848</v>
+        <v>4.67000818252563</v>
       </c>
       <c r="H370" t="n">
         <v>1424349</v>
@@ -11128,7 +11128,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G371" t="n">
-        <v>4.68548679351807</v>
+        <v>4.68548631668091</v>
       </c>
       <c r="H371" t="n">
         <v>1948144</v>
@@ -11302,7 +11302,7 @@
         <v>5.73799991607666</v>
       </c>
       <c r="G377" t="n">
-        <v>4.44091939926147</v>
+        <v>4.44091892242432</v>
       </c>
       <c r="H377" t="n">
         <v>2321157</v>
@@ -11360,7 +11360,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G379" t="n">
-        <v>4.64059686660767</v>
+        <v>4.64059782028198</v>
       </c>
       <c r="H379" t="n">
         <v>5437759</v>
@@ -11418,7 +11418,7 @@
         <v>6.24599981307983</v>
       </c>
       <c r="G381" t="n">
-        <v>4.83408451080322</v>
+        <v>4.83408498764038</v>
       </c>
       <c r="H381" t="n">
         <v>2344904</v>
@@ -11447,7 +11447,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G382" t="n">
-        <v>4.86813879013062</v>
+        <v>4.86813831329346</v>
       </c>
       <c r="H382" t="n">
         <v>1984104</v>
@@ -11476,7 +11476,7 @@
         <v>6.26800012588501</v>
       </c>
       <c r="G383" t="n">
-        <v>4.85111141204834</v>
+        <v>4.8511118888855</v>
       </c>
       <c r="H383" t="n">
         <v>1826983</v>
@@ -11563,7 +11563,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G386" t="n">
-        <v>4.91612386703491</v>
+        <v>4.91612339019775</v>
       </c>
       <c r="H386" t="n">
         <v>2103203</v>
@@ -11650,7 +11650,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G389" t="n">
-        <v>5.02757215499878</v>
+        <v>5.02757263183594</v>
       </c>
       <c r="H389" t="n">
         <v>1436659</v>
@@ -11679,7 +11679,7 @@
         <v>6.5</v>
       </c>
       <c r="G390" t="n">
-        <v>5.03066825866699</v>
+        <v>5.03066778182983</v>
       </c>
       <c r="H390" t="n">
         <v>1844285</v>
@@ -11766,7 +11766,7 @@
         <v>6.44199991226196</v>
       </c>
       <c r="G393" t="n">
-        <v>4.98577880859375</v>
+        <v>4.98577928543091</v>
       </c>
       <c r="H393" t="n">
         <v>2979080</v>
@@ -11795,7 +11795,7 @@
         <v>6.4060001373291</v>
       </c>
       <c r="G394" t="n">
-        <v>4.95791673660278</v>
+        <v>4.95791721343994</v>
       </c>
       <c r="H394" t="n">
         <v>1161802</v>
@@ -11824,7 +11824,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G395" t="n">
-        <v>5.02602434158325</v>
+        <v>5.02602386474609</v>
       </c>
       <c r="H395" t="n">
         <v>1755876</v>
@@ -11853,7 +11853,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G396" t="n">
-        <v>4.99971055984497</v>
+        <v>4.99970960617065</v>
       </c>
       <c r="H396" t="n">
         <v>1301218</v>
@@ -11911,7 +11911,7 @@
         <v>6.30600023269653</v>
       </c>
       <c r="G398" t="n">
-        <v>4.88052225112915</v>
+        <v>4.88052177429199</v>
       </c>
       <c r="H398" t="n">
         <v>1489174</v>
@@ -11940,7 +11940,7 @@
         <v>6.17799997329712</v>
       </c>
       <c r="G399" t="n">
-        <v>4.78145694732666</v>
+        <v>4.7814564704895</v>
       </c>
       <c r="H399" t="n">
         <v>2777477</v>
@@ -12114,7 +12114,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G405" t="n">
-        <v>4.34185409545898</v>
+        <v>4.34185361862183</v>
       </c>
       <c r="H405" t="n">
         <v>2818219</v>
@@ -12143,7 +12143,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G406" t="n">
-        <v>4.40376949310303</v>
+        <v>4.40376901626587</v>
       </c>
       <c r="H406" t="n">
         <v>2618707</v>
@@ -12375,7 +12375,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G414" t="n">
-        <v>4.25039386749268</v>
+        <v>4.25039339065552</v>
       </c>
       <c r="H414" t="n">
         <v>1953616</v>
@@ -12433,7 +12433,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G416" t="n">
-        <v>4.14660835266113</v>
+        <v>4.14660787582397</v>
       </c>
       <c r="H416" t="n">
         <v>3138975</v>
@@ -12491,7 +12491,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G418" t="n">
-        <v>4.14341497421265</v>
+        <v>4.1434154510498</v>
       </c>
       <c r="H418" t="n">
         <v>2326150</v>
@@ -12607,7 +12607,7 @@
         <v>5.17799997329712</v>
       </c>
       <c r="G422" t="n">
-        <v>4.13383531570435</v>
+        <v>4.13383483886719</v>
       </c>
       <c r="H422" t="n">
         <v>1603497</v>
@@ -12636,7 +12636,7 @@
         <v>5.18800020217896</v>
       </c>
       <c r="G423" t="n">
-        <v>4.14181900024414</v>
+        <v>4.14181852340698</v>
       </c>
       <c r="H423" t="n">
         <v>2526796</v>
@@ -12665,7 +12665,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G424" t="n">
-        <v>4.14341497421265</v>
+        <v>4.1434154510498</v>
       </c>
       <c r="H424" t="n">
         <v>1701343</v>
@@ -12723,7 +12723,7 @@
         <v>5.32800006866455</v>
       </c>
       <c r="G426" t="n">
-        <v>4.25358724594116</v>
+        <v>4.25358772277832</v>
       </c>
       <c r="H426" t="n">
         <v>1782929</v>
@@ -12868,7 +12868,7 @@
         <v>5.2979998588562</v>
       </c>
       <c r="G431" t="n">
-        <v>4.22963666915894</v>
+        <v>4.22963619232178</v>
       </c>
       <c r="H431" t="n">
         <v>1833402</v>
@@ -12897,7 +12897,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G432" t="n">
-        <v>4.27913475036621</v>
+        <v>4.27913427352905</v>
       </c>
       <c r="H432" t="n">
         <v>1674854</v>
@@ -12984,7 +12984,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G435" t="n">
-        <v>4.35577535629272</v>
+        <v>4.35577487945557</v>
       </c>
       <c r="H435" t="n">
         <v>1371590</v>
@@ -13042,7 +13042,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>4.23123359680176</v>
+        <v>4.2312331199646</v>
       </c>
       <c r="H437" t="n">
         <v>3128652</v>
@@ -13071,7 +13071,7 @@
         <v>5.19600009918213</v>
       </c>
       <c r="G438" t="n">
-        <v>4.14820575714111</v>
+        <v>4.14820528030396</v>
       </c>
       <c r="H438" t="n">
         <v>3674172</v>
@@ -13216,7 +13216,7 @@
         <v>5.3439998626709</v>
       </c>
       <c r="G443" t="n">
-        <v>4.26636028289795</v>
+        <v>4.26636075973511</v>
       </c>
       <c r="H443" t="n">
         <v>2105073</v>
@@ -13245,7 +13245,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>4.23123359680176</v>
+        <v>4.2312331199646</v>
       </c>
       <c r="H444" t="n">
         <v>2016439</v>
@@ -13303,7 +13303,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G446" t="n">
-        <v>4.25039386749268</v>
+        <v>4.25039339065552</v>
       </c>
       <c r="H446" t="n">
         <v>4262357</v>
@@ -13332,7 +13332,7 @@
         <v>5.39400005340576</v>
       </c>
       <c r="G447" t="n">
-        <v>4.30627775192261</v>
+        <v>4.30627822875977</v>
       </c>
       <c r="H447" t="n">
         <v>2978127</v>
@@ -13419,7 +13419,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54737854003906</v>
+        <v>4.54737901687622</v>
       </c>
       <c r="H450" t="n">
         <v>4693010</v>
@@ -13477,7 +13477,7 @@
         <v>5.36399984359741</v>
       </c>
       <c r="G452" t="n">
-        <v>4.28232765197754</v>
+        <v>4.28232717514038</v>
       </c>
       <c r="H452" t="n">
         <v>4056587</v>
@@ -13506,7 +13506,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G453" t="n">
-        <v>4.15139818191528</v>
+        <v>4.15139865875244</v>
       </c>
       <c r="H453" t="n">
         <v>4787912</v>
@@ -13535,7 +13535,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G454" t="n">
-        <v>4.14022159576416</v>
+        <v>4.14022207260132</v>
       </c>
       <c r="H454" t="n">
         <v>4361773</v>
@@ -13680,7 +13680,7 @@
         <v>5.60799980163574</v>
       </c>
       <c r="G459" t="n">
-        <v>4.47712421417236</v>
+        <v>4.47712373733521</v>
       </c>
       <c r="H459" t="n">
         <v>3761167</v>
@@ -13738,7 +13738,7 @@
         <v>5.31400012969971</v>
       </c>
       <c r="G461" t="n">
-        <v>4.24241065979004</v>
+        <v>4.24241018295288</v>
       </c>
       <c r="H461" t="n">
         <v>4723842</v>
@@ -13767,7 +13767,7 @@
         <v>5.3439998626709</v>
       </c>
       <c r="G462" t="n">
-        <v>4.26636028289795</v>
+        <v>4.26636075973511</v>
       </c>
       <c r="H462" t="n">
         <v>2651816</v>
@@ -13796,7 +13796,7 @@
         <v>5.38800001144409</v>
       </c>
       <c r="G463" t="n">
-        <v>4.30148839950562</v>
+        <v>4.30148792266846</v>
       </c>
       <c r="H463" t="n">
         <v>2317291</v>
@@ -13854,7 +13854,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>3.87197804450989</v>
+        <v>3.87197732925415</v>
       </c>
       <c r="H465" t="n">
         <v>5847939</v>
@@ -13883,7 +13883,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G466" t="n">
-        <v>3.76819229125977</v>
+        <v>3.76819252967834</v>
       </c>
       <c r="H466" t="n">
         <v>4448449</v>
@@ -14028,7 +14028,7 @@
         <v>4.75299978256226</v>
       </c>
       <c r="G471" t="n">
-        <v>3.79453825950623</v>
+        <v>3.79453802108765</v>
       </c>
       <c r="H471" t="n">
         <v>4709323</v>
@@ -14057,7 +14057,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G472" t="n">
-        <v>3.64444875717163</v>
+        <v>3.64444899559021</v>
       </c>
       <c r="H472" t="n">
         <v>2861060</v>
@@ -14086,7 +14086,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G473" t="n">
-        <v>3.60532999038696</v>
+        <v>3.60532975196838</v>
       </c>
       <c r="H473" t="n">
         <v>4311711</v>
@@ -14115,7 +14115,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G474" t="n">
-        <v>3.67957639694214</v>
+        <v>3.67957663536072</v>
       </c>
       <c r="H474" t="n">
         <v>2548271</v>
@@ -14144,7 +14144,7 @@
         <v>4.51300001144409</v>
       </c>
       <c r="G475" t="n">
-        <v>3.60293531417847</v>
+        <v>3.60293507575989</v>
       </c>
       <c r="H475" t="n">
         <v>2278675</v>
@@ -14202,7 +14202,7 @@
         <v>4.81300020217896</v>
       </c>
       <c r="G477" t="n">
-        <v>3.8424391746521</v>
+        <v>3.84243941307068</v>
       </c>
       <c r="H477" t="n">
         <v>2898616</v>
@@ -14231,7 +14231,7 @@
         <v>4.6729998588562</v>
       </c>
       <c r="G478" t="n">
-        <v>3.73067045211792</v>
+        <v>3.7306706905365</v>
       </c>
       <c r="H478" t="n">
         <v>2579458</v>
@@ -14289,7 +14289,7 @@
         <v>4.84700012207031</v>
       </c>
       <c r="G480" t="n">
-        <v>3.86958241462708</v>
+        <v>3.86958265304565</v>
       </c>
       <c r="H480" t="n">
         <v>2567620</v>
@@ -14318,7 +14318,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.82407736778259</v>
+        <v>3.82407689094543</v>
       </c>
       <c r="H481" t="n">
         <v>1581513</v>
@@ -14347,7 +14347,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.74025058746338</v>
+        <v>3.74025011062622</v>
       </c>
       <c r="H482" t="n">
         <v>5781269</v>
@@ -14376,7 +14376,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>3.7721848487854</v>
+        <v>3.77218437194824</v>
       </c>
       <c r="H483" t="n">
         <v>3715855</v>
@@ -14405,7 +14405,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>3.76020908355713</v>
+        <v>3.76020884513855</v>
       </c>
       <c r="H484" t="n">
         <v>1701361</v>
@@ -14434,7 +14434,7 @@
         <v>4.6729998588562</v>
       </c>
       <c r="G485" t="n">
-        <v>3.73067045211792</v>
+        <v>3.7306706905365</v>
       </c>
       <c r="H485" t="n">
         <v>1812903</v>
@@ -14463,7 +14463,7 @@
         <v>4.97300004959106</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97017407417297</v>
+        <v>3.97017359733582</v>
       </c>
       <c r="H486" t="n">
         <v>6818273</v>
@@ -14550,7 +14550,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G489" t="n">
-        <v>4.27274799346924</v>
+        <v>4.27274751663208</v>
       </c>
       <c r="H489" t="n">
         <v>6002211</v>
@@ -14637,7 +14637,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>4.4228367805481</v>
+        <v>4.42283630371094</v>
       </c>
       <c r="H492" t="n">
         <v>5033717</v>
@@ -14840,7 +14840,7 @@
         <v>5.44199991226196</v>
       </c>
       <c r="G499" t="n">
-        <v>4.3445987701416</v>
+        <v>4.34459829330444</v>
       </c>
       <c r="H499" t="n">
         <v>3591458</v>
@@ -14869,7 +14869,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G500" t="n">
-        <v>4.2887134552002</v>
+        <v>4.28871440887451</v>
       </c>
       <c r="H500" t="n">
         <v>3137057</v>
@@ -14956,7 +14956,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>4.4228367805481</v>
+        <v>4.42283630371094</v>
       </c>
       <c r="H503" t="n">
         <v>2428806</v>
@@ -15101,7 +15101,7 @@
         <v>5.11800003051758</v>
       </c>
       <c r="G508" t="n">
-        <v>4.08593416213989</v>
+        <v>4.08593463897705</v>
       </c>
       <c r="H508" t="n">
         <v>5998340</v>
@@ -15188,7 +15188,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G511" t="n">
-        <v>4.07954835891724</v>
+        <v>4.07954788208008</v>
       </c>
       <c r="H511" t="n">
         <v>2798919</v>
@@ -15333,7 +15333,7 @@
         <v>5.69399976730347</v>
       </c>
       <c r="G516" t="n">
-        <v>4.54578161239624</v>
+        <v>4.54578113555908</v>
       </c>
       <c r="H516" t="n">
         <v>2588388</v>
@@ -15362,7 +15362,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G517" t="n">
-        <v>4.43082046508789</v>
+        <v>4.43081998825073</v>
       </c>
       <c r="H517" t="n">
         <v>5183857</v>
@@ -15420,7 +15420,7 @@
         <v>5.4539999961853</v>
       </c>
       <c r="G519" t="n">
-        <v>4.3541784286499</v>
+        <v>4.35417890548706</v>
       </c>
       <c r="H519" t="n">
         <v>4000499</v>
@@ -15478,7 +15478,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G521" t="n">
-        <v>4.31266450881958</v>
+        <v>4.31266498565674</v>
       </c>
       <c r="H521" t="n">
         <v>4443258</v>
@@ -15507,7 +15507,7 @@
         <v>5.4539999961853</v>
       </c>
       <c r="G522" t="n">
-        <v>4.3541784286499</v>
+        <v>4.35417890548706</v>
       </c>
       <c r="H522" t="n">
         <v>2878305</v>
@@ -15536,7 +15536,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>4.4627537727356</v>
+        <v>4.46275329589844</v>
       </c>
       <c r="H523" t="n">
         <v>3621477</v>
@@ -15594,7 +15594,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G525" t="n">
-        <v>4.63679313659668</v>
+        <v>4.63679265975952</v>
       </c>
       <c r="H525" t="n">
         <v>3552700</v>
@@ -15623,7 +15623,7 @@
         <v>5.18800020217896</v>
       </c>
       <c r="G526" t="n">
-        <v>4.14181900024414</v>
+        <v>4.14181852340698</v>
       </c>
       <c r="H526" t="n">
         <v>21203083</v>
@@ -15681,7 +15681,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G528" t="n">
-        <v>4.18333196640015</v>
+        <v>4.1833324432373</v>
       </c>
       <c r="H528" t="n">
         <v>2888851</v>
@@ -15710,7 +15710,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G529" t="n">
-        <v>4.32703447341919</v>
+        <v>4.32703495025635</v>
       </c>
       <c r="H529" t="n">
         <v>6851432</v>
@@ -15884,7 +15884,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.4148530960083</v>
+        <v>4.41485357284546</v>
       </c>
       <c r="H535" t="n">
         <v>4053856</v>
@@ -16029,7 +16029,7 @@
         <v>5.21400022506714</v>
       </c>
       <c r="G540" t="n">
-        <v>4.16257572174072</v>
+        <v>4.16257619857788</v>
       </c>
       <c r="H540" t="n">
         <v>4373570</v>
@@ -16058,7 +16058,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>4.14341497421265</v>
+        <v>4.1434154510498</v>
       </c>
       <c r="H541" t="n">
         <v>3194214</v>
@@ -16087,7 +16087,7 @@
         <v>5.18800020217896</v>
       </c>
       <c r="G542" t="n">
-        <v>4.14181900024414</v>
+        <v>4.14181852340698</v>
       </c>
       <c r="H542" t="n">
         <v>2561605</v>
@@ -16290,7 +16290,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G549" t="n">
-        <v>4.0699667930603</v>
+        <v>4.06996774673462</v>
       </c>
       <c r="H549" t="n">
         <v>3624315</v>
@@ -16319,7 +16319,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G550" t="n">
-        <v>4.03164720535278</v>
+        <v>4.03164672851562</v>
       </c>
       <c r="H550" t="n">
         <v>2770919</v>
@@ -16348,7 +16348,7 @@
         <v>5.09800004959106</v>
       </c>
       <c r="G551" t="n">
-        <v>4.0699667930603</v>
+        <v>4.06996774673462</v>
       </c>
       <c r="H551" t="n">
         <v>2173884</v>
@@ -16406,7 +16406,7 @@
         <v>5.14200019836426</v>
       </c>
       <c r="G553" t="n">
-        <v>4.10509490966797</v>
+        <v>4.10509443283081</v>
       </c>
       <c r="H553" t="n">
         <v>1526086</v>
@@ -16609,7 +16609,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G560" t="n">
-        <v>4.20089626312256</v>
+        <v>4.20089673995972</v>
       </c>
       <c r="H560" t="n">
         <v>1839922</v>
@@ -16638,7 +16638,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G561" t="n">
-        <v>4.16576862335205</v>
+        <v>4.16576910018921</v>
       </c>
       <c r="H561" t="n">
         <v>2216343</v>
@@ -16725,7 +16725,7 @@
         <v>5.21600008010864</v>
       </c>
       <c r="G564" t="n">
-        <v>4.16417217254639</v>
+        <v>4.16417264938354</v>
       </c>
       <c r="H564" t="n">
         <v>1011107</v>
@@ -16754,7 +16754,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G565" t="n">
-        <v>4.15299558639526</v>
+        <v>4.15299510955811</v>
       </c>
       <c r="H565" t="n">
         <v>1322873</v>
@@ -16783,7 +16783,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G566" t="n">
-        <v>4.10349798202515</v>
+        <v>4.10349750518799</v>
       </c>
       <c r="H566" t="n">
         <v>1269644</v>
@@ -16899,7 +16899,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G570" t="n">
-        <v>4.16576862335205</v>
+        <v>4.16576910018921</v>
       </c>
       <c r="H570" t="n">
         <v>3604289</v>
@@ -16928,7 +16928,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G571" t="n">
-        <v>4.24720048904419</v>
+        <v>4.24720001220703</v>
       </c>
       <c r="H571" t="n">
         <v>3827018</v>
@@ -16986,7 +16986,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G573" t="n">
-        <v>4.23123359680176</v>
+        <v>4.2312331199646</v>
       </c>
       <c r="H573" t="n">
         <v>1225817</v>
@@ -17015,7 +17015,7 @@
         <v>5.25400018692017</v>
       </c>
       <c r="G574" t="n">
-        <v>4.19450902938843</v>
+        <v>4.19450950622559</v>
       </c>
       <c r="H574" t="n">
         <v>2166563</v>
@@ -17073,7 +17073,7 @@
         <v>5.02799987792969</v>
       </c>
       <c r="G576" t="n">
-        <v>4.01408243179321</v>
+        <v>4.01408290863037</v>
       </c>
       <c r="H576" t="n">
         <v>3884688</v>
@@ -17102,7 +17102,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G577" t="n">
-        <v>4.0508074760437</v>
+        <v>4.05080652236938</v>
       </c>
       <c r="H577" t="n">
         <v>5524918</v>
@@ -17247,7 +17247,7 @@
         <v>4.91200017929077</v>
       </c>
       <c r="G582" t="n">
-        <v>3.92147564888</v>
+        <v>3.92147588729858</v>
       </c>
       <c r="H582" t="n">
         <v>4658611</v>
@@ -17276,7 +17276,7 @@
         <v>4.78900003433228</v>
       </c>
       <c r="G583" t="n">
-        <v>3.82327890396118</v>
+        <v>3.8232786655426</v>
       </c>
       <c r="H583" t="n">
         <v>11701850</v>
@@ -17334,7 +17334,7 @@
         <v>4.58300018310547</v>
       </c>
       <c r="G585" t="n">
-        <v>3.65881943702698</v>
+        <v>3.65881967544556</v>
       </c>
       <c r="H585" t="n">
         <v>5364133</v>
@@ -17421,7 +17421,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G588" t="n">
-        <v>3.49036884307861</v>
+        <v>3.49036860466003</v>
       </c>
       <c r="H588" t="n">
         <v>6889328</v>
@@ -17479,7 +17479,7 @@
         <v>4.36299991607666</v>
       </c>
       <c r="G590" t="n">
-        <v>3.48318314552307</v>
+        <v>3.48318290710449</v>
       </c>
       <c r="H590" t="n">
         <v>6428207</v>
@@ -17595,7 +17595,7 @@
         <v>4.50899982452393</v>
       </c>
       <c r="G594" t="n">
-        <v>3.59974193572998</v>
+        <v>3.59974145889282</v>
       </c>
       <c r="H594" t="n">
         <v>2408795</v>
@@ -17653,7 +17653,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G596" t="n">
-        <v>3.67957639694214</v>
+        <v>3.67957663536072</v>
       </c>
       <c r="H596" t="n">
         <v>4652125</v>
@@ -17682,7 +17682,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G597" t="n">
-        <v>3.60054016113281</v>
+        <v>3.60054039955139</v>
       </c>
       <c r="H597" t="n">
         <v>6336601</v>
@@ -17711,7 +17711,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>3.60852336883545</v>
+        <v>3.60852360725403</v>
       </c>
       <c r="H598" t="n">
         <v>3399120</v>
@@ -17740,7 +17740,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G599" t="n">
-        <v>3.76819229125977</v>
+        <v>3.76819252967834</v>
       </c>
       <c r="H599" t="n">
         <v>7494823</v>
@@ -17769,7 +17769,7 @@
         <v>4.70900011062622</v>
       </c>
       <c r="G600" t="n">
-        <v>3.75941109657288</v>
+        <v>3.75941061973572</v>
       </c>
       <c r="H600" t="n">
         <v>4447046</v>
@@ -17798,7 +17798,7 @@
         <v>4.86600017547607</v>
       </c>
       <c r="G601" t="n">
-        <v>3.88475179672241</v>
+        <v>3.88475155830383</v>
       </c>
       <c r="H601" t="n">
         <v>10983974</v>
@@ -17856,7 +17856,7 @@
         <v>4.75299978256226</v>
       </c>
       <c r="G603" t="n">
-        <v>3.79453825950623</v>
+        <v>3.79453802108765</v>
       </c>
       <c r="H603" t="n">
         <v>4205571</v>
@@ -17885,7 +17885,7 @@
         <v>4.45900011062622</v>
       </c>
       <c r="G604" t="n">
-        <v>3.5598247051239</v>
+        <v>3.55982422828674</v>
       </c>
       <c r="H604" t="n">
         <v>8229899</v>
@@ -17943,7 +17943,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G606" t="n">
-        <v>3.55742883682251</v>
+        <v>3.55742907524109</v>
       </c>
       <c r="H606" t="n">
         <v>5214931</v>
@@ -17972,7 +17972,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G607" t="n">
-        <v>3.44885396957397</v>
+        <v>3.44885420799255</v>
       </c>
       <c r="H607" t="n">
         <v>7650637</v>
@@ -18001,7 +18001,7 @@
         <v>4.25299978256226</v>
       </c>
       <c r="G608" t="n">
-        <v>3.3953652381897</v>
+        <v>3.39536499977112</v>
       </c>
       <c r="H608" t="n">
         <v>7078011</v>
@@ -18117,7 +18117,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>3.12951564788818</v>
+        <v>3.12951588630676</v>
       </c>
       <c r="H612" t="n">
         <v>6435404</v>
@@ -18146,7 +18146,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G613" t="n">
-        <v>3.1087589263916</v>
+        <v>3.10875916481018</v>
       </c>
       <c r="H613" t="n">
         <v>8219341</v>
@@ -18233,7 +18233,7 @@
         <v>3.81299996376038</v>
       </c>
       <c r="G616" t="n">
-        <v>3.04409265518188</v>
+        <v>3.04409289360046</v>
       </c>
       <c r="H616" t="n">
         <v>7465288</v>
@@ -18349,7 +18349,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G620" t="n">
-        <v>2.68004751205444</v>
+        <v>2.68004727363586</v>
       </c>
       <c r="H620" t="n">
         <v>6043852</v>
@@ -18436,7 +18436,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G623" t="n">
-        <v>2.8740451335907</v>
+        <v>2.87404537200928</v>
       </c>
       <c r="H623" t="n">
         <v>16884906</v>
@@ -18523,7 +18523,7 @@
         <v>3.45300006866455</v>
       </c>
       <c r="G626" t="n">
-        <v>2.75668835639954</v>
+        <v>2.75668859481812</v>
       </c>
       <c r="H626" t="n">
         <v>8623249</v>
@@ -18552,7 +18552,7 @@
         <v>3.38100004196167</v>
       </c>
       <c r="G627" t="n">
-        <v>2.6992073059082</v>
+        <v>2.69920754432678</v>
       </c>
       <c r="H627" t="n">
         <v>9943300</v>
@@ -18581,7 +18581,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G628" t="n">
-        <v>2.65450048446655</v>
+        <v>2.65450024604797</v>
       </c>
       <c r="H628" t="n">
         <v>6000213</v>
@@ -18610,7 +18610,7 @@
         <v>3.34100008010864</v>
       </c>
       <c r="G629" t="n">
-        <v>2.6672739982605</v>
+        <v>2.66727375984192</v>
       </c>
       <c r="H629" t="n">
         <v>3510090</v>
@@ -18784,7 +18784,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G635" t="n">
-        <v>2.56748056411743</v>
+        <v>2.56748080253601</v>
       </c>
       <c r="H635" t="n">
         <v>7899022</v>
@@ -18813,7 +18813,7 @@
         <v>3.38199996948242</v>
       </c>
       <c r="G636" t="n">
-        <v>2.70000553131104</v>
+        <v>2.70000576972961</v>
       </c>
       <c r="H636" t="n">
         <v>4018148</v>
@@ -18842,7 +18842,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G637" t="n">
-        <v>2.69681239128113</v>
+        <v>2.69681262969971</v>
       </c>
       <c r="H637" t="n">
         <v>5445633</v>
@@ -18871,7 +18871,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G638" t="n">
-        <v>2.64731526374817</v>
+        <v>2.64731502532959</v>
       </c>
       <c r="H638" t="n">
         <v>3349455</v>
@@ -18929,7 +18929,7 @@
         <v>3.28600001335144</v>
       </c>
       <c r="G640" t="n">
-        <v>2.62336421012878</v>
+        <v>2.62336444854736</v>
       </c>
       <c r="H640" t="n">
         <v>4401473</v>
@@ -18958,7 +18958,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>2.62655782699585</v>
+        <v>2.62655830383301</v>
       </c>
       <c r="H641" t="n">
         <v>3511058</v>
@@ -19074,7 +19074,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G645" t="n">
-        <v>2.64731526374817</v>
+        <v>2.64731502532959</v>
       </c>
       <c r="H645" t="n">
         <v>1198096</v>
@@ -19103,7 +19103,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G646" t="n">
-        <v>2.68004751205444</v>
+        <v>2.68004727363586</v>
       </c>
       <c r="H646" t="n">
         <v>1543079</v>
@@ -19161,7 +19161,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G648" t="n">
-        <v>2.73513317108154</v>
+        <v>2.73513340950012</v>
       </c>
       <c r="H648" t="n">
         <v>2714923</v>
@@ -19190,7 +19190,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G649" t="n">
-        <v>2.81816101074219</v>
+        <v>2.81816077232361</v>
       </c>
       <c r="H649" t="n">
         <v>3163107</v>
@@ -19219,7 +19219,7 @@
         <v>3.55399990081787</v>
       </c>
       <c r="G650" t="n">
-        <v>2.83732151985168</v>
+        <v>2.83732128143311</v>
       </c>
       <c r="H650" t="n">
         <v>5429729</v>
@@ -19480,7 +19480,7 @@
         <v>3.58699989318848</v>
       </c>
       <c r="G659" t="n">
-        <v>2.86366653442383</v>
+        <v>2.86366677284241</v>
       </c>
       <c r="H659" t="n">
         <v>3081090</v>
@@ -19509,7 +19509,7 @@
         <v>3.59699988365173</v>
       </c>
       <c r="G660" t="n">
-        <v>2.87164998054504</v>
+        <v>2.87165021896362</v>
       </c>
       <c r="H660" t="n">
         <v>3173757</v>
@@ -19567,7 +19567,7 @@
         <v>3.45099997520447</v>
       </c>
       <c r="G662" t="n">
-        <v>2.75509166717529</v>
+        <v>2.75509142875671</v>
       </c>
       <c r="H662" t="n">
         <v>5786998</v>
@@ -19683,7 +19683,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G666" t="n">
-        <v>2.8932056427002</v>
+        <v>2.89320588111877</v>
       </c>
       <c r="H666" t="n">
         <v>1922555</v>
@@ -19741,7 +19741,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G668" t="n">
-        <v>3.05127811431885</v>
+        <v>3.05127835273743</v>
       </c>
       <c r="H668" t="n">
         <v>5929228</v>
@@ -19799,7 +19799,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>3.21733403205872</v>
+        <v>3.21733427047729</v>
       </c>
       <c r="H670" t="n">
         <v>9621540</v>
@@ -19828,7 +19828,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G671" t="n">
-        <v>3.21094727516174</v>
+        <v>3.21094703674316</v>
       </c>
       <c r="H671" t="n">
         <v>2761689</v>
@@ -19857,7 +19857,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G672" t="n">
-        <v>3.25565481185913</v>
+        <v>3.25565457344055</v>
       </c>
       <c r="H672" t="n">
         <v>3468706</v>
@@ -19886,7 +19886,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G673" t="n">
-        <v>3.37380957603455</v>
+        <v>3.37380933761597</v>
       </c>
       <c r="H673" t="n">
         <v>3421967</v>
@@ -20002,7 +20002,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G677" t="n">
-        <v>3.38498640060425</v>
+        <v>3.38498616218567</v>
       </c>
       <c r="H677" t="n">
         <v>3819140</v>
@@ -20031,7 +20031,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G678" t="n">
-        <v>3.36502814292908</v>
+        <v>3.36502838134766</v>
       </c>
       <c r="H678" t="n">
         <v>3499100</v>
@@ -20060,7 +20060,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G679" t="n">
-        <v>3.07762384414673</v>
+        <v>3.07762360572815</v>
       </c>
       <c r="H679" t="n">
         <v>6114529</v>
@@ -20089,7 +20089,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G680" t="n">
-        <v>3.11354947090149</v>
+        <v>3.11354923248291</v>
       </c>
       <c r="H680" t="n">
         <v>3936480</v>
@@ -20118,7 +20118,7 @@
         <v>3.9210000038147</v>
       </c>
       <c r="G681" t="n">
-        <v>3.13031411170959</v>
+        <v>3.13031458854675</v>
       </c>
       <c r="H681" t="n">
         <v>2399572</v>
@@ -20176,7 +20176,7 @@
         <v>4</v>
       </c>
       <c r="G683" t="n">
-        <v>3.19338369369507</v>
+        <v>3.19338393211365</v>
       </c>
       <c r="H683" t="n">
         <v>2791331</v>
@@ -20263,7 +20263,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.11354947090149</v>
+        <v>3.11354923248291</v>
       </c>
       <c r="H686" t="n">
         <v>2395917</v>
@@ -20292,7 +20292,7 @@
         <v>4.01100015640259</v>
       </c>
       <c r="G687" t="n">
-        <v>3.20216584205627</v>
+        <v>3.20216608047485</v>
       </c>
       <c r="H687" t="n">
         <v>3725678</v>
@@ -20321,7 +20321,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G688" t="n">
-        <v>3.04010128974915</v>
+        <v>3.04010152816772</v>
       </c>
       <c r="H688" t="n">
         <v>3753771</v>
@@ -20379,7 +20379,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>3.04010128974915</v>
+        <v>3.04010152816772</v>
       </c>
       <c r="H690" t="n">
         <v>2963869</v>
@@ -20408,7 +20408,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G691" t="n">
-        <v>3.09758234024048</v>
+        <v>3.0975821018219</v>
       </c>
       <c r="H691" t="n">
         <v>2190284</v>
@@ -20437,7 +20437,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G692" t="n">
-        <v>3.01375579833984</v>
+        <v>3.01375603675842</v>
       </c>
       <c r="H692" t="n">
         <v>2650452</v>
@@ -20495,7 +20495,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G694" t="n">
-        <v>3.05447149276733</v>
+        <v>3.05447125434875</v>
       </c>
       <c r="H694" t="n">
         <v>4711399</v>
@@ -20553,7 +20553,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G696" t="n">
-        <v>3.03211760520935</v>
+        <v>3.03211784362793</v>
       </c>
       <c r="H696" t="n">
         <v>2919023</v>
@@ -20582,7 +20582,7 @@
         <v>3.78099989891052</v>
       </c>
       <c r="G697" t="n">
-        <v>3.01854562759399</v>
+        <v>3.01854586601257</v>
       </c>
       <c r="H697" t="n">
         <v>1681574</v>
@@ -20669,7 +20669,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G700" t="n">
-        <v>2.96585464477539</v>
+        <v>2.96585488319397</v>
       </c>
       <c r="H700" t="n">
         <v>3333759</v>
@@ -20727,7 +20727,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G702" t="n">
-        <v>2.96026682853699</v>
+        <v>2.96026635169983</v>
       </c>
       <c r="H702" t="n">
         <v>2786641</v>
@@ -20843,7 +20843,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G706" t="n">
-        <v>2.98581385612488</v>
+        <v>2.9858136177063</v>
       </c>
       <c r="H706" t="n">
         <v>3918653</v>
@@ -20872,7 +20872,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G707" t="n">
-        <v>3.09758234024048</v>
+        <v>3.0975821018219</v>
       </c>
       <c r="H707" t="n">
         <v>4648844</v>
@@ -20930,7 +20930,7 @@
         <v>3.78099989891052</v>
       </c>
       <c r="G709" t="n">
-        <v>3.01854562759399</v>
+        <v>3.01854586601257</v>
       </c>
       <c r="H709" t="n">
         <v>2822705</v>
@@ -21075,7 +21075,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G714" t="n">
-        <v>2.7734534740448</v>
+        <v>2.77345371246338</v>
       </c>
       <c r="H714" t="n">
         <v>3493137</v>
@@ -21104,7 +21104,7 @@
         <v>3.36299991607666</v>
       </c>
       <c r="G715" t="n">
-        <v>2.68483710289001</v>
+        <v>2.68483734130859</v>
       </c>
       <c r="H715" t="n">
         <v>2932370</v>
@@ -21191,7 +21191,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G718" t="n">
-        <v>2.94909000396729</v>
+        <v>2.94908976554871</v>
       </c>
       <c r="H718" t="n">
         <v>2816589</v>
@@ -21220,7 +21220,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G719" t="n">
-        <v>2.80858063697815</v>
+        <v>2.80858087539673</v>
       </c>
       <c r="H719" t="n">
         <v>8851149</v>
@@ -21307,7 +21307,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G722" t="n">
-        <v>2.9682502746582</v>
+        <v>2.96825003623962</v>
       </c>
       <c r="H722" t="n">
         <v>3797095</v>
@@ -21365,7 +21365,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G724" t="n">
-        <v>2.98581385612488</v>
+        <v>2.9858136177063</v>
       </c>
       <c r="H724" t="n">
         <v>1775181</v>
@@ -21481,7 +21481,7 @@
         <v>3.73300004005432</v>
       </c>
       <c r="G728" t="n">
-        <v>2.98022532463074</v>
+        <v>2.98022508621216</v>
       </c>
       <c r="H728" t="n">
         <v>1181940</v>
@@ -21510,7 +21510,7 @@
         <v>3.6470000743866</v>
       </c>
       <c r="G729" t="n">
-        <v>2.91156768798828</v>
+        <v>2.9115674495697</v>
       </c>
       <c r="H729" t="n">
         <v>1509920</v>
@@ -21539,7 +21539,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G730" t="n">
-        <v>2.85488510131836</v>
+        <v>2.85488486289978</v>
       </c>
       <c r="H730" t="n">
         <v>1573218</v>
@@ -21655,7 +21655,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>2.96186327934265</v>
+        <v>2.96186351776123</v>
       </c>
       <c r="H734" t="n">
         <v>1213470</v>
@@ -21684,7 +21684,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G735" t="n">
-        <v>2.90757584571838</v>
+        <v>2.9075756072998</v>
       </c>
       <c r="H735" t="n">
         <v>1203332</v>
@@ -21800,7 +21800,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G739" t="n">
-        <v>2.90597915649414</v>
+        <v>2.90597891807556</v>
       </c>
       <c r="H739" t="n">
         <v>2628723</v>
@@ -21916,7 +21916,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G743" t="n">
-        <v>3.07522821426392</v>
+        <v>3.0752284526825</v>
       </c>
       <c r="H743" t="n">
         <v>2215232</v>
@@ -21945,7 +21945,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G744" t="n">
-        <v>3.11354947090149</v>
+        <v>3.11354923248291</v>
       </c>
       <c r="H744" t="n">
         <v>4111384</v>
@@ -22032,7 +22032,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G747" t="n">
-        <v>3.06165647506714</v>
+        <v>3.06165671348572</v>
       </c>
       <c r="H747" t="n">
         <v>2132412</v>
@@ -22061,7 +22061,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G748" t="n">
-        <v>3.07762384414673</v>
+        <v>3.07762360572815</v>
       </c>
       <c r="H748" t="n">
         <v>1301407</v>
@@ -22119,7 +22119,7 @@
         <v>3.95900011062622</v>
       </c>
       <c r="G750" t="n">
-        <v>3.16065168380737</v>
+        <v>3.16065144538879</v>
       </c>
       <c r="H750" t="n">
         <v>4618724</v>
@@ -22148,7 +22148,7 @@
         <v>3.75699996948242</v>
       </c>
       <c r="G751" t="n">
-        <v>2.99938559532166</v>
+        <v>2.99938535690308</v>
       </c>
       <c r="H751" t="n">
         <v>3188876</v>
@@ -22206,7 +22206,7 @@
         <v>3.81900000572205</v>
       </c>
       <c r="G753" t="n">
-        <v>3.04888319969177</v>
+        <v>3.04888296127319</v>
       </c>
       <c r="H753" t="n">
         <v>2498213</v>
@@ -22264,7 +22264,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G755" t="n">
-        <v>2.90597915649414</v>
+        <v>2.90597891807556</v>
       </c>
       <c r="H755" t="n">
         <v>2609560</v>
@@ -22351,7 +22351,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G758" t="n">
-        <v>2.92354297637939</v>
+        <v>2.92354273796082</v>
       </c>
       <c r="H758" t="n">
         <v>2329517</v>
@@ -22380,7 +22380,7 @@
         <v>3.58299994468689</v>
       </c>
       <c r="G759" t="n">
-        <v>2.86047339439392</v>
+        <v>2.86047315597534</v>
       </c>
       <c r="H759" t="n">
         <v>3222216</v>
@@ -22467,7 +22467,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G762" t="n">
-        <v>3.07762384414673</v>
+        <v>3.07762360572815</v>
       </c>
       <c r="H762" t="n">
         <v>4804396</v>
@@ -22496,7 +22496,7 @@
         <v>3.82699990272522</v>
       </c>
       <c r="G763" t="n">
-        <v>3.05526971817017</v>
+        <v>3.05526995658875</v>
       </c>
       <c r="H763" t="n">
         <v>2346346</v>
@@ -22525,7 +22525,7 @@
         <v>3.9909999370575</v>
       </c>
       <c r="G764" t="n">
-        <v>3.18619847297668</v>
+        <v>3.18619871139526</v>
       </c>
       <c r="H764" t="n">
         <v>8427170</v>
@@ -22583,7 +22583,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G766" t="n">
-        <v>3.11674237251282</v>
+        <v>3.11674213409424</v>
       </c>
       <c r="H766" t="n">
         <v>4213016</v>
@@ -22612,7 +22612,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G767" t="n">
-        <v>3.06564807891846</v>
+        <v>3.06564831733704</v>
       </c>
       <c r="H767" t="n">
         <v>2964395</v>
@@ -22641,7 +22641,7 @@
         <v>3.84400010108948</v>
       </c>
       <c r="G768" t="n">
-        <v>3.06884169578552</v>
+        <v>3.0688419342041</v>
       </c>
       <c r="H768" t="n">
         <v>1475717</v>
@@ -22786,7 +22786,7 @@
         <v>3.68899989128113</v>
       </c>
       <c r="G773" t="n">
-        <v>2.94509768486023</v>
+        <v>2.94509792327881</v>
       </c>
       <c r="H773" t="n">
         <v>3433440</v>
@@ -22815,7 +22815,7 @@
         <v>3.78299999237061</v>
       </c>
       <c r="G774" t="n">
-        <v>3.02014231681824</v>
+        <v>3.02014255523682</v>
       </c>
       <c r="H774" t="n">
         <v>3457710</v>
@@ -22844,7 +22844,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G775" t="n">
-        <v>3.2812020778656</v>
+        <v>3.28120183944702</v>
       </c>
       <c r="H775" t="n">
         <v>13906345</v>
@@ -22902,7 +22902,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G777" t="n">
-        <v>3.00577235221863</v>
+        <v>3.00577259063721</v>
       </c>
       <c r="H777" t="n">
         <v>6184054</v>
@@ -22989,7 +22989,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G780" t="n">
-        <v>2.85807800292969</v>
+        <v>2.85807824134827</v>
       </c>
       <c r="H780" t="n">
         <v>4129192</v>
@@ -23163,7 +23163,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G786" t="n">
-        <v>3.36582636833191</v>
+        <v>3.36582612991333</v>
       </c>
       <c r="H786" t="n">
         <v>12035706</v>
@@ -23192,7 +23192,7 @@
         <v>4.23299980163574</v>
       </c>
       <c r="G787" t="n">
-        <v>3.37939810752869</v>
+        <v>3.37939786911011</v>
       </c>
       <c r="H787" t="n">
         <v>6292817</v>
@@ -23221,7 +23221,7 @@
         <v>4.27899980545044</v>
       </c>
       <c r="G788" t="n">
-        <v>3.41612219810486</v>
+        <v>3.41612195968628</v>
       </c>
       <c r="H788" t="n">
         <v>5193817</v>
@@ -23250,7 +23250,7 @@
         <v>4</v>
       </c>
       <c r="G789" t="n">
-        <v>3.19338369369507</v>
+        <v>3.19338393211365</v>
       </c>
       <c r="H789" t="n">
         <v>10622676</v>
@@ -23482,7 +23482,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G797" t="n">
-        <v>3.40734004974365</v>
+        <v>3.40734028816223</v>
       </c>
       <c r="H797" t="n">
         <v>4608848</v>
@@ -23511,7 +23511,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G798" t="n">
-        <v>3.45843410491943</v>
+        <v>3.45843434333801</v>
       </c>
       <c r="H798" t="n">
         <v>4749283</v>
@@ -23569,7 +23569,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G800" t="n">
-        <v>3.4688127040863</v>
+        <v>3.46881294250488</v>
       </c>
       <c r="H800" t="n">
         <v>8062494</v>
@@ -23627,7 +23627,7 @@
         <v>4.50099992752075</v>
       </c>
       <c r="G802" t="n">
-        <v>3.59335470199585</v>
+        <v>3.59335494041443</v>
       </c>
       <c r="H802" t="n">
         <v>3709710</v>
@@ -23714,7 +23714,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G805" t="n">
-        <v>3.60213685035706</v>
+        <v>3.60213661193848</v>
       </c>
       <c r="H805" t="n">
         <v>3144898</v>
@@ -23743,7 +23743,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>3.55663084983826</v>
+        <v>3.55663061141968</v>
       </c>
       <c r="H806" t="n">
         <v>2012341</v>
@@ -23772,7 +23772,7 @@
         <v>4.45900011062622</v>
       </c>
       <c r="G807" t="n">
-        <v>3.5598247051239</v>
+        <v>3.55982422828674</v>
       </c>
       <c r="H807" t="n">
         <v>1453180</v>
@@ -23917,7 +23917,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G812" t="n">
-        <v>3.51272201538086</v>
+        <v>3.51272225379944</v>
       </c>
       <c r="H812" t="n">
         <v>7525445</v>
@@ -24004,7 +24004,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G815" t="n">
-        <v>3.50793194770813</v>
+        <v>3.50793170928955</v>
       </c>
       <c r="H815" t="n">
         <v>11904185</v>
@@ -24091,7 +24091,7 @@
         <v>4.40299987792969</v>
       </c>
       <c r="G818" t="n">
-        <v>3.51511693000793</v>
+        <v>3.51511669158936</v>
       </c>
       <c r="H818" t="n">
         <v>2717001</v>
@@ -24120,7 +24120,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G819" t="n">
-        <v>3.60453128814697</v>
+        <v>3.60453152656555</v>
       </c>
       <c r="H819" t="n">
         <v>4056509</v>
@@ -24149,7 +24149,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G820" t="n">
-        <v>3.56062245368958</v>
+        <v>3.56062269210815</v>
       </c>
       <c r="H820" t="n">
         <v>1970058</v>
@@ -24207,7 +24207,7 @@
         <v>4.35900020599365</v>
       </c>
       <c r="G822" t="n">
-        <v>3.47998976707458</v>
+        <v>3.47999000549316</v>
       </c>
       <c r="H822" t="n">
         <v>3487392</v>
@@ -24294,7 +24294,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>3.54465579986572</v>
+        <v>3.5446560382843</v>
       </c>
       <c r="H825" t="n">
         <v>4749576</v>
@@ -24323,7 +24323,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G826" t="n">
-        <v>3.54944586753845</v>
+        <v>3.54944610595703</v>
       </c>
       <c r="H826" t="n">
         <v>4809149</v>
@@ -24410,7 +24410,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G829" t="n">
-        <v>3.58297610282898</v>
+        <v>3.58297634124756</v>
       </c>
       <c r="H829" t="n">
         <v>2831592</v>
@@ -24439,7 +24439,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G830" t="n">
-        <v>3.54465579986572</v>
+        <v>3.5446560382843</v>
       </c>
       <c r="H830" t="n">
         <v>2051814</v>
@@ -24468,7 +24468,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G831" t="n">
-        <v>3.46322441101074</v>
+        <v>3.46322417259216</v>
       </c>
       <c r="H831" t="n">
         <v>2158544</v>
@@ -24526,7 +24526,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G833" t="n">
-        <v>3.50793194770813</v>
+        <v>3.50793170928955</v>
       </c>
       <c r="H833" t="n">
         <v>1395315</v>
@@ -24613,7 +24613,7 @@
         <v>4.29099988937378</v>
       </c>
       <c r="G836" t="n">
-        <v>3.42570209503174</v>
+        <v>3.42570233345032</v>
       </c>
       <c r="H836" t="n">
         <v>3192309</v>
@@ -24671,7 +24671,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G838" t="n">
-        <v>3.44885396957397</v>
+        <v>3.44885420799255</v>
       </c>
       <c r="H838" t="n">
         <v>2820049</v>
@@ -24700,7 +24700,7 @@
         <v>4.26900005340576</v>
       </c>
       <c r="G839" t="n">
-        <v>3.40813875198364</v>
+        <v>3.40813851356506</v>
       </c>
       <c r="H839" t="n">
         <v>8596223</v>
@@ -24729,7 +24729,7 @@
         <v>4.27899980545044</v>
       </c>
       <c r="G840" t="n">
-        <v>3.41612219810486</v>
+        <v>3.41612195968628</v>
       </c>
       <c r="H840" t="n">
         <v>4085081</v>
@@ -24874,7 +24874,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G845" t="n">
-        <v>3.72029137611389</v>
+        <v>3.72029161453247</v>
       </c>
       <c r="H845" t="n">
         <v>8839185</v>
@@ -24903,7 +24903,7 @@
         <v>4.67600011825562</v>
       </c>
       <c r="G846" t="n">
-        <v>3.73306560516357</v>
+        <v>3.73306584358215</v>
       </c>
       <c r="H846" t="n">
         <v>5484583</v>
@@ -24932,7 +24932,7 @@
         <v>4.72300004959106</v>
       </c>
       <c r="G847" t="n">
-        <v>3.77058744430542</v>
+        <v>3.770587682724</v>
       </c>
       <c r="H847" t="n">
         <v>3796397</v>
@@ -24961,7 +24961,7 @@
         <v>4.69299983978271</v>
       </c>
       <c r="G848" t="n">
-        <v>3.74663710594177</v>
+        <v>3.74663734436035</v>
       </c>
       <c r="H848" t="n">
         <v>4481975</v>
@@ -24990,7 +24990,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G849" t="n">
-        <v>3.71630072593689</v>
+        <v>3.71630048751831</v>
       </c>
       <c r="H849" t="n">
         <v>2569243</v>
@@ -25077,7 +25077,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>3.78815150260925</v>
+        <v>3.78815102577209</v>
       </c>
       <c r="H852" t="n">
         <v>2450719</v>
@@ -25106,7 +25106,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>3.76420116424561</v>
+        <v>3.76420092582703</v>
       </c>
       <c r="H853" t="n">
         <v>2607308</v>
@@ -25135,7 +25135,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G854" t="n">
-        <v>3.68995499610901</v>
+        <v>3.68995475769043</v>
       </c>
       <c r="H854" t="n">
         <v>3076913</v>
@@ -25164,7 +25164,7 @@
         <v>4.60099983215332</v>
       </c>
       <c r="G855" t="n">
-        <v>3.67318964004517</v>
+        <v>3.67318916320801</v>
       </c>
       <c r="H855" t="n">
         <v>1427684</v>
@@ -25193,7 +25193,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>3.75861287117004</v>
+        <v>3.75861310958862</v>
       </c>
       <c r="H856" t="n">
         <v>1816097</v>
@@ -25222,7 +25222,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>3.90790367126465</v>
+        <v>3.90790295600891</v>
       </c>
       <c r="H857" t="n">
         <v>4999525</v>
@@ -25251,7 +25251,7 @@
         <v>4.77099990844727</v>
       </c>
       <c r="G858" t="n">
-        <v>3.80890822410583</v>
+        <v>3.80890798568726</v>
       </c>
       <c r="H858" t="n">
         <v>3010730</v>
@@ -25280,7 +25280,7 @@
         <v>4.81400012969971</v>
       </c>
       <c r="G859" t="n">
-        <v>3.84323692321777</v>
+        <v>3.84323763847351</v>
       </c>
       <c r="H859" t="n">
         <v>3514103</v>
@@ -25309,7 +25309,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G860" t="n">
-        <v>3.81609392166138</v>
+        <v>3.81609344482422</v>
       </c>
       <c r="H860" t="n">
         <v>2057831</v>
@@ -25338,7 +25338,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G861" t="n">
-        <v>3.8121018409729</v>
+        <v>3.81210160255432</v>
       </c>
       <c r="H861" t="n">
         <v>2749850</v>
@@ -25367,7 +25367,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G862" t="n">
-        <v>3.86399459838867</v>
+        <v>3.86399435997009</v>
       </c>
       <c r="H862" t="n">
         <v>2024564</v>
@@ -25454,7 +25454,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G865" t="n">
-        <v>3.84802746772766</v>
+        <v>3.84802722930908</v>
       </c>
       <c r="H865" t="n">
         <v>3768195</v>
@@ -25512,7 +25512,7 @@
         <v>4.9689998626709</v>
       </c>
       <c r="G867" t="n">
-        <v>3.96698045730591</v>
+        <v>3.96698069572449</v>
       </c>
       <c r="H867" t="n">
         <v>3957020</v>
@@ -25541,7 +25541,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G868" t="n">
-        <v>3.95340895652771</v>
+        <v>3.95340871810913</v>
       </c>
       <c r="H868" t="n">
         <v>3882618</v>
@@ -25599,7 +25599,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G870" t="n">
-        <v>3.91508817672729</v>
+        <v>3.91508793830872</v>
       </c>
       <c r="H870" t="n">
         <v>7781306</v>
@@ -25628,7 +25628,7 @@
         <v>4.90299987792969</v>
       </c>
       <c r="G871" t="n">
-        <v>3.9142894744873</v>
+        <v>3.91428971290588</v>
       </c>
       <c r="H871" t="n">
         <v>2979867</v>
@@ -25686,7 +25686,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G873" t="n">
-        <v>3.91269302368164</v>
+        <v>3.9126935005188</v>
       </c>
       <c r="H873" t="n">
         <v>2975747</v>
@@ -25715,7 +25715,7 @@
         <v>5</v>
       </c>
       <c r="G874" t="n">
-        <v>3.99172902107239</v>
+        <v>3.99172949790955</v>
       </c>
       <c r="H874" t="n">
         <v>3316196</v>
@@ -25802,7 +25802,7 @@
         <v>4.97700023651123</v>
       </c>
       <c r="G877" t="n">
-        <v>3.97336745262146</v>
+        <v>3.97336769104004</v>
       </c>
       <c r="H877" t="n">
         <v>2915800</v>
@@ -25831,7 +25831,7 @@
         <v>4.93599987030029</v>
       </c>
       <c r="G878" t="n">
-        <v>3.94063520431519</v>
+        <v>3.94063544273376</v>
       </c>
       <c r="H878" t="n">
         <v>4286120</v>
@@ -25860,7 +25860,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G879" t="n">
-        <v>3.94622397422791</v>
+        <v>3.94622349739075</v>
       </c>
       <c r="H879" t="n">
         <v>1729053</v>
@@ -25889,7 +25889,7 @@
         <v>5.00799989700317</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99811625480652</v>
+        <v>3.99811601638794</v>
       </c>
       <c r="H880" t="n">
         <v>2362297</v>
@@ -25918,7 +25918,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G881" t="n">
-        <v>3.96777892112732</v>
+        <v>3.96777939796448</v>
       </c>
       <c r="H881" t="n">
         <v>1672411</v>
@@ -25947,7 +25947,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G882" t="n">
-        <v>4.00769710540771</v>
+        <v>4.00769662857056</v>
       </c>
       <c r="H882" t="n">
         <v>1377373</v>
@@ -25976,7 +25976,7 @@
         <v>5.18599987030029</v>
       </c>
       <c r="G883" t="n">
-        <v>4.14022159576416</v>
+        <v>4.14022207260132</v>
       </c>
       <c r="H883" t="n">
         <v>5129041</v>
@@ -26005,7 +26005,7 @@
         <v>5.0019998550415</v>
       </c>
       <c r="G884" t="n">
-        <v>3.99332642555237</v>
+        <v>3.99332618713379</v>
       </c>
       <c r="H884" t="n">
         <v>8991183</v>
@@ -26063,7 +26063,7 @@
         <v>5.02799987792969</v>
       </c>
       <c r="G886" t="n">
-        <v>4.01408243179321</v>
+        <v>4.01408290863037</v>
       </c>
       <c r="H886" t="n">
         <v>3542178</v>
@@ -26121,7 +26121,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G888" t="n">
-        <v>3.9901328086853</v>
+        <v>3.99013304710388</v>
       </c>
       <c r="H888" t="n">
         <v>2928960</v>
@@ -26150,7 +26150,7 @@
         <v>4.9060001373291</v>
       </c>
       <c r="G889" t="n">
-        <v>3.91668462753296</v>
+        <v>3.91668486595154</v>
       </c>
       <c r="H889" t="n">
         <v>3235553</v>
@@ -26295,7 +26295,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G894" t="n">
-        <v>3.99971270561218</v>
+        <v>3.9997136592865</v>
       </c>
       <c r="H894" t="n">
         <v>4210348</v>
@@ -26324,7 +26324,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G895" t="n">
-        <v>3.95740032196045</v>
+        <v>3.95740056037903</v>
       </c>
       <c r="H895" t="n">
         <v>1966290</v>
@@ -26353,7 +26353,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G896" t="n">
-        <v>3.84802746772766</v>
+        <v>3.84802722930908</v>
       </c>
       <c r="H896" t="n">
         <v>3064936</v>
@@ -26382,7 +26382,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G897" t="n">
-        <v>3.91269302368164</v>
+        <v>3.9126935005188</v>
       </c>
       <c r="H897" t="n">
         <v>2075739</v>
@@ -26440,7 +26440,7 @@
         <v>5.0019998550415</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99332642555237</v>
+        <v>3.99332618713379</v>
       </c>
       <c r="H899" t="n">
         <v>2294402</v>
@@ -26498,7 +26498,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G901" t="n">
-        <v>3.94542527198792</v>
+        <v>3.94542503356934</v>
       </c>
       <c r="H901" t="n">
         <v>4957834</v>
@@ -26527,7 +26527,7 @@
         <v>4.79699993133545</v>
       </c>
       <c r="G902" t="n">
-        <v>3.82966542243958</v>
+        <v>3.829665184021</v>
       </c>
       <c r="H902" t="n">
         <v>5237550</v>
@@ -26556,7 +26556,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G903" t="n">
-        <v>3.75701522827148</v>
+        <v>3.75701546669006</v>
       </c>
       <c r="H903" t="n">
         <v>5125936</v>
@@ -26614,7 +26614,7 @@
         <v>4.73299980163574</v>
       </c>
       <c r="G905" t="n">
-        <v>3.77857041358948</v>
+        <v>3.77857089042664</v>
       </c>
       <c r="H905" t="n">
         <v>2260456</v>
@@ -26672,7 +26672,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G907" t="n">
-        <v>3.68436598777771</v>
+        <v>3.68436646461487</v>
       </c>
       <c r="H907" t="n">
         <v>4336143</v>
@@ -26701,7 +26701,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G908" t="n">
-        <v>3.69155168533325</v>
+        <v>3.69155216217041</v>
       </c>
       <c r="H908" t="n">
         <v>4131045</v>
@@ -26759,7 +26759,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G910" t="n">
-        <v>3.71630072593689</v>
+        <v>3.71630048751831</v>
       </c>
       <c r="H910" t="n">
         <v>2630457</v>
@@ -26788,7 +26788,7 @@
         <v>4.58099985122681</v>
       </c>
       <c r="G911" t="n">
-        <v>3.65722227096558</v>
+        <v>3.65722250938416</v>
       </c>
       <c r="H911" t="n">
         <v>3464484</v>
@@ -26846,7 +26846,7 @@
         <v>4.71299982070923</v>
       </c>
       <c r="G913" t="n">
-        <v>3.76260423660278</v>
+        <v>3.76260447502136</v>
       </c>
       <c r="H913" t="n">
         <v>5449345</v>
@@ -26904,7 +26904,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G915" t="n">
-        <v>3.75222563743591</v>
+        <v>3.75222587585449</v>
       </c>
       <c r="H915" t="n">
         <v>1728510</v>
@@ -26933,7 +26933,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G916" t="n">
-        <v>3.79533624649048</v>
+        <v>3.79533648490906</v>
       </c>
       <c r="H916" t="n">
         <v>2356522</v>
@@ -26962,7 +26962,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G917" t="n">
-        <v>3.72029137611389</v>
+        <v>3.72029161453247</v>
       </c>
       <c r="H917" t="n">
         <v>3313504</v>
@@ -27020,7 +27020,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G919" t="n">
-        <v>3.74823451042175</v>
+        <v>3.74823427200317</v>
       </c>
       <c r="H919" t="n">
         <v>2245847</v>
@@ -27049,7 +27049,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G920" t="n">
-        <v>3.76499938964844</v>
+        <v>3.76499962806702</v>
       </c>
       <c r="H920" t="n">
         <v>964384</v>
@@ -27136,7 +27136,7 @@
         <v>4.85200023651123</v>
       </c>
       <c r="G923" t="n">
-        <v>3.87357449531555</v>
+        <v>3.87357497215271</v>
       </c>
       <c r="H923" t="n">
         <v>5070613</v>
@@ -27165,7 +27165,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G924" t="n">
-        <v>3.86399459838867</v>
+        <v>3.86399435997009</v>
       </c>
       <c r="H924" t="n">
         <v>1783174</v>
@@ -27223,7 +27223,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G926" t="n">
-        <v>3.9318540096283</v>
+        <v>3.93185377120972</v>
       </c>
       <c r="H926" t="n">
         <v>2913802</v>
@@ -27252,7 +27252,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G927" t="n">
-        <v>3.97097277641296</v>
+        <v>3.97097229957581</v>
       </c>
       <c r="H927" t="n">
         <v>2943156</v>
@@ -27368,7 +27368,7 @@
         <v>5.17799997329712</v>
       </c>
       <c r="G931" t="n">
-        <v>4.13383531570435</v>
+        <v>4.13383483886719</v>
       </c>
       <c r="H931" t="n">
         <v>3057803</v>
@@ -27397,7 +27397,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G932" t="n">
-        <v>4.10349798202515</v>
+        <v>4.10349750518799</v>
       </c>
       <c r="H932" t="n">
         <v>2229039</v>
@@ -27426,7 +27426,7 @@
         <v>5.16200017929077</v>
       </c>
       <c r="G933" t="n">
-        <v>4.12106132507324</v>
+        <v>4.1210618019104</v>
       </c>
       <c r="H933" t="n">
         <v>2361572</v>
@@ -27455,7 +27455,7 @@
         <v>5.16200017929077</v>
       </c>
       <c r="G934" t="n">
-        <v>4.12106132507324</v>
+        <v>4.1210618019104</v>
       </c>
       <c r="H934" t="n">
         <v>1419462</v>
@@ -27513,7 +27513,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G936" t="n">
-        <v>4.10349798202515</v>
+        <v>4.10349750518799</v>
       </c>
       <c r="H936" t="n">
         <v>1288540</v>
@@ -27542,7 +27542,7 @@
         <v>5.16599988937378</v>
       </c>
       <c r="G937" t="n">
-        <v>4.12425518035889</v>
+        <v>4.12425470352173</v>
       </c>
       <c r="H937" t="n">
         <v>1132810</v>
@@ -27687,7 +27687,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G942" t="n">
-        <v>4.07558107376099</v>
+        <v>4.0755820274353</v>
       </c>
       <c r="H942" t="n">
         <v>1599756</v>
@@ -27716,7 +27716,7 @@
         <v>5.03399991989136</v>
       </c>
       <c r="G943" t="n">
-        <v>4.08369398117065</v>
+        <v>4.0836935043335</v>
       </c>
       <c r="H943" t="n">
         <v>8053981</v>
@@ -27774,7 +27774,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G945" t="n">
-        <v>4.01717376708984</v>
+        <v>4.01717329025269</v>
       </c>
       <c r="H945" t="n">
         <v>2334336</v>
@@ -27832,7 +27832,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G947" t="n">
-        <v>3.97174477577209</v>
+        <v>3.97174525260925</v>
       </c>
       <c r="H947" t="n">
         <v>2427802</v>
@@ -27977,7 +27977,7 @@
         <v>4.99200010299683</v>
       </c>
       <c r="G952" t="n">
-        <v>4.04962205886841</v>
+        <v>4.04962301254272</v>
       </c>
       <c r="H952" t="n">
         <v>1481995</v>
@@ -28006,7 +28006,7 @@
         <v>4.86899995803833</v>
       </c>
       <c r="G953" t="n">
-        <v>3.94984245300293</v>
+        <v>3.94984197616577</v>
       </c>
       <c r="H953" t="n">
         <v>3232585</v>
@@ -28064,7 +28064,7 @@
         <v>4.93100023269653</v>
       </c>
       <c r="G955" t="n">
-        <v>4.00013780593872</v>
+        <v>4.00013828277588</v>
       </c>
       <c r="H955" t="n">
         <v>1526660</v>
@@ -28122,7 +28122,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G957" t="n">
-        <v>3.99608135223389</v>
+        <v>3.99608182907104</v>
       </c>
       <c r="H957" t="n">
         <v>925785</v>
@@ -28151,7 +28151,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G958" t="n">
-        <v>3.94254183769226</v>
+        <v>3.9425413608551</v>
       </c>
       <c r="H958" t="n">
         <v>1551769</v>
@@ -28180,7 +28180,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G959" t="n">
-        <v>3.96850061416626</v>
+        <v>3.96850037574768</v>
       </c>
       <c r="H959" t="n">
         <v>2942863</v>
@@ -28238,7 +28238,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G961" t="n">
-        <v>3.91495966911316</v>
+        <v>3.91495943069458</v>
       </c>
       <c r="H961" t="n">
         <v>4637553</v>
@@ -28267,7 +28267,7 @@
         <v>4.99900007247925</v>
       </c>
       <c r="G962" t="n">
-        <v>4.05530118942261</v>
+        <v>4.05530166625977</v>
       </c>
       <c r="H962" t="n">
         <v>5465593</v>
@@ -28441,7 +28441,7 @@
         <v>5.12400007247925</v>
       </c>
       <c r="G968" t="n">
-        <v>4.15670394897461</v>
+        <v>4.15670442581177</v>
       </c>
       <c r="H968" t="n">
         <v>2419460</v>
@@ -28673,7 +28673,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G976" t="n">
-        <v>4.38222360610962</v>
+        <v>4.38222312927246</v>
       </c>
       <c r="H976" t="n">
         <v>3195338</v>
@@ -28702,7 +28702,7 @@
         <v>5.43200016021729</v>
       </c>
       <c r="G977" t="n">
-        <v>4.40656042098999</v>
+        <v>4.40655994415283</v>
       </c>
       <c r="H977" t="n">
         <v>1428261</v>
@@ -28789,7 +28789,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G980" t="n">
-        <v>4.40007019042969</v>
+        <v>4.40007066726685</v>
       </c>
       <c r="H980" t="n">
         <v>869534</v>
@@ -28818,7 +28818,7 @@
         <v>5.31400012969971</v>
       </c>
       <c r="G981" t="n">
-        <v>4.31083631515503</v>
+        <v>4.31083679199219</v>
       </c>
       <c r="H981" t="n">
         <v>2071429</v>
@@ -28847,7 +28847,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G982" t="n">
-        <v>4.35788774490356</v>
+        <v>4.35788726806641</v>
       </c>
       <c r="H982" t="n">
         <v>1372294</v>
@@ -28876,7 +28876,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G983" t="n">
-        <v>4.24756050109863</v>
+        <v>4.24756097793579</v>
       </c>
       <c r="H983" t="n">
         <v>2469703</v>
@@ -28963,7 +28963,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G986" t="n">
-        <v>4.21024465560913</v>
+        <v>4.21024417877197</v>
       </c>
       <c r="H986" t="n">
         <v>1166057</v>
@@ -29050,7 +29050,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G989" t="n">
-        <v>4.2134895324707</v>
+        <v>4.21348905563354</v>
       </c>
       <c r="H989" t="n">
         <v>1226933</v>
@@ -29108,7 +29108,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G991" t="n">
-        <v>4.11614322662354</v>
+        <v>4.11614274978638</v>
       </c>
       <c r="H991" t="n">
         <v>2172480</v>
@@ -29195,7 +29195,7 @@
         <v>5.12400007247925</v>
       </c>
       <c r="G994" t="n">
-        <v>4.15670394897461</v>
+        <v>4.15670442581177</v>
       </c>
       <c r="H994" t="n">
         <v>965332</v>
@@ -29282,7 +29282,7 @@
         <v>5.13600015640259</v>
       </c>
       <c r="G997" t="n">
-        <v>4.16643905639648</v>
+        <v>4.16643857955933</v>
       </c>
       <c r="H997" t="n">
         <v>3304160</v>
@@ -29369,7 +29369,7 @@
         <v>5.2519998550415</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.26054048538208</v>
+        <v>4.26054000854492</v>
       </c>
       <c r="H1000" t="n">
         <v>4074072</v>
@@ -29427,7 +29427,7 @@
         <v>5.14599990844727</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.17455148696899</v>
+        <v>4.17455053329468</v>
       </c>
       <c r="H1002" t="n">
         <v>1333298</v>
@@ -29456,7 +29456,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.20213174819946</v>
+        <v>4.20213222503662</v>
       </c>
       <c r="H1003" t="n">
         <v>2224645</v>
@@ -29572,7 +29572,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.19564294815063</v>
+        <v>4.19564247131348</v>
       </c>
       <c r="H1007" t="n">
         <v>1233191</v>
@@ -29659,7 +29659,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.23782634735107</v>
+        <v>4.23782587051392</v>
       </c>
       <c r="H1010" t="n">
         <v>849578</v>
@@ -29688,7 +29688,7 @@
         <v>5.12799978256226</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.15994834899902</v>
+        <v>4.15994882583618</v>
       </c>
       <c r="H1011" t="n">
         <v>2491333</v>
@@ -29717,7 +29717,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.13074493408203</v>
+        <v>4.13074445724487</v>
       </c>
       <c r="H1012" t="n">
         <v>1475971</v>
@@ -29804,7 +29804,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.05205631256104</v>
+        <v>4.05205583572388</v>
       </c>
       <c r="H1015" t="n">
         <v>1874139</v>
@@ -29862,7 +29862,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.97661256790161</v>
+        <v>3.97661185264587</v>
       </c>
       <c r="H1017" t="n">
         <v>2260225</v>
@@ -29978,7 +29978,7 @@
         <v>5.03599977493286</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.08531618118286</v>
+        <v>4.0853157043457</v>
       </c>
       <c r="H1021" t="n">
         <v>2181807</v>
@@ -30007,7 +30007,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.07233715057373</v>
+        <v>4.07233619689941</v>
       </c>
       <c r="H1022" t="n">
         <v>1012542</v>
@@ -30036,7 +30036,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.10478591918945</v>
+        <v>4.10478544235229</v>
       </c>
       <c r="H1023" t="n">
         <v>839666</v>
@@ -30065,7 +30065,7 @@
         <v>5.08400011062622</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.12425518035889</v>
+        <v>4.12425470352173</v>
       </c>
       <c r="H1024" t="n">
         <v>1170127</v>
@@ -30123,7 +30123,7 @@
         <v>5.00600004196167</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.06097984313965</v>
+        <v>4.06097936630249</v>
       </c>
       <c r="H1026" t="n">
         <v>952568</v>
@@ -30152,7 +30152,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.11614322662354</v>
+        <v>4.11614274978638</v>
       </c>
       <c r="H1027" t="n">
         <v>1747743</v>
@@ -30181,7 +30181,7 @@
         <v>5.06799983978271</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.11127519607544</v>
+        <v>4.11127471923828</v>
       </c>
       <c r="H1028" t="n">
         <v>1982566</v>
@@ -30210,7 +30210,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.10478591918945</v>
+        <v>4.10478544235229</v>
       </c>
       <c r="H1029" t="n">
         <v>1426503</v>
@@ -30239,7 +30239,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.2134895324707</v>
+        <v>4.21348905563354</v>
       </c>
       <c r="H1030" t="n">
         <v>2386015</v>
@@ -30297,7 +30297,7 @@
         <v>5.31199979782104</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.30921268463135</v>
+        <v>4.30921363830566</v>
       </c>
       <c r="H1032" t="n">
         <v>2330998</v>
@@ -30355,7 +30355,7 @@
         <v>5.31199979782104</v>
       </c>
       <c r="G1034" t="n">
-        <v>4.30921268463135</v>
+        <v>4.30921363830566</v>
       </c>
       <c r="H1034" t="n">
         <v>1389460</v>
@@ -30471,7 +30471,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.42765235900879</v>
+        <v>4.42765188217163</v>
       </c>
       <c r="H1038" t="n">
         <v>2747939</v>
@@ -30500,7 +30500,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.54284572601318</v>
+        <v>4.54284524917603</v>
       </c>
       <c r="H1039" t="n">
         <v>3675186</v>
@@ -30529,7 +30529,7 @@
         <v>5.53800010681152</v>
       </c>
       <c r="G1040" t="n">
-        <v>4.49254989624023</v>
+        <v>4.49255037307739</v>
       </c>
       <c r="H1040" t="n">
         <v>1209926</v>
@@ -30558,7 +30558,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.4665904045105</v>
+        <v>4.46659088134766</v>
       </c>
       <c r="H1041" t="n">
         <v>985475</v>
@@ -30587,7 +30587,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.49579524993896</v>
+        <v>4.49579429626465</v>
       </c>
       <c r="H1042" t="n">
         <v>1640358</v>
@@ -30616,7 +30616,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.51364183425903</v>
+        <v>4.51364231109619</v>
       </c>
       <c r="H1043" t="n">
         <v>5057446</v>
@@ -30761,7 +30761,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.69697761535645</v>
+        <v>4.6969780921936</v>
       </c>
       <c r="H1048" t="n">
         <v>2389181</v>
@@ -30790,7 +30790,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.68399906158447</v>
+        <v>4.68399858474731</v>
       </c>
       <c r="H1049" t="n">
         <v>2601645</v>
@@ -30935,7 +30935,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G1054" t="n">
-        <v>4.43089723587036</v>
+        <v>4.4308967590332</v>
       </c>
       <c r="H1054" t="n">
         <v>4035150</v>
@@ -30964,7 +30964,7 @@
         <v>5.40399980545044</v>
       </c>
       <c r="G1055" t="n">
-        <v>4.38384628295898</v>
+        <v>4.38384580612183</v>
       </c>
       <c r="H1055" t="n">
         <v>1977684</v>
@@ -30993,7 +30993,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G1056" t="n">
-        <v>4.40331506729126</v>
+        <v>4.40331554412842</v>
       </c>
       <c r="H1056" t="n">
         <v>2173376</v>
@@ -31080,7 +31080,7 @@
         <v>5.5460000038147</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.49903964996338</v>
+        <v>4.49903917312622</v>
       </c>
       <c r="H1059" t="n">
         <v>2062162</v>
@@ -31109,7 +31109,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G1060" t="n">
-        <v>4.66128444671631</v>
+        <v>4.66128396987915</v>
       </c>
       <c r="H1060" t="n">
         <v>1523485</v>
@@ -31167,7 +31167,7 @@
         <v>5.9520001411438</v>
       </c>
       <c r="G1062" t="n">
-        <v>4.82839584350586</v>
+        <v>4.82839632034302</v>
       </c>
       <c r="H1062" t="n">
         <v>1625771</v>
@@ -31196,7 +31196,7 @@
         <v>5.96400022506714</v>
       </c>
       <c r="G1063" t="n">
-        <v>4.83813047409058</v>
+        <v>4.83813095092773</v>
       </c>
       <c r="H1063" t="n">
         <v>1383343</v>
@@ -31225,7 +31225,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.84299850463867</v>
+        <v>4.84299802780151</v>
       </c>
       <c r="H1064" t="n">
         <v>2344019</v>
@@ -31312,7 +31312,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.84299850463867</v>
+        <v>4.84299802780151</v>
       </c>
       <c r="H1067" t="n">
         <v>1471367</v>
@@ -31370,7 +31370,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.85111045837402</v>
+        <v>4.85111093521118</v>
       </c>
       <c r="H1069" t="n">
         <v>3844834</v>
@@ -31428,7 +31428,7 @@
         <v>5.95599985122681</v>
       </c>
       <c r="G1071" t="n">
-        <v>4.83164119720459</v>
+        <v>4.83164072036743</v>
       </c>
       <c r="H1071" t="n">
         <v>1049521</v>
@@ -31457,7 +31457,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G1072" t="n">
-        <v>4.87869215011597</v>
+        <v>4.87869167327881</v>
       </c>
       <c r="H1072" t="n">
         <v>1042404</v>
@@ -31515,7 +31515,7 @@
         <v>6.10400009155273</v>
       </c>
       <c r="G1074" t="n">
-        <v>4.95170211791992</v>
+        <v>4.95170164108276</v>
       </c>
       <c r="H1074" t="n">
         <v>1199147</v>
@@ -31573,7 +31573,7 @@
         <v>6.11600017547607</v>
       </c>
       <c r="G1076" t="n">
-        <v>4.96143674850464</v>
+        <v>4.9614372253418</v>
       </c>
       <c r="H1076" t="n">
         <v>879158</v>
@@ -31602,7 +31602,7 @@
         <v>6.10799980163574</v>
       </c>
       <c r="G1077" t="n">
-        <v>4.95494651794434</v>
+        <v>4.95494699478149</v>
       </c>
       <c r="H1077" t="n">
         <v>871315</v>
@@ -31631,7 +31631,7 @@
         <v>6.15199995040894</v>
       </c>
       <c r="G1078" t="n">
-        <v>4.99064064025879</v>
+        <v>4.99063968658447</v>
       </c>
       <c r="H1078" t="n">
         <v>1736834</v>
@@ -31660,7 +31660,7 @@
         <v>6.17600011825562</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.01010942459106</v>
+        <v>5.01010990142822</v>
       </c>
       <c r="H1079" t="n">
         <v>3017051</v>
@@ -31834,7 +31834,7 @@
         <v>6.59200000762939</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.34757852554321</v>
+        <v>5.34757900238037</v>
       </c>
       <c r="H1085" t="n">
         <v>2461626</v>
@@ -31863,7 +31863,7 @@
         <v>6.69600009918213</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.43194627761841</v>
+        <v>5.43194580078125</v>
       </c>
       <c r="H1086" t="n">
         <v>2633796</v>
@@ -32037,7 +32037,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.22427272796631</v>
+        <v>5.22427225112915</v>
       </c>
       <c r="H1092" t="n">
         <v>1674571</v>
@@ -32124,7 +32124,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.00037527084351</v>
+        <v>5.00037574768066</v>
       </c>
       <c r="H1095" t="n">
         <v>1842897</v>
@@ -32211,7 +32211,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.05553865432739</v>
+        <v>5.05553817749023</v>
       </c>
       <c r="H1098" t="n">
         <v>1921905</v>
@@ -32240,7 +32240,7 @@
         <v>6.32200002670288</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.12854814529419</v>
+        <v>5.12854862213135</v>
       </c>
       <c r="H1099" t="n">
         <v>1681490</v>
@@ -32327,7 +32327,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1102" t="n">
-        <v>4.89978361129761</v>
+        <v>4.89978313446045</v>
       </c>
       <c r="H1102" t="n">
         <v>2730930</v>
@@ -32356,7 +32356,7 @@
         <v>6.04400014877319</v>
       </c>
       <c r="G1103" t="n">
-        <v>4.90302848815918</v>
+        <v>4.90302896499634</v>
       </c>
       <c r="H1103" t="n">
         <v>1498815</v>
@@ -32472,7 +32472,7 @@
         <v>6.01200008392334</v>
       </c>
       <c r="G1107" t="n">
-        <v>4.8770694732666</v>
+        <v>4.87706995010376</v>
       </c>
       <c r="H1107" t="n">
         <v>2841431</v>
@@ -32559,7 +32559,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G1110" t="n">
-        <v>4.76025342941284</v>
+        <v>4.76025390625</v>
       </c>
       <c r="H1110" t="n">
         <v>1735712</v>
@@ -32646,7 +32646,7 @@
         <v>5.61199998855591</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.5525803565979</v>
+        <v>4.55258083343506</v>
       </c>
       <c r="H1113" t="n">
         <v>1673732</v>
@@ -32675,7 +32675,7 @@
         <v>5.66200017929077</v>
       </c>
       <c r="G1114" t="n">
-        <v>4.59314155578613</v>
+        <v>4.59314203262329</v>
       </c>
       <c r="H1114" t="n">
         <v>2046864</v>
@@ -32762,7 +32762,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.21024465560913</v>
+        <v>4.21024417877197</v>
       </c>
       <c r="H1117" t="n">
         <v>7442160</v>
@@ -32791,7 +32791,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G1118" t="n">
-        <v>4.0098729133606</v>
+        <v>4.00987243652344</v>
       </c>
       <c r="H1118" t="n">
         <v>5179774</v>
@@ -32849,7 +32849,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.82248020172119</v>
+        <v>3.82247996330261</v>
       </c>
       <c r="H1120" t="n">
         <v>5287521</v>
@@ -32878,7 +32878,7 @@
         <v>4.65700006484985</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.77786350250244</v>
+        <v>3.77786302566528</v>
       </c>
       <c r="H1121" t="n">
         <v>4897326</v>
@@ -32936,7 +32936,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.50772571563721</v>
+        <v>3.50772547721863</v>
       </c>
       <c r="H1123" t="n">
         <v>5368623</v>
@@ -32965,7 +32965,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.43796062469482</v>
+        <v>3.4379608631134</v>
       </c>
       <c r="H1124" t="n">
         <v>4500750</v>
@@ -33023,7 +33023,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.68700623512268</v>
+        <v>3.68700575828552</v>
       </c>
       <c r="H1126" t="n">
         <v>3168181</v>
@@ -33052,7 +33052,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.67402625083923</v>
+        <v>3.67402601242065</v>
       </c>
       <c r="H1127" t="n">
         <v>3583767</v>
@@ -33081,7 +33081,7 @@
         <v>4.66099977493286</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.78110790252686</v>
+        <v>3.78110766410828</v>
       </c>
       <c r="H1128" t="n">
         <v>3248155</v>
@@ -33139,7 +33139,7 @@
         <v>4.90199995040894</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.97661256790161</v>
+        <v>3.97661185264587</v>
       </c>
       <c r="H1130" t="n">
         <v>4326966</v>
@@ -33168,7 +33168,7 @@
         <v>4.84700012207031</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.9319953918457</v>
+        <v>3.93199563026428</v>
       </c>
       <c r="H1131" t="n">
         <v>4300476</v>
@@ -33197,7 +33197,7 @@
         <v>4.84899997711182</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.93361783027649</v>
+        <v>3.93361759185791</v>
       </c>
       <c r="H1132" t="n">
         <v>4774525</v>
@@ -33226,7 +33226,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.86953067779541</v>
+        <v>3.86953091621399</v>
       </c>
       <c r="H1133" t="n">
         <v>1636489</v>
@@ -33255,7 +33255,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.93767356872559</v>
+        <v>3.93767380714417</v>
       </c>
       <c r="H1134" t="n">
         <v>1588173</v>
@@ -33284,7 +33284,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.93118381500244</v>
+        <v>3.9311842918396</v>
       </c>
       <c r="H1135" t="n">
         <v>1943279</v>
@@ -33313,7 +33313,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.86628651618958</v>
+        <v>3.86628603935242</v>
       </c>
       <c r="H1136" t="n">
         <v>1878893</v>
@@ -33342,7 +33342,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.89386749267578</v>
+        <v>3.89386796951294</v>
       </c>
       <c r="H1137" t="n">
         <v>1417907</v>
@@ -33371,7 +33371,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.87358713150024</v>
+        <v>3.87358808517456</v>
       </c>
       <c r="H1138" t="n">
         <v>1654738</v>
@@ -33458,7 +33458,7 @@
         <v>4.93100023269653</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.00013780593872</v>
+        <v>4.00013828277588</v>
       </c>
       <c r="H1141" t="n">
         <v>2150012</v>
@@ -33516,7 +33516,7 @@
         <v>4.8769998550415</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.95633172988892</v>
+        <v>3.9563319683075</v>
       </c>
       <c r="H1143" t="n">
         <v>1366405</v>
@@ -33545,7 +33545,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.8954906463623</v>
+        <v>3.89549040794373</v>
       </c>
       <c r="H1144" t="n">
         <v>2905567</v>
@@ -33574,7 +33574,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.68457245826721</v>
+        <v>3.68457221984863</v>
       </c>
       <c r="H1145" t="n">
         <v>4603345</v>
@@ -33603,7 +33603,7 @@
         <v>4.41300010681152</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.57992506027222</v>
+        <v>3.57992482185364</v>
       </c>
       <c r="H1146" t="n">
         <v>3363384</v>
@@ -33661,7 +33661,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.59209299087524</v>
+        <v>3.59209322929382</v>
       </c>
       <c r="H1148" t="n">
         <v>2403733</v>
@@ -33690,7 +33690,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.60669469833374</v>
+        <v>3.6066951751709</v>
       </c>
       <c r="H1149" t="n">
         <v>2415234</v>
@@ -33719,7 +33719,7 @@
         <v>4.52099990844727</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.66753649711609</v>
+        <v>3.66753625869751</v>
       </c>
       <c r="H1150" t="n">
         <v>1575910</v>
@@ -33806,7 +33806,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.85817360877991</v>
+        <v>3.85817384719849</v>
       </c>
       <c r="H1153" t="n">
         <v>3842670</v>
@@ -33835,7 +33835,7 @@
         <v>4.88100004196167</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.95957684516907</v>
+        <v>3.95957660675049</v>
       </c>
       <c r="H1154" t="n">
         <v>4687157</v>
@@ -33864,7 +33864,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.84924983978271</v>
+        <v>3.84925031661987</v>
       </c>
       <c r="H1155" t="n">
         <v>1572535</v>
@@ -33951,7 +33951,7 @@
         <v>4.66599988937378</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.78516387939453</v>
+        <v>3.78516364097595</v>
       </c>
       <c r="H1158" t="n">
         <v>1365833</v>
@@ -33980,7 +33980,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.85006189346313</v>
+        <v>3.85006141662598</v>
       </c>
       <c r="H1159" t="n">
         <v>1808335</v>
@@ -34038,7 +34038,7 @@
         <v>4.61700010299683</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.74541425704956</v>
+        <v>3.74541449546814</v>
       </c>
       <c r="H1161" t="n">
         <v>2119596</v>
@@ -34067,7 +34067,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.71377635002136</v>
+        <v>3.71377682685852</v>
       </c>
       <c r="H1162" t="n">
         <v>2263738</v>
@@ -34096,7 +34096,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.71215438842773</v>
+        <v>3.71215462684631</v>
       </c>
       <c r="H1163" t="n">
         <v>1303565</v>
@@ -34125,7 +34125,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.60831761360168</v>
+        <v>3.60831737518311</v>
       </c>
       <c r="H1164" t="n">
         <v>1746404</v>
@@ -34154,7 +34154,7 @@
         <v>4.45100021362305</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.61075115203857</v>
+        <v>3.61075162887573</v>
       </c>
       <c r="H1165" t="n">
         <v>1855446</v>
@@ -34183,7 +34183,7 @@
         <v>4.30100011825562</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.48906779289246</v>
+        <v>3.48906803131104</v>
       </c>
       <c r="H1166" t="n">
         <v>2111708</v>
@@ -34212,7 +34212,7 @@
         <v>4.4689998626709</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.62535333633423</v>
+        <v>3.62535285949707</v>
       </c>
       <c r="H1167" t="n">
         <v>2099491</v>
@@ -34270,7 +34270,7 @@
         <v>4.63899993896484</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.76326131820679</v>
+        <v>3.76326107978821</v>
       </c>
       <c r="H1169" t="n">
         <v>1807513</v>
@@ -34328,7 +34328,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.81761264801025</v>
+        <v>3.81761288642883</v>
       </c>
       <c r="H1171" t="n">
         <v>885772</v>
@@ -34415,7 +34415,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.68781757354736</v>
+        <v>3.68781781196594</v>
       </c>
       <c r="H1174" t="n">
         <v>1820197</v>
@@ -34444,7 +34444,7 @@
         <v>4.51399993896484</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.66185784339905</v>
+        <v>3.66185832023621</v>
       </c>
       <c r="H1175" t="n">
         <v>2396662</v>
@@ -34531,7 +34531,7 @@
         <v>4.42899990081787</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.72579121589661</v>
+        <v>3.72579145431519</v>
       </c>
       <c r="H1178" t="n">
         <v>1352870</v>
@@ -34560,7 +34560,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.85449838638306</v>
+        <v>3.85449862480164</v>
       </c>
       <c r="H1179" t="n">
         <v>1272388</v>
@@ -34589,7 +34589,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.86543464660645</v>
+        <v>3.86543440818787</v>
       </c>
       <c r="H1180" t="n">
         <v>803294</v>
@@ -34618,7 +34618,7 @@
         <v>4.66699981689453</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.92600297927856</v>
+        <v>3.92600321769714</v>
       </c>
       <c r="H1181" t="n">
         <v>1236000</v>
@@ -34676,7 +34676,7 @@
         <v>4.65100002288818</v>
       </c>
       <c r="G1183" t="n">
-        <v>3.9125440120697</v>
+        <v>3.91254377365112</v>
       </c>
       <c r="H1183" t="n">
         <v>1244046</v>
@@ -34705,7 +34705,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.92768549919128</v>
+        <v>3.92768597602844</v>
       </c>
       <c r="H1184" t="n">
         <v>429704</v>
@@ -34734,7 +34734,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.84861040115356</v>
+        <v>3.84860992431641</v>
       </c>
       <c r="H1185" t="n">
         <v>982607</v>
@@ -34763,7 +34763,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.92852711677551</v>
+        <v>3.92852735519409</v>
       </c>
       <c r="H1186" t="n">
         <v>661346</v>
@@ -34792,7 +34792,7 @@
         <v>4.58900022506714</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.86038780212402</v>
+        <v>3.8603880405426</v>
       </c>
       <c r="H1187" t="n">
         <v>1054236</v>
@@ -34850,7 +34850,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.74177503585815</v>
+        <v>3.741774559021</v>
       </c>
       <c r="H1189" t="n">
         <v>1501746</v>
@@ -34937,7 +34937,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G1192" t="n">
-        <v>3.37752342224121</v>
+        <v>3.37752366065979</v>
       </c>
       <c r="H1192" t="n">
         <v>2426396</v>
@@ -34995,7 +34995,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.3901424407959</v>
+        <v>3.39014220237732</v>
       </c>
       <c r="H1194" t="n">
         <v>1378418</v>
@@ -35053,7 +35053,7 @@
         <v>4.25899982452393</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.58278250694275</v>
+        <v>3.58278274536133</v>
       </c>
       <c r="H1196" t="n">
         <v>896569</v>
@@ -35111,7 +35111,7 @@
         <v>4.2020001411438</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.53483295440674</v>
+        <v>3.53483271598816</v>
       </c>
       <c r="H1198" t="n">
         <v>853012</v>
@@ -35140,7 +35140,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.33630347251892</v>
+        <v>3.3363037109375</v>
       </c>
       <c r="H1199" t="n">
         <v>2920061</v>
@@ -35198,7 +35198,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.4019193649292</v>
+        <v>3.40191960334778</v>
       </c>
       <c r="H1201" t="n">
         <v>1282641</v>
@@ -35285,7 +35285,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.26059317588806</v>
+        <v>3.26059341430664</v>
       </c>
       <c r="H1204" t="n">
         <v>2512501</v>
@@ -35314,7 +35314,7 @@
         <v>3.93700003623962</v>
       </c>
       <c r="G1205" t="n">
-        <v>3.31190824508667</v>
+        <v>3.31190800666809</v>
       </c>
       <c r="H1205" t="n">
         <v>3530258</v>
@@ -35343,7 +35343,7 @@
         <v>3.90300011634827</v>
       </c>
       <c r="G1206" t="n">
-        <v>3.28330636024475</v>
+        <v>3.28330659866333</v>
       </c>
       <c r="H1206" t="n">
         <v>1259841</v>
@@ -35372,7 +35372,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.17478799819946</v>
+        <v>3.17478823661804</v>
       </c>
       <c r="H1207" t="n">
         <v>2164862</v>
@@ -35430,7 +35430,7 @@
         <v>4.07100009918213</v>
       </c>
       <c r="G1209" t="n">
-        <v>3.42463231086731</v>
+        <v>3.42463254928589</v>
       </c>
       <c r="H1209" t="n">
         <v>2231696</v>
@@ -35488,7 +35488,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.41958475112915</v>
+        <v>3.41958498954773</v>
       </c>
       <c r="H1211" t="n">
         <v>1022124</v>
@@ -35517,7 +35517,7 @@
         <v>4.08699989318848</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.43809199333191</v>
+        <v>3.43809175491333</v>
       </c>
       <c r="H1212" t="n">
         <v>1732968</v>
@@ -35546,7 +35546,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.33125615119934</v>
+        <v>3.33125638961792</v>
       </c>
       <c r="H1213" t="n">
         <v>1482347</v>
@@ -35633,7 +35633,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.49950122833252</v>
+        <v>3.4995014667511</v>
       </c>
       <c r="H1216" t="n">
         <v>1700718</v>
@@ -35778,7 +35778,7 @@
         <v>4.12900018692017</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.47342395782471</v>
+        <v>3.47342371940613</v>
       </c>
       <c r="H1221" t="n">
         <v>1023382</v>
@@ -35923,7 +35923,7 @@
         <v>4.17700004577637</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.51380252838135</v>
+        <v>3.51380228996277</v>
       </c>
       <c r="H1226" t="n">
         <v>1062850</v>
@@ -36010,7 +36010,7 @@
         <v>4.25600004196167</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.5802595615387</v>
+        <v>3.58025932312012</v>
       </c>
       <c r="H1229" t="n">
         <v>1188294</v>
@@ -36039,7 +36039,7 @@
         <v>4.43900012969971</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.73420357704163</v>
+        <v>3.73420381546021</v>
       </c>
       <c r="H1230" t="n">
         <v>4970115</v>
@@ -36068,7 +36068,7 @@
         <v>4.40700006484985</v>
       </c>
       <c r="G1231" t="n">
-        <v>3.70728445053101</v>
+        <v>3.70728397369385</v>
       </c>
       <c r="H1231" t="n">
         <v>2232915</v>
@@ -36097,7 +36097,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.58194184303284</v>
+        <v>3.58194160461426</v>
       </c>
       <c r="H1232" t="n">
         <v>2170413</v>
@@ -36126,7 +36126,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.66774702072144</v>
+        <v>3.66774678230286</v>
       </c>
       <c r="H1233" t="n">
         <v>2584764</v>
@@ -36213,7 +36213,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.59624266624451</v>
+        <v>3.59624290466309</v>
       </c>
       <c r="H1236" t="n">
         <v>1613160</v>
@@ -36300,7 +36300,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.3901424407959</v>
+        <v>3.39014220237732</v>
       </c>
       <c r="H1239" t="n">
         <v>1972997</v>
@@ -36387,7 +36387,7 @@
         <v>3.87899994850159</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.26311683654785</v>
+        <v>3.26311707496643</v>
       </c>
       <c r="H1242" t="n">
         <v>2951087</v>
@@ -36416,7 +36416,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.26059317588806</v>
+        <v>3.26059341430664</v>
       </c>
       <c r="H1243" t="n">
         <v>1691093</v>
@@ -36503,7 +36503,7 @@
         <v>3.70900011062622</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.12010836601257</v>
+        <v>3.12010860443115</v>
       </c>
       <c r="H1246" t="n">
         <v>3276147</v>
@@ -36619,7 +36619,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.07468199729919</v>
+        <v>3.07468223571777</v>
       </c>
       <c r="H1250" t="n">
         <v>2295669</v>
@@ -36648,7 +36648,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.16721725463867</v>
+        <v>3.16721701622009</v>
       </c>
       <c r="H1251" t="n">
         <v>2569808</v>
@@ -36880,7 +36880,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.13609170913696</v>
+        <v>3.13609147071838</v>
       </c>
       <c r="H1259" t="n">
         <v>2664565</v>
@@ -36909,7 +36909,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.16637563705444</v>
+        <v>3.16637587547302</v>
       </c>
       <c r="H1260" t="n">
         <v>1018012</v>
@@ -36967,7 +36967,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.15964603424072</v>
+        <v>3.1596462726593</v>
       </c>
       <c r="H1262" t="n">
         <v>1131519</v>
@@ -36996,7 +36996,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G1263" t="n">
-        <v>3.0469217300415</v>
+        <v>3.04692196846008</v>
       </c>
       <c r="H1263" t="n">
         <v>2294253</v>
@@ -37112,7 +37112,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.87867665290833</v>
+        <v>2.87867641448975</v>
       </c>
       <c r="H1267" t="n">
         <v>1918944</v>
@@ -37286,7 +37286,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.86858201026917</v>
+        <v>2.86858177185059</v>
       </c>
       <c r="H1273" t="n">
         <v>2840074</v>
@@ -37315,7 +37315,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.84839248657227</v>
+        <v>2.84839224815369</v>
       </c>
       <c r="H1274" t="n">
         <v>2266722</v>
@@ -37373,7 +37373,7 @@
         <v>3.40400004386902</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.86353468894958</v>
+        <v>2.86353445053101</v>
       </c>
       <c r="H1276" t="n">
         <v>2153043</v>
@@ -37402,7 +37402,7 @@
         <v>3.41899991035461</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.87615275382996</v>
+        <v>2.87615251541138</v>
       </c>
       <c r="H1277" t="n">
         <v>3459188</v>
@@ -37431,7 +37431,7 @@
         <v>3.5</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.94429206848145</v>
+        <v>2.94429183006287</v>
       </c>
       <c r="H1278" t="n">
         <v>3129866</v>
@@ -37547,7 +37547,7 @@
         <v>3.56900000572205</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.00233697891235</v>
+        <v>3.00233674049377</v>
       </c>
       <c r="H1282" t="n">
         <v>1713888</v>
@@ -37634,7 +37634,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.11085510253906</v>
+        <v>3.11085486412048</v>
       </c>
       <c r="H1285" t="n">
         <v>3358682</v>
@@ -37692,7 +37692,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.17478799819946</v>
+        <v>3.17478823661804</v>
       </c>
       <c r="H1287" t="n">
         <v>1764647</v>
@@ -37750,7 +37750,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.20675468444824</v>
+        <v>3.20675492286682</v>
       </c>
       <c r="H1289" t="n">
         <v>1243466</v>
@@ -37779,7 +37779,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.2118022441864</v>
+        <v>3.21180200576782</v>
       </c>
       <c r="H1290" t="n">
         <v>1372350</v>
@@ -37808,7 +37808,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.13272666931152</v>
+        <v>3.1327269077301</v>
       </c>
       <c r="H1291" t="n">
         <v>3798686</v>
@@ -37837,7 +37837,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1292" t="n">
-        <v>3.16301083564758</v>
+        <v>3.16301107406616</v>
       </c>
       <c r="H1292" t="n">
         <v>2531218</v>
@@ -38040,7 +38040,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.47931218147278</v>
+        <v>3.4793119430542</v>
       </c>
       <c r="H1299" t="n">
         <v>2310985</v>
@@ -38069,7 +38069,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.52053189277649</v>
+        <v>3.52053213119507</v>
       </c>
       <c r="H1300" t="n">
         <v>1535495</v>
@@ -38098,7 +38098,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.5112783908844</v>
+        <v>3.51127862930298</v>
       </c>
       <c r="H1301" t="n">
         <v>1930210</v>
@@ -38127,7 +38127,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.4658522605896</v>
+        <v>3.46585249900818</v>
       </c>
       <c r="H1302" t="n">
         <v>1865038</v>
@@ -38156,7 +38156,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.42883849143982</v>
+        <v>3.4288387298584</v>
       </c>
       <c r="H1303" t="n">
         <v>1307714</v>
@@ -38214,7 +38214,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.45912265777588</v>
+        <v>3.4591224193573</v>
       </c>
       <c r="H1305" t="n">
         <v>1119391</v>
@@ -38243,7 +38243,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.50118398666382</v>
+        <v>3.50118374824524</v>
       </c>
       <c r="H1306" t="n">
         <v>995208</v>
@@ -38330,7 +38330,7 @@
         <v>4.22300004959106</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.55249881744385</v>
+        <v>3.55249905586243</v>
       </c>
       <c r="H1309" t="n">
         <v>1179788</v>
@@ -38388,7 +38388,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.5264208316803</v>
+        <v>3.52642059326172</v>
       </c>
       <c r="H1311" t="n">
         <v>1292056</v>
@@ -38446,7 +38446,7 @@
         <v>4.32600021362305</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.6391453742981</v>
+        <v>3.63914561271667</v>
       </c>
       <c r="H1313" t="n">
         <v>2960871</v>
@@ -38504,7 +38504,7 @@
         <v>4.23600006103516</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.56343460083008</v>
+        <v>3.56343507766724</v>
       </c>
       <c r="H1315" t="n">
         <v>1887472</v>
@@ -38562,7 +38562,7 @@
         <v>4.14300012588501</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.48520064353943</v>
+        <v>3.48520088195801</v>
       </c>
       <c r="H1317" t="n">
         <v>1459082</v>
@@ -38997,7 +38997,7 @@
         <v>4.09299993515015</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.44313931465149</v>
+        <v>3.44313955307007</v>
       </c>
       <c r="H1332" t="n">
         <v>859323</v>
@@ -39113,7 +39113,7 @@
         <v>4.4229998588562</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.72074413299561</v>
+        <v>3.72074389457703</v>
       </c>
       <c r="H1336" t="n">
         <v>2901452</v>
@@ -39142,7 +39142,7 @@
         <v>4.44099998474121</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.73588633537292</v>
+        <v>3.73588609695435</v>
       </c>
       <c r="H1337" t="n">
         <v>1610539</v>
@@ -39171,7 +39171,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G1338" t="n">
-        <v>3.82926225662231</v>
+        <v>3.82926201820374</v>
       </c>
       <c r="H1338" t="n">
         <v>1755535</v>
@@ -39200,7 +39200,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.82926225662231</v>
+        <v>3.82926201820374</v>
       </c>
       <c r="H1339" t="n">
         <v>1241856</v>
@@ -39258,7 +39258,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.84019804000854</v>
+        <v>3.84019827842712</v>
       </c>
       <c r="H1341" t="n">
         <v>1203558</v>
@@ -39316,7 +39316,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.87721276283264</v>
+        <v>3.87721252441406</v>
       </c>
       <c r="H1343" t="n">
         <v>1423586</v>
@@ -39345,7 +39345,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.90329003334045</v>
+        <v>3.90329027175903</v>
       </c>
       <c r="H1344" t="n">
         <v>1141934</v>
@@ -39374,7 +39374,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.94366955757141</v>
+        <v>3.94366931915283</v>
       </c>
       <c r="H1345" t="n">
         <v>1481884</v>
@@ -39461,7 +39461,7 @@
         <v>4.53700017929077</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.81664419174194</v>
+        <v>3.81664443016052</v>
       </c>
       <c r="H1348" t="n">
         <v>2276340</v>
@@ -39490,7 +39490,7 @@
         <v>4.60300016403198</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.8721649646759</v>
+        <v>3.87216520309448</v>
       </c>
       <c r="H1349" t="n">
         <v>864539</v>
@@ -39519,7 +39519,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.85113406181335</v>
+        <v>3.85113453865051</v>
       </c>
       <c r="H1350" t="n">
         <v>693551</v>
@@ -39548,7 +39548,7 @@
         <v>4.56899976730347</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.84356260299683</v>
+        <v>3.84356284141541</v>
       </c>
       <c r="H1351" t="n">
         <v>745424</v>
@@ -39606,7 +39606,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.85618185997009</v>
+        <v>3.85618138313293</v>
       </c>
       <c r="H1353" t="n">
         <v>1766336</v>
@@ -39635,7 +39635,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.82757997512817</v>
+        <v>3.82758021354675</v>
       </c>
       <c r="H1354" t="n">
         <v>1519001</v>
@@ -39664,7 +39664,7 @@
         <v>4.58599996566772</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.85786366462708</v>
+        <v>3.8578634262085</v>
       </c>
       <c r="H1355" t="n">
         <v>1795596</v>
@@ -39693,7 +39693,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.85618185997009</v>
+        <v>3.85618138313293</v>
       </c>
       <c r="H1356" t="n">
         <v>2609924</v>
@@ -39722,7 +39722,7 @@
         <v>4.65899991989136</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.919273853302</v>
+        <v>3.91927337646484</v>
       </c>
       <c r="H1357" t="n">
         <v>2680349</v>
@@ -39809,7 +39809,7 @@
         <v>4.65399980545044</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.91506719589233</v>
+        <v>3.91506743431091</v>
       </c>
       <c r="H1360" t="n">
         <v>2940384</v>
@@ -39867,7 +39867,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.95208144187927</v>
+        <v>3.95208120346069</v>
       </c>
       <c r="H1362" t="n">
         <v>1779581</v>
@@ -39896,7 +39896,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.83767437934875</v>
+        <v>3.83767414093018</v>
       </c>
       <c r="H1363" t="n">
         <v>2263573</v>
@@ -39925,7 +39925,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.90917873382568</v>
+        <v>3.9091784954071</v>
       </c>
       <c r="H1364" t="n">
         <v>1819880</v>
@@ -39954,7 +39954,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.95376324653625</v>
+        <v>3.95376348495483</v>
       </c>
       <c r="H1365" t="n">
         <v>1904113</v>
@@ -39983,7 +39983,7 @@
         <v>4.78900003433228</v>
       </c>
       <c r="G1366" t="n">
-        <v>4.02863311767578</v>
+        <v>4.02863264083862</v>
       </c>
       <c r="H1366" t="n">
         <v>5871194</v>
@@ -40012,7 +40012,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.16406965255737</v>
+        <v>4.16407012939453</v>
       </c>
       <c r="H1367" t="n">
         <v>10998509</v>
@@ -40128,7 +40128,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G1371" t="n">
-        <v>4.04209232330322</v>
+        <v>4.04209184646606</v>
       </c>
       <c r="H1371" t="n">
         <v>1614868</v>
@@ -40157,7 +40157,7 @@
         <v>4.95300006866455</v>
       </c>
       <c r="G1372" t="n">
-        <v>4.16659450531006</v>
+        <v>4.1665940284729</v>
       </c>
       <c r="H1372" t="n">
         <v>5809624</v>
@@ -40186,7 +40186,7 @@
         <v>4.76700019836426</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.01012563705444</v>
+        <v>4.0101261138916</v>
       </c>
       <c r="H1373" t="n">
         <v>3059807</v>
@@ -40273,7 +40273,7 @@
         <v>4.89099979400635</v>
       </c>
       <c r="G1376" t="n">
-        <v>4.1144380569458</v>
+        <v>4.11443758010864</v>
       </c>
       <c r="H1376" t="n">
         <v>2478173</v>
@@ -40331,7 +40331,7 @@
         <v>4.94399976730347</v>
       </c>
       <c r="G1378" t="n">
-        <v>4.15902233123779</v>
+        <v>4.15902280807495</v>
       </c>
       <c r="H1378" t="n">
         <v>1603382</v>
@@ -40418,7 +40418,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1381" t="n">
-        <v>4.16238737106323</v>
+        <v>4.16238784790039</v>
       </c>
       <c r="H1381" t="n">
         <v>1401021</v>
@@ -40476,7 +40476,7 @@
         <v>4.74900007247925</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.99498414993286</v>
+        <v>3.99498438835144</v>
       </c>
       <c r="H1383" t="n">
         <v>2196345</v>
@@ -40505,7 +40505,7 @@
         <v>4.50299978256226</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.78804206848145</v>
+        <v>3.78804183006287</v>
       </c>
       <c r="H1384" t="n">
         <v>3597094</v>
@@ -40534,7 +40534,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.86627650260925</v>
+        <v>3.86627674102783</v>
       </c>
       <c r="H1385" t="n">
         <v>2645603</v>
@@ -40592,7 +40592,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.73672699928284</v>
+        <v>3.73672723770142</v>
       </c>
       <c r="H1387" t="n">
         <v>1881833</v>
@@ -40679,7 +40679,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.79561328887939</v>
+        <v>3.79561305046082</v>
       </c>
       <c r="H1390" t="n">
         <v>2003223</v>
@@ -40708,7 +40708,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.7560760974884</v>
+        <v>3.75607562065125</v>
       </c>
       <c r="H1391" t="n">
         <v>1114169</v>
@@ -40737,7 +40737,7 @@
         <v>4.45699977874756</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.74934530258179</v>
+        <v>3.74934554100037</v>
       </c>
       <c r="H1392" t="n">
         <v>1090790</v>
@@ -40795,7 +40795,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.6963484287262</v>
+        <v>3.69634819030762</v>
       </c>
       <c r="H1394" t="n">
         <v>1311955</v>
@@ -40824,7 +40824,7 @@
         <v>4.40899991989136</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.70896649360657</v>
+        <v>3.70896625518799</v>
       </c>
       <c r="H1395" t="n">
         <v>1151563</v>
@@ -40853,7 +40853,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.76448750495911</v>
+        <v>3.76448774337769</v>
       </c>
       <c r="H1396" t="n">
         <v>1206554</v>
@@ -40882,7 +40882,7 @@
         <v>4.55900001525879</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.83515071868896</v>
+        <v>3.83515095710754</v>
       </c>
       <c r="H1397" t="n">
         <v>1778437</v>
@@ -40911,7 +40911,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.88814854621887</v>
+        <v>3.88814830780029</v>
       </c>
       <c r="H1398" t="n">
         <v>1770472</v>
@@ -40969,7 +40969,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.95460557937622</v>
+        <v>3.95460510253906</v>
       </c>
       <c r="H1400" t="n">
         <v>2792824</v>
@@ -41056,7 +41056,7 @@
         <v>4.61700010299683</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.88394212722778</v>
+        <v>3.88394236564636</v>
       </c>
       <c r="H1403" t="n">
         <v>2993439</v>
@@ -41085,7 +41085,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.88141798973083</v>
+        <v>3.88141775131226</v>
       </c>
       <c r="H1404" t="n">
         <v>1594098</v>
@@ -41114,7 +41114,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.95208144187927</v>
+        <v>3.95208120346069</v>
       </c>
       <c r="H1405" t="n">
         <v>3198683</v>
@@ -41143,7 +41143,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.95796990394592</v>
+        <v>3.95796966552734</v>
       </c>
       <c r="H1406" t="n">
         <v>1496436</v>
@@ -41201,7 +41201,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1408" t="n">
-        <v>4.03788614273071</v>
+        <v>4.03788661956787</v>
       </c>
       <c r="H1408" t="n">
         <v>3190468</v>
@@ -41259,7 +41259,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.92768549919128</v>
+        <v>3.92768597602844</v>
       </c>
       <c r="H1410" t="n">
         <v>3075239</v>
@@ -41288,7 +41288,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.91843199729919</v>
+        <v>3.91843247413635</v>
       </c>
       <c r="H1411" t="n">
         <v>1704307</v>
@@ -41346,7 +41346,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.84861040115356</v>
+        <v>3.84860992431641</v>
       </c>
       <c r="H1413" t="n">
         <v>2048783</v>
@@ -41375,7 +41375,7 @@
         <v>4.62200021743774</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.88814854621887</v>
+        <v>3.88814830780029</v>
       </c>
       <c r="H1414" t="n">
         <v>1677966</v>
@@ -41404,7 +41404,7 @@
         <v>4.63700008392334</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.90076637268066</v>
+        <v>3.90076661109924</v>
       </c>
       <c r="H1415" t="n">
         <v>1839189</v>
@@ -41433,7 +41433,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.99246001243591</v>
+        <v>3.99245977401733</v>
       </c>
       <c r="H1416" t="n">
         <v>2199392</v>
@@ -41462,7 +41462,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.91843199729919</v>
+        <v>3.91843247413635</v>
       </c>
       <c r="H1417" t="n">
         <v>1704997</v>
@@ -41491,7 +41491,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.99414277076721</v>
+        <v>3.99414253234863</v>
       </c>
       <c r="H1418" t="n">
         <v>1526178</v>
@@ -41520,7 +41520,7 @@
         <v>4.72100019454956</v>
       </c>
       <c r="G1419" t="n">
-        <v>3.97142934799194</v>
+        <v>3.97142958641052</v>
       </c>
       <c r="H1419" t="n">
         <v>1366810</v>
@@ -41636,7 +41636,7 @@
         <v>4.90299987792969</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.12453317642212</v>
+        <v>4.12453269958496</v>
       </c>
       <c r="H1423" t="n">
         <v>2276972</v>
@@ -41665,7 +41665,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G1424" t="n">
-        <v>4.0235857963562</v>
+        <v>4.02358531951904</v>
       </c>
       <c r="H1424" t="n">
         <v>2609423</v>
@@ -41694,7 +41694,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.151451587677</v>
+        <v>4.15145206451416</v>
       </c>
       <c r="H1425" t="n">
         <v>3827861</v>
@@ -41723,7 +41723,7 @@
         <v>4.8289999961853</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.06228160858154</v>
+        <v>4.0622820854187</v>
       </c>
       <c r="H1426" t="n">
         <v>2187359</v>
@@ -41752,7 +41752,7 @@
         <v>4.83099985122681</v>
       </c>
       <c r="G1427" t="n">
-        <v>4.06396484375</v>
+        <v>4.06396436691284</v>
       </c>
       <c r="H1427" t="n">
         <v>1218784</v>
@@ -41839,7 +41839,7 @@
         <v>4.88399982452393</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.10854911804199</v>
+        <v>4.10854959487915</v>
       </c>
       <c r="H1430" t="n">
         <v>1479454</v>
@@ -41897,7 +41897,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1432" t="n">
-        <v>4.06312274932861</v>
+        <v>4.06312322616577</v>
       </c>
       <c r="H1432" t="n">
         <v>901576</v>
@@ -41926,7 +41926,7 @@
         <v>4.58699989318848</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.85870552062988</v>
+        <v>3.8587052822113</v>
       </c>
       <c r="H1433" t="n">
         <v>4586945</v>
@@ -41955,7 +41955,7 @@
         <v>4.51900005340576</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.80150151252747</v>
+        <v>3.80150175094604</v>
       </c>
       <c r="H1434" t="n">
         <v>2626813</v>
@@ -41984,7 +41984,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.87468814849854</v>
+        <v>3.87468838691711</v>
       </c>
       <c r="H1435" t="n">
         <v>1604844</v>
@@ -42042,7 +42042,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.82757997512817</v>
+        <v>3.82758021354675</v>
       </c>
       <c r="H1437" t="n">
         <v>765125</v>
@@ -42129,7 +42129,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.87468814849854</v>
+        <v>3.87468838691711</v>
       </c>
       <c r="H1440" t="n">
         <v>1471923</v>
@@ -42158,7 +42158,7 @@
         <v>4.58300018310547</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.85534048080444</v>
+        <v>3.8553409576416</v>
       </c>
       <c r="H1441" t="n">
         <v>1250531</v>
@@ -42187,7 +42187,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.82337403297424</v>
+        <v>3.82337355613708</v>
       </c>
       <c r="H1442" t="n">
         <v>2119319</v>
@@ -42245,7 +42245,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.8317859172821</v>
+        <v>3.83178615570068</v>
       </c>
       <c r="H1444" t="n">
         <v>2233653</v>
@@ -42303,7 +42303,7 @@
         <v>4.64300012588501</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.90581369400024</v>
+        <v>3.90581393241882</v>
       </c>
       <c r="H1446" t="n">
         <v>2353807</v>
@@ -42332,7 +42332,7 @@
         <v>4.68100023269653</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.9377806186676</v>
+        <v>3.93778085708618</v>
       </c>
       <c r="H1447" t="n">
         <v>2173463</v>
@@ -42361,7 +42361,7 @@
         <v>4.67899990081787</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.93609762191772</v>
+        <v>3.93609809875488</v>
       </c>
       <c r="H1448" t="n">
         <v>1534277</v>
@@ -42390,7 +42390,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.90917873382568</v>
+        <v>3.9091784954071</v>
       </c>
       <c r="H1449" t="n">
         <v>1323793</v>
@@ -42419,7 +42419,7 @@
         <v>4.61899995803833</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.88562393188477</v>
+        <v>3.88562417030334</v>
       </c>
       <c r="H1450" t="n">
         <v>3112143</v>
@@ -42506,7 +42506,7 @@
         <v>4.43300008773804</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.72915601730347</v>
+        <v>3.72915577888489</v>
       </c>
       <c r="H1453" t="n">
         <v>4104182</v>
@@ -42535,7 +42535,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.74345707893372</v>
+        <v>3.74345684051514</v>
       </c>
       <c r="H1454" t="n">
         <v>3310751</v>
@@ -42622,7 +42622,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.74345707893372</v>
+        <v>3.74345684051514</v>
       </c>
       <c r="H1457" t="n">
         <v>1671361</v>
@@ -42651,7 +42651,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.78131246566772</v>
+        <v>3.78131222724915</v>
       </c>
       <c r="H1458" t="n">
         <v>2078424</v>
@@ -42680,7 +42680,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.78383612632751</v>
+        <v>3.78383636474609</v>
       </c>
       <c r="H1459" t="n">
         <v>2243918</v>
@@ -42767,7 +42767,7 @@
         <v>4.57100009918213</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.84524536132812</v>
+        <v>3.8452455997467</v>
       </c>
       <c r="H1462" t="n">
         <v>1737710</v>
@@ -42796,7 +42796,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.82085013389587</v>
+        <v>3.82084989547729</v>
       </c>
       <c r="H1463" t="n">
         <v>2290443</v>
@@ -42825,7 +42825,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.7299976348877</v>
+        <v>3.72999739646912</v>
       </c>
       <c r="H1464" t="n">
         <v>3422951</v>
@@ -42883,7 +42883,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.76364684104919</v>
+        <v>3.76364636421204</v>
       </c>
       <c r="H1466" t="n">
         <v>1255557</v>
@@ -42941,7 +42941,7 @@
         <v>4.63700008392334</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.90076637268066</v>
+        <v>3.90076661109924</v>
       </c>
       <c r="H1468" t="n">
         <v>4521681</v>
@@ -42999,7 +42999,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.95544624328613</v>
+        <v>3.95544648170471</v>
       </c>
       <c r="H1470" t="n">
         <v>1507196</v>
@@ -43028,7 +43028,7 @@
         <v>4.64699983596802</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.90917873382568</v>
+        <v>3.9091784954071</v>
       </c>
       <c r="H1471" t="n">
         <v>2049781</v>
@@ -43057,7 +43057,7 @@
         <v>4.71799993515015</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.96890568733215</v>
+        <v>3.96890592575073</v>
       </c>
       <c r="H1472" t="n">
         <v>1326059</v>
@@ -43173,7 +43173,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1476" t="n">
-        <v>4.14024591445923</v>
+        <v>4.14024543762207</v>
       </c>
       <c r="H1476" t="n">
         <v>3762830</v>
@@ -43289,7 +43289,7 @@
         <v>4.91699981689453</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.33140182495117</v>
+        <v>4.33140230178833</v>
       </c>
       <c r="H1480" t="n">
         <v>3639110</v>
@@ -43318,7 +43318,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1481" t="n">
-        <v>4.27238178253174</v>
+        <v>4.27238130569458</v>
       </c>
       <c r="H1481" t="n">
         <v>2743673</v>
@@ -43347,7 +43347,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.29880809783936</v>
+        <v>4.29880857467651</v>
       </c>
       <c r="H1482" t="n">
         <v>1983741</v>
@@ -43376,7 +43376,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1483" t="n">
-        <v>4.27238178253174</v>
+        <v>4.27238130569458</v>
       </c>
       <c r="H1483" t="n">
         <v>1777355</v>
@@ -43405,7 +43405,7 @@
         <v>4.76800012588501</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.20014715194702</v>
+        <v>4.20014762878418</v>
       </c>
       <c r="H1484" t="n">
         <v>1653824</v>
@@ -43492,7 +43492,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.07858324050903</v>
+        <v>4.07858276367188</v>
       </c>
       <c r="H1487" t="n">
         <v>1319825</v>
@@ -43521,7 +43521,7 @@
         <v>4.62099981307983</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.07065391540527</v>
+        <v>4.07065439224243</v>
       </c>
       <c r="H1488" t="n">
         <v>1702173</v>
@@ -43550,7 +43550,7 @@
         <v>4.60400009155273</v>
       </c>
       <c r="G1489" t="n">
-        <v>4.0556788444519</v>
+        <v>4.05567932128906</v>
       </c>
       <c r="H1489" t="n">
         <v>1331597</v>
@@ -43608,7 +43608,7 @@
         <v>4.54400014877319</v>
       </c>
       <c r="G1491" t="n">
-        <v>4.00282526016235</v>
+        <v>4.0028247833252</v>
       </c>
       <c r="H1491" t="n">
         <v>1375002</v>
@@ -43637,7 +43637,7 @@
         <v>4.56899976730347</v>
       </c>
       <c r="G1492" t="n">
-        <v>4.02484750747681</v>
+        <v>4.02484703063965</v>
       </c>
       <c r="H1492" t="n">
         <v>1283800</v>
@@ -43724,7 +43724,7 @@
         <v>4.51700019836426</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.97904062271118</v>
+        <v>3.97904086112976</v>
       </c>
       <c r="H1495" t="n">
         <v>1434114</v>
@@ -43753,7 +43753,7 @@
         <v>4.50699996948242</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.97023153305054</v>
+        <v>3.97023129463196</v>
       </c>
       <c r="H1496" t="n">
         <v>930525</v>
@@ -43811,7 +43811,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.94997096061707</v>
+        <v>3.94997072219849</v>
       </c>
       <c r="H1498" t="n">
         <v>965105</v>
@@ -43840,7 +43840,7 @@
         <v>4.49300003051758</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.95789909362793</v>
+        <v>3.95789885520935</v>
       </c>
       <c r="H1499" t="n">
         <v>971940</v>
@@ -43869,7 +43869,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.99401617050171</v>
+        <v>3.99401593208313</v>
       </c>
       <c r="H1500" t="n">
         <v>794751</v>
@@ -43927,7 +43927,7 @@
         <v>4.58099985122681</v>
       </c>
       <c r="G1502" t="n">
-        <v>4.03541851043701</v>
+        <v>4.03541803359985</v>
       </c>
       <c r="H1502" t="n">
         <v>1449451</v>
@@ -44043,7 +44043,7 @@
         <v>4.73299980163574</v>
       </c>
       <c r="G1506" t="n">
-        <v>4.16931581497192</v>
+        <v>4.16931533813477</v>
       </c>
       <c r="H1506" t="n">
         <v>2129245</v>
@@ -44246,7 +44246,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1513" t="n">
-        <v>4.18252944946289</v>
+        <v>4.18252897262573</v>
       </c>
       <c r="H1513" t="n">
         <v>2073053</v>
@@ -44304,7 +44304,7 @@
         <v>4.68900012969971</v>
       </c>
       <c r="G1515" t="n">
-        <v>4.13055658340454</v>
+        <v>4.13055610656738</v>
       </c>
       <c r="H1515" t="n">
         <v>1251667</v>
@@ -44536,7 +44536,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1523" t="n">
-        <v>4.01868104934692</v>
+        <v>4.01868152618408</v>
       </c>
       <c r="H1523" t="n">
         <v>3026688</v>
@@ -44565,7 +44565,7 @@
         <v>4.56099987030029</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.01779985427856</v>
+        <v>4.01780033111572</v>
       </c>
       <c r="H1524" t="n">
         <v>1977623</v>
@@ -44594,7 +44594,7 @@
         <v>4.47800016403198</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.94468545913696</v>
+        <v>3.94468593597412</v>
       </c>
       <c r="H1525" t="n">
         <v>1481934</v>
@@ -44623,7 +44623,7 @@
         <v>4.44399976730347</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.91473436355591</v>
+        <v>3.91473412513733</v>
       </c>
       <c r="H1526" t="n">
         <v>1426451</v>
@@ -44681,7 +44681,7 @@
         <v>4.35099983215332</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.8328104019165</v>
+        <v>3.83281016349792</v>
       </c>
       <c r="H1528" t="n">
         <v>1313742</v>
@@ -44739,7 +44739,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.91121125221252</v>
+        <v>3.91121077537537</v>
       </c>
       <c r="H1530" t="n">
         <v>2215361</v>
@@ -44768,7 +44768,7 @@
         <v>4.44299983978271</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.91385388374329</v>
+        <v>3.91385364532471</v>
       </c>
       <c r="H1531" t="n">
         <v>2329729</v>
@@ -44797,7 +44797,7 @@
         <v>4.47100019454956</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.93851900100708</v>
+        <v>3.93851923942566</v>
       </c>
       <c r="H1532" t="n">
         <v>1809355</v>
@@ -44855,7 +44855,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.87597513198853</v>
+        <v>3.87597465515137</v>
       </c>
       <c r="H1534" t="n">
         <v>2153280</v>
@@ -44884,7 +44884,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.96230363845825</v>
+        <v>3.96230340003967</v>
       </c>
       <c r="H1535" t="n">
         <v>1963647</v>
@@ -44913,7 +44913,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.95349454879761</v>
+        <v>3.95349407196045</v>
       </c>
       <c r="H1536" t="n">
         <v>1423494</v>
@@ -44942,7 +44942,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.92530536651611</v>
+        <v>3.92530512809753</v>
       </c>
       <c r="H1537" t="n">
         <v>1819378</v>
@@ -44971,7 +44971,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.84073901176453</v>
+        <v>3.84073853492737</v>
       </c>
       <c r="H1538" t="n">
         <v>1558430</v>
@@ -45029,7 +45029,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.66455817222595</v>
+        <v>3.66455769538879</v>
       </c>
       <c r="H1540" t="n">
         <v>4026623</v>
@@ -45116,7 +45116,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.62051320075989</v>
+        <v>3.62051296234131</v>
       </c>
       <c r="H1543" t="n">
         <v>2643345</v>
@@ -45145,7 +45145,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.58527684211731</v>
+        <v>3.58527708053589</v>
       </c>
       <c r="H1544" t="n">
         <v>2170665</v>
@@ -45232,7 +45232,7 @@
         <v>4.23299980163574</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.72886395454407</v>
+        <v>3.72886371612549</v>
       </c>
       <c r="H1547" t="n">
         <v>1519824</v>
@@ -45261,7 +45261,7 @@
         <v>4.3270001411438</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.81166911125183</v>
+        <v>3.81166934967041</v>
       </c>
       <c r="H1548" t="n">
         <v>2203705</v>
@@ -45290,7 +45290,7 @@
         <v>4.39300012588501</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.86980867385864</v>
+        <v>3.86980843544006</v>
       </c>
       <c r="H1549" t="n">
         <v>1570178</v>
@@ -45348,7 +45348,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.84073901176453</v>
+        <v>3.84073853492737</v>
       </c>
       <c r="H1551" t="n">
         <v>1258004</v>
@@ -45377,7 +45377,7 @@
         <v>4.44700002670288</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.91737723350525</v>
+        <v>3.91737747192383</v>
       </c>
       <c r="H1552" t="n">
         <v>1655213</v>
@@ -45464,7 +45464,7 @@
         <v>4.44099998474121</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.91209173202515</v>
+        <v>3.9120922088623</v>
       </c>
       <c r="H1555" t="n">
         <v>1441226</v>
@@ -45493,7 +45493,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.98961114883423</v>
+        <v>3.98961138725281</v>
       </c>
       <c r="H1556" t="n">
         <v>2208333</v>
@@ -45522,7 +45522,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.98961114883423</v>
+        <v>3.98961138725281</v>
       </c>
       <c r="H1557" t="n">
         <v>1771099</v>
@@ -45551,7 +45551,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.93587589263916</v>
+        <v>3.93587636947632</v>
       </c>
       <c r="H1558" t="n">
         <v>1690561</v>
@@ -45609,7 +45609,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G1560" t="n">
-        <v>4.00018215179443</v>
+        <v>4.00018262863159</v>
       </c>
       <c r="H1560" t="n">
         <v>1364027</v>
@@ -45638,7 +45638,7 @@
         <v>4.46099996566772</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.92970991134644</v>
+        <v>3.92970967292786</v>
       </c>
       <c r="H1561" t="n">
         <v>1580647</v>
@@ -45667,7 +45667,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.94997096061707</v>
+        <v>3.94997072219849</v>
       </c>
       <c r="H1562" t="n">
         <v>1166827</v>
@@ -45696,7 +45696,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.95173263549805</v>
+        <v>3.95173239707947</v>
       </c>
       <c r="H1563" t="n">
         <v>930940</v>
@@ -45725,7 +45725,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.97111225128174</v>
+        <v>3.97111248970032</v>
       </c>
       <c r="H1564" t="n">
         <v>811260</v>
@@ -45754,7 +45754,7 @@
         <v>4.54899978637695</v>
       </c>
       <c r="G1565" t="n">
-        <v>4.00722932815552</v>
+        <v>4.00722885131836</v>
       </c>
       <c r="H1565" t="n">
         <v>1716205</v>
@@ -45783,7 +45783,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G1566" t="n">
-        <v>4.0133957862854</v>
+        <v>4.01339626312256</v>
       </c>
       <c r="H1566" t="n">
         <v>1288155</v>
@@ -45870,7 +45870,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.01868104934692</v>
+        <v>4.01868152618408</v>
       </c>
       <c r="H1569" t="n">
         <v>2341666</v>
@@ -46044,7 +46044,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1575" t="n">
-        <v>4.2459545135498</v>
+        <v>4.24595403671265</v>
       </c>
       <c r="H1575" t="n">
         <v>1850014</v>
@@ -46131,7 +46131,7 @@
         <v>4.86100006103516</v>
       </c>
       <c r="G1578" t="n">
-        <v>4.28207111358643</v>
+        <v>4.28207159042358</v>
       </c>
       <c r="H1578" t="n">
         <v>3296575</v>
@@ -46160,7 +46160,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G1579" t="n">
-        <v>4.25123929977417</v>
+        <v>4.25123977661133</v>
       </c>
       <c r="H1579" t="n">
         <v>3303443</v>
@@ -46189,7 +46189,7 @@
         <v>4.78700017929077</v>
       </c>
       <c r="G1580" t="n">
-        <v>4.21688461303711</v>
+        <v>4.21688508987427</v>
       </c>
       <c r="H1580" t="n">
         <v>1853469</v>
@@ -46218,7 +46218,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G1581" t="n">
-        <v>4.23009777069092</v>
+        <v>4.23009824752808</v>
       </c>
       <c r="H1581" t="n">
         <v>1650758</v>
@@ -46363,7 +46363,7 @@
         <v>4.9229998588562</v>
       </c>
       <c r="G1586" t="n">
-        <v>4.3366870880127</v>
+        <v>4.33668756484985</v>
       </c>
       <c r="H1586" t="n">
         <v>2261957</v>
@@ -46392,7 +46392,7 @@
         <v>4.92700004577637</v>
       </c>
       <c r="G1587" t="n">
-        <v>4.34021091461182</v>
+        <v>4.34021043777466</v>
       </c>
       <c r="H1587" t="n">
         <v>1485677</v>
@@ -46421,7 +46421,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G1588" t="n">
-        <v>4.34990167617798</v>
+        <v>4.34990119934082</v>
       </c>
       <c r="H1588" t="n">
         <v>1909391</v>
@@ -46450,7 +46450,7 @@
         <v>4.83099985122681</v>
       </c>
       <c r="G1589" t="n">
-        <v>4.25564384460449</v>
+        <v>4.25564432144165</v>
       </c>
       <c r="H1589" t="n">
         <v>1549886</v>
@@ -46508,7 +46508,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G1591" t="n">
-        <v>4.26181077957153</v>
+        <v>4.26181030273438</v>
       </c>
       <c r="H1591" t="n">
         <v>1494436</v>
@@ -46537,7 +46537,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.39042234420776</v>
+        <v>4.39042282104492</v>
       </c>
       <c r="H1592" t="n">
         <v>2796389</v>
@@ -46595,7 +46595,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1594" t="n">
-        <v>4.56307888031006</v>
+        <v>4.56307935714722</v>
       </c>
       <c r="H1594" t="n">
         <v>2130981</v>
@@ -46624,7 +46624,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G1595" t="n">
-        <v>4.69169187545776</v>
+        <v>4.69169139862061</v>
       </c>
       <c r="H1595" t="n">
         <v>3747916</v>
@@ -46653,7 +46653,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G1596" t="n">
-        <v>4.67231178283691</v>
+        <v>4.67231130599976</v>
       </c>
       <c r="H1596" t="n">
         <v>2803424</v>
@@ -46682,7 +46682,7 @@
         <v>5.19799995422363</v>
       </c>
       <c r="G1597" t="n">
-        <v>4.5789361000061</v>
+        <v>4.57893562316895</v>
       </c>
       <c r="H1597" t="n">
         <v>3083657</v>
@@ -46798,7 +46798,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G1601" t="n">
-        <v>4.50317811965942</v>
+        <v>4.50317859649658</v>
       </c>
       <c r="H1601" t="n">
         <v>2330127</v>
@@ -46914,7 +46914,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G1605" t="n">
-        <v>4.50317811965942</v>
+        <v>4.50317859649658</v>
       </c>
       <c r="H1605" t="n">
         <v>1426290</v>
@@ -46943,7 +46943,7 @@
         <v>5.2039999961853</v>
       </c>
       <c r="G1606" t="n">
-        <v>4.58422136306763</v>
+        <v>4.58422088623047</v>
       </c>
       <c r="H1606" t="n">
         <v>1873235</v>
@@ -46972,7 +46972,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1607" t="n">
-        <v>4.55427026748657</v>
+        <v>4.55427074432373</v>
       </c>
       <c r="H1607" t="n">
         <v>1167250</v>
@@ -47001,7 +47001,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G1608" t="n">
-        <v>4.52255725860596</v>
+        <v>4.52255773544312</v>
       </c>
       <c r="H1608" t="n">
         <v>4438145</v>
@@ -47059,7 +47059,7 @@
         <v>5.01399993896484</v>
       </c>
       <c r="G1610" t="n">
-        <v>4.41684913635254</v>
+        <v>4.4168496131897</v>
       </c>
       <c r="H1610" t="n">
         <v>1491742</v>
@@ -47088,7 +47088,7 @@
         <v>5.03599977493286</v>
       </c>
       <c r="G1611" t="n">
-        <v>4.43622922897339</v>
+        <v>4.43622875213623</v>
       </c>
       <c r="H1611" t="n">
         <v>1457242</v>
@@ -47262,7 +47262,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.74278354644775</v>
+        <v>4.74278402328491</v>
       </c>
       <c r="H1617" t="n">
         <v>1946543</v>
@@ -47320,7 +47320,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1619" t="n">
-        <v>4.75687837600708</v>
+        <v>4.75687885284424</v>
       </c>
       <c r="H1619" t="n">
         <v>1236595</v>
@@ -47494,7 +47494,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1625" t="n">
-        <v>4.77449655532837</v>
+        <v>4.77449607849121</v>
       </c>
       <c r="H1625" t="n">
         <v>1615810</v>
@@ -47523,7 +47523,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G1626" t="n">
-        <v>4.80268573760986</v>
+        <v>4.80268526077271</v>
       </c>
       <c r="H1626" t="n">
         <v>1557790</v>
@@ -47697,7 +47697,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G1632" t="n">
-        <v>4.99472236633301</v>
+        <v>4.99472188949585</v>
       </c>
       <c r="H1632" t="n">
         <v>2851049</v>
@@ -47755,7 +47755,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1634" t="n">
-        <v>4.88020467758179</v>
+        <v>4.88020420074463</v>
       </c>
       <c r="H1634" t="n">
         <v>9217774</v>
@@ -47871,7 +47871,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G1638" t="n">
-        <v>4.71459531784058</v>
+        <v>4.71459484100342</v>
       </c>
       <c r="H1638" t="n">
         <v>2512138</v>
@@ -47958,7 +47958,7 @@
         <v>5.54400014877319</v>
       </c>
       <c r="G1641" t="n">
-        <v>4.88372802734375</v>
+        <v>4.88372850418091</v>
       </c>
       <c r="H1641" t="n">
         <v>4579164</v>
@@ -48016,7 +48016,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1643" t="n">
-        <v>4.91720247268677</v>
+        <v>4.91720199584961</v>
       </c>
       <c r="H1643" t="n">
         <v>1157047</v>
@@ -48045,7 +48045,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G1644" t="n">
-        <v>4.89606094360352</v>
+        <v>4.89606142044067</v>
       </c>
       <c r="H1644" t="n">
         <v>1403328</v>
@@ -48074,7 +48074,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1645" t="n">
-        <v>4.9330587387085</v>
+        <v>4.93305921554565</v>
       </c>
       <c r="H1645" t="n">
         <v>1639165</v>
@@ -48161,7 +48161,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1648" t="n">
-        <v>4.97357988357544</v>
+        <v>4.97358083724976</v>
       </c>
       <c r="H1648" t="n">
         <v>1355402</v>
@@ -48190,7 +48190,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G1649" t="n">
-        <v>4.99472236633301</v>
+        <v>4.99472188949585</v>
       </c>
       <c r="H1649" t="n">
         <v>1087378</v>
@@ -48248,7 +48248,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1651" t="n">
-        <v>4.97357988357544</v>
+        <v>4.97358083724976</v>
       </c>
       <c r="H1651" t="n">
         <v>1114962</v>
@@ -48480,7 +48480,7 @@
         <v>5.83799982070923</v>
       </c>
       <c r="G1659" t="n">
-        <v>5.14271402359009</v>
+        <v>5.14271354675293</v>
       </c>
       <c r="H1659" t="n">
         <v>2031189</v>
@@ -48596,7 +48596,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1663" t="n">
-        <v>5.17090320587158</v>
+        <v>5.17090272903442</v>
       </c>
       <c r="H1663" t="n">
         <v>1114408</v>
@@ -48625,7 +48625,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G1664" t="n">
-        <v>5.1233344078064</v>
+        <v>5.12333393096924</v>
       </c>
       <c r="H1664" t="n">
         <v>1446906</v>
@@ -48654,7 +48654,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1665" t="n">
-        <v>5.23256587982178</v>
+        <v>5.23256635665894</v>
       </c>
       <c r="H1665" t="n">
         <v>2337724</v>
@@ -48683,7 +48683,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G1666" t="n">
-        <v>5.27484893798828</v>
+        <v>5.27484941482544</v>
       </c>
       <c r="H1666" t="n">
         <v>1580963</v>
@@ -48712,7 +48712,7 @@
         <v>5.97800016403198</v>
       </c>
       <c r="G1667" t="n">
-        <v>5.26604032516479</v>
+        <v>5.26604080200195</v>
       </c>
       <c r="H1667" t="n">
         <v>2174296</v>
@@ -48886,7 +48886,7 @@
         <v>6.00400018692017</v>
       </c>
       <c r="G1673" t="n">
-        <v>5.28894376754761</v>
+        <v>5.28894424438477</v>
       </c>
       <c r="H1673" t="n">
         <v>1425999</v>
@@ -48973,7 +48973,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G1676" t="n">
-        <v>5.29951477050781</v>
+        <v>5.29951429367065</v>
       </c>
       <c r="H1676" t="n">
         <v>2412084</v>
@@ -49060,7 +49060,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1679" t="n">
-        <v>5.4616003036499</v>
+        <v>5.46160078048706</v>
       </c>
       <c r="H1679" t="n">
         <v>1683821</v>
@@ -49089,7 +49089,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1680" t="n">
-        <v>5.39112854003906</v>
+        <v>5.39112901687622</v>
       </c>
       <c r="H1680" t="n">
         <v>1681364</v>
@@ -49118,7 +49118,7 @@
         <v>6.15199995040894</v>
       </c>
       <c r="G1681" t="n">
-        <v>5.4193172454834</v>
+        <v>5.41931772232056</v>
       </c>
       <c r="H1681" t="n">
         <v>1011525</v>
@@ -49176,7 +49176,7 @@
         <v>6.15199995040894</v>
       </c>
       <c r="G1683" t="n">
-        <v>5.4193172454834</v>
+        <v>5.41931772232056</v>
       </c>
       <c r="H1683" t="n">
         <v>1197391</v>
@@ -49263,7 +49263,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G1686" t="n">
-        <v>5.36470174789429</v>
+        <v>5.36470127105713</v>
       </c>
       <c r="H1686" t="n">
         <v>2071456</v>
@@ -49292,7 +49292,7 @@
         <v>6.08599996566772</v>
       </c>
       <c r="G1687" t="n">
-        <v>5.36117792129517</v>
+        <v>5.36117744445801</v>
       </c>
       <c r="H1687" t="n">
         <v>1326853</v>
@@ -49321,7 +49321,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1688" t="n">
-        <v>5.43517398834229</v>
+        <v>5.43517351150513</v>
       </c>
       <c r="H1688" t="n">
         <v>2465072</v>
@@ -49379,7 +49379,7 @@
         <v>6.17399978637695</v>
       </c>
       <c r="G1690" t="n">
-        <v>5.43869733810425</v>
+        <v>5.43869686126709</v>
       </c>
       <c r="H1690" t="n">
         <v>1569252</v>
@@ -49408,7 +49408,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G1691" t="n">
-        <v>5.45279216766357</v>
+        <v>5.45279169082642</v>
       </c>
       <c r="H1691" t="n">
         <v>1537873</v>
@@ -49495,7 +49495,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G1694" t="n">
-        <v>5.29775333404541</v>
+        <v>5.29775285720825</v>
       </c>
       <c r="H1694" t="n">
         <v>3090297</v>
@@ -49582,7 +49582,7 @@
         <v>6.0460000038147</v>
       </c>
       <c r="G1697" t="n">
-        <v>5.32594203948975</v>
+        <v>5.32594156265259</v>
       </c>
       <c r="H1697" t="n">
         <v>2203107</v>
@@ -49611,7 +49611,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1698" t="n">
-        <v>5.32946538925171</v>
+        <v>5.32946586608887</v>
       </c>
       <c r="H1698" t="n">
         <v>1405206</v>
@@ -49640,7 +49640,7 @@
         <v>6.04400014877319</v>
       </c>
       <c r="G1699" t="n">
-        <v>5.32418012619019</v>
+        <v>5.32417964935303</v>
       </c>
       <c r="H1699" t="n">
         <v>1299410</v>
@@ -49698,7 +49698,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G1701" t="n">
-        <v>5.29951477050781</v>
+        <v>5.29951429367065</v>
       </c>
       <c r="H1701" t="n">
         <v>2215181</v>
@@ -49843,7 +49843,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1706" t="n">
-        <v>5.135666847229</v>
+        <v>5.13566637039185</v>
       </c>
       <c r="H1706" t="n">
         <v>1336134</v>
@@ -50046,7 +50046,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1713" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1713" t="n">
         <v>1930745</v>
@@ -50075,7 +50075,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1714" t="n">
-        <v>5.12169647216797</v>
+        <v>5.12169694900513</v>
       </c>
       <c r="H1714" t="n">
         <v>1367400</v>
@@ -50104,7 +50104,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1715" t="n">
-        <v>5.02137899398804</v>
+        <v>5.02137851715088</v>
       </c>
       <c r="H1715" t="n">
         <v>2554508</v>
@@ -50191,7 +50191,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G1718" t="n">
-        <v>5.16547155380249</v>
+        <v>5.16547203063965</v>
       </c>
       <c r="H1718" t="n">
         <v>1115062</v>
@@ -50249,7 +50249,7 @@
         <v>5.57399988174438</v>
       </c>
       <c r="G1720" t="n">
-        <v>5.08339309692383</v>
+        <v>5.08339357376099</v>
       </c>
       <c r="H1720" t="n">
         <v>1066536</v>
@@ -50278,7 +50278,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1721" t="n">
-        <v>5.14905595779419</v>
+        <v>5.14905643463135</v>
       </c>
       <c r="H1721" t="n">
         <v>1309301</v>
@@ -50336,7 +50336,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1723" t="n">
-        <v>5.22931051254272</v>
+        <v>5.22931098937988</v>
       </c>
       <c r="H1723" t="n">
         <v>1073822</v>
@@ -50394,7 +50394,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1725" t="n">
-        <v>5.25484609603882</v>
+        <v>5.25484657287598</v>
       </c>
       <c r="H1725" t="n">
         <v>1815362</v>
@@ -50597,7 +50597,7 @@
         <v>5.75</v>
       </c>
       <c r="G1732" t="n">
-        <v>5.2439022064209</v>
+        <v>5.24390268325806</v>
       </c>
       <c r="H1732" t="n">
         <v>2383059</v>
@@ -50626,7 +50626,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1733" t="n">
-        <v>5.30774116516113</v>
+        <v>5.30774164199829</v>
       </c>
       <c r="H1733" t="n">
         <v>1419417</v>
@@ -50655,7 +50655,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1734" t="n">
-        <v>5.26578998565674</v>
+        <v>5.2657904624939</v>
       </c>
       <c r="H1734" t="n">
         <v>1263754</v>
@@ -50742,7 +50742,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1737" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1737" t="n">
         <v>2008071</v>
@@ -50771,7 +50771,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1738" t="n">
-        <v>4.97760343551636</v>
+        <v>4.97760391235352</v>
       </c>
       <c r="H1738" t="n">
         <v>2945125</v>
@@ -50829,7 +50829,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G1740" t="n">
-        <v>4.74960803985596</v>
+        <v>4.7496075630188</v>
       </c>
       <c r="H1740" t="n">
         <v>1995582</v>
@@ -50945,7 +50945,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G1744" t="n">
-        <v>4.78426313400269</v>
+        <v>4.78426265716553</v>
       </c>
       <c r="H1744" t="n">
         <v>872180</v>
@@ -51061,7 +51061,7 @@
         <v>5.38199996948242</v>
       </c>
       <c r="G1748" t="n">
-        <v>4.90829277038574</v>
+        <v>4.90829229354858</v>
       </c>
       <c r="H1748" t="n">
         <v>707574</v>
@@ -51119,7 +51119,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1750" t="n">
-        <v>4.94294834136963</v>
+        <v>4.94294786453247</v>
       </c>
       <c r="H1750" t="n">
         <v>1233465</v>
@@ -51206,7 +51206,7 @@
         <v>5.43200016021729</v>
       </c>
       <c r="G1753" t="n">
-        <v>4.95389175415039</v>
+        <v>4.95389223098755</v>
       </c>
       <c r="H1753" t="n">
         <v>598372</v>
@@ -51351,7 +51351,7 @@
         <v>5.52799987792969</v>
       </c>
       <c r="G1758" t="n">
-        <v>5.04144191741943</v>
+        <v>5.04144239425659</v>
       </c>
       <c r="H1758" t="n">
         <v>749729</v>
@@ -51409,7 +51409,7 @@
         <v>5.47800016403198</v>
       </c>
       <c r="G1760" t="n">
-        <v>4.99584341049194</v>
+        <v>4.99584293365479</v>
       </c>
       <c r="H1760" t="n">
         <v>1110795</v>
@@ -51612,7 +51612,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1767" t="n">
-        <v>4.96118783950806</v>
+        <v>4.9611873626709</v>
       </c>
       <c r="H1767" t="n">
         <v>871216</v>
@@ -51670,7 +51670,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G1769" t="n">
-        <v>4.92106056213379</v>
+        <v>4.92106008529663</v>
       </c>
       <c r="H1769" t="n">
         <v>1142507</v>
@@ -51902,7 +51902,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1777" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1777" t="n">
         <v>1639161</v>
@@ -51989,7 +51989,7 @@
         <v>5.21199989318848</v>
       </c>
       <c r="G1780" t="n">
-        <v>4.75325536727905</v>
+        <v>4.75325584411621</v>
       </c>
       <c r="H1780" t="n">
         <v>7817931</v>
@@ -52134,7 +52134,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G1785" t="n">
-        <v>4.8955249786377</v>
+        <v>4.89552450180054</v>
       </c>
       <c r="H1785" t="n">
         <v>1946243</v>
@@ -52308,7 +52308,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G1791" t="n">
-        <v>4.87546110153198</v>
+        <v>4.87546157836914</v>
       </c>
       <c r="H1791" t="n">
         <v>1464698</v>
@@ -52424,7 +52424,7 @@
         <v>5.24399995803833</v>
       </c>
       <c r="G1795" t="n">
-        <v>4.7824387550354</v>
+        <v>4.78243923187256</v>
       </c>
       <c r="H1795" t="n">
         <v>1922209</v>
@@ -52482,7 +52482,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1797" t="n">
-        <v>4.71677589416504</v>
+        <v>4.7167763710022</v>
       </c>
       <c r="H1797" t="n">
         <v>1952792</v>
@@ -52511,7 +52511,7 @@
         <v>5.15799999237061</v>
       </c>
       <c r="G1798" t="n">
-        <v>4.70400810241699</v>
+        <v>4.70400857925415</v>
       </c>
       <c r="H1798" t="n">
         <v>2608346</v>
@@ -52540,7 +52540,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1799" t="n">
-        <v>4.62010622024536</v>
+        <v>4.6201057434082</v>
       </c>
       <c r="H1799" t="n">
         <v>2142638</v>
@@ -52627,7 +52627,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1802" t="n">
-        <v>4.62010622024536</v>
+        <v>4.6201057434082</v>
       </c>
       <c r="H1802" t="n">
         <v>1304150</v>
@@ -52772,7 +52772,7 @@
         <v>5.10400009155273</v>
       </c>
       <c r="G1807" t="n">
-        <v>4.65476179122925</v>
+        <v>4.65476131439209</v>
       </c>
       <c r="H1807" t="n">
         <v>7182672</v>
@@ -52801,7 +52801,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1808" t="n">
-        <v>4.71677589416504</v>
+        <v>4.7167763710022</v>
       </c>
       <c r="H1808" t="n">
         <v>3272568</v>
@@ -52859,7 +52859,7 @@
         <v>4.96700000762939</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.52981996536255</v>
+        <v>4.52981948852539</v>
       </c>
       <c r="H1810" t="n">
         <v>3621056</v>
@@ -52888,7 +52888,7 @@
         <v>5.08199977874756</v>
       </c>
       <c r="G1811" t="n">
-        <v>4.63469743728638</v>
+        <v>4.63469791412354</v>
       </c>
       <c r="H1811" t="n">
         <v>2020220</v>
@@ -53004,7 +53004,7 @@
         <v>5.16599988937378</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.71130466461182</v>
+        <v>4.71130418777466</v>
       </c>
       <c r="H1815" t="n">
         <v>3075470</v>
@@ -53062,7 +53062,7 @@
         <v>5.17199993133545</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.71677589416504</v>
+        <v>4.7167763710022</v>
       </c>
       <c r="H1817" t="n">
         <v>1675292</v>
@@ -53207,7 +53207,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G1822" t="n">
-        <v>4.68212032318115</v>
+        <v>4.68212080001831</v>
       </c>
       <c r="H1822" t="n">
         <v>1423087</v>
@@ -53294,7 +53294,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G1825" t="n">
-        <v>4.78426313400269</v>
+        <v>4.78426265716553</v>
       </c>
       <c r="H1825" t="n">
         <v>2341827</v>
@@ -53352,7 +53352,7 @@
         <v>5.34600019454956</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.87546110153198</v>
+        <v>4.87546157836914</v>
       </c>
       <c r="H1827" t="n">
         <v>1570389</v>
@@ -53381,7 +53381,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G1828" t="n">
-        <v>4.92106056213379</v>
+        <v>4.92106008529663</v>
       </c>
       <c r="H1828" t="n">
         <v>1505172</v>
@@ -53555,7 +53555,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1834" t="n">
-        <v>5.02137899398804</v>
+        <v>5.02137851715088</v>
       </c>
       <c r="H1834" t="n">
         <v>2061632</v>
@@ -53584,7 +53584,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1835" t="n">
-        <v>5.04326677322388</v>
+        <v>5.04326629638672</v>
       </c>
       <c r="H1835" t="n">
         <v>1605046</v>
@@ -53671,7 +53671,7 @@
         <v>5.45800018310547</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.97760343551636</v>
+        <v>4.97760391235352</v>
       </c>
       <c r="H1838" t="n">
         <v>1222379</v>
@@ -53729,7 +53729,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.99219465255737</v>
+        <v>4.99219512939453</v>
       </c>
       <c r="H1840" t="n">
         <v>1067550</v>
@@ -53903,7 +53903,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1846" t="n">
-        <v>5.09068918228149</v>
+        <v>5.09068870544434</v>
       </c>
       <c r="H1846" t="n">
         <v>2122240</v>
@@ -53932,7 +53932,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1847" t="n">
-        <v>5.09616088867188</v>
+        <v>5.09616136550903</v>
       </c>
       <c r="H1847" t="n">
         <v>1601324</v>
@@ -53961,7 +53961,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1848" t="n">
-        <v>5.07062530517578</v>
+        <v>5.07062578201294</v>
       </c>
       <c r="H1848" t="n">
         <v>1113736</v>
@@ -53990,7 +53990,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1849" t="n">
-        <v>5.18006372451782</v>
+        <v>5.18006324768066</v>
       </c>
       <c r="H1849" t="n">
         <v>4393306</v>
@@ -54048,7 +54048,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1851" t="n">
-        <v>5.22931051254272</v>
+        <v>5.22931098937988</v>
       </c>
       <c r="H1851" t="n">
         <v>2082674</v>
@@ -54135,7 +54135,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1854" t="n">
-        <v>5.23843050003052</v>
+        <v>5.23843002319336</v>
       </c>
       <c r="H1854" t="n">
         <v>1638683</v>
@@ -54193,7 +54193,7 @@
         <v>5.82800006866455</v>
       </c>
       <c r="G1856" t="n">
-        <v>5.3150372505188</v>
+        <v>5.31503677368164</v>
       </c>
       <c r="H1856" t="n">
         <v>2461456</v>
@@ -54222,7 +54222,7 @@
         <v>5.85200023651123</v>
       </c>
       <c r="G1857" t="n">
-        <v>5.33692455291748</v>
+        <v>5.33692502975464</v>
       </c>
       <c r="H1857" t="n">
         <v>1917532</v>
@@ -54309,7 +54309,7 @@
         <v>5.78200006484985</v>
       </c>
       <c r="G1860" t="n">
-        <v>5.27308559417725</v>
+        <v>5.2730860710144</v>
       </c>
       <c r="H1860" t="n">
         <v>1153715</v>
@@ -54396,7 +54396,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1863" t="n">
-        <v>5.13264036178589</v>
+        <v>5.13263988494873</v>
       </c>
       <c r="H1863" t="n">
         <v>6863661</v>
@@ -54425,7 +54425,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1864" t="n">
-        <v>5.10710477828979</v>
+        <v>5.10710525512695</v>
       </c>
       <c r="H1864" t="n">
         <v>1749750</v>
@@ -54454,7 +54454,7 @@
         <v>5.53800010681152</v>
       </c>
       <c r="G1865" t="n">
-        <v>5.05056238174438</v>
+        <v>5.05056190490723</v>
       </c>
       <c r="H1865" t="n">
         <v>1856112</v>
@@ -54483,7 +54483,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1866" t="n">
-        <v>5.10710477828979</v>
+        <v>5.10710525512695</v>
       </c>
       <c r="H1866" t="n">
         <v>1134560</v>
@@ -54541,7 +54541,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1868" t="n">
-        <v>5.10710477828979</v>
+        <v>5.10710525512695</v>
       </c>
       <c r="H1868" t="n">
         <v>1623973</v>
@@ -54570,7 +54570,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1869" t="n">
-        <v>5.14358377456665</v>
+        <v>5.14358425140381</v>
       </c>
       <c r="H1869" t="n">
         <v>1888128</v>
@@ -54628,7 +54628,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G1871" t="n">
-        <v>5.24572658538818</v>
+        <v>5.24572610855103</v>
       </c>
       <c r="H1871" t="n">
         <v>2824097</v>
@@ -54773,7 +54773,7 @@
         <v>5.72800016403198</v>
       </c>
       <c r="G1876" t="n">
-        <v>5.2238392829895</v>
+        <v>5.22383880615234</v>
       </c>
       <c r="H1876" t="n">
         <v>1322234</v>
@@ -54889,7 +54889,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1880" t="n">
-        <v>5.30774116516113</v>
+        <v>5.30774164199829</v>
       </c>
       <c r="H1880" t="n">
         <v>1628098</v>
@@ -54947,7 +54947,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G1882" t="n">
-        <v>5.50290536880493</v>
+        <v>5.50290584564209</v>
       </c>
       <c r="H1882" t="n">
         <v>3694253</v>
@@ -55005,7 +55005,7 @@
         <v>5.75</v>
       </c>
       <c r="G1884" t="n">
-        <v>5.2439022064209</v>
+        <v>5.24390268325806</v>
       </c>
       <c r="H1884" t="n">
         <v>4531783</v>
@@ -55063,7 +55063,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1886" t="n">
-        <v>5.30774116516113</v>
+        <v>5.30774164199829</v>
       </c>
       <c r="H1886" t="n">
         <v>3842206</v>
@@ -55092,7 +55092,7 @@
         <v>5.64599990844727</v>
       </c>
       <c r="G1887" t="n">
-        <v>5.14905595779419</v>
+        <v>5.14905643463135</v>
       </c>
       <c r="H1887" t="n">
         <v>4539598</v>
@@ -55121,7 +55121,7 @@
         <v>5.66599988937378</v>
       </c>
       <c r="G1888" t="n">
-        <v>5.16729593276978</v>
+        <v>5.16729545593262</v>
       </c>
       <c r="H1888" t="n">
         <v>3363922</v>
@@ -55150,7 +55150,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1889" t="n">
-        <v>5.12169647216797</v>
+        <v>5.12169694900513</v>
       </c>
       <c r="H1889" t="n">
         <v>3102908</v>
@@ -55208,7 +55208,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1891" t="n">
-        <v>5.25484609603882</v>
+        <v>5.25484657287598</v>
       </c>
       <c r="H1891" t="n">
         <v>2244420</v>
@@ -55237,7 +55237,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G1892" t="n">
-        <v>5.40258693695068</v>
+        <v>5.40258741378784</v>
       </c>
       <c r="H1892" t="n">
         <v>2940061</v>
@@ -55295,7 +55295,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1894" t="n">
-        <v>5.40441179275513</v>
+        <v>5.40441131591797</v>
       </c>
       <c r="H1894" t="n">
         <v>1732424</v>
@@ -55324,7 +55324,7 @@
         <v>5.92600011825562</v>
       </c>
       <c r="G1895" t="n">
-        <v>5.40441179275513</v>
+        <v>5.40441131591797</v>
       </c>
       <c r="H1895" t="n">
         <v>1130769</v>
@@ -55382,7 +55382,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1897" t="n">
-        <v>5.36246061325073</v>
+        <v>5.36246013641357</v>
       </c>
       <c r="H1897" t="n">
         <v>3402608</v>
@@ -55440,7 +55440,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G1899" t="n">
-        <v>5.24572658538818</v>
+        <v>5.24572610855103</v>
       </c>
       <c r="H1899" t="n">
         <v>5097268</v>
@@ -55469,7 +55469,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1900" t="n">
-        <v>5.09616088867188</v>
+        <v>5.09616136550903</v>
       </c>
       <c r="H1900" t="n">
         <v>4791696</v>
@@ -55556,7 +55556,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.99219465255737</v>
+        <v>4.99219512939453</v>
       </c>
       <c r="H1903" t="n">
         <v>2656525</v>
@@ -55614,7 +55614,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G1905" t="n">
-        <v>4.97577905654907</v>
+        <v>4.97577953338623</v>
       </c>
       <c r="H1905" t="n">
         <v>1974649</v>
@@ -55643,7 +55643,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.84262990951538</v>
+        <v>4.84262943267822</v>
       </c>
       <c r="H1906" t="n">
         <v>2382236</v>
@@ -55788,7 +55788,7 @@
         <v>4.80299997329712</v>
       </c>
       <c r="G1911" t="n">
-        <v>4.38025426864624</v>
+        <v>4.3802547454834</v>
       </c>
       <c r="H1911" t="n">
         <v>3237721</v>
@@ -55846,7 +55846,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G1913" t="n">
-        <v>4.50793218612671</v>
+        <v>4.50793170928955</v>
       </c>
       <c r="H1913" t="n">
         <v>1902362</v>
@@ -55904,7 +55904,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.56903505325317</v>
+        <v>4.56903553009033</v>
       </c>
       <c r="H1915" t="n">
         <v>1697802</v>
@@ -55933,7 +55933,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G1916" t="n">
-        <v>4.58909893035889</v>
+        <v>4.58909845352173</v>
       </c>
       <c r="H1916" t="n">
         <v>1293197</v>
@@ -56078,7 +56078,7 @@
         <v>5.36399984359741</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.89187717437744</v>
+        <v>4.89187669754028</v>
       </c>
       <c r="H1921" t="n">
         <v>2120977</v>
@@ -56223,7 +56223,7 @@
         <v>5.53599977493286</v>
       </c>
       <c r="G1926" t="n">
-        <v>5.04873752593994</v>
+        <v>5.0487380027771</v>
       </c>
       <c r="H1926" t="n">
         <v>1676053</v>
@@ -56339,7 +56339,7 @@
         <v>5.92399978637695</v>
       </c>
       <c r="G1930" t="n">
-        <v>5.40258693695068</v>
+        <v>5.40258741378784</v>
       </c>
       <c r="H1930" t="n">
         <v>2688995</v>
@@ -56455,7 +56455,7 @@
         <v>5.91800022125244</v>
       </c>
       <c r="G1934" t="n">
-        <v>5.39711570739746</v>
+        <v>5.39711618423462</v>
       </c>
       <c r="H1934" t="n">
         <v>2801870</v>
@@ -56484,7 +56484,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1935" t="n">
-        <v>5.45365810394287</v>
+        <v>5.45365858078003</v>
       </c>
       <c r="H1935" t="n">
         <v>1677316</v>
@@ -56513,7 +56513,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G1936" t="n">
-        <v>5.57403993606567</v>
+        <v>5.57404041290283</v>
       </c>
       <c r="H1936" t="n">
         <v>3612638</v>
@@ -56542,7 +56542,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1937" t="n">
-        <v>5.62693500518799</v>
+        <v>5.62693548202515</v>
       </c>
       <c r="H1937" t="n">
         <v>3227462</v>
@@ -56600,7 +56600,7 @@
         <v>6.13800001144409</v>
       </c>
       <c r="G1939" t="n">
-        <v>5.59775161743164</v>
+        <v>5.5977520942688</v>
       </c>
       <c r="H1939" t="n">
         <v>6063161</v>
@@ -56716,7 +56716,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1943" t="n">
-        <v>5.73637342453003</v>
+        <v>5.73637294769287</v>
       </c>
       <c r="H1943" t="n">
         <v>3058422</v>
@@ -56803,7 +56803,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1946" t="n">
-        <v>5.69077348709106</v>
+        <v>5.69077396392822</v>
       </c>
       <c r="H1946" t="n">
         <v>1535277</v>
@@ -56977,7 +56977,7 @@
         <v>6.18599987030029</v>
       </c>
       <c r="G1952" t="n">
-        <v>5.64152717590332</v>
+        <v>5.64152669906616</v>
       </c>
       <c r="H1952" t="n">
         <v>2276866</v>
@@ -57180,7 +57180,7 @@
         <v>6.06599998474121</v>
       </c>
       <c r="G1959" t="n">
-        <v>5.53208875656128</v>
+        <v>5.53208923339844</v>
       </c>
       <c r="H1959" t="n">
         <v>2753548</v>
@@ -67017,6 +67017,35 @@
         <v>1226000</v>
       </c>
       <c r="I2298" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2299" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2299" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="D2299" t="n">
+        <v>6.65000009536743</v>
+      </c>
+      <c r="E2299" t="n">
+        <v>6.55499982833862</v>
+      </c>
+      <c r="F2299" t="n">
+        <v>6.6399998664856</v>
+      </c>
+      <c r="G2299" t="n">
+        <v>6.6399998664856</v>
+      </c>
+      <c r="H2299" t="n">
+        <v>1620424</v>
+      </c>
+      <c r="I2299" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PIRC.MI.xlsx
+++ b/data/PIRC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G2" t="n">
-        <v>5.00744915008545</v>
+        <v>5.00745010375977</v>
       </c>
       <c r="H2" t="n">
         <v>86898069</v>
@@ -456,7 +456,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G3" t="n">
-        <v>5.19319772720337</v>
+        <v>5.19319725036621</v>
       </c>
       <c r="H3" t="n">
         <v>24993644</v>
@@ -485,7 +485,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G4" t="n">
-        <v>5.18545770645142</v>
+        <v>5.18545818328857</v>
       </c>
       <c r="H4" t="n">
         <v>10381356</v>
@@ -514,7 +514,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G5" t="n">
-        <v>5.07710456848145</v>
+        <v>5.0771050453186</v>
       </c>
       <c r="H5" t="n">
         <v>5160664</v>
@@ -543,7 +543,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G6" t="n">
-        <v>5.10419321060181</v>
+        <v>5.10419273376465</v>
       </c>
       <c r="H6" t="n">
         <v>11557809</v>
@@ -572,7 +572,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G7" t="n">
-        <v>5.11193227767944</v>
+        <v>5.1119327545166</v>
       </c>
       <c r="H7" t="n">
         <v>1858638</v>
@@ -630,7 +630,7 @@
         <v>6.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.03066778182983</v>
+        <v>5.03066873550415</v>
       </c>
       <c r="H9" t="n">
         <v>1559429</v>
@@ -688,7 +688,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G11" t="n">
-        <v>4.99970960617065</v>
+        <v>4.99971008300781</v>
       </c>
       <c r="H11" t="n">
         <v>2476184</v>
@@ -833,7 +833,7 @@
         <v>6.5</v>
       </c>
       <c r="G16" t="n">
-        <v>5.03066778182983</v>
+        <v>5.03066873550415</v>
       </c>
       <c r="H16" t="n">
         <v>1266116</v>
@@ -862,7 +862,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G17" t="n">
-        <v>5.02292823791504</v>
+        <v>5.0229287147522</v>
       </c>
       <c r="H17" t="n">
         <v>941108</v>
@@ -920,7 +920,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G19" t="n">
-        <v>5.10806274414062</v>
+        <v>5.10806226730347</v>
       </c>
       <c r="H19" t="n">
         <v>2506280</v>
@@ -949,7 +949,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G20" t="n">
-        <v>5.11580276489258</v>
+        <v>5.11580228805542</v>
       </c>
       <c r="H20" t="n">
         <v>778081</v>
@@ -1007,7 +1007,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G22" t="n">
-        <v>5.40990257263184</v>
+        <v>5.40990304946899</v>
       </c>
       <c r="H22" t="n">
         <v>3306513</v>
@@ -1036,7 +1036,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G23" t="n">
-        <v>5.37507581710815</v>
+        <v>5.37507629394531</v>
       </c>
       <c r="H23" t="n">
         <v>4122333</v>
@@ -1065,7 +1065,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G24" t="n">
-        <v>5.3325080871582</v>
+        <v>5.33250761032104</v>
       </c>
       <c r="H24" t="n">
         <v>2075041</v>
@@ -1152,7 +1152,7 @@
         <v>6.93499994277954</v>
       </c>
       <c r="G27" t="n">
-        <v>5.36733531951904</v>
+        <v>5.3673357963562</v>
       </c>
       <c r="H27" t="n">
         <v>1969234</v>
@@ -1210,7 +1210,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G29" t="n">
-        <v>5.23189544677734</v>
+        <v>5.23189496994019</v>
       </c>
       <c r="H29" t="n">
         <v>1893614</v>
@@ -1239,7 +1239,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G30" t="n">
-        <v>5.29381036758423</v>
+        <v>5.29381084442139</v>
       </c>
       <c r="H30" t="n">
         <v>1171585</v>
@@ -1268,7 +1268,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G31" t="n">
-        <v>5.305419921875</v>
+        <v>5.30541944503784</v>
       </c>
       <c r="H31" t="n">
         <v>842590</v>
@@ -1355,7 +1355,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G34" t="n">
-        <v>5.29381036758423</v>
+        <v>5.29381084442139</v>
       </c>
       <c r="H34" t="n">
         <v>764504</v>
@@ -1471,7 +1471,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G38" t="n">
-        <v>5.45247030258179</v>
+        <v>5.45246982574463</v>
       </c>
       <c r="H38" t="n">
         <v>874776</v>
@@ -1558,7 +1558,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>5.47955799102783</v>
+        <v>5.47955846786499</v>
       </c>
       <c r="H41" t="n">
         <v>1316822</v>
@@ -1587,7 +1587,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G42" t="n">
-        <v>5.46407890319824</v>
+        <v>5.4640793800354</v>
       </c>
       <c r="H42" t="n">
         <v>3264384</v>
@@ -1703,7 +1703,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G46" t="n">
-        <v>5.39442348480225</v>
+        <v>5.3944239616394</v>
       </c>
       <c r="H46" t="n">
         <v>1348979</v>
@@ -1761,7 +1761,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G48" t="n">
-        <v>5.53760433197021</v>
+        <v>5.53760480880737</v>
       </c>
       <c r="H48" t="n">
         <v>1804427</v>
@@ -1790,7 +1790,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G49" t="n">
-        <v>5.56469297409058</v>
+        <v>5.56469249725342</v>
       </c>
       <c r="H49" t="n">
         <v>1856608</v>
@@ -1819,7 +1819,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G50" t="n">
-        <v>5.61886978149414</v>
+        <v>5.61886882781982</v>
       </c>
       <c r="H50" t="n">
         <v>1356581</v>
@@ -1848,7 +1848,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G51" t="n">
-        <v>5.58791017532349</v>
+        <v>5.58791160583496</v>
       </c>
       <c r="H51" t="n">
         <v>1553449</v>
@@ -1877,7 +1877,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>5.62273836135864</v>
+        <v>5.6227388381958</v>
       </c>
       <c r="H52" t="n">
         <v>2277506</v>
@@ -1906,7 +1906,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G53" t="n">
-        <v>5.59178066253662</v>
+        <v>5.59178113937378</v>
       </c>
       <c r="H53" t="n">
         <v>2419795</v>
@@ -2022,7 +2022,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>5.47955799102783</v>
+        <v>5.47955846786499</v>
       </c>
       <c r="H57" t="n">
         <v>1498021</v>
@@ -2196,7 +2196,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G63" t="n">
-        <v>5.68078565597534</v>
+        <v>5.68078517913818</v>
       </c>
       <c r="H63" t="n">
         <v>1436706</v>
@@ -2225,7 +2225,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>5.73496150970459</v>
+        <v>5.73496198654175</v>
       </c>
       <c r="H64" t="n">
         <v>1747691</v>
@@ -2283,7 +2283,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G66" t="n">
-        <v>5.99036455154419</v>
+        <v>5.99036407470703</v>
       </c>
       <c r="H66" t="n">
         <v>3411604</v>
@@ -2341,7 +2341,7 @@
         <v>7.94500017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>6.14902448654175</v>
+        <v>6.14902400970459</v>
       </c>
       <c r="H68" t="n">
         <v>2619744</v>
@@ -2370,7 +2370,7 @@
         <v>7.75</v>
       </c>
       <c r="G69" t="n">
-        <v>5.99810457229614</v>
+        <v>5.99810409545898</v>
       </c>
       <c r="H69" t="n">
         <v>2947971</v>
@@ -2399,7 +2399,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G70" t="n">
-        <v>6.09871768951416</v>
+        <v>6.098717212677</v>
       </c>
       <c r="H70" t="n">
         <v>2140774</v>
@@ -2428,7 +2428,7 @@
         <v>7.86499977111816</v>
       </c>
       <c r="G71" t="n">
-        <v>6.08710813522339</v>
+        <v>6.08710861206055</v>
       </c>
       <c r="H71" t="n">
         <v>1712288</v>
@@ -2544,7 +2544,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>6.03680229187012</v>
+        <v>6.0368013381958</v>
       </c>
       <c r="H75" t="n">
         <v>1814794</v>
@@ -2660,7 +2660,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G79" t="n">
-        <v>5.97101593017578</v>
+        <v>5.97101640701294</v>
       </c>
       <c r="H79" t="n">
         <v>1358430</v>
@@ -2689,7 +2689,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>5.94392776489258</v>
+        <v>5.94392824172974</v>
       </c>
       <c r="H80" t="n">
         <v>1674841</v>
@@ -2776,7 +2776,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G83" t="n">
-        <v>6.00584411621094</v>
+        <v>6.00584363937378</v>
       </c>
       <c r="H83" t="n">
         <v>1192678</v>
@@ -2805,7 +2805,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G84" t="n">
-        <v>6.00584411621094</v>
+        <v>6.00584363937378</v>
       </c>
       <c r="H84" t="n">
         <v>1034704</v>
@@ -2834,7 +2834,7 @@
         <v>7.76399993896484</v>
       </c>
       <c r="G85" t="n">
-        <v>6.00893974304199</v>
+        <v>6.00893926620483</v>
       </c>
       <c r="H85" t="n">
         <v>1196110</v>
@@ -2921,7 +2921,7 @@
         <v>7.28599977493286</v>
       </c>
       <c r="G88" t="n">
-        <v>5.63899183273315</v>
+        <v>5.638991355896</v>
       </c>
       <c r="H88" t="n">
         <v>3950924</v>
@@ -2979,7 +2979,7 @@
         <v>7.32800006866455</v>
       </c>
       <c r="G90" t="n">
-        <v>5.67149829864502</v>
+        <v>5.67149782180786</v>
       </c>
       <c r="H90" t="n">
         <v>2134999</v>
@@ -3008,7 +3008,7 @@
         <v>7.23799991607666</v>
       </c>
       <c r="G91" t="n">
-        <v>5.60184240341187</v>
+        <v>5.60184192657471</v>
       </c>
       <c r="H91" t="n">
         <v>2095551</v>
@@ -3124,7 +3124,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G95" t="n">
-        <v>5.78139877319336</v>
+        <v>5.7813982963562</v>
       </c>
       <c r="H95" t="n">
         <v>1798735</v>
@@ -3153,7 +3153,7 @@
         <v>7.67600011825562</v>
       </c>
       <c r="G96" t="n">
-        <v>5.94083166122437</v>
+        <v>5.94083261489868</v>
       </c>
       <c r="H96" t="n">
         <v>3982258</v>
@@ -3182,7 +3182,7 @@
         <v>7.52199983596802</v>
       </c>
       <c r="G97" t="n">
-        <v>5.8216438293457</v>
+        <v>5.82164335250854</v>
       </c>
       <c r="H97" t="n">
         <v>766003</v>
@@ -3211,7 +3211,7 @@
         <v>7.41599988937378</v>
       </c>
       <c r="G98" t="n">
-        <v>5.73960447311401</v>
+        <v>5.73960542678833</v>
       </c>
       <c r="H98" t="n">
         <v>1049117</v>
@@ -3240,7 +3240,7 @@
         <v>7.4060001373291</v>
       </c>
       <c r="G99" t="n">
-        <v>5.73186540603638</v>
+        <v>5.73186588287354</v>
       </c>
       <c r="H99" t="n">
         <v>1618284</v>
@@ -3385,7 +3385,7 @@
         <v>7.28800010681152</v>
       </c>
       <c r="G104" t="n">
-        <v>5.64053964614868</v>
+        <v>5.64053916931152</v>
       </c>
       <c r="H104" t="n">
         <v>1988206</v>
@@ -3472,7 +3472,7 @@
         <v>6.89200019836426</v>
       </c>
       <c r="G107" t="n">
-        <v>5.33405590057373</v>
+        <v>5.33405542373657</v>
       </c>
       <c r="H107" t="n">
         <v>2889957</v>
@@ -3501,7 +3501,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G108" t="n">
-        <v>5.48574924468994</v>
+        <v>5.4857497215271</v>
       </c>
       <c r="H108" t="n">
         <v>2296418</v>
@@ -3530,7 +3530,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G109" t="n">
-        <v>5.56159639358521</v>
+        <v>5.56159687042236</v>
       </c>
       <c r="H109" t="n">
         <v>2743718</v>
@@ -3588,7 +3588,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>5.62660884857178</v>
+        <v>5.62660837173462</v>
       </c>
       <c r="H111" t="n">
         <v>1667359</v>
@@ -3733,7 +3733,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>5.58017206192017</v>
+        <v>5.58017158508301</v>
       </c>
       <c r="H116" t="n">
         <v>3945713</v>
@@ -3762,7 +3762,7 @@
         <v>7.08199977874756</v>
       </c>
       <c r="G117" t="n">
-        <v>5.48110675811768</v>
+        <v>5.48110580444336</v>
       </c>
       <c r="H117" t="n">
         <v>1463476</v>
@@ -3791,7 +3791,7 @@
         <v>7.19799995422363</v>
       </c>
       <c r="G118" t="n">
-        <v>5.57088375091553</v>
+        <v>5.57088470458984</v>
       </c>
       <c r="H118" t="n">
         <v>1960942</v>
@@ -3820,7 +3820,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G119" t="n">
-        <v>5.61886978149414</v>
+        <v>5.61886882781982</v>
       </c>
       <c r="H119" t="n">
         <v>1697131</v>
@@ -3878,7 +3878,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G121" t="n">
-        <v>5.46407890319824</v>
+        <v>5.4640793800354</v>
       </c>
       <c r="H121" t="n">
         <v>1962224</v>
@@ -3907,7 +3907,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>5.4021635055542</v>
+        <v>5.40216398239136</v>
       </c>
       <c r="H122" t="n">
         <v>1605771</v>
@@ -4023,7 +4023,7 @@
         <v>7.16800022125244</v>
       </c>
       <c r="G126" t="n">
-        <v>5.5476655960083</v>
+        <v>5.54766607284546</v>
       </c>
       <c r="H126" t="n">
         <v>1469569</v>
@@ -4081,7 +4081,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G128" t="n">
-        <v>5.5554051399231</v>
+        <v>5.55540561676025</v>
       </c>
       <c r="H128" t="n">
         <v>2509350</v>
@@ -4110,7 +4110,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>5.54147434234619</v>
+        <v>5.54147386550903</v>
       </c>
       <c r="H129" t="n">
         <v>1457912</v>
@@ -4139,7 +4139,7 @@
         <v>7.11199998855591</v>
       </c>
       <c r="G130" t="n">
-        <v>5.50432538986206</v>
+        <v>5.50432443618774</v>
       </c>
       <c r="H130" t="n">
         <v>1790452</v>
@@ -4168,7 +4168,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G131" t="n">
-        <v>5.56159639358521</v>
+        <v>5.56159687042236</v>
       </c>
       <c r="H131" t="n">
         <v>1483323</v>
@@ -4255,7 +4255,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G134" t="n">
-        <v>5.61886978149414</v>
+        <v>5.61886882781982</v>
       </c>
       <c r="H134" t="n">
         <v>3548151</v>
@@ -4342,7 +4342,7 @@
         <v>7.02199983596802</v>
       </c>
       <c r="G137" t="n">
-        <v>5.43466997146606</v>
+        <v>5.43466854095459</v>
       </c>
       <c r="H137" t="n">
         <v>8167240</v>
@@ -4371,7 +4371,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G138" t="n">
-        <v>5.44086122512817</v>
+        <v>5.44086074829102</v>
       </c>
       <c r="H138" t="n">
         <v>4304794</v>
@@ -4429,7 +4429,7 @@
         <v>7.08400011062622</v>
       </c>
       <c r="G140" t="n">
-        <v>5.48265361785889</v>
+        <v>5.48265409469604</v>
       </c>
       <c r="H140" t="n">
         <v>1915810</v>
@@ -4487,7 +4487,7 @@
         <v>7.13600015640259</v>
       </c>
       <c r="G142" t="n">
-        <v>5.52290010452271</v>
+        <v>5.52289962768555</v>
       </c>
       <c r="H142" t="n">
         <v>3308006</v>
@@ -4574,7 +4574,7 @@
         <v>7.2039999961853</v>
       </c>
       <c r="G145" t="n">
-        <v>5.57552814483643</v>
+        <v>5.57552862167358</v>
       </c>
       <c r="H145" t="n">
         <v>1195513</v>
@@ -4632,7 +4632,7 @@
         <v>7.28200006484985</v>
       </c>
       <c r="G147" t="n">
-        <v>5.6358962059021</v>
+        <v>5.63589572906494</v>
       </c>
       <c r="H147" t="n">
         <v>1337297</v>
@@ -4661,7 +4661,7 @@
         <v>7.28599977493286</v>
       </c>
       <c r="G148" t="n">
-        <v>5.63899183273315</v>
+        <v>5.638991355896</v>
       </c>
       <c r="H148" t="n">
         <v>2206570</v>
@@ -4690,7 +4690,7 @@
         <v>7.32800006866455</v>
       </c>
       <c r="G149" t="n">
-        <v>5.67149829864502</v>
+        <v>5.67149782180786</v>
       </c>
       <c r="H149" t="n">
         <v>933654</v>
@@ -4719,7 +4719,7 @@
         <v>7.26800012588501</v>
       </c>
       <c r="G150" t="n">
-        <v>5.62506055831909</v>
+        <v>5.62506103515625</v>
       </c>
       <c r="H150" t="n">
         <v>2888493</v>
@@ -4777,7 +4777,7 @@
         <v>7.01200008392334</v>
       </c>
       <c r="G152" t="n">
-        <v>5.42693042755127</v>
+        <v>5.42692995071411</v>
       </c>
       <c r="H152" t="n">
         <v>2957840</v>
@@ -4806,7 +4806,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G153" t="n">
-        <v>5.38823223114014</v>
+        <v>5.38823270797729</v>
       </c>
       <c r="H153" t="n">
         <v>3075765</v>
@@ -4864,7 +4864,7 @@
         <v>7.4539999961853</v>
       </c>
       <c r="G155" t="n">
-        <v>5.76901578903198</v>
+        <v>5.76901483535767</v>
       </c>
       <c r="H155" t="n">
         <v>12483969</v>
@@ -4893,7 +4893,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G156" t="n">
-        <v>5.73496150970459</v>
+        <v>5.73496198654175</v>
       </c>
       <c r="H156" t="n">
         <v>6137151</v>
@@ -4922,7 +4922,7 @@
         <v>7.5479998588562</v>
       </c>
       <c r="G157" t="n">
-        <v>5.84176683425903</v>
+        <v>5.84176635742188</v>
       </c>
       <c r="H157" t="n">
         <v>4087859</v>
@@ -4980,7 +4980,7 @@
         <v>7.67799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>5.94237947463989</v>
+        <v>5.94238042831421</v>
       </c>
       <c r="H159" t="n">
         <v>2586916</v>
@@ -5009,7 +5009,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>5.89749050140381</v>
+        <v>5.89749097824097</v>
       </c>
       <c r="H160" t="n">
         <v>3125732</v>
@@ -5038,7 +5038,7 @@
         <v>7.41599988937378</v>
       </c>
       <c r="G161" t="n">
-        <v>5.73960447311401</v>
+        <v>5.73960542678833</v>
       </c>
       <c r="H161" t="n">
         <v>2822860</v>
@@ -5067,7 +5067,7 @@
         <v>7.28599977493286</v>
       </c>
       <c r="G162" t="n">
-        <v>5.63899183273315</v>
+        <v>5.638991355896</v>
       </c>
       <c r="H162" t="n">
         <v>3232347</v>
@@ -5154,7 +5154,7 @@
         <v>7.20800018310547</v>
       </c>
       <c r="G165" t="n">
-        <v>5.57862424850464</v>
+        <v>5.57862377166748</v>
       </c>
       <c r="H165" t="n">
         <v>5358633</v>
@@ -5212,7 +5212,7 @@
         <v>7.31799983978271</v>
       </c>
       <c r="G167" t="n">
-        <v>5.66375827789307</v>
+        <v>5.66375732421875</v>
       </c>
       <c r="H167" t="n">
         <v>43240003</v>
@@ -5241,7 +5241,7 @@
         <v>7.32800006866455</v>
       </c>
       <c r="G168" t="n">
-        <v>5.67149829864502</v>
+        <v>5.67149782180786</v>
       </c>
       <c r="H168" t="n">
         <v>2311280</v>
@@ -5270,7 +5270,7 @@
         <v>7.36199998855591</v>
       </c>
       <c r="G169" t="n">
-        <v>5.69781112670898</v>
+        <v>5.69781255722046</v>
       </c>
       <c r="H169" t="n">
         <v>2575130</v>
@@ -5299,7 +5299,7 @@
         <v>7.47599983215332</v>
       </c>
       <c r="G170" t="n">
-        <v>5.78604173660278</v>
+        <v>5.78604221343994</v>
       </c>
       <c r="H170" t="n">
         <v>4178875</v>
@@ -5444,7 +5444,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>5.77365827560425</v>
+        <v>5.77365875244141</v>
       </c>
       <c r="H175" t="n">
         <v>1681767</v>
@@ -5647,7 +5647,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G182" t="n">
-        <v>5.60339021682739</v>
+        <v>5.60338926315308</v>
       </c>
       <c r="H182" t="n">
         <v>2048172</v>
@@ -5676,7 +5676,7 @@
         <v>7.35599994659424</v>
       </c>
       <c r="G183" t="n">
-        <v>5.69316864013672</v>
+        <v>5.69316816329956</v>
       </c>
       <c r="H183" t="n">
         <v>1521415</v>
@@ -5763,7 +5763,7 @@
         <v>7.29199981689453</v>
       </c>
       <c r="G186" t="n">
-        <v>5.64363479614258</v>
+        <v>5.64363527297974</v>
       </c>
       <c r="H186" t="n">
         <v>2057580</v>
@@ -5821,7 +5821,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G188" t="n">
-        <v>5.53528261184692</v>
+        <v>5.53528308868408</v>
       </c>
       <c r="H188" t="n">
         <v>1687495</v>
@@ -5850,7 +5850,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G189" t="n">
-        <v>5.53528261184692</v>
+        <v>5.53528308868408</v>
       </c>
       <c r="H189" t="n">
         <v>2030021</v>
@@ -5879,7 +5879,7 @@
         <v>7.24200010299683</v>
       </c>
       <c r="G190" t="n">
-        <v>5.60493850708008</v>
+        <v>5.60493803024292</v>
       </c>
       <c r="H190" t="n">
         <v>1380536</v>
@@ -5908,7 +5908,7 @@
         <v>7.17799997329712</v>
       </c>
       <c r="G191" t="n">
-        <v>5.5554051399231</v>
+        <v>5.55540561676025</v>
       </c>
       <c r="H191" t="n">
         <v>1748330</v>
@@ -5937,7 +5937,7 @@
         <v>7.2960000038147</v>
       </c>
       <c r="G192" t="n">
-        <v>5.64673137664795</v>
+        <v>5.64673089981079</v>
       </c>
       <c r="H192" t="n">
         <v>2442319</v>
@@ -5966,7 +5966,7 @@
         <v>7.13600015640259</v>
       </c>
       <c r="G193" t="n">
-        <v>5.52290010452271</v>
+        <v>5.52289962768555</v>
       </c>
       <c r="H193" t="n">
         <v>1880138</v>
@@ -5995,7 +5995,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G194" t="n">
-        <v>5.56469297409058</v>
+        <v>5.56469249725342</v>
       </c>
       <c r="H194" t="n">
         <v>2271355</v>
@@ -6024,7 +6024,7 @@
         <v>7.15799999237061</v>
       </c>
       <c r="G195" t="n">
-        <v>5.53992605209351</v>
+        <v>5.53992652893066</v>
       </c>
       <c r="H195" t="n">
         <v>2685820</v>
@@ -6169,7 +6169,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>5.47955799102783</v>
+        <v>5.47955846786499</v>
       </c>
       <c r="H200" t="n">
         <v>1257767</v>
@@ -6198,7 +6198,7 @@
         <v>7.0460000038147</v>
       </c>
       <c r="G201" t="n">
-        <v>5.45324468612671</v>
+        <v>5.45324373245239</v>
       </c>
       <c r="H201" t="n">
         <v>1269104</v>
@@ -6314,7 +6314,7 @@
         <v>7.13399982452393</v>
       </c>
       <c r="G205" t="n">
-        <v>5.5213508605957</v>
+        <v>5.52135133743286</v>
       </c>
       <c r="H205" t="n">
         <v>1601027</v>
@@ -6372,7 +6372,7 @@
         <v>7.44600009918213</v>
       </c>
       <c r="G207" t="n">
-        <v>5.76282405853271</v>
+        <v>5.76282358169556</v>
       </c>
       <c r="H207" t="n">
         <v>2963238</v>
@@ -6401,7 +6401,7 @@
         <v>7.46600008010864</v>
       </c>
       <c r="G208" t="n">
-        <v>5.77830266952515</v>
+        <v>5.7783031463623</v>
       </c>
       <c r="H208" t="n">
         <v>1423117</v>
@@ -6430,7 +6430,7 @@
         <v>7.52199983596802</v>
       </c>
       <c r="G209" t="n">
-        <v>5.8216438293457</v>
+        <v>5.82164335250854</v>
       </c>
       <c r="H209" t="n">
         <v>1510800</v>
@@ -6459,7 +6459,7 @@
         <v>7.47200012207031</v>
       </c>
       <c r="G210" t="n">
-        <v>5.78294610977173</v>
+        <v>5.78294658660889</v>
       </c>
       <c r="H210" t="n">
         <v>1742076</v>
@@ -6517,7 +6517,7 @@
         <v>7.19799995422363</v>
       </c>
       <c r="G212" t="n">
-        <v>5.57088375091553</v>
+        <v>5.57088470458984</v>
       </c>
       <c r="H212" t="n">
         <v>2297120</v>
@@ -6546,7 +6546,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G213" t="n">
-        <v>5.51825618743896</v>
+        <v>5.51825571060181</v>
       </c>
       <c r="H213" t="n">
         <v>1073404</v>
@@ -6575,7 +6575,7 @@
         <v>7.20800018310547</v>
       </c>
       <c r="G214" t="n">
-        <v>5.57862424850464</v>
+        <v>5.57862377166748</v>
       </c>
       <c r="H214" t="n">
         <v>1044217</v>
@@ -6604,7 +6604,7 @@
         <v>7.48799991607666</v>
       </c>
       <c r="G215" t="n">
-        <v>5.79532957077026</v>
+        <v>5.79533004760742</v>
       </c>
       <c r="H215" t="n">
         <v>2318033</v>
@@ -6691,7 +6691,7 @@
         <v>7.60400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>5.88510751724243</v>
+        <v>5.88510799407959</v>
       </c>
       <c r="H218" t="n">
         <v>1267206</v>
@@ -6778,7 +6778,7 @@
         <v>7.63800001144409</v>
       </c>
       <c r="G221" t="n">
-        <v>5.91142129898071</v>
+        <v>5.91142177581787</v>
       </c>
       <c r="H221" t="n">
         <v>957497</v>
@@ -6836,7 +6836,7 @@
         <v>7.57800006866455</v>
       </c>
       <c r="G223" t="n">
-        <v>5.8649845123291</v>
+        <v>5.86498498916626</v>
       </c>
       <c r="H223" t="n">
         <v>1266692</v>
@@ -6865,7 +6865,7 @@
         <v>7.59800004959106</v>
       </c>
       <c r="G224" t="n">
-        <v>5.88046407699585</v>
+        <v>5.88046360015869</v>
       </c>
       <c r="H224" t="n">
         <v>869374</v>
@@ -6952,7 +6952,7 @@
         <v>7.1560001373291</v>
       </c>
       <c r="G227" t="n">
-        <v>5.53837919235229</v>
+        <v>5.53837823867798</v>
       </c>
       <c r="H227" t="n">
         <v>2180122</v>
@@ -6981,7 +6981,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G228" t="n">
-        <v>5.56159639358521</v>
+        <v>5.56159687042236</v>
       </c>
       <c r="H228" t="n">
         <v>1290570</v>
@@ -7126,7 +7126,7 @@
         <v>6.86199998855591</v>
       </c>
       <c r="G233" t="n">
-        <v>5.3108377456665</v>
+        <v>5.31083726882935</v>
       </c>
       <c r="H233" t="n">
         <v>1785974</v>
@@ -7242,7 +7242,7 @@
         <v>6.67199993133545</v>
       </c>
       <c r="G237" t="n">
-        <v>5.16378688812256</v>
+        <v>5.16378736495972</v>
       </c>
       <c r="H237" t="n">
         <v>1786947</v>
@@ -7300,7 +7300,7 @@
         <v>7.01200008392334</v>
       </c>
       <c r="G239" t="n">
-        <v>5.42693042755127</v>
+        <v>5.42692995071411</v>
       </c>
       <c r="H239" t="n">
         <v>2109539</v>
@@ -7329,7 +7329,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G240" t="n">
-        <v>5.49813270568848</v>
+        <v>5.49813318252563</v>
       </c>
       <c r="H240" t="n">
         <v>2318680</v>
@@ -7387,7 +7387,7 @@
         <v>7.10400009155273</v>
       </c>
       <c r="G242" t="n">
-        <v>5.49813270568848</v>
+        <v>5.49813318252563</v>
       </c>
       <c r="H242" t="n">
         <v>1618816</v>
@@ -7474,7 +7474,7 @@
         <v>7.18800020217896</v>
       </c>
       <c r="G245" t="n">
-        <v>5.56314468383789</v>
+        <v>5.56314516067505</v>
       </c>
       <c r="H245" t="n">
         <v>1349255</v>
@@ -7503,7 +7503,7 @@
         <v>7.20599985122681</v>
       </c>
       <c r="G246" t="n">
-        <v>5.57707548141479</v>
+        <v>5.57707643508911</v>
       </c>
       <c r="H246" t="n">
         <v>1630112</v>
@@ -7561,7 +7561,7 @@
         <v>7.10599994659424</v>
       </c>
       <c r="G248" t="n">
-        <v>5.49968099594116</v>
+        <v>5.499680519104</v>
       </c>
       <c r="H248" t="n">
         <v>1099500</v>
@@ -7590,7 +7590,7 @@
         <v>7.08799982070923</v>
       </c>
       <c r="G249" t="n">
-        <v>5.48574924468994</v>
+        <v>5.4857497215271</v>
       </c>
       <c r="H249" t="n">
         <v>1354493</v>
@@ -7619,7 +7619,7 @@
         <v>7.18599987030029</v>
       </c>
       <c r="G250" t="n">
-        <v>5.56159639358521</v>
+        <v>5.56159687042236</v>
       </c>
       <c r="H250" t="n">
         <v>1511622</v>
@@ -7648,7 +7648,7 @@
         <v>7.25600004196167</v>
       </c>
       <c r="G251" t="n">
-        <v>5.61577320098877</v>
+        <v>5.61577367782593</v>
       </c>
       <c r="H251" t="n">
         <v>2061190</v>
@@ -7706,7 +7706,7 @@
         <v>7.19199991226196</v>
       </c>
       <c r="G253" t="n">
-        <v>5.5662407875061</v>
+        <v>5.56624031066895</v>
       </c>
       <c r="H253" t="n">
         <v>1107860</v>
@@ -7735,7 +7735,7 @@
         <v>6.99200010299683</v>
       </c>
       <c r="G254" t="n">
-        <v>5.41145086288452</v>
+        <v>5.41145133972168</v>
       </c>
       <c r="H254" t="n">
         <v>2263864</v>
@@ -7822,7 +7822,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>5.25511360168457</v>
+        <v>5.25511312484741</v>
       </c>
       <c r="H257" t="n">
         <v>2167315</v>
@@ -7851,7 +7851,7 @@
         <v>6.56599998474121</v>
       </c>
       <c r="G258" t="n">
-        <v>5.08174896240234</v>
+        <v>5.08174848556519</v>
       </c>
       <c r="H258" t="n">
         <v>2220756</v>
@@ -7880,7 +7880,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G259" t="n">
-        <v>5.17771863937378</v>
+        <v>5.17771911621094</v>
       </c>
       <c r="H259" t="n">
         <v>1767287</v>
@@ -7938,7 +7938,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G261" t="n">
-        <v>4.73037624359131</v>
+        <v>4.73037576675415</v>
       </c>
       <c r="H261" t="n">
         <v>4291834</v>
@@ -7967,7 +7967,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>4.87587881088257</v>
+        <v>4.87587833404541</v>
       </c>
       <c r="H262" t="n">
         <v>2856462</v>
@@ -7996,7 +7996,7 @@
         <v>6.26200008392334</v>
       </c>
       <c r="G263" t="n">
-        <v>4.84646844863892</v>
+        <v>4.84646797180176</v>
       </c>
       <c r="H263" t="n">
         <v>1904690</v>
@@ -8025,7 +8025,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>4.99197006225586</v>
+        <v>4.99197053909302</v>
       </c>
       <c r="H264" t="n">
         <v>2054662</v>
@@ -8054,7 +8054,7 @@
         <v>6.24200010299683</v>
       </c>
       <c r="G265" t="n">
-        <v>4.83098888397217</v>
+        <v>4.83098936080933</v>
       </c>
       <c r="H265" t="n">
         <v>1949193</v>
@@ -8141,7 +8141,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G268" t="n">
-        <v>4.57094192504883</v>
+        <v>4.57094240188599</v>
       </c>
       <c r="H268" t="n">
         <v>3844094</v>
@@ -8257,7 +8257,7 @@
         <v>6.2480001449585</v>
       </c>
       <c r="G272" t="n">
-        <v>4.83563280105591</v>
+        <v>4.83563327789307</v>
       </c>
       <c r="H272" t="n">
         <v>2873517</v>
@@ -8286,7 +8286,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G273" t="n">
-        <v>4.91457509994507</v>
+        <v>4.91457557678223</v>
       </c>
       <c r="H273" t="n">
         <v>3077722</v>
@@ -8315,7 +8315,7 @@
         <v>6.53800010681152</v>
       </c>
       <c r="G274" t="n">
-        <v>5.06007766723633</v>
+        <v>5.06007814407349</v>
       </c>
       <c r="H274" t="n">
         <v>2925266</v>
@@ -8344,7 +8344,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G275" t="n">
-        <v>5.02602386474609</v>
+        <v>5.02602434158325</v>
       </c>
       <c r="H275" t="n">
         <v>3419765</v>
@@ -8402,7 +8402,7 @@
         <v>6.38399982452393</v>
       </c>
       <c r="G277" t="n">
-        <v>4.94088935852051</v>
+        <v>4.94088983535767</v>
       </c>
       <c r="H277" t="n">
         <v>2480733</v>
@@ -8489,7 +8489,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G280" t="n">
-        <v>5.0151891708374</v>
+        <v>5.01518964767456</v>
       </c>
       <c r="H280" t="n">
         <v>1181822</v>
@@ -8547,7 +8547,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G282" t="n">
-        <v>4.79074382781982</v>
+        <v>4.79074478149414</v>
       </c>
       <c r="H282" t="n">
         <v>1581746</v>
@@ -8605,7 +8605,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G284" t="n">
-        <v>4.63440608978271</v>
+        <v>4.63440656661987</v>
       </c>
       <c r="H284" t="n">
         <v>2793354</v>
@@ -8692,7 +8692,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G287" t="n">
-        <v>4.80467462539673</v>
+        <v>4.80467557907104</v>
       </c>
       <c r="H287" t="n">
         <v>1577631</v>
@@ -8721,7 +8721,7 @@
         <v>6.29199981689453</v>
       </c>
       <c r="G288" t="n">
-        <v>4.86968660354614</v>
+        <v>4.86968612670898</v>
       </c>
       <c r="H288" t="n">
         <v>1424566</v>
@@ -8779,7 +8779,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G290" t="n">
-        <v>4.93005466461182</v>
+        <v>4.93005418777466</v>
       </c>
       <c r="H290" t="n">
         <v>1189099</v>
@@ -8837,7 +8837,7 @@
         <v>6.42399978637695</v>
       </c>
       <c r="G292" t="n">
-        <v>4.97184753417969</v>
+        <v>4.97184801101685</v>
       </c>
       <c r="H292" t="n">
         <v>854708</v>
@@ -8866,7 +8866,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G293" t="n">
-        <v>5.02602386474609</v>
+        <v>5.02602434158325</v>
       </c>
       <c r="H293" t="n">
         <v>2085690</v>
@@ -8895,7 +8895,7 @@
         <v>6.40799999237061</v>
       </c>
       <c r="G294" t="n">
-        <v>4.95946455001831</v>
+        <v>4.95946502685547</v>
       </c>
       <c r="H294" t="n">
         <v>1622501</v>
@@ -8982,7 +8982,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G297" t="n">
-        <v>4.80467462539673</v>
+        <v>4.80467557907104</v>
       </c>
       <c r="H297" t="n">
         <v>2974670</v>
@@ -9011,7 +9011,7 @@
         <v>6.43400001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>4.97958707809448</v>
+        <v>4.9795880317688</v>
       </c>
       <c r="H298" t="n">
         <v>2398005</v>
@@ -9040,7 +9040,7 @@
         <v>6.22599983215332</v>
       </c>
       <c r="G299" t="n">
-        <v>4.81860637664795</v>
+        <v>4.81860589981079</v>
       </c>
       <c r="H299" t="n">
         <v>1316365</v>
@@ -9069,7 +9069,7 @@
         <v>6.20599985122681</v>
       </c>
       <c r="G300" t="n">
-        <v>4.80312633514404</v>
+        <v>4.80312728881836</v>
       </c>
       <c r="H300" t="n">
         <v>1098983</v>
@@ -9098,7 +9098,7 @@
         <v>6.00400018692017</v>
       </c>
       <c r="G301" t="n">
-        <v>4.64678907394409</v>
+        <v>4.64678955078125</v>
       </c>
       <c r="H301" t="n">
         <v>2292669</v>
@@ -9243,7 +9243,7 @@
         <v>6.00799989700317</v>
       </c>
       <c r="G306" t="n">
-        <v>4.6498851776123</v>
+        <v>4.64988565444946</v>
       </c>
       <c r="H306" t="n">
         <v>2121220</v>
@@ -9272,7 +9272,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>4.52760076522827</v>
+        <v>4.52760124206543</v>
       </c>
       <c r="H307" t="n">
         <v>1240333</v>
@@ -9301,7 +9301,7 @@
         <v>5.72599983215332</v>
       </c>
       <c r="G308" t="n">
-        <v>4.43163108825684</v>
+        <v>4.43163156509399</v>
       </c>
       <c r="H308" t="n">
         <v>1935193</v>
@@ -9330,7 +9330,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G309" t="n">
-        <v>4.38674306869507</v>
+        <v>4.38674211502075</v>
       </c>
       <c r="H309" t="n">
         <v>2277365</v>
@@ -9504,7 +9504,7 @@
         <v>5.55399990081787</v>
       </c>
       <c r="G315" t="n">
-        <v>4.29851245880127</v>
+        <v>4.29851293563843</v>
       </c>
       <c r="H315" t="n">
         <v>1066440</v>
@@ -9533,7 +9533,7 @@
         <v>5.44600009918213</v>
       </c>
       <c r="G316" t="n">
-        <v>4.21492576599121</v>
+        <v>4.21492624282837</v>
       </c>
       <c r="H316" t="n">
         <v>1823690</v>
@@ -9562,7 +9562,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G317" t="n">
-        <v>4.40531730651855</v>
+        <v>4.4053168296814</v>
       </c>
       <c r="H317" t="n">
         <v>1289113</v>
@@ -9591,7 +9591,7 @@
         <v>5.63800001144409</v>
       </c>
       <c r="G318" t="n">
-        <v>4.36352396011353</v>
+        <v>4.36352443695068</v>
       </c>
       <c r="H318" t="n">
         <v>2183353</v>
@@ -9620,7 +9620,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G319" t="n">
-        <v>4.48116445541382</v>
+        <v>4.48116397857666</v>
       </c>
       <c r="H319" t="n">
         <v>2117640</v>
@@ -9649,7 +9649,7 @@
         <v>5.96600008010864</v>
       </c>
       <c r="G320" t="n">
-        <v>4.61737966537476</v>
+        <v>4.6173791885376</v>
       </c>
       <c r="H320" t="n">
         <v>2084581</v>
@@ -9707,7 +9707,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G322" t="n">
-        <v>4.69013071060181</v>
+        <v>4.69013023376465</v>
       </c>
       <c r="H322" t="n">
         <v>2666205</v>
@@ -9736,7 +9736,7 @@
         <v>6.0460000038147</v>
       </c>
       <c r="G323" t="n">
-        <v>4.67929458618164</v>
+        <v>4.6792950630188</v>
       </c>
       <c r="H323" t="n">
         <v>1558020</v>
@@ -9765,7 +9765,7 @@
         <v>6.06199979782104</v>
       </c>
       <c r="G324" t="n">
-        <v>4.69167804718018</v>
+        <v>4.69167852401733</v>
       </c>
       <c r="H324" t="n">
         <v>2672651</v>
@@ -9852,7 +9852,7 @@
         <v>6.05200004577637</v>
       </c>
       <c r="G327" t="n">
-        <v>4.68393898010254</v>
+        <v>4.68393850326538</v>
       </c>
       <c r="H327" t="n">
         <v>1956207</v>
@@ -9881,7 +9881,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>4.72108888626099</v>
+        <v>4.72108793258667</v>
       </c>
       <c r="H328" t="n">
         <v>654265</v>
@@ -9910,7 +9910,7 @@
         <v>6.02799987792969</v>
       </c>
       <c r="G329" t="n">
-        <v>4.66536331176758</v>
+        <v>4.66536378860474</v>
       </c>
       <c r="H329" t="n">
         <v>1011597</v>
@@ -9939,7 +9939,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G330" t="n">
-        <v>4.63440608978271</v>
+        <v>4.63440656661987</v>
       </c>
       <c r="H330" t="n">
         <v>914177</v>
@@ -10026,7 +10026,7 @@
         <v>5.94799995422363</v>
       </c>
       <c r="G333" t="n">
-        <v>4.60344791412354</v>
+        <v>4.60344839096069</v>
       </c>
       <c r="H333" t="n">
         <v>1981272</v>
@@ -10171,7 +10171,7 @@
         <v>5.77600002288818</v>
       </c>
       <c r="G338" t="n">
-        <v>4.47032880783081</v>
+        <v>4.47032928466797</v>
       </c>
       <c r="H338" t="n">
         <v>1791028</v>
@@ -10200,7 +10200,7 @@
         <v>5.98199987411499</v>
       </c>
       <c r="G339" t="n">
-        <v>4.62976312637329</v>
+        <v>4.62976264953613</v>
       </c>
       <c r="H339" t="n">
         <v>2743128</v>
@@ -10258,7 +10258,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G341" t="n">
-        <v>4.49199962615967</v>
+        <v>4.49199914932251</v>
       </c>
       <c r="H341" t="n">
         <v>3253843</v>
@@ -10316,7 +10316,7 @@
         <v>5.71799993515015</v>
       </c>
       <c r="G343" t="n">
-        <v>4.42543935775757</v>
+        <v>4.42544031143188</v>
       </c>
       <c r="H343" t="n">
         <v>1859747</v>
@@ -10345,7 +10345,7 @@
         <v>6.06799983978271</v>
       </c>
       <c r="G344" t="n">
-        <v>4.69632244110107</v>
+        <v>4.69632148742676</v>
       </c>
       <c r="H344" t="n">
         <v>4045783</v>
@@ -10432,7 +10432,7 @@
         <v>6.07399988174438</v>
       </c>
       <c r="G347" t="n">
-        <v>4.7009654045105</v>
+        <v>4.70096588134766</v>
       </c>
       <c r="H347" t="n">
         <v>3636485</v>
@@ -10461,7 +10461,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G348" t="n">
-        <v>4.65452861785889</v>
+        <v>4.65452909469604</v>
       </c>
       <c r="H348" t="n">
         <v>1808439</v>
@@ -10548,7 +10548,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G351" t="n">
-        <v>4.72108888626099</v>
+        <v>4.72108793258667</v>
       </c>
       <c r="H351" t="n">
         <v>1185777</v>
@@ -10577,7 +10577,7 @@
         <v>6.01200008392334</v>
       </c>
       <c r="G352" t="n">
-        <v>4.65298080444336</v>
+        <v>4.65298128128052</v>
       </c>
       <c r="H352" t="n">
         <v>1049220</v>
@@ -10693,7 +10693,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G356" t="n">
-        <v>4.5662989616394</v>
+        <v>4.56629848480225</v>
       </c>
       <c r="H356" t="n">
         <v>3354155</v>
@@ -10722,7 +10722,7 @@
         <v>6.07600021362305</v>
       </c>
       <c r="G357" t="n">
-        <v>4.70251417160034</v>
+        <v>4.70251369476318</v>
       </c>
       <c r="H357" t="n">
         <v>3568457</v>
@@ -10780,7 +10780,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>4.72108888626099</v>
+        <v>4.72108793258667</v>
       </c>
       <c r="H359" t="n">
         <v>1704799</v>
@@ -10809,7 +10809,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G360" t="n">
-        <v>4.67465162277222</v>
+        <v>4.6746506690979</v>
       </c>
       <c r="H360" t="n">
         <v>1624225</v>
@@ -10867,7 +10867,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G362" t="n">
-        <v>4.54772329330444</v>
+        <v>4.5477237701416</v>
       </c>
       <c r="H362" t="n">
         <v>1919771</v>
@@ -10896,7 +10896,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G363" t="n">
-        <v>4.49509525299072</v>
+        <v>4.49509477615356</v>
       </c>
       <c r="H363" t="n">
         <v>3344560</v>
@@ -10925,7 +10925,7 @@
         <v>5.76800012588501</v>
       </c>
       <c r="G364" t="n">
-        <v>4.46413803100586</v>
+        <v>4.4641375541687</v>
       </c>
       <c r="H364" t="n">
         <v>3500087</v>
@@ -10954,7 +10954,7 @@
         <v>5.80600023269653</v>
       </c>
       <c r="G365" t="n">
-        <v>4.4935474395752</v>
+        <v>4.49354791641235</v>
       </c>
       <c r="H365" t="n">
         <v>2427346</v>
@@ -10983,7 +10983,7 @@
         <v>5.83799982070923</v>
       </c>
       <c r="G366" t="n">
-        <v>4.51831436157227</v>
+        <v>4.51831340789795</v>
       </c>
       <c r="H366" t="n">
         <v>2273085</v>
@@ -11041,7 +11041,7 @@
         <v>5.97200012207031</v>
       </c>
       <c r="G368" t="n">
-        <v>4.62202310562134</v>
+        <v>4.62202262878418</v>
       </c>
       <c r="H368" t="n">
         <v>1871770</v>
@@ -11070,7 +11070,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G369" t="n">
-        <v>4.67000818252563</v>
+        <v>4.67000722885132</v>
       </c>
       <c r="H369" t="n">
         <v>2627829</v>
@@ -11099,7 +11099,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G370" t="n">
-        <v>4.67000818252563</v>
+        <v>4.67000722885132</v>
       </c>
       <c r="H370" t="n">
         <v>1424349</v>
@@ -11128,7 +11128,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G371" t="n">
-        <v>4.68548631668091</v>
+        <v>4.68548679351807</v>
       </c>
       <c r="H371" t="n">
         <v>1948144</v>
@@ -11215,7 +11215,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G374" t="n">
-        <v>4.53069686889648</v>
+        <v>4.53069734573364</v>
       </c>
       <c r="H374" t="n">
         <v>1872965</v>
@@ -11302,7 +11302,7 @@
         <v>5.73799991607666</v>
       </c>
       <c r="G377" t="n">
-        <v>4.44091892242432</v>
+        <v>4.44091939926147</v>
       </c>
       <c r="H377" t="n">
         <v>2321157</v>
@@ -11331,7 +11331,7 @@
         <v>5.82800006866455</v>
       </c>
       <c r="G378" t="n">
-        <v>4.51057434082031</v>
+        <v>4.51057386398315</v>
       </c>
       <c r="H378" t="n">
         <v>3033773</v>
@@ -11418,7 +11418,7 @@
         <v>6.24599981307983</v>
       </c>
       <c r="G381" t="n">
-        <v>4.83408498764038</v>
+        <v>4.83408451080322</v>
       </c>
       <c r="H381" t="n">
         <v>2344904</v>
@@ -11505,7 +11505,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>4.79074382781982</v>
+        <v>4.79074478149414</v>
       </c>
       <c r="H384" t="n">
         <v>1694409</v>
@@ -11534,7 +11534,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G385" t="n">
-        <v>4.84492015838623</v>
+        <v>4.84492063522339</v>
       </c>
       <c r="H385" t="n">
         <v>1864595</v>
@@ -11563,7 +11563,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G386" t="n">
-        <v>4.91612339019775</v>
+        <v>4.91612386703491</v>
       </c>
       <c r="H386" t="n">
         <v>2103203</v>
@@ -11592,7 +11592,7 @@
         <v>6.60200023651123</v>
       </c>
       <c r="G387" t="n">
-        <v>5.10961151123047</v>
+        <v>5.10961055755615</v>
       </c>
       <c r="H387" t="n">
         <v>3211150</v>
@@ -11650,7 +11650,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G389" t="n">
-        <v>5.02757263183594</v>
+        <v>5.02757215499878</v>
       </c>
       <c r="H389" t="n">
         <v>1436659</v>
@@ -11679,7 +11679,7 @@
         <v>6.5</v>
       </c>
       <c r="G390" t="n">
-        <v>5.03066778182983</v>
+        <v>5.03066873550415</v>
       </c>
       <c r="H390" t="n">
         <v>1844285</v>
@@ -11766,7 +11766,7 @@
         <v>6.44199991226196</v>
       </c>
       <c r="G393" t="n">
-        <v>4.98577928543091</v>
+        <v>4.98577880859375</v>
       </c>
       <c r="H393" t="n">
         <v>2979080</v>
@@ -11824,7 +11824,7 @@
         <v>6.49399995803833</v>
       </c>
       <c r="G395" t="n">
-        <v>5.02602386474609</v>
+        <v>5.02602434158325</v>
       </c>
       <c r="H395" t="n">
         <v>1755876</v>
@@ -11853,7 +11853,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G396" t="n">
-        <v>4.99970960617065</v>
+        <v>4.99971008300781</v>
       </c>
       <c r="H396" t="n">
         <v>1301218</v>
@@ -11882,7 +11882,7 @@
         <v>6.50799989700317</v>
       </c>
       <c r="G397" t="n">
-        <v>5.0368595123291</v>
+        <v>5.03685903549194</v>
       </c>
       <c r="H397" t="n">
         <v>2084969</v>
@@ -11911,7 +11911,7 @@
         <v>6.30600023269653</v>
       </c>
       <c r="G398" t="n">
-        <v>4.88052177429199</v>
+        <v>4.88052225112915</v>
       </c>
       <c r="H398" t="n">
         <v>1489174</v>
@@ -11940,7 +11940,7 @@
         <v>6.17799997329712</v>
       </c>
       <c r="G399" t="n">
-        <v>4.7814564704895</v>
+        <v>4.78145599365234</v>
       </c>
       <c r="H399" t="n">
         <v>2777477</v>
@@ -12027,7 +12027,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>4.5662989616394</v>
+        <v>4.56629848480225</v>
       </c>
       <c r="H402" t="n">
         <v>2088683</v>
@@ -12056,7 +12056,7 @@
         <v>5.77799987792969</v>
       </c>
       <c r="G403" t="n">
-        <v>4.4718770980835</v>
+        <v>4.47187614440918</v>
       </c>
       <c r="H403" t="n">
         <v>3719246</v>
@@ -12085,7 +12085,7 @@
         <v>5.72800016403198</v>
       </c>
       <c r="G404" t="n">
-        <v>4.43317937850952</v>
+        <v>4.43317985534668</v>
       </c>
       <c r="H404" t="n">
         <v>2771135</v>
@@ -12143,7 +12143,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G406" t="n">
-        <v>4.40376901626587</v>
+        <v>4.40376996994019</v>
       </c>
       <c r="H406" t="n">
         <v>2618707</v>
@@ -12172,7 +12172,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G407" t="n">
-        <v>4.53069686889648</v>
+        <v>4.53069734573364</v>
       </c>
       <c r="H407" t="n">
         <v>6401824</v>
@@ -12230,7 +12230,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G409" t="n">
-        <v>4.48271131515503</v>
+        <v>4.48271179199219</v>
       </c>
       <c r="H409" t="n">
         <v>2991538</v>
@@ -12317,7 +12317,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G412" t="n">
-        <v>4.36695146560669</v>
+        <v>4.36695194244385</v>
       </c>
       <c r="H412" t="n">
         <v>1777324</v>
@@ -12346,7 +12346,7 @@
         <v>5.34800004959106</v>
       </c>
       <c r="G413" t="n">
-        <v>4.26955366134644</v>
+        <v>4.26955413818359</v>
       </c>
       <c r="H413" t="n">
         <v>2649682</v>
@@ -12375,7 +12375,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G414" t="n">
-        <v>4.25039339065552</v>
+        <v>4.25039291381836</v>
       </c>
       <c r="H414" t="n">
         <v>1953616</v>
@@ -12404,7 +12404,7 @@
         <v>5.23400020599365</v>
       </c>
       <c r="G415" t="n">
-        <v>4.17854261398315</v>
+        <v>4.17854309082031</v>
       </c>
       <c r="H415" t="n">
         <v>1839026</v>
@@ -12433,7 +12433,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G416" t="n">
-        <v>4.14660787582397</v>
+        <v>4.14660835266113</v>
       </c>
       <c r="H416" t="n">
         <v>3138975</v>
@@ -12462,7 +12462,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G417" t="n">
-        <v>4.07635450363159</v>
+        <v>4.07635402679443</v>
       </c>
       <c r="H417" t="n">
         <v>2466397</v>
@@ -12491,7 +12491,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G418" t="n">
-        <v>4.1434154510498</v>
+        <v>4.14341449737549</v>
       </c>
       <c r="H418" t="n">
         <v>2326150</v>
@@ -12520,7 +12520,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G419" t="n">
-        <v>4.07635450363159</v>
+        <v>4.07635402679443</v>
       </c>
       <c r="H419" t="n">
         <v>3191803</v>
@@ -12549,7 +12549,7 @@
         <v>5.11199998855591</v>
       </c>
       <c r="G420" t="n">
-        <v>4.08114433288574</v>
+        <v>4.08114385604858</v>
       </c>
       <c r="H420" t="n">
         <v>2549135</v>
@@ -12578,7 +12578,7 @@
         <v>5.25600004196167</v>
       </c>
       <c r="G421" t="n">
-        <v>4.19610643386841</v>
+        <v>4.19610595703125</v>
       </c>
       <c r="H421" t="n">
         <v>3174708</v>
@@ -12665,7 +12665,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G424" t="n">
-        <v>4.1434154510498</v>
+        <v>4.14341449737549</v>
       </c>
       <c r="H424" t="n">
         <v>1701343</v>
@@ -12723,7 +12723,7 @@
         <v>5.32800006866455</v>
       </c>
       <c r="G426" t="n">
-        <v>4.25358772277832</v>
+        <v>4.253586769104</v>
       </c>
       <c r="H426" t="n">
         <v>1782929</v>
@@ -12752,7 +12752,7 @@
         <v>5.17600011825562</v>
       </c>
       <c r="G427" t="n">
-        <v>4.13223838806152</v>
+        <v>4.13223886489868</v>
       </c>
       <c r="H427" t="n">
         <v>2230171</v>
@@ -12781,7 +12781,7 @@
         <v>5.25</v>
       </c>
       <c r="G428" t="n">
-        <v>4.19131565093994</v>
+        <v>4.1913161277771</v>
       </c>
       <c r="H428" t="n">
         <v>1872527</v>
@@ -12810,7 +12810,7 @@
         <v>5.29199981689453</v>
       </c>
       <c r="G429" t="n">
-        <v>4.22484636306763</v>
+        <v>4.22484683990479</v>
       </c>
       <c r="H429" t="n">
         <v>2364383</v>
@@ -12839,7 +12839,7 @@
         <v>5.2519998550415</v>
       </c>
       <c r="G430" t="n">
-        <v>4.19291305541992</v>
+        <v>4.19291257858276</v>
       </c>
       <c r="H430" t="n">
         <v>1071567</v>
@@ -12955,7 +12955,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G434" t="n">
-        <v>4.39249897003174</v>
+        <v>4.3924994468689</v>
       </c>
       <c r="H434" t="n">
         <v>5746006</v>
@@ -13013,7 +13013,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G436" t="n">
-        <v>4.29829454421997</v>
+        <v>4.29829359054565</v>
       </c>
       <c r="H436" t="n">
         <v>1263878</v>
@@ -13071,7 +13071,7 @@
         <v>5.19600009918213</v>
       </c>
       <c r="G438" t="n">
-        <v>4.14820528030396</v>
+        <v>4.14820575714111</v>
       </c>
       <c r="H438" t="n">
         <v>3674172</v>
@@ -13100,7 +13100,7 @@
         <v>5.19799995422363</v>
       </c>
       <c r="G439" t="n">
-        <v>4.14980173110962</v>
+        <v>4.14980220794678</v>
       </c>
       <c r="H439" t="n">
         <v>3592521</v>
@@ -13129,7 +13129,7 @@
         <v>5.30600023269653</v>
       </c>
       <c r="G440" t="n">
-        <v>4.23602390289307</v>
+        <v>4.23602294921875</v>
       </c>
       <c r="H440" t="n">
         <v>3874778</v>
@@ -13187,7 +13187,7 @@
         <v>5.25</v>
       </c>
       <c r="G442" t="n">
-        <v>4.19131565093994</v>
+        <v>4.1913161277771</v>
       </c>
       <c r="H442" t="n">
         <v>2076406</v>
@@ -13303,7 +13303,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G446" t="n">
-        <v>4.25039339065552</v>
+        <v>4.25039291381836</v>
       </c>
       <c r="H446" t="n">
         <v>4262357</v>
@@ -13332,7 +13332,7 @@
         <v>5.39400005340576</v>
       </c>
       <c r="G447" t="n">
-        <v>4.30627822875977</v>
+        <v>4.30627775192261</v>
       </c>
       <c r="H447" t="n">
         <v>2978127</v>
@@ -13419,7 +13419,7 @@
         <v>5.69600009918213</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54737901687622</v>
+        <v>4.54737854003906</v>
       </c>
       <c r="H450" t="n">
         <v>4693010</v>
@@ -13448,7 +13448,7 @@
         <v>5.55399990081787</v>
       </c>
       <c r="G451" t="n">
-        <v>4.43401336669922</v>
+        <v>4.43401384353638</v>
       </c>
       <c r="H451" t="n">
         <v>4935845</v>
@@ -13622,7 +13622,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G457" t="n">
-        <v>4.63359975814819</v>
+        <v>4.63359928131104</v>
       </c>
       <c r="H457" t="n">
         <v>7038921</v>
@@ -13651,7 +13651,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G458" t="n">
-        <v>4.55057191848755</v>
+        <v>4.55057144165039</v>
       </c>
       <c r="H458" t="n">
         <v>5385901</v>
@@ -13825,7 +13825,7 @@
         <v>5.01599979400635</v>
       </c>
       <c r="G464" t="n">
-        <v>4.00450325012207</v>
+        <v>4.00450277328491</v>
       </c>
       <c r="H464" t="n">
         <v>10393285</v>
@@ -13883,7 +13883,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G466" t="n">
-        <v>3.76819252967834</v>
+        <v>3.76819276809692</v>
       </c>
       <c r="H466" t="n">
         <v>4448449</v>
@@ -13970,7 +13970,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>3.70831680297852</v>
+        <v>3.70831656455994</v>
       </c>
       <c r="H469" t="n">
         <v>4777891</v>
@@ -14028,7 +14028,7 @@
         <v>4.75299978256226</v>
       </c>
       <c r="G471" t="n">
-        <v>3.79453802108765</v>
+        <v>3.79453778266907</v>
       </c>
       <c r="H471" t="n">
         <v>4709323</v>
@@ -14057,7 +14057,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G472" t="n">
-        <v>3.64444899559021</v>
+        <v>3.64444947242737</v>
       </c>
       <c r="H472" t="n">
         <v>2861060</v>
@@ -14115,7 +14115,7 @@
         <v>4.60900020599365</v>
       </c>
       <c r="G474" t="n">
-        <v>3.67957663536072</v>
+        <v>3.6795768737793</v>
       </c>
       <c r="H474" t="n">
         <v>2548271</v>
@@ -14173,7 +14173,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G476" t="n">
-        <v>3.74264550209045</v>
+        <v>3.74264574050903</v>
       </c>
       <c r="H476" t="n">
         <v>5137879</v>
@@ -14202,7 +14202,7 @@
         <v>4.81300020217896</v>
       </c>
       <c r="G477" t="n">
-        <v>3.84243941307068</v>
+        <v>3.84243893623352</v>
       </c>
       <c r="H477" t="n">
         <v>2898616</v>
@@ -14231,7 +14231,7 @@
         <v>4.6729998588562</v>
       </c>
       <c r="G478" t="n">
-        <v>3.7306706905365</v>
+        <v>3.73066997528076</v>
       </c>
       <c r="H478" t="n">
         <v>2579458</v>
@@ -14289,7 +14289,7 @@
         <v>4.84700012207031</v>
       </c>
       <c r="G480" t="n">
-        <v>3.86958265304565</v>
+        <v>3.86958289146423</v>
       </c>
       <c r="H480" t="n">
         <v>2567620</v>
@@ -14318,7 +14318,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>3.82407689094543</v>
+        <v>3.82407736778259</v>
       </c>
       <c r="H481" t="n">
         <v>1581513</v>
@@ -14347,7 +14347,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G482" t="n">
-        <v>3.74025011062622</v>
+        <v>3.74025082588196</v>
       </c>
       <c r="H482" t="n">
         <v>5781269</v>
@@ -14376,7 +14376,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>3.77218437194824</v>
+        <v>3.77218413352966</v>
       </c>
       <c r="H483" t="n">
         <v>3715855</v>
@@ -14405,7 +14405,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>3.76020884513855</v>
+        <v>3.76020956039429</v>
       </c>
       <c r="H484" t="n">
         <v>1701361</v>
@@ -14434,7 +14434,7 @@
         <v>4.6729998588562</v>
       </c>
       <c r="G485" t="n">
-        <v>3.7306706905365</v>
+        <v>3.73066997528076</v>
       </c>
       <c r="H485" t="n">
         <v>1812903</v>
@@ -14463,7 +14463,7 @@
         <v>4.97300004959106</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97017359733582</v>
+        <v>3.97017455101013</v>
       </c>
       <c r="H486" t="n">
         <v>6818273</v>
@@ -14550,7 +14550,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G489" t="n">
-        <v>4.27274751663208</v>
+        <v>4.27274703979492</v>
       </c>
       <c r="H489" t="n">
         <v>6002211</v>
@@ -14608,7 +14608,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G491" t="n">
-        <v>4.26316690444946</v>
+        <v>4.26316738128662</v>
       </c>
       <c r="H491" t="n">
         <v>4086248</v>
@@ -14637,7 +14637,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G492" t="n">
-        <v>4.42283630371094</v>
+        <v>4.42283582687378</v>
       </c>
       <c r="H492" t="n">
         <v>5033717</v>
@@ -14666,7 +14666,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G493" t="n">
-        <v>4.51863765716553</v>
+        <v>4.51863813400269</v>
       </c>
       <c r="H493" t="n">
         <v>5379056</v>
@@ -14695,7 +14695,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G494" t="n">
-        <v>4.55057191848755</v>
+        <v>4.55057144165039</v>
       </c>
       <c r="H494" t="n">
         <v>4943046</v>
@@ -14724,7 +14724,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G495" t="n">
-        <v>4.49468755722046</v>
+        <v>4.49468803405762</v>
       </c>
       <c r="H495" t="n">
         <v>4049726</v>
@@ -14753,7 +14753,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G496" t="n">
-        <v>4.52183103561401</v>
+        <v>4.52183151245117</v>
       </c>
       <c r="H496" t="n">
         <v>3180033</v>
@@ -14811,7 +14811,7 @@
         <v>5.66400003433228</v>
       </c>
       <c r="G498" t="n">
-        <v>4.52183103561401</v>
+        <v>4.52183151245117</v>
       </c>
       <c r="H498" t="n">
         <v>3193617</v>
@@ -14956,7 +14956,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>4.42283630371094</v>
+        <v>4.42283582687378</v>
       </c>
       <c r="H503" t="n">
         <v>2428806</v>
@@ -14985,7 +14985,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G504" t="n">
-        <v>4.33342170715332</v>
+        <v>4.33342218399048</v>
       </c>
       <c r="H504" t="n">
         <v>3521555</v>
@@ -15043,7 +15043,7 @@
         <v>5.25</v>
       </c>
       <c r="G506" t="n">
-        <v>4.19131565093994</v>
+        <v>4.1913161277771</v>
       </c>
       <c r="H506" t="n">
         <v>4996046</v>
@@ -15072,7 +15072,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G507" t="n">
-        <v>4.17055892944336</v>
+        <v>4.17055940628052</v>
       </c>
       <c r="H507" t="n">
         <v>2153129</v>
@@ -15101,7 +15101,7 @@
         <v>5.11800003051758</v>
       </c>
       <c r="G508" t="n">
-        <v>4.08593463897705</v>
+        <v>4.08593416213989</v>
       </c>
       <c r="H508" t="n">
         <v>5998340</v>
@@ -15188,7 +15188,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G511" t="n">
-        <v>4.07954788208008</v>
+        <v>4.07954740524292</v>
       </c>
       <c r="H511" t="n">
         <v>2798919</v>
@@ -15217,7 +15217,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G512" t="n">
-        <v>4.25518369674683</v>
+        <v>4.25518321990967</v>
       </c>
       <c r="H512" t="n">
         <v>4570455</v>
@@ -15275,7 +15275,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G514" t="n">
-        <v>4.33342170715332</v>
+        <v>4.33342218399048</v>
       </c>
       <c r="H514" t="n">
         <v>1809786</v>
@@ -15304,7 +15304,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G515" t="n">
-        <v>4.485107421875</v>
+        <v>4.48510694503784</v>
       </c>
       <c r="H515" t="n">
         <v>4177311</v>
@@ -15333,7 +15333,7 @@
         <v>5.69399976730347</v>
       </c>
       <c r="G516" t="n">
-        <v>4.54578113555908</v>
+        <v>4.54578161239624</v>
       </c>
       <c r="H516" t="n">
         <v>2588388</v>
@@ -15362,7 +15362,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G517" t="n">
-        <v>4.43081998825073</v>
+        <v>4.43081951141357</v>
       </c>
       <c r="H517" t="n">
         <v>5183857</v>
@@ -15449,7 +15449,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G520" t="n">
-        <v>4.40048265457153</v>
+        <v>4.40048313140869</v>
       </c>
       <c r="H520" t="n">
         <v>2491770</v>
@@ -15478,7 +15478,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G521" t="n">
-        <v>4.31266498565674</v>
+        <v>4.31266403198242</v>
       </c>
       <c r="H521" t="n">
         <v>4443258</v>
@@ -15768,7 +15768,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.28711748123169</v>
+        <v>4.28711795806885</v>
       </c>
       <c r="H531" t="n">
         <v>2940450</v>
@@ -15884,7 +15884,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G535" t="n">
-        <v>4.41485357284546</v>
+        <v>4.41485261917114</v>
       </c>
       <c r="H535" t="n">
         <v>4053856</v>
@@ -16000,7 +16000,7 @@
         <v>5.27600002288818</v>
       </c>
       <c r="G539" t="n">
-        <v>4.21207284927368</v>
+        <v>4.21207332611084</v>
       </c>
       <c r="H539" t="n">
         <v>3407347</v>
@@ -16058,7 +16058,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>4.1434154510498</v>
+        <v>4.14341449737549</v>
       </c>
       <c r="H541" t="n">
         <v>3194214</v>
@@ -16145,7 +16145,7 @@
         <v>5.27600002288818</v>
       </c>
       <c r="G544" t="n">
-        <v>4.21207284927368</v>
+        <v>4.21207332611084</v>
       </c>
       <c r="H544" t="n">
         <v>2108071</v>
@@ -16174,7 +16174,7 @@
         <v>5.39200019836426</v>
       </c>
       <c r="G545" t="n">
-        <v>4.30468082427979</v>
+        <v>4.30468130111694</v>
       </c>
       <c r="H545" t="n">
         <v>5095042</v>
@@ -16261,7 +16261,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G548" t="n">
-        <v>4.11148118972778</v>
+        <v>4.11148166656494</v>
       </c>
       <c r="H548" t="n">
         <v>3196759</v>
@@ -16319,7 +16319,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G550" t="n">
-        <v>4.03164672851562</v>
+        <v>4.03164720535278</v>
       </c>
       <c r="H550" t="n">
         <v>2770919</v>
@@ -16435,7 +16435,7 @@
     